--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="322">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2324,7 +2324,21 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="447">
+  <dxfs count="449">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5759,7 +5773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y66"/>
+  <dimension ref="A1:AA66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5769,19 +5783,19 @@
     <col min="5" max="5" width="9.42578125" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="11" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="11.28515625" style="133" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="20" width="9.140625" style="133"/>
-    <col min="21" max="21" width="14.140625" style="133" customWidth="1"/>
-    <col min="22" max="22" width="12" style="133" customWidth="1"/>
-    <col min="23" max="23" width="15.85546875" style="133" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="13" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="11.28515625" style="133" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="22" width="9.140625" style="133"/>
+    <col min="23" max="23" width="14.140625" style="133" customWidth="1"/>
+    <col min="24" max="24" width="12" style="133" customWidth="1"/>
+    <col min="25" max="25" width="15.85546875" style="133" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
@@ -5795,15 +5809,21 @@
       <c r="K2" s="256">
         <v>46269</v>
       </c>
-      <c r="L2" s="183"/>
-      <c r="M2" s="184" t="s">
+      <c r="L2" s="256">
+        <v>46272</v>
+      </c>
+      <c r="M2" s="256">
+        <v>46273</v>
+      </c>
+      <c r="N2" s="183"/>
+      <c r="O2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="N2" s="185" t="s">
+      <c r="P2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5835,17 +5855,23 @@
       <c r="K3" s="179" t="s">
         <v>235</v>
       </c>
-      <c r="L3" s="180"/>
-      <c r="M3" s="189"/>
+      <c r="L3" s="179" t="s">
+        <v>234</v>
+      </c>
+      <c r="M3" s="179" t="s">
+        <v>233</v>
+      </c>
       <c r="N3" s="180"/>
-      <c r="U3" s="133" t="s">
+      <c r="O3" s="189"/>
+      <c r="P3" s="180"/>
+      <c r="W3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="V3" s="133">
+      <c r="X3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5877,23 +5903,29 @@
       <c r="K4" s="158">
         <v>-649</v>
       </c>
-      <c r="L4" s="211"/>
-      <c r="M4" s="171">
-        <f t="shared" ref="M4:M30" si="0">SUM(H4:L4)</f>
-        <v>-12411</v>
-      </c>
-      <c r="N4" s="149">
-        <f t="shared" ref="N4:N30" si="1">IFERROR(M4/F4*100,0)/10000000</f>
-        <v>-0.24822</v>
-      </c>
-      <c r="U4" s="133" t="s">
+      <c r="L4" s="158">
+        <v>8090</v>
+      </c>
+      <c r="M4" s="158">
+        <v>5321</v>
+      </c>
+      <c r="N4" s="211"/>
+      <c r="O4" s="171">
+        <f t="shared" ref="O4:O30" si="0">SUM(H4:N4)</f>
+        <v>1000</v>
+      </c>
+      <c r="P4" s="149">
+        <f t="shared" ref="P4:P30" si="1">IFERROR(O4/F4*100,0)/10000000</f>
+        <v>0.02</v>
+      </c>
+      <c r="W4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="V4" s="133">
+      <c r="X4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -5925,17 +5957,23 @@
       <c r="K5" s="147">
         <v>73349</v>
       </c>
-      <c r="L5" s="174"/>
-      <c r="M5" s="171">
+      <c r="L5" s="147">
+        <v>38045</v>
+      </c>
+      <c r="M5" s="147">
+        <v>22400</v>
+      </c>
+      <c r="N5" s="174"/>
+      <c r="O5" s="171">
         <f t="shared" si="0"/>
-        <v>-34831</v>
-      </c>
-      <c r="N5" s="149">
+        <v>25614</v>
+      </c>
+      <c r="P5" s="149">
         <f t="shared" si="1"/>
-        <v>-0.11610333333333335</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>8.5379999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -5967,17 +6005,23 @@
       <c r="K6" s="147">
         <v>0</v>
       </c>
-      <c r="L6" s="174"/>
-      <c r="M6" s="171">
+      <c r="L6" s="147">
+        <v>11900</v>
+      </c>
+      <c r="M6" s="147">
+        <v>0</v>
+      </c>
+      <c r="N6" s="174"/>
+      <c r="O6" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="149">
+        <v>11900</v>
+      </c>
+      <c r="P6" s="149">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.11899999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="141" t="s">
         <v>309</v>
@@ -6007,17 +6051,23 @@
       <c r="K7" s="147">
         <v>37000</v>
       </c>
-      <c r="L7" s="174"/>
-      <c r="M7" s="171">
+      <c r="L7" s="147">
+        <v>31000</v>
+      </c>
+      <c r="M7" s="147">
+        <v>0</v>
+      </c>
+      <c r="N7" s="174"/>
+      <c r="O7" s="171">
         <f t="shared" si="0"/>
-        <v>-7700</v>
-      </c>
-      <c r="N7" s="149">
+        <v>23300</v>
+      </c>
+      <c r="P7" s="149">
         <f t="shared" si="1"/>
-        <v>-7.6999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.23300000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6049,21 +6099,27 @@
       <c r="K8" s="147">
         <v>-46000</v>
       </c>
-      <c r="L8" s="174"/>
-      <c r="M8" s="171">
+      <c r="L8" s="147">
+        <v>-59835</v>
+      </c>
+      <c r="M8" s="147">
+        <v>25445</v>
+      </c>
+      <c r="N8" s="174"/>
+      <c r="O8" s="171">
         <f t="shared" si="0"/>
-        <v>61757</v>
-      </c>
-      <c r="N8" s="149">
+        <v>27367</v>
+      </c>
+      <c r="P8" s="149">
         <f t="shared" si="1"/>
-        <v>0.20585666666666669</v>
-      </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="134">
-        <v>-7168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>9.1223333333333337E-2</v>
+      </c>
+      <c r="R8" s="5"/>
+      <c r="S8" s="134">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6095,21 +6151,27 @@
       <c r="K9" s="147">
         <v>-5025</v>
       </c>
-      <c r="L9" s="174"/>
-      <c r="M9" s="171">
+      <c r="L9" s="147">
+        <v>18806</v>
+      </c>
+      <c r="M9" s="147">
+        <v>-500</v>
+      </c>
+      <c r="N9" s="174"/>
+      <c r="O9" s="171">
         <f t="shared" si="0"/>
-        <v>76523</v>
-      </c>
-      <c r="N9" s="149">
+        <v>94829</v>
+      </c>
+      <c r="P9" s="149">
         <f t="shared" si="1"/>
-        <v>0.51015333333333335</v>
-      </c>
-      <c r="P9" s="134">
-        <v>512493</v>
-      </c>
-      <c r="Q9" s="134"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.63219333333333338</v>
+      </c>
+      <c r="R9" s="134">
+        <v>207187</v>
+      </c>
+      <c r="S9" s="134"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6139,24 +6201,30 @@
       <c r="K10" s="147">
         <v>2000</v>
       </c>
-      <c r="L10" s="174"/>
-      <c r="M10" s="171">
+      <c r="L10" s="147">
+        <v>8920</v>
+      </c>
+      <c r="M10" s="147">
+        <v>2577</v>
+      </c>
+      <c r="N10" s="174"/>
+      <c r="O10" s="171">
         <f t="shared" si="0"/>
-        <v>10274</v>
-      </c>
-      <c r="N10" s="149">
+        <v>21771</v>
+      </c>
+      <c r="P10" s="149">
         <f t="shared" si="1"/>
-        <v>0.17123333333333335</v>
-      </c>
-      <c r="P10" s="134">
-        <v>505325</v>
-      </c>
-      <c r="Q10" s="134">
-        <f>(P10+P9)/10000000*13780</f>
-        <v>1402.5532040000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.36285000000000001</v>
+      </c>
+      <c r="R10" s="134">
+        <v>190388</v>
+      </c>
+      <c r="S10" s="134">
+        <f>(R10+R9)/10000000*13780</f>
+        <v>547.85834999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6188,19 +6256,25 @@
       <c r="K11" s="147">
         <v>27700</v>
       </c>
-      <c r="L11" s="174"/>
-      <c r="M11" s="171">
+      <c r="L11" s="147">
+        <v>59800</v>
+      </c>
+      <c r="M11" s="147">
+        <v>87600</v>
+      </c>
+      <c r="N11" s="174"/>
+      <c r="O11" s="171">
         <f t="shared" si="0"/>
-        <v>-386040</v>
-      </c>
-      <c r="N11" s="149">
+        <v>-238640</v>
+      </c>
+      <c r="P11" s="149">
         <f t="shared" si="1"/>
-        <v>-0.25735999999999998</v>
-      </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.15909333333333334</v>
+      </c>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6232,19 +6306,25 @@
       <c r="K12" s="147">
         <v>0</v>
       </c>
-      <c r="L12" s="174"/>
-      <c r="M12" s="171">
+      <c r="L12" s="147">
+        <v>80</v>
+      </c>
+      <c r="M12" s="147">
+        <v>-7456</v>
+      </c>
+      <c r="N12" s="174"/>
+      <c r="O12" s="171">
         <f t="shared" si="0"/>
-        <v>-112135</v>
-      </c>
-      <c r="N12" s="149">
+        <v>-119511</v>
+      </c>
+      <c r="P12" s="149">
         <f t="shared" si="1"/>
-        <v>-0.18689166666666668</v>
-      </c>
-      <c r="P12" s="134"/>
-      <c r="Q12" s="134"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.199185</v>
+      </c>
+      <c r="R12" s="134"/>
+      <c r="S12" s="134"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6276,19 +6356,25 @@
       <c r="K13" s="147">
         <v>1467</v>
       </c>
-      <c r="L13" s="174"/>
-      <c r="M13" s="171">
+      <c r="L13" s="147">
+        <v>-2290</v>
+      </c>
+      <c r="M13" s="147">
+        <v>365</v>
+      </c>
+      <c r="N13" s="174"/>
+      <c r="O13" s="171">
         <f t="shared" si="0"/>
-        <v>-2640</v>
-      </c>
-      <c r="N13" s="149">
+        <v>-4565</v>
+      </c>
+      <c r="P13" s="149">
         <f t="shared" si="1"/>
-        <v>-2.64E-2</v>
-      </c>
-      <c r="P13" s="134"/>
-      <c r="Q13" s="134"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-4.5650000000000003E-2</v>
+      </c>
+      <c r="R13" s="134"/>
+      <c r="S13" s="134"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6320,19 +6406,25 @@
       <c r="K14" s="147">
         <v>8298</v>
       </c>
-      <c r="L14" s="174"/>
-      <c r="M14" s="171">
+      <c r="L14" s="147">
+        <v>3141</v>
+      </c>
+      <c r="M14" s="147">
+        <v>5219</v>
+      </c>
+      <c r="N14" s="174"/>
+      <c r="O14" s="171">
         <f t="shared" si="0"/>
-        <v>5194</v>
-      </c>
-      <c r="N14" s="149">
+        <v>13554</v>
+      </c>
+      <c r="P14" s="149">
         <f t="shared" si="1"/>
-        <v>2.0775999999999999E-2</v>
-      </c>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>5.4216E-2</v>
+      </c>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6364,29 +6456,35 @@
       <c r="K15" s="147">
         <v>11194</v>
       </c>
-      <c r="L15" s="174"/>
-      <c r="M15" s="171">
+      <c r="L15" s="147">
+        <v>3225</v>
+      </c>
+      <c r="M15" s="147">
+        <v>3927</v>
+      </c>
+      <c r="N15" s="174"/>
+      <c r="O15" s="171">
         <f t="shared" si="0"/>
-        <v>6197</v>
-      </c>
-      <c r="N15" s="149">
+        <v>13349</v>
+      </c>
+      <c r="P15" s="149">
         <f t="shared" si="1"/>
-        <v>2.8168181818181818E-2</v>
-      </c>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="193">
-        <f>Q8-Q10</f>
-        <v>-8570.5532039999998</v>
-      </c>
-      <c r="T15" s="133">
+        <v>6.0677272727272719E-2</v>
+      </c>
+      <c r="R15" s="134"/>
+      <c r="S15" s="193">
+        <f>S8-S10</f>
+        <v>16251.14165</v>
+      </c>
+      <c r="V15" s="133">
         <v>116185</v>
       </c>
-      <c r="V15" s="133">
-        <f>T15+Q15</f>
-        <v>107614.446796</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X15" s="133">
+        <f>V15+S15</f>
+        <v>132436.14165000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6418,17 +6516,23 @@
       <c r="K16" s="147">
         <v>5065</v>
       </c>
-      <c r="L16" s="174"/>
-      <c r="M16" s="171">
+      <c r="L16" s="147">
+        <v>-7918</v>
+      </c>
+      <c r="M16" s="147">
+        <v>6627</v>
+      </c>
+      <c r="N16" s="174"/>
+      <c r="O16" s="171">
         <f t="shared" si="0"/>
-        <v>-1356</v>
-      </c>
-      <c r="N16" s="149">
+        <v>-2647</v>
+      </c>
+      <c r="P16" s="149">
         <f t="shared" si="1"/>
-        <v>-1.3559999999999999E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-2.647E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6460,28 +6564,34 @@
       <c r="K17" s="147">
         <v>0</v>
       </c>
-      <c r="L17" s="174"/>
-      <c r="M17" s="171">
+      <c r="L17" s="147">
+        <v>0</v>
+      </c>
+      <c r="M17" s="147">
+        <v>0</v>
+      </c>
+      <c r="N17" s="174"/>
+      <c r="O17" s="171">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N17" s="149">
+      <c r="P17" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V17" s="133">
+      <c r="X17" s="133">
         <v>4000000</v>
       </c>
-      <c r="W17" s="133">
-        <f>V17*7/100</f>
+      <c r="Y17" s="133">
+        <f>X17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="Y17" s="133">
+      <c r="AA17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6513,21 +6623,27 @@
       <c r="K18" s="147">
         <v>0</v>
       </c>
-      <c r="L18" s="174"/>
-      <c r="M18" s="171">
+      <c r="L18" s="147">
+        <v>-1657</v>
+      </c>
+      <c r="M18" s="147">
+        <v>1600</v>
+      </c>
+      <c r="N18" s="174"/>
+      <c r="O18" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="149">
+        <v>-57</v>
+      </c>
+      <c r="P18" s="149">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="133">
-        <f>W17/12</f>
+        <v>-1.4249999999999999E-4</v>
+      </c>
+      <c r="Y18" s="133">
+        <f>Y17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6559,17 +6675,23 @@
       <c r="K19" s="147">
         <v>7586</v>
       </c>
-      <c r="L19" s="174"/>
-      <c r="M19" s="171">
+      <c r="L19" s="147">
+        <v>40075</v>
+      </c>
+      <c r="M19" s="147">
+        <v>-1738</v>
+      </c>
+      <c r="N19" s="174"/>
+      <c r="O19" s="171">
         <f t="shared" si="0"/>
-        <v>10520</v>
-      </c>
-      <c r="N19" s="149">
+        <v>48857</v>
+      </c>
+      <c r="P19" s="149">
         <f t="shared" si="1"/>
-        <v>7.0133333333333325E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.3257133333333333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6601,17 +6723,23 @@
       <c r="K20" s="147">
         <v>0</v>
       </c>
-      <c r="L20" s="174"/>
-      <c r="M20" s="171">
+      <c r="L20" s="147">
+        <v>1670</v>
+      </c>
+      <c r="M20" s="147">
+        <v>700</v>
+      </c>
+      <c r="N20" s="174"/>
+      <c r="O20" s="171">
         <f t="shared" si="0"/>
-        <v>-2058</v>
-      </c>
-      <c r="N20" s="149">
+        <v>312</v>
+      </c>
+      <c r="P20" s="149">
         <f t="shared" si="1"/>
-        <v>-1.8709090909090908E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+        <v>2.8363636363636364E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -6643,17 +6771,23 @@
       <c r="K21" s="147">
         <v>-8570</v>
       </c>
-      <c r="L21" s="174"/>
-      <c r="M21" s="171">
+      <c r="L21" s="147">
+        <v>4268</v>
+      </c>
+      <c r="M21" s="147">
+        <v>6521</v>
+      </c>
+      <c r="N21" s="174"/>
+      <c r="O21" s="171">
         <f t="shared" si="0"/>
-        <v>-4799</v>
-      </c>
-      <c r="N21" s="149">
+        <v>5990</v>
+      </c>
+      <c r="P21" s="149">
         <f t="shared" si="1"/>
-        <v>-0.19195999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.23960000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -6685,17 +6819,23 @@
       <c r="K22" s="147">
         <v>-1344</v>
       </c>
-      <c r="L22" s="174"/>
-      <c r="M22" s="171">
+      <c r="L22" s="147">
+        <v>-2921</v>
+      </c>
+      <c r="M22" s="147">
+        <v>-3207</v>
+      </c>
+      <c r="N22" s="174"/>
+      <c r="O22" s="171">
         <f t="shared" si="0"/>
-        <v>7135</v>
-      </c>
-      <c r="N22" s="149">
+        <v>1007</v>
+      </c>
+      <c r="P22" s="149">
         <f t="shared" si="1"/>
-        <v>3.5674999999999998E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+        <v>5.0350000000000004E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -6725,17 +6865,23 @@
       <c r="K23" s="147">
         <v>260</v>
       </c>
-      <c r="L23" s="174"/>
-      <c r="M23" s="171">
+      <c r="L23" s="147">
+        <v>80</v>
+      </c>
+      <c r="M23" s="147">
+        <v>0</v>
+      </c>
+      <c r="N23" s="174"/>
+      <c r="O23" s="171">
         <f t="shared" si="0"/>
-        <v>260</v>
-      </c>
-      <c r="N23" s="149">
+        <v>340</v>
+      </c>
+      <c r="P23" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -6767,17 +6913,23 @@
       <c r="K24" s="147">
         <v>8477</v>
       </c>
-      <c r="L24" s="174"/>
-      <c r="M24" s="171">
+      <c r="L24" s="147">
+        <v>6822</v>
+      </c>
+      <c r="M24" s="147">
+        <v>-1500</v>
+      </c>
+      <c r="N24" s="174"/>
+      <c r="O24" s="171">
         <f t="shared" si="0"/>
-        <v>24445</v>
-      </c>
-      <c r="N24" s="149">
+        <v>29767</v>
+      </c>
+      <c r="P24" s="149">
         <f t="shared" si="1"/>
-        <v>0.22222727272727272</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.27060909090909085</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -6809,17 +6961,23 @@
       <c r="K25" s="147">
         <v>-105800</v>
       </c>
-      <c r="L25" s="174"/>
-      <c r="M25" s="171">
+      <c r="L25" s="147">
+        <v>-169700</v>
+      </c>
+      <c r="M25" s="147">
+        <v>-41112</v>
+      </c>
+      <c r="N25" s="174"/>
+      <c r="O25" s="171">
         <f t="shared" si="0"/>
-        <v>-512700</v>
-      </c>
-      <c r="N25" s="149">
+        <v>-723512</v>
+      </c>
+      <c r="P25" s="149">
         <f t="shared" si="1"/>
-        <v>-2.2291304347826091</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-3.1457043478260873</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -6849,17 +7007,23 @@
       <c r="K26" s="147">
         <v>-1640</v>
       </c>
-      <c r="L26" s="174"/>
-      <c r="M26" s="171">
+      <c r="L26" s="147">
+        <v>1580</v>
+      </c>
+      <c r="M26" s="147">
+        <v>1768</v>
+      </c>
+      <c r="N26" s="174"/>
+      <c r="O26" s="171">
         <f t="shared" si="0"/>
-        <v>3420</v>
-      </c>
-      <c r="N26" s="149">
+        <v>6768</v>
+      </c>
+      <c r="P26" s="149">
         <f t="shared" si="1"/>
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.33839999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -6891,17 +7055,23 @@
       <c r="K27" s="147">
         <v>0</v>
       </c>
-      <c r="L27" s="174"/>
-      <c r="M27" s="171">
+      <c r="L27" s="147">
+        <v>7600</v>
+      </c>
+      <c r="M27" s="147">
+        <v>1500</v>
+      </c>
+      <c r="N27" s="174"/>
+      <c r="O27" s="171">
         <f t="shared" si="0"/>
-        <v>39000</v>
-      </c>
-      <c r="N27" s="149">
+        <v>48100</v>
+      </c>
+      <c r="P27" s="149">
         <f t="shared" si="1"/>
-        <v>7.8E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+        <v>9.6199999999999994E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -6933,17 +7103,23 @@
       <c r="K28" s="147">
         <v>-205430</v>
       </c>
-      <c r="L28" s="174"/>
-      <c r="M28" s="171">
+      <c r="L28" s="147">
+        <v>22180</v>
+      </c>
+      <c r="M28" s="147">
+        <v>84000</v>
+      </c>
+      <c r="N28" s="174"/>
+      <c r="O28" s="171">
         <f t="shared" si="0"/>
-        <v>-132675</v>
-      </c>
-      <c r="N28" s="149">
+        <v>-26495</v>
+      </c>
+      <c r="P28" s="149">
         <f t="shared" si="1"/>
-        <v>-0.13267499999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-2.6495000000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -6975,17 +7151,23 @@
       <c r="K29" s="147">
         <v>0</v>
       </c>
-      <c r="L29" s="174"/>
-      <c r="M29" s="171">
+      <c r="L29" s="147">
+        <v>0</v>
+      </c>
+      <c r="M29" s="147">
+        <v>256217</v>
+      </c>
+      <c r="N29" s="174"/>
+      <c r="O29" s="171">
         <f t="shared" si="0"/>
-        <v>-475000</v>
-      </c>
-      <c r="N29" s="149">
+        <v>-218783</v>
+      </c>
+      <c r="P29" s="149">
         <f t="shared" si="1"/>
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-0.43756600000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -7017,17 +7199,23 @@
       <c r="K30" s="147">
         <v>163183</v>
       </c>
-      <c r="L30" s="174"/>
-      <c r="M30" s="171">
+      <c r="L30" s="147">
+        <v>50598</v>
+      </c>
+      <c r="M30" s="147">
+        <v>104979</v>
+      </c>
+      <c r="N30" s="174"/>
+      <c r="O30" s="171">
         <f t="shared" si="0"/>
-        <v>-9724</v>
-      </c>
-      <c r="N30" s="149">
+        <v>145853</v>
+      </c>
+      <c r="P30" s="149">
         <f t="shared" si="1"/>
-        <v>-1.9448E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.29170600000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -7059,17 +7247,23 @@
       <c r="K31" s="147">
         <v>-5269</v>
       </c>
-      <c r="L31" s="174"/>
-      <c r="M31" s="171">
-        <f t="shared" ref="M31:M56" si="2">SUM(H31:L31)</f>
-        <v>-103387</v>
-      </c>
-      <c r="N31" s="149">
-        <f t="shared" ref="N31:N56" si="3">IFERROR(M31/F31*100,0)/10000000</f>
-        <v>-2.0677400000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="L31" s="147">
+        <v>14000</v>
+      </c>
+      <c r="M31" s="147">
+        <v>16250</v>
+      </c>
+      <c r="N31" s="174"/>
+      <c r="O31" s="171">
+        <f t="shared" ref="O31:O56" si="2">SUM(H31:N31)</f>
+        <v>-73137</v>
+      </c>
+      <c r="P31" s="149">
+        <f t="shared" ref="P31:P56" si="3">IFERROR(O31/F31*100,0)/10000000</f>
+        <v>-1.4627399999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -7101,18 +7295,24 @@
       <c r="K32" s="147">
         <v>-9429</v>
       </c>
-      <c r="L32" s="174"/>
-      <c r="M32" s="171">
+      <c r="L32" s="147">
+        <v>-16229</v>
+      </c>
+      <c r="M32" s="147">
+        <v>50168</v>
+      </c>
+      <c r="N32" s="174"/>
+      <c r="O32" s="171">
         <f t="shared" si="2"/>
-        <v>-843</v>
-      </c>
-      <c r="N32" s="149">
+        <v>33096</v>
+      </c>
+      <c r="P32" s="149">
         <f t="shared" si="3"/>
-        <v>-2.1075E-2</v>
-      </c>
-      <c r="Q32" s="134"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.82740000000000002</v>
+      </c>
+      <c r="S32" s="134"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -7144,21 +7344,27 @@
       <c r="K33" s="147">
         <v>0</v>
       </c>
-      <c r="L33" s="174"/>
-      <c r="M33" s="171">
+      <c r="L33" s="147">
+        <v>0</v>
+      </c>
+      <c r="M33" s="147">
+        <v>0</v>
+      </c>
+      <c r="N33" s="174"/>
+      <c r="O33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N33" s="149">
+      <c r="P33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="134">
-        <v>6680</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" s="5"/>
+      <c r="S33" s="134">
+        <v>-28252</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -7190,19 +7396,25 @@
       <c r="K34" s="147">
         <v>0</v>
       </c>
-      <c r="L34" s="174"/>
-      <c r="M34" s="171">
+      <c r="L34" s="147">
+        <v>0</v>
+      </c>
+      <c r="M34" s="147">
+        <v>0</v>
+      </c>
+      <c r="N34" s="174"/>
+      <c r="O34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N34" s="149">
+      <c r="P34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="134"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34" s="5"/>
+      <c r="S34" s="134"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -7234,24 +7446,30 @@
       <c r="K35" s="147">
         <v>-54126</v>
       </c>
-      <c r="L35" s="174"/>
-      <c r="M35" s="171">
+      <c r="L35" s="147">
+        <v>49670</v>
+      </c>
+      <c r="M35" s="147">
+        <v>11813</v>
+      </c>
+      <c r="N35" s="174"/>
+      <c r="O35" s="171">
         <f t="shared" si="2"/>
-        <v>-138378</v>
-      </c>
-      <c r="N35" s="149">
+        <v>-76895</v>
+      </c>
+      <c r="P35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.345945</v>
-      </c>
-      <c r="P35" s="134">
-        <v>198924</v>
-      </c>
-      <c r="Q35" s="134">
-        <f>(P36+P35)/10000000*13780</f>
-        <v>557.61872400000004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-0.19223750000000001</v>
+      </c>
+      <c r="R35" s="134">
+        <v>796796</v>
+      </c>
+      <c r="S35" s="134">
+        <f>(R36+R35)/10000000*13780</f>
+        <v>2157.0371420000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -7283,21 +7501,27 @@
       <c r="K36" s="147">
         <v>3870</v>
       </c>
-      <c r="L36" s="174"/>
-      <c r="M36" s="171">
+      <c r="L36" s="147">
+        <v>-24318</v>
+      </c>
+      <c r="M36" s="147">
+        <v>6866</v>
+      </c>
+      <c r="N36" s="174"/>
+      <c r="O36" s="171">
         <f t="shared" si="2"/>
-        <v>-3547</v>
-      </c>
-      <c r="N36" s="149">
+        <v>-20999</v>
+      </c>
+      <c r="P36" s="149">
         <f t="shared" si="3"/>
-        <v>-3.5470000000000002E-2</v>
-      </c>
-      <c r="P36" s="134">
-        <v>205734</v>
-      </c>
-      <c r="Q36" s="134"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-0.20999000000000001</v>
+      </c>
+      <c r="R36" s="134">
+        <v>768543</v>
+      </c>
+      <c r="S36" s="134"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -7327,22 +7551,28 @@
       <c r="K37" s="147">
         <v>0</v>
       </c>
-      <c r="L37" s="174"/>
-      <c r="M37" s="171">
+      <c r="L37" s="147">
+        <v>0</v>
+      </c>
+      <c r="M37" s="147">
+        <v>0</v>
+      </c>
+      <c r="N37" s="174"/>
+      <c r="O37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N37" s="149">
+      <c r="P37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P37" s="134"/>
-      <c r="Q37" s="134">
-        <f>+Q33-Q35</f>
-        <v>6122.3812760000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R37" s="134"/>
+      <c r="S37" s="134">
+        <f>+S33-S35</f>
+        <v>-30409.037142000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -7374,19 +7604,25 @@
       <c r="K38" s="147">
         <v>-680</v>
       </c>
-      <c r="L38" s="174"/>
-      <c r="M38" s="171">
+      <c r="L38" s="147">
+        <v>12908</v>
+      </c>
+      <c r="M38" s="147">
+        <v>11984</v>
+      </c>
+      <c r="N38" s="174"/>
+      <c r="O38" s="171">
         <f t="shared" si="2"/>
-        <v>-29440</v>
-      </c>
-      <c r="N38" s="149">
+        <v>-4548</v>
+      </c>
+      <c r="P38" s="149">
         <f t="shared" si="3"/>
-        <v>-0.58879999999999999</v>
-      </c>
-      <c r="P38" s="134"/>
-      <c r="Q38" s="134"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-9.0959999999999999E-2</v>
+      </c>
+      <c r="R38" s="134"/>
+      <c r="S38" s="134"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -7418,19 +7654,25 @@
       <c r="K39" s="147">
         <v>0</v>
       </c>
-      <c r="L39" s="174"/>
-      <c r="M39" s="171">
+      <c r="L39" s="147">
+        <v>0</v>
+      </c>
+      <c r="M39" s="147">
+        <v>0</v>
+      </c>
+      <c r="N39" s="174"/>
+      <c r="O39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N39" s="149">
+      <c r="P39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="134"/>
-    </row>
-    <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R39" s="134"/>
+      <c r="S39" s="134"/>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -7462,19 +7704,25 @@
       <c r="K40" s="147">
         <v>-48027</v>
       </c>
-      <c r="L40" s="174"/>
-      <c r="M40" s="171">
+      <c r="L40" s="147">
+        <v>39050</v>
+      </c>
+      <c r="M40" s="147">
+        <v>17728</v>
+      </c>
+      <c r="N40" s="174"/>
+      <c r="O40" s="171">
         <f t="shared" si="2"/>
-        <v>-104433</v>
-      </c>
-      <c r="N40" s="149">
+        <v>-47655</v>
+      </c>
+      <c r="P40" s="149">
         <f t="shared" si="3"/>
-        <v>-0.34810999999999998</v>
-      </c>
-      <c r="P40" s="134"/>
-      <c r="Q40" s="134"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-0.15884999999999999</v>
+      </c>
+      <c r="R40" s="134"/>
+      <c r="S40" s="134"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -7504,18 +7752,24 @@
       <c r="K41" s="147">
         <v>14970</v>
       </c>
-      <c r="L41" s="174"/>
-      <c r="M41" s="171">
+      <c r="L41" s="147">
+        <v>-8091</v>
+      </c>
+      <c r="M41" s="147">
+        <v>-30106</v>
+      </c>
+      <c r="N41" s="174"/>
+      <c r="O41" s="171">
         <f t="shared" si="2"/>
-        <v>35315</v>
-      </c>
-      <c r="N41" s="149">
+        <v>-2882</v>
+      </c>
+      <c r="P41" s="149">
         <f t="shared" si="3"/>
-        <v>3.5314999999999999</v>
-      </c>
-      <c r="P41" s="134"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-0.28820000000000001</v>
+      </c>
+      <c r="R41" s="134"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -7547,17 +7801,23 @@
       <c r="K42" s="147">
         <v>-1908</v>
       </c>
-      <c r="L42" s="174"/>
-      <c r="M42" s="171">
+      <c r="L42" s="147">
+        <v>-4245</v>
+      </c>
+      <c r="M42" s="147">
+        <v>0</v>
+      </c>
+      <c r="N42" s="174"/>
+      <c r="O42" s="171">
         <f t="shared" si="2"/>
-        <v>377</v>
-      </c>
-      <c r="N42" s="149">
+        <v>-3868</v>
+      </c>
+      <c r="P42" s="149">
         <f t="shared" si="3"/>
-        <v>7.5399999999999998E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-7.7359999999999998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -7589,17 +7849,23 @@
       <c r="K43" s="147">
         <v>-34150</v>
       </c>
-      <c r="L43" s="174"/>
-      <c r="M43" s="171">
+      <c r="L43" s="147">
+        <v>15150</v>
+      </c>
+      <c r="M43" s="147">
+        <v>45690</v>
+      </c>
+      <c r="N43" s="174"/>
+      <c r="O43" s="171">
         <f t="shared" si="2"/>
-        <v>-69717</v>
-      </c>
-      <c r="N43" s="149">
+        <v>-8877</v>
+      </c>
+      <c r="P43" s="149">
         <f t="shared" si="3"/>
-        <v>-0.69716999999999996</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-8.8770000000000002E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -7629,17 +7895,23 @@
       <c r="K44" s="147">
         <v>974</v>
       </c>
-      <c r="L44" s="174"/>
-      <c r="M44" s="171">
+      <c r="L44" s="147">
+        <v>1303</v>
+      </c>
+      <c r="M44" s="147">
+        <v>394</v>
+      </c>
+      <c r="N44" s="174"/>
+      <c r="O44" s="171">
         <f t="shared" si="2"/>
-        <v>7454</v>
-      </c>
-      <c r="N44" s="149">
+        <v>9151</v>
+      </c>
+      <c r="P44" s="149">
         <f t="shared" si="3"/>
-        <v>0.74539999999999995</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0.91510000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -7671,17 +7943,23 @@
       <c r="K45" s="147">
         <v>0</v>
       </c>
-      <c r="L45" s="174"/>
-      <c r="M45" s="171">
+      <c r="L45" s="147">
+        <v>0</v>
+      </c>
+      <c r="M45" s="147">
+        <v>0</v>
+      </c>
+      <c r="N45" s="174"/>
+      <c r="O45" s="171">
         <f t="shared" si="2"/>
         <v>-156125</v>
       </c>
-      <c r="N45" s="149">
+      <c r="P45" s="149">
         <f t="shared" si="3"/>
         <v>-0.39031250000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -7713,17 +7991,23 @@
       <c r="K46" s="147">
         <v>8481</v>
       </c>
-      <c r="L46" s="174"/>
-      <c r="M46" s="171">
+      <c r="L46" s="147">
+        <v>0</v>
+      </c>
+      <c r="M46" s="147">
+        <v>-106345</v>
+      </c>
+      <c r="N46" s="174"/>
+      <c r="O46" s="171">
         <f t="shared" si="2"/>
-        <v>39740</v>
-      </c>
-      <c r="N46" s="149">
+        <v>-66605</v>
+      </c>
+      <c r="P46" s="149">
         <f t="shared" si="3"/>
-        <v>9.9349999999999994E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-0.16651250000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -7755,17 +8039,23 @@
       <c r="K47" s="147">
         <v>-16640</v>
       </c>
-      <c r="L47" s="174"/>
-      <c r="M47" s="171">
+      <c r="L47" s="147">
+        <v>-15194</v>
+      </c>
+      <c r="M47" s="147">
+        <v>28061</v>
+      </c>
+      <c r="N47" s="174"/>
+      <c r="O47" s="171">
         <f t="shared" si="2"/>
-        <v>16024</v>
-      </c>
-      <c r="N47" s="149">
+        <v>28891</v>
+      </c>
+      <c r="P47" s="149">
         <f t="shared" si="3"/>
-        <v>5.3413333333333327E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+        <v>9.6303333333333338E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -7795,17 +8085,23 @@
       <c r="K48" s="151">
         <v>86600</v>
       </c>
-      <c r="L48" s="174"/>
-      <c r="M48" s="171">
+      <c r="L48" s="151">
+        <v>44400</v>
+      </c>
+      <c r="M48" s="151">
+        <v>-152025</v>
+      </c>
+      <c r="N48" s="174"/>
+      <c r="O48" s="171">
         <f t="shared" si="2"/>
-        <v>-284900</v>
-      </c>
-      <c r="N48" s="149">
+        <v>-392525</v>
+      </c>
+      <c r="P48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.28489999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.39252500000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -7833,17 +8129,23 @@
       <c r="K49" s="151">
         <v>0</v>
       </c>
-      <c r="L49" s="174"/>
-      <c r="M49" s="171">
+      <c r="L49" s="151">
+        <v>0</v>
+      </c>
+      <c r="M49" s="151">
+        <v>0</v>
+      </c>
+      <c r="N49" s="174"/>
+      <c r="O49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N49" s="149">
+      <c r="P49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -7875,17 +8177,23 @@
       <c r="K50" s="151">
         <v>-10394</v>
       </c>
-      <c r="L50" s="174"/>
-      <c r="M50" s="171">
+      <c r="L50" s="151">
+        <v>-4300</v>
+      </c>
+      <c r="M50" s="151">
+        <v>18690</v>
+      </c>
+      <c r="N50" s="174"/>
+      <c r="O50" s="171">
         <f t="shared" si="2"/>
-        <v>4538</v>
-      </c>
-      <c r="N50" s="149">
+        <v>18928</v>
+      </c>
+      <c r="P50" s="149">
         <f t="shared" si="3"/>
-        <v>9.0759999999999993E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.37856000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -7917,17 +8225,23 @@
       <c r="K51" s="151">
         <v>0</v>
       </c>
-      <c r="L51" s="174"/>
-      <c r="M51" s="171">
+      <c r="L51" s="151">
+        <v>0</v>
+      </c>
+      <c r="M51" s="151">
+        <v>40800</v>
+      </c>
+      <c r="N51" s="174"/>
+      <c r="O51" s="171">
         <f t="shared" si="2"/>
-        <v>-152273</v>
-      </c>
-      <c r="N51" s="149">
+        <v>-111473</v>
+      </c>
+      <c r="P51" s="149">
         <f t="shared" si="3"/>
-        <v>-0.23426615384615385</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.17149692307692307</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -7959,17 +8273,23 @@
       <c r="K52" s="151">
         <v>0</v>
       </c>
-      <c r="L52" s="174"/>
-      <c r="M52" s="171">
+      <c r="L52" s="151">
+        <v>0</v>
+      </c>
+      <c r="M52" s="151">
+        <v>-540</v>
+      </c>
+      <c r="N52" s="174"/>
+      <c r="O52" s="171">
         <f t="shared" si="2"/>
-        <v>-157736</v>
-      </c>
-      <c r="N52" s="149">
+        <v>-158276</v>
+      </c>
+      <c r="P52" s="149">
         <f t="shared" si="3"/>
-        <v>-1.2618879999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-1.266208</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -8001,17 +8321,23 @@
       <c r="K53" s="151">
         <v>0</v>
       </c>
-      <c r="L53" s="174"/>
-      <c r="M53" s="171">
+      <c r="L53" s="151">
+        <v>0</v>
+      </c>
+      <c r="M53" s="151">
+        <v>-30409</v>
+      </c>
+      <c r="N53" s="174"/>
+      <c r="O53" s="171">
         <f t="shared" si="2"/>
-        <v>-106641</v>
-      </c>
-      <c r="N53" s="149">
+        <v>-137050</v>
+      </c>
+      <c r="P53" s="149">
         <f t="shared" si="3"/>
-        <v>-0.35547000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.45683333333333337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -8041,17 +8367,23 @@
       <c r="K54" s="151">
         <v>0</v>
       </c>
-      <c r="L54" s="174"/>
-      <c r="M54" s="171">
+      <c r="L54" s="151">
+        <v>0</v>
+      </c>
+      <c r="M54" s="151">
+        <v>3265</v>
+      </c>
+      <c r="N54" s="174"/>
+      <c r="O54" s="171">
         <f t="shared" si="2"/>
-        <v>8135</v>
-      </c>
-      <c r="N54" s="149">
+        <v>11400</v>
+      </c>
+      <c r="P54" s="149">
         <f t="shared" si="3"/>
-        <v>5.4233333333333328E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -8081,17 +8413,23 @@
       <c r="K55" s="151">
         <v>6100</v>
       </c>
-      <c r="L55" s="174"/>
-      <c r="M55" s="171">
+      <c r="L55" s="151">
+        <v>28900</v>
+      </c>
+      <c r="M55" s="151">
+        <v>14300</v>
+      </c>
+      <c r="N55" s="174"/>
+      <c r="O55" s="171">
         <f t="shared" si="2"/>
-        <v>48246</v>
-      </c>
-      <c r="N55" s="149">
+        <v>91446</v>
+      </c>
+      <c r="P55" s="149">
         <f t="shared" si="3"/>
-        <v>9.6492000000000008E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.182892</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -8117,18 +8455,26 @@
       </c>
       <c r="L56" s="254">
         <f>SUM(L4:L55)</f>
-        <v>0</v>
+        <v>206563</v>
       </c>
       <c r="M56" s="254">
+        <f>SUM(M4:M55)</f>
+        <v>507837</v>
+      </c>
+      <c r="N56" s="254">
+        <f>SUM(N4:N55)</f>
+        <v>0</v>
+      </c>
+      <c r="O56" s="254">
         <f t="shared" si="2"/>
-        <v>-2596935</v>
-      </c>
-      <c r="N56" s="255">
+        <v>-1882535</v>
+      </c>
+      <c r="P56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -8142,9 +8488,11 @@
       <c r="K57" s="250"/>
       <c r="L57" s="250"/>
       <c r="M57" s="250"/>
-      <c r="N57" s="252"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N57" s="250"/>
+      <c r="O57" s="250"/>
+      <c r="P57" s="252"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -8176,18 +8524,24 @@
       <c r="K58" s="162">
         <v>0</v>
       </c>
-      <c r="L58" s="246"/>
-      <c r="M58" s="247">
-        <f>SUM(H58:L58)</f>
-        <v>-387560</v>
-      </c>
-      <c r="N58" s="248">
-        <f>IFERROR(M58/F58*100,0)/10000000</f>
-        <v>-1.2918666666666667</v>
-      </c>
-      <c r="Q58" s="134"/>
-    </row>
-    <row r="59" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L58" s="162">
+        <v>2780</v>
+      </c>
+      <c r="M58" s="162">
+        <v>77900</v>
+      </c>
+      <c r="N58" s="246"/>
+      <c r="O58" s="247">
+        <f>SUM(H58:N58)</f>
+        <v>-306880</v>
+      </c>
+      <c r="P58" s="248">
+        <f>IFERROR(O58/F58*100,0)/10000000</f>
+        <v>-1.0229333333333333</v>
+      </c>
+      <c r="S58" s="134"/>
+    </row>
+    <row r="59" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -8217,18 +8571,24 @@
       <c r="K59" s="162">
         <v>0</v>
       </c>
-      <c r="L59" s="174"/>
-      <c r="M59" s="171">
-        <f>SUM(H59:L59)</f>
-        <v>-246000</v>
-      </c>
-      <c r="N59" s="149">
-        <f>IFERROR(M59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="P59" s="134"/>
-    </row>
-    <row r="60" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L59" s="162">
+        <v>3816</v>
+      </c>
+      <c r="M59" s="162">
+        <v>377300</v>
+      </c>
+      <c r="N59" s="174"/>
+      <c r="O59" s="171">
+        <f>SUM(H59:N59)</f>
+        <v>135116</v>
+      </c>
+      <c r="P59" s="149">
+        <f>IFERROR(O59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="R59" s="134"/>
+    </row>
+    <row r="60" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -8254,130 +8614,138 @@
       </c>
       <c r="L60" s="170">
         <f>SUM(L58:L59)</f>
-        <v>0</v>
-      </c>
-      <c r="M60" s="254">
-        <f>SUM(H60:L60)</f>
-        <v>-633560</v>
-      </c>
-      <c r="N60" s="19"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="134"/>
-      <c r="R60" s="237"/>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P61" s="134"/>
-      <c r="Q61" s="134"/>
-      <c r="R61" s="237"/>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P62" s="134"/>
-      <c r="Q62" s="134"/>
-      <c r="R62" s="237"/>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P63" s="134"/>
-      <c r="Q63" s="134"/>
-      <c r="R63" s="237"/>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="P64" s="134"/>
-      <c r="Q64" s="134"/>
-      <c r="R64" s="237"/>
-    </row>
-    <row r="65" spans="16:18" x14ac:dyDescent="0.25">
-      <c r="P65" s="134"/>
-      <c r="Q65" s="237"/>
-      <c r="R65" s="237"/>
-    </row>
-    <row r="66" spans="16:18" x14ac:dyDescent="0.25">
-      <c r="P66" s="237"/>
-      <c r="Q66" s="237"/>
+        <v>6596</v>
+      </c>
+      <c r="M60" s="170">
+        <f>SUM(M58:M59)</f>
+        <v>455200</v>
+      </c>
+      <c r="N60" s="170">
+        <f>SUM(N58:N59)</f>
+        <v>0</v>
+      </c>
+      <c r="O60" s="254">
+        <f>SUM(H60:N60)</f>
+        <v>-171764</v>
+      </c>
+      <c r="P60" s="19"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="134"/>
+      <c r="T60" s="237"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R61" s="134"/>
+      <c r="S61" s="134"/>
+      <c r="T61" s="237"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R62" s="134"/>
+      <c r="S62" s="134"/>
+      <c r="T62" s="237"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R63" s="134"/>
+      <c r="S63" s="134"/>
+      <c r="T63" s="237"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R64" s="134"/>
+      <c r="S64" s="134"/>
+      <c r="T64" s="237"/>
+    </row>
+    <row r="65" spans="18:20" x14ac:dyDescent="0.25">
+      <c r="R65" s="134"/>
+      <c r="S65" s="237"/>
+      <c r="T65" s="237"/>
+    </row>
+    <row r="66" spans="18:20" x14ac:dyDescent="0.25">
       <c r="R66" s="237"/>
+      <c r="S66" s="237"/>
+      <c r="T66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 N56:N57 M55:N55 N60 M43:N43 M5:N10 M24:N25 H2:N3 A58:N59 A37:M37 N11:N21 M11:M22 M45:N53 M27:M36 N27:N35 A4:L36 M38:M41 A38:L39 G40:L40 A41:L56 A60:L60">
-    <cfRule type="expression" dxfId="446" priority="21">
+  <conditionalFormatting sqref="G2 A3:G3 P56:P57 O55:P55 P60 O43:P43 O5:P10 O24:P25 H2:P3 A58:P59 A37:O37 P11:P21 O11:O22 O45:P53 O27:O36 P27:P35 A4:N36 O38:O41 A38:N39 G40:N40 A41:N56 A60:N60">
+    <cfRule type="expression" dxfId="448" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N36">
-    <cfRule type="expression" dxfId="445" priority="20">
+  <conditionalFormatting sqref="P36">
+    <cfRule type="expression" dxfId="447" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N39:N40">
-    <cfRule type="expression" dxfId="444" priority="19">
+  <conditionalFormatting sqref="P39:P40">
+    <cfRule type="expression" dxfId="446" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="443" priority="18">
+  <conditionalFormatting sqref="O4:P4">
+    <cfRule type="expression" dxfId="445" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N38">
-    <cfRule type="expression" dxfId="442" priority="17">
+  <conditionalFormatting sqref="P38">
+    <cfRule type="expression" dxfId="444" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N22">
-    <cfRule type="expression" dxfId="441" priority="14">
+  <conditionalFormatting sqref="P22">
+    <cfRule type="expression" dxfId="443" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M56">
-    <cfRule type="expression" dxfId="440" priority="13">
+  <conditionalFormatting sqref="O56">
+    <cfRule type="expression" dxfId="442" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N41">
-    <cfRule type="expression" dxfId="439" priority="12">
+  <conditionalFormatting sqref="P41">
+    <cfRule type="expression" dxfId="441" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M26:N26">
-    <cfRule type="expression" dxfId="438" priority="11">
+  <conditionalFormatting sqref="O26:P26">
+    <cfRule type="expression" dxfId="440" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M54:N54">
-    <cfRule type="expression" dxfId="437" priority="10">
+  <conditionalFormatting sqref="O54:P54">
+    <cfRule type="expression" dxfId="439" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44:N44">
-    <cfRule type="expression" dxfId="436" priority="9">
+  <conditionalFormatting sqref="O44:P44">
+    <cfRule type="expression" dxfId="438" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M60">
-    <cfRule type="expression" dxfId="435" priority="8">
+  <conditionalFormatting sqref="O60">
+    <cfRule type="expression" dxfId="437" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M42:N42">
-    <cfRule type="expression" dxfId="434" priority="6">
+  <conditionalFormatting sqref="O42:P42">
+    <cfRule type="expression" dxfId="436" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M23">
-    <cfRule type="expression" dxfId="433" priority="5">
+  <conditionalFormatting sqref="O23">
+    <cfRule type="expression" dxfId="435" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="432" priority="4">
+  <conditionalFormatting sqref="P23">
+    <cfRule type="expression" dxfId="434" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="431" priority="2">
+  <conditionalFormatting sqref="P37">
+    <cfRule type="expression" dxfId="433" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="430" priority="1">
+    <cfRule type="expression" dxfId="432" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8402,9 +8770,10 @@
     <col min="24" max="24" width="11.42578125" style="133" customWidth="1" outlineLevel="1"/>
     <col min="25" max="27" width="11.28515625" style="133" customWidth="1" outlineLevel="1"/>
     <col min="28" max="28" width="11.28515625" style="133" customWidth="1"/>
-    <col min="29" max="29" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="36" width="9.140625" style="133"/>
+    <col min="29" max="29" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="9.140625" style="133" collapsed="1"/>
+    <col min="32" max="36" width="9.140625" style="133"/>
     <col min="37" max="37" width="14.140625" style="133" customWidth="1"/>
     <col min="38" max="38" width="12" style="133" customWidth="1"/>
     <col min="39" max="39" width="15.85546875" style="133" customWidth="1"/>
@@ -14844,112 +15213,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="429" priority="22">
+    <cfRule type="expression" dxfId="431" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="428" priority="21">
+    <cfRule type="expression" dxfId="430" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="427" priority="20">
+    <cfRule type="expression" dxfId="429" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="426" priority="19">
+    <cfRule type="expression" dxfId="428" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="425" priority="18">
+    <cfRule type="expression" dxfId="427" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="424" priority="17">
+    <cfRule type="expression" dxfId="426" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="423" priority="16">
+    <cfRule type="expression" dxfId="425" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="422" priority="15">
+    <cfRule type="expression" dxfId="424" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="421" priority="14">
+    <cfRule type="expression" dxfId="423" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="420" priority="13">
+    <cfRule type="expression" dxfId="422" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="419" priority="12">
+    <cfRule type="expression" dxfId="421" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="418" priority="11">
+    <cfRule type="expression" dxfId="420" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="417" priority="10">
+    <cfRule type="expression" dxfId="419" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="416" priority="9">
+    <cfRule type="expression" dxfId="418" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="415" priority="8">
+    <cfRule type="expression" dxfId="417" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="414" priority="7">
+    <cfRule type="expression" dxfId="416" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="413" priority="6">
+    <cfRule type="expression" dxfId="415" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="412" priority="5">
+    <cfRule type="expression" dxfId="414" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="411" priority="4">
+    <cfRule type="expression" dxfId="413" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="410" priority="3">
+    <cfRule type="expression" dxfId="412" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="409" priority="2">
+    <cfRule type="expression" dxfId="411" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="408" priority="1">
+    <cfRule type="expression" dxfId="410" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21249,82 +21618,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="407" priority="20">
+    <cfRule type="expression" dxfId="409" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="406" priority="19">
+    <cfRule type="expression" dxfId="408" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="405" priority="18">
+    <cfRule type="expression" dxfId="407" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="404" priority="16">
+    <cfRule type="expression" dxfId="406" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="403" priority="14">
+    <cfRule type="expression" dxfId="405" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="402" priority="13">
+    <cfRule type="expression" dxfId="404" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="401" priority="12">
+    <cfRule type="expression" dxfId="403" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="400" priority="11">
+    <cfRule type="expression" dxfId="402" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="399" priority="10">
+    <cfRule type="expression" dxfId="401" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="398" priority="9">
+    <cfRule type="expression" dxfId="400" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="397" priority="6">
+    <cfRule type="expression" dxfId="399" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="396" priority="5">
+    <cfRule type="expression" dxfId="398" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="395" priority="4">
+    <cfRule type="expression" dxfId="397" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="394" priority="3">
+    <cfRule type="expression" dxfId="396" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="393" priority="2">
+    <cfRule type="expression" dxfId="395" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="392" priority="1">
+    <cfRule type="expression" dxfId="394" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21448,20 +21817,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-12411</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>1000</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.24822</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.02</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-39455</v>
+        <v>-26044</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-0.78910000000000002</v>
+        <v>-0.52088000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -21500,20 +21869,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-34831</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>25614</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.11610333333333335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>8.5379999999999998E-2</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-285802</v>
+        <v>-225357</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-0.95267333333333337</v>
+        <v>-0.75119000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -21552,20 +21921,20 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>11900</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M6" s="71">
         <f t="shared" ref="M6:M7" si="1">G6+I6+K6</f>
-        <v>116185</v>
+        <v>128085</v>
       </c>
       <c r="N6" s="166">
         <f t="shared" ref="N6:N7" si="2">H6+J6+L6</f>
-        <v>1.16185</v>
+        <v>1.28085</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -21602,11 +21971,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="71">
@@ -21654,20 +22023,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>61757</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>27367</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0.20585666666666669</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>9.1223333333333337E-2</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-393340</v>
+        <v>-427730</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.3111333333333333</v>
+        <v>-1.4257666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -21706,20 +22075,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>76523</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>94829</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0.51015333333333335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.63219333333333338</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-217613</v>
+        <v>-199307</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4507533333333336</v>
+        <v>-1.3287133333333336</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -21758,20 +22127,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>10274</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>21771</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0.17123333333333335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.36285000000000001</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-181975</v>
+        <v>-170478</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-3.0329166666666669</v>
+        <v>-2.8413000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -21810,20 +22179,20 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-386040</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-238640</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.25735999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.15909333333333334</v>
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>581225</v>
+        <v>728625</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.38748333333333346</v>
+        <v>0.48575000000000013</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -21862,20 +22231,20 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-112135</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-119511</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.18689166666666668</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.199185</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>295645</v>
+        <v>288269</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.49274166666666674</v>
+        <v>0.48044833333333342</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -21914,20 +22283,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-2640</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-4565</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-2.64E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-4.5650000000000003E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>10776</v>
+        <v>8851</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>0.10775999999999999</v>
+        <v>8.8510000000000005E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -21966,20 +22335,20 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>5194</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>13554</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>2.0775999999999999E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>5.4216E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>50114</v>
+        <v>58474</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.20045599999999994</v>
+        <v>0.23389599999999994</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -22018,11 +22387,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -22070,20 +22439,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-1356</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-2647</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-1.3559999999999999E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-2.647E-2</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>72051</v>
+        <v>70760</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.72050999999999998</v>
+        <v>0.70760000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -22122,20 +22491,20 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>6197</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>13349</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>2.8168181818181818E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>6.0677272727272719E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-81711</v>
+        <v>-74559</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.37141363636363633</v>
+        <v>-0.3389045454545454</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -22174,11 +22543,11 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M18" s="71">
@@ -22226,20 +22595,20 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-57</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-1.4249999999999999E-4</v>
       </c>
       <c r="M19" s="71">
         <f t="shared" si="0"/>
-        <v>267315</v>
+        <v>267258</v>
       </c>
       <c r="N19" s="166">
         <f t="shared" si="0"/>
-        <v>0.66828749999999992</v>
+        <v>0.66814499999999988</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -22278,20 +22647,20 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-2058</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>312</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-1.8709090909090908E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>2.8363636363636364E-3</v>
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>85624</v>
+        <v>87994</v>
       </c>
       <c r="N20" s="166">
         <f t="shared" si="0"/>
-        <v>0.77839999999999987</v>
+        <v>0.7999454545454544</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -22330,20 +22699,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-4799</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>5990</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.19195999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.23960000000000001</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-48345</v>
+        <v>-37556</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-1.9337999999999997</v>
+        <v>-1.5022399999999998</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -22382,20 +22751,20 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>7135</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>1007</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>3.5674999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>5.0350000000000004E-3</v>
       </c>
       <c r="M22" s="71">
         <f t="shared" si="7"/>
-        <v>23267</v>
+        <v>17139</v>
       </c>
       <c r="N22" s="166">
         <f t="shared" si="8"/>
-        <v>0.11633499999999999</v>
+        <v>8.5694999999999993E-2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -22434,20 +22803,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>10520</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>48857</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>7.0133333333333325E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.3257133333333333</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>125533</v>
+        <v>163870</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>0.83688666666666678</v>
+        <v>1.0924666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -22486,11 +22855,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -22538,20 +22907,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>24445</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>29767</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0.22222727272727272</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.27060909090909085</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>229149</v>
+        <v>234471</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>2.0831727272727267</v>
+        <v>2.131554545454545</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -22590,20 +22959,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-512700</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-723512</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-2.2291304347826091</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-3.1457043478260873</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-158639</v>
+        <v>-369451</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-0.68973478260869658</v>
+        <v>-1.6063086956521748</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -22640,20 +23009,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>3420</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>6768</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0.17100000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.33839999999999998</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-16876</v>
+        <v>-13528</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.84379999999999988</v>
+        <v>-0.67639999999999989</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -22692,20 +23061,20 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>39000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>48100</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>7.8E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>9.6199999999999994E-2</v>
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>-225918</v>
+        <v>-216818</v>
       </c>
       <c r="N28" s="166">
         <f t="shared" si="0"/>
-        <v>-0.45183599999999996</v>
+        <v>-0.43363599999999997</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -22744,20 +23113,20 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-132675</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-26495</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.13267499999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-2.6495000000000001E-2</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>3334737</v>
+        <v>3440917</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>3.3347370000000001</v>
+        <v>3.4409169999999998</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -22797,11 +23166,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -22849,11 +23218,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -22901,11 +23270,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -22953,11 +23322,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -23005,11 +23374,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -23057,20 +23426,20 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-475000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-218783</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.95</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.43756600000000001</v>
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>224852</v>
+        <v>481069</v>
       </c>
       <c r="N35" s="166">
         <f t="shared" si="0"/>
-        <v>0.44970399999999988</v>
+        <v>0.96213799999999983</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -23109,20 +23478,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-9724</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>145853</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-1.9448E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.29170600000000002</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>1017683</v>
+        <v>1173260</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>2.0353659999999998</v>
+        <v>2.3465199999999999</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -23161,20 +23530,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-103387</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-73137</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-2.0677400000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-1.4627399999999999</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-182751</v>
+        <v>-152501</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-3.6550200000000004</v>
+        <v>-3.05002</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -23213,20 +23582,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-843</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>33096</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-2.1075E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.82740000000000002</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-66368</v>
+        <v>-32429</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6591999999999998</v>
+        <v>-0.81072499999999981</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -23265,11 +23634,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -23317,11 +23686,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -23369,20 +23738,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-138378</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-76895</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.345945</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.19223750000000001</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>572558</v>
+        <v>634041</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.4313950000000002</v>
+        <v>1.5851025000000001</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -23421,20 +23790,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-3547</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-20999</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-3.5470000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.20999000000000001</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>200085</v>
+        <v>182633</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>2.0008499999999998</v>
+        <v>1.82633</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -23471,11 +23840,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -23523,20 +23892,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-29440</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-4548</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.58879999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-9.0959999999999999E-2</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-95823</v>
+        <v>-70931</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.9164599999999998</v>
+        <v>-1.4186199999999998</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -23575,20 +23944,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-104433</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-47655</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.34810999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.15884999999999999</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-215225</v>
+        <v>-158447</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.71741666666666659</v>
+        <v>-0.52815666666666661</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -23627,11 +23996,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -23679,11 +24048,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -23729,20 +24098,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>35315</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-2882</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>3.5314999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.28820000000000001</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>18383</v>
+        <v>-19814</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>1.8382999999999998</v>
+        <v>-1.9814000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -23781,20 +24150,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>377</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-3868</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>7.5399999999999998E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-7.7359999999999998E-2</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>34705</v>
+        <v>30460</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.3735</v>
+        <v>0.28860000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -23833,20 +24202,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-69717</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-8877</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.69716999999999996</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-8.8770000000000002E-2</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>817657</v>
+        <v>878497</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>8.1765699999999999</v>
+        <v>8.7849699999999995</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -23883,20 +24252,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>7454</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>9151</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>0.74539999999999995</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.91510000000000002</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>3908</v>
+        <v>5605</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.39079999999999993</v>
+        <v>0.5605</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -23935,20 +24304,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>16024</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>28891</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>5.3413333333333327E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>9.6303333333333338E-2</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>7291</v>
+        <v>20158</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>2.4303333333333357E-2</v>
+        <v>6.7193333333333369E-2</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -23981,11 +24350,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -24033,11 +24402,11 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>-156125</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>-0.39031250000000001</v>
       </c>
       <c r="M54" s="71">
@@ -24085,20 +24454,20 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>39740</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-66605</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>9.9349999999999994E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.16651250000000001</v>
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>382014</v>
+        <v>275669</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>0.95503499999999986</v>
+        <v>0.68917249999999997</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -24135,20 +24504,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-284900</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-392525</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.28489999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.39252500000000001</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1319980</v>
+        <v>-1427605</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.3200799999999999</v>
+        <v>-1.427705</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -24181,11 +24550,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -24233,20 +24602,20 @@
         <v>-0.14384</v>
       </c>
       <c r="K58" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>4538</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>18928</v>
       </c>
       <c r="L58" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>9.0759999999999993E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.37856000000000001</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-29757</v>
+        <v>-15367</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-0.59514</v>
+        <v>-0.30733999999999995</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -24285,20 +24654,20 @@
         <v>0.10279846153846153</v>
       </c>
       <c r="K59" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-152273</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-111473</v>
       </c>
       <c r="L59" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.23426615384615385</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.17149692307692307</v>
       </c>
       <c r="M59" s="71">
         <f t="shared" si="0"/>
-        <v>791671</v>
+        <v>832471</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" si="0"/>
-        <v>2.0613448076923078</v>
+        <v>2.1241140384615385</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -24337,20 +24706,20 @@
         <v>-0.20608799999999999</v>
       </c>
       <c r="K60" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-157736</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-158276</v>
       </c>
       <c r="L60" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-1.2618879999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-1.266208</v>
       </c>
       <c r="M60" s="71">
         <f t="shared" si="0"/>
-        <v>25522</v>
+        <v>24982</v>
       </c>
       <c r="N60" s="166">
         <f t="shared" si="0"/>
-        <v>0.20417600000000014</v>
+        <v>0.19985600000000003</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -24389,20 +24758,20 @@
         <v>-0.86802666666666684</v>
       </c>
       <c r="K61" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-106641</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-137050</v>
       </c>
       <c r="L61" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-0.35547000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-0.45683333333333337</v>
       </c>
       <c r="M61" s="71">
         <f t="shared" si="0"/>
-        <v>597432</v>
+        <v>567023</v>
       </c>
       <c r="N61" s="166">
         <f t="shared" si="0"/>
-        <v>1.9914400000000003</v>
+        <v>1.8900766666666668</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -24441,11 +24810,11 @@
         <v>-0.31176799999999999</v>
       </c>
       <c r="K62" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L62" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M62" s="71">
@@ -24491,20 +24860,20 @@
         <v>0.55113999999999996</v>
       </c>
       <c r="K63" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>8135</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>11400</v>
       </c>
       <c r="L63" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>5.4233333333333328E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="M63" s="71">
         <f t="shared" ref="M63" si="25">G63+I63+K63</f>
-        <v>88300</v>
+        <v>91565</v>
       </c>
       <c r="N63" s="166">
         <f t="shared" ref="N63" si="26">H63+J63+L63</f>
-        <v>0.50513333333333332</v>
+        <v>0.52689999999999992</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -24541,20 +24910,20 @@
         <v>0.43251600000000001</v>
       </c>
       <c r="K64" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>48246</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>91446</v>
       </c>
       <c r="L64" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>9.6492000000000008E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>0.182892</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>537651</v>
+        <v>580851</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>1.075302</v>
+        <v>1.161702</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -24576,12 +24945,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-2645876</v>
+        <v>-2009021</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>9134161</v>
+        <v>9771016</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -24661,20 +25030,20 @@
         <v>0.2384333333333333</v>
       </c>
       <c r="K69" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-387560</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-306880</v>
       </c>
       <c r="L69" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-1.2918666666666667</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>-1.0229333333333333</v>
       </c>
       <c r="M69" s="153">
         <f t="shared" ref="M69:N69" si="29">G69+I69+K69</f>
-        <v>298950</v>
+        <v>379630</v>
       </c>
       <c r="N69" s="167">
         <f t="shared" si="29"/>
-        <v>0.99650000000000039</v>
+        <v>1.2654333333333339</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -24711,16 +25080,16 @@
         <v>0</v>
       </c>
       <c r="K70" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
-        <v>-246000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <v>135116</v>
       </c>
       <c r="L70" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADO$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DP$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="153">
         <f t="shared" ref="M70" si="30">G70+I70+K70</f>
-        <v>922885</v>
+        <v>1304001</v>
       </c>
       <c r="N70" s="167">
         <f t="shared" ref="N70" si="31">H70+J70+L70</f>
@@ -24740,508 +25109,508 @@
       <c r="J71" s="104"/>
       <c r="K71" s="93">
         <f>SUM(K69:K70)</f>
-        <v>-633560</v>
+        <v>-171764</v>
       </c>
       <c r="L71" s="113"/>
       <c r="M71" s="93">
         <f>SUM(M69:M70)</f>
-        <v>1221835</v>
+        <v>1683631</v>
       </c>
       <c r="N71" s="236"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
-    <cfRule type="expression" dxfId="391" priority="229">
+    <cfRule type="expression" dxfId="393" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="390" priority="228">
+    <cfRule type="expression" dxfId="392" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="389" priority="227">
+    <cfRule type="expression" dxfId="391" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="388" priority="226">
+    <cfRule type="expression" dxfId="390" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="387" priority="222">
+    <cfRule type="expression" dxfId="389" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="386" priority="220">
+    <cfRule type="expression" dxfId="388" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="385" priority="218">
+    <cfRule type="expression" dxfId="387" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="384" priority="212">
+    <cfRule type="expression" dxfId="386" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="383" priority="202">
+    <cfRule type="expression" dxfId="385" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="382" priority="207">
+    <cfRule type="expression" dxfId="384" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="381" priority="203">
+    <cfRule type="expression" dxfId="383" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="380" priority="188">
+    <cfRule type="expression" dxfId="382" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="379" priority="183">
+    <cfRule type="expression" dxfId="381" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="378" priority="189">
+    <cfRule type="expression" dxfId="380" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="377" priority="174">
+    <cfRule type="expression" dxfId="379" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="376" priority="172">
+    <cfRule type="expression" dxfId="378" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="375" priority="171">
+    <cfRule type="expression" dxfId="377" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="374" priority="166">
+    <cfRule type="expression" dxfId="376" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="373" priority="162">
+    <cfRule type="expression" dxfId="375" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="372" priority="163">
+    <cfRule type="expression" dxfId="374" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="371" priority="157">
+    <cfRule type="expression" dxfId="373" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="370" priority="143">
+    <cfRule type="expression" dxfId="372" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="369" priority="142">
+    <cfRule type="expression" dxfId="371" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="368" priority="132">
+    <cfRule type="expression" dxfId="370" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="367" priority="126">
+    <cfRule type="expression" dxfId="369" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="366" priority="125">
+    <cfRule type="expression" dxfId="368" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="365" priority="124">
+    <cfRule type="expression" dxfId="367" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="364" priority="123">
+    <cfRule type="expression" dxfId="366" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="363" priority="122">
+    <cfRule type="expression" dxfId="365" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="362" priority="121">
+    <cfRule type="expression" dxfId="364" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="361" priority="120">
+    <cfRule type="expression" dxfId="363" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="360" priority="109">
+    <cfRule type="expression" dxfId="362" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="359" priority="105">
+    <cfRule type="expression" dxfId="361" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="358" priority="104">
+    <cfRule type="expression" dxfId="360" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="357" priority="101">
+    <cfRule type="expression" dxfId="359" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="356" priority="97">
+    <cfRule type="expression" dxfId="358" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="355" priority="92">
+    <cfRule type="expression" dxfId="357" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="354" priority="91">
+    <cfRule type="expression" dxfId="356" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="353" priority="88">
+    <cfRule type="expression" dxfId="355" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="352" priority="89">
+    <cfRule type="expression" dxfId="354" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="351" priority="83">
+    <cfRule type="expression" dxfId="353" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="350" priority="82">
+    <cfRule type="expression" dxfId="352" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="349" priority="74">
+    <cfRule type="expression" dxfId="351" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="348" priority="73">
+    <cfRule type="expression" dxfId="350" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="347" priority="70">
+    <cfRule type="expression" dxfId="349" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="346" priority="71">
+    <cfRule type="expression" dxfId="348" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="345" priority="63">
+    <cfRule type="expression" dxfId="347" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="344" priority="62">
+    <cfRule type="expression" dxfId="346" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="343" priority="61">
+    <cfRule type="expression" dxfId="345" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="342" priority="60">
+    <cfRule type="expression" dxfId="344" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="341" priority="59">
+    <cfRule type="expression" dxfId="343" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="340" priority="58">
+    <cfRule type="expression" dxfId="342" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="339" priority="47">
+    <cfRule type="expression" dxfId="341" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="338" priority="57">
+    <cfRule type="expression" dxfId="340" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="337" priority="56">
+    <cfRule type="expression" dxfId="339" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="336" priority="55">
+    <cfRule type="expression" dxfId="338" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="335" priority="54">
+    <cfRule type="expression" dxfId="337" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="334" priority="53">
+    <cfRule type="expression" dxfId="336" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="333" priority="52">
+    <cfRule type="expression" dxfId="335" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="332" priority="51">
+    <cfRule type="expression" dxfId="334" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="331" priority="50">
+    <cfRule type="expression" dxfId="333" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="330" priority="48">
+    <cfRule type="expression" dxfId="332" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="329" priority="46">
+    <cfRule type="expression" dxfId="331" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="328" priority="45">
+    <cfRule type="expression" dxfId="330" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="327" priority="42">
+    <cfRule type="expression" dxfId="329" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="326" priority="41">
+    <cfRule type="expression" dxfId="328" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="325" priority="34">
+    <cfRule type="expression" dxfId="327" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 M64:N64">
-    <cfRule type="expression" dxfId="324" priority="33">
+    <cfRule type="expression" dxfId="326" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="323" priority="32">
+    <cfRule type="expression" dxfId="325" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="322" priority="31">
+    <cfRule type="expression" dxfId="324" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="321" priority="30">
+    <cfRule type="expression" dxfId="323" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="320" priority="29">
+    <cfRule type="expression" dxfId="322" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="319" priority="28">
+    <cfRule type="expression" dxfId="321" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="318" priority="27">
+    <cfRule type="expression" dxfId="320" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="317" priority="26">
+    <cfRule type="expression" dxfId="319" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="316" priority="25">
+    <cfRule type="expression" dxfId="318" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="315" priority="24">
+    <cfRule type="expression" dxfId="317" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="314" priority="20">
+    <cfRule type="expression" dxfId="316" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="313" priority="23">
+    <cfRule type="expression" dxfId="315" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="312" priority="22">
+    <cfRule type="expression" dxfId="314" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="311" priority="21">
+    <cfRule type="expression" dxfId="313" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="310" priority="19">
+    <cfRule type="expression" dxfId="312" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="309" priority="17">
+    <cfRule type="expression" dxfId="311" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="308" priority="16">
+    <cfRule type="expression" dxfId="310" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="307" priority="15">
+    <cfRule type="expression" dxfId="309" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="306" priority="14">
+    <cfRule type="expression" dxfId="308" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="305" priority="13">
+    <cfRule type="expression" dxfId="307" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="304" priority="12">
+    <cfRule type="expression" dxfId="306" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="303" priority="11">
+    <cfRule type="expression" dxfId="305" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="302" priority="10">
+    <cfRule type="expression" dxfId="304" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="301" priority="9">
+    <cfRule type="expression" dxfId="303" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="300" priority="8">
+    <cfRule type="expression" dxfId="302" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="299" priority="7">
+    <cfRule type="expression" dxfId="301" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="298" priority="6">
+    <cfRule type="expression" dxfId="300" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="297" priority="5">
+    <cfRule type="expression" dxfId="299" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="296" priority="4">
+    <cfRule type="expression" dxfId="298" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="295" priority="3">
+    <cfRule type="expression" dxfId="297" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:J57 M57:N57">
-    <cfRule type="expression" dxfId="294" priority="2">
+    <cfRule type="expression" dxfId="296" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:L70">
-    <cfRule type="expression" dxfId="293" priority="1">
+    <cfRule type="expression" dxfId="295" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30932,42 +31301,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="292" priority="13">
+    <cfRule type="expression" dxfId="294" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="291" priority="12">
+    <cfRule type="expression" dxfId="293" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="290" priority="11">
+    <cfRule type="expression" dxfId="292" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="289" priority="5">
+    <cfRule type="expression" dxfId="291" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="288" priority="4">
+    <cfRule type="expression" dxfId="290" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="287" priority="3">
+    <cfRule type="expression" dxfId="289" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="286" priority="2">
+    <cfRule type="expression" dxfId="288" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="285" priority="1">
+    <cfRule type="expression" dxfId="287" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37005,112 +37374,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="284" priority="28">
+    <cfRule type="expression" dxfId="286" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="283" priority="27">
+    <cfRule type="expression" dxfId="285" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="282" priority="26">
+    <cfRule type="expression" dxfId="284" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="281" priority="25">
+    <cfRule type="expression" dxfId="283" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="280" priority="23">
+    <cfRule type="expression" dxfId="282" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="279" priority="22">
+    <cfRule type="expression" dxfId="281" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="278" priority="20">
+    <cfRule type="expression" dxfId="280" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="277" priority="19">
+    <cfRule type="expression" dxfId="279" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="276" priority="15">
+    <cfRule type="expression" dxfId="278" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="275" priority="14">
+    <cfRule type="expression" dxfId="277" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="274" priority="13">
+    <cfRule type="expression" dxfId="276" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="273" priority="12">
+    <cfRule type="expression" dxfId="275" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="272" priority="11">
+    <cfRule type="expression" dxfId="274" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="271" priority="10">
+    <cfRule type="expression" dxfId="273" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="270" priority="9">
+    <cfRule type="expression" dxfId="272" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="269" priority="8">
+    <cfRule type="expression" dxfId="271" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="268" priority="7">
+    <cfRule type="expression" dxfId="270" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="267" priority="6">
+    <cfRule type="expression" dxfId="269" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="266" priority="1">
+    <cfRule type="expression" dxfId="268" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="265" priority="5">
+    <cfRule type="expression" dxfId="267" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="264" priority="4">
+    <cfRule type="expression" dxfId="266" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="263" priority="2">
+    <cfRule type="expression" dxfId="265" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43025,107 +43394,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="262" priority="24">
+    <cfRule type="expression" dxfId="264" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="261" priority="23">
+    <cfRule type="expression" dxfId="263" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="260" priority="22">
+    <cfRule type="expression" dxfId="262" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="259" priority="21">
+    <cfRule type="expression" dxfId="261" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="258" priority="20">
+    <cfRule type="expression" dxfId="260" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="257" priority="19">
+    <cfRule type="expression" dxfId="259" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="256" priority="18">
+    <cfRule type="expression" dxfId="258" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="255" priority="15">
+    <cfRule type="expression" dxfId="257" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="254" priority="14">
+    <cfRule type="expression" dxfId="256" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="253" priority="13">
+    <cfRule type="expression" dxfId="255" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="252" priority="12">
+    <cfRule type="expression" dxfId="254" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="251" priority="1">
+    <cfRule type="expression" dxfId="253" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="250" priority="10">
+    <cfRule type="expression" dxfId="252" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="249" priority="9">
+    <cfRule type="expression" dxfId="251" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="248" priority="8">
+    <cfRule type="expression" dxfId="250" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="247" priority="7">
+    <cfRule type="expression" dxfId="249" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="246" priority="6">
+    <cfRule type="expression" dxfId="248" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="245" priority="5">
+    <cfRule type="expression" dxfId="247" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="244" priority="4">
+    <cfRule type="expression" dxfId="246" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="243" priority="3">
+    <cfRule type="expression" dxfId="245" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="242" priority="2">
+    <cfRule type="expression" dxfId="244" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43477,11 +43846,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-39455</v>
+        <v>-26044</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.78910000000000002</v>
+        <v>-0.52088000000000001</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -43498,11 +43867,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-87791</v>
+        <v>-74380</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-1.7558199999999999</v>
+        <v>-1.4876</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43559,11 +43928,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-285802</v>
+        <v>-225357</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.95267333333333337</v>
+        <v>-0.75119000000000002</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -43580,11 +43949,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>1048472</v>
+        <v>1108917</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.494906666666667</v>
+        <v>3.6963900000000001</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43641,11 +44010,11 @@
       <c r="O8" s="215"/>
       <c r="P8" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>116185</v>
+        <v>128085</v>
       </c>
       <c r="Q8" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.16185</v>
+        <v>1.28085</v>
       </c>
       <c r="R8" s="159"/>
       <c r="S8" s="153">
@@ -43662,11 +44031,11 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="154">
         <f t="shared" si="0"/>
-        <v>-269242</v>
+        <v>-257342</v>
       </c>
       <c r="Z8" s="168">
         <f t="shared" si="1"/>
-        <v>-2.6924200000000003</v>
+        <v>-2.57342</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43756,11 +44125,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-393340</v>
+        <v>-427730</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.3111333333333333</v>
+        <v>-1.4257666666666666</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -43776,11 +44145,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-752249</v>
+        <v>-786639</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-3.9518133333333334</v>
+        <v>-4.0664466666666668</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43837,11 +44206,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-217613</v>
+        <v>-199307</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4507533333333336</v>
+        <v>-1.3287133333333336</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -43857,11 +44226,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-392575</v>
+        <v>-374269</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.6171666666666669</v>
+        <v>-2.4951266666666667</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43918,11 +44287,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-181975</v>
+        <v>-170478</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.0329166666666669</v>
+        <v>-2.8413000000000004</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -43938,11 +44307,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-181975</v>
+        <v>-170478</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-3.0329166666666669</v>
+        <v>-2.8413000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43999,11 +44368,11 @@
       <c r="O13" s="215"/>
       <c r="P13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>581225</v>
+        <v>728625</v>
       </c>
       <c r="Q13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.38748333333333346</v>
+        <v>0.48575000000000013</v>
       </c>
       <c r="R13" s="159"/>
       <c r="S13" s="88">
@@ -44020,11 +44389,11 @@
       <c r="X13"/>
       <c r="Y13" s="154">
         <f t="shared" si="0"/>
-        <v>-786974</v>
+        <v>-639574</v>
       </c>
       <c r="Z13" s="168">
         <f t="shared" si="1"/>
-        <v>-0.5246493333333333</v>
+        <v>-0.42638266666666658</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44408,11 +44777,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>295645</v>
+        <v>288269</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.49274166666666674</v>
+        <v>0.48044833333333342</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -44428,11 +44797,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>100311</v>
+        <v>92935</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.924878333333333</v>
+        <v>-2.9371716666666665</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44489,11 +44858,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>10776</v>
+        <v>8851</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.10775999999999999</v>
+        <v>8.8510000000000005E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -44509,11 +44878,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>14455</v>
+        <v>12530</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>0.14455000000000001</v>
+        <v>0.12530000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44660,11 +45029,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>50114</v>
+        <v>58474</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.20045599999999994</v>
+        <v>0.23389599999999994</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -44680,11 +45049,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-217302</v>
+        <v>-208942</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4737040000000001</v>
+        <v>-2.440264</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44741,11 +45110,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-81711</v>
+        <v>-74559</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.37141363636363633</v>
+        <v>-0.3389045454545454</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -44761,11 +45130,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-170611</v>
+        <v>-163459</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.2604136363636362</v>
+        <v>-1.2279045454545454</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44903,11 +45272,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>72051</v>
+        <v>70760</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.72050999999999998</v>
+        <v>0.70760000000000001</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -44923,11 +45292,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1787396</v>
+        <v>1786105</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.87396</v>
+        <v>17.861049999999999</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45306,11 +45675,11 @@
       <c r="O29" s="215"/>
       <c r="P29" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>267315</v>
+        <v>267258</v>
       </c>
       <c r="Q29" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.66828749999999992</v>
+        <v>0.66814499999999988</v>
       </c>
       <c r="R29" s="159"/>
       <c r="S29" s="88">
@@ -45327,11 +45696,11 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="154">
         <f t="shared" si="0"/>
-        <v>937778</v>
+        <v>937721</v>
       </c>
       <c r="Z29" s="168">
         <f t="shared" si="1"/>
-        <v>2.3444449999999999</v>
+        <v>2.3443025</v>
       </c>
     </row>
     <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45388,11 +45757,11 @@
       <c r="O30" s="215"/>
       <c r="P30" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>85624</v>
+        <v>87994</v>
       </c>
       <c r="Q30" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.77839999999999987</v>
+        <v>0.7999454545454544</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="88">
@@ -45409,11 +45778,11 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="154">
         <f t="shared" si="0"/>
-        <v>85342</v>
+        <v>87712</v>
       </c>
       <c r="Z30" s="168">
         <f t="shared" si="1"/>
-        <v>0.77583636363636355</v>
+        <v>0.79738181818181808</v>
       </c>
     </row>
     <row r="31" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45559,11 +45928,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>125533</v>
+        <v>163870</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.83688666666666678</v>
+        <v>1.0924666666666667</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -45580,11 +45949,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-379536</v>
+        <v>-341199</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5302400000000009</v>
+        <v>-2.2746600000000008</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45722,11 +46091,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>229149</v>
+        <v>234471</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0831727272727267</v>
+        <v>2.131554545454545</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -45742,11 +46111,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-89791</v>
+        <v>-84469</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.81628181818181833</v>
+        <v>-0.76790000000000003</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -45891,11 +46260,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-158639</v>
+        <v>-369451</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.68973478260869658</v>
+        <v>-1.6063086956521748</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -45911,11 +46280,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>4002464</v>
+        <v>3791652</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>17.402017391304348</v>
+        <v>16.485443478260869</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45970,11 +46339,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-16876</v>
+        <v>-13528</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.84379999999999988</v>
+        <v>-0.67639999999999989</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -45990,11 +46359,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-16876</v>
+        <v>-13528</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.84379999999999988</v>
+        <v>-0.67639999999999989</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46051,11 +46420,11 @@
       <c r="O38" s="215"/>
       <c r="P38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-225918</v>
+        <v>-216818</v>
       </c>
       <c r="Q38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.45183599999999996</v>
+        <v>-0.43363599999999997</v>
       </c>
       <c r="R38" s="159"/>
       <c r="S38" s="88">
@@ -46071,11 +46440,11 @@
       <c r="W38" s="72"/>
       <c r="Y38" s="154">
         <f t="shared" si="0"/>
-        <v>2840488</v>
+        <v>2849588</v>
       </c>
       <c r="Z38" s="168">
         <f t="shared" si="1"/>
-        <v>5.6809759999999994</v>
+        <v>5.6991759999999996</v>
       </c>
     </row>
     <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46132,11 +46501,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3334737</v>
+        <v>3440917</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.3347370000000001</v>
+        <v>3.4409169999999998</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -46153,11 +46522,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>6928143</v>
+        <v>7034323</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>6.9281430000000004</v>
+        <v>7.0343230000000005</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -46648,11 +47017,11 @@
       <c r="O45" s="215"/>
       <c r="P45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>224852</v>
+        <v>481069</v>
       </c>
       <c r="Q45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.44970399999999988</v>
+        <v>0.96213799999999983</v>
       </c>
       <c r="R45" s="159"/>
       <c r="S45" s="88">
@@ -46668,11 +47037,11 @@
       <c r="W45" s="72"/>
       <c r="Y45" s="154">
         <f t="shared" si="22"/>
-        <v>1442170</v>
+        <v>1698387</v>
       </c>
       <c r="Z45" s="168">
         <f t="shared" si="23"/>
-        <v>2.8843399999999999</v>
+        <v>3.3967739999999997</v>
       </c>
     </row>
     <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46729,11 +47098,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1017683</v>
+        <v>1173260</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0353659999999998</v>
+        <v>2.3465199999999999</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -46750,11 +47119,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>969945</v>
+        <v>1125522</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>1.9398899999999997</v>
+        <v>2.2510439999999998</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -46812,11 +47181,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-182751</v>
+        <v>-152501</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.6550200000000004</v>
+        <v>-3.05002</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -46832,11 +47201,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-65856</v>
+        <v>-35606</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-1.3171200000000005</v>
+        <v>-0.71212000000000009</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -46981,11 +47350,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-66368</v>
+        <v>-32429</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6591999999999998</v>
+        <v>-0.81072499999999981</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -47001,11 +47370,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>-78196</v>
+        <v>-44257</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>-1.9548999999999999</v>
+        <v>-1.1064249999999998</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -47236,11 +47605,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>572558</v>
+        <v>634041</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.4313950000000002</v>
+        <v>1.5851025000000001</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -47256,11 +47625,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>172259</v>
+        <v>233742</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.43064750000000007</v>
+        <v>0.58435499999999996</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47317,11 +47686,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>200085</v>
+        <v>182633</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0008499999999998</v>
+        <v>1.82633</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -47337,11 +47706,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>945878</v>
+        <v>928426</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>9.4587800000000009</v>
+        <v>9.2842600000000015</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47479,11 +47848,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-95823</v>
+        <v>-70931</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.9164599999999998</v>
+        <v>-1.4186199999999998</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -47500,11 +47869,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-341601</v>
+        <v>-316709</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.83202</v>
+        <v>-6.3341799999999999</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -47562,11 +47931,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-215225</v>
+        <v>-158447</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.71741666666666659</v>
+        <v>-0.52815666666666661</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -47582,11 +47951,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4914200</v>
+        <v>-4857422</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.38066666666667</v>
+        <v>-16.191406666666669</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -47816,11 +48185,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>34705</v>
+        <v>30460</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.3735</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -47837,11 +48206,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>71428</v>
+        <v>67183</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.70233333333333325</v>
+        <v>0.61743333333333328</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -47905,11 +48274,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>817657</v>
+        <v>878497</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8.1765699999999999</v>
+        <v>8.7849699999999995</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -47925,11 +48294,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>4367726</v>
+        <v>4428566</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>43.677259999999997</v>
+        <v>44.28566</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -47991,11 +48360,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3908</v>
+        <v>5605</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.39079999999999993</v>
+        <v>0.5605</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -48011,11 +48380,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>3908</v>
+        <v>5605</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.39079999999999993</v>
+        <v>0.5605</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48072,11 +48441,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>7291</v>
+        <v>20158</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.4303333333333357E-2</v>
+        <v>6.7193333333333369E-2</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -48092,11 +48461,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>680140</v>
+        <v>693007</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>2.2671333333333332</v>
+        <v>2.3100233333333331</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -48323,11 +48692,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>382014</v>
+        <v>275669</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.95503499999999986</v>
+        <v>0.68917249999999997</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -48344,11 +48713,11 @@
       <c r="X65" s="132"/>
       <c r="Y65" s="154">
         <f t="shared" si="22"/>
-        <v>906426</v>
+        <v>800081</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" si="23"/>
-        <v>2.2660650000000002</v>
+        <v>2.0002025000000003</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48485,11 +48854,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1319980</v>
+        <v>-1427605</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.3200799999999999</v>
+        <v>-1.427705</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -48505,11 +48874,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1319980</v>
+        <v>-1427605</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.3200799999999999</v>
+        <v>-1.427705</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48623,11 +48992,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-29757</v>
+        <v>-15367</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.59514</v>
+        <v>-0.30733999999999995</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -48643,11 +49012,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-76411</v>
+        <v>-62021</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-1.5282200000000001</v>
+        <v>-1.2404199999999999</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -48704,11 +49073,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>791671</v>
+        <v>832471</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0613448076923078</v>
+        <v>2.1241140384615385</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="153">
@@ -48724,11 +49093,11 @@
       <c r="W70" s="150"/>
       <c r="Y70" s="154">
         <f t="shared" si="22"/>
-        <v>383719</v>
+        <v>424519</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="23"/>
-        <v>1.0414648076923076</v>
+        <v>1.1042340384615383</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
@@ -48785,11 +49154,11 @@
       <c r="O71" s="215"/>
       <c r="P71" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>25522</v>
+        <v>24982</v>
       </c>
       <c r="Q71" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.20417600000000014</v>
+        <v>0.19985600000000003</v>
       </c>
       <c r="R71" s="159"/>
       <c r="S71" s="153">
@@ -48805,11 +49174,11 @@
       <c r="W71" s="150"/>
       <c r="Y71" s="154">
         <f t="shared" si="22"/>
-        <v>2240</v>
+        <v>1700</v>
       </c>
       <c r="Z71" s="168">
         <f t="shared" si="23"/>
-        <v>-2.8643999999999892E-2</v>
+        <v>-3.2963999999999993E-2</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
@@ -48947,11 +49316,11 @@
       <c r="O73" s="215"/>
       <c r="P73" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>597432</v>
+        <v>567023</v>
       </c>
       <c r="Q73" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.9914400000000003</v>
+        <v>1.8900766666666668</v>
       </c>
       <c r="R73" s="159"/>
       <c r="S73" s="88">
@@ -48967,11 +49336,11 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="154">
         <f t="shared" si="22"/>
-        <v>430050</v>
+        <v>399641</v>
       </c>
       <c r="Z73" s="168">
         <f t="shared" si="23"/>
-        <v>1.4335000000000004</v>
+        <v>1.332136666666667</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
@@ -49107,11 +49476,11 @@
       <c r="O75" s="215"/>
       <c r="P75" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>88300</v>
+        <v>91565</v>
       </c>
       <c r="Q75" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.50513333333333332</v>
+        <v>0.52689999999999992</v>
       </c>
       <c r="R75" s="159"/>
       <c r="S75" s="153">
@@ -49127,11 +49496,11 @@
       <c r="W75" s="150"/>
       <c r="Y75" s="154">
         <f t="shared" ref="Y75:Y76" si="53">M75+P75+S75+V75</f>
-        <v>88300</v>
+        <v>91565</v>
       </c>
       <c r="Z75" s="168">
         <f t="shared" ref="Z75:Z76" si="54">(N75+Q75+T75+W75)</f>
-        <v>0.50513333333333332</v>
+        <v>0.52689999999999992</v>
       </c>
     </row>
     <row r="76" spans="1:26" s="132" customFormat="1" x14ac:dyDescent="0.25">
@@ -49186,11 +49555,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>537651</v>
+        <v>580851</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.075302</v>
+        <v>1.161702</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -49206,11 +49575,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>537651</v>
+        <v>580851</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>1.075302</v>
+        <v>1.161702</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -49243,7 +49612,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>9140856</v>
+        <v>9811247</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -49254,7 +49623,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>29124342</v>
+        <v>29841198</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -49550,11 +49919,11 @@
       <c r="O82" s="167"/>
       <c r="P82" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>298950</v>
+        <v>379630</v>
       </c>
       <c r="Q82" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.99650000000000039</v>
+        <v>1.2654333333333339</v>
       </c>
       <c r="R82" s="159"/>
       <c r="S82" s="153">
@@ -49571,11 +49940,11 @@
       <c r="X82" s="132"/>
       <c r="Y82" s="52">
         <f t="shared" si="56"/>
-        <v>510450</v>
+        <v>591130</v>
       </c>
       <c r="Z82" s="53">
         <f t="shared" si="56"/>
-        <v>0.99650000000000039</v>
+        <v>1.2654333333333339</v>
       </c>
       <c r="AA82" s="132"/>
     </row>
@@ -49631,7 +50000,7 @@
       <c r="O83" s="167"/>
       <c r="P83" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>922885</v>
+        <v>1304001</v>
       </c>
       <c r="Q83" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
@@ -49651,7 +50020,7 @@
       <c r="W83" s="53"/>
       <c r="Y83" s="52">
         <f t="shared" ref="Y83" si="59">M83+P83+S83+V83</f>
-        <v>512885</v>
+        <v>894001</v>
       </c>
       <c r="Z83" s="53">
         <f t="shared" ref="Z83" si="60">N83+Q83+T83+W83</f>
@@ -49685,7 +50054,7 @@
       <c r="O84" s="123"/>
       <c r="P84" s="112">
         <f>SUM(P80:P83)</f>
-        <v>1221835</v>
+        <v>1683631</v>
       </c>
       <c r="Q84" s="123"/>
       <c r="R84" s="123"/>
@@ -49709,1212 +50078,1212 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 G77:W78">
-    <cfRule type="expression" dxfId="241" priority="448">
+    <cfRule type="expression" dxfId="243" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="240" priority="447">
+    <cfRule type="expression" dxfId="242" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="239" priority="444">
+    <cfRule type="expression" dxfId="241" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="238" priority="441">
+    <cfRule type="expression" dxfId="240" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="237" priority="442">
+    <cfRule type="expression" dxfId="239" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="236" priority="432">
+    <cfRule type="expression" dxfId="238" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="235" priority="433">
+    <cfRule type="expression" dxfId="237" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="234" priority="422">
+    <cfRule type="expression" dxfId="236" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="233" priority="420">
+    <cfRule type="expression" dxfId="235" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="232" priority="418">
+    <cfRule type="expression" dxfId="234" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="231" priority="409">
+    <cfRule type="expression" dxfId="233" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="230" priority="408">
+    <cfRule type="expression" dxfId="232" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="229" priority="380">
+    <cfRule type="expression" dxfId="231" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="228" priority="406">
+    <cfRule type="expression" dxfId="230" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="227" priority="405">
+    <cfRule type="expression" dxfId="229" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="226" priority="403">
+    <cfRule type="expression" dxfId="228" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="225" priority="402">
+    <cfRule type="expression" dxfId="227" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="224" priority="400">
+    <cfRule type="expression" dxfId="226" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="223" priority="387">
+    <cfRule type="expression" dxfId="225" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="222" priority="331">
+    <cfRule type="expression" dxfId="224" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="221" priority="378">
+    <cfRule type="expression" dxfId="223" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="220" priority="330">
+    <cfRule type="expression" dxfId="222" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="219" priority="383">
+    <cfRule type="expression" dxfId="221" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="218" priority="349">
+    <cfRule type="expression" dxfId="220" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="217" priority="347">
+    <cfRule type="expression" dxfId="219" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="216" priority="355">
+    <cfRule type="expression" dxfId="218" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="215" priority="354">
+    <cfRule type="expression" dxfId="217" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="214" priority="339">
+    <cfRule type="expression" dxfId="216" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="213" priority="338">
+    <cfRule type="expression" dxfId="215" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="212" priority="369">
+    <cfRule type="expression" dxfId="214" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="211" priority="329">
+    <cfRule type="expression" dxfId="213" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="210" priority="340">
+    <cfRule type="expression" dxfId="212" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="209" priority="350">
+    <cfRule type="expression" dxfId="211" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="208" priority="348">
+    <cfRule type="expression" dxfId="210" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="207" priority="341">
+    <cfRule type="expression" dxfId="209" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="206" priority="328">
+    <cfRule type="expression" dxfId="208" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="205" priority="286">
+    <cfRule type="expression" dxfId="207" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="204" priority="285">
+    <cfRule type="expression" dxfId="206" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="203" priority="283">
+    <cfRule type="expression" dxfId="205" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="202" priority="275">
+    <cfRule type="expression" dxfId="204" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="201" priority="274">
+    <cfRule type="expression" dxfId="203" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="200" priority="288">
+    <cfRule type="expression" dxfId="202" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="199" priority="287">
+    <cfRule type="expression" dxfId="201" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="198" priority="284">
+    <cfRule type="expression" dxfId="200" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="197" priority="282">
+    <cfRule type="expression" dxfId="199" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="196" priority="273">
+    <cfRule type="expression" dxfId="198" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="195" priority="267">
+    <cfRule type="expression" dxfId="197" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="194" priority="272">
+    <cfRule type="expression" dxfId="196" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="193" priority="271">
+    <cfRule type="expression" dxfId="195" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="192" priority="268">
+    <cfRule type="expression" dxfId="194" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="191" priority="270">
+    <cfRule type="expression" dxfId="193" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="190" priority="269">
+    <cfRule type="expression" dxfId="192" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="189" priority="260">
+    <cfRule type="expression" dxfId="191" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="188" priority="259">
+    <cfRule type="expression" dxfId="190" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="187" priority="256">
+    <cfRule type="expression" dxfId="189" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="186" priority="255">
+    <cfRule type="expression" dxfId="188" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="185" priority="253">
+    <cfRule type="expression" dxfId="187" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="184" priority="258">
+    <cfRule type="expression" dxfId="186" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="183" priority="257">
+    <cfRule type="expression" dxfId="185" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="182" priority="254">
+    <cfRule type="expression" dxfId="184" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="181" priority="246">
+    <cfRule type="expression" dxfId="183" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="180" priority="245">
+    <cfRule type="expression" dxfId="182" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="179" priority="244">
+    <cfRule type="expression" dxfId="181" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="178" priority="239">
+    <cfRule type="expression" dxfId="180" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="177" priority="238">
+    <cfRule type="expression" dxfId="179" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="176" priority="242">
+    <cfRule type="expression" dxfId="178" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="175" priority="241">
+    <cfRule type="expression" dxfId="177" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="174" priority="240">
+    <cfRule type="expression" dxfId="176" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="173" priority="243">
+    <cfRule type="expression" dxfId="175" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="172" priority="231">
+    <cfRule type="expression" dxfId="174" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="171" priority="227">
+    <cfRule type="expression" dxfId="173" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="170" priority="226">
+    <cfRule type="expression" dxfId="172" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="169" priority="220">
+    <cfRule type="expression" dxfId="171" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="168" priority="219">
+    <cfRule type="expression" dxfId="170" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="167" priority="223">
+    <cfRule type="expression" dxfId="169" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="166" priority="222">
+    <cfRule type="expression" dxfId="168" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="165" priority="221">
+    <cfRule type="expression" dxfId="167" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="164" priority="224">
+    <cfRule type="expression" dxfId="166" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="163" priority="208">
+    <cfRule type="expression" dxfId="165" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="162" priority="207">
+    <cfRule type="expression" dxfId="164" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="161" priority="206">
+    <cfRule type="expression" dxfId="163" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="160" priority="200">
+    <cfRule type="expression" dxfId="162" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="159" priority="199">
+    <cfRule type="expression" dxfId="161" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="158" priority="193">
+    <cfRule type="expression" dxfId="160" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="157" priority="198">
+    <cfRule type="expression" dxfId="159" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="156" priority="197">
+    <cfRule type="expression" dxfId="158" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="155" priority="194">
+    <cfRule type="expression" dxfId="157" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="154" priority="196">
+    <cfRule type="expression" dxfId="156" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="153" priority="195">
+    <cfRule type="expression" dxfId="155" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="152" priority="191">
+    <cfRule type="expression" dxfId="154" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="151" priority="190">
+    <cfRule type="expression" dxfId="153" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="150" priority="177">
+    <cfRule type="expression" dxfId="152" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="149" priority="186">
+    <cfRule type="expression" dxfId="151" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="148" priority="185">
+    <cfRule type="expression" dxfId="150" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="147" priority="175">
+    <cfRule type="expression" dxfId="149" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="146" priority="174">
+    <cfRule type="expression" dxfId="148" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="145" priority="173">
+    <cfRule type="expression" dxfId="147" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="144" priority="168">
+    <cfRule type="expression" dxfId="146" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="143" priority="165">
+    <cfRule type="expression" dxfId="145" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="142" priority="164">
+    <cfRule type="expression" dxfId="144" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="141" priority="163">
+    <cfRule type="expression" dxfId="143" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="140" priority="162">
+    <cfRule type="expression" dxfId="142" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="139" priority="161">
+    <cfRule type="expression" dxfId="141" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="138" priority="160">
+    <cfRule type="expression" dxfId="140" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="137" priority="147">
+    <cfRule type="expression" dxfId="139" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="136" priority="157">
+    <cfRule type="expression" dxfId="138" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="135" priority="156">
+    <cfRule type="expression" dxfId="137" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="134" priority="155">
+    <cfRule type="expression" dxfId="136" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="133" priority="154">
+    <cfRule type="expression" dxfId="135" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="132" priority="153">
+    <cfRule type="expression" dxfId="134" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="131" priority="152">
+    <cfRule type="expression" dxfId="133" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="130" priority="151">
+    <cfRule type="expression" dxfId="132" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="129" priority="142">
+    <cfRule type="expression" dxfId="131" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="128" priority="148">
+    <cfRule type="expression" dxfId="130" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="127" priority="146">
+    <cfRule type="expression" dxfId="129" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="126" priority="145">
+    <cfRule type="expression" dxfId="128" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="125" priority="144">
+    <cfRule type="expression" dxfId="127" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="124" priority="143">
+    <cfRule type="expression" dxfId="126" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="123" priority="141">
+    <cfRule type="expression" dxfId="125" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="122" priority="138">
+    <cfRule type="expression" dxfId="124" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="121" priority="137">
+    <cfRule type="expression" dxfId="123" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="120" priority="136">
+    <cfRule type="expression" dxfId="122" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="119" priority="135">
+    <cfRule type="expression" dxfId="121" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="118" priority="134">
+    <cfRule type="expression" dxfId="120" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="117" priority="133">
+    <cfRule type="expression" dxfId="119" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="116" priority="130">
+    <cfRule type="expression" dxfId="118" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="115" priority="132">
+    <cfRule type="expression" dxfId="117" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="114" priority="131">
+    <cfRule type="expression" dxfId="116" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="113" priority="129">
+    <cfRule type="expression" dxfId="115" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="112" priority="128">
+    <cfRule type="expression" dxfId="114" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="111" priority="127">
+    <cfRule type="expression" dxfId="113" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="110" priority="126">
+    <cfRule type="expression" dxfId="112" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="109" priority="124">
+    <cfRule type="expression" dxfId="111" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="108" priority="123">
+    <cfRule type="expression" dxfId="110" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="107" priority="122">
+    <cfRule type="expression" dxfId="109" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="106" priority="121">
+    <cfRule type="expression" dxfId="108" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="105" priority="120">
+    <cfRule type="expression" dxfId="107" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="104" priority="115">
+    <cfRule type="expression" dxfId="106" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="103" priority="114">
+    <cfRule type="expression" dxfId="105" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="102" priority="118">
+    <cfRule type="expression" dxfId="104" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="101" priority="117">
+    <cfRule type="expression" dxfId="103" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="100" priority="116">
+    <cfRule type="expression" dxfId="102" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="99" priority="119">
+    <cfRule type="expression" dxfId="101" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="98" priority="113">
+    <cfRule type="expression" dxfId="100" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="97" priority="111">
+    <cfRule type="expression" dxfId="99" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="96" priority="109">
+    <cfRule type="expression" dxfId="98" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="95" priority="108">
+    <cfRule type="expression" dxfId="97" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="94" priority="107">
+    <cfRule type="expression" dxfId="96" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="93" priority="106">
+    <cfRule type="expression" dxfId="95" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="92" priority="105">
+    <cfRule type="expression" dxfId="94" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="91" priority="104">
+    <cfRule type="expression" dxfId="93" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="90" priority="102">
+    <cfRule type="expression" dxfId="92" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="89" priority="92">
+    <cfRule type="expression" dxfId="91" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="88" priority="100">
+    <cfRule type="expression" dxfId="90" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="87" priority="99">
+    <cfRule type="expression" dxfId="89" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="86" priority="96">
+    <cfRule type="expression" dxfId="88" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="85" priority="95">
+    <cfRule type="expression" dxfId="87" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="84" priority="93">
+    <cfRule type="expression" dxfId="86" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="83" priority="98">
+    <cfRule type="expression" dxfId="85" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="82" priority="97">
+    <cfRule type="expression" dxfId="84" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="81" priority="94">
+    <cfRule type="expression" dxfId="83" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="80" priority="91">
+    <cfRule type="expression" dxfId="82" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="79" priority="90">
+    <cfRule type="expression" dxfId="81" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="78" priority="89">
+    <cfRule type="expression" dxfId="80" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="77" priority="88">
+    <cfRule type="expression" dxfId="79" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="76" priority="87">
+    <cfRule type="expression" dxfId="78" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="75" priority="86">
+    <cfRule type="expression" dxfId="77" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="74" priority="85">
+    <cfRule type="expression" dxfId="76" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="73" priority="84">
+    <cfRule type="expression" dxfId="75" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="72" priority="72">
+    <cfRule type="expression" dxfId="74" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="71" priority="82">
+    <cfRule type="expression" dxfId="73" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="70" priority="81">
+    <cfRule type="expression" dxfId="72" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="69" priority="80">
+    <cfRule type="expression" dxfId="71" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="68" priority="79">
+    <cfRule type="expression" dxfId="70" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="67" priority="78">
+    <cfRule type="expression" dxfId="69" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="66" priority="77">
+    <cfRule type="expression" dxfId="68" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="65" priority="76">
+    <cfRule type="expression" dxfId="67" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="64" priority="75">
+    <cfRule type="expression" dxfId="66" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="63" priority="74">
+    <cfRule type="expression" dxfId="65" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="62" priority="73">
+    <cfRule type="expression" dxfId="64" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="61" priority="71">
+    <cfRule type="expression" dxfId="63" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="60" priority="70">
+    <cfRule type="expression" dxfId="62" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="59" priority="69">
+    <cfRule type="expression" dxfId="61" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="58" priority="68">
+    <cfRule type="expression" dxfId="60" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="57" priority="62">
+    <cfRule type="expression" dxfId="59" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="56" priority="67">
+    <cfRule type="expression" dxfId="58" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="55" priority="66">
+    <cfRule type="expression" dxfId="57" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="54" priority="63">
+    <cfRule type="expression" dxfId="56" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="53" priority="65">
+    <cfRule type="expression" dxfId="55" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="52" priority="64">
+    <cfRule type="expression" dxfId="54" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q55:Q60 Q62:Q76">
-    <cfRule type="expression" dxfId="51" priority="59">
+    <cfRule type="expression" dxfId="53" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q11 P38:Q53 P55:Q60 P62:Q76">
-    <cfRule type="expression" dxfId="50" priority="58">
+    <cfRule type="expression" dxfId="52" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="49" priority="57">
+    <cfRule type="expression" dxfId="51" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="48" priority="56">
+    <cfRule type="expression" dxfId="50" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="47" priority="55">
+    <cfRule type="expression" dxfId="49" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="46" priority="54">
+    <cfRule type="expression" dxfId="48" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="45" priority="53">
+    <cfRule type="expression" dxfId="47" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="44" priority="52">
+    <cfRule type="expression" dxfId="46" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="43" priority="39">
+    <cfRule type="expression" dxfId="45" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="42" priority="48">
+    <cfRule type="expression" dxfId="44" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="41" priority="24">
+    <cfRule type="expression" dxfId="43" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="40" priority="46">
+    <cfRule type="expression" dxfId="42" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="39" priority="45">
+    <cfRule type="expression" dxfId="41" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="38" priority="44">
+    <cfRule type="expression" dxfId="40" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="37" priority="43">
+    <cfRule type="expression" dxfId="39" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="36" priority="42">
+    <cfRule type="expression" dxfId="38" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="35" priority="41">
+    <cfRule type="expression" dxfId="37" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="34" priority="40">
+    <cfRule type="expression" dxfId="36" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="33" priority="25">
+    <cfRule type="expression" dxfId="35" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="34" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="31" priority="35">
+    <cfRule type="expression" dxfId="33" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="30" priority="34">
+    <cfRule type="expression" dxfId="32" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="29" priority="33">
+    <cfRule type="expression" dxfId="31" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="28" priority="32">
+    <cfRule type="expression" dxfId="30" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="27" priority="31">
+    <cfRule type="expression" dxfId="29" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="26" priority="30">
+    <cfRule type="expression" dxfId="28" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="25" priority="29">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="24" priority="28">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="23" priority="27">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="22" priority="26">
+    <cfRule type="expression" dxfId="24" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="23" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="22" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="14" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="10" priority="15">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="11" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="8" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="323">
   <si>
     <t>Sudeep</t>
   </si>
@@ -987,6 +987,9 @@
   </si>
   <si>
     <t>Aman Sharma</t>
+  </si>
+  <si>
+    <t>Fri</t>
   </si>
 </sst>
 </file>
@@ -5773,7 +5776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA66"/>
+  <dimension ref="A1:AD66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5783,19 +5786,21 @@
     <col min="5" max="5" width="9.42578125" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="13" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="11.28515625" style="133" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="22" width="9.140625" style="133"/>
-    <col min="23" max="23" width="14.140625" style="133" customWidth="1"/>
-    <col min="24" max="24" width="12" style="133" customWidth="1"/>
-    <col min="25" max="25" width="15.85546875" style="133" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="15" width="13.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="11.28515625" style="133" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="9.140625" style="133" collapsed="1"/>
+    <col min="21" max="25" width="9.140625" style="133"/>
+    <col min="26" max="26" width="14.140625" style="133" customWidth="1"/>
+    <col min="27" max="27" width="12" style="133" customWidth="1"/>
+    <col min="28" max="28" width="15.85546875" style="133" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
@@ -5815,15 +5820,24 @@
       <c r="M2" s="256">
         <v>46273</v>
       </c>
-      <c r="N2" s="183"/>
-      <c r="O2" s="184" t="s">
+      <c r="N2" s="256">
+        <v>46274</v>
+      </c>
+      <c r="O2" s="256">
+        <v>46275</v>
+      </c>
+      <c r="P2" s="256">
+        <v>46276</v>
+      </c>
+      <c r="Q2" s="183"/>
+      <c r="R2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="P2" s="185" t="s">
+      <c r="S2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5861,17 +5875,26 @@
       <c r="M3" s="179" t="s">
         <v>233</v>
       </c>
-      <c r="N3" s="180"/>
-      <c r="O3" s="189"/>
-      <c r="P3" s="180"/>
-      <c r="W3" s="133" t="s">
+      <c r="N3" s="179" t="s">
+        <v>237</v>
+      </c>
+      <c r="O3" s="179" t="s">
+        <v>236</v>
+      </c>
+      <c r="P3" s="179" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q3" s="180"/>
+      <c r="R3" s="189"/>
+      <c r="S3" s="180"/>
+      <c r="Z3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="X3" s="133">
+      <c r="AA3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5909,23 +5932,32 @@
       <c r="M4" s="158">
         <v>5321</v>
       </c>
-      <c r="N4" s="211"/>
-      <c r="O4" s="171">
-        <f t="shared" ref="O4:O30" si="0">SUM(H4:N4)</f>
-        <v>1000</v>
-      </c>
-      <c r="P4" s="149">
-        <f t="shared" ref="P4:P30" si="1">IFERROR(O4/F4*100,0)/10000000</f>
-        <v>0.02</v>
-      </c>
-      <c r="W4" s="133" t="s">
+      <c r="N4" s="158">
+        <v>-27681</v>
+      </c>
+      <c r="O4" s="158">
+        <v>-22117</v>
+      </c>
+      <c r="P4" s="158">
+        <v>-1063</v>
+      </c>
+      <c r="Q4" s="211"/>
+      <c r="R4" s="171">
+        <f t="shared" ref="R4:R30" si="0">SUM(H4:Q4)</f>
+        <v>-49861</v>
+      </c>
+      <c r="S4" s="149">
+        <f t="shared" ref="S4:S30" si="1">IFERROR(R4/F4*100,0)/10000000</f>
+        <v>-0.99722</v>
+      </c>
+      <c r="Z4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="X4" s="133">
+      <c r="AA4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -5963,17 +5995,26 @@
       <c r="M5" s="147">
         <v>22400</v>
       </c>
-      <c r="N5" s="174"/>
-      <c r="O5" s="171">
+      <c r="N5" s="147">
+        <v>-11568</v>
+      </c>
+      <c r="O5" s="147">
+        <v>80488</v>
+      </c>
+      <c r="P5" s="147">
+        <v>-190900</v>
+      </c>
+      <c r="Q5" s="174"/>
+      <c r="R5" s="171">
         <f t="shared" si="0"/>
-        <v>25614</v>
-      </c>
-      <c r="P5" s="149">
+        <v>-96366</v>
+      </c>
+      <c r="S5" s="149">
         <f t="shared" si="1"/>
-        <v>8.5379999999999998E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.32122000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -6011,17 +6052,26 @@
       <c r="M6" s="147">
         <v>0</v>
       </c>
-      <c r="N6" s="174"/>
-      <c r="O6" s="171">
+      <c r="N6" s="147">
+        <v>-18730</v>
+      </c>
+      <c r="O6" s="147">
+        <v>0</v>
+      </c>
+      <c r="P6" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="174"/>
+      <c r="R6" s="171">
         <f t="shared" si="0"/>
-        <v>11900</v>
-      </c>
-      <c r="P6" s="149">
+        <v>-6830</v>
+      </c>
+      <c r="S6" s="149">
         <f t="shared" si="1"/>
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-6.83E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="141" t="s">
         <v>309</v>
@@ -6057,17 +6107,24 @@
       <c r="M7" s="147">
         <v>0</v>
       </c>
-      <c r="N7" s="174"/>
-      <c r="O7" s="171">
+      <c r="N7" s="147"/>
+      <c r="O7" s="147">
+        <v>0</v>
+      </c>
+      <c r="P7" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="174"/>
+      <c r="R7" s="171">
         <f t="shared" si="0"/>
         <v>23300</v>
       </c>
-      <c r="P7" s="149">
+      <c r="S7" s="149">
         <f t="shared" si="1"/>
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6105,21 +6162,30 @@
       <c r="M8" s="147">
         <v>25445</v>
       </c>
-      <c r="N8" s="174"/>
-      <c r="O8" s="171">
+      <c r="N8" s="147">
+        <v>-46828</v>
+      </c>
+      <c r="O8" s="147">
+        <v>94220</v>
+      </c>
+      <c r="P8" s="147">
+        <v>-131800</v>
+      </c>
+      <c r="Q8" s="174"/>
+      <c r="R8" s="171">
         <f t="shared" si="0"/>
-        <v>27367</v>
-      </c>
-      <c r="P8" s="149">
+        <v>-57041</v>
+      </c>
+      <c r="S8" s="149">
         <f t="shared" si="1"/>
-        <v>9.1223333333333337E-2</v>
-      </c>
-      <c r="R8" s="5"/>
-      <c r="S8" s="134">
-        <v>16799</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.19013666666666668</v>
+      </c>
+      <c r="U8" s="5"/>
+      <c r="V8" s="134">
+        <v>-15795</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6157,21 +6223,30 @@
       <c r="M9" s="147">
         <v>-500</v>
       </c>
-      <c r="N9" s="174"/>
-      <c r="O9" s="171">
+      <c r="N9" s="147">
+        <v>-34321</v>
+      </c>
+      <c r="O9" s="147">
+        <v>4630</v>
+      </c>
+      <c r="P9" s="147">
+        <v>17255</v>
+      </c>
+      <c r="Q9" s="174"/>
+      <c r="R9" s="171">
         <f t="shared" si="0"/>
-        <v>94829</v>
-      </c>
-      <c r="P9" s="149">
+        <v>82393</v>
+      </c>
+      <c r="S9" s="149">
         <f t="shared" si="1"/>
-        <v>0.63219333333333338</v>
-      </c>
-      <c r="R9" s="134">
-        <v>207187</v>
-      </c>
-      <c r="S9" s="134"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.54928666666666659</v>
+      </c>
+      <c r="U9" s="134">
+        <v>4660847</v>
+      </c>
+      <c r="V9" s="134"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6207,24 +6282,33 @@
       <c r="M10" s="147">
         <v>2577</v>
       </c>
-      <c r="N10" s="174"/>
-      <c r="O10" s="171">
+      <c r="N10" s="147">
+        <v>-1822</v>
+      </c>
+      <c r="O10" s="147">
+        <v>2900</v>
+      </c>
+      <c r="P10" s="147">
+        <v>8888</v>
+      </c>
+      <c r="Q10" s="174"/>
+      <c r="R10" s="171">
         <f t="shared" si="0"/>
-        <v>21771</v>
-      </c>
-      <c r="P10" s="149">
+        <v>31737</v>
+      </c>
+      <c r="S10" s="149">
         <f t="shared" si="1"/>
-        <v>0.36285000000000001</v>
-      </c>
-      <c r="R10" s="134">
-        <v>190388</v>
-      </c>
-      <c r="S10" s="134">
-        <f>(R10+R9)/10000000*13780</f>
-        <v>547.85834999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.52895000000000003</v>
+      </c>
+      <c r="U10" s="134">
+        <v>4676642</v>
+      </c>
+      <c r="V10" s="134">
+        <f>(U10+U9)/10000000*13780</f>
+        <v>12867.059842000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6262,19 +6346,28 @@
       <c r="M11" s="147">
         <v>87600</v>
       </c>
-      <c r="N11" s="174"/>
-      <c r="O11" s="171">
+      <c r="N11" s="147">
+        <v>0</v>
+      </c>
+      <c r="O11" s="147">
+        <v>-8276</v>
+      </c>
+      <c r="P11" s="147">
+        <v>-182170</v>
+      </c>
+      <c r="Q11" s="174"/>
+      <c r="R11" s="171">
         <f t="shared" si="0"/>
-        <v>-238640</v>
-      </c>
-      <c r="P11" s="149">
+        <v>-429086</v>
+      </c>
+      <c r="S11" s="149">
         <f t="shared" si="1"/>
-        <v>-0.15909333333333334</v>
-      </c>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.28605733333333333</v>
+      </c>
+      <c r="U11" s="134"/>
+      <c r="V11" s="134"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6312,19 +6405,28 @@
       <c r="M12" s="147">
         <v>-7456</v>
       </c>
-      <c r="N12" s="174"/>
-      <c r="O12" s="171">
+      <c r="N12" s="147">
+        <v>0</v>
+      </c>
+      <c r="O12" s="147">
+        <v>-400</v>
+      </c>
+      <c r="P12" s="147">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="174"/>
+      <c r="R12" s="171">
         <f t="shared" si="0"/>
-        <v>-119511</v>
-      </c>
-      <c r="P12" s="149">
+        <v>-119861</v>
+      </c>
+      <c r="S12" s="149">
         <f t="shared" si="1"/>
-        <v>-0.199185</v>
-      </c>
-      <c r="R12" s="134"/>
-      <c r="S12" s="134"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.19976833333333333</v>
+      </c>
+      <c r="U12" s="134"/>
+      <c r="V12" s="134"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6362,19 +6464,28 @@
       <c r="M13" s="147">
         <v>365</v>
       </c>
-      <c r="N13" s="174"/>
-      <c r="O13" s="171">
+      <c r="N13" s="147">
+        <v>-161</v>
+      </c>
+      <c r="O13" s="147">
+        <v>190</v>
+      </c>
+      <c r="P13" s="147">
+        <v>-2915</v>
+      </c>
+      <c r="Q13" s="174"/>
+      <c r="R13" s="171">
         <f t="shared" si="0"/>
-        <v>-4565</v>
-      </c>
-      <c r="P13" s="149">
+        <v>-7451</v>
+      </c>
+      <c r="S13" s="149">
         <f t="shared" si="1"/>
-        <v>-4.5650000000000003E-2</v>
-      </c>
-      <c r="R13" s="134"/>
-      <c r="S13" s="134"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-7.4510000000000007E-2</v>
+      </c>
+      <c r="U13" s="134"/>
+      <c r="V13" s="134"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6412,19 +6523,28 @@
       <c r="M14" s="147">
         <v>5219</v>
       </c>
-      <c r="N14" s="174"/>
-      <c r="O14" s="171">
+      <c r="N14" s="147">
+        <v>0</v>
+      </c>
+      <c r="O14" s="147">
+        <v>9114</v>
+      </c>
+      <c r="P14" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="174"/>
+      <c r="R14" s="171">
         <f t="shared" si="0"/>
-        <v>13554</v>
-      </c>
-      <c r="P14" s="149">
+        <v>22668</v>
+      </c>
+      <c r="S14" s="149">
         <f t="shared" si="1"/>
-        <v>5.4216E-2</v>
-      </c>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+        <v>9.0672000000000016E-2</v>
+      </c>
+      <c r="U14" s="134"/>
+      <c r="V14" s="134"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6462,29 +6582,38 @@
       <c r="M15" s="147">
         <v>3927</v>
       </c>
-      <c r="N15" s="174"/>
-      <c r="O15" s="171">
+      <c r="N15" s="147">
+        <v>0</v>
+      </c>
+      <c r="O15" s="147">
+        <v>8417</v>
+      </c>
+      <c r="P15" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="174"/>
+      <c r="R15" s="171">
         <f t="shared" si="0"/>
-        <v>13349</v>
-      </c>
-      <c r="P15" s="149">
+        <v>21766</v>
+      </c>
+      <c r="S15" s="149">
         <f t="shared" si="1"/>
-        <v>6.0677272727272719E-2</v>
-      </c>
-      <c r="R15" s="134"/>
-      <c r="S15" s="193">
-        <f>S8-S10</f>
-        <v>16251.14165</v>
-      </c>
-      <c r="V15" s="133">
+        <v>9.8936363636363628E-2</v>
+      </c>
+      <c r="U15" s="134"/>
+      <c r="V15" s="193">
+        <f>V8-V10</f>
+        <v>-28662.059842000002</v>
+      </c>
+      <c r="Y15" s="133">
         <v>116185</v>
       </c>
-      <c r="X15" s="133">
-        <f>V15+S15</f>
-        <v>132436.14165000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AA15" s="133">
+        <f>Y15+V15</f>
+        <v>87522.940157999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6522,17 +6651,26 @@
       <c r="M16" s="147">
         <v>6627</v>
       </c>
-      <c r="N16" s="174"/>
-      <c r="O16" s="171">
+      <c r="N16" s="147">
+        <v>-4941</v>
+      </c>
+      <c r="O16" s="147">
+        <v>-4200</v>
+      </c>
+      <c r="P16" s="147">
+        <v>7421</v>
+      </c>
+      <c r="Q16" s="174"/>
+      <c r="R16" s="171">
         <f t="shared" si="0"/>
-        <v>-2647</v>
-      </c>
-      <c r="P16" s="149">
+        <v>-4367</v>
+      </c>
+      <c r="S16" s="149">
         <f t="shared" si="1"/>
-        <v>-2.647E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-4.367E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6570,28 +6708,37 @@
       <c r="M17" s="147">
         <v>0</v>
       </c>
-      <c r="N17" s="174"/>
-      <c r="O17" s="171">
+      <c r="N17" s="147">
+        <v>-32641</v>
+      </c>
+      <c r="O17" s="147">
+        <v>0</v>
+      </c>
+      <c r="P17" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="174"/>
+      <c r="R17" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="149">
+        <v>-32641</v>
+      </c>
+      <c r="S17" s="149">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="133">
+        <v>-0.13056400000000001</v>
+      </c>
+      <c r="AA17" s="133">
         <v>4000000</v>
       </c>
-      <c r="Y17" s="133">
-        <f>X17*7/100</f>
+      <c r="AB17" s="133">
+        <f>AA17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="AA17" s="133">
+      <c r="AD17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6629,21 +6776,30 @@
       <c r="M18" s="147">
         <v>1600</v>
       </c>
-      <c r="N18" s="174"/>
-      <c r="O18" s="171">
+      <c r="N18" s="147">
+        <v>-48000</v>
+      </c>
+      <c r="O18" s="147">
+        <v>0</v>
+      </c>
+      <c r="P18" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="174"/>
+      <c r="R18" s="171">
         <f t="shared" si="0"/>
-        <v>-57</v>
-      </c>
-      <c r="P18" s="149">
+        <v>-48057</v>
+      </c>
+      <c r="S18" s="149">
         <f t="shared" si="1"/>
-        <v>-1.4249999999999999E-4</v>
-      </c>
-      <c r="Y18" s="133">
-        <f>Y17/12</f>
+        <v>-0.1201425</v>
+      </c>
+      <c r="AB18" s="133">
+        <f>AB17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6681,17 +6837,26 @@
       <c r="M19" s="147">
         <v>-1738</v>
       </c>
-      <c r="N19" s="174"/>
-      <c r="O19" s="171">
+      <c r="N19" s="147">
+        <v>-62019</v>
+      </c>
+      <c r="O19" s="147">
+        <v>13500</v>
+      </c>
+      <c r="P19" s="147">
+        <v>-140844</v>
+      </c>
+      <c r="Q19" s="174"/>
+      <c r="R19" s="171">
         <f t="shared" si="0"/>
-        <v>48857</v>
-      </c>
-      <c r="P19" s="149">
+        <v>-140506</v>
+      </c>
+      <c r="S19" s="149">
         <f t="shared" si="1"/>
-        <v>0.3257133333333333</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-0.9367066666666668</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6729,17 +6894,29 @@
       <c r="M20" s="147">
         <v>700</v>
       </c>
-      <c r="N20" s="174"/>
-      <c r="O20" s="171">
+      <c r="N20" s="147">
+        <v>10000</v>
+      </c>
+      <c r="O20" s="147">
+        <v>25655</v>
+      </c>
+      <c r="P20" s="147">
+        <v>-28662</v>
+      </c>
+      <c r="Q20" s="174"/>
+      <c r="R20" s="171">
         <f t="shared" si="0"/>
-        <v>312</v>
-      </c>
-      <c r="P20" s="149">
+        <v>7305</v>
+      </c>
+      <c r="S20" s="149">
         <f t="shared" si="1"/>
-        <v>2.8363636363636364E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+        <v>6.6409090909090904E-2</v>
+      </c>
+      <c r="W20" s="133">
+        <v>-38300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -6777,17 +6954,29 @@
       <c r="M21" s="147">
         <v>6521</v>
       </c>
-      <c r="N21" s="174"/>
-      <c r="O21" s="171">
+      <c r="N21" s="147">
+        <v>0</v>
+      </c>
+      <c r="O21" s="147">
+        <v>20992</v>
+      </c>
+      <c r="P21" s="147">
+        <v>-23384</v>
+      </c>
+      <c r="Q21" s="174"/>
+      <c r="R21" s="171">
         <f t="shared" si="0"/>
-        <v>5990</v>
-      </c>
-      <c r="P21" s="149">
+        <v>3598</v>
+      </c>
+      <c r="S21" s="149">
         <f t="shared" si="1"/>
-        <v>0.23960000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.14391999999999999</v>
+      </c>
+      <c r="W21" s="133">
+        <v>-35300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -6825,17 +7014,29 @@
       <c r="M22" s="147">
         <v>-3207</v>
       </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="171">
+      <c r="N22" s="147">
+        <v>0</v>
+      </c>
+      <c r="O22" s="147">
+        <v>0</v>
+      </c>
+      <c r="P22" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="171">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="P22" s="149">
+      <c r="S22" s="149">
         <f t="shared" si="1"/>
         <v>5.0350000000000004E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="W22" s="133">
+        <v>-21500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -6871,17 +7072,26 @@
       <c r="M23" s="147">
         <v>0</v>
       </c>
-      <c r="N23" s="174"/>
-      <c r="O23" s="171">
+      <c r="N23" s="147">
+        <v>0</v>
+      </c>
+      <c r="O23" s="147">
+        <v>0</v>
+      </c>
+      <c r="P23" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="174"/>
+      <c r="R23" s="171">
         <f t="shared" si="0"/>
         <v>340</v>
       </c>
-      <c r="P23" s="149">
+      <c r="S23" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -6919,17 +7129,26 @@
       <c r="M24" s="147">
         <v>-1500</v>
       </c>
-      <c r="N24" s="174"/>
-      <c r="O24" s="171">
+      <c r="N24" s="147">
+        <v>18235</v>
+      </c>
+      <c r="O24" s="147">
+        <v>19473</v>
+      </c>
+      <c r="P24" s="147">
+        <v>-41546</v>
+      </c>
+      <c r="Q24" s="174"/>
+      <c r="R24" s="171">
         <f t="shared" si="0"/>
-        <v>29767</v>
-      </c>
-      <c r="P24" s="149">
+        <v>25929</v>
+      </c>
+      <c r="S24" s="149">
         <f t="shared" si="1"/>
-        <v>0.27060909090909085</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.2357181818181818</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -6967,17 +7186,26 @@
       <c r="M25" s="147">
         <v>-41112</v>
       </c>
-      <c r="N25" s="174"/>
-      <c r="O25" s="171">
+      <c r="N25" s="147">
+        <v>-132811</v>
+      </c>
+      <c r="O25" s="147">
+        <v>-26800</v>
+      </c>
+      <c r="P25" s="147">
+        <v>-144000</v>
+      </c>
+      <c r="Q25" s="174"/>
+      <c r="R25" s="171">
         <f t="shared" si="0"/>
-        <v>-723512</v>
-      </c>
-      <c r="P25" s="149">
+        <v>-1027123</v>
+      </c>
+      <c r="S25" s="149">
         <f t="shared" si="1"/>
-        <v>-3.1457043478260873</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-4.4657521739130441</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -7013,17 +7241,26 @@
       <c r="M26" s="147">
         <v>1768</v>
       </c>
-      <c r="N26" s="174"/>
-      <c r="O26" s="171">
+      <c r="N26" s="147">
+        <v>-4426</v>
+      </c>
+      <c r="O26" s="147">
+        <v>2020</v>
+      </c>
+      <c r="P26" s="147">
+        <v>1432</v>
+      </c>
+      <c r="Q26" s="174"/>
+      <c r="R26" s="171">
         <f t="shared" si="0"/>
-        <v>6768</v>
-      </c>
-      <c r="P26" s="149">
+        <v>5794</v>
+      </c>
+      <c r="S26" s="149">
         <f t="shared" si="1"/>
-        <v>0.33839999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.28970000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -7061,17 +7298,26 @@
       <c r="M27" s="147">
         <v>1500</v>
       </c>
-      <c r="N27" s="174"/>
-      <c r="O27" s="171">
+      <c r="N27" s="147">
+        <v>-95100</v>
+      </c>
+      <c r="O27" s="147">
+        <v>0</v>
+      </c>
+      <c r="P27" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="174"/>
+      <c r="R27" s="171">
         <f t="shared" si="0"/>
-        <v>48100</v>
-      </c>
-      <c r="P27" s="149">
+        <v>-47000</v>
+      </c>
+      <c r="S27" s="149">
         <f t="shared" si="1"/>
-        <v>9.6199999999999994E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-9.4E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -7109,17 +7355,26 @@
       <c r="M28" s="147">
         <v>84000</v>
       </c>
-      <c r="N28" s="174"/>
-      <c r="O28" s="171">
+      <c r="N28" s="147">
+        <v>-10651</v>
+      </c>
+      <c r="O28" s="147">
+        <v>7930</v>
+      </c>
+      <c r="P28" s="147">
+        <v>-431450</v>
+      </c>
+      <c r="Q28" s="174"/>
+      <c r="R28" s="171">
         <f t="shared" si="0"/>
-        <v>-26495</v>
-      </c>
-      <c r="P28" s="149">
+        <v>-460666</v>
+      </c>
+      <c r="S28" s="149">
         <f t="shared" si="1"/>
-        <v>-2.6495000000000001E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-0.46066600000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -7157,17 +7412,26 @@
       <c r="M29" s="147">
         <v>256217</v>
       </c>
-      <c r="N29" s="174"/>
-      <c r="O29" s="171">
+      <c r="N29" s="147">
+        <v>2100</v>
+      </c>
+      <c r="O29" s="147">
+        <v>-92200</v>
+      </c>
+      <c r="P29" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="174"/>
+      <c r="R29" s="171">
         <f t="shared" si="0"/>
-        <v>-218783</v>
-      </c>
-      <c r="P29" s="149">
+        <v>-308883</v>
+      </c>
+      <c r="S29" s="149">
         <f t="shared" si="1"/>
-        <v>-0.43756600000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-0.61776600000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -7205,17 +7469,26 @@
       <c r="M30" s="147">
         <v>104979</v>
       </c>
-      <c r="N30" s="174"/>
-      <c r="O30" s="171">
+      <c r="N30" s="147">
+        <v>-138000</v>
+      </c>
+      <c r="O30" s="147">
+        <v>102550</v>
+      </c>
+      <c r="P30" s="147">
+        <v>37112</v>
+      </c>
+      <c r="Q30" s="174"/>
+      <c r="R30" s="171">
         <f t="shared" si="0"/>
-        <v>145853</v>
-      </c>
-      <c r="P30" s="149">
+        <v>147515</v>
+      </c>
+      <c r="S30" s="149">
         <f t="shared" si="1"/>
-        <v>0.29170600000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.29503000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -7253,17 +7526,26 @@
       <c r="M31" s="147">
         <v>16250</v>
       </c>
-      <c r="N31" s="174"/>
-      <c r="O31" s="171">
-        <f t="shared" ref="O31:O56" si="2">SUM(H31:N31)</f>
-        <v>-73137</v>
-      </c>
-      <c r="P31" s="149">
-        <f t="shared" ref="P31:P56" si="3">IFERROR(O31/F31*100,0)/10000000</f>
-        <v>-1.4627399999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="N31" s="147">
+        <v>-46322</v>
+      </c>
+      <c r="O31" s="147">
+        <v>-4565</v>
+      </c>
+      <c r="P31" s="147">
+        <v>-21920</v>
+      </c>
+      <c r="Q31" s="174"/>
+      <c r="R31" s="171">
+        <f t="shared" ref="R31:R56" si="2">SUM(H31:Q31)</f>
+        <v>-145944</v>
+      </c>
+      <c r="S31" s="149">
+        <f t="shared" ref="S31:S56" si="3">IFERROR(R31/F31*100,0)/10000000</f>
+        <v>-2.9188800000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -7301,18 +7583,27 @@
       <c r="M32" s="147">
         <v>50168</v>
       </c>
-      <c r="N32" s="174"/>
-      <c r="O32" s="171">
+      <c r="N32" s="147">
+        <v>8433</v>
+      </c>
+      <c r="O32" s="147">
+        <v>10192</v>
+      </c>
+      <c r="P32" s="147">
+        <v>44092</v>
+      </c>
+      <c r="Q32" s="174"/>
+      <c r="R32" s="171">
         <f t="shared" si="2"/>
-        <v>33096</v>
-      </c>
-      <c r="P32" s="149">
+        <v>95813</v>
+      </c>
+      <c r="S32" s="149">
         <f t="shared" si="3"/>
-        <v>0.82740000000000002</v>
-      </c>
-      <c r="S32" s="134"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+        <v>2.3953250000000001</v>
+      </c>
+      <c r="V32" s="134"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -7350,21 +7641,30 @@
       <c r="M33" s="147">
         <v>0</v>
       </c>
-      <c r="N33" s="174"/>
-      <c r="O33" s="171">
+      <c r="N33" s="147">
+        <v>0</v>
+      </c>
+      <c r="O33" s="147">
+        <v>0</v>
+      </c>
+      <c r="P33" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="174"/>
+      <c r="R33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P33" s="149">
+      <c r="S33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R33" s="5"/>
-      <c r="S33" s="134">
-        <v>-28252</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U33" s="5"/>
+      <c r="V33" s="134">
+        <v>39838</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -7402,19 +7702,28 @@
       <c r="M34" s="147">
         <v>0</v>
       </c>
-      <c r="N34" s="174"/>
-      <c r="O34" s="171">
+      <c r="N34" s="147">
+        <v>0</v>
+      </c>
+      <c r="O34" s="147">
+        <v>0</v>
+      </c>
+      <c r="P34" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="174"/>
+      <c r="R34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P34" s="149">
+      <c r="S34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R34" s="5"/>
-      <c r="S34" s="134"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U34" s="5"/>
+      <c r="V34" s="134"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -7452,24 +7761,33 @@
       <c r="M35" s="147">
         <v>11813</v>
       </c>
-      <c r="N35" s="174"/>
-      <c r="O35" s="171">
+      <c r="N35" s="147">
+        <v>-57818</v>
+      </c>
+      <c r="O35" s="147">
+        <v>5239</v>
+      </c>
+      <c r="P35" s="147">
+        <v>3072</v>
+      </c>
+      <c r="Q35" s="174"/>
+      <c r="R35" s="171">
         <f t="shared" si="2"/>
-        <v>-76895</v>
-      </c>
-      <c r="P35" s="149">
+        <v>-126402</v>
+      </c>
+      <c r="S35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.19223750000000001</v>
-      </c>
-      <c r="R35" s="134">
-        <v>796796</v>
-      </c>
-      <c r="S35" s="134">
-        <f>(R36+R35)/10000000*13780</f>
-        <v>2157.0371420000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.31600499999999998</v>
+      </c>
+      <c r="U35" s="134">
+        <v>969020</v>
+      </c>
+      <c r="V35" s="134">
+        <f>(U36+U35)/10000000*13780</f>
+        <v>2725.5158840000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -7507,21 +7825,30 @@
       <c r="M36" s="147">
         <v>6866</v>
       </c>
-      <c r="N36" s="174"/>
-      <c r="O36" s="171">
+      <c r="N36" s="147">
+        <v>-29330</v>
+      </c>
+      <c r="O36" s="147">
+        <v>-5138</v>
+      </c>
+      <c r="P36" s="147">
+        <v>-32612</v>
+      </c>
+      <c r="Q36" s="174"/>
+      <c r="R36" s="171">
         <f t="shared" si="2"/>
-        <v>-20999</v>
-      </c>
-      <c r="P36" s="149">
+        <v>-88079</v>
+      </c>
+      <c r="S36" s="149">
         <f t="shared" si="3"/>
-        <v>-0.20999000000000001</v>
-      </c>
-      <c r="R36" s="134">
-        <v>768543</v>
-      </c>
-      <c r="S36" s="134"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.88078999999999996</v>
+      </c>
+      <c r="U36" s="134">
+        <v>1008858</v>
+      </c>
+      <c r="V36" s="134"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -7557,22 +7884,31 @@
       <c r="M37" s="147">
         <v>0</v>
       </c>
-      <c r="N37" s="174"/>
-      <c r="O37" s="171">
+      <c r="N37" s="147">
+        <v>0</v>
+      </c>
+      <c r="O37" s="147">
+        <v>0</v>
+      </c>
+      <c r="P37" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="174"/>
+      <c r="R37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P37" s="149">
+      <c r="S37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R37" s="134"/>
-      <c r="S37" s="134">
-        <f>+S33-S35</f>
-        <v>-30409.037142000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U37" s="134"/>
+      <c r="V37" s="134">
+        <f>+V33-V35</f>
+        <v>37112.484116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -7610,19 +7946,28 @@
       <c r="M38" s="147">
         <v>11984</v>
       </c>
-      <c r="N38" s="174"/>
-      <c r="O38" s="171">
+      <c r="N38" s="147">
+        <v>-6200</v>
+      </c>
+      <c r="O38" s="147">
+        <v>-9128</v>
+      </c>
+      <c r="P38" s="147">
+        <v>3788</v>
+      </c>
+      <c r="Q38" s="174"/>
+      <c r="R38" s="171">
         <f t="shared" si="2"/>
-        <v>-4548</v>
-      </c>
-      <c r="P38" s="149">
+        <v>-16088</v>
+      </c>
+      <c r="S38" s="149">
         <f t="shared" si="3"/>
-        <v>-9.0959999999999999E-2</v>
-      </c>
-      <c r="R38" s="134"/>
-      <c r="S38" s="134"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.32175999999999999</v>
+      </c>
+      <c r="U38" s="134"/>
+      <c r="V38" s="134"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -7660,19 +8005,28 @@
       <c r="M39" s="147">
         <v>0</v>
       </c>
-      <c r="N39" s="174"/>
-      <c r="O39" s="171">
+      <c r="N39" s="147">
+        <v>0</v>
+      </c>
+      <c r="O39" s="147">
+        <v>0</v>
+      </c>
+      <c r="P39" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="174"/>
+      <c r="R39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P39" s="149">
+      <c r="S39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R39" s="134"/>
-      <c r="S39" s="134"/>
-    </row>
-    <row r="40" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U39" s="134"/>
+      <c r="V39" s="134"/>
+    </row>
+    <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -7710,19 +8064,28 @@
       <c r="M40" s="147">
         <v>17728</v>
       </c>
-      <c r="N40" s="174"/>
-      <c r="O40" s="171">
+      <c r="N40" s="147">
+        <v>31677</v>
+      </c>
+      <c r="O40" s="147">
+        <v>0</v>
+      </c>
+      <c r="P40" s="147">
+        <v>13700</v>
+      </c>
+      <c r="Q40" s="174"/>
+      <c r="R40" s="171">
         <f t="shared" si="2"/>
-        <v>-47655</v>
-      </c>
-      <c r="P40" s="149">
+        <v>-2278</v>
+      </c>
+      <c r="S40" s="149">
         <f t="shared" si="3"/>
-        <v>-0.15884999999999999</v>
-      </c>
-      <c r="R40" s="134"/>
-      <c r="S40" s="134"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-7.5933333333333339E-3</v>
+      </c>
+      <c r="U40" s="134"/>
+      <c r="V40" s="134"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -7758,18 +8121,27 @@
       <c r="M41" s="147">
         <v>-30106</v>
       </c>
-      <c r="N41" s="174"/>
-      <c r="O41" s="171">
+      <c r="N41" s="147">
+        <v>-41487</v>
+      </c>
+      <c r="O41" s="147">
+        <v>-20744</v>
+      </c>
+      <c r="P41" s="147">
+        <v>25334</v>
+      </c>
+      <c r="Q41" s="174"/>
+      <c r="R41" s="171">
         <f t="shared" si="2"/>
-        <v>-2882</v>
-      </c>
-      <c r="P41" s="149">
+        <v>-39779</v>
+      </c>
+      <c r="S41" s="149">
         <f t="shared" si="3"/>
-        <v>-0.28820000000000001</v>
-      </c>
-      <c r="R41" s="134"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-3.9779</v>
+      </c>
+      <c r="U41" s="134"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -7807,17 +8179,26 @@
       <c r="M42" s="147">
         <v>0</v>
       </c>
-      <c r="N42" s="174"/>
-      <c r="O42" s="171">
+      <c r="N42" s="147">
+        <v>-14900</v>
+      </c>
+      <c r="O42" s="147">
+        <v>-1051</v>
+      </c>
+      <c r="P42" s="147">
+        <v>8722</v>
+      </c>
+      <c r="Q42" s="174"/>
+      <c r="R42" s="171">
         <f t="shared" si="2"/>
-        <v>-3868</v>
-      </c>
-      <c r="P42" s="149">
+        <v>-11097</v>
+      </c>
+      <c r="S42" s="149">
         <f t="shared" si="3"/>
-        <v>-7.7359999999999998E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.22194</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -7855,17 +8236,26 @@
       <c r="M43" s="147">
         <v>45690</v>
       </c>
-      <c r="N43" s="174"/>
-      <c r="O43" s="171">
+      <c r="N43" s="147">
+        <v>-47330</v>
+      </c>
+      <c r="O43" s="147">
+        <v>87600</v>
+      </c>
+      <c r="P43" s="147">
+        <v>-165000</v>
+      </c>
+      <c r="Q43" s="174"/>
+      <c r="R43" s="171">
         <f t="shared" si="2"/>
-        <v>-8877</v>
-      </c>
-      <c r="P43" s="149">
+        <v>-133607</v>
+      </c>
+      <c r="S43" s="149">
         <f t="shared" si="3"/>
-        <v>-8.8770000000000002E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.3360700000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -7901,17 +8291,26 @@
       <c r="M44" s="147">
         <v>394</v>
       </c>
-      <c r="N44" s="174"/>
-      <c r="O44" s="171">
+      <c r="N44" s="147">
+        <v>-6453</v>
+      </c>
+      <c r="O44" s="147">
+        <v>-500</v>
+      </c>
+      <c r="P44" s="147">
+        <v>-1652</v>
+      </c>
+      <c r="Q44" s="174"/>
+      <c r="R44" s="171">
         <f t="shared" si="2"/>
-        <v>9151</v>
-      </c>
-      <c r="P44" s="149">
+        <v>546</v>
+      </c>
+      <c r="S44" s="149">
         <f t="shared" si="3"/>
-        <v>0.91510000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+        <v>5.4600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -7949,17 +8348,26 @@
       <c r="M45" s="147">
         <v>0</v>
       </c>
-      <c r="N45" s="174"/>
-      <c r="O45" s="171">
+      <c r="N45" s="147">
+        <v>0</v>
+      </c>
+      <c r="O45" s="147">
+        <v>0</v>
+      </c>
+      <c r="P45" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="174"/>
+      <c r="R45" s="171">
         <f t="shared" si="2"/>
         <v>-156125</v>
       </c>
-      <c r="P45" s="149">
+      <c r="S45" s="149">
         <f t="shared" si="3"/>
         <v>-0.39031250000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -7997,17 +8405,26 @@
       <c r="M46" s="147">
         <v>-106345</v>
       </c>
-      <c r="N46" s="174"/>
-      <c r="O46" s="171">
+      <c r="N46" s="147">
+        <v>0</v>
+      </c>
+      <c r="O46" s="147">
+        <v>-6600</v>
+      </c>
+      <c r="P46" s="147">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="174"/>
+      <c r="R46" s="171">
         <f t="shared" si="2"/>
-        <v>-66605</v>
-      </c>
-      <c r="P46" s="149">
+        <v>-73205</v>
+      </c>
+      <c r="S46" s="149">
         <f t="shared" si="3"/>
-        <v>-0.16651250000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-0.18301249999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -8045,17 +8462,26 @@
       <c r="M47" s="147">
         <v>28061</v>
       </c>
-      <c r="N47" s="174"/>
-      <c r="O47" s="171">
+      <c r="N47" s="147">
+        <v>-183866</v>
+      </c>
+      <c r="O47" s="147">
+        <v>22209</v>
+      </c>
+      <c r="P47" s="147">
+        <v>388268</v>
+      </c>
+      <c r="Q47" s="174"/>
+      <c r="R47" s="171">
         <f t="shared" si="2"/>
-        <v>28891</v>
-      </c>
-      <c r="P47" s="149">
+        <v>255502</v>
+      </c>
+      <c r="S47" s="149">
         <f t="shared" si="3"/>
-        <v>9.6303333333333338E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0.85167333333333317</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -8091,17 +8517,26 @@
       <c r="M48" s="151">
         <v>-152025</v>
       </c>
-      <c r="N48" s="174"/>
-      <c r="O48" s="171">
+      <c r="N48" s="151">
+        <v>83800</v>
+      </c>
+      <c r="O48" s="151">
+        <v>-910511</v>
+      </c>
+      <c r="P48" s="151">
+        <v>458900</v>
+      </c>
+      <c r="Q48" s="174"/>
+      <c r="R48" s="171">
         <f t="shared" si="2"/>
-        <v>-392525</v>
-      </c>
-      <c r="P48" s="149">
+        <v>-760336</v>
+      </c>
+      <c r="S48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.39252500000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+        <v>-0.76033600000000012</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -8135,17 +8570,26 @@
       <c r="M49" s="151">
         <v>0</v>
       </c>
-      <c r="N49" s="174"/>
-      <c r="O49" s="171">
+      <c r="N49" s="151">
+        <v>0</v>
+      </c>
+      <c r="O49" s="151">
+        <v>0</v>
+      </c>
+      <c r="P49" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="174"/>
+      <c r="R49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P49" s="149">
+      <c r="S49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -8183,17 +8627,26 @@
       <c r="M50" s="151">
         <v>18690</v>
       </c>
-      <c r="N50" s="174"/>
-      <c r="O50" s="171">
+      <c r="N50" s="151">
+        <v>5200</v>
+      </c>
+      <c r="O50" s="151">
+        <v>14401</v>
+      </c>
+      <c r="P50" s="151">
+        <v>-27401</v>
+      </c>
+      <c r="Q50" s="174"/>
+      <c r="R50" s="171">
         <f t="shared" si="2"/>
-        <v>18928</v>
-      </c>
-      <c r="P50" s="149">
+        <v>11128</v>
+      </c>
+      <c r="S50" s="149">
         <f t="shared" si="3"/>
-        <v>0.37856000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.22256000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -8231,17 +8684,26 @@
       <c r="M51" s="151">
         <v>40800</v>
       </c>
-      <c r="N51" s="174"/>
-      <c r="O51" s="171">
+      <c r="N51" s="151">
+        <v>-7308</v>
+      </c>
+      <c r="O51" s="151">
+        <v>153270</v>
+      </c>
+      <c r="P51" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="174"/>
+      <c r="R51" s="171">
         <f t="shared" si="2"/>
-        <v>-111473</v>
-      </c>
-      <c r="P51" s="149">
+        <v>34489</v>
+      </c>
+      <c r="S51" s="149">
         <f t="shared" si="3"/>
-        <v>-0.17149692307692307</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+        <v>5.3060000000000003E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -8279,17 +8741,26 @@
       <c r="M52" s="151">
         <v>-540</v>
       </c>
-      <c r="N52" s="174"/>
-      <c r="O52" s="171">
+      <c r="N52" s="151">
+        <v>0</v>
+      </c>
+      <c r="O52" s="151">
+        <v>0</v>
+      </c>
+      <c r="P52" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="174"/>
+      <c r="R52" s="171">
         <f t="shared" si="2"/>
         <v>-158276</v>
       </c>
-      <c r="P52" s="149">
+      <c r="S52" s="149">
         <f t="shared" si="3"/>
         <v>-1.266208</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -8327,17 +8798,26 @@
       <c r="M53" s="151">
         <v>-30409</v>
       </c>
-      <c r="N53" s="174"/>
-      <c r="O53" s="171">
+      <c r="N53" s="151">
+        <v>0</v>
+      </c>
+      <c r="O53" s="151">
+        <v>-41730</v>
+      </c>
+      <c r="P53" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="174"/>
+      <c r="R53" s="171">
         <f t="shared" si="2"/>
-        <v>-137050</v>
-      </c>
-      <c r="P53" s="149">
+        <v>-178780</v>
+      </c>
+      <c r="S53" s="149">
         <f t="shared" si="3"/>
-        <v>-0.45683333333333337</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+        <v>-0.59593333333333343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -8373,17 +8853,26 @@
       <c r="M54" s="151">
         <v>3265</v>
       </c>
-      <c r="N54" s="174"/>
-      <c r="O54" s="171">
+      <c r="N54" s="151">
+        <v>0</v>
+      </c>
+      <c r="O54" s="151">
+        <v>0</v>
+      </c>
+      <c r="P54" s="151">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="174"/>
+      <c r="R54" s="171">
         <f t="shared" si="2"/>
         <v>11400</v>
       </c>
-      <c r="P54" s="149">
+      <c r="S54" s="149">
         <f t="shared" si="3"/>
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -8419,17 +8908,26 @@
       <c r="M55" s="151">
         <v>14300</v>
       </c>
-      <c r="N55" s="174"/>
-      <c r="O55" s="171">
+      <c r="N55" s="151">
+        <v>-7772</v>
+      </c>
+      <c r="O55" s="151">
+        <v>-89336</v>
+      </c>
+      <c r="P55" s="151">
+        <v>9600</v>
+      </c>
+      <c r="Q55" s="174"/>
+      <c r="R55" s="171">
         <f t="shared" si="2"/>
-        <v>91446</v>
-      </c>
-      <c r="P55" s="149">
+        <v>3938</v>
+      </c>
+      <c r="S55" s="149">
         <f t="shared" si="3"/>
-        <v>0.182892</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7.8759999999999993E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -8438,43 +8936,55 @@
       <c r="F56" s="115"/>
       <c r="G56" s="16"/>
       <c r="H56" s="254">
-        <f>SUM(H4:H55)</f>
+        <f t="shared" ref="H56:P56" si="4">SUM(H4:H55)</f>
         <v>-2118400</v>
       </c>
       <c r="I56" s="254">
-        <f>SUM(I4:I55)</f>
+        <f t="shared" si="4"/>
         <v>-531590</v>
       </c>
       <c r="J56" s="254">
-        <f>SUM(J4:J55)</f>
+        <f t="shared" si="4"/>
         <v>141562</v>
       </c>
       <c r="K56" s="254">
-        <f>SUM(K4:K55)</f>
+        <f t="shared" si="4"/>
         <v>-88507</v>
       </c>
       <c r="L56" s="254">
-        <f>SUM(L4:L55)</f>
+        <f t="shared" si="4"/>
         <v>206563</v>
       </c>
       <c r="M56" s="254">
-        <f>SUM(M4:M55)</f>
+        <f t="shared" si="4"/>
         <v>507837</v>
       </c>
       <c r="N56" s="254">
-        <f>SUM(N4:N55)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-959041</v>
       </c>
       <c r="O56" s="254">
+        <f t="shared" si="4"/>
+        <v>-558306</v>
+      </c>
+      <c r="P56" s="254">
+        <f t="shared" si="4"/>
+        <v>-539685</v>
+      </c>
+      <c r="Q56" s="254">
+        <f>SUM(Q4:Q55)</f>
+        <v>0</v>
+      </c>
+      <c r="R56" s="254">
         <f t="shared" si="2"/>
-        <v>-1882535</v>
-      </c>
-      <c r="P56" s="255">
+        <v>-3939567</v>
+      </c>
+      <c r="S56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -8490,9 +9000,12 @@
       <c r="M57" s="250"/>
       <c r="N57" s="250"/>
       <c r="O57" s="250"/>
-      <c r="P57" s="252"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P57" s="250"/>
+      <c r="Q57" s="250"/>
+      <c r="R57" s="250"/>
+      <c r="S57" s="252"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -8530,18 +9043,27 @@
       <c r="M58" s="162">
         <v>77900</v>
       </c>
-      <c r="N58" s="246"/>
-      <c r="O58" s="247">
-        <f>SUM(H58:N58)</f>
-        <v>-306880</v>
-      </c>
-      <c r="P58" s="248">
-        <f>IFERROR(O58/F58*100,0)/10000000</f>
-        <v>-1.0229333333333333</v>
-      </c>
-      <c r="S58" s="134"/>
-    </row>
-    <row r="59" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N58" s="162">
+        <v>19032</v>
+      </c>
+      <c r="O58" s="162">
+        <v>53520</v>
+      </c>
+      <c r="P58" s="162">
+        <v>-49300</v>
+      </c>
+      <c r="Q58" s="246"/>
+      <c r="R58" s="247">
+        <f>SUM(H58:Q58)</f>
+        <v>-283628</v>
+      </c>
+      <c r="S58" s="248">
+        <f>IFERROR(R58/F58*100,0)/10000000</f>
+        <v>-0.94542666666666675</v>
+      </c>
+      <c r="V58" s="134"/>
+    </row>
+    <row r="59" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -8577,18 +9099,27 @@
       <c r="M59" s="162">
         <v>377300</v>
       </c>
-      <c r="N59" s="174"/>
-      <c r="O59" s="171">
-        <f>SUM(H59:N59)</f>
-        <v>135116</v>
-      </c>
-      <c r="P59" s="149">
-        <f>IFERROR(O59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="R59" s="134"/>
-    </row>
-    <row r="60" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="162">
+        <v>0</v>
+      </c>
+      <c r="O59" s="162">
+        <v>0</v>
+      </c>
+      <c r="P59" s="162">
+        <v>-500</v>
+      </c>
+      <c r="Q59" s="174"/>
+      <c r="R59" s="171">
+        <f>SUM(H59:Q59)</f>
+        <v>134616</v>
+      </c>
+      <c r="S59" s="149">
+        <f>IFERROR(R59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="U59" s="134"/>
+    </row>
+    <row r="60" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -8597,149 +9128,161 @@
       <c r="F60" s="74"/>
       <c r="G60" s="17"/>
       <c r="H60" s="170">
-        <f>SUM(H58:H59)</f>
+        <f t="shared" ref="H60:P60" si="5">SUM(H58:H59)</f>
         <v>-616080</v>
       </c>
       <c r="I60" s="170">
-        <f>SUM(I58:I59)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J60" s="170">
-        <f>SUM(J58:J59)</f>
+        <f t="shared" si="5"/>
         <v>-17480</v>
       </c>
       <c r="K60" s="170">
-        <f>SUM(K58:K59)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L60" s="170">
-        <f>SUM(L58:L59)</f>
+        <f t="shared" si="5"/>
         <v>6596</v>
       </c>
       <c r="M60" s="170">
-        <f>SUM(M58:M59)</f>
+        <f t="shared" si="5"/>
         <v>455200</v>
       </c>
       <c r="N60" s="170">
-        <f>SUM(N58:N59)</f>
-        <v>0</v>
-      </c>
-      <c r="O60" s="254">
-        <f>SUM(H60:N60)</f>
-        <v>-171764</v>
-      </c>
-      <c r="P60" s="19"/>
-      <c r="R60" s="5"/>
-      <c r="S60" s="134"/>
-      <c r="T60" s="237"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R61" s="134"/>
-      <c r="S61" s="134"/>
-      <c r="T61" s="237"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R62" s="134"/>
-      <c r="S62" s="134"/>
-      <c r="T62" s="237"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R63" s="134"/>
-      <c r="S63" s="134"/>
-      <c r="T63" s="237"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="R64" s="134"/>
-      <c r="S64" s="134"/>
-      <c r="T64" s="237"/>
-    </row>
-    <row r="65" spans="18:20" x14ac:dyDescent="0.25">
-      <c r="R65" s="134"/>
-      <c r="S65" s="237"/>
-      <c r="T65" s="237"/>
-    </row>
-    <row r="66" spans="18:20" x14ac:dyDescent="0.25">
-      <c r="R66" s="237"/>
-      <c r="S66" s="237"/>
-      <c r="T66" s="237"/>
+        <f t="shared" si="5"/>
+        <v>19032</v>
+      </c>
+      <c r="O60" s="170">
+        <f t="shared" si="5"/>
+        <v>53520</v>
+      </c>
+      <c r="P60" s="170">
+        <f t="shared" si="5"/>
+        <v>-49800</v>
+      </c>
+      <c r="Q60" s="170">
+        <f>SUM(Q58:Q59)</f>
+        <v>0</v>
+      </c>
+      <c r="R60" s="254">
+        <f>SUM(H60:Q60)</f>
+        <v>-149012</v>
+      </c>
+      <c r="S60" s="19"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="134"/>
+      <c r="W60" s="237"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U61" s="134"/>
+      <c r="V61" s="134"/>
+      <c r="W61" s="237"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U62" s="134"/>
+      <c r="V62" s="134"/>
+      <c r="W62" s="237"/>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U63" s="134"/>
+      <c r="V63" s="134"/>
+      <c r="W63" s="237"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U64" s="134"/>
+      <c r="V64" s="134"/>
+      <c r="W64" s="237"/>
+    </row>
+    <row r="65" spans="21:23" x14ac:dyDescent="0.25">
+      <c r="U65" s="134"/>
+      <c r="V65" s="237"/>
+      <c r="W65" s="237"/>
+    </row>
+    <row r="66" spans="21:23" x14ac:dyDescent="0.25">
+      <c r="U66" s="237"/>
+      <c r="V66" s="237"/>
+      <c r="W66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 P56:P57 O55:P55 P60 O43:P43 O5:P10 O24:P25 H2:P3 A58:P59 A37:O37 P11:P21 O11:O22 O45:P53 O27:O36 P27:P35 A4:N36 O38:O41 A38:N39 G40:N40 A41:N56 A60:N60">
+  <conditionalFormatting sqref="G2 A3:G3 S56:S57 R55:S55 S60 R43:S43 R5:S10 R24:S25 H2:S3 A58:S59 A37:R37 S11:S21 R11:R22 R45:S53 R27:R36 S27:S35 A4:Q36 R38:R41 A38:Q39 G40:Q40 A41:Q56 A60:Q60">
     <cfRule type="expression" dxfId="448" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P36">
+  <conditionalFormatting sqref="S36">
     <cfRule type="expression" dxfId="447" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P39:P40">
+  <conditionalFormatting sqref="S39:S40">
     <cfRule type="expression" dxfId="446" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:P4">
+  <conditionalFormatting sqref="R4:S4">
     <cfRule type="expression" dxfId="445" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P38">
+  <conditionalFormatting sqref="S38">
     <cfRule type="expression" dxfId="444" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P22">
+  <conditionalFormatting sqref="S22">
     <cfRule type="expression" dxfId="443" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O56">
+  <conditionalFormatting sqref="R56">
     <cfRule type="expression" dxfId="442" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P41">
+  <conditionalFormatting sqref="S41">
     <cfRule type="expression" dxfId="441" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O26:P26">
+  <conditionalFormatting sqref="R26:S26">
     <cfRule type="expression" dxfId="440" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O54:P54">
+  <conditionalFormatting sqref="R54:S54">
     <cfRule type="expression" dxfId="439" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O44:P44">
+  <conditionalFormatting sqref="R44:S44">
     <cfRule type="expression" dxfId="438" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O60">
+  <conditionalFormatting sqref="R60">
     <cfRule type="expression" dxfId="437" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O42:P42">
+  <conditionalFormatting sqref="R42:S42">
     <cfRule type="expression" dxfId="436" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O23">
+  <conditionalFormatting sqref="R23">
     <cfRule type="expression" dxfId="435" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P23">
+  <conditionalFormatting sqref="S23">
     <cfRule type="expression" dxfId="434" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P37">
+  <conditionalFormatting sqref="S37">
     <cfRule type="expression" dxfId="433" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -21817,20 +22360,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>1000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-49861</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.02</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.99722</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-26044</v>
+        <v>-76905</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-0.52088000000000001</v>
+        <v>-1.5381</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -21869,20 +22412,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>25614</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-96366</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>8.5379999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.32122000000000001</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-225357</v>
+        <v>-347337</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-0.75119000000000002</v>
+        <v>-1.1577900000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -21921,20 +22464,20 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>11900</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-6830</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.11899999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-6.83E-2</v>
       </c>
       <c r="M6" s="71">
         <f t="shared" ref="M6:M7" si="1">G6+I6+K6</f>
-        <v>128085</v>
+        <v>109355</v>
       </c>
       <c r="N6" s="166">
         <f t="shared" ref="N6:N7" si="2">H6+J6+L6</f>
-        <v>1.28085</v>
+        <v>1.09355</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -21971,11 +22514,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="71">
@@ -22023,20 +22566,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>27367</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-57041</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>9.1223333333333337E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.19013666666666668</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-427730</v>
+        <v>-512138</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4257666666666666</v>
+        <v>-1.7071266666666667</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -22075,20 +22618,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>94829</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>82393</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.63219333333333338</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.54928666666666659</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-199307</v>
+        <v>-211743</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.3287133333333336</v>
+        <v>-1.4116200000000005</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -22127,20 +22670,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>21771</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>31737</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.36285000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.52895000000000003</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-170478</v>
+        <v>-160512</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-2.8413000000000004</v>
+        <v>-2.6752000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -22179,20 +22722,20 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-238640</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-429086</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.15909333333333334</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.28605733333333333</v>
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>728625</v>
+        <v>538179</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.48575000000000013</v>
+        <v>0.3587860000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -22231,20 +22774,20 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-119511</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-119861</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.199185</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.19976833333333333</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>288269</v>
+        <v>287919</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.48044833333333342</v>
+        <v>0.4798650000000001</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -22283,20 +22826,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-4565</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-7451</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-4.5650000000000003E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-7.4510000000000007E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>8851</v>
+        <v>5965</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>8.8510000000000005E-2</v>
+        <v>5.9649999999999995E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -22335,20 +22878,20 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>13554</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>22668</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>5.4216E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>9.0672000000000016E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>58474</v>
+        <v>67588</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.23389599999999994</v>
+        <v>0.27035199999999998</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -22387,11 +22930,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -22439,20 +22982,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-2647</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-4367</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-2.647E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-4.367E-2</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>70760</v>
+        <v>69040</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.70760000000000001</v>
+        <v>0.69040000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -22491,20 +23034,20 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>13349</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>21766</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>6.0677272727272719E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>9.8936363636363628E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-74559</v>
+        <v>-66142</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.3389045454545454</v>
+        <v>-0.30064545454545455</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -22543,20 +23086,20 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-32641</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.13056400000000001</v>
       </c>
       <c r="M18" s="71">
         <f t="shared" si="0"/>
-        <v>-63917</v>
+        <v>-96558</v>
       </c>
       <c r="N18" s="166">
         <f t="shared" si="0"/>
-        <v>-0.25566800000000001</v>
+        <v>-0.38623200000000002</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -22595,20 +23138,20 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-57</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-48057</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-1.4249999999999999E-4</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.1201425</v>
       </c>
       <c r="M19" s="71">
         <f t="shared" si="0"/>
-        <v>267258</v>
+        <v>219258</v>
       </c>
       <c r="N19" s="166">
         <f t="shared" si="0"/>
-        <v>0.66814499999999988</v>
+        <v>0.54814499999999988</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -22647,20 +23190,20 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>312</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>7305</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>2.8363636363636364E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>6.6409090909090904E-2</v>
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>87994</v>
+        <v>94987</v>
       </c>
       <c r="N20" s="166">
         <f t="shared" si="0"/>
-        <v>0.7999454545454544</v>
+        <v>0.86351818181818163</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -22699,20 +23242,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>5990</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>3598</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.23960000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.14391999999999999</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-37556</v>
+        <v>-39948</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-1.5022399999999998</v>
+        <v>-1.5979199999999998</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -22751,11 +23294,11 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>1007</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>5.0350000000000004E-3</v>
       </c>
       <c r="M22" s="71">
@@ -22803,20 +23346,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>48857</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-140506</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.3257133333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.9367066666666668</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>163870</v>
+        <v>-25493</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>1.0924666666666667</v>
+        <v>-0.1699533333333334</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -22855,11 +23398,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -22907,20 +23450,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>29767</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>25929</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.27060909090909085</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.2357181818181818</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>234471</v>
+        <v>230633</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>2.131554545454545</v>
+        <v>2.096663636363636</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -22959,20 +23502,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-723512</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-1027123</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-3.1457043478260873</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-4.4657521739130441</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-369451</v>
+        <v>-673062</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6063086956521748</v>
+        <v>-2.9263565217391316</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -23009,20 +23552,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>6768</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>5794</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.33839999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.28970000000000001</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-13528</v>
+        <v>-14502</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.67639999999999989</v>
+        <v>-0.72509999999999986</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -23061,20 +23604,20 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>48100</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-47000</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>9.6199999999999994E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-9.4E-2</v>
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>-216818</v>
+        <v>-311918</v>
       </c>
       <c r="N28" s="166">
         <f t="shared" si="0"/>
-        <v>-0.43363599999999997</v>
+        <v>-0.62383599999999995</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -23113,20 +23656,20 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-26495</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-460666</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-2.6495000000000001E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.46066600000000002</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>3440917</v>
+        <v>3006746</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>3.4409169999999998</v>
+        <v>3.0067459999999997</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -23166,11 +23709,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -23218,11 +23761,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -23270,11 +23813,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -23322,11 +23865,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -23374,11 +23917,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -23426,20 +23969,20 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-218783</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-308883</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.43756600000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.61776600000000004</v>
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>481069</v>
+        <v>390969</v>
       </c>
       <c r="N35" s="166">
         <f t="shared" si="0"/>
-        <v>0.96213799999999983</v>
+        <v>0.7819379999999998</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -23478,20 +24021,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>145853</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>147515</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.29170600000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.29503000000000001</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>1173260</v>
+        <v>1174922</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>2.3465199999999999</v>
+        <v>2.349844</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -23530,20 +24073,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-73137</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-145944</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-1.4627399999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-2.9188800000000001</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-152501</v>
+        <v>-225308</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-3.05002</v>
+        <v>-4.5061600000000004</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -23582,20 +24125,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>33096</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>95813</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.82740000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>2.3953250000000001</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-32429</v>
+        <v>30288</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>-0.81072499999999981</v>
+        <v>0.75720000000000032</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -23634,11 +24177,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -23686,11 +24229,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -23738,20 +24281,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-76895</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-126402</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.19223750000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.31600499999999998</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>634041</v>
+        <v>584534</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.5851025000000001</v>
+        <v>1.4613350000000001</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -23790,20 +24333,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-20999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-88079</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.20999000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.88078999999999996</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>182633</v>
+        <v>115553</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>1.82633</v>
+        <v>1.1555299999999999</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -23840,11 +24383,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -23892,20 +24435,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-4548</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-16088</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-9.0959999999999999E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.32175999999999999</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-70931</v>
+        <v>-82471</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4186199999999998</v>
+        <v>-1.6494199999999999</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -23944,20 +24487,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-47655</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-2278</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.15884999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-7.5933333333333339E-3</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-158447</v>
+        <v>-113070</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.52815666666666661</v>
+        <v>-0.37690000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -23996,11 +24539,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -24048,11 +24591,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -24098,20 +24641,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-2882</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-39779</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.28820000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-3.9779</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>-19814</v>
+        <v>-56711</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>-1.9814000000000001</v>
+        <v>-5.6711</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -24150,20 +24693,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-3868</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-11097</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-7.7359999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.22194</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>30460</v>
+        <v>23231</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.28860000000000002</v>
+        <v>0.14402000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -24202,20 +24745,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-8877</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-133607</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-8.8770000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-1.3360700000000001</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>878497</v>
+        <v>753767</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>8.7849699999999995</v>
+        <v>7.5376699999999994</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -24252,20 +24795,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>9151</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>546</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.91510000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>5.4600000000000003E-2</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>5605</v>
+        <v>-3000</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.5605</v>
+        <v>-0.30000000000000004</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -24304,20 +24847,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>28891</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>255502</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>9.6303333333333338E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.85167333333333317</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>20158</v>
+        <v>246769</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>6.7193333333333369E-2</v>
+        <v>0.8225633333333332</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -24350,11 +24893,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -24402,11 +24945,11 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>-156125</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>-0.39031250000000001</v>
       </c>
       <c r="M54" s="71">
@@ -24454,20 +24997,20 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-66605</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-73205</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.16651250000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.18301249999999999</v>
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>275669</v>
+        <v>269069</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>0.68917249999999997</v>
+        <v>0.6726724999999999</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -24504,20 +25047,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-392525</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-760336</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.39252500000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.76033600000000012</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1427605</v>
+        <v>-1795416</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.427705</v>
+        <v>-1.7955160000000001</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -24550,11 +25093,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -24602,20 +25145,20 @@
         <v>-0.14384</v>
       </c>
       <c r="K58" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>18928</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>11128</v>
       </c>
       <c r="L58" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.37856000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>0.22256000000000001</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-15367</v>
+        <v>-23167</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-0.30733999999999995</v>
+        <v>-0.46333999999999997</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -24654,20 +25197,20 @@
         <v>0.10279846153846153</v>
       </c>
       <c r="K59" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-111473</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>34489</v>
       </c>
       <c r="L59" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.17149692307692307</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>5.3060000000000003E-2</v>
       </c>
       <c r="M59" s="71">
         <f t="shared" si="0"/>
-        <v>832471</v>
+        <v>978433</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" si="0"/>
-        <v>2.1241140384615385</v>
+        <v>2.3486709615384616</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -24706,11 +25249,11 @@
         <v>-0.20608799999999999</v>
       </c>
       <c r="K60" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>-158276</v>
       </c>
       <c r="L60" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>-1.266208</v>
       </c>
       <c r="M60" s="71">
@@ -24758,20 +25301,20 @@
         <v>-0.86802666666666684</v>
       </c>
       <c r="K61" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-137050</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-178780</v>
       </c>
       <c r="L61" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-0.45683333333333337</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.59593333333333343</v>
       </c>
       <c r="M61" s="71">
         <f t="shared" si="0"/>
-        <v>567023</v>
+        <v>525293</v>
       </c>
       <c r="N61" s="166">
         <f t="shared" si="0"/>
-        <v>1.8900766666666668</v>
+        <v>1.7509766666666668</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -24810,11 +25353,11 @@
         <v>-0.31176799999999999</v>
       </c>
       <c r="K62" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L62" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M62" s="71">
@@ -24860,11 +25403,11 @@
         <v>0.55113999999999996</v>
       </c>
       <c r="K63" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>11400</v>
       </c>
       <c r="L63" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="M63" s="71">
@@ -24910,20 +25453,20 @@
         <v>0.43251600000000001</v>
       </c>
       <c r="K64" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>91446</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>3938</v>
       </c>
       <c r="L64" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>0.182892</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>7.8759999999999993E-3</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>580851</v>
+        <v>493343</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>1.161702</v>
+        <v>0.98668599999999995</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -24945,12 +25488,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-2009021</v>
+        <v>-3978545</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>9771016</v>
+        <v>7801492</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -25030,20 +25573,20 @@
         <v>0.2384333333333333</v>
       </c>
       <c r="K69" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-306880</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-283628</v>
       </c>
       <c r="L69" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>-1.0229333333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>-0.94542666666666675</v>
       </c>
       <c r="M69" s="153">
         <f t="shared" ref="M69:N69" si="29">G69+I69+K69</f>
-        <v>379630</v>
+        <v>402882</v>
       </c>
       <c r="N69" s="167">
         <f t="shared" si="29"/>
-        <v>1.2654333333333339</v>
+        <v>1.3429400000000005</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -25080,16 +25623,16 @@
         <v>0</v>
       </c>
       <c r="K70" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
-        <v>135116</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <v>134616</v>
       </c>
       <c r="L70" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADQ$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DR$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="153">
         <f t="shared" ref="M70" si="30">G70+I70+K70</f>
-        <v>1304001</v>
+        <v>1303501</v>
       </c>
       <c r="N70" s="167">
         <f t="shared" ref="N70" si="31">H70+J70+L70</f>
@@ -25109,12 +25652,12 @@
       <c r="J71" s="104"/>
       <c r="K71" s="93">
         <f>SUM(K69:K70)</f>
-        <v>-171764</v>
+        <v>-149012</v>
       </c>
       <c r="L71" s="113"/>
       <c r="M71" s="93">
         <f>SUM(M69:M70)</f>
-        <v>1683631</v>
+        <v>1706383</v>
       </c>
       <c r="N71" s="236"/>
     </row>
@@ -43846,11 +44389,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-26044</v>
+        <v>-76905</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.52088000000000001</v>
+        <v>-1.5381</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -43867,11 +44410,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-74380</v>
+        <v>-125241</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-1.4876</v>
+        <v>-2.50482</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43928,11 +44471,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-225357</v>
+        <v>-347337</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.75119000000000002</v>
+        <v>-1.1577900000000001</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -43949,11 +44492,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>1108917</v>
+        <v>986937</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.6963900000000001</v>
+        <v>3.28979</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44010,11 +44553,11 @@
       <c r="O8" s="215"/>
       <c r="P8" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>128085</v>
+        <v>109355</v>
       </c>
       <c r="Q8" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.28085</v>
+        <v>1.09355</v>
       </c>
       <c r="R8" s="159"/>
       <c r="S8" s="153">
@@ -44031,11 +44574,11 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="154">
         <f t="shared" si="0"/>
-        <v>-257342</v>
+        <v>-276072</v>
       </c>
       <c r="Z8" s="168">
         <f t="shared" si="1"/>
-        <v>-2.57342</v>
+        <v>-2.7607200000000001</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44125,11 +44668,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-427730</v>
+        <v>-512138</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4257666666666666</v>
+        <v>-1.7071266666666667</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -44145,11 +44688,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-786639</v>
+        <v>-871047</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-4.0664466666666668</v>
+        <v>-4.347806666666667</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44206,11 +44749,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-199307</v>
+        <v>-211743</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.3287133333333336</v>
+        <v>-1.4116200000000005</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -44226,11 +44769,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-374269</v>
+        <v>-386705</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4951266666666667</v>
+        <v>-2.5780333333333338</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44287,11 +44830,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-170478</v>
+        <v>-160512</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-2.8413000000000004</v>
+        <v>-2.6752000000000002</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -44307,11 +44850,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-170478</v>
+        <v>-160512</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-2.8413000000000004</v>
+        <v>-2.6752000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44368,11 +44911,11 @@
       <c r="O13" s="215"/>
       <c r="P13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>728625</v>
+        <v>538179</v>
       </c>
       <c r="Q13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.48575000000000013</v>
+        <v>0.3587860000000001</v>
       </c>
       <c r="R13" s="159"/>
       <c r="S13" s="88">
@@ -44389,11 +44932,11 @@
       <c r="X13"/>
       <c r="Y13" s="154">
         <f t="shared" si="0"/>
-        <v>-639574</v>
+        <v>-830020</v>
       </c>
       <c r="Z13" s="168">
         <f t="shared" si="1"/>
-        <v>-0.42638266666666658</v>
+        <v>-0.55334666666666665</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44777,11 +45320,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>288269</v>
+        <v>287919</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.48044833333333342</v>
+        <v>0.4798650000000001</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -44797,11 +45340,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>92935</v>
+        <v>92585</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.9371716666666665</v>
+        <v>-2.9377549999999997</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44858,11 +45401,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8851</v>
+        <v>5965</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8.8510000000000005E-2</v>
+        <v>5.9649999999999995E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -44878,11 +45421,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>12530</v>
+        <v>9644</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>0.12530000000000002</v>
+        <v>9.6439999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45029,11 +45572,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>58474</v>
+        <v>67588</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.23389599999999994</v>
+        <v>0.27035199999999998</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -45049,11 +45592,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-208942</v>
+        <v>-199828</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.440264</v>
+        <v>-2.4038080000000002</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45110,11 +45653,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-74559</v>
+        <v>-66142</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.3389045454545454</v>
+        <v>-0.30064545454545455</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -45130,11 +45673,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-163459</v>
+        <v>-155042</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.2279045454545454</v>
+        <v>-1.1896454545454547</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45272,11 +45815,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>70760</v>
+        <v>69040</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.70760000000000001</v>
+        <v>0.69040000000000001</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -45292,11 +45835,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1786105</v>
+        <v>1784385</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.861049999999999</v>
+        <v>17.84385</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45594,11 +46137,11 @@
       <c r="O28" s="215"/>
       <c r="P28" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-63917</v>
+        <v>-96558</v>
       </c>
       <c r="Q28" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.25566800000000001</v>
+        <v>-0.38623200000000002</v>
       </c>
       <c r="R28" s="159"/>
       <c r="S28" s="88">
@@ -45614,11 +46157,11 @@
       <c r="W28" s="72"/>
       <c r="Y28" s="154">
         <f t="shared" si="0"/>
-        <v>294296</v>
+        <v>261655</v>
       </c>
       <c r="Z28" s="168">
         <f t="shared" si="1"/>
-        <v>1.177184</v>
+        <v>1.0466199999999999</v>
       </c>
     </row>
     <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45675,11 +46218,11 @@
       <c r="O29" s="215"/>
       <c r="P29" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>267258</v>
+        <v>219258</v>
       </c>
       <c r="Q29" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.66814499999999988</v>
+        <v>0.54814499999999988</v>
       </c>
       <c r="R29" s="159"/>
       <c r="S29" s="88">
@@ -45696,11 +46239,11 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="154">
         <f t="shared" si="0"/>
-        <v>937721</v>
+        <v>889721</v>
       </c>
       <c r="Z29" s="168">
         <f t="shared" si="1"/>
-        <v>2.3443025</v>
+        <v>2.2243024999999998</v>
       </c>
     </row>
     <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45757,11 +46300,11 @@
       <c r="O30" s="215"/>
       <c r="P30" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>87994</v>
+        <v>94987</v>
       </c>
       <c r="Q30" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.7999454545454544</v>
+        <v>0.86351818181818163</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="88">
@@ -45778,11 +46321,11 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="154">
         <f t="shared" si="0"/>
-        <v>87712</v>
+        <v>94705</v>
       </c>
       <c r="Z30" s="168">
         <f t="shared" si="1"/>
-        <v>0.79738181818181808</v>
+        <v>0.86095454545454531</v>
       </c>
     </row>
     <row r="31" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45928,11 +46471,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>163870</v>
+        <v>-25493</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.0924666666666667</v>
+        <v>-0.1699533333333334</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -45949,11 +46492,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-341199</v>
+        <v>-530562</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-2.2746600000000008</v>
+        <v>-3.5370800000000009</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46091,11 +46634,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>234471</v>
+        <v>230633</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.131554545454545</v>
+        <v>2.096663636363636</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -46111,11 +46654,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-84469</v>
+        <v>-88307</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.76790000000000003</v>
+        <v>-0.80279090909090911</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -46260,11 +46803,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-369451</v>
+        <v>-673062</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6063086956521748</v>
+        <v>-2.9263565217391316</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -46280,11 +46823,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>3791652</v>
+        <v>3488041</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>16.485443478260869</v>
+        <v>15.165395652173912</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46339,11 +46882,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-13528</v>
+        <v>-14502</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.67639999999999989</v>
+        <v>-0.72509999999999986</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -46359,11 +46902,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-13528</v>
+        <v>-14502</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.67639999999999989</v>
+        <v>-0.72509999999999986</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46420,11 +46963,11 @@
       <c r="O38" s="215"/>
       <c r="P38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-216818</v>
+        <v>-311918</v>
       </c>
       <c r="Q38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.43363599999999997</v>
+        <v>-0.62383599999999995</v>
       </c>
       <c r="R38" s="159"/>
       <c r="S38" s="88">
@@ -46440,11 +46983,11 @@
       <c r="W38" s="72"/>
       <c r="Y38" s="154">
         <f t="shared" si="0"/>
-        <v>2849588</v>
+        <v>2754488</v>
       </c>
       <c r="Z38" s="168">
         <f t="shared" si="1"/>
-        <v>5.6991759999999996</v>
+        <v>5.5089759999999997</v>
       </c>
     </row>
     <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46501,11 +47044,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3440917</v>
+        <v>3006746</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.4409169999999998</v>
+        <v>3.0067459999999997</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -46522,11 +47065,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>7034323</v>
+        <v>6600152</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>7.0343230000000005</v>
+        <v>6.6001519999999996</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -47017,11 +47560,11 @@
       <c r="O45" s="215"/>
       <c r="P45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>481069</v>
+        <v>390969</v>
       </c>
       <c r="Q45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.96213799999999983</v>
+        <v>0.7819379999999998</v>
       </c>
       <c r="R45" s="159"/>
       <c r="S45" s="88">
@@ -47037,11 +47580,11 @@
       <c r="W45" s="72"/>
       <c r="Y45" s="154">
         <f t="shared" si="22"/>
-        <v>1698387</v>
+        <v>1608287</v>
       </c>
       <c r="Z45" s="168">
         <f t="shared" si="23"/>
-        <v>3.3967739999999997</v>
+        <v>3.2165739999999996</v>
       </c>
     </row>
     <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47098,11 +47641,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1173260</v>
+        <v>1174922</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.3465199999999999</v>
+        <v>2.349844</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -47119,11 +47662,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>1125522</v>
+        <v>1127184</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>2.2510439999999998</v>
+        <v>2.2543679999999999</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -47181,11 +47724,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-152501</v>
+        <v>-225308</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.05002</v>
+        <v>-4.5061600000000004</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -47201,11 +47744,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-35606</v>
+        <v>-108413</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-0.71212000000000009</v>
+        <v>-2.1682600000000005</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -47350,11 +47893,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-32429</v>
+        <v>30288</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.81072499999999981</v>
+        <v>0.75720000000000032</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -47370,11 +47913,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>-44257</v>
+        <v>18460</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>-1.1064249999999998</v>
+        <v>0.46150000000000024</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -47605,11 +48148,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>634041</v>
+        <v>584534</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.5851025000000001</v>
+        <v>1.4613350000000001</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -47625,11 +48168,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>233742</v>
+        <v>184235</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.58435499999999996</v>
+        <v>0.46058749999999993</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47686,11 +48229,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>182633</v>
+        <v>115553</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.82633</v>
+        <v>1.1555299999999999</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -47706,11 +48249,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>928426</v>
+        <v>861346</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>9.2842600000000015</v>
+        <v>8.6134600000000017</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47848,11 +48391,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-70931</v>
+        <v>-82471</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4186199999999998</v>
+        <v>-1.6494199999999999</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -47869,11 +48412,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-316709</v>
+        <v>-328249</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.3341799999999999</v>
+        <v>-6.5649800000000003</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -47931,11 +48474,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-158447</v>
+        <v>-113070</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.52815666666666661</v>
+        <v>-0.37690000000000001</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -47951,11 +48494,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4857422</v>
+        <v>-4812045</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.191406666666669</v>
+        <v>-16.040150000000004</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -48185,11 +48728,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>30460</v>
+        <v>23231</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.28860000000000002</v>
+        <v>0.14402000000000001</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -48206,11 +48749,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>67183</v>
+        <v>59954</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.61743333333333328</v>
+        <v>0.47285333333333335</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -48274,11 +48817,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>878497</v>
+        <v>753767</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8.7849699999999995</v>
+        <v>7.5376699999999994</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -48294,11 +48837,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>4428566</v>
+        <v>4303836</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>44.28566</v>
+        <v>43.038359999999997</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -48360,11 +48903,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5605</v>
+        <v>-3000</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.5605</v>
+        <v>-0.30000000000000004</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -48380,11 +48923,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>5605</v>
+        <v>-3000</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.5605</v>
+        <v>-0.30000000000000004</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48441,11 +48984,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>20158</v>
+        <v>246769</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>6.7193333333333369E-2</v>
+        <v>0.8225633333333332</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -48461,11 +49004,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>693007</v>
+        <v>919618</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>2.3100233333333331</v>
+        <v>3.0653933333333327</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -48692,11 +49235,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>275669</v>
+        <v>269069</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.68917249999999997</v>
+        <v>0.6726724999999999</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -48713,11 +49256,11 @@
       <c r="X65" s="132"/>
       <c r="Y65" s="154">
         <f t="shared" si="22"/>
-        <v>800081</v>
+        <v>793481</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" si="23"/>
-        <v>2.0002025000000003</v>
+        <v>1.9837025000000001</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48854,11 +49397,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1427605</v>
+        <v>-1795416</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.427705</v>
+        <v>-1.7955160000000001</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -48874,11 +49417,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1427605</v>
+        <v>-1795416</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.427705</v>
+        <v>-1.7955160000000001</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48992,11 +49535,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-15367</v>
+        <v>-23167</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.30733999999999995</v>
+        <v>-0.46333999999999997</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -49012,11 +49555,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-62021</v>
+        <v>-69821</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-1.2404199999999999</v>
+        <v>-1.39642</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -49073,11 +49616,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>832471</v>
+        <v>978433</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.1241140384615385</v>
+        <v>2.3486709615384616</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="153">
@@ -49093,11 +49636,11 @@
       <c r="W70" s="150"/>
       <c r="Y70" s="154">
         <f t="shared" si="22"/>
-        <v>424519</v>
+        <v>570481</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="23"/>
-        <v>1.1042340384615383</v>
+        <v>1.3287909615384614</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
@@ -49316,11 +49859,11 @@
       <c r="O73" s="215"/>
       <c r="P73" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>567023</v>
+        <v>525293</v>
       </c>
       <c r="Q73" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.8900766666666668</v>
+        <v>1.7509766666666668</v>
       </c>
       <c r="R73" s="159"/>
       <c r="S73" s="88">
@@ -49336,11 +49879,11 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="154">
         <f t="shared" si="22"/>
-        <v>399641</v>
+        <v>357911</v>
       </c>
       <c r="Z73" s="168">
         <f t="shared" si="23"/>
-        <v>1.332136666666667</v>
+        <v>1.193036666666667</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
@@ -49555,11 +50098,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>580851</v>
+        <v>493343</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.161702</v>
+        <v>0.98668599999999995</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -49575,11 +50118,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>580851</v>
+        <v>493343</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>1.161702</v>
+        <v>0.98668599999999995</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -49612,7 +50155,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>9811247</v>
+        <v>7881012</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -49623,7 +50166,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>29841198</v>
+        <v>27823455</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -49919,11 +50462,11 @@
       <c r="O82" s="167"/>
       <c r="P82" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>379630</v>
+        <v>402882</v>
       </c>
       <c r="Q82" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.2654333333333339</v>
+        <v>1.3429400000000005</v>
       </c>
       <c r="R82" s="159"/>
       <c r="S82" s="153">
@@ -49940,11 +50483,11 @@
       <c r="X82" s="132"/>
       <c r="Y82" s="52">
         <f t="shared" si="56"/>
-        <v>591130</v>
+        <v>614382</v>
       </c>
       <c r="Z82" s="53">
         <f t="shared" si="56"/>
-        <v>1.2654333333333339</v>
+        <v>1.3429400000000005</v>
       </c>
       <c r="AA82" s="132"/>
     </row>
@@ -50000,7 +50543,7 @@
       <c r="O83" s="167"/>
       <c r="P83" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1304001</v>
+        <v>1303501</v>
       </c>
       <c r="Q83" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
@@ -50020,7 +50563,7 @@
       <c r="W83" s="53"/>
       <c r="Y83" s="52">
         <f t="shared" ref="Y83" si="59">M83+P83+S83+V83</f>
-        <v>894001</v>
+        <v>893501</v>
       </c>
       <c r="Z83" s="53">
         <f t="shared" ref="Z83" si="60">N83+Q83+T83+W83</f>
@@ -50054,7 +50597,7 @@
       <c r="O84" s="123"/>
       <c r="P84" s="112">
         <f>SUM(P80:P83)</f>
-        <v>1683631</v>
+        <v>1706383</v>
       </c>
       <c r="Q84" s="123"/>
       <c r="R84" s="123"/>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="323">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2327,7 +2327,21 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="449">
+  <dxfs count="451">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5776,7 +5790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD66"/>
+  <dimension ref="A1:AG66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5786,21 +5800,21 @@
     <col min="5" max="5" width="9.42578125" style="133" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="133" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
-    <col min="8" max="15" width="13.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="13.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="11.28515625" style="133" customWidth="1"/>
-    <col min="18" max="18" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="9.140625" style="133" collapsed="1"/>
-    <col min="21" max="25" width="9.140625" style="133"/>
-    <col min="26" max="26" width="14.140625" style="133" customWidth="1"/>
-    <col min="27" max="27" width="12" style="133" customWidth="1"/>
-    <col min="28" max="28" width="15.85546875" style="133" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="133"/>
+    <col min="8" max="17" width="13.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="13.42578125" style="133" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="13.42578125" style="133" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" style="133" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="28" width="9.140625" style="133"/>
+    <col min="29" max="29" width="14.140625" style="133" customWidth="1"/>
+    <col min="30" max="30" width="12" style="133" customWidth="1"/>
+    <col min="31" max="31" width="15.85546875" style="133" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
@@ -5829,15 +5843,22 @@
       <c r="P2" s="256">
         <v>46276</v>
       </c>
-      <c r="Q2" s="183"/>
-      <c r="R2" s="184" t="s">
+      <c r="Q2" s="256">
+        <v>46280</v>
+      </c>
+      <c r="R2" s="256">
+        <v>46281</v>
+      </c>
+      <c r="S2" s="256"/>
+      <c r="T2" s="183"/>
+      <c r="U2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="S2" s="185" t="s">
+      <c r="V2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5884,17 +5905,24 @@
       <c r="P3" s="179" t="s">
         <v>322</v>
       </c>
-      <c r="Q3" s="180"/>
-      <c r="R3" s="189"/>
-      <c r="S3" s="180"/>
-      <c r="Z3" s="133" t="s">
+      <c r="Q3" s="179" t="s">
+        <v>233</v>
+      </c>
+      <c r="R3" s="179" t="s">
+        <v>237</v>
+      </c>
+      <c r="S3" s="179"/>
+      <c r="T3" s="180"/>
+      <c r="U3" s="189"/>
+      <c r="V3" s="180"/>
+      <c r="AC3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="AA3" s="133">
+      <c r="AD3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5941,23 +5969,28 @@
       <c r="P4" s="158">
         <v>-1063</v>
       </c>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="171">
-        <f t="shared" ref="R4:R30" si="0">SUM(H4:Q4)</f>
-        <v>-49861</v>
-      </c>
-      <c r="S4" s="149">
-        <f t="shared" ref="S4:S30" si="1">IFERROR(R4/F4*100,0)/10000000</f>
-        <v>-0.99722</v>
-      </c>
-      <c r="Z4" s="133" t="s">
+      <c r="Q4" s="158">
+        <v>9212</v>
+      </c>
+      <c r="R4" s="158"/>
+      <c r="S4" s="158"/>
+      <c r="T4" s="211"/>
+      <c r="U4" s="171">
+        <f t="shared" ref="U4:U30" si="0">SUM(H4:T4)</f>
+        <v>-40649</v>
+      </c>
+      <c r="V4" s="149">
+        <f t="shared" ref="V4:V30" si="1">IFERROR(U4/F4*100,0)/10000000</f>
+        <v>-0.81298000000000004</v>
+      </c>
+      <c r="AC4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="AA4" s="133">
+      <c r="AD4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -6004,17 +6037,22 @@
       <c r="P5" s="147">
         <v>-190900</v>
       </c>
-      <c r="Q5" s="174"/>
-      <c r="R5" s="171">
+      <c r="Q5" s="147">
+        <v>182819</v>
+      </c>
+      <c r="R5" s="147"/>
+      <c r="S5" s="147"/>
+      <c r="T5" s="174"/>
+      <c r="U5" s="171">
         <f t="shared" si="0"/>
-        <v>-96366</v>
-      </c>
-      <c r="S5" s="149">
+        <v>86453</v>
+      </c>
+      <c r="V5" s="149">
         <f t="shared" si="1"/>
-        <v>-0.32122000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.28817666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -6061,17 +6099,24 @@
       <c r="P6" s="147">
         <v>0</v>
       </c>
-      <c r="Q6" s="174"/>
-      <c r="R6" s="171">
+      <c r="Q6" s="147">
+        <v>0</v>
+      </c>
+      <c r="R6" s="147">
+        <v>0</v>
+      </c>
+      <c r="S6" s="147"/>
+      <c r="T6" s="174"/>
+      <c r="U6" s="171">
         <f t="shared" si="0"/>
         <v>-6830</v>
       </c>
-      <c r="S6" s="149">
+      <c r="V6" s="149">
         <f t="shared" si="1"/>
         <v>-6.83E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="141" t="s">
         <v>309</v>
@@ -6114,17 +6159,22 @@
       <c r="P7" s="147">
         <v>0</v>
       </c>
-      <c r="Q7" s="174"/>
-      <c r="R7" s="171">
+      <c r="Q7" s="147">
+        <v>0</v>
+      </c>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="174"/>
+      <c r="U7" s="171">
         <f t="shared" si="0"/>
         <v>23300</v>
       </c>
-      <c r="S7" s="149">
+      <c r="V7" s="149">
         <f t="shared" si="1"/>
         <v>0.23300000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6171,21 +6221,26 @@
       <c r="P8" s="147">
         <v>-131800</v>
       </c>
-      <c r="Q8" s="174"/>
-      <c r="R8" s="171">
+      <c r="Q8" s="147">
+        <v>121400</v>
+      </c>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="174"/>
+      <c r="U8" s="171">
         <f t="shared" si="0"/>
-        <v>-57041</v>
-      </c>
-      <c r="S8" s="149">
+        <v>64359</v>
+      </c>
+      <c r="V8" s="149">
         <f t="shared" si="1"/>
-        <v>-0.19013666666666668</v>
-      </c>
-      <c r="U8" s="5"/>
-      <c r="V8" s="134">
-        <v>-15795</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.21453</v>
+      </c>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="134">
+        <v>8466</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6232,21 +6287,26 @@
       <c r="P9" s="147">
         <v>17255</v>
       </c>
-      <c r="Q9" s="174"/>
-      <c r="R9" s="171">
+      <c r="Q9" s="147">
+        <v>30940</v>
+      </c>
+      <c r="R9" s="147"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="174"/>
+      <c r="U9" s="171">
         <f t="shared" si="0"/>
-        <v>82393</v>
-      </c>
-      <c r="S9" s="149">
+        <v>113333</v>
+      </c>
+      <c r="V9" s="149">
         <f t="shared" si="1"/>
-        <v>0.54928666666666659</v>
-      </c>
-      <c r="U9" s="134">
-        <v>4660847</v>
-      </c>
-      <c r="V9" s="134"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.7555533333333333</v>
+      </c>
+      <c r="X9" s="134">
+        <v>116535</v>
+      </c>
+      <c r="Y9" s="134"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6291,24 +6351,29 @@
       <c r="P10" s="147">
         <v>8888</v>
       </c>
-      <c r="Q10" s="174"/>
-      <c r="R10" s="171">
+      <c r="Q10" s="147">
+        <v>9100</v>
+      </c>
+      <c r="R10" s="147"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="174"/>
+      <c r="U10" s="171">
         <f t="shared" si="0"/>
-        <v>31737</v>
-      </c>
-      <c r="S10" s="149">
+        <v>40837</v>
+      </c>
+      <c r="V10" s="149">
         <f t="shared" si="1"/>
-        <v>0.52895000000000003</v>
-      </c>
-      <c r="U10" s="134">
-        <v>4676642</v>
-      </c>
-      <c r="V10" s="134">
-        <f>(U10+U9)/10000000*13780</f>
-        <v>12867.059842000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.68061666666666665</v>
+      </c>
+      <c r="X10" s="134">
+        <v>125001</v>
+      </c>
+      <c r="Y10" s="134">
+        <f>(X10+X9)/10000000*13780</f>
+        <v>332.83660800000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6355,19 +6420,24 @@
       <c r="P11" s="147">
         <v>-182170</v>
       </c>
-      <c r="Q11" s="174"/>
-      <c r="R11" s="171">
+      <c r="Q11" s="147">
+        <v>-335162</v>
+      </c>
+      <c r="R11" s="147"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="174"/>
+      <c r="U11" s="171">
         <f t="shared" si="0"/>
-        <v>-429086</v>
-      </c>
-      <c r="S11" s="149">
+        <v>-764248</v>
+      </c>
+      <c r="V11" s="149">
         <f t="shared" si="1"/>
-        <v>-0.28605733333333333</v>
-      </c>
-      <c r="U11" s="134"/>
-      <c r="V11" s="134"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-0.50949866666666666</v>
+      </c>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6414,19 +6484,24 @@
       <c r="P12" s="147">
         <v>50</v>
       </c>
-      <c r="Q12" s="174"/>
-      <c r="R12" s="171">
+      <c r="Q12" s="147">
+        <v>145167</v>
+      </c>
+      <c r="R12" s="147"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="174"/>
+      <c r="U12" s="171">
         <f t="shared" si="0"/>
-        <v>-119861</v>
-      </c>
-      <c r="S12" s="149">
+        <v>25306</v>
+      </c>
+      <c r="V12" s="149">
         <f t="shared" si="1"/>
-        <v>-0.19976833333333333</v>
-      </c>
-      <c r="U12" s="134"/>
-      <c r="V12" s="134"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+        <v>4.2176666666666668E-2</v>
+      </c>
+      <c r="X12" s="134"/>
+      <c r="Y12" s="134"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6473,19 +6548,24 @@
       <c r="P13" s="147">
         <v>-2915</v>
       </c>
-      <c r="Q13" s="174"/>
-      <c r="R13" s="171">
+      <c r="Q13" s="147">
+        <v>-2745</v>
+      </c>
+      <c r="R13" s="147"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="174"/>
+      <c r="U13" s="171">
         <f t="shared" si="0"/>
-        <v>-7451</v>
-      </c>
-      <c r="S13" s="149">
+        <v>-10196</v>
+      </c>
+      <c r="V13" s="149">
         <f t="shared" si="1"/>
-        <v>-7.4510000000000007E-2</v>
-      </c>
-      <c r="U13" s="134"/>
-      <c r="V13" s="134"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+        <v>-0.10196</v>
+      </c>
+      <c r="X13" s="134"/>
+      <c r="Y13" s="134"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6532,19 +6612,24 @@
       <c r="P14" s="147">
         <v>0</v>
       </c>
-      <c r="Q14" s="174"/>
-      <c r="R14" s="171">
+      <c r="Q14" s="147">
+        <v>-8766</v>
+      </c>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="174"/>
+      <c r="U14" s="171">
         <f t="shared" si="0"/>
-        <v>22668</v>
-      </c>
-      <c r="S14" s="149">
+        <v>13902</v>
+      </c>
+      <c r="V14" s="149">
         <f t="shared" si="1"/>
-        <v>9.0672000000000016E-2</v>
-      </c>
-      <c r="U14" s="134"/>
-      <c r="V14" s="134"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+        <v>5.5607999999999998E-2</v>
+      </c>
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6591,29 +6676,34 @@
       <c r="P15" s="147">
         <v>0</v>
       </c>
-      <c r="Q15" s="174"/>
-      <c r="R15" s="171">
+      <c r="Q15" s="147">
+        <v>-8566</v>
+      </c>
+      <c r="R15" s="147"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="174"/>
+      <c r="U15" s="171">
         <f t="shared" si="0"/>
-        <v>21766</v>
-      </c>
-      <c r="S15" s="149">
+        <v>13200</v>
+      </c>
+      <c r="V15" s="149">
         <f t="shared" si="1"/>
-        <v>9.8936363636363628E-2</v>
-      </c>
-      <c r="U15" s="134"/>
-      <c r="V15" s="193">
-        <f>V8-V10</f>
-        <v>-28662.059842000002</v>
-      </c>
-      <c r="Y15" s="133">
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="X15" s="134"/>
+      <c r="Y15" s="193">
+        <f>Y8-Y10</f>
+        <v>8133.1633920000004</v>
+      </c>
+      <c r="AB15" s="133">
         <v>116185</v>
       </c>
-      <c r="AA15" s="133">
-        <f>Y15+V15</f>
-        <v>87522.940157999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AD15" s="133">
+        <f>AB15+Y15</f>
+        <v>124318.163392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6660,17 +6750,22 @@
       <c r="P16" s="147">
         <v>7421</v>
       </c>
-      <c r="Q16" s="174"/>
-      <c r="R16" s="171">
+      <c r="Q16" s="147">
+        <v>-27500</v>
+      </c>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="174"/>
+      <c r="U16" s="171">
         <f t="shared" si="0"/>
-        <v>-4367</v>
-      </c>
-      <c r="S16" s="149">
+        <v>-31867</v>
+      </c>
+      <c r="V16" s="149">
         <f t="shared" si="1"/>
-        <v>-4.367E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-0.31867000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6717,28 +6812,35 @@
       <c r="P17" s="147">
         <v>0</v>
       </c>
-      <c r="Q17" s="174"/>
-      <c r="R17" s="171">
+      <c r="Q17" s="147">
+        <v>42220</v>
+      </c>
+      <c r="R17" s="147">
+        <v>0</v>
+      </c>
+      <c r="S17" s="147"/>
+      <c r="T17" s="174"/>
+      <c r="U17" s="171">
         <f t="shared" si="0"/>
-        <v>-32641</v>
-      </c>
-      <c r="S17" s="149">
+        <v>9579</v>
+      </c>
+      <c r="V17" s="149">
         <f t="shared" si="1"/>
-        <v>-0.13056400000000001</v>
-      </c>
-      <c r="AA17" s="133">
+        <v>3.8316000000000003E-2</v>
+      </c>
+      <c r="AD17" s="133">
         <v>4000000</v>
       </c>
-      <c r="AB17" s="133">
-        <f>AA17*7/100</f>
+      <c r="AE17" s="133">
+        <f>AD17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="AD17" s="133">
+      <c r="AG17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6785,21 +6887,28 @@
       <c r="P18" s="147">
         <v>0</v>
       </c>
-      <c r="Q18" s="174"/>
-      <c r="R18" s="171">
+      <c r="Q18" s="147">
+        <v>61600</v>
+      </c>
+      <c r="R18" s="147">
+        <v>0</v>
+      </c>
+      <c r="S18" s="147"/>
+      <c r="T18" s="174"/>
+      <c r="U18" s="171">
         <f t="shared" si="0"/>
-        <v>-48057</v>
-      </c>
-      <c r="S18" s="149">
+        <v>13543</v>
+      </c>
+      <c r="V18" s="149">
         <f t="shared" si="1"/>
-        <v>-0.1201425</v>
-      </c>
-      <c r="AB18" s="133">
-        <f>AB17/12</f>
+        <v>3.3857499999999999E-2</v>
+      </c>
+      <c r="AE18" s="133">
+        <f>AE17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -6846,17 +6955,22 @@
       <c r="P19" s="147">
         <v>-140844</v>
       </c>
-      <c r="Q19" s="174"/>
-      <c r="R19" s="171">
+      <c r="Q19" s="147">
+        <v>13508</v>
+      </c>
+      <c r="R19" s="147"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="174"/>
+      <c r="U19" s="171">
         <f t="shared" si="0"/>
-        <v>-140506</v>
-      </c>
-      <c r="S19" s="149">
+        <v>-126998</v>
+      </c>
+      <c r="V19" s="149">
         <f t="shared" si="1"/>
-        <v>-0.9367066666666668</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-0.84665333333333326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -6903,20 +7017,25 @@
       <c r="P20" s="147">
         <v>-28662</v>
       </c>
-      <c r="Q20" s="174"/>
-      <c r="R20" s="171">
+      <c r="Q20" s="147">
+        <v>-29599</v>
+      </c>
+      <c r="R20" s="147"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="174"/>
+      <c r="U20" s="171">
         <f t="shared" si="0"/>
-        <v>7305</v>
-      </c>
-      <c r="S20" s="149">
+        <v>-22294</v>
+      </c>
+      <c r="V20" s="149">
         <f t="shared" si="1"/>
-        <v>6.6409090909090904E-2</v>
-      </c>
-      <c r="W20" s="133">
-        <v>-38300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-0.20267272727272725</v>
+      </c>
+      <c r="Z20" s="133">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -6963,20 +7082,25 @@
       <c r="P21" s="147">
         <v>-23384</v>
       </c>
-      <c r="Q21" s="174"/>
-      <c r="R21" s="171">
+      <c r="Q21" s="147">
+        <v>-23681</v>
+      </c>
+      <c r="R21" s="147"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="174"/>
+      <c r="U21" s="171">
         <f t="shared" si="0"/>
-        <v>3598</v>
-      </c>
-      <c r="S21" s="149">
+        <v>-20083</v>
+      </c>
+      <c r="V21" s="149">
         <f t="shared" si="1"/>
-        <v>0.14391999999999999</v>
-      </c>
-      <c r="W21" s="133">
-        <v>-35300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-0.80332000000000003</v>
+      </c>
+      <c r="Z21" s="133">
+        <v>30400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -7023,20 +7147,27 @@
       <c r="P22" s="147">
         <v>0</v>
       </c>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="171">
+      <c r="Q22" s="147">
+        <v>0</v>
+      </c>
+      <c r="R22" s="147">
+        <v>0</v>
+      </c>
+      <c r="S22" s="147"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="171">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="S22" s="149">
+      <c r="V22" s="149">
         <f t="shared" si="1"/>
         <v>5.0350000000000004E-3</v>
       </c>
-      <c r="W22" s="133">
-        <v>-21500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="Z22" s="133">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -7052,7 +7183,9 @@
       <c r="E23" s="142" t="s">
         <v>256</v>
       </c>
-      <c r="F23" s="156"/>
+      <c r="F23" s="156">
+        <v>0.25</v>
+      </c>
       <c r="G23" s="190"/>
       <c r="H23" s="147">
         <v>0</v>
@@ -7081,17 +7214,24 @@
       <c r="P23" s="147">
         <v>0</v>
       </c>
-      <c r="Q23" s="174"/>
-      <c r="R23" s="171">
+      <c r="Q23" s="147">
+        <v>0</v>
+      </c>
+      <c r="R23" s="147">
+        <v>0</v>
+      </c>
+      <c r="S23" s="147"/>
+      <c r="T23" s="174"/>
+      <c r="U23" s="171">
         <f t="shared" si="0"/>
         <v>340</v>
       </c>
-      <c r="S23" s="149">
+      <c r="V23" s="149">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+        <v>1.3599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -7138,17 +7278,22 @@
       <c r="P24" s="147">
         <v>-41546</v>
       </c>
-      <c r="Q24" s="174"/>
-      <c r="R24" s="171">
+      <c r="Q24" s="147">
+        <v>-5250</v>
+      </c>
+      <c r="R24" s="147"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="174"/>
+      <c r="U24" s="171">
         <f t="shared" si="0"/>
-        <v>25929</v>
-      </c>
-      <c r="S24" s="149">
+        <v>20679</v>
+      </c>
+      <c r="V24" s="149">
         <f t="shared" si="1"/>
-        <v>0.2357181818181818</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.18799090909090907</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -7195,17 +7340,22 @@
       <c r="P25" s="147">
         <v>-144000</v>
       </c>
-      <c r="Q25" s="174"/>
-      <c r="R25" s="171">
+      <c r="Q25" s="147">
+        <v>-470000</v>
+      </c>
+      <c r="R25" s="147"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="174"/>
+      <c r="U25" s="171">
         <f t="shared" si="0"/>
-        <v>-1027123</v>
-      </c>
-      <c r="S25" s="149">
+        <v>-1497123</v>
+      </c>
+      <c r="V25" s="149">
         <f t="shared" si="1"/>
-        <v>-4.4657521739130441</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-6.5092304347826087</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -7250,17 +7400,22 @@
       <c r="P26" s="147">
         <v>1432</v>
       </c>
-      <c r="Q26" s="174"/>
-      <c r="R26" s="171">
+      <c r="Q26" s="147">
+        <v>-1700</v>
+      </c>
+      <c r="R26" s="147"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="174"/>
+      <c r="U26" s="171">
         <f t="shared" si="0"/>
-        <v>5794</v>
-      </c>
-      <c r="S26" s="149">
+        <v>4094</v>
+      </c>
+      <c r="V26" s="149">
         <f t="shared" si="1"/>
-        <v>0.28970000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.20469999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -7307,17 +7462,24 @@
       <c r="P27" s="147">
         <v>0</v>
       </c>
-      <c r="Q27" s="174"/>
-      <c r="R27" s="171">
+      <c r="Q27" s="147">
+        <v>81666</v>
+      </c>
+      <c r="R27" s="147">
+        <v>0</v>
+      </c>
+      <c r="S27" s="147"/>
+      <c r="T27" s="174"/>
+      <c r="U27" s="171">
         <f t="shared" si="0"/>
-        <v>-47000</v>
-      </c>
-      <c r="S27" s="149">
+        <v>34666</v>
+      </c>
+      <c r="V27" s="149">
         <f t="shared" si="1"/>
-        <v>-9.4E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+        <v>6.9332000000000005E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -7364,17 +7526,24 @@
       <c r="P28" s="147">
         <v>-431450</v>
       </c>
-      <c r="Q28" s="174"/>
-      <c r="R28" s="171">
+      <c r="Q28" s="147">
+        <v>-290000</v>
+      </c>
+      <c r="R28" s="147">
+        <v>-481200</v>
+      </c>
+      <c r="S28" s="147"/>
+      <c r="T28" s="174"/>
+      <c r="U28" s="171">
         <f t="shared" si="0"/>
-        <v>-460666</v>
-      </c>
-      <c r="S28" s="149">
+        <v>-1231866</v>
+      </c>
+      <c r="V28" s="149">
         <f t="shared" si="1"/>
-        <v>-0.46066600000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-1.2318659999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -7421,17 +7590,24 @@
       <c r="P29" s="147">
         <v>0</v>
       </c>
-      <c r="Q29" s="174"/>
-      <c r="R29" s="171">
+      <c r="Q29" s="147">
+        <v>-33106</v>
+      </c>
+      <c r="R29" s="147">
+        <v>0</v>
+      </c>
+      <c r="S29" s="147"/>
+      <c r="T29" s="174"/>
+      <c r="U29" s="171">
         <f t="shared" si="0"/>
-        <v>-308883</v>
-      </c>
-      <c r="S29" s="149">
+        <v>-341989</v>
+      </c>
+      <c r="V29" s="149">
         <f t="shared" si="1"/>
-        <v>-0.61776600000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-0.68397799999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -7478,17 +7654,22 @@
       <c r="P30" s="147">
         <v>37112</v>
       </c>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="171">
+      <c r="Q30" s="147">
+        <v>18328</v>
+      </c>
+      <c r="R30" s="147"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="171">
         <f t="shared" si="0"/>
-        <v>147515</v>
-      </c>
-      <c r="S30" s="149">
+        <v>165843</v>
+      </c>
+      <c r="V30" s="149">
         <f t="shared" si="1"/>
-        <v>0.29503000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.33168599999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -7535,17 +7716,22 @@
       <c r="P31" s="147">
         <v>-21920</v>
       </c>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="171">
-        <f t="shared" ref="R31:R56" si="2">SUM(H31:Q31)</f>
-        <v>-145944</v>
-      </c>
-      <c r="S31" s="149">
-        <f t="shared" ref="S31:S56" si="3">IFERROR(R31/F31*100,0)/10000000</f>
-        <v>-2.9188800000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="Q31" s="147">
+        <v>15560</v>
+      </c>
+      <c r="R31" s="147"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="174"/>
+      <c r="U31" s="171">
+        <f t="shared" ref="U31:U56" si="2">SUM(H31:T31)</f>
+        <v>-130384</v>
+      </c>
+      <c r="V31" s="149">
+        <f t="shared" ref="V31:V56" si="3">IFERROR(U31/F31*100,0)/10000000</f>
+        <v>-2.6076800000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -7592,18 +7778,23 @@
       <c r="P32" s="147">
         <v>44092</v>
       </c>
-      <c r="Q32" s="174"/>
-      <c r="R32" s="171">
+      <c r="Q32" s="147">
+        <v>44376</v>
+      </c>
+      <c r="R32" s="147"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="174"/>
+      <c r="U32" s="171">
         <f t="shared" si="2"/>
-        <v>95813</v>
-      </c>
-      <c r="S32" s="149">
+        <v>140189</v>
+      </c>
+      <c r="V32" s="149">
         <f t="shared" si="3"/>
-        <v>2.3953250000000001</v>
-      </c>
-      <c r="V32" s="134"/>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3.5047250000000001</v>
+      </c>
+      <c r="Y32" s="134"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -7650,21 +7841,28 @@
       <c r="P33" s="147">
         <v>0</v>
       </c>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="171">
+      <c r="Q33" s="147">
+        <v>0</v>
+      </c>
+      <c r="R33" s="147">
+        <v>0</v>
+      </c>
+      <c r="S33" s="147"/>
+      <c r="T33" s="174"/>
+      <c r="U33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S33" s="149">
+      <c r="V33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U33" s="5"/>
-      <c r="V33" s="134">
-        <v>39838</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X33" s="5"/>
+      <c r="Y33" s="134">
+        <v>19176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -7711,19 +7909,26 @@
       <c r="P34" s="147">
         <v>0</v>
       </c>
-      <c r="Q34" s="174"/>
-      <c r="R34" s="171">
+      <c r="Q34" s="147">
+        <v>0</v>
+      </c>
+      <c r="R34" s="147">
+        <v>0</v>
+      </c>
+      <c r="S34" s="147"/>
+      <c r="T34" s="174"/>
+      <c r="U34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S34" s="149">
+      <c r="V34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U34" s="5"/>
-      <c r="V34" s="134"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X34" s="5"/>
+      <c r="Y34" s="134"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -7770,24 +7975,29 @@
       <c r="P35" s="147">
         <v>3072</v>
       </c>
-      <c r="Q35" s="174"/>
-      <c r="R35" s="171">
+      <c r="Q35" s="147">
+        <v>9822</v>
+      </c>
+      <c r="R35" s="147"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="174"/>
+      <c r="U35" s="171">
         <f t="shared" si="2"/>
-        <v>-126402</v>
-      </c>
-      <c r="S35" s="149">
+        <v>-116580</v>
+      </c>
+      <c r="V35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.31600499999999998</v>
-      </c>
-      <c r="U35" s="134">
-        <v>969020</v>
-      </c>
-      <c r="V35" s="134">
-        <f>(U36+U35)/10000000*13780</f>
-        <v>2725.5158840000004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.29144999999999999</v>
+      </c>
+      <c r="X35" s="134">
+        <v>346085</v>
+      </c>
+      <c r="Y35" s="134">
+        <f>(X36+X35)/10000000*13780</f>
+        <v>985.0550320000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -7834,21 +8044,26 @@
       <c r="P36" s="147">
         <v>-32612</v>
       </c>
-      <c r="Q36" s="174"/>
-      <c r="R36" s="171">
+      <c r="Q36" s="147">
+        <v>-120800</v>
+      </c>
+      <c r="R36" s="147"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="174"/>
+      <c r="U36" s="171">
         <f t="shared" si="2"/>
-        <v>-88079</v>
-      </c>
-      <c r="S36" s="149">
+        <v>-208879</v>
+      </c>
+      <c r="V36" s="149">
         <f t="shared" si="3"/>
-        <v>-0.88078999999999996</v>
-      </c>
-      <c r="U36" s="134">
-        <v>1008858</v>
-      </c>
-      <c r="V36" s="134"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-2.0887899999999999</v>
+      </c>
+      <c r="X36" s="134">
+        <v>368759</v>
+      </c>
+      <c r="Y36" s="134"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -7893,22 +8108,29 @@
       <c r="P37" s="147">
         <v>0</v>
       </c>
-      <c r="Q37" s="174"/>
-      <c r="R37" s="171">
+      <c r="Q37" s="147">
+        <v>0</v>
+      </c>
+      <c r="R37" s="147">
+        <v>0</v>
+      </c>
+      <c r="S37" s="147"/>
+      <c r="T37" s="174"/>
+      <c r="U37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S37" s="149">
+      <c r="V37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U37" s="134"/>
-      <c r="V37" s="134">
-        <f>+V33-V35</f>
-        <v>37112.484116</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="X37" s="134"/>
+      <c r="Y37" s="134">
+        <f>+Y33-Y35</f>
+        <v>18190.944968</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -7955,19 +8177,24 @@
       <c r="P38" s="147">
         <v>3788</v>
       </c>
-      <c r="Q38" s="174"/>
-      <c r="R38" s="171">
+      <c r="Q38" s="147">
+        <v>8133</v>
+      </c>
+      <c r="R38" s="147"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="174"/>
+      <c r="U38" s="171">
         <f t="shared" si="2"/>
-        <v>-16088</v>
-      </c>
-      <c r="S38" s="149">
+        <v>-7955</v>
+      </c>
+      <c r="V38" s="149">
         <f t="shared" si="3"/>
-        <v>-0.32175999999999999</v>
-      </c>
-      <c r="U38" s="134"/>
-      <c r="V38" s="134"/>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.15909999999999999</v>
+      </c>
+      <c r="X38" s="134"/>
+      <c r="Y38" s="134"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -8014,19 +8241,24 @@
       <c r="P39" s="147">
         <v>0</v>
       </c>
-      <c r="Q39" s="174"/>
-      <c r="R39" s="171">
+      <c r="Q39" s="147">
+        <v>0</v>
+      </c>
+      <c r="R39" s="147"/>
+      <c r="S39" s="147"/>
+      <c r="T39" s="174"/>
+      <c r="U39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S39" s="149">
+      <c r="V39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U39" s="134"/>
-      <c r="V39" s="134"/>
-    </row>
-    <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X39" s="134"/>
+      <c r="Y39" s="134"/>
+    </row>
+    <row r="40" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -8073,19 +8305,24 @@
       <c r="P40" s="147">
         <v>13700</v>
       </c>
-      <c r="Q40" s="174"/>
-      <c r="R40" s="171">
+      <c r="Q40" s="147">
+        <v>58211</v>
+      </c>
+      <c r="R40" s="147"/>
+      <c r="S40" s="147"/>
+      <c r="T40" s="174"/>
+      <c r="U40" s="171">
         <f t="shared" si="2"/>
-        <v>-2278</v>
-      </c>
-      <c r="S40" s="149">
+        <v>55933</v>
+      </c>
+      <c r="V40" s="149">
         <f t="shared" si="3"/>
-        <v>-7.5933333333333339E-3</v>
-      </c>
-      <c r="U40" s="134"/>
-      <c r="V40" s="134"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.18644333333333332</v>
+      </c>
+      <c r="X40" s="134"/>
+      <c r="Y40" s="134"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -8130,18 +8367,25 @@
       <c r="P41" s="147">
         <v>25334</v>
       </c>
-      <c r="Q41" s="174"/>
-      <c r="R41" s="171">
+      <c r="Q41" s="147">
+        <v>-21750</v>
+      </c>
+      <c r="R41" s="147">
+        <v>0</v>
+      </c>
+      <c r="S41" s="147"/>
+      <c r="T41" s="174"/>
+      <c r="U41" s="171">
         <f t="shared" si="2"/>
-        <v>-39779</v>
-      </c>
-      <c r="S41" s="149">
+        <v>-61529</v>
+      </c>
+      <c r="V41" s="149">
         <f t="shared" si="3"/>
-        <v>-3.9779</v>
-      </c>
-      <c r="U41" s="134"/>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-6.1528999999999998</v>
+      </c>
+      <c r="X41" s="134"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -8188,17 +8432,22 @@
       <c r="P42" s="147">
         <v>8722</v>
       </c>
-      <c r="Q42" s="174"/>
-      <c r="R42" s="171">
+      <c r="Q42" s="147">
+        <v>20519</v>
+      </c>
+      <c r="R42" s="147"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="174"/>
+      <c r="U42" s="171">
         <f t="shared" si="2"/>
-        <v>-11097</v>
-      </c>
-      <c r="S42" s="149">
+        <v>9422</v>
+      </c>
+      <c r="V42" s="149">
         <f t="shared" si="3"/>
-        <v>-0.22194</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.18844</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -8245,17 +8494,22 @@
       <c r="P43" s="147">
         <v>-165000</v>
       </c>
-      <c r="Q43" s="174"/>
-      <c r="R43" s="171">
+      <c r="Q43" s="147">
+        <v>-316146</v>
+      </c>
+      <c r="R43" s="147"/>
+      <c r="S43" s="147"/>
+      <c r="T43" s="174"/>
+      <c r="U43" s="171">
         <f t="shared" si="2"/>
-        <v>-133607</v>
-      </c>
-      <c r="S43" s="149">
+        <v>-449753</v>
+      </c>
+      <c r="V43" s="149">
         <f t="shared" si="3"/>
-        <v>-1.3360700000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-4.4975300000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -8300,17 +8554,22 @@
       <c r="P44" s="147">
         <v>-1652</v>
       </c>
-      <c r="Q44" s="174"/>
-      <c r="R44" s="171">
+      <c r="Q44" s="147">
+        <v>11400</v>
+      </c>
+      <c r="R44" s="147"/>
+      <c r="S44" s="147"/>
+      <c r="T44" s="174"/>
+      <c r="U44" s="171">
         <f t="shared" si="2"/>
-        <v>546</v>
-      </c>
-      <c r="S44" s="149">
+        <v>11946</v>
+      </c>
+      <c r="V44" s="149">
         <f t="shared" si="3"/>
-        <v>5.4600000000000003E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.1946000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -8357,17 +8616,22 @@
       <c r="P45" s="147">
         <v>0</v>
       </c>
-      <c r="Q45" s="174"/>
-      <c r="R45" s="171">
+      <c r="Q45" s="147">
+        <v>0</v>
+      </c>
+      <c r="R45" s="147"/>
+      <c r="S45" s="147"/>
+      <c r="T45" s="174"/>
+      <c r="U45" s="171">
         <f t="shared" si="2"/>
         <v>-156125</v>
       </c>
-      <c r="S45" s="149">
+      <c r="V45" s="149">
         <f t="shared" si="3"/>
         <v>-0.39031250000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -8414,17 +8678,22 @@
       <c r="P46" s="147">
         <v>0</v>
       </c>
-      <c r="Q46" s="174"/>
-      <c r="R46" s="171">
+      <c r="Q46" s="147">
+        <v>-3600</v>
+      </c>
+      <c r="R46" s="147"/>
+      <c r="S46" s="147"/>
+      <c r="T46" s="174"/>
+      <c r="U46" s="171">
         <f t="shared" si="2"/>
-        <v>-73205</v>
-      </c>
-      <c r="S46" s="149">
+        <v>-76805</v>
+      </c>
+      <c r="V46" s="149">
         <f t="shared" si="3"/>
-        <v>-0.18301249999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.1920125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -8471,17 +8740,22 @@
       <c r="P47" s="147">
         <v>388268</v>
       </c>
-      <c r="Q47" s="174"/>
-      <c r="R47" s="171">
+      <c r="Q47" s="147">
+        <v>416846</v>
+      </c>
+      <c r="R47" s="147"/>
+      <c r="S47" s="147"/>
+      <c r="T47" s="174"/>
+      <c r="U47" s="171">
         <f t="shared" si="2"/>
-        <v>255502</v>
-      </c>
-      <c r="S47" s="149">
+        <v>672348</v>
+      </c>
+      <c r="V47" s="149">
         <f t="shared" si="3"/>
-        <v>0.85167333333333317</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2.2411599999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -8526,17 +8800,22 @@
       <c r="P48" s="151">
         <v>458900</v>
       </c>
-      <c r="Q48" s="174"/>
-      <c r="R48" s="171">
+      <c r="Q48" s="151">
+        <v>52400</v>
+      </c>
+      <c r="R48" s="151"/>
+      <c r="S48" s="151"/>
+      <c r="T48" s="174"/>
+      <c r="U48" s="171">
         <f t="shared" si="2"/>
-        <v>-760336</v>
-      </c>
-      <c r="S48" s="149">
+        <v>-707936</v>
+      </c>
+      <c r="V48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.76033600000000012</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-0.70793600000000012</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -8579,17 +8858,24 @@
       <c r="P49" s="151">
         <v>0</v>
       </c>
-      <c r="Q49" s="174"/>
-      <c r="R49" s="171">
+      <c r="Q49" s="151">
+        <v>0</v>
+      </c>
+      <c r="R49" s="151">
+        <v>0</v>
+      </c>
+      <c r="S49" s="151"/>
+      <c r="T49" s="174"/>
+      <c r="U49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S49" s="149">
+      <c r="V49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -8636,17 +8922,22 @@
       <c r="P50" s="151">
         <v>-27401</v>
       </c>
-      <c r="Q50" s="174"/>
-      <c r="R50" s="171">
+      <c r="Q50" s="151">
+        <v>19542</v>
+      </c>
+      <c r="R50" s="151"/>
+      <c r="S50" s="151"/>
+      <c r="T50" s="174"/>
+      <c r="U50" s="171">
         <f t="shared" si="2"/>
-        <v>11128</v>
-      </c>
-      <c r="S50" s="149">
+        <v>30670</v>
+      </c>
+      <c r="V50" s="149">
         <f t="shared" si="3"/>
-        <v>0.22256000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.61339999999999995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -8693,17 +8984,24 @@
       <c r="P51" s="151">
         <v>0</v>
       </c>
-      <c r="Q51" s="174"/>
-      <c r="R51" s="171">
+      <c r="Q51" s="151">
+        <v>-652202</v>
+      </c>
+      <c r="R51" s="151">
+        <v>0</v>
+      </c>
+      <c r="S51" s="151"/>
+      <c r="T51" s="174"/>
+      <c r="U51" s="171">
         <f t="shared" si="2"/>
-        <v>34489</v>
-      </c>
-      <c r="S51" s="149">
+        <v>-617713</v>
+      </c>
+      <c r="V51" s="149">
         <f t="shared" si="3"/>
-        <v>5.3060000000000003E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-0.95032769230769243</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -8750,17 +9048,24 @@
       <c r="P52" s="151">
         <v>0</v>
       </c>
-      <c r="Q52" s="174"/>
-      <c r="R52" s="171">
+      <c r="Q52" s="151">
+        <v>0</v>
+      </c>
+      <c r="R52" s="151">
+        <v>0</v>
+      </c>
+      <c r="S52" s="151"/>
+      <c r="T52" s="174"/>
+      <c r="U52" s="171">
         <f t="shared" si="2"/>
         <v>-158276</v>
       </c>
-      <c r="S52" s="149">
+      <c r="V52" s="149">
         <f t="shared" si="3"/>
         <v>-1.266208</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -8807,17 +9112,24 @@
       <c r="P53" s="151">
         <v>0</v>
       </c>
-      <c r="Q53" s="174"/>
-      <c r="R53" s="171">
+      <c r="Q53" s="151">
+        <v>4264</v>
+      </c>
+      <c r="R53" s="151">
+        <v>0</v>
+      </c>
+      <c r="S53" s="151"/>
+      <c r="T53" s="174"/>
+      <c r="U53" s="171">
         <f t="shared" si="2"/>
-        <v>-178780</v>
-      </c>
-      <c r="S53" s="149">
+        <v>-174516</v>
+      </c>
+      <c r="V53" s="149">
         <f t="shared" si="3"/>
-        <v>-0.59593333333333343</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+        <v>-0.58172000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -8862,17 +9174,22 @@
       <c r="P54" s="151">
         <v>0</v>
       </c>
-      <c r="Q54" s="174"/>
-      <c r="R54" s="171">
+      <c r="Q54" s="151">
+        <v>0</v>
+      </c>
+      <c r="R54" s="151"/>
+      <c r="S54" s="151"/>
+      <c r="T54" s="174"/>
+      <c r="U54" s="171">
         <f t="shared" si="2"/>
         <v>11400</v>
       </c>
-      <c r="S54" s="149">
+      <c r="V54" s="149">
         <f t="shared" si="3"/>
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -8917,17 +9234,22 @@
       <c r="P55" s="151">
         <v>9600</v>
       </c>
-      <c r="Q55" s="174"/>
-      <c r="R55" s="171">
+      <c r="Q55" s="151">
+        <v>18190</v>
+      </c>
+      <c r="R55" s="151"/>
+      <c r="S55" s="151"/>
+      <c r="T55" s="174"/>
+      <c r="U55" s="171">
         <f t="shared" si="2"/>
-        <v>3938</v>
-      </c>
-      <c r="S55" s="149">
+        <v>22128</v>
+      </c>
+      <c r="V55" s="149">
         <f t="shared" si="3"/>
-        <v>7.8759999999999993E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.4256000000000004E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -8936,7 +9258,7 @@
       <c r="F56" s="115"/>
       <c r="G56" s="16"/>
       <c r="H56" s="254">
-        <f t="shared" ref="H56:P56" si="4">SUM(H4:H55)</f>
+        <f t="shared" ref="H56:S56" si="4">SUM(H4:H55)</f>
         <v>-2118400</v>
       </c>
       <c r="I56" s="254">
@@ -8972,19 +9294,31 @@
         <v>-539685</v>
       </c>
       <c r="Q56" s="254">
-        <f>SUM(Q4:Q55)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>-955350</v>
       </c>
       <c r="R56" s="254">
+        <f t="shared" si="4"/>
+        <v>-481200</v>
+      </c>
+      <c r="S56" s="254">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="254">
+        <f>SUM(T4:T55)</f>
+        <v>0</v>
+      </c>
+      <c r="U56" s="254">
         <f t="shared" si="2"/>
-        <v>-3939567</v>
-      </c>
-      <c r="S56" s="255">
+        <v>-5376117</v>
+      </c>
+      <c r="V56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:23" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -9003,9 +9337,12 @@
       <c r="P57" s="250"/>
       <c r="Q57" s="250"/>
       <c r="R57" s="250"/>
-      <c r="S57" s="252"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S57" s="250"/>
+      <c r="T57" s="250"/>
+      <c r="U57" s="250"/>
+      <c r="V57" s="252"/>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -9052,18 +9389,23 @@
       <c r="P58" s="162">
         <v>-49300</v>
       </c>
-      <c r="Q58" s="246"/>
-      <c r="R58" s="247">
-        <f>SUM(H58:Q58)</f>
-        <v>-283628</v>
-      </c>
-      <c r="S58" s="248">
-        <f>IFERROR(R58/F58*100,0)/10000000</f>
-        <v>-0.94542666666666675</v>
-      </c>
-      <c r="V58" s="134"/>
-    </row>
-    <row r="59" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q58" s="162">
+        <v>-431925</v>
+      </c>
+      <c r="R58" s="162"/>
+      <c r="S58" s="162"/>
+      <c r="T58" s="246"/>
+      <c r="U58" s="247">
+        <f>SUM(H58:T58)</f>
+        <v>-715553</v>
+      </c>
+      <c r="V58" s="248">
+        <f>IFERROR(U58/F58*100,0)/10000000</f>
+        <v>-2.3851766666666663</v>
+      </c>
+      <c r="Y58" s="134"/>
+    </row>
+    <row r="59" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -9108,18 +9450,23 @@
       <c r="P59" s="162">
         <v>-500</v>
       </c>
-      <c r="Q59" s="174"/>
-      <c r="R59" s="171">
-        <f>SUM(H59:Q59)</f>
-        <v>134616</v>
-      </c>
-      <c r="S59" s="149">
-        <f>IFERROR(R59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="U59" s="134"/>
-    </row>
-    <row r="60" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q59" s="162">
+        <v>-47350</v>
+      </c>
+      <c r="R59" s="162"/>
+      <c r="S59" s="162"/>
+      <c r="T59" s="174"/>
+      <c r="U59" s="171">
+        <f>SUM(H59:T59)</f>
+        <v>87266</v>
+      </c>
+      <c r="V59" s="149">
+        <f>IFERROR(U59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="X59" s="134"/>
+    </row>
+    <row r="60" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -9128,7 +9475,7 @@
       <c r="F60" s="74"/>
       <c r="G60" s="17"/>
       <c r="H60" s="170">
-        <f t="shared" ref="H60:P60" si="5">SUM(H58:H59)</f>
+        <f t="shared" ref="H60:S60" si="5">SUM(H58:H59)</f>
         <v>-616080</v>
       </c>
       <c r="I60" s="170">
@@ -9164,131 +9511,143 @@
         <v>-49800</v>
       </c>
       <c r="Q60" s="170">
-        <f>SUM(Q58:Q59)</f>
-        <v>0</v>
-      </c>
-      <c r="R60" s="254">
-        <f>SUM(H60:Q60)</f>
-        <v>-149012</v>
-      </c>
-      <c r="S60" s="19"/>
-      <c r="U60" s="5"/>
-      <c r="V60" s="134"/>
-      <c r="W60" s="237"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="U61" s="134"/>
-      <c r="V61" s="134"/>
-      <c r="W61" s="237"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="U62" s="134"/>
-      <c r="V62" s="134"/>
-      <c r="W62" s="237"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="U63" s="134"/>
-      <c r="V63" s="134"/>
-      <c r="W63" s="237"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="U64" s="134"/>
-      <c r="V64" s="134"/>
-      <c r="W64" s="237"/>
-    </row>
-    <row r="65" spans="21:23" x14ac:dyDescent="0.25">
-      <c r="U65" s="134"/>
-      <c r="V65" s="237"/>
-      <c r="W65" s="237"/>
-    </row>
-    <row r="66" spans="21:23" x14ac:dyDescent="0.25">
-      <c r="U66" s="237"/>
-      <c r="V66" s="237"/>
-      <c r="W66" s="237"/>
+        <f t="shared" si="5"/>
+        <v>-479275</v>
+      </c>
+      <c r="R60" s="170">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="170">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="170">
+        <f>SUM(T58:T59)</f>
+        <v>0</v>
+      </c>
+      <c r="U60" s="254">
+        <f>SUM(H60:T60)</f>
+        <v>-628287</v>
+      </c>
+      <c r="V60" s="19"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="134"/>
+      <c r="Z60" s="237"/>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X61" s="134"/>
+      <c r="Y61" s="134"/>
+      <c r="Z61" s="237"/>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X62" s="134"/>
+      <c r="Y62" s="134"/>
+      <c r="Z62" s="237"/>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X63" s="134"/>
+      <c r="Y63" s="134"/>
+      <c r="Z63" s="237"/>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X64" s="134"/>
+      <c r="Y64" s="134"/>
+      <c r="Z64" s="237"/>
+    </row>
+    <row r="65" spans="24:26" x14ac:dyDescent="0.25">
+      <c r="X65" s="134"/>
+      <c r="Y65" s="237"/>
+      <c r="Z65" s="237"/>
+    </row>
+    <row r="66" spans="24:26" x14ac:dyDescent="0.25">
+      <c r="X66" s="237"/>
+      <c r="Y66" s="237"/>
+      <c r="Z66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 S56:S57 R55:S55 S60 R43:S43 R5:S10 R24:S25 H2:S3 A58:S59 A37:R37 S11:S21 R11:R22 R45:S53 R27:R36 S27:S35 A4:Q36 R38:R41 A38:Q39 G40:Q40 A41:Q56 A60:Q60">
-    <cfRule type="expression" dxfId="448" priority="21">
+  <conditionalFormatting sqref="G2 A3:G3 V56:V57 U55:V55 V60 U43:V43 U5:V10 U24:V25 H2:V3 A58:V59 A37:U37 V11:V21 U11:U22 U45:V53 U27:U36 V27:V35 A4:T36 U38:U41 A38:T39 G40:T40 A41:T56 A60:T60">
+    <cfRule type="expression" dxfId="450" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S36">
-    <cfRule type="expression" dxfId="447" priority="20">
+  <conditionalFormatting sqref="V36">
+    <cfRule type="expression" dxfId="449" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S39:S40">
-    <cfRule type="expression" dxfId="446" priority="19">
+  <conditionalFormatting sqref="V39:V40">
+    <cfRule type="expression" dxfId="448" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R4:S4">
-    <cfRule type="expression" dxfId="445" priority="18">
+  <conditionalFormatting sqref="U4:V4">
+    <cfRule type="expression" dxfId="447" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S38">
-    <cfRule type="expression" dxfId="444" priority="17">
+  <conditionalFormatting sqref="V38">
+    <cfRule type="expression" dxfId="446" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S22">
-    <cfRule type="expression" dxfId="443" priority="14">
+  <conditionalFormatting sqref="V22">
+    <cfRule type="expression" dxfId="445" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R56">
-    <cfRule type="expression" dxfId="442" priority="13">
+  <conditionalFormatting sqref="U56">
+    <cfRule type="expression" dxfId="444" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S41">
-    <cfRule type="expression" dxfId="441" priority="12">
+  <conditionalFormatting sqref="V41">
+    <cfRule type="expression" dxfId="443" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R26:S26">
-    <cfRule type="expression" dxfId="440" priority="11">
+  <conditionalFormatting sqref="U26:V26">
+    <cfRule type="expression" dxfId="442" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R54:S54">
-    <cfRule type="expression" dxfId="439" priority="10">
+  <conditionalFormatting sqref="U54:V54">
+    <cfRule type="expression" dxfId="441" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R44:S44">
-    <cfRule type="expression" dxfId="438" priority="9">
+  <conditionalFormatting sqref="U44:V44">
+    <cfRule type="expression" dxfId="440" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R60">
-    <cfRule type="expression" dxfId="437" priority="8">
+  <conditionalFormatting sqref="U60">
+    <cfRule type="expression" dxfId="439" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R42:S42">
-    <cfRule type="expression" dxfId="436" priority="6">
+  <conditionalFormatting sqref="U42:V42">
+    <cfRule type="expression" dxfId="438" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R23">
-    <cfRule type="expression" dxfId="435" priority="5">
+  <conditionalFormatting sqref="U23">
+    <cfRule type="expression" dxfId="437" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S23">
-    <cfRule type="expression" dxfId="434" priority="4">
+  <conditionalFormatting sqref="V23">
+    <cfRule type="expression" dxfId="436" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S37">
-    <cfRule type="expression" dxfId="433" priority="2">
+  <conditionalFormatting sqref="V37">
+    <cfRule type="expression" dxfId="435" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="432" priority="1">
+    <cfRule type="expression" dxfId="434" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9313,10 +9672,9 @@
     <col min="24" max="24" width="11.42578125" style="133" customWidth="1" outlineLevel="1"/>
     <col min="25" max="27" width="11.28515625" style="133" customWidth="1" outlineLevel="1"/>
     <col min="28" max="28" width="11.28515625" style="133" customWidth="1"/>
-    <col min="29" max="29" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="9.140625" style="133" collapsed="1"/>
-    <col min="32" max="36" width="9.140625" style="133"/>
+    <col min="29" max="29" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="36" width="9.140625" style="133"/>
     <col min="37" max="37" width="14.140625" style="133" customWidth="1"/>
     <col min="38" max="38" width="12" style="133" customWidth="1"/>
     <col min="39" max="39" width="15.85546875" style="133" customWidth="1"/>
@@ -15756,112 +16114,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="431" priority="22">
+    <cfRule type="expression" dxfId="433" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="430" priority="21">
+    <cfRule type="expression" dxfId="432" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="429" priority="20">
+    <cfRule type="expression" dxfId="431" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="428" priority="19">
+    <cfRule type="expression" dxfId="430" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="427" priority="18">
+    <cfRule type="expression" dxfId="429" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="426" priority="17">
+    <cfRule type="expression" dxfId="428" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="425" priority="16">
+    <cfRule type="expression" dxfId="427" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="424" priority="15">
+    <cfRule type="expression" dxfId="426" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="423" priority="14">
+    <cfRule type="expression" dxfId="425" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="422" priority="13">
+    <cfRule type="expression" dxfId="424" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="421" priority="12">
+    <cfRule type="expression" dxfId="423" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="420" priority="11">
+    <cfRule type="expression" dxfId="422" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="419" priority="10">
+    <cfRule type="expression" dxfId="421" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="418" priority="9">
+    <cfRule type="expression" dxfId="420" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="417" priority="8">
+    <cfRule type="expression" dxfId="419" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="416" priority="7">
+    <cfRule type="expression" dxfId="418" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="415" priority="6">
+    <cfRule type="expression" dxfId="417" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="414" priority="5">
+    <cfRule type="expression" dxfId="416" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="413" priority="4">
+    <cfRule type="expression" dxfId="415" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="412" priority="3">
+    <cfRule type="expression" dxfId="414" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="411" priority="2">
+    <cfRule type="expression" dxfId="413" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="410" priority="1">
+    <cfRule type="expression" dxfId="412" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22161,82 +22519,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="409" priority="20">
+    <cfRule type="expression" dxfId="411" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="408" priority="19">
+    <cfRule type="expression" dxfId="410" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="407" priority="18">
+    <cfRule type="expression" dxfId="409" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="406" priority="16">
+    <cfRule type="expression" dxfId="408" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="405" priority="14">
+    <cfRule type="expression" dxfId="407" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="404" priority="13">
+    <cfRule type="expression" dxfId="406" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="403" priority="12">
+    <cfRule type="expression" dxfId="405" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="402" priority="11">
+    <cfRule type="expression" dxfId="404" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="401" priority="10">
+    <cfRule type="expression" dxfId="403" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="400" priority="9">
+    <cfRule type="expression" dxfId="402" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="399" priority="6">
+    <cfRule type="expression" dxfId="401" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="398" priority="5">
+    <cfRule type="expression" dxfId="400" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="397" priority="4">
+    <cfRule type="expression" dxfId="399" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="396" priority="3">
+    <cfRule type="expression" dxfId="398" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="395" priority="2">
+    <cfRule type="expression" dxfId="397" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="394" priority="1">
+    <cfRule type="expression" dxfId="396" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22360,20 +22718,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-49861</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-40649</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.99722</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.81298000000000004</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-76905</v>
+        <v>-67693</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-1.5381</v>
+        <v>-1.3538600000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -22412,20 +22770,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-96366</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>86453</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.32122000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.28817666666666669</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-347337</v>
+        <v>-164518</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-1.1577900000000001</v>
+        <v>-0.54839333333333329</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -22464,11 +22822,11 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>-6830</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>-6.83E-2</v>
       </c>
       <c r="M6" s="71">
@@ -22514,11 +22872,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M7" s="71">
@@ -22566,20 +22924,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-57041</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>64359</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.19013666666666668</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.21453</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-512138</v>
+        <v>-390738</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.7071266666666667</v>
+        <v>-1.30246</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -22618,20 +22976,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>82393</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>113333</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.54928666666666659</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.7555533333333333</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-211743</v>
+        <v>-180803</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4116200000000005</v>
+        <v>-1.2053533333333337</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -22670,20 +23028,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>31737</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>40837</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.52895000000000003</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.68061666666666665</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-160512</v>
+        <v>-151412</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-2.6752000000000002</v>
+        <v>-2.5235333333333339</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -22722,20 +23080,20 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-429086</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-764248</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.28605733333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.50949866666666666</v>
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>538179</v>
+        <v>203017</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.3587860000000001</v>
+        <v>0.13534466666666678</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -22774,20 +23132,20 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-119861</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>25306</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.19976833333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>4.2176666666666668E-2</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>287919</v>
+        <v>433086</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.4798650000000001</v>
+        <v>0.72181000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -22826,20 +23184,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-7451</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-10196</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-7.4510000000000007E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.10196</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>5965</v>
+        <v>3220</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>5.9649999999999995E-2</v>
+        <v>3.2200000000000006E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -22878,20 +23236,20 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>22668</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>13902</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>9.0672000000000016E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>5.5607999999999998E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>67588</v>
+        <v>58822</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.27035199999999998</v>
+        <v>0.23528799999999994</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -22930,11 +23288,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -22982,20 +23340,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-4367</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-31867</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-4.367E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.31867000000000001</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>69040</v>
+        <v>41540</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.69040000000000001</v>
+        <v>0.41539999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -23034,20 +23392,20 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>21766</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>13200</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>9.8936363636363628E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>5.9999999999999991E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-66142</v>
+        <v>-74708</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.30064545454545455</v>
+        <v>-0.33958181818181815</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -23086,20 +23444,20 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-32641</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>9579</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.13056400000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>3.8316000000000003E-2</v>
       </c>
       <c r="M18" s="71">
         <f t="shared" si="0"/>
-        <v>-96558</v>
+        <v>-54338</v>
       </c>
       <c r="N18" s="166">
         <f t="shared" si="0"/>
-        <v>-0.38623200000000002</v>
+        <v>-0.21735199999999999</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -23138,20 +23496,20 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-48057</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>13543</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.1201425</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>3.3857499999999999E-2</v>
       </c>
       <c r="M19" s="71">
         <f t="shared" si="0"/>
-        <v>219258</v>
+        <v>280858</v>
       </c>
       <c r="N19" s="166">
         <f t="shared" si="0"/>
-        <v>0.54814499999999988</v>
+        <v>0.70214499999999991</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -23190,20 +23548,20 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>7305</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-22294</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>6.6409090909090904E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.20267272727272725</v>
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>94987</v>
+        <v>65388</v>
       </c>
       <c r="N20" s="166">
         <f t="shared" si="0"/>
-        <v>0.86351818181818163</v>
+        <v>0.59443636363636354</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -23242,20 +23600,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>3598</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-20083</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.14391999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.80332000000000003</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-39948</v>
+        <v>-63629</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-1.5979199999999998</v>
+        <v>-2.5451600000000001</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -23294,11 +23652,11 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>1007</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>5.0350000000000004E-3</v>
       </c>
       <c r="M22" s="71">
@@ -23346,20 +23704,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-140506</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-126998</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.9367066666666668</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.84665333333333326</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>-25493</v>
+        <v>-11985</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>-0.1699533333333334</v>
+        <v>-7.989999999999986E-2</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -23398,11 +23756,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -23450,20 +23808,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>25929</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>20679</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.2357181818181818</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.18799090909090907</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>230633</v>
+        <v>225383</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>2.096663636363636</v>
+        <v>2.0489363636363631</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -23502,20 +23860,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-1027123</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-1497123</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-4.4657521739130441</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-6.5092304347826087</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-673062</v>
+        <v>-1143062</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-2.9263565217391316</v>
+        <v>-4.9698347826086966</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -23552,20 +23910,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>5794</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>4094</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.28970000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.20469999999999999</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-14502</v>
+        <v>-16202</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.72509999999999986</v>
+        <v>-0.81009999999999993</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -23604,20 +23962,20 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-47000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>34666</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-9.4E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>6.9332000000000005E-2</v>
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>-311918</v>
+        <v>-230252</v>
       </c>
       <c r="N28" s="166">
         <f t="shared" si="0"/>
-        <v>-0.62383599999999995</v>
+        <v>-0.46050399999999997</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -23656,20 +24014,20 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-460666</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-1231866</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.46066600000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-1.2318659999999999</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>3006746</v>
+        <v>2235546</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>3.0067459999999997</v>
+        <v>2.2355460000000003</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -23709,11 +24067,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -23761,11 +24119,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -23813,11 +24171,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -23865,11 +24223,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -23917,11 +24275,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -23969,20 +24327,20 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-308883</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-341989</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.61776600000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.68397799999999997</v>
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>390969</v>
+        <v>357863</v>
       </c>
       <c r="N35" s="166">
         <f t="shared" si="0"/>
-        <v>0.7819379999999998</v>
+        <v>0.71572599999999986</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -24021,20 +24379,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>147515</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>165843</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.29503000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.33168599999999998</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>1174922</v>
+        <v>1193250</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>2.349844</v>
+        <v>2.3864999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -24073,20 +24431,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-145944</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-130384</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-2.9188800000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-2.6076800000000002</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-225308</v>
+        <v>-209748</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-4.5061600000000004</v>
+        <v>-4.19496</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -24125,20 +24483,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>95813</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>140189</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>2.3953250000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>3.5047250000000001</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>30288</v>
+        <v>74664</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>0.75720000000000032</v>
+        <v>1.8666000000000003</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -24177,11 +24535,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -24229,11 +24587,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -24281,20 +24639,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-126402</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-116580</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.31600499999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.29144999999999999</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>584534</v>
+        <v>594356</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.4613350000000001</v>
+        <v>1.4858900000000002</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -24333,20 +24691,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-88079</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-208879</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.88078999999999996</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-2.0887899999999999</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>115553</v>
+        <v>-5247</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>1.1555299999999999</v>
+        <v>-5.2470000000000017E-2</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -24383,11 +24741,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -24435,20 +24793,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-16088</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-7955</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.32175999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.15909999999999999</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-82471</v>
+        <v>-74338</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6494199999999999</v>
+        <v>-1.4867599999999999</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -24487,20 +24845,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-2278</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>55933</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-7.5933333333333339E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.18644333333333332</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-113070</v>
+        <v>-54859</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.37690000000000001</v>
+        <v>-0.18286333333333335</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -24539,11 +24897,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -24591,11 +24949,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -24641,20 +24999,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-39779</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-61529</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-3.9779</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-6.1528999999999998</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>-56711</v>
+        <v>-78461</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>-5.6711</v>
+        <v>-7.8460999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -24693,20 +25051,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-11097</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>9422</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.22194</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.18844</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>23231</v>
+        <v>43750</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.14402000000000001</v>
+        <v>0.5544</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -24745,20 +25103,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-133607</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-449753</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-1.3360700000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-4.4975300000000002</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>753767</v>
+        <v>437621</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>7.5376699999999994</v>
+        <v>4.3762099999999995</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -24795,20 +25153,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>546</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>11946</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>5.4600000000000003E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>1.1946000000000001</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>-3000</v>
+        <v>8400</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>-0.30000000000000004</v>
+        <v>0.84000000000000008</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -24847,20 +25205,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>255502</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>672348</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.85167333333333317</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>2.2411599999999998</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>246769</v>
+        <v>663615</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>0.8225633333333332</v>
+        <v>2.2120499999999996</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -24893,11 +25251,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -24945,11 +25303,11 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>-156125</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>-0.39031250000000001</v>
       </c>
       <c r="M54" s="71">
@@ -24997,20 +25355,20 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-73205</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-76805</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.18301249999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.1920125</v>
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>269069</v>
+        <v>265469</v>
       </c>
       <c r="N55" s="166">
         <f t="shared" si="0"/>
-        <v>0.6726724999999999</v>
+        <v>0.66367249999999989</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -25047,20 +25405,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-760336</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-707936</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.76033600000000012</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.70793600000000012</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1795416</v>
+        <v>-1743016</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.7955160000000001</v>
+        <v>-1.7431160000000001</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -25093,11 +25451,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -25145,20 +25503,20 @@
         <v>-0.14384</v>
       </c>
       <c r="K58" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>11128</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>30670</v>
       </c>
       <c r="L58" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>0.22256000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>0.61339999999999995</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-23167</v>
+        <v>-3625</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-0.46333999999999997</v>
+        <v>-7.2500000000000009E-2</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -25197,20 +25555,20 @@
         <v>0.10279846153846153</v>
       </c>
       <c r="K59" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>34489</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-617713</v>
       </c>
       <c r="L59" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>5.3060000000000003E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.95032769230769243</v>
       </c>
       <c r="M59" s="71">
         <f t="shared" si="0"/>
-        <v>978433</v>
+        <v>326231</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" si="0"/>
-        <v>2.3486709615384616</v>
+        <v>1.3452832692307692</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -25249,11 +25607,11 @@
         <v>-0.20608799999999999</v>
       </c>
       <c r="K60" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>-158276</v>
       </c>
       <c r="L60" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>-1.266208</v>
       </c>
       <c r="M60" s="71">
@@ -25301,20 +25659,20 @@
         <v>-0.86802666666666684</v>
       </c>
       <c r="K61" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-178780</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-174516</v>
       </c>
       <c r="L61" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.59593333333333343</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-0.58172000000000001</v>
       </c>
       <c r="M61" s="71">
         <f t="shared" si="0"/>
-        <v>525293</v>
+        <v>529557</v>
       </c>
       <c r="N61" s="166">
         <f t="shared" si="0"/>
-        <v>1.7509766666666668</v>
+        <v>1.7651900000000003</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -25353,11 +25711,11 @@
         <v>-0.31176799999999999</v>
       </c>
       <c r="K62" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L62" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M62" s="71">
@@ -25403,11 +25761,11 @@
         <v>0.55113999999999996</v>
       </c>
       <c r="K63" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>11400</v>
       </c>
       <c r="L63" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="M63" s="71">
@@ -25453,20 +25811,20 @@
         <v>0.43251600000000001</v>
       </c>
       <c r="K64" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>3938</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>22128</v>
       </c>
       <c r="L64" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>7.8759999999999993E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>4.4256000000000004E-2</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>493343</v>
+        <v>511533</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>0.98668599999999995</v>
+        <v>1.023066</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -25488,12 +25846,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-3978545</v>
+        <v>-5433285</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>7801492</v>
+        <v>6346752</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -25573,20 +25931,20 @@
         <v>0.2384333333333333</v>
       </c>
       <c r="K69" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-283628</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-715553</v>
       </c>
       <c r="L69" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>-0.94542666666666675</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>-2.3851766666666663</v>
       </c>
       <c r="M69" s="153">
         <f t="shared" ref="M69:N69" si="29">G69+I69+K69</f>
-        <v>402882</v>
+        <v>-29043</v>
       </c>
       <c r="N69" s="167">
         <f t="shared" si="29"/>
-        <v>1.3429400000000005</v>
+        <v>-9.6809999999999174E-2</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -25623,16 +25981,16 @@
         <v>0</v>
       </c>
       <c r="K70" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
-        <v>134616</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <v>87266</v>
       </c>
       <c r="L70" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADT$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DU$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="153">
         <f t="shared" ref="M70" si="30">G70+I70+K70</f>
-        <v>1303501</v>
+        <v>1256151</v>
       </c>
       <c r="N70" s="167">
         <f t="shared" ref="N70" si="31">H70+J70+L70</f>
@@ -25652,508 +26010,508 @@
       <c r="J71" s="104"/>
       <c r="K71" s="93">
         <f>SUM(K69:K70)</f>
-        <v>-149012</v>
+        <v>-628287</v>
       </c>
       <c r="L71" s="113"/>
       <c r="M71" s="93">
         <f>SUM(M69:M70)</f>
-        <v>1706383</v>
+        <v>1227108</v>
       </c>
       <c r="N71" s="236"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
-    <cfRule type="expression" dxfId="393" priority="229">
+    <cfRule type="expression" dxfId="395" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="392" priority="228">
+    <cfRule type="expression" dxfId="394" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="391" priority="227">
+    <cfRule type="expression" dxfId="393" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="390" priority="226">
+    <cfRule type="expression" dxfId="392" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="389" priority="222">
+    <cfRule type="expression" dxfId="391" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="388" priority="220">
+    <cfRule type="expression" dxfId="390" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="387" priority="218">
+    <cfRule type="expression" dxfId="389" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="386" priority="212">
+    <cfRule type="expression" dxfId="388" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="385" priority="202">
+    <cfRule type="expression" dxfId="387" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="384" priority="207">
+    <cfRule type="expression" dxfId="386" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="383" priority="203">
+    <cfRule type="expression" dxfId="385" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="382" priority="188">
+    <cfRule type="expression" dxfId="384" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="381" priority="183">
+    <cfRule type="expression" dxfId="383" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="380" priority="189">
+    <cfRule type="expression" dxfId="382" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="379" priority="174">
+    <cfRule type="expression" dxfId="381" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="378" priority="172">
+    <cfRule type="expression" dxfId="380" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="377" priority="171">
+    <cfRule type="expression" dxfId="379" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="376" priority="166">
+    <cfRule type="expression" dxfId="378" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="375" priority="162">
+    <cfRule type="expression" dxfId="377" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="374" priority="163">
+    <cfRule type="expression" dxfId="376" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="373" priority="157">
+    <cfRule type="expression" dxfId="375" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="372" priority="143">
+    <cfRule type="expression" dxfId="374" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="371" priority="142">
+    <cfRule type="expression" dxfId="373" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="370" priority="132">
+    <cfRule type="expression" dxfId="372" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="369" priority="126">
+    <cfRule type="expression" dxfId="371" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="368" priority="125">
+    <cfRule type="expression" dxfId="370" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="367" priority="124">
+    <cfRule type="expression" dxfId="369" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="366" priority="123">
+    <cfRule type="expression" dxfId="368" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="365" priority="122">
+    <cfRule type="expression" dxfId="367" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="364" priority="121">
+    <cfRule type="expression" dxfId="366" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="363" priority="120">
+    <cfRule type="expression" dxfId="365" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="362" priority="109">
+    <cfRule type="expression" dxfId="364" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="361" priority="105">
+    <cfRule type="expression" dxfId="363" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="360" priority="104">
+    <cfRule type="expression" dxfId="362" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="359" priority="101">
+    <cfRule type="expression" dxfId="361" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="358" priority="97">
+    <cfRule type="expression" dxfId="360" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="357" priority="92">
+    <cfRule type="expression" dxfId="359" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="356" priority="91">
+    <cfRule type="expression" dxfId="358" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="355" priority="88">
+    <cfRule type="expression" dxfId="357" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="354" priority="89">
+    <cfRule type="expression" dxfId="356" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="353" priority="83">
+    <cfRule type="expression" dxfId="355" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="352" priority="82">
+    <cfRule type="expression" dxfId="354" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="351" priority="74">
+    <cfRule type="expression" dxfId="353" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="350" priority="73">
+    <cfRule type="expression" dxfId="352" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="349" priority="70">
+    <cfRule type="expression" dxfId="351" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="348" priority="71">
+    <cfRule type="expression" dxfId="350" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="347" priority="63">
+    <cfRule type="expression" dxfId="349" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="346" priority="62">
+    <cfRule type="expression" dxfId="348" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="345" priority="61">
+    <cfRule type="expression" dxfId="347" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="344" priority="60">
+    <cfRule type="expression" dxfId="346" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="343" priority="59">
+    <cfRule type="expression" dxfId="345" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="342" priority="58">
+    <cfRule type="expression" dxfId="344" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="341" priority="47">
+    <cfRule type="expression" dxfId="343" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="340" priority="57">
+    <cfRule type="expression" dxfId="342" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="339" priority="56">
+    <cfRule type="expression" dxfId="341" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="338" priority="55">
+    <cfRule type="expression" dxfId="340" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="337" priority="54">
+    <cfRule type="expression" dxfId="339" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="336" priority="53">
+    <cfRule type="expression" dxfId="338" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="335" priority="52">
+    <cfRule type="expression" dxfId="337" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="334" priority="51">
+    <cfRule type="expression" dxfId="336" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="333" priority="50">
+    <cfRule type="expression" dxfId="335" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="332" priority="48">
+    <cfRule type="expression" dxfId="334" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="331" priority="46">
+    <cfRule type="expression" dxfId="333" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="330" priority="45">
+    <cfRule type="expression" dxfId="332" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="329" priority="42">
+    <cfRule type="expression" dxfId="331" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="328" priority="41">
+    <cfRule type="expression" dxfId="330" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="327" priority="34">
+    <cfRule type="expression" dxfId="329" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 M64:N64">
-    <cfRule type="expression" dxfId="326" priority="33">
+    <cfRule type="expression" dxfId="328" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="325" priority="32">
+    <cfRule type="expression" dxfId="327" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="324" priority="31">
+    <cfRule type="expression" dxfId="326" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="323" priority="30">
+    <cfRule type="expression" dxfId="325" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="322" priority="29">
+    <cfRule type="expression" dxfId="324" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="321" priority="28">
+    <cfRule type="expression" dxfId="323" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="320" priority="27">
+    <cfRule type="expression" dxfId="322" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="319" priority="26">
+    <cfRule type="expression" dxfId="321" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="318" priority="25">
+    <cfRule type="expression" dxfId="320" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="317" priority="24">
+    <cfRule type="expression" dxfId="319" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="316" priority="20">
+    <cfRule type="expression" dxfId="318" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="315" priority="23">
+    <cfRule type="expression" dxfId="317" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="314" priority="22">
+    <cfRule type="expression" dxfId="316" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="313" priority="21">
+    <cfRule type="expression" dxfId="315" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="312" priority="19">
+    <cfRule type="expression" dxfId="314" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="311" priority="17">
+    <cfRule type="expression" dxfId="313" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="310" priority="16">
+    <cfRule type="expression" dxfId="312" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="309" priority="15">
+    <cfRule type="expression" dxfId="311" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="308" priority="14">
+    <cfRule type="expression" dxfId="310" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="307" priority="13">
+    <cfRule type="expression" dxfId="309" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="306" priority="12">
+    <cfRule type="expression" dxfId="308" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="305" priority="11">
+    <cfRule type="expression" dxfId="307" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="304" priority="10">
+    <cfRule type="expression" dxfId="306" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="303" priority="9">
+    <cfRule type="expression" dxfId="305" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="302" priority="8">
+    <cfRule type="expression" dxfId="304" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="301" priority="7">
+    <cfRule type="expression" dxfId="303" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="300" priority="6">
+    <cfRule type="expression" dxfId="302" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="299" priority="5">
+    <cfRule type="expression" dxfId="301" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="298" priority="4">
+    <cfRule type="expression" dxfId="300" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="297" priority="3">
+    <cfRule type="expression" dxfId="299" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:J57 M57:N57">
-    <cfRule type="expression" dxfId="296" priority="2">
+    <cfRule type="expression" dxfId="298" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:L70">
-    <cfRule type="expression" dxfId="295" priority="1">
+    <cfRule type="expression" dxfId="297" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31844,42 +32202,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="294" priority="13">
+    <cfRule type="expression" dxfId="296" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="293" priority="12">
+    <cfRule type="expression" dxfId="295" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="292" priority="11">
+    <cfRule type="expression" dxfId="294" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="291" priority="5">
+    <cfRule type="expression" dxfId="293" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="290" priority="4">
+    <cfRule type="expression" dxfId="292" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="289" priority="3">
+    <cfRule type="expression" dxfId="291" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="288" priority="2">
+    <cfRule type="expression" dxfId="290" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="287" priority="1">
+    <cfRule type="expression" dxfId="289" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37917,112 +38275,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="286" priority="28">
+    <cfRule type="expression" dxfId="288" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="285" priority="27">
+    <cfRule type="expression" dxfId="287" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="284" priority="26">
+    <cfRule type="expression" dxfId="286" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="283" priority="25">
+    <cfRule type="expression" dxfId="285" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="282" priority="23">
+    <cfRule type="expression" dxfId="284" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="281" priority="22">
+    <cfRule type="expression" dxfId="283" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="280" priority="20">
+    <cfRule type="expression" dxfId="282" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="279" priority="19">
+    <cfRule type="expression" dxfId="281" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="278" priority="15">
+    <cfRule type="expression" dxfId="280" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="277" priority="14">
+    <cfRule type="expression" dxfId="279" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="276" priority="13">
+    <cfRule type="expression" dxfId="278" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="275" priority="12">
+    <cfRule type="expression" dxfId="277" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="274" priority="11">
+    <cfRule type="expression" dxfId="276" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="273" priority="10">
+    <cfRule type="expression" dxfId="275" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="272" priority="9">
+    <cfRule type="expression" dxfId="274" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="271" priority="8">
+    <cfRule type="expression" dxfId="273" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="270" priority="7">
+    <cfRule type="expression" dxfId="272" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="269" priority="6">
+    <cfRule type="expression" dxfId="271" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="268" priority="1">
+    <cfRule type="expression" dxfId="270" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="267" priority="5">
+    <cfRule type="expression" dxfId="269" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="266" priority="4">
+    <cfRule type="expression" dxfId="268" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="265" priority="2">
+    <cfRule type="expression" dxfId="267" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43937,107 +44295,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="264" priority="24">
+    <cfRule type="expression" dxfId="266" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="263" priority="23">
+    <cfRule type="expression" dxfId="265" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="262" priority="22">
+    <cfRule type="expression" dxfId="264" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="261" priority="21">
+    <cfRule type="expression" dxfId="263" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="260" priority="20">
+    <cfRule type="expression" dxfId="262" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="259" priority="19">
+    <cfRule type="expression" dxfId="261" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="258" priority="18">
+    <cfRule type="expression" dxfId="260" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="257" priority="15">
+    <cfRule type="expression" dxfId="259" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="256" priority="14">
+    <cfRule type="expression" dxfId="258" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="255" priority="13">
+    <cfRule type="expression" dxfId="257" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="254" priority="12">
+    <cfRule type="expression" dxfId="256" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="253" priority="1">
+    <cfRule type="expression" dxfId="255" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="252" priority="10">
+    <cfRule type="expression" dxfId="254" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="251" priority="9">
+    <cfRule type="expression" dxfId="253" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="250" priority="8">
+    <cfRule type="expression" dxfId="252" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="249" priority="7">
+    <cfRule type="expression" dxfId="251" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="248" priority="6">
+    <cfRule type="expression" dxfId="250" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="247" priority="5">
+    <cfRule type="expression" dxfId="249" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="246" priority="4">
+    <cfRule type="expression" dxfId="248" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="245" priority="3">
+    <cfRule type="expression" dxfId="247" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="244" priority="2">
+    <cfRule type="expression" dxfId="246" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44389,11 +44747,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-76905</v>
+        <v>-67693</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.5381</v>
+        <v>-1.3538600000000001</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -44410,11 +44768,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-125241</v>
+        <v>-116029</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-2.50482</v>
+        <v>-2.3205800000000001</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44471,11 +44829,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-347337</v>
+        <v>-164518</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.1577900000000001</v>
+        <v>-0.54839333333333329</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -44492,11 +44850,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>986937</v>
+        <v>1169756</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.28979</v>
+        <v>3.899186666666667</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44668,11 +45026,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-512138</v>
+        <v>-390738</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.7071266666666667</v>
+        <v>-1.30246</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -44688,11 +45046,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-871047</v>
+        <v>-749647</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-4.347806666666667</v>
+        <v>-3.9431400000000001</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44749,11 +45107,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-211743</v>
+        <v>-180803</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4116200000000005</v>
+        <v>-1.2053533333333337</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -44769,11 +45127,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-386705</v>
+        <v>-355765</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5780333333333338</v>
+        <v>-2.3717666666666668</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44830,11 +45188,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-160512</v>
+        <v>-151412</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-2.6752000000000002</v>
+        <v>-2.5235333333333339</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -44850,11 +45208,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-160512</v>
+        <v>-151412</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-2.6752000000000002</v>
+        <v>-2.5235333333333339</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44911,11 +45269,11 @@
       <c r="O13" s="215"/>
       <c r="P13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>538179</v>
+        <v>203017</v>
       </c>
       <c r="Q13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.3587860000000001</v>
+        <v>0.13534466666666678</v>
       </c>
       <c r="R13" s="159"/>
       <c r="S13" s="88">
@@ -44932,11 +45290,11 @@
       <c r="X13"/>
       <c r="Y13" s="154">
         <f t="shared" si="0"/>
-        <v>-830020</v>
+        <v>-1165182</v>
       </c>
       <c r="Z13" s="168">
         <f t="shared" si="1"/>
-        <v>-0.55334666666666665</v>
+        <v>-0.77678799999999992</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45320,11 +45678,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>287919</v>
+        <v>433086</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.4798650000000001</v>
+        <v>0.72181000000000006</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -45340,11 +45698,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>92585</v>
+        <v>237752</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.9377549999999997</v>
+        <v>-2.6958099999999998</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45401,11 +45759,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5965</v>
+        <v>3220</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5.9649999999999995E-2</v>
+        <v>3.2200000000000006E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -45421,11 +45779,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>9644</v>
+        <v>6899</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>9.6439999999999998E-2</v>
+        <v>6.899000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45572,11 +45930,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>67588</v>
+        <v>58822</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.27035199999999998</v>
+        <v>0.23528799999999994</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -45592,11 +45950,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-199828</v>
+        <v>-208594</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4038080000000002</v>
+        <v>-2.4388719999999999</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45653,11 +46011,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-66142</v>
+        <v>-74708</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.30064545454545455</v>
+        <v>-0.33958181818181815</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -45673,11 +46031,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-155042</v>
+        <v>-163608</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.1896454545454547</v>
+        <v>-1.2285818181818182</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45815,11 +46173,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>69040</v>
+        <v>41540</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.69040000000000001</v>
+        <v>0.41539999999999999</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -45835,11 +46193,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1784385</v>
+        <v>1756885</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.84385</v>
+        <v>17.568849999999998</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46137,11 +46495,11 @@
       <c r="O28" s="215"/>
       <c r="P28" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-96558</v>
+        <v>-54338</v>
       </c>
       <c r="Q28" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.38623200000000002</v>
+        <v>-0.21735199999999999</v>
       </c>
       <c r="R28" s="159"/>
       <c r="S28" s="88">
@@ -46157,11 +46515,11 @@
       <c r="W28" s="72"/>
       <c r="Y28" s="154">
         <f t="shared" si="0"/>
-        <v>261655</v>
+        <v>303875</v>
       </c>
       <c r="Z28" s="168">
         <f t="shared" si="1"/>
-        <v>1.0466199999999999</v>
+        <v>1.2155</v>
       </c>
     </row>
     <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46218,11 +46576,11 @@
       <c r="O29" s="215"/>
       <c r="P29" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>219258</v>
+        <v>280858</v>
       </c>
       <c r="Q29" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.54814499999999988</v>
+        <v>0.70214499999999991</v>
       </c>
       <c r="R29" s="159"/>
       <c r="S29" s="88">
@@ -46239,11 +46597,11 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="154">
         <f t="shared" si="0"/>
-        <v>889721</v>
+        <v>951321</v>
       </c>
       <c r="Z29" s="168">
         <f t="shared" si="1"/>
-        <v>2.2243024999999998</v>
+        <v>2.3783024999999998</v>
       </c>
     </row>
     <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46300,11 +46658,11 @@
       <c r="O30" s="215"/>
       <c r="P30" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>94987</v>
+        <v>65388</v>
       </c>
       <c r="Q30" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.86351818181818163</v>
+        <v>0.59443636363636354</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="88">
@@ -46321,11 +46679,11 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="154">
         <f t="shared" si="0"/>
-        <v>94705</v>
+        <v>65106</v>
       </c>
       <c r="Z30" s="168">
         <f t="shared" si="1"/>
-        <v>0.86095454545454531</v>
+        <v>0.59187272727272722</v>
       </c>
     </row>
     <row r="31" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46471,11 +46829,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-25493</v>
+        <v>-11985</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.1699533333333334</v>
+        <v>-7.989999999999986E-2</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -46492,11 +46850,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-530562</v>
+        <v>-517054</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-3.5370800000000009</v>
+        <v>-3.4470266666666673</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46634,11 +46992,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>230633</v>
+        <v>225383</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.096663636363636</v>
+        <v>2.0489363636363631</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -46654,11 +47012,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-88307</v>
+        <v>-93557</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.80279090909090911</v>
+        <v>-0.85051818181818195</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -46803,11 +47161,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-673062</v>
+        <v>-1143062</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-2.9263565217391316</v>
+        <v>-4.9698347826086966</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -46823,11 +47181,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>3488041</v>
+        <v>3018041</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>15.165395652173912</v>
+        <v>13.121917391304347</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46882,11 +47240,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-14502</v>
+        <v>-16202</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.72509999999999986</v>
+        <v>-0.81009999999999993</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -46902,11 +47260,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-14502</v>
+        <v>-16202</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.72509999999999986</v>
+        <v>-0.81009999999999993</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46963,11 +47321,11 @@
       <c r="O38" s="215"/>
       <c r="P38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-311918</v>
+        <v>-230252</v>
       </c>
       <c r="Q38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.62383599999999995</v>
+        <v>-0.46050399999999997</v>
       </c>
       <c r="R38" s="159"/>
       <c r="S38" s="88">
@@ -46983,11 +47341,11 @@
       <c r="W38" s="72"/>
       <c r="Y38" s="154">
         <f t="shared" si="0"/>
-        <v>2754488</v>
+        <v>2836154</v>
       </c>
       <c r="Z38" s="168">
         <f t="shared" si="1"/>
-        <v>5.5089759999999997</v>
+        <v>5.6723079999999992</v>
       </c>
     </row>
     <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47044,11 +47402,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3006746</v>
+        <v>2235546</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.0067459999999997</v>
+        <v>2.2355460000000003</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -47065,11 +47423,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>6600152</v>
+        <v>5828952</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>6.6001519999999996</v>
+        <v>5.828952000000001</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -47560,11 +47918,11 @@
       <c r="O45" s="215"/>
       <c r="P45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>390969</v>
+        <v>357863</v>
       </c>
       <c r="Q45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.7819379999999998</v>
+        <v>0.71572599999999986</v>
       </c>
       <c r="R45" s="159"/>
       <c r="S45" s="88">
@@ -47580,11 +47938,11 @@
       <c r="W45" s="72"/>
       <c r="Y45" s="154">
         <f t="shared" si="22"/>
-        <v>1608287</v>
+        <v>1575181</v>
       </c>
       <c r="Z45" s="168">
         <f t="shared" si="23"/>
-        <v>3.2165739999999996</v>
+        <v>3.1503619999999994</v>
       </c>
     </row>
     <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47641,11 +47999,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1174922</v>
+        <v>1193250</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.349844</v>
+        <v>2.3864999999999998</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -47662,11 +48020,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>1127184</v>
+        <v>1145512</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>2.2543679999999999</v>
+        <v>2.2910239999999997</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -47724,11 +48082,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-225308</v>
+        <v>-209748</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4.5061600000000004</v>
+        <v>-4.19496</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -47744,11 +48102,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-108413</v>
+        <v>-92853</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-2.1682600000000005</v>
+        <v>-1.8570600000000002</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -47893,11 +48251,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>30288</v>
+        <v>74664</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.75720000000000032</v>
+        <v>1.8666000000000003</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -47913,11 +48271,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>18460</v>
+        <v>62836</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>0.46150000000000024</v>
+        <v>1.5709000000000002</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -48148,11 +48506,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>584534</v>
+        <v>594356</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.4613350000000001</v>
+        <v>1.4858900000000002</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -48168,11 +48526,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>184235</v>
+        <v>194057</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.46058749999999993</v>
+        <v>0.48514250000000003</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48229,11 +48587,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>115553</v>
+        <v>-5247</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.1555299999999999</v>
+        <v>-5.2470000000000017E-2</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -48249,11 +48607,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>861346</v>
+        <v>740546</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>8.6134600000000017</v>
+        <v>7.4054600000000015</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48391,11 +48749,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-82471</v>
+        <v>-74338</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6494199999999999</v>
+        <v>-1.4867599999999999</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -48412,11 +48770,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-328249</v>
+        <v>-320116</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.5649800000000003</v>
+        <v>-6.4023199999999996</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -48474,11 +48832,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-113070</v>
+        <v>-54859</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.37690000000000001</v>
+        <v>-0.18286333333333335</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -48494,11 +48852,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4812045</v>
+        <v>-4753834</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.040150000000004</v>
+        <v>-15.846113333333337</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -48728,11 +49086,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>23231</v>
+        <v>43750</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.14402000000000001</v>
+        <v>0.5544</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -48749,11 +49107,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>59954</v>
+        <v>80473</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.47285333333333335</v>
+        <v>0.88323333333333331</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -48817,11 +49175,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>753767</v>
+        <v>437621</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>7.5376699999999994</v>
+        <v>4.3762099999999995</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -48837,11 +49195,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>4303836</v>
+        <v>3987690</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>43.038359999999997</v>
+        <v>39.876899999999999</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -48903,11 +49261,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3000</v>
+        <v>8400</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.30000000000000004</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -48923,11 +49281,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>-3000</v>
+        <v>8400</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>-0.30000000000000004</v>
+        <v>0.84000000000000008</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48984,11 +49342,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>246769</v>
+        <v>663615</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.8225633333333332</v>
+        <v>2.2120499999999996</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -49004,11 +49362,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>919618</v>
+        <v>1336464</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>3.0653933333333327</v>
+        <v>4.4548799999999993</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -49235,11 +49593,11 @@
       <c r="O65" s="215"/>
       <c r="P65" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>269069</v>
+        <v>265469</v>
       </c>
       <c r="Q65" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.6726724999999999</v>
+        <v>0.66367249999999989</v>
       </c>
       <c r="R65" s="159"/>
       <c r="S65" s="153">
@@ -49256,11 +49614,11 @@
       <c r="X65" s="132"/>
       <c r="Y65" s="154">
         <f t="shared" si="22"/>
-        <v>793481</v>
+        <v>789881</v>
       </c>
       <c r="Z65" s="168">
         <f t="shared" si="23"/>
-        <v>1.9837025000000001</v>
+        <v>1.9747025</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49397,11 +49755,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1795416</v>
+        <v>-1743016</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.7955160000000001</v>
+        <v>-1.7431160000000001</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -49417,11 +49775,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1795416</v>
+        <v>-1743016</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.7955160000000001</v>
+        <v>-1.7431160000000001</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49535,11 +49893,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-23167</v>
+        <v>-3625</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.46333999999999997</v>
+        <v>-7.2500000000000009E-2</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -49555,11 +49913,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-69821</v>
+        <v>-50279</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-1.39642</v>
+        <v>-1.0055800000000001</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -49616,11 +49974,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>978433</v>
+        <v>326231</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.3486709615384616</v>
+        <v>1.3452832692307692</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="153">
@@ -49636,11 +49994,11 @@
       <c r="W70" s="150"/>
       <c r="Y70" s="154">
         <f t="shared" si="22"/>
-        <v>570481</v>
+        <v>-81721</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="23"/>
-        <v>1.3287909615384614</v>
+        <v>0.32540326923076912</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
@@ -49859,11 +50217,11 @@
       <c r="O73" s="215"/>
       <c r="P73" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>525293</v>
+        <v>529557</v>
       </c>
       <c r="Q73" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.7509766666666668</v>
+        <v>1.7651900000000003</v>
       </c>
       <c r="R73" s="159"/>
       <c r="S73" s="88">
@@ -49879,11 +50237,11 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="154">
         <f t="shared" si="22"/>
-        <v>357911</v>
+        <v>362175</v>
       </c>
       <c r="Z73" s="168">
         <f t="shared" si="23"/>
-        <v>1.193036666666667</v>
+        <v>1.2072500000000002</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
@@ -50098,11 +50456,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>493343</v>
+        <v>511533</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.98668599999999995</v>
+        <v>1.023066</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -50118,11 +50476,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>493343</v>
+        <v>511533</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>0.98668599999999995</v>
+        <v>1.023066</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -50155,7 +50513,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>7881012</v>
+        <v>6471703</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -50166,7 +50524,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>27823455</v>
+        <v>26432336</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -50462,11 +50820,11 @@
       <c r="O82" s="167"/>
       <c r="P82" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>402882</v>
+        <v>-29043</v>
       </c>
       <c r="Q82" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.3429400000000005</v>
+        <v>-9.6809999999999174E-2</v>
       </c>
       <c r="R82" s="159"/>
       <c r="S82" s="153">
@@ -50483,11 +50841,11 @@
       <c r="X82" s="132"/>
       <c r="Y82" s="52">
         <f t="shared" si="56"/>
-        <v>614382</v>
+        <v>182457</v>
       </c>
       <c r="Z82" s="53">
         <f t="shared" si="56"/>
-        <v>1.3429400000000005</v>
+        <v>-9.6809999999999174E-2</v>
       </c>
       <c r="AA82" s="132"/>
     </row>
@@ -50543,7 +50901,7 @@
       <c r="O83" s="167"/>
       <c r="P83" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1303501</v>
+        <v>1256151</v>
       </c>
       <c r="Q83" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
@@ -50563,7 +50921,7 @@
       <c r="W83" s="53"/>
       <c r="Y83" s="52">
         <f t="shared" ref="Y83" si="59">M83+P83+S83+V83</f>
-        <v>893501</v>
+        <v>846151</v>
       </c>
       <c r="Z83" s="53">
         <f t="shared" ref="Z83" si="60">N83+Q83+T83+W83</f>
@@ -50597,7 +50955,7 @@
       <c r="O84" s="123"/>
       <c r="P84" s="112">
         <f>SUM(P80:P83)</f>
-        <v>1706383</v>
+        <v>1227108</v>
       </c>
       <c r="Q84" s="123"/>
       <c r="R84" s="123"/>
@@ -50621,1212 +50979,1212 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 G77:W78">
-    <cfRule type="expression" dxfId="243" priority="448">
+    <cfRule type="expression" dxfId="245" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="242" priority="447">
+    <cfRule type="expression" dxfId="244" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="241" priority="444">
+    <cfRule type="expression" dxfId="243" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="240" priority="441">
+    <cfRule type="expression" dxfId="242" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="239" priority="442">
+    <cfRule type="expression" dxfId="241" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="238" priority="432">
+    <cfRule type="expression" dxfId="240" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="237" priority="433">
+    <cfRule type="expression" dxfId="239" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="236" priority="422">
+    <cfRule type="expression" dxfId="238" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="235" priority="420">
+    <cfRule type="expression" dxfId="237" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="234" priority="418">
+    <cfRule type="expression" dxfId="236" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="233" priority="409">
+    <cfRule type="expression" dxfId="235" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="232" priority="408">
+    <cfRule type="expression" dxfId="234" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="231" priority="380">
+    <cfRule type="expression" dxfId="233" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="230" priority="406">
+    <cfRule type="expression" dxfId="232" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="229" priority="405">
+    <cfRule type="expression" dxfId="231" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="228" priority="403">
+    <cfRule type="expression" dxfId="230" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="227" priority="402">
+    <cfRule type="expression" dxfId="229" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="226" priority="400">
+    <cfRule type="expression" dxfId="228" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="225" priority="387">
+    <cfRule type="expression" dxfId="227" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="224" priority="331">
+    <cfRule type="expression" dxfId="226" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="223" priority="378">
+    <cfRule type="expression" dxfId="225" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="222" priority="330">
+    <cfRule type="expression" dxfId="224" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="221" priority="383">
+    <cfRule type="expression" dxfId="223" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="220" priority="349">
+    <cfRule type="expression" dxfId="222" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="219" priority="347">
+    <cfRule type="expression" dxfId="221" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="218" priority="355">
+    <cfRule type="expression" dxfId="220" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="217" priority="354">
+    <cfRule type="expression" dxfId="219" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="216" priority="339">
+    <cfRule type="expression" dxfId="218" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="215" priority="338">
+    <cfRule type="expression" dxfId="217" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="214" priority="369">
+    <cfRule type="expression" dxfId="216" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="213" priority="329">
+    <cfRule type="expression" dxfId="215" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="212" priority="340">
+    <cfRule type="expression" dxfId="214" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="211" priority="350">
+    <cfRule type="expression" dxfId="213" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="210" priority="348">
+    <cfRule type="expression" dxfId="212" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="209" priority="341">
+    <cfRule type="expression" dxfId="211" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="208" priority="328">
+    <cfRule type="expression" dxfId="210" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="207" priority="286">
+    <cfRule type="expression" dxfId="209" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="206" priority="285">
+    <cfRule type="expression" dxfId="208" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="205" priority="283">
+    <cfRule type="expression" dxfId="207" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="204" priority="275">
+    <cfRule type="expression" dxfId="206" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="203" priority="274">
+    <cfRule type="expression" dxfId="205" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="202" priority="288">
+    <cfRule type="expression" dxfId="204" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="201" priority="287">
+    <cfRule type="expression" dxfId="203" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="200" priority="284">
+    <cfRule type="expression" dxfId="202" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="199" priority="282">
+    <cfRule type="expression" dxfId="201" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="198" priority="273">
+    <cfRule type="expression" dxfId="200" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="197" priority="267">
+    <cfRule type="expression" dxfId="199" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="196" priority="272">
+    <cfRule type="expression" dxfId="198" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="195" priority="271">
+    <cfRule type="expression" dxfId="197" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="194" priority="268">
+    <cfRule type="expression" dxfId="196" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="193" priority="270">
+    <cfRule type="expression" dxfId="195" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="192" priority="269">
+    <cfRule type="expression" dxfId="194" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="191" priority="260">
+    <cfRule type="expression" dxfId="193" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="190" priority="259">
+    <cfRule type="expression" dxfId="192" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="189" priority="256">
+    <cfRule type="expression" dxfId="191" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="188" priority="255">
+    <cfRule type="expression" dxfId="190" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="187" priority="253">
+    <cfRule type="expression" dxfId="189" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="186" priority="258">
+    <cfRule type="expression" dxfId="188" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="185" priority="257">
+    <cfRule type="expression" dxfId="187" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="184" priority="254">
+    <cfRule type="expression" dxfId="186" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="183" priority="246">
+    <cfRule type="expression" dxfId="185" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="182" priority="245">
+    <cfRule type="expression" dxfId="184" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="181" priority="244">
+    <cfRule type="expression" dxfId="183" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="180" priority="239">
+    <cfRule type="expression" dxfId="182" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="179" priority="238">
+    <cfRule type="expression" dxfId="181" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="178" priority="242">
+    <cfRule type="expression" dxfId="180" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="177" priority="241">
+    <cfRule type="expression" dxfId="179" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="176" priority="240">
+    <cfRule type="expression" dxfId="178" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="175" priority="243">
+    <cfRule type="expression" dxfId="177" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="174" priority="231">
+    <cfRule type="expression" dxfId="176" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="173" priority="227">
+    <cfRule type="expression" dxfId="175" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="172" priority="226">
+    <cfRule type="expression" dxfId="174" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="171" priority="220">
+    <cfRule type="expression" dxfId="173" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="170" priority="219">
+    <cfRule type="expression" dxfId="172" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="169" priority="223">
+    <cfRule type="expression" dxfId="171" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="168" priority="222">
+    <cfRule type="expression" dxfId="170" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="167" priority="221">
+    <cfRule type="expression" dxfId="169" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="166" priority="224">
+    <cfRule type="expression" dxfId="168" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="165" priority="208">
+    <cfRule type="expression" dxfId="167" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="164" priority="207">
+    <cfRule type="expression" dxfId="166" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="163" priority="206">
+    <cfRule type="expression" dxfId="165" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="162" priority="200">
+    <cfRule type="expression" dxfId="164" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="161" priority="199">
+    <cfRule type="expression" dxfId="163" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="160" priority="193">
+    <cfRule type="expression" dxfId="162" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="159" priority="198">
+    <cfRule type="expression" dxfId="161" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="158" priority="197">
+    <cfRule type="expression" dxfId="160" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="157" priority="194">
+    <cfRule type="expression" dxfId="159" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="156" priority="196">
+    <cfRule type="expression" dxfId="158" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="155" priority="195">
+    <cfRule type="expression" dxfId="157" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="154" priority="191">
+    <cfRule type="expression" dxfId="156" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="153" priority="190">
+    <cfRule type="expression" dxfId="155" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="152" priority="177">
+    <cfRule type="expression" dxfId="154" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="151" priority="186">
+    <cfRule type="expression" dxfId="153" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="150" priority="185">
+    <cfRule type="expression" dxfId="152" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="149" priority="175">
+    <cfRule type="expression" dxfId="151" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="148" priority="174">
+    <cfRule type="expression" dxfId="150" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="147" priority="173">
+    <cfRule type="expression" dxfId="149" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="146" priority="168">
+    <cfRule type="expression" dxfId="148" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="145" priority="165">
+    <cfRule type="expression" dxfId="147" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="144" priority="164">
+    <cfRule type="expression" dxfId="146" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="143" priority="163">
+    <cfRule type="expression" dxfId="145" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="142" priority="162">
+    <cfRule type="expression" dxfId="144" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="141" priority="161">
+    <cfRule type="expression" dxfId="143" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="140" priority="160">
+    <cfRule type="expression" dxfId="142" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="139" priority="147">
+    <cfRule type="expression" dxfId="141" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="138" priority="157">
+    <cfRule type="expression" dxfId="140" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="137" priority="156">
+    <cfRule type="expression" dxfId="139" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="136" priority="155">
+    <cfRule type="expression" dxfId="138" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="135" priority="154">
+    <cfRule type="expression" dxfId="137" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="134" priority="153">
+    <cfRule type="expression" dxfId="136" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="133" priority="152">
+    <cfRule type="expression" dxfId="135" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="132" priority="151">
+    <cfRule type="expression" dxfId="134" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="131" priority="142">
+    <cfRule type="expression" dxfId="133" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="130" priority="148">
+    <cfRule type="expression" dxfId="132" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="129" priority="146">
+    <cfRule type="expression" dxfId="131" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="128" priority="145">
+    <cfRule type="expression" dxfId="130" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="127" priority="144">
+    <cfRule type="expression" dxfId="129" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="126" priority="143">
+    <cfRule type="expression" dxfId="128" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="125" priority="141">
+    <cfRule type="expression" dxfId="127" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="124" priority="138">
+    <cfRule type="expression" dxfId="126" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="123" priority="137">
+    <cfRule type="expression" dxfId="125" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="122" priority="136">
+    <cfRule type="expression" dxfId="124" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="121" priority="135">
+    <cfRule type="expression" dxfId="123" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="120" priority="134">
+    <cfRule type="expression" dxfId="122" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="119" priority="133">
+    <cfRule type="expression" dxfId="121" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="118" priority="130">
+    <cfRule type="expression" dxfId="120" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="117" priority="132">
+    <cfRule type="expression" dxfId="119" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="116" priority="131">
+    <cfRule type="expression" dxfId="118" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="115" priority="129">
+    <cfRule type="expression" dxfId="117" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="114" priority="128">
+    <cfRule type="expression" dxfId="116" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="113" priority="127">
+    <cfRule type="expression" dxfId="115" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="112" priority="126">
+    <cfRule type="expression" dxfId="114" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="111" priority="124">
+    <cfRule type="expression" dxfId="113" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="110" priority="123">
+    <cfRule type="expression" dxfId="112" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="109" priority="122">
+    <cfRule type="expression" dxfId="111" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="108" priority="121">
+    <cfRule type="expression" dxfId="110" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="107" priority="120">
+    <cfRule type="expression" dxfId="109" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="106" priority="115">
+    <cfRule type="expression" dxfId="108" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="105" priority="114">
+    <cfRule type="expression" dxfId="107" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="104" priority="118">
+    <cfRule type="expression" dxfId="106" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="103" priority="117">
+    <cfRule type="expression" dxfId="105" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="102" priority="116">
+    <cfRule type="expression" dxfId="104" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="101" priority="119">
+    <cfRule type="expression" dxfId="103" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="100" priority="113">
+    <cfRule type="expression" dxfId="102" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="99" priority="111">
+    <cfRule type="expression" dxfId="101" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="98" priority="109">
+    <cfRule type="expression" dxfId="100" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="97" priority="108">
+    <cfRule type="expression" dxfId="99" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="96" priority="107">
+    <cfRule type="expression" dxfId="98" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="95" priority="106">
+    <cfRule type="expression" dxfId="97" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="94" priority="105">
+    <cfRule type="expression" dxfId="96" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="93" priority="104">
+    <cfRule type="expression" dxfId="95" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="92" priority="102">
+    <cfRule type="expression" dxfId="94" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="91" priority="92">
+    <cfRule type="expression" dxfId="93" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="90" priority="100">
+    <cfRule type="expression" dxfId="92" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="89" priority="99">
+    <cfRule type="expression" dxfId="91" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="88" priority="96">
+    <cfRule type="expression" dxfId="90" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="87" priority="95">
+    <cfRule type="expression" dxfId="89" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="86" priority="93">
+    <cfRule type="expression" dxfId="88" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="85" priority="98">
+    <cfRule type="expression" dxfId="87" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="84" priority="97">
+    <cfRule type="expression" dxfId="86" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="83" priority="94">
+    <cfRule type="expression" dxfId="85" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="82" priority="91">
+    <cfRule type="expression" dxfId="84" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="81" priority="90">
+    <cfRule type="expression" dxfId="83" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="80" priority="89">
+    <cfRule type="expression" dxfId="82" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="79" priority="88">
+    <cfRule type="expression" dxfId="81" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="78" priority="87">
+    <cfRule type="expression" dxfId="80" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="77" priority="86">
+    <cfRule type="expression" dxfId="79" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="76" priority="85">
+    <cfRule type="expression" dxfId="78" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="75" priority="84">
+    <cfRule type="expression" dxfId="77" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="74" priority="72">
+    <cfRule type="expression" dxfId="76" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="73" priority="82">
+    <cfRule type="expression" dxfId="75" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="72" priority="81">
+    <cfRule type="expression" dxfId="74" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="71" priority="80">
+    <cfRule type="expression" dxfId="73" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="70" priority="79">
+    <cfRule type="expression" dxfId="72" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="69" priority="78">
+    <cfRule type="expression" dxfId="71" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="68" priority="77">
+    <cfRule type="expression" dxfId="70" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="67" priority="76">
+    <cfRule type="expression" dxfId="69" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="66" priority="75">
+    <cfRule type="expression" dxfId="68" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="65" priority="74">
+    <cfRule type="expression" dxfId="67" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="64" priority="73">
+    <cfRule type="expression" dxfId="66" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="63" priority="71">
+    <cfRule type="expression" dxfId="65" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="62" priority="70">
+    <cfRule type="expression" dxfId="64" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="61" priority="69">
+    <cfRule type="expression" dxfId="63" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="60" priority="68">
+    <cfRule type="expression" dxfId="62" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="59" priority="62">
+    <cfRule type="expression" dxfId="61" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="58" priority="67">
+    <cfRule type="expression" dxfId="60" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="57" priority="66">
+    <cfRule type="expression" dxfId="59" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="56" priority="63">
+    <cfRule type="expression" dxfId="58" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="55" priority="65">
+    <cfRule type="expression" dxfId="57" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="54" priority="64">
+    <cfRule type="expression" dxfId="56" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q55:Q60 Q62:Q76">
-    <cfRule type="expression" dxfId="53" priority="59">
+    <cfRule type="expression" dxfId="55" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q11 P38:Q53 P55:Q60 P62:Q76">
-    <cfRule type="expression" dxfId="52" priority="58">
+    <cfRule type="expression" dxfId="54" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="51" priority="57">
+    <cfRule type="expression" dxfId="53" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="50" priority="56">
+    <cfRule type="expression" dxfId="52" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="49" priority="55">
+    <cfRule type="expression" dxfId="51" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="48" priority="54">
+    <cfRule type="expression" dxfId="50" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="47" priority="53">
+    <cfRule type="expression" dxfId="49" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="46" priority="52">
+    <cfRule type="expression" dxfId="48" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="45" priority="39">
+    <cfRule type="expression" dxfId="47" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="44" priority="48">
+    <cfRule type="expression" dxfId="46" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="43" priority="24">
+    <cfRule type="expression" dxfId="45" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="42" priority="46">
+    <cfRule type="expression" dxfId="44" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="41" priority="45">
+    <cfRule type="expression" dxfId="43" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="40" priority="44">
+    <cfRule type="expression" dxfId="42" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="39" priority="43">
+    <cfRule type="expression" dxfId="41" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="38" priority="42">
+    <cfRule type="expression" dxfId="40" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="37" priority="41">
+    <cfRule type="expression" dxfId="39" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="36" priority="40">
+    <cfRule type="expression" dxfId="38" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="35" priority="25">
+    <cfRule type="expression" dxfId="37" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="36" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="35" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="32" priority="34">
+    <cfRule type="expression" dxfId="34" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="33" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="30" priority="32">
+    <cfRule type="expression" dxfId="32" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="29" priority="31">
+    <cfRule type="expression" dxfId="31" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="28" priority="30">
+    <cfRule type="expression" dxfId="30" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="27" priority="29">
+    <cfRule type="expression" dxfId="29" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="26" priority="28">
+    <cfRule type="expression" dxfId="28" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="25" priority="27">
+    <cfRule type="expression" dxfId="27" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="24" priority="26">
+    <cfRule type="expression" dxfId="26" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="25" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="24" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="22" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="17" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="16" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="13" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="11" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="324">
   <si>
     <t>Sudeep</t>
   </si>
@@ -990,6 +990,9 @@
   </si>
   <si>
     <t>Fri</t>
+  </si>
+  <si>
+    <t>P2990</t>
   </si>
 </sst>
 </file>
@@ -2327,35 +2330,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="451">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="447">
     <dxf>
       <fill>
         <patternFill>
@@ -5972,16 +5947,18 @@
       <c r="Q4" s="158">
         <v>9212</v>
       </c>
-      <c r="R4" s="158"/>
+      <c r="R4" s="158">
+        <v>-149</v>
+      </c>
       <c r="S4" s="158"/>
       <c r="T4" s="211"/>
       <c r="U4" s="171">
         <f t="shared" ref="U4:U30" si="0">SUM(H4:T4)</f>
-        <v>-40649</v>
+        <v>-40798</v>
       </c>
       <c r="V4" s="149">
         <f t="shared" ref="V4:V30" si="1">IFERROR(U4/F4*100,0)/10000000</f>
-        <v>-0.81298000000000004</v>
+        <v>-0.81596000000000002</v>
       </c>
       <c r="AC4" s="133" t="s">
         <v>170</v>
@@ -6040,16 +6017,18 @@
       <c r="Q5" s="147">
         <v>182819</v>
       </c>
-      <c r="R5" s="147"/>
+      <c r="R5" s="147">
+        <v>81831</v>
+      </c>
       <c r="S5" s="147"/>
       <c r="T5" s="174"/>
       <c r="U5" s="171">
         <f t="shared" si="0"/>
-        <v>86453</v>
+        <v>168284</v>
       </c>
       <c r="V5" s="149">
         <f t="shared" si="1"/>
-        <v>0.28817666666666669</v>
+        <v>0.56094666666666659</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -6117,7 +6096,9 @@
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="142"/>
+      <c r="A7" s="142" t="s">
+        <v>323</v>
+      </c>
       <c r="B7" s="141" t="s">
         <v>309</v>
       </c>
@@ -6135,7 +6116,7 @@
       </c>
       <c r="G7" s="191"/>
       <c r="H7" s="147">
-        <v>-57700</v>
+        <v>-63700</v>
       </c>
       <c r="I7" s="147">
         <v>13000</v>
@@ -6152,26 +6133,30 @@
       <c r="M7" s="147">
         <v>0</v>
       </c>
-      <c r="N7" s="147"/>
+      <c r="N7" s="147">
+        <v>6500</v>
+      </c>
       <c r="O7" s="147">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="P7" s="147">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="Q7" s="147">
-        <v>0</v>
-      </c>
-      <c r="R7" s="147"/>
+        <v>29500</v>
+      </c>
+      <c r="R7" s="147">
+        <v>23300</v>
+      </c>
       <c r="S7" s="147"/>
       <c r="T7" s="174"/>
       <c r="U7" s="171">
         <f t="shared" si="0"/>
-        <v>23300</v>
+        <v>105547</v>
       </c>
       <c r="V7" s="149">
         <f t="shared" si="1"/>
-        <v>0.23300000000000001</v>
+        <v>1.0554699999999999</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6224,20 +6209,22 @@
       <c r="Q8" s="147">
         <v>121400</v>
       </c>
-      <c r="R8" s="147"/>
+      <c r="R8" s="147">
+        <v>-30125</v>
+      </c>
       <c r="S8" s="147"/>
       <c r="T8" s="174"/>
       <c r="U8" s="171">
         <f t="shared" si="0"/>
-        <v>64359</v>
+        <v>34234</v>
       </c>
       <c r="V8" s="149">
         <f t="shared" si="1"/>
-        <v>0.21453</v>
+        <v>0.11411333333333334</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="134">
-        <v>8466</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -6290,19 +6277,21 @@
       <c r="Q9" s="147">
         <v>30940</v>
       </c>
-      <c r="R9" s="147"/>
+      <c r="R9" s="147">
+        <v>-63430</v>
+      </c>
       <c r="S9" s="147"/>
       <c r="T9" s="174"/>
       <c r="U9" s="171">
         <f t="shared" si="0"/>
-        <v>113333</v>
+        <v>49903</v>
       </c>
       <c r="V9" s="149">
         <f t="shared" si="1"/>
-        <v>0.7555533333333333</v>
+        <v>0.33268666666666663</v>
       </c>
       <c r="X9" s="134">
-        <v>116535</v>
+        <v>32574</v>
       </c>
       <c r="Y9" s="134"/>
     </row>
@@ -6354,23 +6343,25 @@
       <c r="Q10" s="147">
         <v>9100</v>
       </c>
-      <c r="R10" s="147"/>
+      <c r="R10" s="147">
+        <v>-31500</v>
+      </c>
       <c r="S10" s="147"/>
       <c r="T10" s="174"/>
       <c r="U10" s="171">
         <f t="shared" si="0"/>
-        <v>40837</v>
+        <v>9337</v>
       </c>
       <c r="V10" s="149">
         <f t="shared" si="1"/>
-        <v>0.68061666666666665</v>
+        <v>0.15561666666666668</v>
       </c>
       <c r="X10" s="134">
-        <v>125001</v>
+        <v>32587</v>
       </c>
       <c r="Y10" s="134">
         <f>(X10+X9)/10000000*13780</f>
-        <v>332.83660800000001</v>
+        <v>89.791858000000005</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -6423,7 +6414,9 @@
       <c r="Q11" s="147">
         <v>-335162</v>
       </c>
-      <c r="R11" s="147"/>
+      <c r="R11" s="147">
+        <v>0</v>
+      </c>
       <c r="S11" s="147"/>
       <c r="T11" s="174"/>
       <c r="U11" s="171">
@@ -6487,16 +6480,18 @@
       <c r="Q12" s="147">
         <v>145167</v>
       </c>
-      <c r="R12" s="147"/>
+      <c r="R12" s="147">
+        <v>-100</v>
+      </c>
       <c r="S12" s="147"/>
       <c r="T12" s="174"/>
       <c r="U12" s="171">
         <f t="shared" si="0"/>
-        <v>25306</v>
+        <v>25206</v>
       </c>
       <c r="V12" s="149">
         <f t="shared" si="1"/>
-        <v>4.2176666666666668E-2</v>
+        <v>4.2009999999999999E-2</v>
       </c>
       <c r="X12" s="134"/>
       <c r="Y12" s="134"/>
@@ -6551,16 +6546,18 @@
       <c r="Q13" s="147">
         <v>-2745</v>
       </c>
-      <c r="R13" s="147"/>
+      <c r="R13" s="147">
+        <v>2399</v>
+      </c>
       <c r="S13" s="147"/>
       <c r="T13" s="174"/>
       <c r="U13" s="171">
         <f t="shared" si="0"/>
-        <v>-10196</v>
+        <v>-7797</v>
       </c>
       <c r="V13" s="149">
         <f t="shared" si="1"/>
-        <v>-0.10196</v>
+        <v>-7.7969999999999998E-2</v>
       </c>
       <c r="X13" s="134"/>
       <c r="Y13" s="134"/>
@@ -6615,16 +6612,18 @@
       <c r="Q14" s="147">
         <v>-8766</v>
       </c>
-      <c r="R14" s="147"/>
+      <c r="R14" s="147">
+        <v>-10140</v>
+      </c>
       <c r="S14" s="147"/>
       <c r="T14" s="174"/>
       <c r="U14" s="171">
         <f t="shared" si="0"/>
-        <v>13902</v>
+        <v>3762</v>
       </c>
       <c r="V14" s="149">
         <f t="shared" si="1"/>
-        <v>5.5607999999999998E-2</v>
+        <v>1.5048000000000001E-2</v>
       </c>
       <c r="X14" s="134"/>
       <c r="Y14" s="134"/>
@@ -6679,28 +6678,30 @@
       <c r="Q15" s="147">
         <v>-8566</v>
       </c>
-      <c r="R15" s="147"/>
+      <c r="R15" s="147">
+        <v>-6220</v>
+      </c>
       <c r="S15" s="147"/>
       <c r="T15" s="174"/>
       <c r="U15" s="171">
         <f t="shared" si="0"/>
-        <v>13200</v>
+        <v>6980</v>
       </c>
       <c r="V15" s="149">
         <f t="shared" si="1"/>
-        <v>5.9999999999999991E-2</v>
+        <v>3.1727272727272722E-2</v>
       </c>
       <c r="X15" s="134"/>
       <c r="Y15" s="193">
         <f>Y8-Y10</f>
-        <v>8133.1633920000004</v>
+        <v>-76.791858000000005</v>
       </c>
       <c r="AB15" s="133">
         <v>116185</v>
       </c>
       <c r="AD15" s="133">
         <f>AB15+Y15</f>
-        <v>124318.163392</v>
+        <v>116108.208142</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -6753,16 +6754,18 @@
       <c r="Q16" s="147">
         <v>-27500</v>
       </c>
-      <c r="R16" s="147"/>
+      <c r="R16" s="147">
+        <v>5959</v>
+      </c>
       <c r="S16" s="147"/>
       <c r="T16" s="174"/>
       <c r="U16" s="171">
         <f t="shared" si="0"/>
-        <v>-31867</v>
+        <v>-25908</v>
       </c>
       <c r="V16" s="149">
         <f t="shared" si="1"/>
-        <v>-0.31867000000000001</v>
+        <v>-0.25907999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -6958,16 +6961,18 @@
       <c r="Q19" s="147">
         <v>13508</v>
       </c>
-      <c r="R19" s="147"/>
+      <c r="R19" s="147">
+        <v>-73400</v>
+      </c>
       <c r="S19" s="147"/>
       <c r="T19" s="174"/>
       <c r="U19" s="171">
         <f t="shared" si="0"/>
-        <v>-126998</v>
+        <v>-200398</v>
       </c>
       <c r="V19" s="149">
         <f t="shared" si="1"/>
-        <v>-0.84665333333333326</v>
+        <v>-1.3359866666666667</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -7020,16 +7025,18 @@
       <c r="Q20" s="147">
         <v>-29599</v>
       </c>
-      <c r="R20" s="147"/>
+      <c r="R20" s="147">
+        <v>-52025</v>
+      </c>
       <c r="S20" s="147"/>
       <c r="T20" s="174"/>
       <c r="U20" s="171">
         <f t="shared" si="0"/>
-        <v>-22294</v>
+        <v>-74319</v>
       </c>
       <c r="V20" s="149">
         <f t="shared" si="1"/>
-        <v>-0.20267272727272725</v>
+        <v>-0.67562727272727263</v>
       </c>
       <c r="Z20" s="133">
         <v>49000</v>
@@ -7085,16 +7092,18 @@
       <c r="Q21" s="147">
         <v>-23681</v>
       </c>
-      <c r="R21" s="147"/>
+      <c r="R21" s="147">
+        <v>580</v>
+      </c>
       <c r="S21" s="147"/>
       <c r="T21" s="174"/>
       <c r="U21" s="171">
         <f t="shared" si="0"/>
-        <v>-20083</v>
+        <v>-19503</v>
       </c>
       <c r="V21" s="149">
         <f t="shared" si="1"/>
-        <v>-0.80332000000000003</v>
+        <v>-0.78012000000000004</v>
       </c>
       <c r="Z21" s="133">
         <v>30400</v>
@@ -7281,16 +7290,18 @@
       <c r="Q24" s="147">
         <v>-5250</v>
       </c>
-      <c r="R24" s="147"/>
+      <c r="R24" s="147">
+        <v>-32214</v>
+      </c>
       <c r="S24" s="147"/>
       <c r="T24" s="174"/>
       <c r="U24" s="171">
         <f t="shared" si="0"/>
-        <v>20679</v>
+        <v>-11535</v>
       </c>
       <c r="V24" s="149">
         <f t="shared" si="1"/>
-        <v>0.18799090909090907</v>
+        <v>-0.10486363636363635</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
@@ -7343,16 +7354,18 @@
       <c r="Q25" s="147">
         <v>-470000</v>
       </c>
-      <c r="R25" s="147"/>
+      <c r="R25" s="147">
+        <v>48600</v>
+      </c>
       <c r="S25" s="147"/>
       <c r="T25" s="174"/>
       <c r="U25" s="171">
         <f t="shared" si="0"/>
-        <v>-1497123</v>
+        <v>-1448523</v>
       </c>
       <c r="V25" s="149">
         <f t="shared" si="1"/>
-        <v>-6.5092304347826087</v>
+        <v>-6.2979260869565215</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
@@ -7403,16 +7416,18 @@
       <c r="Q26" s="147">
         <v>-1700</v>
       </c>
-      <c r="R26" s="147"/>
+      <c r="R26" s="147">
+        <v>1700</v>
+      </c>
       <c r="S26" s="147"/>
       <c r="T26" s="174"/>
       <c r="U26" s="171">
         <f t="shared" si="0"/>
-        <v>4094</v>
+        <v>5794</v>
       </c>
       <c r="V26" s="149">
         <f t="shared" si="1"/>
-        <v>0.20469999999999999</v>
+        <v>0.28970000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
@@ -7657,16 +7672,18 @@
       <c r="Q30" s="147">
         <v>18328</v>
       </c>
-      <c r="R30" s="147"/>
+      <c r="R30" s="147">
+        <v>-100709</v>
+      </c>
       <c r="S30" s="147"/>
       <c r="T30" s="174"/>
       <c r="U30" s="171">
         <f t="shared" si="0"/>
-        <v>165843</v>
+        <v>65134</v>
       </c>
       <c r="V30" s="149">
         <f t="shared" si="1"/>
-        <v>0.33168599999999998</v>
+        <v>0.13026799999999999</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
@@ -7719,16 +7736,18 @@
       <c r="Q31" s="147">
         <v>15560</v>
       </c>
-      <c r="R31" s="147"/>
+      <c r="R31" s="147">
+        <v>-55712</v>
+      </c>
       <c r="S31" s="147"/>
       <c r="T31" s="174"/>
       <c r="U31" s="171">
         <f t="shared" ref="U31:U56" si="2">SUM(H31:T31)</f>
-        <v>-130384</v>
+        <v>-186096</v>
       </c>
       <c r="V31" s="149">
         <f t="shared" ref="V31:V56" si="3">IFERROR(U31/F31*100,0)/10000000</f>
-        <v>-2.6076800000000002</v>
+        <v>-3.7219199999999999</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
@@ -7781,16 +7800,18 @@
       <c r="Q32" s="147">
         <v>44376</v>
       </c>
-      <c r="R32" s="147"/>
+      <c r="R32" s="147">
+        <v>-24900</v>
+      </c>
       <c r="S32" s="147"/>
       <c r="T32" s="174"/>
       <c r="U32" s="171">
         <f t="shared" si="2"/>
-        <v>140189</v>
+        <v>115289</v>
       </c>
       <c r="V32" s="149">
         <f t="shared" si="3"/>
-        <v>3.5047250000000001</v>
+        <v>2.882225</v>
       </c>
       <c r="Y32" s="134"/>
     </row>
@@ -7859,7 +7880,7 @@
       </c>
       <c r="X33" s="5"/>
       <c r="Y33" s="134">
-        <v>19176</v>
+        <v>-97634</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
@@ -7978,23 +7999,25 @@
       <c r="Q35" s="147">
         <v>9822</v>
       </c>
-      <c r="R35" s="147"/>
+      <c r="R35" s="147">
+        <v>-14983</v>
+      </c>
       <c r="S35" s="147"/>
       <c r="T35" s="174"/>
       <c r="U35" s="171">
         <f t="shared" si="2"/>
-        <v>-116580</v>
+        <v>-131563</v>
       </c>
       <c r="V35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.29144999999999999</v>
+        <v>-0.32890750000000002</v>
       </c>
       <c r="X35" s="134">
-        <v>346085</v>
+        <v>1164469</v>
       </c>
       <c r="Y35" s="134">
         <f>(X36+X35)/10000000*13780</f>
-        <v>985.0550320000001</v>
+        <v>3074.7369120000003</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
@@ -8047,19 +8070,21 @@
       <c r="Q36" s="147">
         <v>-120800</v>
       </c>
-      <c r="R36" s="147"/>
+      <c r="R36" s="147">
+        <v>17600</v>
+      </c>
       <c r="S36" s="147"/>
       <c r="T36" s="174"/>
       <c r="U36" s="171">
         <f t="shared" si="2"/>
-        <v>-208879</v>
+        <v>-191279</v>
       </c>
       <c r="V36" s="149">
         <f t="shared" si="3"/>
-        <v>-2.0887899999999999</v>
+        <v>-1.91279</v>
       </c>
       <c r="X36" s="134">
-        <v>368759</v>
+        <v>1066835</v>
       </c>
       <c r="Y36" s="134"/>
     </row>
@@ -8127,7 +8152,7 @@
       <c r="X37" s="134"/>
       <c r="Y37" s="134">
         <f>+Y33-Y35</f>
-        <v>18190.944968</v>
+        <v>-100708.73691199999</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
@@ -8180,16 +8205,18 @@
       <c r="Q38" s="147">
         <v>8133</v>
       </c>
-      <c r="R38" s="147"/>
+      <c r="R38" s="147">
+        <v>-5240</v>
+      </c>
       <c r="S38" s="147"/>
       <c r="T38" s="174"/>
       <c r="U38" s="171">
         <f t="shared" si="2"/>
-        <v>-7955</v>
+        <v>-13195</v>
       </c>
       <c r="V38" s="149">
         <f t="shared" si="3"/>
-        <v>-0.15909999999999999</v>
+        <v>-0.26390000000000002</v>
       </c>
       <c r="X38" s="134"/>
       <c r="Y38" s="134"/>
@@ -8244,7 +8271,9 @@
       <c r="Q39" s="147">
         <v>0</v>
       </c>
-      <c r="R39" s="147"/>
+      <c r="R39" s="147">
+        <v>0</v>
+      </c>
       <c r="S39" s="147"/>
       <c r="T39" s="174"/>
       <c r="U39" s="171">
@@ -8308,16 +8337,18 @@
       <c r="Q40" s="147">
         <v>58211</v>
       </c>
-      <c r="R40" s="147"/>
+      <c r="R40" s="147">
+        <v>-83825</v>
+      </c>
       <c r="S40" s="147"/>
       <c r="T40" s="174"/>
       <c r="U40" s="171">
         <f t="shared" si="2"/>
-        <v>55933</v>
+        <v>-27892</v>
       </c>
       <c r="V40" s="149">
         <f t="shared" si="3"/>
-        <v>0.18644333333333332</v>
+        <v>-9.2973333333333338E-2</v>
       </c>
       <c r="X40" s="134"/>
       <c r="Y40" s="134"/>
@@ -8435,16 +8466,18 @@
       <c r="Q42" s="147">
         <v>20519</v>
       </c>
-      <c r="R42" s="147"/>
+      <c r="R42" s="147">
+        <v>-15800</v>
+      </c>
       <c r="S42" s="147"/>
       <c r="T42" s="174"/>
       <c r="U42" s="171">
         <f t="shared" si="2"/>
-        <v>9422</v>
+        <v>-6378</v>
       </c>
       <c r="V42" s="149">
         <f t="shared" si="3"/>
-        <v>0.18844</v>
+        <v>-0.12756000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
@@ -8497,16 +8530,18 @@
       <c r="Q43" s="147">
         <v>-316146</v>
       </c>
-      <c r="R43" s="147"/>
+      <c r="R43" s="147">
+        <v>-13600</v>
+      </c>
       <c r="S43" s="147"/>
       <c r="T43" s="174"/>
       <c r="U43" s="171">
         <f t="shared" si="2"/>
-        <v>-449753</v>
+        <v>-463353</v>
       </c>
       <c r="V43" s="149">
         <f t="shared" si="3"/>
-        <v>-4.4975300000000002</v>
+        <v>-4.6335300000000004</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
@@ -8557,16 +8592,18 @@
       <c r="Q44" s="147">
         <v>11400</v>
       </c>
-      <c r="R44" s="147"/>
+      <c r="R44" s="147">
+        <v>-4699</v>
+      </c>
       <c r="S44" s="147"/>
       <c r="T44" s="174"/>
       <c r="U44" s="171">
         <f t="shared" si="2"/>
-        <v>11946</v>
+        <v>7247</v>
       </c>
       <c r="V44" s="149">
         <f t="shared" si="3"/>
-        <v>1.1946000000000001</v>
+        <v>0.72470000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
@@ -8619,16 +8656,18 @@
       <c r="Q45" s="147">
         <v>0</v>
       </c>
-      <c r="R45" s="147"/>
+      <c r="R45" s="147">
+        <v>-29500</v>
+      </c>
       <c r="S45" s="147"/>
       <c r="T45" s="174"/>
       <c r="U45" s="171">
         <f t="shared" si="2"/>
-        <v>-156125</v>
+        <v>-185625</v>
       </c>
       <c r="V45" s="149">
         <f t="shared" si="3"/>
-        <v>-0.39031250000000001</v>
+        <v>-0.46406249999999999</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
@@ -8681,7 +8720,9 @@
       <c r="Q46" s="147">
         <v>-3600</v>
       </c>
-      <c r="R46" s="147"/>
+      <c r="R46" s="147">
+        <v>0</v>
+      </c>
       <c r="S46" s="147"/>
       <c r="T46" s="174"/>
       <c r="U46" s="171">
@@ -8743,16 +8784,18 @@
       <c r="Q47" s="147">
         <v>416846</v>
       </c>
-      <c r="R47" s="147"/>
+      <c r="R47" s="147">
+        <v>-296157</v>
+      </c>
       <c r="S47" s="147"/>
       <c r="T47" s="174"/>
       <c r="U47" s="171">
         <f t="shared" si="2"/>
-        <v>672348</v>
+        <v>376191</v>
       </c>
       <c r="V47" s="149">
         <f t="shared" si="3"/>
-        <v>2.2411599999999998</v>
+        <v>1.25397</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
@@ -8803,16 +8846,18 @@
       <c r="Q48" s="151">
         <v>52400</v>
       </c>
-      <c r="R48" s="151"/>
+      <c r="R48" s="151">
+        <v>54600</v>
+      </c>
       <c r="S48" s="151"/>
       <c r="T48" s="174"/>
       <c r="U48" s="171">
         <f t="shared" si="2"/>
-        <v>-707936</v>
+        <v>-653336</v>
       </c>
       <c r="V48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.70793600000000012</v>
+        <v>-0.65333600000000003</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
@@ -8925,16 +8970,18 @@
       <c r="Q50" s="151">
         <v>19542</v>
       </c>
-      <c r="R50" s="151"/>
+      <c r="R50" s="151">
+        <v>-100</v>
+      </c>
       <c r="S50" s="151"/>
       <c r="T50" s="174"/>
       <c r="U50" s="171">
         <f t="shared" si="2"/>
-        <v>30670</v>
+        <v>30570</v>
       </c>
       <c r="V50" s="149">
         <f t="shared" si="3"/>
-        <v>0.61339999999999995</v>
+        <v>0.61140000000000005</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
@@ -8988,17 +9035,17 @@
         <v>-652202</v>
       </c>
       <c r="R51" s="151">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="S51" s="151"/>
       <c r="T51" s="174"/>
       <c r="U51" s="171">
         <f t="shared" si="2"/>
-        <v>-617713</v>
+        <v>-618213</v>
       </c>
       <c r="V51" s="149">
         <f t="shared" si="3"/>
-        <v>-0.95032769230769243</v>
+        <v>-0.95109692307692317</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
@@ -9177,7 +9224,9 @@
       <c r="Q54" s="151">
         <v>0</v>
       </c>
-      <c r="R54" s="151"/>
+      <c r="R54" s="151">
+        <v>0</v>
+      </c>
       <c r="S54" s="151"/>
       <c r="T54" s="174"/>
       <c r="U54" s="171">
@@ -9237,16 +9286,18 @@
       <c r="Q55" s="151">
         <v>18190</v>
       </c>
-      <c r="R55" s="151"/>
+      <c r="R55" s="151">
+        <v>-13500</v>
+      </c>
       <c r="S55" s="151"/>
       <c r="T55" s="174"/>
       <c r="U55" s="171">
         <f t="shared" si="2"/>
-        <v>22128</v>
+        <v>8628</v>
       </c>
       <c r="V55" s="149">
         <f t="shared" si="3"/>
-        <v>4.4256000000000004E-2</v>
+        <v>1.7256000000000001E-2</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9259,7 +9310,7 @@
       <c r="G56" s="16"/>
       <c r="H56" s="254">
         <f t="shared" ref="H56:S56" si="4">SUM(H4:H55)</f>
-        <v>-2118400</v>
+        <v>-2124400</v>
       </c>
       <c r="I56" s="254">
         <f t="shared" si="4"/>
@@ -9283,23 +9334,23 @@
       </c>
       <c r="N56" s="254">
         <f t="shared" si="4"/>
-        <v>-959041</v>
+        <v>-952541</v>
       </c>
       <c r="O56" s="254">
         <f t="shared" si="4"/>
-        <v>-558306</v>
+        <v>-529806</v>
       </c>
       <c r="P56" s="254">
         <f t="shared" si="4"/>
-        <v>-539685</v>
+        <v>-539238</v>
       </c>
       <c r="Q56" s="254">
         <f t="shared" si="4"/>
-        <v>-955350</v>
+        <v>-925850</v>
       </c>
       <c r="R56" s="254">
         <f t="shared" si="4"/>
-        <v>-481200</v>
+        <v>-1203159</v>
       </c>
       <c r="S56" s="254">
         <f t="shared" si="4"/>
@@ -9311,7 +9362,7 @@
       </c>
       <c r="U56" s="254">
         <f t="shared" si="2"/>
-        <v>-5376117</v>
+        <v>-6039129</v>
       </c>
       <c r="V56" s="255">
         <f t="shared" si="3"/>
@@ -9392,7 +9443,9 @@
       <c r="Q58" s="162">
         <v>-431925</v>
       </c>
-      <c r="R58" s="162"/>
+      <c r="R58" s="162">
+        <v>0</v>
+      </c>
       <c r="S58" s="162"/>
       <c r="T58" s="246"/>
       <c r="U58" s="247">
@@ -9453,7 +9506,9 @@
       <c r="Q59" s="162">
         <v>-47350</v>
       </c>
-      <c r="R59" s="162"/>
+      <c r="R59" s="162">
+        <v>0</v>
+      </c>
       <c r="S59" s="162"/>
       <c r="T59" s="174"/>
       <c r="U59" s="171">
@@ -9567,87 +9622,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 V56:V57 U55:V55 V60 U43:V43 U5:V10 U24:V25 H2:V3 A58:V59 A37:U37 V11:V21 U11:U22 U45:V53 U27:U36 V27:V35 A4:T36 U38:U41 A38:T39 G40:T40 A41:T56 A60:T60">
-    <cfRule type="expression" dxfId="450" priority="21">
+    <cfRule type="expression" dxfId="446" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V36">
-    <cfRule type="expression" dxfId="449" priority="20">
+    <cfRule type="expression" dxfId="445" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V39:V40">
-    <cfRule type="expression" dxfId="448" priority="19">
+    <cfRule type="expression" dxfId="444" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:V4">
-    <cfRule type="expression" dxfId="447" priority="18">
+    <cfRule type="expression" dxfId="443" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38">
-    <cfRule type="expression" dxfId="446" priority="17">
+    <cfRule type="expression" dxfId="442" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="445" priority="14">
+    <cfRule type="expression" dxfId="441" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U56">
-    <cfRule type="expression" dxfId="444" priority="13">
+    <cfRule type="expression" dxfId="440" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="443" priority="12">
+    <cfRule type="expression" dxfId="439" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U26:V26">
-    <cfRule type="expression" dxfId="442" priority="11">
+    <cfRule type="expression" dxfId="438" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U54:V54">
-    <cfRule type="expression" dxfId="441" priority="10">
+    <cfRule type="expression" dxfId="437" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U44:V44">
-    <cfRule type="expression" dxfId="440" priority="9">
+    <cfRule type="expression" dxfId="436" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U60">
-    <cfRule type="expression" dxfId="439" priority="8">
+    <cfRule type="expression" dxfId="435" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U42:V42">
-    <cfRule type="expression" dxfId="438" priority="6">
+    <cfRule type="expression" dxfId="434" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U23">
-    <cfRule type="expression" dxfId="437" priority="5">
+    <cfRule type="expression" dxfId="433" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V23">
-    <cfRule type="expression" dxfId="436" priority="4">
+    <cfRule type="expression" dxfId="432" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V37">
-    <cfRule type="expression" dxfId="435" priority="2">
+    <cfRule type="expression" dxfId="431" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="434" priority="1">
+    <cfRule type="expression" dxfId="430" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10105,7 +10160,9 @@
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A7" s="142"/>
+      <c r="A7" s="142" t="s">
+        <v>323</v>
+      </c>
       <c r="B7" s="141" t="s">
         <v>309</v>
       </c>
@@ -16114,112 +16171,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="433" priority="22">
+    <cfRule type="expression" dxfId="429" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="432" priority="21">
+    <cfRule type="expression" dxfId="428" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="431" priority="20">
+    <cfRule type="expression" dxfId="427" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="430" priority="19">
+    <cfRule type="expression" dxfId="426" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="429" priority="18">
+    <cfRule type="expression" dxfId="425" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="428" priority="17">
+    <cfRule type="expression" dxfId="424" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="427" priority="16">
+    <cfRule type="expression" dxfId="423" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="426" priority="15">
+    <cfRule type="expression" dxfId="422" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="425" priority="14">
+    <cfRule type="expression" dxfId="421" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="424" priority="13">
+    <cfRule type="expression" dxfId="420" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="423" priority="12">
+    <cfRule type="expression" dxfId="419" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="422" priority="11">
+    <cfRule type="expression" dxfId="418" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="421" priority="10">
+    <cfRule type="expression" dxfId="417" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="420" priority="9">
+    <cfRule type="expression" dxfId="416" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="419" priority="8">
+    <cfRule type="expression" dxfId="415" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="418" priority="7">
+    <cfRule type="expression" dxfId="414" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="417" priority="6">
+    <cfRule type="expression" dxfId="413" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="416" priority="5">
+    <cfRule type="expression" dxfId="412" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="415" priority="4">
+    <cfRule type="expression" dxfId="411" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="414" priority="3">
+    <cfRule type="expression" dxfId="410" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="413" priority="2">
+    <cfRule type="expression" dxfId="409" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="412" priority="1">
+    <cfRule type="expression" dxfId="408" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22519,82 +22576,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="411" priority="20">
+    <cfRule type="expression" dxfId="407" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="410" priority="19">
+    <cfRule type="expression" dxfId="406" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="409" priority="18">
+    <cfRule type="expression" dxfId="405" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="408" priority="16">
+    <cfRule type="expression" dxfId="404" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="407" priority="14">
+    <cfRule type="expression" dxfId="403" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="406" priority="13">
+    <cfRule type="expression" dxfId="402" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="405" priority="12">
+    <cfRule type="expression" dxfId="401" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="404" priority="11">
+    <cfRule type="expression" dxfId="400" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="403" priority="10">
+    <cfRule type="expression" dxfId="399" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="402" priority="9">
+    <cfRule type="expression" dxfId="398" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="401" priority="6">
+    <cfRule type="expression" dxfId="397" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="400" priority="5">
+    <cfRule type="expression" dxfId="396" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="399" priority="4">
+    <cfRule type="expression" dxfId="395" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="398" priority="3">
+    <cfRule type="expression" dxfId="394" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="397" priority="2">
+    <cfRule type="expression" dxfId="393" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="396" priority="1">
+    <cfRule type="expression" dxfId="392" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22719,19 +22776,19 @@
       </c>
       <c r="K4" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-40649</v>
+        <v>-40798</v>
       </c>
       <c r="L4" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.81298000000000004</v>
+        <v>-0.81596000000000002</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-67693</v>
+        <v>-67842</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-1.3538600000000001</v>
+        <v>-1.35684</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -22771,19 +22828,19 @@
       </c>
       <c r="K5" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>86453</v>
+        <v>168284</v>
       </c>
       <c r="L5" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.28817666666666669</v>
+        <v>0.56094666666666659</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-164518</v>
+        <v>-82687</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-0.54839333333333329</v>
+        <v>-0.27562333333333344</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -22839,7 +22896,9 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="142"/>
+      <c r="A7" s="142" t="s">
+        <v>323</v>
+      </c>
       <c r="B7" s="141" t="s">
         <v>309</v>
       </c>
@@ -22865,7 +22924,7 @@
       </c>
       <c r="I7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>0</v>
+        <v>-28990</v>
       </c>
       <c r="J7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -22873,19 +22932,19 @@
       </c>
       <c r="K7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0</v>
+        <v>105547</v>
       </c>
       <c r="L7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0</v>
+        <v>1.0554699999999999</v>
       </c>
       <c r="M7" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>76557</v>
       </c>
       <c r="N7" s="166">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.0554699999999999</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -22925,19 +22984,19 @@
       </c>
       <c r="K8" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>64359</v>
+        <v>34234</v>
       </c>
       <c r="L8" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.21453</v>
+        <v>0.11411333333333334</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-390738</v>
+        <v>-420863</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.30246</v>
+        <v>-1.4028766666666668</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -22977,19 +23036,19 @@
       </c>
       <c r="K9" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>113333</v>
+        <v>49903</v>
       </c>
       <c r="L9" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.7555533333333333</v>
+        <v>0.33268666666666663</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-180803</v>
+        <v>-244233</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.2053533333333337</v>
+        <v>-1.6282200000000004</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -23029,19 +23088,19 @@
       </c>
       <c r="K10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>40837</v>
+        <v>9337</v>
       </c>
       <c r="L10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.68061666666666665</v>
+        <v>0.15561666666666668</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-151412</v>
+        <v>-182912</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-2.5235333333333339</v>
+        <v>-3.0485333333333338</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -23133,19 +23192,19 @@
       </c>
       <c r="K12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>25306</v>
+        <v>25206</v>
       </c>
       <c r="L12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>4.2176666666666668E-2</v>
+        <v>4.2009999999999999E-2</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>433086</v>
+        <v>432986</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.72181000000000006</v>
+        <v>0.72164333333333341</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -23185,19 +23244,19 @@
       </c>
       <c r="K13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-10196</v>
+        <v>-7797</v>
       </c>
       <c r="L13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.10196</v>
+        <v>-7.7969999999999998E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>3220</v>
+        <v>5619</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>3.2200000000000006E-2</v>
+        <v>5.6190000000000004E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -23237,19 +23296,19 @@
       </c>
       <c r="K14" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>13902</v>
+        <v>3762</v>
       </c>
       <c r="L14" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>5.5607999999999998E-2</v>
+        <v>1.5048000000000001E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>58822</v>
+        <v>48682</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.23528799999999994</v>
+        <v>0.19472799999999996</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -23341,19 +23400,19 @@
       </c>
       <c r="K16" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-31867</v>
+        <v>-25908</v>
       </c>
       <c r="L16" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.31867000000000001</v>
+        <v>-0.25907999999999998</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>41540</v>
+        <v>47499</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.41539999999999999</v>
+        <v>0.47499000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -23393,19 +23452,19 @@
       </c>
       <c r="K17" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>13200</v>
+        <v>6980</v>
       </c>
       <c r="L17" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>5.9999999999999991E-2</v>
+        <v>3.1727272727272722E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-74708</v>
+        <v>-80928</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.33958181818181815</v>
+        <v>-0.36785454545454543</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -23549,19 +23608,19 @@
       </c>
       <c r="K20" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-22294</v>
+        <v>-74319</v>
       </c>
       <c r="L20" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.20267272727272725</v>
+        <v>-0.67562727272727263</v>
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>65388</v>
+        <v>13363</v>
       </c>
       <c r="N20" s="166">
         <f t="shared" si="0"/>
-        <v>0.59443636363636354</v>
+        <v>0.12148181818181814</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -23601,19 +23660,19 @@
       </c>
       <c r="K21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-20083</v>
+        <v>-19503</v>
       </c>
       <c r="L21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.80332000000000003</v>
+        <v>-0.78012000000000004</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-63629</v>
+        <v>-63049</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-2.5451600000000001</v>
+        <v>-2.52196</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -23705,19 +23764,19 @@
       </c>
       <c r="K23" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-126998</v>
+        <v>-200398</v>
       </c>
       <c r="L23" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.84665333333333326</v>
+        <v>-1.3359866666666667</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>-11985</v>
+        <v>-85385</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>-7.989999999999986E-2</v>
+        <v>-0.56923333333333326</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -23809,19 +23868,19 @@
       </c>
       <c r="K25" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>20679</v>
+        <v>-11535</v>
       </c>
       <c r="L25" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.18799090909090907</v>
+        <v>-0.10486363636363635</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>225383</v>
+        <v>193169</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>2.0489363636363631</v>
+        <v>1.7560818181818176</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -23861,19 +23920,19 @@
       </c>
       <c r="K26" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1497123</v>
+        <v>-1448523</v>
       </c>
       <c r="L26" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-6.5092304347826087</v>
+        <v>-6.2979260869565215</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-1143062</v>
+        <v>-1094462</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-4.9698347826086966</v>
+        <v>-4.7585304347826085</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -23911,19 +23970,19 @@
       </c>
       <c r="K27" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>4094</v>
+        <v>5794</v>
       </c>
       <c r="L27" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.20469999999999999</v>
+        <v>0.28970000000000001</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-16202</v>
+        <v>-14502</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.81009999999999993</v>
+        <v>-0.72509999999999986</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -24380,19 +24439,19 @@
       </c>
       <c r="K36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>165843</v>
+        <v>65134</v>
       </c>
       <c r="L36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.33168599999999998</v>
+        <v>0.13026799999999999</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>1193250</v>
+        <v>1092541</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>2.3864999999999998</v>
+        <v>2.185082</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -24432,19 +24491,19 @@
       </c>
       <c r="K37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-130384</v>
+        <v>-186096</v>
       </c>
       <c r="L37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-2.6076800000000002</v>
+        <v>-3.7219199999999999</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-209748</v>
+        <v>-265460</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-4.19496</v>
+        <v>-5.3091999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -24484,19 +24543,19 @@
       </c>
       <c r="K38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>140189</v>
+        <v>115289</v>
       </c>
       <c r="L38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>3.5047250000000001</v>
+        <v>2.882225</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>74664</v>
+        <v>49764</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>1.8666000000000003</v>
+        <v>1.2441000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -24640,19 +24699,19 @@
       </c>
       <c r="K41" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-116580</v>
+        <v>-131563</v>
       </c>
       <c r="L41" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.29144999999999999</v>
+        <v>-0.32890750000000002</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>594356</v>
+        <v>579373</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.4858900000000002</v>
+        <v>1.4484325</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -24692,19 +24751,19 @@
       </c>
       <c r="K42" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-208879</v>
+        <v>-191279</v>
       </c>
       <c r="L42" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-2.0887899999999999</v>
+        <v>-1.91279</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>-5247</v>
+        <v>12353</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>-5.2470000000000017E-2</v>
+        <v>0.12352999999999992</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -24794,19 +24853,19 @@
       </c>
       <c r="K44" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-7955</v>
+        <v>-13195</v>
       </c>
       <c r="L44" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.15909999999999999</v>
+        <v>-0.26390000000000002</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-74338</v>
+        <v>-79578</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4867599999999999</v>
+        <v>-1.5915599999999999</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -24846,19 +24905,19 @@
       </c>
       <c r="K45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>55933</v>
+        <v>-27892</v>
       </c>
       <c r="L45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.18644333333333332</v>
+        <v>-9.2973333333333338E-2</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-54859</v>
+        <v>-138684</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.18286333333333335</v>
+        <v>-0.46228000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -25052,19 +25111,19 @@
       </c>
       <c r="K49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>9422</v>
+        <v>-6378</v>
       </c>
       <c r="L49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.18844</v>
+        <v>-0.12756000000000001</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>43750</v>
+        <v>27950</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.5544</v>
+        <v>0.2384</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -25104,19 +25163,19 @@
       </c>
       <c r="K50" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-449753</v>
+        <v>-463353</v>
       </c>
       <c r="L50" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-4.4975300000000002</v>
+        <v>-4.6335300000000004</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>437621</v>
+        <v>424021</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>4.3762099999999995</v>
+        <v>4.2402099999999994</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -25154,19 +25213,19 @@
       </c>
       <c r="K51" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>11946</v>
+        <v>7247</v>
       </c>
       <c r="L51" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>1.1946000000000001</v>
+        <v>0.72470000000000001</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>8400</v>
+        <v>3701</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.84000000000000008</v>
+        <v>0.37009999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -25206,19 +25265,19 @@
       </c>
       <c r="K52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>672348</v>
+        <v>376191</v>
       </c>
       <c r="L52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>2.2411599999999998</v>
+        <v>1.25397</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>663615</v>
+        <v>367458</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>2.2120499999999996</v>
+        <v>1.2248600000000001</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -25304,19 +25363,19 @@
       </c>
       <c r="K54" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-156125</v>
+        <v>-185625</v>
       </c>
       <c r="L54" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.39031250000000001</v>
+        <v>-0.46406249999999999</v>
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>319077</v>
+        <v>289577</v>
       </c>
       <c r="N54" s="166">
         <f t="shared" si="0"/>
-        <v>0.79769249999999992</v>
+        <v>0.72394249999999993</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -25406,19 +25465,19 @@
       </c>
       <c r="K56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-707936</v>
+        <v>-653336</v>
       </c>
       <c r="L56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.70793600000000012</v>
+        <v>-0.65333600000000003</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1743016</v>
+        <v>-1688416</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.7431160000000001</v>
+        <v>-1.6885159999999999</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -25504,19 +25563,19 @@
       </c>
       <c r="K58" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>30670</v>
+        <v>30570</v>
       </c>
       <c r="L58" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.61339999999999995</v>
+        <v>0.61140000000000005</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-3625</v>
+        <v>-3725</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-7.2500000000000009E-2</v>
+        <v>-7.44999999999999E-2</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -25556,19 +25615,19 @@
       </c>
       <c r="K59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-617713</v>
+        <v>-618213</v>
       </c>
       <c r="L59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.95032769230769243</v>
+        <v>-0.95109692307692317</v>
       </c>
       <c r="M59" s="71">
         <f t="shared" si="0"/>
-        <v>326231</v>
+        <v>325731</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" si="0"/>
-        <v>1.3452832692307692</v>
+        <v>1.3445140384615386</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -25812,19 +25871,19 @@
       </c>
       <c r="K64" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>22128</v>
+        <v>8628</v>
       </c>
       <c r="L64" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>4.4256000000000004E-2</v>
+        <v>1.7256000000000001E-2</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>511533</v>
+        <v>498033</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>1.023066</v>
+        <v>0.99606600000000001</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -25841,17 +25900,17 @@
       <c r="H65" s="90"/>
       <c r="I65" s="99">
         <f>SUM(I4:I62)</f>
-        <v>-5644903</v>
+        <v>-5673893</v>
       </c>
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-5433285</v>
+        <v>-6059497</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>6346752</v>
+        <v>5691550</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -26021,497 +26080,497 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
-    <cfRule type="expression" dxfId="395" priority="229">
+    <cfRule type="expression" dxfId="391" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="394" priority="228">
+    <cfRule type="expression" dxfId="390" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="393" priority="227">
+    <cfRule type="expression" dxfId="389" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="392" priority="226">
+    <cfRule type="expression" dxfId="388" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="391" priority="222">
+    <cfRule type="expression" dxfId="387" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="390" priority="220">
+    <cfRule type="expression" dxfId="386" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="389" priority="218">
+    <cfRule type="expression" dxfId="385" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="388" priority="212">
+    <cfRule type="expression" dxfId="384" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="387" priority="202">
+    <cfRule type="expression" dxfId="383" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="386" priority="207">
+    <cfRule type="expression" dxfId="382" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="385" priority="203">
+    <cfRule type="expression" dxfId="381" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="384" priority="188">
+    <cfRule type="expression" dxfId="380" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="383" priority="183">
+    <cfRule type="expression" dxfId="379" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="382" priority="189">
+    <cfRule type="expression" dxfId="378" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="381" priority="174">
+    <cfRule type="expression" dxfId="377" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="380" priority="172">
+    <cfRule type="expression" dxfId="376" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="379" priority="171">
+    <cfRule type="expression" dxfId="375" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="378" priority="166">
+    <cfRule type="expression" dxfId="374" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="377" priority="162">
+    <cfRule type="expression" dxfId="373" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="376" priority="163">
+    <cfRule type="expression" dxfId="372" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="375" priority="157">
+    <cfRule type="expression" dxfId="371" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="374" priority="143">
+    <cfRule type="expression" dxfId="370" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="373" priority="142">
+    <cfRule type="expression" dxfId="369" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="372" priority="132">
+    <cfRule type="expression" dxfId="368" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="371" priority="126">
+    <cfRule type="expression" dxfId="367" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="370" priority="125">
+    <cfRule type="expression" dxfId="366" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="369" priority="124">
+    <cfRule type="expression" dxfId="365" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="368" priority="123">
+    <cfRule type="expression" dxfId="364" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="367" priority="122">
+    <cfRule type="expression" dxfId="363" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="366" priority="121">
+    <cfRule type="expression" dxfId="362" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="365" priority="120">
+    <cfRule type="expression" dxfId="361" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="364" priority="109">
+    <cfRule type="expression" dxfId="360" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="363" priority="105">
+    <cfRule type="expression" dxfId="359" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="362" priority="104">
+    <cfRule type="expression" dxfId="358" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="361" priority="101">
+    <cfRule type="expression" dxfId="357" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="360" priority="97">
+    <cfRule type="expression" dxfId="356" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="359" priority="92">
+    <cfRule type="expression" dxfId="355" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="358" priority="91">
+    <cfRule type="expression" dxfId="354" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="357" priority="88">
+    <cfRule type="expression" dxfId="353" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="356" priority="89">
+    <cfRule type="expression" dxfId="352" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="355" priority="83">
+    <cfRule type="expression" dxfId="351" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="354" priority="82">
+    <cfRule type="expression" dxfId="350" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="353" priority="74">
+    <cfRule type="expression" dxfId="349" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="352" priority="73">
+    <cfRule type="expression" dxfId="348" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="351" priority="70">
+    <cfRule type="expression" dxfId="347" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="350" priority="71">
+    <cfRule type="expression" dxfId="346" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="349" priority="63">
+    <cfRule type="expression" dxfId="345" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="348" priority="62">
+    <cfRule type="expression" dxfId="344" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="347" priority="61">
+    <cfRule type="expression" dxfId="343" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="346" priority="60">
+    <cfRule type="expression" dxfId="342" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="345" priority="59">
+    <cfRule type="expression" dxfId="341" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="344" priority="58">
+    <cfRule type="expression" dxfId="340" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="343" priority="47">
+    <cfRule type="expression" dxfId="339" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="342" priority="57">
+    <cfRule type="expression" dxfId="338" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="341" priority="56">
+    <cfRule type="expression" dxfId="337" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="340" priority="55">
+    <cfRule type="expression" dxfId="336" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="339" priority="54">
+    <cfRule type="expression" dxfId="335" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="338" priority="53">
+    <cfRule type="expression" dxfId="334" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="337" priority="52">
+    <cfRule type="expression" dxfId="333" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="336" priority="51">
+    <cfRule type="expression" dxfId="332" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="335" priority="50">
+    <cfRule type="expression" dxfId="331" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="334" priority="48">
+    <cfRule type="expression" dxfId="330" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="333" priority="46">
+    <cfRule type="expression" dxfId="329" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="332" priority="45">
+    <cfRule type="expression" dxfId="328" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="331" priority="42">
+    <cfRule type="expression" dxfId="327" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="330" priority="41">
+    <cfRule type="expression" dxfId="326" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="329" priority="34">
+    <cfRule type="expression" dxfId="325" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 M64:N64">
-    <cfRule type="expression" dxfId="328" priority="33">
+    <cfRule type="expression" dxfId="324" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="327" priority="32">
+    <cfRule type="expression" dxfId="323" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="326" priority="31">
+    <cfRule type="expression" dxfId="322" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="325" priority="30">
+    <cfRule type="expression" dxfId="321" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="324" priority="29">
+    <cfRule type="expression" dxfId="320" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="323" priority="28">
+    <cfRule type="expression" dxfId="319" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="322" priority="27">
+    <cfRule type="expression" dxfId="318" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="321" priority="26">
+    <cfRule type="expression" dxfId="317" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="320" priority="25">
+    <cfRule type="expression" dxfId="316" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="319" priority="24">
+    <cfRule type="expression" dxfId="315" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="318" priority="20">
+    <cfRule type="expression" dxfId="314" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="317" priority="23">
+    <cfRule type="expression" dxfId="313" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="316" priority="22">
+    <cfRule type="expression" dxfId="312" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="315" priority="21">
+    <cfRule type="expression" dxfId="311" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="314" priority="19">
+    <cfRule type="expression" dxfId="310" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="313" priority="17">
+    <cfRule type="expression" dxfId="309" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="312" priority="16">
+    <cfRule type="expression" dxfId="308" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="311" priority="15">
+    <cfRule type="expression" dxfId="307" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="310" priority="14">
+    <cfRule type="expression" dxfId="306" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="309" priority="13">
+    <cfRule type="expression" dxfId="305" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="308" priority="12">
+    <cfRule type="expression" dxfId="304" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="307" priority="11">
+    <cfRule type="expression" dxfId="303" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="306" priority="10">
+    <cfRule type="expression" dxfId="302" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="305" priority="9">
+    <cfRule type="expression" dxfId="301" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="304" priority="8">
+    <cfRule type="expression" dxfId="300" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="303" priority="7">
+    <cfRule type="expression" dxfId="299" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="302" priority="6">
+    <cfRule type="expression" dxfId="298" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="301" priority="5">
+    <cfRule type="expression" dxfId="297" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="300" priority="4">
+    <cfRule type="expression" dxfId="296" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="299" priority="3">
+    <cfRule type="expression" dxfId="295" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:J57 M57:N57">
-    <cfRule type="expression" dxfId="298" priority="2">
+    <cfRule type="expression" dxfId="294" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:L70">
-    <cfRule type="expression" dxfId="297" priority="1">
+    <cfRule type="expression" dxfId="293" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32202,42 +32261,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="296" priority="13">
+    <cfRule type="expression" dxfId="292" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="295" priority="12">
+    <cfRule type="expression" dxfId="291" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="294" priority="11">
+    <cfRule type="expression" dxfId="290" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="293" priority="5">
+    <cfRule type="expression" dxfId="289" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="292" priority="4">
+    <cfRule type="expression" dxfId="288" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="291" priority="3">
+    <cfRule type="expression" dxfId="287" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="290" priority="2">
+    <cfRule type="expression" dxfId="286" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="289" priority="1">
+    <cfRule type="expression" dxfId="285" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38275,112 +38334,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="288" priority="28">
+    <cfRule type="expression" dxfId="284" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="287" priority="27">
+    <cfRule type="expression" dxfId="283" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="286" priority="26">
+    <cfRule type="expression" dxfId="282" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="285" priority="25">
+    <cfRule type="expression" dxfId="281" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="284" priority="23">
+    <cfRule type="expression" dxfId="280" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="283" priority="22">
+    <cfRule type="expression" dxfId="279" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="282" priority="20">
+    <cfRule type="expression" dxfId="278" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="281" priority="19">
+    <cfRule type="expression" dxfId="277" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="280" priority="15">
+    <cfRule type="expression" dxfId="276" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="279" priority="14">
+    <cfRule type="expression" dxfId="275" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="278" priority="13">
+    <cfRule type="expression" dxfId="274" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="277" priority="12">
+    <cfRule type="expression" dxfId="273" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="276" priority="11">
+    <cfRule type="expression" dxfId="272" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="275" priority="10">
+    <cfRule type="expression" dxfId="271" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="274" priority="9">
+    <cfRule type="expression" dxfId="270" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="273" priority="8">
+    <cfRule type="expression" dxfId="269" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="272" priority="7">
+    <cfRule type="expression" dxfId="268" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="271" priority="6">
+    <cfRule type="expression" dxfId="267" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="270" priority="1">
+    <cfRule type="expression" dxfId="266" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="269" priority="5">
+    <cfRule type="expression" dxfId="265" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="268" priority="4">
+    <cfRule type="expression" dxfId="264" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="267" priority="2">
+    <cfRule type="expression" dxfId="263" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44295,107 +44354,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="266" priority="24">
+    <cfRule type="expression" dxfId="262" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="265" priority="23">
+    <cfRule type="expression" dxfId="261" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="264" priority="22">
+    <cfRule type="expression" dxfId="260" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="263" priority="21">
+    <cfRule type="expression" dxfId="259" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="262" priority="20">
+    <cfRule type="expression" dxfId="258" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="261" priority="19">
+    <cfRule type="expression" dxfId="257" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="260" priority="18">
+    <cfRule type="expression" dxfId="256" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="259" priority="15">
+    <cfRule type="expression" dxfId="255" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="258" priority="14">
+    <cfRule type="expression" dxfId="254" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="257" priority="13">
+    <cfRule type="expression" dxfId="253" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="256" priority="12">
+    <cfRule type="expression" dxfId="252" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="255" priority="1">
+    <cfRule type="expression" dxfId="251" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="254" priority="10">
+    <cfRule type="expression" dxfId="250" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="253" priority="9">
+    <cfRule type="expression" dxfId="249" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="252" priority="8">
+    <cfRule type="expression" dxfId="248" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="247" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="250" priority="6">
+    <cfRule type="expression" dxfId="246" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="249" priority="5">
+    <cfRule type="expression" dxfId="245" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="248" priority="4">
+    <cfRule type="expression" dxfId="244" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="247" priority="3">
+    <cfRule type="expression" dxfId="243" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="246" priority="2">
+    <cfRule type="expression" dxfId="242" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44747,11 +44806,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-67693</v>
+        <v>-67842</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.3538600000000001</v>
+        <v>-1.35684</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -44768,11 +44827,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-116029</v>
+        <v>-116178</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-2.3205800000000001</v>
+        <v>-2.3235600000000001</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44829,11 +44888,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-164518</v>
+        <v>-82687</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.54839333333333329</v>
+        <v>-0.27562333333333344</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -44850,11 +44909,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>1169756</v>
+        <v>1251587</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.899186666666667</v>
+        <v>4.1719566666666665</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45026,11 +45085,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-390738</v>
+        <v>-420863</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.30246</v>
+        <v>-1.4028766666666668</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -45046,11 +45105,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-749647</v>
+        <v>-779772</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-3.9431400000000001</v>
+        <v>-4.0435566666666674</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45107,11 +45166,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-180803</v>
+        <v>-244233</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.2053533333333337</v>
+        <v>-1.6282200000000004</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -45127,11 +45186,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-355765</v>
+        <v>-419195</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.3717666666666668</v>
+        <v>-2.7946333333333335</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45188,11 +45247,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-151412</v>
+        <v>-182912</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-2.5235333333333339</v>
+        <v>-3.0485333333333338</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -45208,11 +45267,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-151412</v>
+        <v>-182912</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-2.5235333333333339</v>
+        <v>-3.0485333333333338</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45678,11 +45737,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>433086</v>
+        <v>432986</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.72181000000000006</v>
+        <v>0.72164333333333341</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -45698,11 +45757,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>237752</v>
+        <v>237652</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.6958099999999998</v>
+        <v>-2.6959766666666667</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45759,11 +45818,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3220</v>
+        <v>5619</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3.2200000000000006E-2</v>
+        <v>5.6190000000000004E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -45779,11 +45838,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>6899</v>
+        <v>9298</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>6.899000000000001E-2</v>
+        <v>9.2980000000000007E-2</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45930,11 +45989,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>58822</v>
+        <v>48682</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.23528799999999994</v>
+        <v>0.19472799999999996</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -45950,11 +46009,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-208594</v>
+        <v>-218734</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4388719999999999</v>
+        <v>-2.4794320000000001</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46011,11 +46070,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-74708</v>
+        <v>-80928</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.33958181818181815</v>
+        <v>-0.36785454545454543</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -46031,11 +46090,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-163608</v>
+        <v>-169828</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.2285818181818182</v>
+        <v>-1.2568545454545454</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46173,11 +46232,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>41540</v>
+        <v>47499</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.41539999999999999</v>
+        <v>0.47499000000000002</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -46193,11 +46252,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1756885</v>
+        <v>1762844</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.568849999999998</v>
+        <v>17.628439999999998</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46658,11 +46717,11 @@
       <c r="O30" s="215"/>
       <c r="P30" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>65388</v>
+        <v>13363</v>
       </c>
       <c r="Q30" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.59443636363636354</v>
+        <v>0.12148181818181814</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="88">
@@ -46679,11 +46738,11 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="154">
         <f t="shared" si="0"/>
-        <v>65106</v>
+        <v>13081</v>
       </c>
       <c r="Z30" s="168">
         <f t="shared" si="1"/>
-        <v>0.59187272727272722</v>
+        <v>0.11891818181818181</v>
       </c>
     </row>
     <row r="31" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46829,11 +46888,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-11985</v>
+        <v>-85385</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-7.989999999999986E-2</v>
+        <v>-0.56923333333333326</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -46850,11 +46909,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-517054</v>
+        <v>-590454</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-3.4470266666666673</v>
+        <v>-3.9363600000000005</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46992,11 +47051,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>225383</v>
+        <v>193169</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.0489363636363631</v>
+        <v>1.7560818181818176</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -47012,11 +47071,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-93557</v>
+        <v>-125771</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-0.85051818181818195</v>
+        <v>-1.1433727272727274</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -47161,11 +47220,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1143062</v>
+        <v>-1094462</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4.9698347826086966</v>
+        <v>-4.7585304347826085</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -47181,11 +47240,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>3018041</v>
+        <v>3066641</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>13.121917391304347</v>
+        <v>13.333221739130435</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47240,11 +47299,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-16202</v>
+        <v>-14502</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.81009999999999993</v>
+        <v>-0.72509999999999986</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -47260,11 +47319,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-16202</v>
+        <v>-14502</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.81009999999999993</v>
+        <v>-0.72509999999999986</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47999,11 +48058,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1193250</v>
+        <v>1092541</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.3864999999999998</v>
+        <v>2.185082</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -48020,11 +48079,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>1145512</v>
+        <v>1044803</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>2.2910239999999997</v>
+        <v>2.0896059999999999</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -48082,11 +48141,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-209748</v>
+        <v>-265460</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4.19496</v>
+        <v>-5.3091999999999997</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -48102,11 +48161,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-92853</v>
+        <v>-148565</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-1.8570600000000002</v>
+        <v>-2.9712999999999998</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -48251,11 +48310,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>74664</v>
+        <v>49764</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.8666000000000003</v>
+        <v>1.2441000000000002</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -48271,11 +48330,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>62836</v>
+        <v>37936</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>1.5709000000000002</v>
+        <v>0.94840000000000013</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -48506,11 +48565,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>594356</v>
+        <v>579373</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.4858900000000002</v>
+        <v>1.4484325</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -48526,11 +48585,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>194057</v>
+        <v>179074</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.48514250000000003</v>
+        <v>0.44768499999999989</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48587,11 +48646,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-5247</v>
+        <v>12353</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-5.2470000000000017E-2</v>
+        <v>0.12352999999999992</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -48607,11 +48666,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>740546</v>
+        <v>758146</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>7.4054600000000015</v>
+        <v>7.5814600000000008</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48749,11 +48808,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-74338</v>
+        <v>-79578</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4867599999999999</v>
+        <v>-1.5915599999999999</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -48770,11 +48829,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-320116</v>
+        <v>-325356</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.4023199999999996</v>
+        <v>-6.5071200000000005</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -48832,11 +48891,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-54859</v>
+        <v>-138684</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.18286333333333335</v>
+        <v>-0.46228000000000002</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -48852,11 +48911,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4753834</v>
+        <v>-4837659</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-15.846113333333337</v>
+        <v>-16.125530000000005</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -49086,11 +49145,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>43750</v>
+        <v>27950</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.5544</v>
+        <v>0.2384</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -49107,11 +49166,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>80473</v>
+        <v>64673</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.88323333333333331</v>
+        <v>0.56723333333333326</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -49175,11 +49234,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>437621</v>
+        <v>424021</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>4.3762099999999995</v>
+        <v>4.2402099999999994</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -49195,11 +49254,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>3987690</v>
+        <v>3974090</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>39.876899999999999</v>
+        <v>39.740899999999996</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -49261,11 +49320,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>8400</v>
+        <v>3701</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.84000000000000008</v>
+        <v>0.37009999999999998</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -49281,11 +49340,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>8400</v>
+        <v>3701</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.84000000000000008</v>
+        <v>0.37009999999999998</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49342,11 +49401,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>663615</v>
+        <v>367458</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.2120499999999996</v>
+        <v>1.2248600000000001</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -49362,11 +49421,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>1336464</v>
+        <v>1040307</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>4.4548799999999993</v>
+        <v>3.4676899999999997</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -49430,11 +49489,11 @@
       <c r="O63" s="215"/>
       <c r="P63" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>319077</v>
+        <v>289577</v>
       </c>
       <c r="Q63" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.79769249999999992</v>
+        <v>0.72394249999999993</v>
       </c>
       <c r="R63" s="159"/>
       <c r="S63" s="88">
@@ -49450,11 +49509,11 @@
       <c r="W63" s="72"/>
       <c r="Y63" s="154">
         <f t="shared" si="22"/>
-        <v>994077</v>
+        <v>964577</v>
       </c>
       <c r="Z63" s="168">
         <f t="shared" si="23"/>
-        <v>2.4851925000000001</v>
+        <v>2.4114424999999997</v>
       </c>
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49755,11 +49814,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1743016</v>
+        <v>-1688416</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.7431160000000001</v>
+        <v>-1.6885159999999999</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -49775,11 +49834,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1743016</v>
+        <v>-1688416</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.7431160000000001</v>
+        <v>-1.6885159999999999</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49893,11 +49952,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3625</v>
+        <v>-3725</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-7.2500000000000009E-2</v>
+        <v>-7.44999999999999E-2</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -49913,11 +49972,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-50279</v>
+        <v>-50379</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-1.0055800000000001</v>
+        <v>-1.0075799999999999</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -49974,11 +50033,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>326231</v>
+        <v>325731</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.3452832692307692</v>
+        <v>1.3445140384615386</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="153">
@@ -49994,11 +50053,11 @@
       <c r="W70" s="150"/>
       <c r="Y70" s="154">
         <f t="shared" si="22"/>
-        <v>-81721</v>
+        <v>-82221</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="23"/>
-        <v>0.32540326923076912</v>
+        <v>0.32463403846153849</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
@@ -50456,11 +50515,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>511533</v>
+        <v>498033</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.023066</v>
+        <v>0.99606600000000001</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -50476,11 +50535,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>511533</v>
+        <v>498033</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>1.023066</v>
+        <v>0.99606600000000001</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -50513,7 +50572,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>6471703</v>
+        <v>5739364</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -50524,7 +50583,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>26432336</v>
+        <v>25686497</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -50979,1212 +51038,1212 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 G77:W78">
-    <cfRule type="expression" dxfId="245" priority="448">
+    <cfRule type="expression" dxfId="241" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="244" priority="447">
+    <cfRule type="expression" dxfId="240" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="243" priority="444">
+    <cfRule type="expression" dxfId="239" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="242" priority="441">
+    <cfRule type="expression" dxfId="238" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="241" priority="442">
+    <cfRule type="expression" dxfId="237" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="240" priority="432">
+    <cfRule type="expression" dxfId="236" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="239" priority="433">
+    <cfRule type="expression" dxfId="235" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="238" priority="422">
+    <cfRule type="expression" dxfId="234" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="237" priority="420">
+    <cfRule type="expression" dxfId="233" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="236" priority="418">
+    <cfRule type="expression" dxfId="232" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="235" priority="409">
+    <cfRule type="expression" dxfId="231" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="234" priority="408">
+    <cfRule type="expression" dxfId="230" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="233" priority="380">
+    <cfRule type="expression" dxfId="229" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="232" priority="406">
+    <cfRule type="expression" dxfId="228" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="231" priority="405">
+    <cfRule type="expression" dxfId="227" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="230" priority="403">
+    <cfRule type="expression" dxfId="226" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="229" priority="402">
+    <cfRule type="expression" dxfId="225" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="228" priority="400">
+    <cfRule type="expression" dxfId="224" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="227" priority="387">
+    <cfRule type="expression" dxfId="223" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="226" priority="331">
+    <cfRule type="expression" dxfId="222" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="225" priority="378">
+    <cfRule type="expression" dxfId="221" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="224" priority="330">
+    <cfRule type="expression" dxfId="220" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="223" priority="383">
+    <cfRule type="expression" dxfId="219" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="222" priority="349">
+    <cfRule type="expression" dxfId="218" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="221" priority="347">
+    <cfRule type="expression" dxfId="217" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="220" priority="355">
+    <cfRule type="expression" dxfId="216" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="219" priority="354">
+    <cfRule type="expression" dxfId="215" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="218" priority="339">
+    <cfRule type="expression" dxfId="214" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="217" priority="338">
+    <cfRule type="expression" dxfId="213" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="216" priority="369">
+    <cfRule type="expression" dxfId="212" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="215" priority="329">
+    <cfRule type="expression" dxfId="211" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="214" priority="340">
+    <cfRule type="expression" dxfId="210" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="213" priority="350">
+    <cfRule type="expression" dxfId="209" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="212" priority="348">
+    <cfRule type="expression" dxfId="208" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="211" priority="341">
+    <cfRule type="expression" dxfId="207" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="210" priority="328">
+    <cfRule type="expression" dxfId="206" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="209" priority="286">
+    <cfRule type="expression" dxfId="205" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="208" priority="285">
+    <cfRule type="expression" dxfId="204" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="207" priority="283">
+    <cfRule type="expression" dxfId="203" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="206" priority="275">
+    <cfRule type="expression" dxfId="202" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="205" priority="274">
+    <cfRule type="expression" dxfId="201" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="204" priority="288">
+    <cfRule type="expression" dxfId="200" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="203" priority="287">
+    <cfRule type="expression" dxfId="199" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="202" priority="284">
+    <cfRule type="expression" dxfId="198" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="201" priority="282">
+    <cfRule type="expression" dxfId="197" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="200" priority="273">
+    <cfRule type="expression" dxfId="196" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="199" priority="267">
+    <cfRule type="expression" dxfId="195" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="198" priority="272">
+    <cfRule type="expression" dxfId="194" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="197" priority="271">
+    <cfRule type="expression" dxfId="193" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="196" priority="268">
+    <cfRule type="expression" dxfId="192" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="195" priority="270">
+    <cfRule type="expression" dxfId="191" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="194" priority="269">
+    <cfRule type="expression" dxfId="190" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="193" priority="260">
+    <cfRule type="expression" dxfId="189" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="192" priority="259">
+    <cfRule type="expression" dxfId="188" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="191" priority="256">
+    <cfRule type="expression" dxfId="187" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="190" priority="255">
+    <cfRule type="expression" dxfId="186" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="189" priority="253">
+    <cfRule type="expression" dxfId="185" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="188" priority="258">
+    <cfRule type="expression" dxfId="184" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="187" priority="257">
+    <cfRule type="expression" dxfId="183" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="186" priority="254">
+    <cfRule type="expression" dxfId="182" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="185" priority="246">
+    <cfRule type="expression" dxfId="181" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="184" priority="245">
+    <cfRule type="expression" dxfId="180" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="183" priority="244">
+    <cfRule type="expression" dxfId="179" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="182" priority="239">
+    <cfRule type="expression" dxfId="178" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="181" priority="238">
+    <cfRule type="expression" dxfId="177" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="180" priority="242">
+    <cfRule type="expression" dxfId="176" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="179" priority="241">
+    <cfRule type="expression" dxfId="175" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="178" priority="240">
+    <cfRule type="expression" dxfId="174" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="177" priority="243">
+    <cfRule type="expression" dxfId="173" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="176" priority="231">
+    <cfRule type="expression" dxfId="172" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="175" priority="227">
+    <cfRule type="expression" dxfId="171" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="174" priority="226">
+    <cfRule type="expression" dxfId="170" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="173" priority="220">
+    <cfRule type="expression" dxfId="169" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="172" priority="219">
+    <cfRule type="expression" dxfId="168" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="171" priority="223">
+    <cfRule type="expression" dxfId="167" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="170" priority="222">
+    <cfRule type="expression" dxfId="166" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="169" priority="221">
+    <cfRule type="expression" dxfId="165" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="168" priority="224">
+    <cfRule type="expression" dxfId="164" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="167" priority="208">
+    <cfRule type="expression" dxfId="163" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="166" priority="207">
+    <cfRule type="expression" dxfId="162" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="165" priority="206">
+    <cfRule type="expression" dxfId="161" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="164" priority="200">
+    <cfRule type="expression" dxfId="160" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="163" priority="199">
+    <cfRule type="expression" dxfId="159" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="162" priority="193">
+    <cfRule type="expression" dxfId="158" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="161" priority="198">
+    <cfRule type="expression" dxfId="157" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="160" priority="197">
+    <cfRule type="expression" dxfId="156" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="159" priority="194">
+    <cfRule type="expression" dxfId="155" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="158" priority="196">
+    <cfRule type="expression" dxfId="154" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="157" priority="195">
+    <cfRule type="expression" dxfId="153" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="156" priority="191">
+    <cfRule type="expression" dxfId="152" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="155" priority="190">
+    <cfRule type="expression" dxfId="151" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="154" priority="177">
+    <cfRule type="expression" dxfId="150" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="153" priority="186">
+    <cfRule type="expression" dxfId="149" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="152" priority="185">
+    <cfRule type="expression" dxfId="148" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="151" priority="175">
+    <cfRule type="expression" dxfId="147" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="150" priority="174">
+    <cfRule type="expression" dxfId="146" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="149" priority="173">
+    <cfRule type="expression" dxfId="145" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="148" priority="168">
+    <cfRule type="expression" dxfId="144" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="147" priority="165">
+    <cfRule type="expression" dxfId="143" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="146" priority="164">
+    <cfRule type="expression" dxfId="142" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="145" priority="163">
+    <cfRule type="expression" dxfId="141" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="144" priority="162">
+    <cfRule type="expression" dxfId="140" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="143" priority="161">
+    <cfRule type="expression" dxfId="139" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="142" priority="160">
+    <cfRule type="expression" dxfId="138" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="141" priority="147">
+    <cfRule type="expression" dxfId="137" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="140" priority="157">
+    <cfRule type="expression" dxfId="136" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="139" priority="156">
+    <cfRule type="expression" dxfId="135" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="138" priority="155">
+    <cfRule type="expression" dxfId="134" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="137" priority="154">
+    <cfRule type="expression" dxfId="133" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="136" priority="153">
+    <cfRule type="expression" dxfId="132" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="135" priority="152">
+    <cfRule type="expression" dxfId="131" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="134" priority="151">
+    <cfRule type="expression" dxfId="130" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="133" priority="142">
+    <cfRule type="expression" dxfId="129" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="132" priority="148">
+    <cfRule type="expression" dxfId="128" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="131" priority="146">
+    <cfRule type="expression" dxfId="127" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="130" priority="145">
+    <cfRule type="expression" dxfId="126" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="129" priority="144">
+    <cfRule type="expression" dxfId="125" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="128" priority="143">
+    <cfRule type="expression" dxfId="124" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="127" priority="141">
+    <cfRule type="expression" dxfId="123" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="126" priority="138">
+    <cfRule type="expression" dxfId="122" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="125" priority="137">
+    <cfRule type="expression" dxfId="121" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="124" priority="136">
+    <cfRule type="expression" dxfId="120" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="123" priority="135">
+    <cfRule type="expression" dxfId="119" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="122" priority="134">
+    <cfRule type="expression" dxfId="118" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="121" priority="133">
+    <cfRule type="expression" dxfId="117" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="120" priority="130">
+    <cfRule type="expression" dxfId="116" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="119" priority="132">
+    <cfRule type="expression" dxfId="115" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="118" priority="131">
+    <cfRule type="expression" dxfId="114" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="117" priority="129">
+    <cfRule type="expression" dxfId="113" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="116" priority="128">
+    <cfRule type="expression" dxfId="112" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="115" priority="127">
+    <cfRule type="expression" dxfId="111" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="114" priority="126">
+    <cfRule type="expression" dxfId="110" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="113" priority="124">
+    <cfRule type="expression" dxfId="109" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="112" priority="123">
+    <cfRule type="expression" dxfId="108" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="111" priority="122">
+    <cfRule type="expression" dxfId="107" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="110" priority="121">
+    <cfRule type="expression" dxfId="106" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="109" priority="120">
+    <cfRule type="expression" dxfId="105" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="108" priority="115">
+    <cfRule type="expression" dxfId="104" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="107" priority="114">
+    <cfRule type="expression" dxfId="103" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="106" priority="118">
+    <cfRule type="expression" dxfId="102" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="105" priority="117">
+    <cfRule type="expression" dxfId="101" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="104" priority="116">
+    <cfRule type="expression" dxfId="100" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="103" priority="119">
+    <cfRule type="expression" dxfId="99" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="102" priority="113">
+    <cfRule type="expression" dxfId="98" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="101" priority="111">
+    <cfRule type="expression" dxfId="97" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="100" priority="109">
+    <cfRule type="expression" dxfId="96" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="99" priority="108">
+    <cfRule type="expression" dxfId="95" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="98" priority="107">
+    <cfRule type="expression" dxfId="94" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="97" priority="106">
+    <cfRule type="expression" dxfId="93" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="96" priority="105">
+    <cfRule type="expression" dxfId="92" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="95" priority="104">
+    <cfRule type="expression" dxfId="91" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="94" priority="102">
+    <cfRule type="expression" dxfId="90" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="93" priority="92">
+    <cfRule type="expression" dxfId="89" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="92" priority="100">
+    <cfRule type="expression" dxfId="88" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="91" priority="99">
+    <cfRule type="expression" dxfId="87" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="90" priority="96">
+    <cfRule type="expression" dxfId="86" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="89" priority="95">
+    <cfRule type="expression" dxfId="85" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="88" priority="93">
+    <cfRule type="expression" dxfId="84" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="87" priority="98">
+    <cfRule type="expression" dxfId="83" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="86" priority="97">
+    <cfRule type="expression" dxfId="82" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="85" priority="94">
+    <cfRule type="expression" dxfId="81" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="84" priority="91">
+    <cfRule type="expression" dxfId="80" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="83" priority="90">
+    <cfRule type="expression" dxfId="79" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="82" priority="89">
+    <cfRule type="expression" dxfId="78" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="81" priority="88">
+    <cfRule type="expression" dxfId="77" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="80" priority="87">
+    <cfRule type="expression" dxfId="76" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="79" priority="86">
+    <cfRule type="expression" dxfId="75" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="78" priority="85">
+    <cfRule type="expression" dxfId="74" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="77" priority="84">
+    <cfRule type="expression" dxfId="73" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="76" priority="72">
+    <cfRule type="expression" dxfId="72" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="75" priority="82">
+    <cfRule type="expression" dxfId="71" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="74" priority="81">
+    <cfRule type="expression" dxfId="70" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="73" priority="80">
+    <cfRule type="expression" dxfId="69" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="72" priority="79">
+    <cfRule type="expression" dxfId="68" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="71" priority="78">
+    <cfRule type="expression" dxfId="67" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="70" priority="77">
+    <cfRule type="expression" dxfId="66" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="69" priority="76">
+    <cfRule type="expression" dxfId="65" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="68" priority="75">
+    <cfRule type="expression" dxfId="64" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="67" priority="74">
+    <cfRule type="expression" dxfId="63" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="66" priority="73">
+    <cfRule type="expression" dxfId="62" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="65" priority="71">
+    <cfRule type="expression" dxfId="61" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="64" priority="70">
+    <cfRule type="expression" dxfId="60" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="63" priority="69">
+    <cfRule type="expression" dxfId="59" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="62" priority="68">
+    <cfRule type="expression" dxfId="58" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="61" priority="62">
+    <cfRule type="expression" dxfId="57" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="60" priority="67">
+    <cfRule type="expression" dxfId="56" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="59" priority="66">
+    <cfRule type="expression" dxfId="55" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="58" priority="63">
+    <cfRule type="expression" dxfId="54" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="57" priority="65">
+    <cfRule type="expression" dxfId="53" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="56" priority="64">
+    <cfRule type="expression" dxfId="52" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q55:Q60 Q62:Q76">
-    <cfRule type="expression" dxfId="55" priority="59">
+    <cfRule type="expression" dxfId="51" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q11 P38:Q53 P55:Q60 P62:Q76">
-    <cfRule type="expression" dxfId="54" priority="58">
+    <cfRule type="expression" dxfId="50" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="53" priority="57">
+    <cfRule type="expression" dxfId="49" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="52" priority="56">
+    <cfRule type="expression" dxfId="48" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="51" priority="55">
+    <cfRule type="expression" dxfId="47" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="50" priority="54">
+    <cfRule type="expression" dxfId="46" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="49" priority="53">
+    <cfRule type="expression" dxfId="45" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="48" priority="52">
+    <cfRule type="expression" dxfId="44" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="47" priority="39">
+    <cfRule type="expression" dxfId="43" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="46" priority="48">
+    <cfRule type="expression" dxfId="42" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="45" priority="24">
+    <cfRule type="expression" dxfId="41" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="44" priority="46">
+    <cfRule type="expression" dxfId="40" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="43" priority="45">
+    <cfRule type="expression" dxfId="39" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="42" priority="44">
+    <cfRule type="expression" dxfId="38" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="41" priority="43">
+    <cfRule type="expression" dxfId="37" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="40" priority="42">
+    <cfRule type="expression" dxfId="36" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="39" priority="41">
+    <cfRule type="expression" dxfId="35" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="38" priority="40">
+    <cfRule type="expression" dxfId="34" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="37" priority="25">
+    <cfRule type="expression" dxfId="33" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="36" priority="36">
+    <cfRule type="expression" dxfId="32" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="35" priority="35">
+    <cfRule type="expression" dxfId="31" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="34" priority="34">
+    <cfRule type="expression" dxfId="30" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="33" priority="33">
+    <cfRule type="expression" dxfId="29" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="32" priority="32">
+    <cfRule type="expression" dxfId="28" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="31" priority="31">
+    <cfRule type="expression" dxfId="27" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="30" priority="30">
+    <cfRule type="expression" dxfId="26" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="29" priority="29">
+    <cfRule type="expression" dxfId="25" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="28" priority="28">
+    <cfRule type="expression" dxfId="24" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="27" priority="27">
+    <cfRule type="expression" dxfId="23" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="26" priority="26">
+    <cfRule type="expression" dxfId="22" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="21" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="24" priority="22">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="23" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="22" priority="20">
+    <cfRule type="expression" dxfId="18" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="20" priority="18">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="17" priority="13">
+    <cfRule type="expression" dxfId="13" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="16" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="15" priority="10">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="9" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="324">
   <si>
     <t>Sudeep</t>
   </si>
@@ -5779,9 +5779,10 @@
     <col min="18" max="18" width="13.42578125" style="133" customWidth="1" collapsed="1"/>
     <col min="19" max="19" width="13.42578125" style="133" customWidth="1"/>
     <col min="20" max="20" width="11.28515625" style="133" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="10.7109375" style="133" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="28" width="9.140625" style="133"/>
+    <col min="21" max="21" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="9.140625" style="133" collapsed="1"/>
+    <col min="24" max="28" width="9.140625" style="133"/>
     <col min="29" max="29" width="14.140625" style="133" customWidth="1"/>
     <col min="30" max="30" width="12" style="133" customWidth="1"/>
     <col min="31" max="31" width="15.85546875" style="133" customWidth="1"/>
@@ -5824,7 +5825,9 @@
       <c r="R2" s="256">
         <v>46281</v>
       </c>
-      <c r="S2" s="256"/>
+      <c r="S2" s="256">
+        <v>46282</v>
+      </c>
       <c r="T2" s="183"/>
       <c r="U2" s="184" t="s">
         <v>281</v>
@@ -5886,7 +5889,9 @@
       <c r="R3" s="179" t="s">
         <v>237</v>
       </c>
-      <c r="S3" s="179"/>
+      <c r="S3" s="179" t="s">
+        <v>236</v>
+      </c>
       <c r="T3" s="180"/>
       <c r="U3" s="189"/>
       <c r="V3" s="180"/>
@@ -5950,15 +5955,17 @@
       <c r="R4" s="158">
         <v>-149</v>
       </c>
-      <c r="S4" s="158"/>
+      <c r="S4" s="158">
+        <v>-21850</v>
+      </c>
       <c r="T4" s="211"/>
       <c r="U4" s="171">
         <f t="shared" ref="U4:U30" si="0">SUM(H4:T4)</f>
-        <v>-40798</v>
+        <v>-62648</v>
       </c>
       <c r="V4" s="149">
         <f t="shared" ref="V4:V30" si="1">IFERROR(U4/F4*100,0)/10000000</f>
-        <v>-0.81596000000000002</v>
+        <v>-1.2529600000000001</v>
       </c>
       <c r="AC4" s="133" t="s">
         <v>170</v>
@@ -6020,15 +6027,17 @@
       <c r="R5" s="147">
         <v>81831</v>
       </c>
-      <c r="S5" s="147"/>
+      <c r="S5" s="147">
+        <v>-92500</v>
+      </c>
       <c r="T5" s="174"/>
       <c r="U5" s="171">
         <f t="shared" si="0"/>
-        <v>168284</v>
+        <v>75784</v>
       </c>
       <c r="V5" s="149">
         <f t="shared" si="1"/>
-        <v>0.56094666666666659</v>
+        <v>0.2526133333333333</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -6084,7 +6093,9 @@
       <c r="R6" s="147">
         <v>0</v>
       </c>
-      <c r="S6" s="147"/>
+      <c r="S6" s="147">
+        <v>0</v>
+      </c>
       <c r="T6" s="174"/>
       <c r="U6" s="171">
         <f t="shared" si="0"/>
@@ -6148,15 +6159,17 @@
       <c r="R7" s="147">
         <v>23300</v>
       </c>
-      <c r="S7" s="147"/>
+      <c r="S7" s="147">
+        <v>-85900</v>
+      </c>
       <c r="T7" s="174"/>
       <c r="U7" s="171">
         <f t="shared" si="0"/>
-        <v>105547</v>
+        <v>19647</v>
       </c>
       <c r="V7" s="149">
         <f t="shared" si="1"/>
-        <v>1.0554699999999999</v>
+        <v>0.19647000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6212,19 +6225,21 @@
       <c r="R8" s="147">
         <v>-30125</v>
       </c>
-      <c r="S8" s="147"/>
+      <c r="S8" s="147">
+        <v>-78630</v>
+      </c>
       <c r="T8" s="174"/>
       <c r="U8" s="171">
         <f t="shared" si="0"/>
-        <v>34234</v>
+        <v>-44396</v>
       </c>
       <c r="V8" s="149">
         <f t="shared" si="1"/>
-        <v>0.11411333333333334</v>
+        <v>-0.14798666666666666</v>
       </c>
       <c r="X8" s="5"/>
       <c r="Y8" s="134">
-        <v>13</v>
+        <v>-11170</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -6280,18 +6295,20 @@
       <c r="R9" s="147">
         <v>-63430</v>
       </c>
-      <c r="S9" s="147"/>
+      <c r="S9" s="147">
+        <v>-31200</v>
+      </c>
       <c r="T9" s="174"/>
       <c r="U9" s="171">
         <f t="shared" si="0"/>
-        <v>49903</v>
+        <v>18703</v>
       </c>
       <c r="V9" s="149">
         <f t="shared" si="1"/>
-        <v>0.33268666666666663</v>
+        <v>0.12468666666666665</v>
       </c>
       <c r="X9" s="134">
-        <v>32574</v>
+        <v>97890</v>
       </c>
       <c r="Y9" s="134"/>
     </row>
@@ -6346,22 +6363,24 @@
       <c r="R10" s="147">
         <v>-31500</v>
       </c>
-      <c r="S10" s="147"/>
+      <c r="S10" s="147">
+        <v>-900</v>
+      </c>
       <c r="T10" s="174"/>
       <c r="U10" s="171">
         <f t="shared" si="0"/>
-        <v>9337</v>
+        <v>8437</v>
       </c>
       <c r="V10" s="149">
         <f t="shared" si="1"/>
-        <v>0.15561666666666668</v>
+        <v>0.14061666666666667</v>
       </c>
       <c r="X10" s="134">
-        <v>32587</v>
+        <v>86719</v>
       </c>
       <c r="Y10" s="134">
         <f>(X10+X9)/10000000*13780</f>
-        <v>89.791858000000005</v>
+        <v>254.39120199999999</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
@@ -6417,15 +6436,17 @@
       <c r="R11" s="147">
         <v>0</v>
       </c>
-      <c r="S11" s="147"/>
+      <c r="S11" s="147">
+        <v>4326</v>
+      </c>
       <c r="T11" s="174"/>
       <c r="U11" s="171">
         <f t="shared" si="0"/>
-        <v>-764248</v>
+        <v>-759922</v>
       </c>
       <c r="V11" s="149">
         <f t="shared" si="1"/>
-        <v>-0.50949866666666666</v>
+        <v>-0.50661466666666666</v>
       </c>
       <c r="X11" s="134"/>
       <c r="Y11" s="134"/>
@@ -6483,15 +6504,17 @@
       <c r="R12" s="147">
         <v>-100</v>
       </c>
-      <c r="S12" s="147"/>
+      <c r="S12" s="147">
+        <v>-35135</v>
+      </c>
       <c r="T12" s="174"/>
       <c r="U12" s="171">
         <f t="shared" si="0"/>
-        <v>25206</v>
+        <v>-9929</v>
       </c>
       <c r="V12" s="149">
         <f t="shared" si="1"/>
-        <v>4.2009999999999999E-2</v>
+        <v>-1.6548333333333332E-2</v>
       </c>
       <c r="X12" s="134"/>
       <c r="Y12" s="134"/>
@@ -6549,7 +6572,9 @@
       <c r="R13" s="147">
         <v>2399</v>
       </c>
-      <c r="S13" s="147"/>
+      <c r="S13" s="147">
+        <v>0</v>
+      </c>
       <c r="T13" s="174"/>
       <c r="U13" s="171">
         <f t="shared" si="0"/>
@@ -6615,15 +6640,17 @@
       <c r="R14" s="147">
         <v>-10140</v>
       </c>
-      <c r="S14" s="147"/>
+      <c r="S14" s="147">
+        <v>-16054</v>
+      </c>
       <c r="T14" s="174"/>
       <c r="U14" s="171">
         <f t="shared" si="0"/>
-        <v>3762</v>
+        <v>-12292</v>
       </c>
       <c r="V14" s="149">
         <f t="shared" si="1"/>
-        <v>1.5048000000000001E-2</v>
+        <v>-4.9168000000000003E-2</v>
       </c>
       <c r="X14" s="134"/>
       <c r="Y14" s="134"/>
@@ -6681,27 +6708,29 @@
       <c r="R15" s="147">
         <v>-6220</v>
       </c>
-      <c r="S15" s="147"/>
+      <c r="S15" s="147">
+        <v>-17616</v>
+      </c>
       <c r="T15" s="174"/>
       <c r="U15" s="171">
         <f t="shared" si="0"/>
-        <v>6980</v>
+        <v>-10636</v>
       </c>
       <c r="V15" s="149">
         <f t="shared" si="1"/>
-        <v>3.1727272727272722E-2</v>
+        <v>-4.8345454545454539E-2</v>
       </c>
       <c r="X15" s="134"/>
       <c r="Y15" s="193">
         <f>Y8-Y10</f>
-        <v>-76.791858000000005</v>
+        <v>-11424.391202000001</v>
       </c>
       <c r="AB15" s="133">
         <v>116185</v>
       </c>
       <c r="AD15" s="133">
         <f>AB15+Y15</f>
-        <v>116108.208142</v>
+        <v>104760.608798</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -6757,15 +6786,17 @@
       <c r="R16" s="147">
         <v>5959</v>
       </c>
-      <c r="S16" s="147"/>
+      <c r="S16" s="147">
+        <v>7570</v>
+      </c>
       <c r="T16" s="174"/>
       <c r="U16" s="171">
         <f t="shared" si="0"/>
-        <v>-25908</v>
+        <v>-18338</v>
       </c>
       <c r="V16" s="149">
         <f t="shared" si="1"/>
-        <v>-0.25907999999999998</v>
+        <v>-0.18337999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -6821,15 +6852,17 @@
       <c r="R17" s="147">
         <v>0</v>
       </c>
-      <c r="S17" s="147"/>
+      <c r="S17" s="147">
+        <v>-22321</v>
+      </c>
       <c r="T17" s="174"/>
       <c r="U17" s="171">
         <f t="shared" si="0"/>
-        <v>9579</v>
+        <v>-12742</v>
       </c>
       <c r="V17" s="149">
         <f t="shared" si="1"/>
-        <v>3.8316000000000003E-2</v>
+        <v>-5.0967999999999999E-2</v>
       </c>
       <c r="AD17" s="133">
         <v>4000000</v>
@@ -6896,15 +6929,17 @@
       <c r="R18" s="147">
         <v>0</v>
       </c>
-      <c r="S18" s="147"/>
+      <c r="S18" s="147">
+        <v>-38652</v>
+      </c>
       <c r="T18" s="174"/>
       <c r="U18" s="171">
         <f t="shared" si="0"/>
-        <v>13543</v>
+        <v>-25109</v>
       </c>
       <c r="V18" s="149">
         <f t="shared" si="1"/>
-        <v>3.3857499999999999E-2</v>
+        <v>-6.2772499999999995E-2</v>
       </c>
       <c r="AE18" s="133">
         <f>AE17/12</f>
@@ -6964,15 +6999,17 @@
       <c r="R19" s="147">
         <v>-73400</v>
       </c>
-      <c r="S19" s="147"/>
+      <c r="S19" s="147">
+        <v>-81145</v>
+      </c>
       <c r="T19" s="174"/>
       <c r="U19" s="171">
         <f t="shared" si="0"/>
-        <v>-200398</v>
+        <v>-281543</v>
       </c>
       <c r="V19" s="149">
         <f t="shared" si="1"/>
-        <v>-1.3359866666666667</v>
+        <v>-1.8769533333333335</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -7028,7 +7065,9 @@
       <c r="R20" s="147">
         <v>-52025</v>
       </c>
-      <c r="S20" s="147"/>
+      <c r="S20" s="147">
+        <v>0</v>
+      </c>
       <c r="T20" s="174"/>
       <c r="U20" s="171">
         <f t="shared" si="0"/>
@@ -7095,15 +7134,17 @@
       <c r="R21" s="147">
         <v>580</v>
       </c>
-      <c r="S21" s="147"/>
+      <c r="S21" s="147">
+        <v>-13500</v>
+      </c>
       <c r="T21" s="174"/>
       <c r="U21" s="171">
         <f t="shared" si="0"/>
-        <v>-19503</v>
+        <v>-33003</v>
       </c>
       <c r="V21" s="149">
         <f t="shared" si="1"/>
-        <v>-0.78012000000000004</v>
+        <v>-1.32012</v>
       </c>
       <c r="Z21" s="133">
         <v>30400</v>
@@ -7162,7 +7203,9 @@
       <c r="R22" s="147">
         <v>0</v>
       </c>
-      <c r="S22" s="147"/>
+      <c r="S22" s="147">
+        <v>0</v>
+      </c>
       <c r="T22" s="174"/>
       <c r="U22" s="171">
         <f t="shared" si="0"/>
@@ -7229,7 +7272,9 @@
       <c r="R23" s="147">
         <v>0</v>
       </c>
-      <c r="S23" s="147"/>
+      <c r="S23" s="147">
+        <v>0</v>
+      </c>
       <c r="T23" s="174"/>
       <c r="U23" s="171">
         <f t="shared" si="0"/>
@@ -7293,15 +7338,17 @@
       <c r="R24" s="147">
         <v>-32214</v>
       </c>
-      <c r="S24" s="147"/>
+      <c r="S24" s="147">
+        <v>9741</v>
+      </c>
       <c r="T24" s="174"/>
       <c r="U24" s="171">
         <f t="shared" si="0"/>
-        <v>-11535</v>
+        <v>-1794</v>
       </c>
       <c r="V24" s="149">
         <f t="shared" si="1"/>
-        <v>-0.10486363636363635</v>
+        <v>-1.6309090909090908E-2</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
@@ -7357,15 +7404,17 @@
       <c r="R25" s="147">
         <v>48600</v>
       </c>
-      <c r="S25" s="147"/>
+      <c r="S25" s="147">
+        <v>181200</v>
+      </c>
       <c r="T25" s="174"/>
       <c r="U25" s="171">
         <f t="shared" si="0"/>
-        <v>-1448523</v>
+        <v>-1267323</v>
       </c>
       <c r="V25" s="149">
         <f t="shared" si="1"/>
-        <v>-6.2979260869565215</v>
+        <v>-5.5101000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
@@ -7419,15 +7468,17 @@
       <c r="R26" s="147">
         <v>1700</v>
       </c>
-      <c r="S26" s="147"/>
+      <c r="S26" s="147">
+        <v>1785</v>
+      </c>
       <c r="T26" s="174"/>
       <c r="U26" s="171">
         <f t="shared" si="0"/>
-        <v>5794</v>
+        <v>7579</v>
       </c>
       <c r="V26" s="149">
         <f t="shared" si="1"/>
-        <v>0.28970000000000001</v>
+        <v>0.37895000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
@@ -7483,15 +7534,17 @@
       <c r="R27" s="147">
         <v>0</v>
       </c>
-      <c r="S27" s="147"/>
+      <c r="S27" s="147">
+        <v>-65000</v>
+      </c>
       <c r="T27" s="174"/>
       <c r="U27" s="171">
         <f t="shared" si="0"/>
-        <v>34666</v>
+        <v>-30334</v>
       </c>
       <c r="V27" s="149">
         <f t="shared" si="1"/>
-        <v>6.9332000000000005E-2</v>
+        <v>-6.0668E-2</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
@@ -7547,15 +7600,17 @@
       <c r="R28" s="147">
         <v>-481200</v>
       </c>
-      <c r="S28" s="147"/>
+      <c r="S28" s="147">
+        <v>-443700</v>
+      </c>
       <c r="T28" s="174"/>
       <c r="U28" s="171">
         <f t="shared" si="0"/>
-        <v>-1231866</v>
+        <v>-1675566</v>
       </c>
       <c r="V28" s="149">
         <f t="shared" si="1"/>
-        <v>-1.2318659999999999</v>
+        <v>-1.6755660000000001</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
@@ -7611,15 +7666,17 @@
       <c r="R29" s="147">
         <v>0</v>
       </c>
-      <c r="S29" s="147"/>
+      <c r="S29" s="147">
+        <v>-33000</v>
+      </c>
       <c r="T29" s="174"/>
       <c r="U29" s="171">
         <f t="shared" si="0"/>
-        <v>-341989</v>
+        <v>-374989</v>
       </c>
       <c r="V29" s="149">
         <f t="shared" si="1"/>
-        <v>-0.68397799999999997</v>
+        <v>-0.74997800000000003</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
@@ -7675,15 +7732,17 @@
       <c r="R30" s="147">
         <v>-100709</v>
       </c>
-      <c r="S30" s="147"/>
+      <c r="S30" s="147">
+        <v>-184894</v>
+      </c>
       <c r="T30" s="174"/>
       <c r="U30" s="171">
         <f t="shared" si="0"/>
-        <v>65134</v>
+        <v>-119760</v>
       </c>
       <c r="V30" s="149">
         <f t="shared" si="1"/>
-        <v>0.13026799999999999</v>
+        <v>-0.23952000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
@@ -7739,15 +7798,17 @@
       <c r="R31" s="147">
         <v>-55712</v>
       </c>
-      <c r="S31" s="147"/>
+      <c r="S31" s="147">
+        <v>-11425</v>
+      </c>
       <c r="T31" s="174"/>
       <c r="U31" s="171">
         <f t="shared" ref="U31:U56" si="2">SUM(H31:T31)</f>
-        <v>-186096</v>
+        <v>-197521</v>
       </c>
       <c r="V31" s="149">
         <f t="shared" ref="V31:V56" si="3">IFERROR(U31/F31*100,0)/10000000</f>
-        <v>-3.7219199999999999</v>
+        <v>-3.9504199999999998</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
@@ -7803,15 +7864,17 @@
       <c r="R32" s="147">
         <v>-24900</v>
       </c>
-      <c r="S32" s="147"/>
+      <c r="S32" s="147">
+        <v>-6308</v>
+      </c>
       <c r="T32" s="174"/>
       <c r="U32" s="171">
         <f t="shared" si="2"/>
-        <v>115289</v>
+        <v>108981</v>
       </c>
       <c r="V32" s="149">
         <f t="shared" si="3"/>
-        <v>2.882225</v>
+        <v>2.7245249999999999</v>
       </c>
       <c r="Y32" s="134"/>
     </row>
@@ -7868,7 +7931,9 @@
       <c r="R33" s="147">
         <v>0</v>
       </c>
-      <c r="S33" s="147"/>
+      <c r="S33" s="147">
+        <v>0</v>
+      </c>
       <c r="T33" s="174"/>
       <c r="U33" s="171">
         <f t="shared" si="2"/>
@@ -7880,7 +7945,7 @@
       </c>
       <c r="X33" s="5"/>
       <c r="Y33" s="134">
-        <v>-97634</v>
+        <v>-23327</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
@@ -7936,7 +8001,9 @@
       <c r="R34" s="147">
         <v>0</v>
       </c>
-      <c r="S34" s="147"/>
+      <c r="S34" s="147">
+        <v>0</v>
+      </c>
       <c r="T34" s="174"/>
       <c r="U34" s="171">
         <f t="shared" si="2"/>
@@ -8002,22 +8069,24 @@
       <c r="R35" s="147">
         <v>-14983</v>
       </c>
-      <c r="S35" s="147"/>
+      <c r="S35" s="147">
+        <v>-31590</v>
+      </c>
       <c r="T35" s="174"/>
       <c r="U35" s="171">
         <f t="shared" si="2"/>
-        <v>-131563</v>
+        <v>-163153</v>
       </c>
       <c r="V35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.32890750000000002</v>
+        <v>-0.40788249999999998</v>
       </c>
       <c r="X35" s="134">
-        <v>1164469</v>
+        <v>3334436</v>
       </c>
       <c r="Y35" s="134">
         <f>(X36+X35)/10000000*13780</f>
-        <v>3074.7369120000003</v>
+        <v>9554.3078800000003</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
@@ -8073,18 +8142,20 @@
       <c r="R36" s="147">
         <v>17600</v>
       </c>
-      <c r="S36" s="147"/>
+      <c r="S36" s="147">
+        <v>30200</v>
+      </c>
       <c r="T36" s="174"/>
       <c r="U36" s="171">
         <f t="shared" si="2"/>
-        <v>-191279</v>
+        <v>-161079</v>
       </c>
       <c r="V36" s="149">
         <f t="shared" si="3"/>
-        <v>-1.91279</v>
+        <v>-1.6107899999999999</v>
       </c>
       <c r="X36" s="134">
-        <v>1066835</v>
+        <v>3599024</v>
       </c>
       <c r="Y36" s="134"/>
     </row>
@@ -8139,7 +8210,9 @@
       <c r="R37" s="147">
         <v>0</v>
       </c>
-      <c r="S37" s="147"/>
+      <c r="S37" s="147">
+        <v>0</v>
+      </c>
       <c r="T37" s="174"/>
       <c r="U37" s="171">
         <f t="shared" si="2"/>
@@ -8152,7 +8225,7 @@
       <c r="X37" s="134"/>
       <c r="Y37" s="134">
         <f>+Y33-Y35</f>
-        <v>-100708.73691199999</v>
+        <v>-32881.30788</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
@@ -8208,15 +8281,17 @@
       <c r="R38" s="147">
         <v>-5240</v>
       </c>
-      <c r="S38" s="147"/>
+      <c r="S38" s="147">
+        <v>52612</v>
+      </c>
       <c r="T38" s="174"/>
       <c r="U38" s="171">
         <f t="shared" si="2"/>
-        <v>-13195</v>
+        <v>39417</v>
       </c>
       <c r="V38" s="149">
         <f t="shared" si="3"/>
-        <v>-0.26390000000000002</v>
+        <v>0.78834000000000004</v>
       </c>
       <c r="X38" s="134"/>
       <c r="Y38" s="134"/>
@@ -8274,7 +8349,9 @@
       <c r="R39" s="147">
         <v>0</v>
       </c>
-      <c r="S39" s="147"/>
+      <c r="S39" s="147">
+        <v>0</v>
+      </c>
       <c r="T39" s="174"/>
       <c r="U39" s="171">
         <f t="shared" si="2"/>
@@ -8340,15 +8417,17 @@
       <c r="R40" s="147">
         <v>-83825</v>
       </c>
-      <c r="S40" s="147"/>
+      <c r="S40" s="147">
+        <v>-44514</v>
+      </c>
       <c r="T40" s="174"/>
       <c r="U40" s="171">
         <f t="shared" si="2"/>
-        <v>-27892</v>
+        <v>-72406</v>
       </c>
       <c r="V40" s="149">
         <f t="shared" si="3"/>
-        <v>-9.2973333333333338E-2</v>
+        <v>-0.24135333333333331</v>
       </c>
       <c r="X40" s="134"/>
       <c r="Y40" s="134"/>
@@ -8404,7 +8483,9 @@
       <c r="R41" s="147">
         <v>0</v>
       </c>
-      <c r="S41" s="147"/>
+      <c r="S41" s="147">
+        <v>0</v>
+      </c>
       <c r="T41" s="174"/>
       <c r="U41" s="171">
         <f t="shared" si="2"/>
@@ -8469,15 +8550,17 @@
       <c r="R42" s="147">
         <v>-15800</v>
       </c>
-      <c r="S42" s="147"/>
+      <c r="S42" s="147">
+        <v>-7355</v>
+      </c>
       <c r="T42" s="174"/>
       <c r="U42" s="171">
         <f t="shared" si="2"/>
-        <v>-6378</v>
+        <v>-13733</v>
       </c>
       <c r="V42" s="149">
         <f t="shared" si="3"/>
-        <v>-0.12756000000000001</v>
+        <v>-0.27466000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
@@ -8533,15 +8616,17 @@
       <c r="R43" s="147">
         <v>-13600</v>
       </c>
-      <c r="S43" s="147"/>
+      <c r="S43" s="147">
+        <v>25400</v>
+      </c>
       <c r="T43" s="174"/>
       <c r="U43" s="171">
         <f t="shared" si="2"/>
-        <v>-463353</v>
+        <v>-437953</v>
       </c>
       <c r="V43" s="149">
         <f t="shared" si="3"/>
-        <v>-4.6335300000000004</v>
+        <v>-4.3795299999999999</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
@@ -8595,15 +8680,17 @@
       <c r="R44" s="147">
         <v>-4699</v>
       </c>
-      <c r="S44" s="147"/>
+      <c r="S44" s="147">
+        <v>534</v>
+      </c>
       <c r="T44" s="174"/>
       <c r="U44" s="171">
         <f t="shared" si="2"/>
-        <v>7247</v>
+        <v>7781</v>
       </c>
       <c r="V44" s="149">
         <f t="shared" si="3"/>
-        <v>0.72470000000000001</v>
+        <v>0.77810000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
@@ -8659,15 +8746,17 @@
       <c r="R45" s="147">
         <v>-29500</v>
       </c>
-      <c r="S45" s="147"/>
+      <c r="S45" s="147">
+        <v>-42504</v>
+      </c>
       <c r="T45" s="174"/>
       <c r="U45" s="171">
         <f t="shared" si="2"/>
-        <v>-185625</v>
+        <v>-228129</v>
       </c>
       <c r="V45" s="149">
         <f t="shared" si="3"/>
-        <v>-0.46406249999999999</v>
+        <v>-0.57032249999999995</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
@@ -8723,7 +8812,9 @@
       <c r="R46" s="147">
         <v>0</v>
       </c>
-      <c r="S46" s="147"/>
+      <c r="S46" s="147">
+        <v>0</v>
+      </c>
       <c r="T46" s="174"/>
       <c r="U46" s="171">
         <f t="shared" si="2"/>
@@ -8787,15 +8878,17 @@
       <c r="R47" s="147">
         <v>-296157</v>
       </c>
-      <c r="S47" s="147"/>
+      <c r="S47" s="147">
+        <v>-211473</v>
+      </c>
       <c r="T47" s="174"/>
       <c r="U47" s="171">
         <f t="shared" si="2"/>
-        <v>376191</v>
+        <v>164718</v>
       </c>
       <c r="V47" s="149">
         <f t="shared" si="3"/>
-        <v>1.25397</v>
+        <v>0.54905999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
@@ -8849,15 +8942,17 @@
       <c r="R48" s="151">
         <v>54600</v>
       </c>
-      <c r="S48" s="151"/>
+      <c r="S48" s="151">
+        <v>219000</v>
+      </c>
       <c r="T48" s="174"/>
       <c r="U48" s="171">
         <f t="shared" si="2"/>
-        <v>-653336</v>
+        <v>-434336</v>
       </c>
       <c r="V48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.65333600000000003</v>
+        <v>-0.434336</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
@@ -8909,7 +9004,9 @@
       <c r="R49" s="151">
         <v>0</v>
       </c>
-      <c r="S49" s="151"/>
+      <c r="S49" s="151">
+        <v>0</v>
+      </c>
       <c r="T49" s="174"/>
       <c r="U49" s="171">
         <f t="shared" si="2"/>
@@ -8973,15 +9070,17 @@
       <c r="R50" s="151">
         <v>-100</v>
       </c>
-      <c r="S50" s="151"/>
+      <c r="S50" s="151">
+        <v>4098</v>
+      </c>
       <c r="T50" s="174"/>
       <c r="U50" s="171">
         <f t="shared" si="2"/>
-        <v>30570</v>
+        <v>34668</v>
       </c>
       <c r="V50" s="149">
         <f t="shared" si="3"/>
-        <v>0.61140000000000005</v>
+        <v>0.69335999999999998</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
@@ -9037,15 +9136,17 @@
       <c r="R51" s="151">
         <v>-500</v>
       </c>
-      <c r="S51" s="151"/>
+      <c r="S51" s="151">
+        <v>36340</v>
+      </c>
       <c r="T51" s="174"/>
       <c r="U51" s="171">
         <f t="shared" si="2"/>
-        <v>-618213</v>
+        <v>-581873</v>
       </c>
       <c r="V51" s="149">
         <f t="shared" si="3"/>
-        <v>-0.95109692307692317</v>
+        <v>-0.89518923076923085</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
@@ -9101,7 +9202,9 @@
       <c r="R52" s="151">
         <v>0</v>
       </c>
-      <c r="S52" s="151"/>
+      <c r="S52" s="151">
+        <v>0</v>
+      </c>
       <c r="T52" s="174"/>
       <c r="U52" s="171">
         <f t="shared" si="2"/>
@@ -9165,15 +9268,17 @@
       <c r="R53" s="151">
         <v>0</v>
       </c>
-      <c r="S53" s="151"/>
+      <c r="S53" s="151">
+        <v>-42834</v>
+      </c>
       <c r="T53" s="174"/>
       <c r="U53" s="171">
         <f t="shared" si="2"/>
-        <v>-174516</v>
+        <v>-217350</v>
       </c>
       <c r="V53" s="149">
         <f t="shared" si="3"/>
-        <v>-0.58172000000000001</v>
+        <v>-0.72450000000000003</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
@@ -9227,7 +9332,9 @@
       <c r="R54" s="151">
         <v>0</v>
       </c>
-      <c r="S54" s="151"/>
+      <c r="S54" s="151">
+        <v>0</v>
+      </c>
       <c r="T54" s="174"/>
       <c r="U54" s="171">
         <f t="shared" si="2"/>
@@ -9289,15 +9396,17 @@
       <c r="R55" s="151">
         <v>-13500</v>
       </c>
-      <c r="S55" s="151"/>
+      <c r="S55" s="151">
+        <v>14150</v>
+      </c>
       <c r="T55" s="174"/>
       <c r="U55" s="171">
         <f t="shared" si="2"/>
-        <v>8628</v>
+        <v>22778</v>
       </c>
       <c r="V55" s="149">
         <f t="shared" si="3"/>
-        <v>1.7256000000000001E-2</v>
+        <v>4.5556000000000006E-2</v>
       </c>
     </row>
     <row r="56" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9354,7 +9463,7 @@
       </c>
       <c r="S56" s="254">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1073044</v>
       </c>
       <c r="T56" s="254">
         <f>SUM(T4:T55)</f>
@@ -9362,7 +9471,7 @@
       </c>
       <c r="U56" s="254">
         <f t="shared" si="2"/>
-        <v>-6039129</v>
+        <v>-7112173</v>
       </c>
       <c r="V56" s="255">
         <f t="shared" si="3"/>
@@ -9446,15 +9555,17 @@
       <c r="R58" s="162">
         <v>0</v>
       </c>
-      <c r="S58" s="162"/>
+      <c r="S58" s="162">
+        <v>-101150</v>
+      </c>
       <c r="T58" s="246"/>
       <c r="U58" s="247">
         <f>SUM(H58:T58)</f>
-        <v>-715553</v>
+        <v>-816703</v>
       </c>
       <c r="V58" s="248">
         <f>IFERROR(U58/F58*100,0)/10000000</f>
-        <v>-2.3851766666666663</v>
+        <v>-2.7223433333333333</v>
       </c>
       <c r="Y58" s="134"/>
     </row>
@@ -9509,7 +9620,9 @@
       <c r="R59" s="162">
         <v>0</v>
       </c>
-      <c r="S59" s="162"/>
+      <c r="S59" s="162">
+        <v>0</v>
+      </c>
       <c r="T59" s="174"/>
       <c r="U59" s="171">
         <f>SUM(H59:T59)</f>
@@ -9575,7 +9688,7 @@
       </c>
       <c r="S60" s="170">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-101150</v>
       </c>
       <c r="T60" s="170">
         <f>SUM(T58:T59)</f>
@@ -9583,7 +9696,7 @@
       </c>
       <c r="U60" s="254">
         <f>SUM(H60:T60)</f>
-        <v>-628287</v>
+        <v>-729437</v>
       </c>
       <c r="V60" s="19"/>
       <c r="X60" s="5"/>
@@ -22776,19 +22889,19 @@
       </c>
       <c r="K4" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-40798</v>
+        <v>-62648</v>
       </c>
       <c r="L4" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.81596000000000002</v>
+        <v>-1.2529600000000001</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-67842</v>
+        <v>-89692</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-1.35684</v>
+        <v>-1.7938400000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -22828,19 +22941,19 @@
       </c>
       <c r="K5" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>168284</v>
+        <v>75784</v>
       </c>
       <c r="L5" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.56094666666666659</v>
+        <v>0.2526133333333333</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-82687</v>
+        <v>-175187</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-0.27562333333333344</v>
+        <v>-0.58395666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -22932,19 +23045,19 @@
       </c>
       <c r="K7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>105547</v>
+        <v>19647</v>
       </c>
       <c r="L7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>1.0554699999999999</v>
+        <v>0.19647000000000001</v>
       </c>
       <c r="M7" s="71">
         <f t="shared" si="1"/>
-        <v>76557</v>
+        <v>-9343</v>
       </c>
       <c r="N7" s="166">
         <f t="shared" si="2"/>
-        <v>1.0554699999999999</v>
+        <v>0.19647000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -22984,19 +23097,19 @@
       </c>
       <c r="K8" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>34234</v>
+        <v>-44396</v>
       </c>
       <c r="L8" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.11411333333333334</v>
+        <v>-0.14798666666666666</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-420863</v>
+        <v>-499493</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.4028766666666668</v>
+        <v>-1.6649766666666668</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -23036,19 +23149,19 @@
       </c>
       <c r="K9" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>49903</v>
+        <v>18703</v>
       </c>
       <c r="L9" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.33268666666666663</v>
+        <v>0.12468666666666665</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-244233</v>
+        <v>-275433</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6282200000000004</v>
+        <v>-1.8362200000000004</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -23088,19 +23201,19 @@
       </c>
       <c r="K10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>9337</v>
+        <v>8437</v>
       </c>
       <c r="L10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.15561666666666668</v>
+        <v>0.14061666666666667</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-182912</v>
+        <v>-183812</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-3.0485333333333338</v>
+        <v>-3.0635333333333334</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -23140,19 +23253,19 @@
       </c>
       <c r="K11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-764248</v>
+        <v>-759922</v>
       </c>
       <c r="L11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.50949866666666666</v>
+        <v>-0.50661466666666666</v>
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>203017</v>
+        <v>207343</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.13534466666666678</v>
+        <v>0.13822866666666678</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -23192,19 +23305,19 @@
       </c>
       <c r="K12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>25206</v>
+        <v>-9929</v>
       </c>
       <c r="L12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>4.2009999999999999E-2</v>
+        <v>-1.6548333333333332E-2</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>432986</v>
+        <v>397851</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.72164333333333341</v>
+        <v>0.66308500000000015</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -23296,19 +23409,19 @@
       </c>
       <c r="K14" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>3762</v>
+        <v>-12292</v>
       </c>
       <c r="L14" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>1.5048000000000001E-2</v>
+        <v>-4.9168000000000003E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>48682</v>
+        <v>32628</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.19472799999999996</v>
+        <v>0.13051199999999996</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -23400,19 +23513,19 @@
       </c>
       <c r="K16" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-25908</v>
+        <v>-18338</v>
       </c>
       <c r="L16" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.25907999999999998</v>
+        <v>-0.18337999999999999</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>47499</v>
+        <v>55069</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.47499000000000002</v>
+        <v>0.55069000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -23452,19 +23565,19 @@
       </c>
       <c r="K17" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>6980</v>
+        <v>-10636</v>
       </c>
       <c r="L17" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>3.1727272727272722E-2</v>
+        <v>-4.8345454545454539E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-80928</v>
+        <v>-98544</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.36785454545454543</v>
+        <v>-0.44792727272727267</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -23504,19 +23617,19 @@
       </c>
       <c r="K18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>9579</v>
+        <v>-12742</v>
       </c>
       <c r="L18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>3.8316000000000003E-2</v>
+        <v>-5.0967999999999999E-2</v>
       </c>
       <c r="M18" s="71">
         <f t="shared" si="0"/>
-        <v>-54338</v>
+        <v>-76659</v>
       </c>
       <c r="N18" s="166">
         <f t="shared" si="0"/>
-        <v>-0.21735199999999999</v>
+        <v>-0.30663600000000002</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -23556,19 +23669,19 @@
       </c>
       <c r="K19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>13543</v>
+        <v>-25109</v>
       </c>
       <c r="L19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>3.3857499999999999E-2</v>
+        <v>-6.2772499999999995E-2</v>
       </c>
       <c r="M19" s="71">
         <f t="shared" si="0"/>
-        <v>280858</v>
+        <v>242206</v>
       </c>
       <c r="N19" s="166">
         <f t="shared" si="0"/>
-        <v>0.70214499999999991</v>
+        <v>0.60551499999999991</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -23660,19 +23773,19 @@
       </c>
       <c r="K21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-19503</v>
+        <v>-33003</v>
       </c>
       <c r="L21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.78012000000000004</v>
+        <v>-1.32012</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-63049</v>
+        <v>-76549</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-2.52196</v>
+        <v>-3.06196</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -23764,19 +23877,19 @@
       </c>
       <c r="K23" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-200398</v>
+        <v>-281543</v>
       </c>
       <c r="L23" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.3359866666666667</v>
+        <v>-1.8769533333333335</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>-85385</v>
+        <v>-166530</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>-0.56923333333333326</v>
+        <v>-1.1102000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -23868,19 +23981,19 @@
       </c>
       <c r="K25" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-11535</v>
+        <v>-1794</v>
       </c>
       <c r="L25" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.10486363636363635</v>
+        <v>-1.6309090909090908E-2</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>193169</v>
+        <v>202910</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>1.7560818181818176</v>
+        <v>1.8446363636363632</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -23920,19 +24033,19 @@
       </c>
       <c r="K26" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1448523</v>
+        <v>-1267323</v>
       </c>
       <c r="L26" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-6.2979260869565215</v>
+        <v>-5.5101000000000004</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-1094462</v>
+        <v>-913262</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-4.7585304347826085</v>
+        <v>-3.9707043478260879</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -23970,19 +24083,19 @@
       </c>
       <c r="K27" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>5794</v>
+        <v>7579</v>
       </c>
       <c r="L27" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.28970000000000001</v>
+        <v>0.37895000000000001</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-14502</v>
+        <v>-12717</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.72509999999999986</v>
+        <v>-0.63584999999999992</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -24022,19 +24135,19 @@
       </c>
       <c r="K28" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>34666</v>
+        <v>-30334</v>
       </c>
       <c r="L28" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>6.9332000000000005E-2</v>
+        <v>-6.0668E-2</v>
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>-230252</v>
+        <v>-295252</v>
       </c>
       <c r="N28" s="166">
         <f t="shared" si="0"/>
-        <v>-0.46050399999999997</v>
+        <v>-0.59050399999999992</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -24074,19 +24187,19 @@
       </c>
       <c r="K29" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1231866</v>
+        <v>-1675566</v>
       </c>
       <c r="L29" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.2318659999999999</v>
+        <v>-1.6755660000000001</v>
       </c>
       <c r="M29" s="71">
         <f t="shared" si="0"/>
-        <v>2235546</v>
+        <v>1791846</v>
       </c>
       <c r="N29" s="166">
         <f t="shared" si="0"/>
-        <v>2.2355460000000003</v>
+        <v>1.7918459999999998</v>
       </c>
       <c r="O29" s="131"/>
     </row>
@@ -24387,19 +24500,19 @@
       </c>
       <c r="K35" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-341989</v>
+        <v>-374989</v>
       </c>
       <c r="L35" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.68397799999999997</v>
+        <v>-0.74997800000000003</v>
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>357863</v>
+        <v>324863</v>
       </c>
       <c r="N35" s="166">
         <f t="shared" si="0"/>
-        <v>0.71572599999999986</v>
+        <v>0.6497259999999998</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -24439,19 +24552,19 @@
       </c>
       <c r="K36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>65134</v>
+        <v>-119760</v>
       </c>
       <c r="L36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.13026799999999999</v>
+        <v>-0.23952000000000001</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>1092541</v>
+        <v>907647</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>2.185082</v>
+        <v>1.815294</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -24491,19 +24604,19 @@
       </c>
       <c r="K37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-186096</v>
+        <v>-197521</v>
       </c>
       <c r="L37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-3.7219199999999999</v>
+        <v>-3.9504199999999998</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-265460</v>
+        <v>-276885</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-5.3091999999999997</v>
+        <v>-5.5377000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -24543,19 +24656,19 @@
       </c>
       <c r="K38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>115289</v>
+        <v>108981</v>
       </c>
       <c r="L38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>2.882225</v>
+        <v>2.7245249999999999</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>49764</v>
+        <v>43456</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>1.2441000000000002</v>
+        <v>1.0864</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -24699,19 +24812,19 @@
       </c>
       <c r="K41" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-131563</v>
+        <v>-163153</v>
       </c>
       <c r="L41" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.32890750000000002</v>
+        <v>-0.40788249999999998</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>579373</v>
+        <v>547783</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.4484325</v>
+        <v>1.3694575000000002</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -24751,19 +24864,19 @@
       </c>
       <c r="K42" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-191279</v>
+        <v>-161079</v>
       </c>
       <c r="L42" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.91279</v>
+        <v>-1.6107899999999999</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>12353</v>
+        <v>42553</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>0.12352999999999992</v>
+        <v>0.42552999999999996</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -24853,19 +24966,19 @@
       </c>
       <c r="K44" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-13195</v>
+        <v>39417</v>
       </c>
       <c r="L44" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.26390000000000002</v>
+        <v>0.78834000000000004</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-79578</v>
+        <v>-26966</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-1.5915599999999999</v>
+        <v>-0.5393199999999998</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -24905,19 +25018,19 @@
       </c>
       <c r="K45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-27892</v>
+        <v>-72406</v>
       </c>
       <c r="L45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-9.2973333333333338E-2</v>
+        <v>-0.24135333333333331</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-138684</v>
+        <v>-183198</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.46228000000000002</v>
+        <v>-0.61065999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -25111,19 +25224,19 @@
       </c>
       <c r="K49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-6378</v>
+        <v>-13733</v>
       </c>
       <c r="L49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.12756000000000001</v>
+        <v>-0.27466000000000002</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>27950</v>
+        <v>20595</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>0.2384</v>
+        <v>9.1299999999999992E-2</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -25163,19 +25276,19 @@
       </c>
       <c r="K50" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-463353</v>
+        <v>-437953</v>
       </c>
       <c r="L50" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-4.6335300000000004</v>
+        <v>-4.3795299999999999</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>424021</v>
+        <v>449421</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>4.2402099999999994</v>
+        <v>4.4942099999999998</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -25213,19 +25326,19 @@
       </c>
       <c r="K51" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>7247</v>
+        <v>7781</v>
       </c>
       <c r="L51" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.72470000000000001</v>
+        <v>0.77810000000000001</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>3701</v>
+        <v>4235</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.37009999999999998</v>
+        <v>0.42349999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -25265,19 +25378,19 @@
       </c>
       <c r="K52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>376191</v>
+        <v>164718</v>
       </c>
       <c r="L52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>1.25397</v>
+        <v>0.54905999999999999</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>367458</v>
+        <v>155985</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>1.2248600000000001</v>
+        <v>0.51995000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -25363,19 +25476,19 @@
       </c>
       <c r="K54" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-185625</v>
+        <v>-228129</v>
       </c>
       <c r="L54" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.46406249999999999</v>
+        <v>-0.57032249999999995</v>
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>289577</v>
+        <v>247073</v>
       </c>
       <c r="N54" s="166">
         <f t="shared" si="0"/>
-        <v>0.72394249999999993</v>
+        <v>0.61768250000000002</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -25465,19 +25578,19 @@
       </c>
       <c r="K56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-653336</v>
+        <v>-434336</v>
       </c>
       <c r="L56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.65333600000000003</v>
+        <v>-0.434336</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1688416</v>
+        <v>-1469416</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.6885159999999999</v>
+        <v>-1.469516</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -25563,19 +25676,19 @@
       </c>
       <c r="K58" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>30570</v>
+        <v>34668</v>
       </c>
       <c r="L58" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.61140000000000005</v>
+        <v>0.69335999999999998</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>-3725</v>
+        <v>373</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>-7.44999999999999E-2</v>
+        <v>7.4600000000000222E-3</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -25615,19 +25728,19 @@
       </c>
       <c r="K59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-618213</v>
+        <v>-581873</v>
       </c>
       <c r="L59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.95109692307692317</v>
+        <v>-0.89518923076923085</v>
       </c>
       <c r="M59" s="71">
         <f t="shared" si="0"/>
-        <v>325731</v>
+        <v>362071</v>
       </c>
       <c r="N59" s="166">
         <f t="shared" si="0"/>
-        <v>1.3445140384615386</v>
+        <v>1.4004217307692308</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -25719,19 +25832,19 @@
       </c>
       <c r="K61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-174516</v>
+        <v>-217350</v>
       </c>
       <c r="L61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.58172000000000001</v>
+        <v>-0.72450000000000003</v>
       </c>
       <c r="M61" s="71">
         <f t="shared" si="0"/>
-        <v>529557</v>
+        <v>486723</v>
       </c>
       <c r="N61" s="166">
         <f t="shared" si="0"/>
-        <v>1.7651900000000003</v>
+        <v>1.6224100000000004</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -25871,19 +25984,19 @@
       </c>
       <c r="K64" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>8628</v>
+        <v>22778</v>
       </c>
       <c r="L64" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>1.7256000000000001E-2</v>
+        <v>4.5556000000000006E-2</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>498033</v>
+        <v>512183</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>0.99606600000000001</v>
+        <v>1.0243659999999999</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -25905,12 +26018,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-6059497</v>
+        <v>-7146691</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>5691550</v>
+        <v>4604356</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -25991,19 +26104,19 @@
       </c>
       <c r="K69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-715553</v>
+        <v>-816703</v>
       </c>
       <c r="L69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-2.3851766666666663</v>
+        <v>-2.7223433333333333</v>
       </c>
       <c r="M69" s="153">
         <f t="shared" ref="M69:N69" si="29">G69+I69+K69</f>
-        <v>-29043</v>
+        <v>-130193</v>
       </c>
       <c r="N69" s="167">
         <f t="shared" si="29"/>
-        <v>-9.6809999999999174E-2</v>
+        <v>-0.43397666666666623</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -26069,12 +26182,12 @@
       <c r="J71" s="104"/>
       <c r="K71" s="93">
         <f>SUM(K69:K70)</f>
-        <v>-628287</v>
+        <v>-729437</v>
       </c>
       <c r="L71" s="113"/>
       <c r="M71" s="93">
         <f>SUM(M69:M70)</f>
-        <v>1227108</v>
+        <v>1125958</v>
       </c>
       <c r="N71" s="236"/>
     </row>
@@ -44806,11 +44919,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-67842</v>
+        <v>-89692</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.35684</v>
+        <v>-1.7938400000000001</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -44827,11 +44940,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-116178</v>
+        <v>-138028</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-2.3235600000000001</v>
+        <v>-2.7605599999999999</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44888,11 +45001,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-82687</v>
+        <v>-175187</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.27562333333333344</v>
+        <v>-0.58395666666666668</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -44909,11 +45022,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>1251587</v>
+        <v>1159087</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>4.1719566666666665</v>
+        <v>3.8636233333333339</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45085,11 +45198,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-420863</v>
+        <v>-499493</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.4028766666666668</v>
+        <v>-1.6649766666666668</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -45105,11 +45218,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-779772</v>
+        <v>-858402</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-4.0435566666666674</v>
+        <v>-4.3056566666666667</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45166,11 +45279,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-244233</v>
+        <v>-275433</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6282200000000004</v>
+        <v>-1.8362200000000004</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -45186,11 +45299,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-419195</v>
+        <v>-450395</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-2.7946333333333335</v>
+        <v>-3.0026333333333337</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45247,11 +45360,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-182912</v>
+        <v>-183812</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.0485333333333338</v>
+        <v>-3.0635333333333334</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -45267,11 +45380,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-182912</v>
+        <v>-183812</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-3.0485333333333338</v>
+        <v>-3.0635333333333334</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45328,11 +45441,11 @@
       <c r="O13" s="215"/>
       <c r="P13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>203017</v>
+        <v>207343</v>
       </c>
       <c r="Q13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.13534466666666678</v>
+        <v>0.13822866666666678</v>
       </c>
       <c r="R13" s="159"/>
       <c r="S13" s="88">
@@ -45349,11 +45462,11 @@
       <c r="X13"/>
       <c r="Y13" s="154">
         <f t="shared" si="0"/>
-        <v>-1165182</v>
+        <v>-1160856</v>
       </c>
       <c r="Z13" s="168">
         <f t="shared" si="1"/>
-        <v>-0.77678799999999992</v>
+        <v>-0.77390399999999993</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45737,11 +45850,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>432986</v>
+        <v>397851</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.72164333333333341</v>
+        <v>0.66308500000000015</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -45757,11 +45870,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>237652</v>
+        <v>202517</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.6959766666666667</v>
+        <v>-2.7545349999999997</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45989,11 +46102,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>48682</v>
+        <v>32628</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.19472799999999996</v>
+        <v>0.13051199999999996</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -46009,11 +46122,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-218734</v>
+        <v>-234788</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.4794320000000001</v>
+        <v>-2.5436480000000001</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46070,11 +46183,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-80928</v>
+        <v>-98544</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.36785454545454543</v>
+        <v>-0.44792727272727267</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -46090,11 +46203,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-169828</v>
+        <v>-187444</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.2568545454545454</v>
+        <v>-1.3369272727272727</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46232,11 +46345,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>47499</v>
+        <v>55069</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.47499000000000002</v>
+        <v>0.55069000000000001</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -46252,11 +46365,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1762844</v>
+        <v>1770414</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.628439999999998</v>
+        <v>17.704139999999999</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46554,11 +46667,11 @@
       <c r="O28" s="215"/>
       <c r="P28" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-54338</v>
+        <v>-76659</v>
       </c>
       <c r="Q28" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.21735199999999999</v>
+        <v>-0.30663600000000002</v>
       </c>
       <c r="R28" s="159"/>
       <c r="S28" s="88">
@@ -46574,11 +46687,11 @@
       <c r="W28" s="72"/>
       <c r="Y28" s="154">
         <f t="shared" si="0"/>
-        <v>303875</v>
+        <v>281554</v>
       </c>
       <c r="Z28" s="168">
         <f t="shared" si="1"/>
-        <v>1.2155</v>
+        <v>1.1262159999999999</v>
       </c>
     </row>
     <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46635,11 +46748,11 @@
       <c r="O29" s="215"/>
       <c r="P29" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>280858</v>
+        <v>242206</v>
       </c>
       <c r="Q29" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.70214499999999991</v>
+        <v>0.60551499999999991</v>
       </c>
       <c r="R29" s="159"/>
       <c r="S29" s="88">
@@ -46656,11 +46769,11 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="154">
         <f t="shared" si="0"/>
-        <v>951321</v>
+        <v>912669</v>
       </c>
       <c r="Z29" s="168">
         <f t="shared" si="1"/>
-        <v>2.3783024999999998</v>
+        <v>2.2816725</v>
       </c>
     </row>
     <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46888,11 +47001,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-85385</v>
+        <v>-166530</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.56923333333333326</v>
+        <v>-1.1102000000000001</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -46909,11 +47022,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-590454</v>
+        <v>-671599</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-3.9363600000000005</v>
+        <v>-4.4773266666666673</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47051,11 +47164,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>193169</v>
+        <v>202910</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.7560818181818176</v>
+        <v>1.8446363636363632</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -47071,11 +47184,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-125771</v>
+        <v>-116030</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-1.1433727272727274</v>
+        <v>-1.0548181818181819</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -47220,11 +47333,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1094462</v>
+        <v>-913262</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4.7585304347826085</v>
+        <v>-3.9707043478260879</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -47240,11 +47353,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>3066641</v>
+        <v>3247841</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>13.333221739130435</v>
+        <v>14.121047826086956</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47299,11 +47412,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-14502</v>
+        <v>-12717</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.72509999999999986</v>
+        <v>-0.63584999999999992</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -47319,11 +47432,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-14502</v>
+        <v>-12717</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.72509999999999986</v>
+        <v>-0.63584999999999992</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47380,11 +47493,11 @@
       <c r="O38" s="215"/>
       <c r="P38" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-230252</v>
+        <v>-295252</v>
       </c>
       <c r="Q38" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.46050399999999997</v>
+        <v>-0.59050399999999992</v>
       </c>
       <c r="R38" s="159"/>
       <c r="S38" s="88">
@@ -47400,11 +47513,11 @@
       <c r="W38" s="72"/>
       <c r="Y38" s="154">
         <f t="shared" si="0"/>
-        <v>2836154</v>
+        <v>2771154</v>
       </c>
       <c r="Z38" s="168">
         <f t="shared" si="1"/>
-        <v>5.6723079999999992</v>
+        <v>5.5423079999999993</v>
       </c>
     </row>
     <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47461,11 +47574,11 @@
       <c r="O39" s="215"/>
       <c r="P39" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2235546</v>
+        <v>1791846</v>
       </c>
       <c r="Q39" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.2355460000000003</v>
+        <v>1.7918459999999998</v>
       </c>
       <c r="R39" s="159"/>
       <c r="S39" s="88">
@@ -47482,11 +47595,11 @@
       <c r="X39" s="132"/>
       <c r="Y39" s="154">
         <f t="shared" ref="Y39:Y74" si="22">M39+P39+S39+V39</f>
-        <v>5828952</v>
+        <v>5385252</v>
       </c>
       <c r="Z39" s="168">
         <f t="shared" ref="Z39:Z74" si="23">(N39+Q39+T39+W39)</f>
-        <v>5.828952000000001</v>
+        <v>5.3852520000000004</v>
       </c>
       <c r="AB39" s="131"/>
     </row>
@@ -47977,11 +48090,11 @@
       <c r="O45" s="215"/>
       <c r="P45" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>357863</v>
+        <v>324863</v>
       </c>
       <c r="Q45" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.71572599999999986</v>
+        <v>0.6497259999999998</v>
       </c>
       <c r="R45" s="159"/>
       <c r="S45" s="88">
@@ -47997,11 +48110,11 @@
       <c r="W45" s="72"/>
       <c r="Y45" s="154">
         <f t="shared" si="22"/>
-        <v>1575181</v>
+        <v>1542181</v>
       </c>
       <c r="Z45" s="168">
         <f t="shared" si="23"/>
-        <v>3.1503619999999994</v>
+        <v>3.0843619999999996</v>
       </c>
     </row>
     <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48058,11 +48171,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1092541</v>
+        <v>907647</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>2.185082</v>
+        <v>1.815294</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -48079,11 +48192,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>1044803</v>
+        <v>859909</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>2.0896059999999999</v>
+        <v>1.7198179999999998</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -48141,11 +48254,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-265460</v>
+        <v>-276885</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-5.3091999999999997</v>
+        <v>-5.5377000000000001</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -48161,11 +48274,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-148565</v>
+        <v>-159990</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-2.9712999999999998</v>
+        <v>-3.1998000000000002</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -48310,11 +48423,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>49764</v>
+        <v>43456</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.2441000000000002</v>
+        <v>1.0864</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -48330,11 +48443,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>37936</v>
+        <v>31628</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>0.94840000000000013</v>
+        <v>0.79069999999999996</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -48565,11 +48678,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>579373</v>
+        <v>547783</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.4484325</v>
+        <v>1.3694575000000002</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -48585,11 +48698,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>179074</v>
+        <v>147484</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.44768499999999989</v>
+        <v>0.36871000000000009</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48646,11 +48759,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>12353</v>
+        <v>42553</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.12352999999999992</v>
+        <v>0.42552999999999996</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -48666,11 +48779,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>758146</v>
+        <v>788346</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>7.5814600000000008</v>
+        <v>7.8834600000000012</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48808,11 +48921,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-79578</v>
+        <v>-26966</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.5915599999999999</v>
+        <v>-0.5393199999999998</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -48829,11 +48942,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-325356</v>
+        <v>-272744</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-6.5071200000000005</v>
+        <v>-5.4548800000000002</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -48891,11 +49004,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-138684</v>
+        <v>-183198</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.46228000000000002</v>
+        <v>-0.61065999999999998</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -48911,11 +49024,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4837659</v>
+        <v>-4882173</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.125530000000005</v>
+        <v>-16.273910000000004</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -49145,11 +49258,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>27950</v>
+        <v>20595</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.2384</v>
+        <v>9.1299999999999992E-2</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -49166,11 +49279,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>64673</v>
+        <v>57318</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.56723333333333326</v>
+        <v>0.4201333333333333</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -49234,11 +49347,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>424021</v>
+        <v>449421</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>4.2402099999999994</v>
+        <v>4.4942099999999998</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -49254,11 +49367,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>3974090</v>
+        <v>3999490</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>39.740899999999996</v>
+        <v>39.994900000000001</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -49320,11 +49433,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>3701</v>
+        <v>4235</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.37009999999999998</v>
+        <v>0.42349999999999999</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -49340,11 +49453,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>3701</v>
+        <v>4235</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.37009999999999998</v>
+        <v>0.42349999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49401,11 +49514,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>367458</v>
+        <v>155985</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.2248600000000001</v>
+        <v>0.51995000000000002</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -49421,11 +49534,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>1040307</v>
+        <v>828834</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>3.4676899999999997</v>
+        <v>2.7627799999999998</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -49489,11 +49602,11 @@
       <c r="O63" s="215"/>
       <c r="P63" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>289577</v>
+        <v>247073</v>
       </c>
       <c r="Q63" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.72394249999999993</v>
+        <v>0.61768250000000002</v>
       </c>
       <c r="R63" s="159"/>
       <c r="S63" s="88">
@@ -49509,11 +49622,11 @@
       <c r="W63" s="72"/>
       <c r="Y63" s="154">
         <f t="shared" si="22"/>
-        <v>964577</v>
+        <v>922073</v>
       </c>
       <c r="Z63" s="168">
         <f t="shared" si="23"/>
-        <v>2.4114424999999997</v>
+        <v>2.3051824999999999</v>
       </c>
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49814,11 +49927,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1688416</v>
+        <v>-1469416</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6885159999999999</v>
+        <v>-1.469516</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -49834,11 +49947,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1688416</v>
+        <v>-1469416</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.6885159999999999</v>
+        <v>-1.469516</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49952,11 +50065,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3725</v>
+        <v>373</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-7.44999999999999E-2</v>
+        <v>7.4600000000000222E-3</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -49972,11 +50085,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-50379</v>
+        <v>-46281</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-1.0075799999999999</v>
+        <v>-0.92562</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -50033,11 +50146,11 @@
       <c r="O70" s="215"/>
       <c r="P70" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>325731</v>
+        <v>362071</v>
       </c>
       <c r="Q70" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.3445140384615386</v>
+        <v>1.4004217307692308</v>
       </c>
       <c r="R70" s="159"/>
       <c r="S70" s="153">
@@ -50053,11 +50166,11 @@
       <c r="W70" s="150"/>
       <c r="Y70" s="154">
         <f t="shared" si="22"/>
-        <v>-82221</v>
+        <v>-45881</v>
       </c>
       <c r="Z70" s="168">
         <f t="shared" si="23"/>
-        <v>0.32463403846153849</v>
+        <v>0.3805417307692307</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
@@ -50276,11 +50389,11 @@
       <c r="O73" s="215"/>
       <c r="P73" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>529557</v>
+        <v>486723</v>
       </c>
       <c r="Q73" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.7651900000000003</v>
+        <v>1.6224100000000004</v>
       </c>
       <c r="R73" s="159"/>
       <c r="S73" s="88">
@@ -50296,11 +50409,11 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="154">
         <f t="shared" si="22"/>
-        <v>362175</v>
+        <v>319341</v>
       </c>
       <c r="Z73" s="168">
         <f t="shared" si="23"/>
-        <v>1.2072500000000002</v>
+        <v>1.0644700000000005</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
@@ -50515,11 +50628,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>498033</v>
+        <v>512183</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.99606600000000001</v>
+        <v>1.0243659999999999</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -50535,11 +50648,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>498033</v>
+        <v>512183</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>0.99606600000000001</v>
+        <v>1.0243659999999999</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -50572,7 +50685,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>5739364</v>
+        <v>4751570</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -50583,7 +50696,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>25686497</v>
+        <v>24712853</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -50879,11 +50992,11 @@
       <c r="O82" s="167"/>
       <c r="P82" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-29043</v>
+        <v>-130193</v>
       </c>
       <c r="Q82" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-9.6809999999999174E-2</v>
+        <v>-0.43397666666666623</v>
       </c>
       <c r="R82" s="159"/>
       <c r="S82" s="153">
@@ -50900,11 +51013,11 @@
       <c r="X82" s="132"/>
       <c r="Y82" s="52">
         <f t="shared" si="56"/>
-        <v>182457</v>
+        <v>81307</v>
       </c>
       <c r="Z82" s="53">
         <f t="shared" si="56"/>
-        <v>-9.6809999999999174E-2</v>
+        <v>-0.43397666666666623</v>
       </c>
       <c r="AA82" s="132"/>
     </row>
@@ -51014,7 +51127,7 @@
       <c r="O84" s="123"/>
       <c r="P84" s="112">
         <f>SUM(P80:P83)</f>
-        <v>1227108</v>
+        <v>1125958</v>
       </c>
       <c r="Q84" s="123"/>
       <c r="R84" s="123"/>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2661" uniqueCount="324">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2330,7 +2330,14 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="447">
+  <dxfs count="448">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5765,7 +5772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG66"/>
+  <dimension ref="A1:AI66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="133" customWidth="1" outlineLevel="1"/>
@@ -5777,20 +5784,20 @@
     <col min="7" max="7" width="1.7109375" style="133" customWidth="1"/>
     <col min="8" max="17" width="13.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="18" max="18" width="13.42578125" style="133" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="13.42578125" style="133" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" style="133" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="9.140625" style="133" collapsed="1"/>
-    <col min="24" max="28" width="9.140625" style="133"/>
-    <col min="29" max="29" width="14.140625" style="133" customWidth="1"/>
-    <col min="30" max="30" width="12" style="133" customWidth="1"/>
-    <col min="31" max="31" width="15.85546875" style="133" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="133"/>
+    <col min="19" max="21" width="13.42578125" style="133" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" style="133" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="10.7109375" style="133" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="9.140625" style="133" collapsed="1"/>
+    <col min="26" max="30" width="9.140625" style="133"/>
+    <col min="31" max="31" width="14.140625" style="133" customWidth="1"/>
+    <col min="32" max="32" width="12" style="133" customWidth="1"/>
+    <col min="33" max="33" width="15.85546875" style="133" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="133"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="221"/>
       <c r="H2" s="222">
         <v>46266</v>
@@ -5828,15 +5835,21 @@
       <c r="S2" s="256">
         <v>46282</v>
       </c>
-      <c r="T2" s="183"/>
-      <c r="U2" s="184" t="s">
+      <c r="T2" s="256">
+        <v>46283</v>
+      </c>
+      <c r="U2" s="256">
+        <v>46286</v>
+      </c>
+      <c r="V2" s="183"/>
+      <c r="W2" s="184" t="s">
         <v>281</v>
       </c>
-      <c r="V2" s="185" t="s">
+      <c r="X2" s="185" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="186" t="s">
         <v>54</v>
       </c>
@@ -5892,17 +5905,23 @@
       <c r="S3" s="179" t="s">
         <v>236</v>
       </c>
-      <c r="T3" s="180"/>
-      <c r="U3" s="189"/>
+      <c r="T3" s="179" t="s">
+        <v>235</v>
+      </c>
+      <c r="U3" s="179" t="s">
+        <v>234</v>
+      </c>
       <c r="V3" s="180"/>
-      <c r="AC3" s="133" t="s">
+      <c r="W3" s="189"/>
+      <c r="X3" s="180"/>
+      <c r="AE3" s="133" t="s">
         <v>198</v>
       </c>
-      <c r="AD3" s="133">
+      <c r="AF3" s="133">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
         <v>216</v>
       </c>
@@ -5958,23 +5977,29 @@
       <c r="S4" s="158">
         <v>-21850</v>
       </c>
-      <c r="T4" s="211"/>
-      <c r="U4" s="171">
-        <f t="shared" ref="U4:U30" si="0">SUM(H4:T4)</f>
-        <v>-62648</v>
-      </c>
-      <c r="V4" s="149">
-        <f t="shared" ref="V4:V30" si="1">IFERROR(U4/F4*100,0)/10000000</f>
-        <v>-1.2529600000000001</v>
-      </c>
-      <c r="AC4" s="133" t="s">
+      <c r="T4" s="158">
+        <v>-420855</v>
+      </c>
+      <c r="U4" s="158">
+        <v>34091</v>
+      </c>
+      <c r="V4" s="211"/>
+      <c r="W4" s="171">
+        <f t="shared" ref="W4:W30" si="0">SUM(H4:V4)</f>
+        <v>-449412</v>
+      </c>
+      <c r="X4" s="149">
+        <f t="shared" ref="X4:X30" si="1">IFERROR(W4/F4*100,0)/10000000</f>
+        <v>-8.9882399999999993</v>
+      </c>
+      <c r="AE4" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="AD4" s="133">
+      <c r="AF4" s="133">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="142" t="s">
         <v>30</v>
       </c>
@@ -6030,17 +6055,23 @@
       <c r="S5" s="147">
         <v>-92500</v>
       </c>
-      <c r="T5" s="174"/>
-      <c r="U5" s="171">
+      <c r="T5" s="147">
+        <v>144762</v>
+      </c>
+      <c r="U5" s="147">
+        <v>32233</v>
+      </c>
+      <c r="V5" s="174"/>
+      <c r="W5" s="171">
         <f t="shared" si="0"/>
-        <v>75784</v>
-      </c>
-      <c r="V5" s="149">
+        <v>252779</v>
+      </c>
+      <c r="X5" s="149">
         <f t="shared" si="1"/>
-        <v>0.2526133333333333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.84259666666666677</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="142" t="s">
         <v>177</v>
       </c>
@@ -6096,17 +6127,23 @@
       <c r="S6" s="147">
         <v>0</v>
       </c>
-      <c r="T6" s="174"/>
-      <c r="U6" s="171">
+      <c r="T6" s="147">
+        <v>0</v>
+      </c>
+      <c r="U6" s="147">
+        <v>0</v>
+      </c>
+      <c r="V6" s="174"/>
+      <c r="W6" s="171">
         <f t="shared" si="0"/>
         <v>-6830</v>
       </c>
-      <c r="V6" s="149">
+      <c r="X6" s="149">
         <f t="shared" si="1"/>
         <v>-6.83E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="142" t="s">
         <v>323</v>
       </c>
@@ -6162,17 +6199,23 @@
       <c r="S7" s="147">
         <v>-85900</v>
       </c>
-      <c r="T7" s="174"/>
-      <c r="U7" s="171">
+      <c r="T7" s="147">
+        <v>56700</v>
+      </c>
+      <c r="U7" s="147">
+        <v>-13800</v>
+      </c>
+      <c r="V7" s="174"/>
+      <c r="W7" s="171">
         <f t="shared" si="0"/>
-        <v>19647</v>
-      </c>
-      <c r="V7" s="149">
+        <v>62547</v>
+      </c>
+      <c r="X7" s="149">
         <f t="shared" si="1"/>
-        <v>0.19647000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.62546999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="142" t="s">
         <v>134</v>
       </c>
@@ -6228,21 +6271,27 @@
       <c r="S8" s="147">
         <v>-78630</v>
       </c>
-      <c r="T8" s="174"/>
-      <c r="U8" s="171">
+      <c r="T8" s="147">
+        <v>3450</v>
+      </c>
+      <c r="U8" s="147">
+        <v>81400</v>
+      </c>
+      <c r="V8" s="174"/>
+      <c r="W8" s="171">
         <f t="shared" si="0"/>
-        <v>-44396</v>
-      </c>
-      <c r="V8" s="149">
+        <v>40454</v>
+      </c>
+      <c r="X8" s="149">
         <f t="shared" si="1"/>
-        <v>-0.14798666666666666</v>
-      </c>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="134">
-        <v>-11170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.13484666666666664</v>
+      </c>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="134">
+        <v>-3557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="142" t="s">
         <v>217</v>
       </c>
@@ -6298,21 +6347,27 @@
       <c r="S9" s="147">
         <v>-31200</v>
       </c>
-      <c r="T9" s="174"/>
-      <c r="U9" s="171">
+      <c r="T9" s="147">
+        <v>-20828</v>
+      </c>
+      <c r="U9" s="147">
+        <v>32323</v>
+      </c>
+      <c r="V9" s="174"/>
+      <c r="W9" s="171">
         <f t="shared" si="0"/>
-        <v>18703</v>
-      </c>
-      <c r="V9" s="149">
+        <v>30198</v>
+      </c>
+      <c r="X9" s="149">
         <f t="shared" si="1"/>
-        <v>0.12468666666666665</v>
-      </c>
-      <c r="X9" s="134">
-        <v>97890</v>
-      </c>
-      <c r="Y9" s="134"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.20132</v>
+      </c>
+      <c r="Z9" s="134">
+        <v>106460</v>
+      </c>
+      <c r="AA9" s="134"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>313</v>
       </c>
@@ -6366,24 +6421,30 @@
       <c r="S10" s="147">
         <v>-900</v>
       </c>
-      <c r="T10" s="174"/>
-      <c r="U10" s="171">
+      <c r="T10" s="147">
+        <v>-18262</v>
+      </c>
+      <c r="U10" s="147">
+        <v>43007</v>
+      </c>
+      <c r="V10" s="174"/>
+      <c r="W10" s="171">
         <f t="shared" si="0"/>
-        <v>8437</v>
-      </c>
-      <c r="V10" s="149">
+        <v>33182</v>
+      </c>
+      <c r="X10" s="149">
         <f t="shared" si="1"/>
-        <v>0.14061666666666667</v>
-      </c>
-      <c r="X10" s="134">
-        <v>86719</v>
-      </c>
-      <c r="Y10" s="134">
-        <f>(X10+X9)/10000000*13780</f>
-        <v>254.39120199999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0.55303333333333338</v>
+      </c>
+      <c r="Z10" s="134">
+        <v>102901</v>
+      </c>
+      <c r="AA10" s="134">
+        <f>(Z10+Z9)/10000000*13780</f>
+        <v>288.499458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>35</v>
       </c>
@@ -6439,19 +6500,25 @@
       <c r="S11" s="147">
         <v>4326</v>
       </c>
-      <c r="T11" s="174"/>
-      <c r="U11" s="171">
+      <c r="T11" s="147">
+        <v>0</v>
+      </c>
+      <c r="U11" s="147">
+        <v>40700</v>
+      </c>
+      <c r="V11" s="174"/>
+      <c r="W11" s="171">
         <f t="shared" si="0"/>
-        <v>-759922</v>
-      </c>
-      <c r="V11" s="149">
+        <v>-719222</v>
+      </c>
+      <c r="X11" s="149">
         <f t="shared" si="1"/>
-        <v>-0.50661466666666666</v>
-      </c>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-0.47948133333333331</v>
+      </c>
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="143" t="s">
         <v>137</v>
       </c>
@@ -6507,19 +6574,25 @@
       <c r="S12" s="147">
         <v>-35135</v>
       </c>
-      <c r="T12" s="174"/>
-      <c r="U12" s="171">
+      <c r="T12" s="147">
+        <v>0</v>
+      </c>
+      <c r="U12" s="147">
+        <v>19322</v>
+      </c>
+      <c r="V12" s="174"/>
+      <c r="W12" s="171">
         <f t="shared" si="0"/>
-        <v>-9929</v>
-      </c>
-      <c r="V12" s="149">
+        <v>9393</v>
+      </c>
+      <c r="X12" s="149">
         <f t="shared" si="1"/>
-        <v>-1.6548333333333332E-2</v>
-      </c>
-      <c r="X12" s="134"/>
-      <c r="Y12" s="134"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+        <v>1.5654999999999999E-2</v>
+      </c>
+      <c r="Z12" s="134"/>
+      <c r="AA12" s="134"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="143" t="s">
         <v>42</v>
       </c>
@@ -6575,19 +6648,25 @@
       <c r="S13" s="147">
         <v>0</v>
       </c>
-      <c r="T13" s="174"/>
-      <c r="U13" s="171">
+      <c r="T13" s="147">
+        <v>3861</v>
+      </c>
+      <c r="U13" s="147">
+        <v>-1101</v>
+      </c>
+      <c r="V13" s="174"/>
+      <c r="W13" s="171">
         <f t="shared" si="0"/>
-        <v>-7797</v>
-      </c>
-      <c r="V13" s="149">
+        <v>-5037</v>
+      </c>
+      <c r="X13" s="149">
         <f t="shared" si="1"/>
-        <v>-7.7969999999999998E-2</v>
-      </c>
-      <c r="X13" s="134"/>
-      <c r="Y13" s="134"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-5.0369999999999998E-2</v>
+      </c>
+      <c r="Z13" s="134"/>
+      <c r="AA13" s="134"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="142" t="s">
         <v>212</v>
       </c>
@@ -6643,19 +6722,25 @@
       <c r="S14" s="147">
         <v>-16054</v>
       </c>
-      <c r="T14" s="174"/>
-      <c r="U14" s="171">
+      <c r="T14" s="147">
+        <v>10240</v>
+      </c>
+      <c r="U14" s="147">
+        <v>-6096</v>
+      </c>
+      <c r="V14" s="174"/>
+      <c r="W14" s="171">
         <f t="shared" si="0"/>
-        <v>-12292</v>
-      </c>
-      <c r="V14" s="149">
+        <v>-8148</v>
+      </c>
+      <c r="X14" s="149">
         <f t="shared" si="1"/>
-        <v>-4.9168000000000003E-2</v>
-      </c>
-      <c r="X14" s="134"/>
-      <c r="Y14" s="134"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+        <v>-3.2592000000000003E-2</v>
+      </c>
+      <c r="Z14" s="134"/>
+      <c r="AA14" s="134"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="142" t="s">
         <v>51</v>
       </c>
@@ -6711,29 +6796,35 @@
       <c r="S15" s="147">
         <v>-17616</v>
       </c>
-      <c r="T15" s="174"/>
-      <c r="U15" s="171">
+      <c r="T15" s="147">
+        <v>10247</v>
+      </c>
+      <c r="U15" s="147">
+        <v>-3845</v>
+      </c>
+      <c r="V15" s="174"/>
+      <c r="W15" s="171">
         <f t="shared" si="0"/>
-        <v>-10636</v>
-      </c>
-      <c r="V15" s="149">
+        <v>-4234</v>
+      </c>
+      <c r="X15" s="149">
         <f t="shared" si="1"/>
-        <v>-4.8345454545454539E-2</v>
-      </c>
-      <c r="X15" s="134"/>
-      <c r="Y15" s="193">
-        <f>Y8-Y10</f>
-        <v>-11424.391202000001</v>
-      </c>
-      <c r="AB15" s="133">
+        <v>-1.9245454545454545E-2</v>
+      </c>
+      <c r="Z15" s="134"/>
+      <c r="AA15" s="193">
+        <f>AA8-AA10</f>
+        <v>-3845.4994580000002</v>
+      </c>
+      <c r="AD15" s="133">
         <v>116185</v>
       </c>
-      <c r="AD15" s="133">
-        <f>AB15+Y15</f>
-        <v>104760.608798</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AF15" s="133">
+        <f>AD15+AA15</f>
+        <v>112339.50054199999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="142" t="s">
         <v>43</v>
       </c>
@@ -6789,17 +6880,23 @@
       <c r="S16" s="147">
         <v>7570</v>
       </c>
-      <c r="T16" s="174"/>
-      <c r="U16" s="171">
+      <c r="T16" s="147">
+        <v>21453</v>
+      </c>
+      <c r="U16" s="147">
+        <v>250</v>
+      </c>
+      <c r="V16" s="174"/>
+      <c r="W16" s="171">
         <f t="shared" si="0"/>
-        <v>-18338</v>
-      </c>
-      <c r="V16" s="149">
+        <v>3365</v>
+      </c>
+      <c r="X16" s="149">
         <f t="shared" si="1"/>
-        <v>-0.18337999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+        <v>3.3649999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="142" t="s">
         <v>24</v>
       </c>
@@ -6855,28 +6952,34 @@
       <c r="S17" s="147">
         <v>-22321</v>
       </c>
-      <c r="T17" s="174"/>
-      <c r="U17" s="171">
+      <c r="T17" s="147">
+        <v>0</v>
+      </c>
+      <c r="U17" s="147">
+        <v>0</v>
+      </c>
+      <c r="V17" s="174"/>
+      <c r="W17" s="171">
         <f t="shared" si="0"/>
         <v>-12742</v>
       </c>
-      <c r="V17" s="149">
+      <c r="X17" s="149">
         <f t="shared" si="1"/>
         <v>-5.0967999999999999E-2</v>
       </c>
-      <c r="AD17" s="133">
+      <c r="AF17" s="133">
         <v>4000000</v>
       </c>
-      <c r="AE17" s="133">
-        <f>AD17*7/100</f>
+      <c r="AG17" s="133">
+        <f>AF17*7/100</f>
         <v>280000</v>
       </c>
-      <c r="AG17" s="133">
+      <c r="AI17" s="133">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="142" t="s">
         <v>23</v>
       </c>
@@ -6932,21 +7035,27 @@
       <c r="S18" s="147">
         <v>-38652</v>
       </c>
-      <c r="T18" s="174"/>
-      <c r="U18" s="171">
+      <c r="T18" s="147">
+        <v>0</v>
+      </c>
+      <c r="U18" s="147">
+        <v>0</v>
+      </c>
+      <c r="V18" s="174"/>
+      <c r="W18" s="171">
         <f t="shared" si="0"/>
         <v>-25109</v>
       </c>
-      <c r="V18" s="149">
+      <c r="X18" s="149">
         <f t="shared" si="1"/>
         <v>-6.2772499999999995E-2</v>
       </c>
-      <c r="AE18" s="133">
-        <f>AE17/12</f>
+      <c r="AG18" s="133">
+        <f>AG17/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="142" t="s">
         <v>165</v>
       </c>
@@ -7002,17 +7111,23 @@
       <c r="S19" s="147">
         <v>-81145</v>
       </c>
-      <c r="T19" s="174"/>
-      <c r="U19" s="171">
+      <c r="T19" s="147">
+        <v>42700</v>
+      </c>
+      <c r="U19" s="147">
+        <v>-9354</v>
+      </c>
+      <c r="V19" s="174"/>
+      <c r="W19" s="171">
         <f t="shared" si="0"/>
-        <v>-281543</v>
-      </c>
-      <c r="V19" s="149">
+        <v>-248197</v>
+      </c>
+      <c r="X19" s="149">
         <f t="shared" si="1"/>
-        <v>-1.8769533333333335</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+        <v>-1.6546466666666666</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="142" t="s">
         <v>110</v>
       </c>
@@ -7068,20 +7183,26 @@
       <c r="S20" s="147">
         <v>0</v>
       </c>
-      <c r="T20" s="174"/>
-      <c r="U20" s="171">
+      <c r="T20" s="147">
+        <v>0</v>
+      </c>
+      <c r="U20" s="147">
+        <v>41261</v>
+      </c>
+      <c r="V20" s="174"/>
+      <c r="W20" s="171">
         <f t="shared" si="0"/>
-        <v>-74319</v>
-      </c>
-      <c r="V20" s="149">
+        <v>-33058</v>
+      </c>
+      <c r="X20" s="149">
         <f t="shared" si="1"/>
-        <v>-0.67562727272727263</v>
-      </c>
-      <c r="Z20" s="133">
+        <v>-0.3005272727272727</v>
+      </c>
+      <c r="AB20" s="133">
         <v>49000</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="142" t="s">
         <v>319</v>
       </c>
@@ -7137,20 +7258,26 @@
       <c r="S21" s="147">
         <v>-13500</v>
       </c>
-      <c r="T21" s="174"/>
-      <c r="U21" s="171">
+      <c r="T21" s="147">
+        <v>7233</v>
+      </c>
+      <c r="U21" s="147">
+        <v>18527</v>
+      </c>
+      <c r="V21" s="174"/>
+      <c r="W21" s="171">
         <f t="shared" si="0"/>
-        <v>-33003</v>
-      </c>
-      <c r="V21" s="149">
+        <v>-7243</v>
+      </c>
+      <c r="X21" s="149">
         <f t="shared" si="1"/>
-        <v>-1.32012</v>
-      </c>
-      <c r="Z21" s="133">
+        <v>-0.28971999999999998</v>
+      </c>
+      <c r="AB21" s="133">
         <v>30400</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="142" t="s">
         <v>316</v>
       </c>
@@ -7206,20 +7333,26 @@
       <c r="S22" s="147">
         <v>0</v>
       </c>
-      <c r="T22" s="174"/>
-      <c r="U22" s="171">
+      <c r="T22" s="147">
+        <v>-714</v>
+      </c>
+      <c r="U22" s="147">
+        <v>-6082</v>
+      </c>
+      <c r="V22" s="174"/>
+      <c r="W22" s="171">
         <f t="shared" si="0"/>
-        <v>1007</v>
-      </c>
-      <c r="V22" s="149">
+        <v>-5789</v>
+      </c>
+      <c r="X22" s="149">
         <f t="shared" si="1"/>
-        <v>5.0350000000000004E-3</v>
-      </c>
-      <c r="Z22" s="133">
+        <v>-2.8944999999999999E-2</v>
+      </c>
+      <c r="AB22" s="133">
         <v>2266</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="142" t="s">
         <v>317</v>
       </c>
@@ -7275,17 +7408,23 @@
       <c r="S23" s="147">
         <v>0</v>
       </c>
-      <c r="T23" s="174"/>
-      <c r="U23" s="171">
+      <c r="T23" s="147">
+        <v>0</v>
+      </c>
+      <c r="U23" s="147">
+        <v>144</v>
+      </c>
+      <c r="V23" s="174"/>
+      <c r="W23" s="171">
         <f t="shared" si="0"/>
-        <v>340</v>
-      </c>
-      <c r="V23" s="149">
+        <v>484</v>
+      </c>
+      <c r="X23" s="149">
         <f t="shared" si="1"/>
-        <v>1.3599999999999999E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+        <v>1.9359999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="142" t="s">
         <v>32</v>
       </c>
@@ -7341,17 +7480,23 @@
       <c r="S24" s="147">
         <v>9741</v>
       </c>
-      <c r="T24" s="174"/>
-      <c r="U24" s="171">
+      <c r="T24" s="147">
+        <v>0</v>
+      </c>
+      <c r="U24" s="147">
+        <v>13962</v>
+      </c>
+      <c r="V24" s="174"/>
+      <c r="W24" s="171">
         <f t="shared" si="0"/>
-        <v>-1794</v>
-      </c>
-      <c r="V24" s="149">
+        <v>12168</v>
+      </c>
+      <c r="X24" s="149">
         <f t="shared" si="1"/>
-        <v>-1.6309090909090908E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+        <v>0.11061818181818181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="142" t="s">
         <v>97</v>
       </c>
@@ -7407,17 +7552,23 @@
       <c r="S25" s="147">
         <v>181200</v>
       </c>
-      <c r="T25" s="174"/>
-      <c r="U25" s="171">
+      <c r="T25" s="147">
+        <v>184377</v>
+      </c>
+      <c r="U25" s="147">
+        <v>27500</v>
+      </c>
+      <c r="V25" s="174"/>
+      <c r="W25" s="171">
         <f t="shared" si="0"/>
-        <v>-1267323</v>
-      </c>
-      <c r="V25" s="149">
+        <v>-1055446</v>
+      </c>
+      <c r="X25" s="149">
         <f t="shared" si="1"/>
-        <v>-5.5101000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+        <v>-4.588895652173913</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="142" t="s">
         <v>302</v>
       </c>
@@ -7471,17 +7622,23 @@
       <c r="S26" s="147">
         <v>1785</v>
       </c>
-      <c r="T26" s="174"/>
-      <c r="U26" s="171">
+      <c r="T26" s="147">
+        <v>-3200</v>
+      </c>
+      <c r="U26" s="147">
+        <v>1623</v>
+      </c>
+      <c r="V26" s="174"/>
+      <c r="W26" s="171">
         <f t="shared" si="0"/>
-        <v>7579</v>
-      </c>
-      <c r="V26" s="149">
+        <v>6002</v>
+      </c>
+      <c r="X26" s="149">
         <f t="shared" si="1"/>
-        <v>0.37895000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+        <v>0.30009999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="142" t="s">
         <v>29</v>
       </c>
@@ -7537,17 +7694,23 @@
       <c r="S27" s="147">
         <v>-65000</v>
       </c>
-      <c r="T27" s="174"/>
-      <c r="U27" s="171">
+      <c r="T27" s="147">
+        <v>0</v>
+      </c>
+      <c r="U27" s="147">
+        <v>0</v>
+      </c>
+      <c r="V27" s="174"/>
+      <c r="W27" s="171">
         <f t="shared" si="0"/>
         <v>-30334</v>
       </c>
-      <c r="V27" s="149">
+      <c r="X27" s="149">
         <f t="shared" si="1"/>
         <v>-6.0668E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="142" t="s">
         <v>28</v>
       </c>
@@ -7603,17 +7766,23 @@
       <c r="S28" s="147">
         <v>-443700</v>
       </c>
-      <c r="T28" s="174"/>
-      <c r="U28" s="171">
+      <c r="T28" s="147">
+        <v>0</v>
+      </c>
+      <c r="U28" s="147">
+        <v>0</v>
+      </c>
+      <c r="V28" s="174"/>
+      <c r="W28" s="171">
         <f t="shared" si="0"/>
         <v>-1675566</v>
       </c>
-      <c r="V28" s="149">
+      <c r="X28" s="149">
         <f t="shared" si="1"/>
         <v>-1.6755660000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="142" t="s">
         <v>65</v>
       </c>
@@ -7669,17 +7838,23 @@
       <c r="S29" s="147">
         <v>-33000</v>
       </c>
-      <c r="T29" s="174"/>
-      <c r="U29" s="171">
+      <c r="T29" s="147">
+        <v>0</v>
+      </c>
+      <c r="U29" s="147">
+        <v>0</v>
+      </c>
+      <c r="V29" s="174"/>
+      <c r="W29" s="171">
         <f t="shared" si="0"/>
         <v>-374989</v>
       </c>
-      <c r="V29" s="149">
+      <c r="X29" s="149">
         <f t="shared" si="1"/>
         <v>-0.74997800000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>34</v>
       </c>
@@ -7735,17 +7910,23 @@
       <c r="S30" s="147">
         <v>-184894</v>
       </c>
-      <c r="T30" s="174"/>
-      <c r="U30" s="171">
+      <c r="T30" s="147">
+        <v>182425</v>
+      </c>
+      <c r="U30" s="147">
+        <v>42524</v>
+      </c>
+      <c r="V30" s="174"/>
+      <c r="W30" s="171">
         <f t="shared" si="0"/>
-        <v>-119760</v>
-      </c>
-      <c r="V30" s="149">
+        <v>105189</v>
+      </c>
+      <c r="X30" s="149">
         <f t="shared" si="1"/>
-        <v>-0.23952000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+        <v>0.21037800000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="141" t="s">
         <v>131</v>
       </c>
@@ -7801,17 +7982,23 @@
       <c r="S31" s="147">
         <v>-11425</v>
       </c>
-      <c r="T31" s="174"/>
-      <c r="U31" s="171">
-        <f t="shared" ref="U31:U56" si="2">SUM(H31:T31)</f>
-        <v>-197521</v>
-      </c>
-      <c r="V31" s="149">
-        <f t="shared" ref="V31:V56" si="3">IFERROR(U31/F31*100,0)/10000000</f>
-        <v>-3.9504199999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T31" s="147">
+        <v>22325</v>
+      </c>
+      <c r="U31" s="147">
+        <v>37021</v>
+      </c>
+      <c r="V31" s="174"/>
+      <c r="W31" s="171">
+        <f t="shared" ref="W31:W56" si="2">SUM(H31:V31)</f>
+        <v>-138175</v>
+      </c>
+      <c r="X31" s="149">
+        <f t="shared" ref="X31:X56" si="3">IFERROR(W31/F31*100,0)/10000000</f>
+        <v>-2.7635000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
         <v>67</v>
       </c>
@@ -7867,18 +8054,24 @@
       <c r="S32" s="147">
         <v>-6308</v>
       </c>
-      <c r="T32" s="174"/>
-      <c r="U32" s="171">
+      <c r="T32" s="147">
+        <v>14932</v>
+      </c>
+      <c r="U32" s="147">
+        <v>-4676</v>
+      </c>
+      <c r="V32" s="174"/>
+      <c r="W32" s="171">
         <f t="shared" si="2"/>
-        <v>108981</v>
-      </c>
-      <c r="V32" s="149">
+        <v>119237</v>
+      </c>
+      <c r="X32" s="149">
         <f t="shared" si="3"/>
-        <v>2.7245249999999999</v>
-      </c>
-      <c r="Y32" s="134"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+        <v>2.980925</v>
+      </c>
+      <c r="AA32" s="134"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>143</v>
       </c>
@@ -7934,21 +8127,27 @@
       <c r="S33" s="147">
         <v>0</v>
       </c>
-      <c r="T33" s="174"/>
-      <c r="U33" s="171">
+      <c r="T33" s="147">
+        <v>0</v>
+      </c>
+      <c r="U33" s="147">
+        <v>0</v>
+      </c>
+      <c r="V33" s="174"/>
+      <c r="W33" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V33" s="149">
+      <c r="X33" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="134">
-        <v>-23327</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="134">
+        <v>-5250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
         <v>144</v>
       </c>
@@ -8004,19 +8203,25 @@
       <c r="S34" s="147">
         <v>0</v>
       </c>
-      <c r="T34" s="174"/>
-      <c r="U34" s="171">
+      <c r="T34" s="147">
+        <v>0</v>
+      </c>
+      <c r="U34" s="147">
+        <v>0</v>
+      </c>
+      <c r="V34" s="174"/>
+      <c r="W34" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V34" s="149">
+      <c r="X34" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X34" s="5"/>
-      <c r="Y34" s="134"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="134"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="142" t="s">
         <v>31</v>
       </c>
@@ -8072,24 +8277,30 @@
       <c r="S35" s="147">
         <v>-31590</v>
       </c>
-      <c r="T35" s="174"/>
-      <c r="U35" s="171">
+      <c r="T35" s="147">
+        <v>6576</v>
+      </c>
+      <c r="U35" s="147">
+        <v>-3230</v>
+      </c>
+      <c r="V35" s="174"/>
+      <c r="W35" s="171">
         <f t="shared" si="2"/>
-        <v>-163153</v>
-      </c>
-      <c r="V35" s="149">
+        <v>-159807</v>
+      </c>
+      <c r="X35" s="149">
         <f t="shared" si="3"/>
-        <v>-0.40788249999999998</v>
-      </c>
-      <c r="X35" s="134">
-        <v>3334436</v>
-      </c>
-      <c r="Y35" s="134">
-        <f>(X36+X35)/10000000*13780</f>
-        <v>9554.3078800000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-0.39951750000000003</v>
+      </c>
+      <c r="Z35" s="134">
+        <v>39183</v>
+      </c>
+      <c r="AA35" s="134">
+        <f>(Z36+Z35)/10000000*13780</f>
+        <v>181.88910999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="142" t="s">
         <v>104</v>
       </c>
@@ -8145,21 +8356,27 @@
       <c r="S36" s="147">
         <v>30200</v>
       </c>
-      <c r="T36" s="174"/>
-      <c r="U36" s="171">
+      <c r="T36" s="147">
+        <v>80456</v>
+      </c>
+      <c r="U36" s="147">
+        <v>-1381</v>
+      </c>
+      <c r="V36" s="174"/>
+      <c r="W36" s="171">
         <f t="shared" si="2"/>
-        <v>-161079</v>
-      </c>
-      <c r="V36" s="149">
+        <v>-82004</v>
+      </c>
+      <c r="X36" s="149">
         <f t="shared" si="3"/>
-        <v>-1.6107899999999999</v>
-      </c>
-      <c r="X36" s="134">
-        <v>3599024</v>
-      </c>
-      <c r="Y36" s="134"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-0.82003999999999999</v>
+      </c>
+      <c r="Z36" s="134">
+        <v>92812</v>
+      </c>
+      <c r="AA36" s="134"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="142" t="s">
         <v>314</v>
       </c>
@@ -8213,22 +8430,28 @@
       <c r="S37" s="147">
         <v>0</v>
       </c>
-      <c r="T37" s="174"/>
-      <c r="U37" s="171">
+      <c r="T37" s="147">
+        <v>0</v>
+      </c>
+      <c r="U37" s="147">
+        <v>0</v>
+      </c>
+      <c r="V37" s="174"/>
+      <c r="W37" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V37" s="149">
+      <c r="X37" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X37" s="134"/>
-      <c r="Y37" s="134">
-        <f>+Y33-Y35</f>
-        <v>-32881.30788</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z37" s="134"/>
+      <c r="AA37" s="134">
+        <f>+AA33-AA35</f>
+        <v>-5431.8891100000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="142" t="s">
         <v>229</v>
       </c>
@@ -8284,19 +8507,25 @@
       <c r="S38" s="147">
         <v>52612</v>
       </c>
-      <c r="T38" s="174"/>
-      <c r="U38" s="171">
+      <c r="T38" s="147">
+        <v>-8156</v>
+      </c>
+      <c r="U38" s="147">
+        <v>19040</v>
+      </c>
+      <c r="V38" s="174"/>
+      <c r="W38" s="171">
         <f t="shared" si="2"/>
-        <v>39417</v>
-      </c>
-      <c r="V38" s="149">
+        <v>50301</v>
+      </c>
+      <c r="X38" s="149">
         <f t="shared" si="3"/>
-        <v>0.78834000000000004</v>
-      </c>
-      <c r="X38" s="134"/>
-      <c r="Y38" s="134"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+        <v>1.0060199999999999</v>
+      </c>
+      <c r="Z38" s="134"/>
+      <c r="AA38" s="134"/>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="142" t="s">
         <v>52</v>
       </c>
@@ -8352,19 +8581,25 @@
       <c r="S39" s="147">
         <v>0</v>
       </c>
-      <c r="T39" s="174"/>
-      <c r="U39" s="171">
+      <c r="T39" s="147">
+        <v>0</v>
+      </c>
+      <c r="U39" s="147">
+        <v>0</v>
+      </c>
+      <c r="V39" s="174"/>
+      <c r="W39" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V39" s="149">
+      <c r="X39" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X39" s="134"/>
-      <c r="Y39" s="134"/>
-    </row>
-    <row r="40" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z39" s="134"/>
+      <c r="AA39" s="134"/>
+    </row>
+    <row r="40" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="142" t="s">
         <v>45</v>
       </c>
@@ -8420,19 +8655,25 @@
       <c r="S40" s="147">
         <v>-44514</v>
       </c>
-      <c r="T40" s="174"/>
-      <c r="U40" s="171">
+      <c r="T40" s="147">
+        <v>79156</v>
+      </c>
+      <c r="U40" s="147">
+        <v>34906</v>
+      </c>
+      <c r="V40" s="174"/>
+      <c r="W40" s="171">
         <f t="shared" si="2"/>
-        <v>-72406</v>
-      </c>
-      <c r="V40" s="149">
+        <v>41656</v>
+      </c>
+      <c r="X40" s="149">
         <f t="shared" si="3"/>
-        <v>-0.24135333333333331</v>
-      </c>
-      <c r="X40" s="134"/>
-      <c r="Y40" s="134"/>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.13885333333333336</v>
+      </c>
+      <c r="Z40" s="134"/>
+      <c r="AA40" s="134"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>292</v>
       </c>
@@ -8486,18 +8727,24 @@
       <c r="S41" s="147">
         <v>0</v>
       </c>
-      <c r="T41" s="174"/>
-      <c r="U41" s="171">
+      <c r="T41" s="147">
+        <v>0</v>
+      </c>
+      <c r="U41" s="147">
+        <v>-5072</v>
+      </c>
+      <c r="V41" s="174"/>
+      <c r="W41" s="171">
         <f t="shared" si="2"/>
-        <v>-61529</v>
-      </c>
-      <c r="V41" s="149">
+        <v>-66601</v>
+      </c>
+      <c r="X41" s="149">
         <f t="shared" si="3"/>
-        <v>-6.1528999999999998</v>
-      </c>
-      <c r="X41" s="134"/>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-6.6600999999999999</v>
+      </c>
+      <c r="Z41" s="134"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>132</v>
       </c>
@@ -8553,17 +8800,23 @@
       <c r="S42" s="147">
         <v>-7355</v>
       </c>
-      <c r="T42" s="174"/>
-      <c r="U42" s="171">
+      <c r="T42" s="147">
+        <v>1034</v>
+      </c>
+      <c r="U42" s="147">
+        <v>-14906</v>
+      </c>
+      <c r="V42" s="174"/>
+      <c r="W42" s="171">
         <f t="shared" si="2"/>
-        <v>-13733</v>
-      </c>
-      <c r="V42" s="149">
+        <v>-27605</v>
+      </c>
+      <c r="X42" s="149">
         <f t="shared" si="3"/>
-        <v>-0.27466000000000002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-0.55210000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>48</v>
       </c>
@@ -8619,17 +8872,23 @@
       <c r="S43" s="147">
         <v>25400</v>
       </c>
-      <c r="T43" s="174"/>
-      <c r="U43" s="171">
+      <c r="T43" s="147">
+        <v>229212</v>
+      </c>
+      <c r="U43" s="147">
+        <v>-12181</v>
+      </c>
+      <c r="V43" s="174"/>
+      <c r="W43" s="171">
         <f t="shared" si="2"/>
-        <v>-437953</v>
-      </c>
-      <c r="V43" s="149">
+        <v>-220922</v>
+      </c>
+      <c r="X43" s="149">
         <f t="shared" si="3"/>
-        <v>-4.3795299999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+        <v>-2.2092200000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
         <v>301</v>
       </c>
@@ -8683,17 +8942,23 @@
       <c r="S44" s="147">
         <v>534</v>
       </c>
-      <c r="T44" s="174"/>
-      <c r="U44" s="171">
+      <c r="T44" s="147">
+        <v>2268</v>
+      </c>
+      <c r="U44" s="147">
+        <v>0</v>
+      </c>
+      <c r="V44" s="174"/>
+      <c r="W44" s="171">
         <f t="shared" si="2"/>
-        <v>7781</v>
-      </c>
-      <c r="V44" s="149">
+        <v>10049</v>
+      </c>
+      <c r="X44" s="149">
         <f t="shared" si="3"/>
-        <v>0.77810000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+        <v>1.0048999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="143" t="s">
         <v>168</v>
       </c>
@@ -8749,17 +9014,23 @@
       <c r="S45" s="147">
         <v>-42504</v>
       </c>
-      <c r="T45" s="174"/>
-      <c r="U45" s="171">
+      <c r="T45" s="147">
+        <v>0</v>
+      </c>
+      <c r="U45" s="147">
+        <v>0</v>
+      </c>
+      <c r="V45" s="174"/>
+      <c r="W45" s="171">
         <f t="shared" si="2"/>
         <v>-228129</v>
       </c>
-      <c r="V45" s="149">
+      <c r="X45" s="149">
         <f t="shared" si="3"/>
         <v>-0.57032249999999995</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="143" t="s">
         <v>202</v>
       </c>
@@ -8815,17 +9086,23 @@
       <c r="S46" s="147">
         <v>0</v>
       </c>
-      <c r="T46" s="174"/>
-      <c r="U46" s="171">
+      <c r="T46" s="147">
+        <v>0</v>
+      </c>
+      <c r="U46" s="147">
+        <v>0</v>
+      </c>
+      <c r="V46" s="174"/>
+      <c r="W46" s="171">
         <f t="shared" si="2"/>
         <v>-76805</v>
       </c>
-      <c r="V46" s="149">
+      <c r="X46" s="149">
         <f t="shared" si="3"/>
         <v>-0.1920125</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="143" t="s">
         <v>33</v>
       </c>
@@ -8881,17 +9158,23 @@
       <c r="S47" s="147">
         <v>-211473</v>
       </c>
-      <c r="T47" s="174"/>
-      <c r="U47" s="171">
+      <c r="T47" s="147">
+        <v>70842</v>
+      </c>
+      <c r="U47" s="147">
+        <v>26462</v>
+      </c>
+      <c r="V47" s="174"/>
+      <c r="W47" s="171">
         <f t="shared" si="2"/>
-        <v>164718</v>
-      </c>
-      <c r="V47" s="149">
+        <v>262022</v>
+      </c>
+      <c r="X47" s="149">
         <f t="shared" si="3"/>
-        <v>0.54905999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.87340666666666678</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>306</v>
       </c>
@@ -8945,17 +9228,23 @@
       <c r="S48" s="151">
         <v>219000</v>
       </c>
-      <c r="T48" s="174"/>
-      <c r="U48" s="171">
+      <c r="T48" s="151">
+        <v>571611</v>
+      </c>
+      <c r="U48" s="151">
+        <v>268100</v>
+      </c>
+      <c r="V48" s="174"/>
+      <c r="W48" s="171">
         <f t="shared" si="2"/>
-        <v>-434336</v>
-      </c>
-      <c r="V48" s="149">
+        <v>405375</v>
+      </c>
+      <c r="X48" s="149">
         <f t="shared" si="3"/>
-        <v>-0.434336</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.40537499999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>320</v>
       </c>
@@ -9007,17 +9296,23 @@
       <c r="S49" s="151">
         <v>0</v>
       </c>
-      <c r="T49" s="174"/>
-      <c r="U49" s="171">
+      <c r="T49" s="151">
+        <v>0</v>
+      </c>
+      <c r="U49" s="151">
+        <v>0</v>
+      </c>
+      <c r="V49" s="174"/>
+      <c r="W49" s="171">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V49" s="149">
+      <c r="X49" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>197</v>
       </c>
@@ -9073,17 +9368,23 @@
       <c r="S50" s="151">
         <v>4098</v>
       </c>
-      <c r="T50" s="174"/>
-      <c r="U50" s="171">
+      <c r="T50" s="151">
+        <v>0</v>
+      </c>
+      <c r="U50" s="151">
+        <v>-6096</v>
+      </c>
+      <c r="V50" s="174"/>
+      <c r="W50" s="171">
         <f t="shared" si="2"/>
-        <v>34668</v>
-      </c>
-      <c r="V50" s="149">
+        <v>28572</v>
+      </c>
+      <c r="X50" s="149">
         <f t="shared" si="3"/>
-        <v>0.69335999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.57143999999999995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>213</v>
       </c>
@@ -9139,17 +9440,23 @@
       <c r="S51" s="151">
         <v>36340</v>
       </c>
-      <c r="T51" s="174"/>
-      <c r="U51" s="171">
+      <c r="T51" s="151">
+        <v>0</v>
+      </c>
+      <c r="U51" s="151">
+        <v>0</v>
+      </c>
+      <c r="V51" s="174"/>
+      <c r="W51" s="171">
         <f t="shared" si="2"/>
         <v>-581873</v>
       </c>
-      <c r="V51" s="149">
+      <c r="X51" s="149">
         <f t="shared" si="3"/>
         <v>-0.89518923076923085</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>214</v>
       </c>
@@ -9205,17 +9512,23 @@
       <c r="S52" s="151">
         <v>0</v>
       </c>
-      <c r="T52" s="174"/>
-      <c r="U52" s="171">
+      <c r="T52" s="151">
+        <v>0</v>
+      </c>
+      <c r="U52" s="151">
+        <v>0</v>
+      </c>
+      <c r="V52" s="174"/>
+      <c r="W52" s="171">
         <f t="shared" si="2"/>
         <v>-158276</v>
       </c>
-      <c r="V52" s="149">
+      <c r="X52" s="149">
         <f t="shared" si="3"/>
         <v>-1.266208</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="s">
         <v>49</v>
       </c>
@@ -9271,17 +9584,23 @@
       <c r="S53" s="151">
         <v>-42834</v>
       </c>
-      <c r="T53" s="174"/>
-      <c r="U53" s="171">
+      <c r="T53" s="151">
+        <v>0</v>
+      </c>
+      <c r="U53" s="151">
+        <v>0</v>
+      </c>
+      <c r="V53" s="174"/>
+      <c r="W53" s="171">
         <f t="shared" si="2"/>
         <v>-217350</v>
       </c>
-      <c r="V53" s="149">
+      <c r="X53" s="149">
         <f t="shared" si="3"/>
         <v>-0.72450000000000003</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
         <v>300</v>
       </c>
@@ -9335,17 +9654,23 @@
       <c r="S54" s="151">
         <v>0</v>
       </c>
-      <c r="T54" s="174"/>
-      <c r="U54" s="171">
+      <c r="T54" s="151">
+        <v>0</v>
+      </c>
+      <c r="U54" s="151">
+        <v>0</v>
+      </c>
+      <c r="V54" s="174"/>
+      <c r="W54" s="171">
         <f t="shared" si="2"/>
         <v>11400</v>
       </c>
-      <c r="V54" s="149">
+      <c r="X54" s="149">
         <f t="shared" si="3"/>
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:28" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="59" t="s">
         <v>288</v>
       </c>
@@ -9399,17 +9724,23 @@
       <c r="S55" s="151">
         <v>14150</v>
       </c>
-      <c r="T55" s="174"/>
-      <c r="U55" s="171">
+      <c r="T55" s="151">
+        <v>51605</v>
+      </c>
+      <c r="U55" s="151">
+        <v>-5500</v>
+      </c>
+      <c r="V55" s="174"/>
+      <c r="W55" s="171">
         <f t="shared" si="2"/>
-        <v>22778</v>
-      </c>
-      <c r="V55" s="149">
+        <v>68883</v>
+      </c>
+      <c r="X55" s="149">
         <f t="shared" si="3"/>
-        <v>4.5556000000000006E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.137766</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -9418,7 +9749,7 @@
       <c r="F56" s="115"/>
       <c r="G56" s="16"/>
       <c r="H56" s="254">
-        <f t="shared" ref="H56:S56" si="4">SUM(H4:H55)</f>
+        <f t="shared" ref="H56:U56" si="4">SUM(H4:H55)</f>
         <v>-2124400</v>
       </c>
       <c r="I56" s="254">
@@ -9466,19 +9797,27 @@
         <v>-1073044</v>
       </c>
       <c r="T56" s="254">
-        <f>SUM(T4:T55)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1325450</v>
       </c>
       <c r="U56" s="254">
+        <f t="shared" si="4"/>
+        <v>721076</v>
+      </c>
+      <c r="V56" s="254">
+        <f>SUM(V4:V55)</f>
+        <v>0</v>
+      </c>
+      <c r="W56" s="254">
         <f t="shared" si="2"/>
-        <v>-7112173</v>
-      </c>
-      <c r="V56" s="255">
+        <v>-5065647</v>
+      </c>
+      <c r="X56" s="255">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:26" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:28" s="249" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="250"/>
       <c r="B57" s="250"/>
       <c r="C57" s="250"/>
@@ -9500,9 +9839,11 @@
       <c r="S57" s="250"/>
       <c r="T57" s="250"/>
       <c r="U57" s="250"/>
-      <c r="V57" s="252"/>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V57" s="250"/>
+      <c r="W57" s="250"/>
+      <c r="X57" s="252"/>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" s="202" t="s">
         <v>241</v>
       </c>
@@ -9558,18 +9899,24 @@
       <c r="S58" s="162">
         <v>-101150</v>
       </c>
-      <c r="T58" s="246"/>
-      <c r="U58" s="247">
-        <f>SUM(H58:T58)</f>
-        <v>-816703</v>
-      </c>
-      <c r="V58" s="248">
-        <f>IFERROR(U58/F58*100,0)/10000000</f>
-        <v>-2.7223433333333333</v>
-      </c>
-      <c r="Y58" s="134"/>
-    </row>
-    <row r="59" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T58" s="162">
+        <v>110</v>
+      </c>
+      <c r="U58" s="162">
+        <v>-4072</v>
+      </c>
+      <c r="V58" s="246"/>
+      <c r="W58" s="247">
+        <f>SUM(H58:V58)</f>
+        <v>-820665</v>
+      </c>
+      <c r="X58" s="248">
+        <f>IFERROR(W58/F58*100,0)/10000000</f>
+        <v>-2.7355499999999999</v>
+      </c>
+      <c r="AA58" s="134"/>
+    </row>
+    <row r="59" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="202" t="s">
         <v>273</v>
       </c>
@@ -9623,18 +9970,24 @@
       <c r="S59" s="162">
         <v>0</v>
       </c>
-      <c r="T59" s="174"/>
-      <c r="U59" s="171">
-        <f>SUM(H59:T59)</f>
+      <c r="T59" s="162">
+        <v>0</v>
+      </c>
+      <c r="U59" s="162">
+        <v>0</v>
+      </c>
+      <c r="V59" s="174"/>
+      <c r="W59" s="171">
+        <f>SUM(H59:V59)</f>
         <v>87266</v>
       </c>
-      <c r="V59" s="149">
-        <f>IFERROR(U59/F59*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="X59" s="134"/>
-    </row>
-    <row r="60" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X59" s="149">
+        <f>IFERROR(W59/F59*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="Z59" s="134"/>
+    </row>
+    <row r="60" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="200"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -9643,7 +9996,7 @@
       <c r="F60" s="74"/>
       <c r="G60" s="17"/>
       <c r="H60" s="170">
-        <f t="shared" ref="H60:S60" si="5">SUM(H58:H59)</f>
+        <f t="shared" ref="H60:U60" si="5">SUM(H58:H59)</f>
         <v>-616080</v>
       </c>
       <c r="I60" s="170">
@@ -9691,131 +10044,139 @@
         <v>-101150</v>
       </c>
       <c r="T60" s="170">
-        <f>SUM(T58:T59)</f>
-        <v>0</v>
-      </c>
-      <c r="U60" s="254">
-        <f>SUM(H60:T60)</f>
-        <v>-729437</v>
-      </c>
-      <c r="V60" s="19"/>
-      <c r="X60" s="5"/>
-      <c r="Y60" s="134"/>
-      <c r="Z60" s="237"/>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="X61" s="134"/>
-      <c r="Y61" s="134"/>
-      <c r="Z61" s="237"/>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="X62" s="134"/>
-      <c r="Y62" s="134"/>
-      <c r="Z62" s="237"/>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="X63" s="134"/>
-      <c r="Y63" s="134"/>
-      <c r="Z63" s="237"/>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="X64" s="134"/>
-      <c r="Y64" s="134"/>
-      <c r="Z64" s="237"/>
-    </row>
-    <row r="65" spans="24:26" x14ac:dyDescent="0.25">
-      <c r="X65" s="134"/>
-      <c r="Y65" s="237"/>
-      <c r="Z65" s="237"/>
-    </row>
-    <row r="66" spans="24:26" x14ac:dyDescent="0.25">
-      <c r="X66" s="237"/>
-      <c r="Y66" s="237"/>
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="U60" s="170">
+        <f t="shared" si="5"/>
+        <v>-4072</v>
+      </c>
+      <c r="V60" s="170">
+        <f>SUM(V58:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="254">
+        <f>SUM(H60:V60)</f>
+        <v>-733399</v>
+      </c>
+      <c r="X60" s="19"/>
+      <c r="Z60" s="5"/>
+      <c r="AA60" s="134"/>
+      <c r="AB60" s="237"/>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z61" s="134"/>
+      <c r="AA61" s="134"/>
+      <c r="AB61" s="237"/>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z62" s="134"/>
+      <c r="AA62" s="134"/>
+      <c r="AB62" s="237"/>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z63" s="134"/>
+      <c r="AA63" s="134"/>
+      <c r="AB63" s="237"/>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z64" s="134"/>
+      <c r="AA64" s="134"/>
+      <c r="AB64" s="237"/>
+    </row>
+    <row r="65" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z65" s="134"/>
+      <c r="AA65" s="237"/>
+      <c r="AB65" s="237"/>
+    </row>
+    <row r="66" spans="26:28" x14ac:dyDescent="0.25">
       <c r="Z66" s="237"/>
+      <c r="AA66" s="237"/>
+      <c r="AB66" s="237"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 V56:V57 U55:V55 V60 U43:V43 U5:V10 U24:V25 H2:V3 A58:V59 A37:U37 V11:V21 U11:U22 U45:V53 U27:U36 V27:V35 A4:T36 U38:U41 A38:T39 G40:T40 A41:T56 A60:T60">
-    <cfRule type="expression" dxfId="446" priority="21">
+  <conditionalFormatting sqref="G2 A3:G3 X56:X57 W55:X55 X60 W43:X43 W5:X10 W24:X25 H2:X3 A58:X59 A37:W37 X11:X21 W11:W22 W45:X53 W27:W36 X27:X35 A4:V36 W38:W41 A38:V39 G40:V40 A41:V56 A60:V60">
+    <cfRule type="expression" dxfId="447" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V36">
-    <cfRule type="expression" dxfId="445" priority="20">
+  <conditionalFormatting sqref="X36">
+    <cfRule type="expression" dxfId="446" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V39:V40">
-    <cfRule type="expression" dxfId="444" priority="19">
+  <conditionalFormatting sqref="X39:X40">
+    <cfRule type="expression" dxfId="445" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:V4">
-    <cfRule type="expression" dxfId="443" priority="18">
+  <conditionalFormatting sqref="W4:X4">
+    <cfRule type="expression" dxfId="444" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V38">
-    <cfRule type="expression" dxfId="442" priority="17">
+  <conditionalFormatting sqref="X38">
+    <cfRule type="expression" dxfId="443" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="441" priority="14">
+  <conditionalFormatting sqref="X22">
+    <cfRule type="expression" dxfId="442" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U56">
-    <cfRule type="expression" dxfId="440" priority="13">
+  <conditionalFormatting sqref="W56">
+    <cfRule type="expression" dxfId="441" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="439" priority="12">
+  <conditionalFormatting sqref="X41">
+    <cfRule type="expression" dxfId="440" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U26:V26">
-    <cfRule type="expression" dxfId="438" priority="11">
+  <conditionalFormatting sqref="W26:X26">
+    <cfRule type="expression" dxfId="439" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U54:V54">
-    <cfRule type="expression" dxfId="437" priority="10">
+  <conditionalFormatting sqref="W54:X54">
+    <cfRule type="expression" dxfId="438" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U44:V44">
-    <cfRule type="expression" dxfId="436" priority="9">
+  <conditionalFormatting sqref="W44:X44">
+    <cfRule type="expression" dxfId="437" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U60">
-    <cfRule type="expression" dxfId="435" priority="8">
+  <conditionalFormatting sqref="W60">
+    <cfRule type="expression" dxfId="436" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U42:V42">
-    <cfRule type="expression" dxfId="434" priority="6">
+  <conditionalFormatting sqref="W42:X42">
+    <cfRule type="expression" dxfId="435" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U23">
-    <cfRule type="expression" dxfId="433" priority="5">
+  <conditionalFormatting sqref="W23">
+    <cfRule type="expression" dxfId="434" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V23">
-    <cfRule type="expression" dxfId="432" priority="4">
+  <conditionalFormatting sqref="X23">
+    <cfRule type="expression" dxfId="433" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V37">
-    <cfRule type="expression" dxfId="431" priority="2">
+  <conditionalFormatting sqref="X37">
+    <cfRule type="expression" dxfId="432" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="430" priority="1">
+    <cfRule type="expression" dxfId="431" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16284,112 +16645,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="429" priority="22">
+    <cfRule type="expression" dxfId="430" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="428" priority="21">
+    <cfRule type="expression" dxfId="429" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="427" priority="20">
+    <cfRule type="expression" dxfId="428" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="426" priority="19">
+    <cfRule type="expression" dxfId="427" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="425" priority="18">
+    <cfRule type="expression" dxfId="426" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="424" priority="17">
+    <cfRule type="expression" dxfId="425" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="423" priority="16">
+    <cfRule type="expression" dxfId="424" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="422" priority="15">
+    <cfRule type="expression" dxfId="423" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="421" priority="14">
+    <cfRule type="expression" dxfId="422" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="420" priority="13">
+    <cfRule type="expression" dxfId="421" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="419" priority="12">
+    <cfRule type="expression" dxfId="420" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="418" priority="11">
+    <cfRule type="expression" dxfId="419" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="417" priority="10">
+    <cfRule type="expression" dxfId="418" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="416" priority="9">
+    <cfRule type="expression" dxfId="417" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="415" priority="8">
+    <cfRule type="expression" dxfId="416" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="414" priority="7">
+    <cfRule type="expression" dxfId="415" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="413" priority="6">
+    <cfRule type="expression" dxfId="414" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="412" priority="5">
+    <cfRule type="expression" dxfId="413" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="411" priority="4">
+    <cfRule type="expression" dxfId="412" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="410" priority="3">
+    <cfRule type="expression" dxfId="411" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="409" priority="2">
+    <cfRule type="expression" dxfId="410" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="408" priority="1">
+    <cfRule type="expression" dxfId="409" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22689,82 +23050,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="407" priority="20">
+    <cfRule type="expression" dxfId="408" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="406" priority="19">
+    <cfRule type="expression" dxfId="407" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="405" priority="18">
+    <cfRule type="expression" dxfId="406" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="404" priority="16">
+    <cfRule type="expression" dxfId="405" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="403" priority="14">
+    <cfRule type="expression" dxfId="404" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="402" priority="13">
+    <cfRule type="expression" dxfId="403" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="401" priority="12">
+    <cfRule type="expression" dxfId="402" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="400" priority="11">
+    <cfRule type="expression" dxfId="401" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="399" priority="10">
+    <cfRule type="expression" dxfId="400" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="398" priority="9">
+    <cfRule type="expression" dxfId="399" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="397" priority="6">
+    <cfRule type="expression" dxfId="398" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="396" priority="5">
+    <cfRule type="expression" dxfId="397" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="395" priority="4">
+    <cfRule type="expression" dxfId="396" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="394" priority="3">
+    <cfRule type="expression" dxfId="395" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="393" priority="2">
+    <cfRule type="expression" dxfId="394" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="392" priority="1">
+    <cfRule type="expression" dxfId="393" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22888,20 +23249,20 @@
         <v>-0.20805999999999999</v>
       </c>
       <c r="K4" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-62648</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-449412</v>
       </c>
       <c r="L4" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.2529600000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-8.9882399999999993</v>
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N62" si="0">G4+I4+K4</f>
-        <v>-89692</v>
+        <v>-476456</v>
       </c>
       <c r="N4" s="166">
         <f t="shared" si="0"/>
-        <v>-1.7938400000000001</v>
+        <v>-9.5291199999999989</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -22940,20 +23301,20 @@
         <v>-1.2725900000000001</v>
       </c>
       <c r="K5" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>75784</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>252779</v>
       </c>
       <c r="L5" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.2526133333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.84259666666666677</v>
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-175187</v>
+        <v>1808</v>
       </c>
       <c r="N5" s="166">
         <f t="shared" si="0"/>
-        <v>-0.58395666666666668</v>
+        <v>6.0266666666667357E-3</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -22992,11 +23353,11 @@
         <v>1.16185</v>
       </c>
       <c r="K6" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-6830</v>
       </c>
       <c r="L6" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-6.83E-2</v>
       </c>
       <c r="M6" s="71">
@@ -23044,20 +23405,20 @@
         <v>0</v>
       </c>
       <c r="K7" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>19647</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>62547</v>
       </c>
       <c r="L7" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.19647000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.62546999999999997</v>
       </c>
       <c r="M7" s="71">
         <f t="shared" si="1"/>
-        <v>-9343</v>
+        <v>33557</v>
       </c>
       <c r="N7" s="166">
         <f t="shared" si="2"/>
-        <v>0.19647000000000001</v>
+        <v>0.62546999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -23096,20 +23457,20 @@
         <v>-1.6494500000000001</v>
       </c>
       <c r="K8" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-44396</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>40454</v>
       </c>
       <c r="L8" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.14798666666666666</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.13484666666666664</v>
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>-499493</v>
+        <v>-414643</v>
       </c>
       <c r="N8" s="166">
         <f t="shared" si="0"/>
-        <v>-1.6649766666666668</v>
+        <v>-1.3821433333333335</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -23148,20 +23509,20 @@
         <v>0.16230666666666665</v>
       </c>
       <c r="K9" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>18703</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>30198</v>
       </c>
       <c r="L9" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.12468666666666665</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.20132</v>
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>-275433</v>
+        <v>-263938</v>
       </c>
       <c r="N9" s="166">
         <f t="shared" si="0"/>
-        <v>-1.8362200000000004</v>
+        <v>-1.7595866666666671</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -23200,20 +23561,20 @@
         <v>-1.1035999999999999</v>
       </c>
       <c r="K10" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>8437</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>33182</v>
       </c>
       <c r="L10" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.14061666666666667</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.55303333333333338</v>
       </c>
       <c r="M10" s="71">
         <f t="shared" ref="M10" si="3">G10+I10+K10</f>
-        <v>-183812</v>
+        <v>-159067</v>
       </c>
       <c r="N10" s="166">
         <f t="shared" ref="N10" si="4">H10+J10+L10</f>
-        <v>-3.0635333333333334</v>
+        <v>-2.6511166666666668</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -23252,20 +23613,20 @@
         <v>-0.91267399999999999</v>
       </c>
       <c r="K11" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-759922</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-719222</v>
       </c>
       <c r="L11" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.50661466666666666</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-0.47948133333333331</v>
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>207343</v>
+        <v>248043</v>
       </c>
       <c r="N11" s="166">
         <f t="shared" si="0"/>
-        <v>0.13822866666666678</v>
+        <v>0.16536200000000012</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -23304,20 +23665,20 @@
         <v>3.0566666666666667E-3</v>
       </c>
       <c r="K12" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-9929</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>9393</v>
       </c>
       <c r="L12" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.6548333333333332E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>1.5654999999999999E-2</v>
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>397851</v>
+        <v>417173</v>
       </c>
       <c r="N12" s="166">
         <f t="shared" si="0"/>
-        <v>0.66308500000000015</v>
+        <v>0.6952883333333334</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -23356,20 +23717,20 @@
         <v>0.12322</v>
       </c>
       <c r="K13" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-7797</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-5037</v>
       </c>
       <c r="L13" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-7.7969999999999998E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-5.0369999999999998E-2</v>
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>5619</v>
+        <v>8379</v>
       </c>
       <c r="N13" s="166">
         <f t="shared" si="0"/>
-        <v>5.6190000000000004E-2</v>
+        <v>8.3790000000000003E-2</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -23408,20 +23769,20 @@
         <v>-0.65036000000000005</v>
       </c>
       <c r="K14" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-12292</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-8148</v>
       </c>
       <c r="L14" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-4.9168000000000003E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-3.2592000000000003E-2</v>
       </c>
       <c r="M14" s="71">
         <f t="shared" si="0"/>
-        <v>32628</v>
+        <v>36772</v>
       </c>
       <c r="N14" s="166">
         <f t="shared" si="0"/>
-        <v>0.13051199999999996</v>
+        <v>0.14708799999999994</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -23460,11 +23821,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L15" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M15" s="71">
@@ -23512,20 +23873,20 @@
         <v>0.33139000000000002</v>
       </c>
       <c r="K16" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-18338</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>3365</v>
       </c>
       <c r="L16" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.18337999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>3.3649999999999999E-2</v>
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>55069</v>
+        <v>76772</v>
       </c>
       <c r="N16" s="166">
         <f t="shared" si="0"/>
-        <v>0.55069000000000001</v>
+        <v>0.76771999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -23564,20 +23925,20 @@
         <v>-0.4931636363636363</v>
       </c>
       <c r="K17" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-10636</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-4234</v>
       </c>
       <c r="L17" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-4.8345454545454539E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-1.9245454545454545E-2</v>
       </c>
       <c r="M17" s="71">
         <f t="shared" ref="M17" si="5">G17+I17+K17</f>
-        <v>-98544</v>
+        <v>-92142</v>
       </c>
       <c r="N17" s="166">
         <f t="shared" ref="N17" si="6">H17+J17+L17</f>
-        <v>-0.44792727272727267</v>
+        <v>-0.41882727272727271</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -23616,11 +23977,11 @@
         <v>-0.44636399999999998</v>
       </c>
       <c r="K18" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-12742</v>
       </c>
       <c r="L18" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-5.0967999999999999E-2</v>
       </c>
       <c r="M18" s="71">
@@ -23668,11 +24029,11 @@
         <v>-0.20675499999999999</v>
       </c>
       <c r="K19" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-25109</v>
       </c>
       <c r="L19" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-6.2772499999999995E-2</v>
       </c>
       <c r="M19" s="71">
@@ -23720,20 +24081,20 @@
         <v>0.25088181818181815</v>
       </c>
       <c r="K20" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-74319</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-33058</v>
       </c>
       <c r="L20" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.67562727272727263</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-0.3005272727272727</v>
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>13363</v>
+        <v>54624</v>
       </c>
       <c r="N20" s="166">
         <f t="shared" si="0"/>
-        <v>0.12148181818181814</v>
+        <v>0.49658181818181807</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -23772,20 +24133,20 @@
         <v>-2.8835999999999999</v>
       </c>
       <c r="K21" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-33003</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-7243</v>
       </c>
       <c r="L21" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.32012</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-0.28971999999999998</v>
       </c>
       <c r="M21" s="71">
         <f t="shared" ref="M21:M22" si="7">G21+I21+K21</f>
-        <v>-76549</v>
+        <v>-50789</v>
       </c>
       <c r="N21" s="166">
         <f t="shared" ref="N21:N22" si="8">H21+J21+L21</f>
-        <v>-3.06196</v>
+        <v>-2.0315599999999998</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -23824,20 +24185,20 @@
         <v>0.15673999999999999</v>
       </c>
       <c r="K22" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>1007</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-5789</v>
       </c>
       <c r="L22" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>5.0350000000000004E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-2.8944999999999999E-2</v>
       </c>
       <c r="M22" s="71">
         <f t="shared" si="7"/>
-        <v>17139</v>
+        <v>10343</v>
       </c>
       <c r="N22" s="166">
         <f t="shared" si="8"/>
-        <v>8.5694999999999993E-2</v>
+        <v>5.1714999999999997E-2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -23876,20 +24237,20 @@
         <v>9.7766666666666668E-2</v>
       </c>
       <c r="K23" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-281543</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-248197</v>
       </c>
       <c r="L23" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.8769533333333335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-1.6546466666666666</v>
       </c>
       <c r="M23" s="71">
         <f t="shared" si="0"/>
-        <v>-166530</v>
+        <v>-133184</v>
       </c>
       <c r="N23" s="166">
         <f t="shared" si="0"/>
-        <v>-1.1102000000000001</v>
+        <v>-0.8878933333333332</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -23928,11 +24289,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L24" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M24" s="71">
@@ -23980,20 +24341,20 @@
         <v>-1.1453363636363634</v>
       </c>
       <c r="K25" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1794</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>12168</v>
       </c>
       <c r="L25" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.6309090909090908E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.11061818181818181</v>
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>202910</v>
+        <v>216872</v>
       </c>
       <c r="N25" s="166">
         <f t="shared" si="0"/>
-        <v>1.8446363636363632</v>
+        <v>1.9715636363636357</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -24032,20 +24393,20 @@
         <v>-2.2903086956521741</v>
       </c>
       <c r="K26" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1267323</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-1055446</v>
       </c>
       <c r="L26" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-5.5101000000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-4.588895652173913</v>
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-913262</v>
+        <v>-701385</v>
       </c>
       <c r="N26" s="166">
         <f t="shared" si="0"/>
-        <v>-3.9707043478260879</v>
+        <v>-3.0495000000000005</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -24082,20 +24443,20 @@
         <v>-0.8901</v>
       </c>
       <c r="K27" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>7579</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>6002</v>
       </c>
       <c r="L27" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.37895000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.30009999999999998</v>
       </c>
       <c r="M27" s="71">
         <f t="shared" ref="M27" si="9">G27+I27+K27</f>
-        <v>-12717</v>
+        <v>-14294</v>
       </c>
       <c r="N27" s="166">
         <f t="shared" ref="N27" si="10">H27+J27+L27</f>
-        <v>-0.63584999999999992</v>
+        <v>-0.71469999999999989</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -24134,11 +24495,11 @@
         <v>-0.33289600000000003</v>
       </c>
       <c r="K28" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-30334</v>
       </c>
       <c r="L28" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-6.0668E-2</v>
       </c>
       <c r="M28" s="71">
@@ -24186,11 +24547,11 @@
         <v>0.19531499999999999</v>
       </c>
       <c r="K29" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-1675566</v>
       </c>
       <c r="L29" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-1.6755660000000001</v>
       </c>
       <c r="M29" s="71">
@@ -24239,11 +24600,11 @@
         <v>-0.60594000000000003</v>
       </c>
       <c r="K30" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L30" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M30" s="71">
@@ -24291,11 +24652,11 @@
         <v>-0.58230000000000004</v>
       </c>
       <c r="K31" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L31" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M31" s="71">
@@ -24343,11 +24704,11 @@
         <v>-0.58148999999999995</v>
       </c>
       <c r="K32" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L32" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M32" s="71">
@@ -24395,11 +24756,11 @@
         <v>-0.69791999999999998</v>
       </c>
       <c r="K33" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L33" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M33" s="71">
@@ -24447,11 +24808,11 @@
         <v>-0.58009333333333335</v>
       </c>
       <c r="K34" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L34" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M34" s="71">
@@ -24499,11 +24860,11 @@
         <v>-1.010926</v>
       </c>
       <c r="K35" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-374989</v>
       </c>
       <c r="L35" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-0.74997800000000003</v>
       </c>
       <c r="M35" s="71">
@@ -24551,20 +24912,20 @@
         <v>1.1398239999999999</v>
       </c>
       <c r="K36" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-119760</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>105189</v>
       </c>
       <c r="L36" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.23952000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.21037800000000001</v>
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>907647</v>
+        <v>1132596</v>
       </c>
       <c r="N36" s="166">
         <f t="shared" si="0"/>
-        <v>1.815294</v>
+        <v>2.2651919999999999</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -24603,20 +24964,20 @@
         <v>-1.28678</v>
       </c>
       <c r="K37" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-197521</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-138175</v>
       </c>
       <c r="L37" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-3.9504199999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-2.7635000000000001</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>-276885</v>
+        <v>-217539</v>
       </c>
       <c r="N37" s="166">
         <f t="shared" si="0"/>
-        <v>-5.5377000000000001</v>
+        <v>-4.3507800000000003</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -24655,20 +25016,20 @@
         <v>1.3305</v>
       </c>
       <c r="K38" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>108981</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>119237</v>
       </c>
       <c r="L38" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>2.7245249999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>2.980925</v>
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>43456</v>
+        <v>53712</v>
       </c>
       <c r="N38" s="166">
         <f t="shared" si="0"/>
-        <v>1.0864</v>
+        <v>1.3428000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -24707,11 +25068,11 @@
         <v>0.12665999999999999</v>
       </c>
       <c r="K39" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L39" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M39" s="71">
@@ -24759,11 +25120,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L40" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M40" s="71">
@@ -24811,20 +25172,20 @@
         <v>0.8756275</v>
       </c>
       <c r="K41" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-163153</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-159807</v>
       </c>
       <c r="L41" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.40788249999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-0.39951750000000003</v>
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>547783</v>
+        <v>551129</v>
       </c>
       <c r="N41" s="166">
         <f t="shared" si="0"/>
-        <v>1.3694575000000002</v>
+        <v>1.3778225000000002</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -24863,20 +25224,20 @@
         <v>0.53249000000000002</v>
       </c>
       <c r="K42" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-161079</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-82004</v>
       </c>
       <c r="L42" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-1.6107899999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-0.82003999999999999</v>
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>42553</v>
+        <v>121628</v>
       </c>
       <c r="N42" s="166">
         <f t="shared" si="0"/>
-        <v>0.42552999999999996</v>
+        <v>1.2162799999999998</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -24913,11 +25274,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L43" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M43" s="71">
@@ -24965,20 +25326,20 @@
         <v>-0.28554000000000002</v>
       </c>
       <c r="K44" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>39417</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>50301</v>
       </c>
       <c r="L44" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.78834000000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>1.0060199999999999</v>
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>-26966</v>
+        <v>-16082</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" si="0"/>
-        <v>-0.5393199999999998</v>
+        <v>-0.32163999999999993</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -25017,20 +25378,20 @@
         <v>-0.63329999999999997</v>
       </c>
       <c r="K45" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-72406</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>41656</v>
       </c>
       <c r="L45" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.24135333333333331</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.13885333333333336</v>
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>-183198</v>
+        <v>-69136</v>
       </c>
       <c r="N45" s="166">
         <f t="shared" si="0"/>
-        <v>-0.61065999999999998</v>
+        <v>-0.23045333333333332</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -25069,11 +25430,11 @@
         <v>-0.34641333333333335</v>
       </c>
       <c r="K46" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L46" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M46" s="71">
@@ -25121,11 +25482,11 @@
         <v>-0.37293333333333334</v>
       </c>
       <c r="K47" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L47" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M47" s="71">
@@ -25171,20 +25532,20 @@
         <v>-0.49170000000000003</v>
       </c>
       <c r="K48" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-61529</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-66601</v>
       </c>
       <c r="L48" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-6.1528999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-6.6600999999999999</v>
       </c>
       <c r="M48" s="71">
         <f t="shared" ref="M48" si="15">G48+I48+K48</f>
-        <v>-78461</v>
+        <v>-83533</v>
       </c>
       <c r="N48" s="166">
         <f t="shared" ref="N48" si="16">H48+J48+L48</f>
-        <v>-7.8460999999999999</v>
+        <v>-8.3533000000000008</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -25223,20 +25584,20 @@
         <v>4.5359999999999998E-2</v>
       </c>
       <c r="K49" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-13733</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-27605</v>
       </c>
       <c r="L49" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.27466000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-0.55210000000000004</v>
       </c>
       <c r="M49" s="71">
         <f t="shared" si="0"/>
-        <v>20595</v>
+        <v>6723</v>
       </c>
       <c r="N49" s="166">
         <f t="shared" si="0"/>
-        <v>9.1299999999999992E-2</v>
+        <v>-0.18614000000000003</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -25275,20 +25636,20 @@
         <v>7.0315700000000003</v>
       </c>
       <c r="K50" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-437953</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-220922</v>
       </c>
       <c r="L50" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-4.3795299999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-2.2092200000000002</v>
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>449421</v>
+        <v>666452</v>
       </c>
       <c r="N50" s="166">
         <f t="shared" si="0"/>
-        <v>4.4942099999999998</v>
+        <v>6.6645199999999996</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -25325,20 +25686,20 @@
         <v>9.1899999999999996E-2</v>
       </c>
       <c r="K51" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>7781</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>10049</v>
       </c>
       <c r="L51" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.77810000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>1.0048999999999999</v>
       </c>
       <c r="M51" s="71">
         <f t="shared" ref="M51" si="17">G51+I51+K51</f>
-        <v>4235</v>
+        <v>6503</v>
       </c>
       <c r="N51" s="166">
         <f t="shared" ref="N51" si="18">H51+J51+L51</f>
-        <v>0.42349999999999999</v>
+        <v>0.65029999999999988</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -25377,20 +25738,20 @@
         <v>-1.2057033333333331</v>
       </c>
       <c r="K52" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>164718</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>262022</v>
       </c>
       <c r="L52" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.54905999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.87340666666666678</v>
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>155985</v>
+        <v>253289</v>
       </c>
       <c r="N52" s="166">
         <f t="shared" si="0"/>
-        <v>0.51995000000000002</v>
+        <v>0.84429666666666681</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -25423,11 +25784,11 @@
         <v>-9.0149999999999994E-2</v>
       </c>
       <c r="K53" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="71">
@@ -25475,11 +25836,11 @@
         <v>0.15198</v>
       </c>
       <c r="K54" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-228129</v>
       </c>
       <c r="L54" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-0.57032249999999995</v>
       </c>
       <c r="M54" s="71">
@@ -25527,11 +25888,11 @@
         <v>-0.25410250000000001</v>
       </c>
       <c r="K55" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-76805</v>
       </c>
       <c r="L55" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-0.1920125</v>
       </c>
       <c r="M55" s="71">
@@ -25577,20 +25938,20 @@
         <v>-1.03518</v>
       </c>
       <c r="K56" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-434336</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>405375</v>
       </c>
       <c r="L56" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-0.434336</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.40537499999999999</v>
       </c>
       <c r="M56" s="71">
         <f t="shared" ref="M56" si="21">G56+I56+K56</f>
-        <v>-1469416</v>
+        <v>-629705</v>
       </c>
       <c r="N56" s="166">
         <f t="shared" ref="N56" si="22">H56+J56+L56</f>
-        <v>-1.469516</v>
+        <v>-0.62980499999999995</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -25623,11 +25984,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L57" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M57" s="71">
@@ -25675,20 +26036,20 @@
         <v>-0.14384</v>
       </c>
       <c r="K58" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>34668</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>28572</v>
       </c>
       <c r="L58" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>0.69335999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.57143999999999995</v>
       </c>
       <c r="M58" s="71">
         <f t="shared" si="0"/>
-        <v>373</v>
+        <v>-5723</v>
       </c>
       <c r="N58" s="166">
         <f t="shared" si="0"/>
-        <v>7.4600000000000222E-3</v>
+        <v>-0.11446000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -25727,11 +26088,11 @@
         <v>0.10279846153846153</v>
       </c>
       <c r="K59" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-581873</v>
       </c>
       <c r="L59" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-0.89518923076923085</v>
       </c>
       <c r="M59" s="71">
@@ -25779,11 +26140,11 @@
         <v>-0.20608799999999999</v>
       </c>
       <c r="K60" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-158276</v>
       </c>
       <c r="L60" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-1.266208</v>
       </c>
       <c r="M60" s="71">
@@ -25831,11 +26192,11 @@
         <v>-0.86802666666666684</v>
       </c>
       <c r="K61" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-217350</v>
       </c>
       <c r="L61" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>-0.72450000000000003</v>
       </c>
       <c r="M61" s="71">
@@ -25883,11 +26244,11 @@
         <v>-0.31176799999999999</v>
       </c>
       <c r="K62" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="L62" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M62" s="71">
@@ -25933,11 +26294,11 @@
         <v>0.55113999999999996</v>
       </c>
       <c r="K63" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>11400</v>
       </c>
       <c r="L63" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="M63" s="71">
@@ -25983,20 +26344,20 @@
         <v>0.43251600000000001</v>
       </c>
       <c r="K64" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>22778</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>68883</v>
       </c>
       <c r="L64" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>4.5556000000000006E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>0.137766</v>
       </c>
       <c r="M64" s="71">
         <f t="shared" ref="M64" si="27">G64+I64+K64</f>
-        <v>512183</v>
+        <v>558288</v>
       </c>
       <c r="N64" s="166">
         <f t="shared" ref="N64" si="28">H64+J64+L64</f>
-        <v>1.0243659999999999</v>
+        <v>1.116576</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -26018,12 +26379,12 @@
       <c r="J65" s="100"/>
       <c r="K65" s="109">
         <f>SUM(K4:K62)</f>
-        <v>-7146691</v>
+        <v>-5146414</v>
       </c>
       <c r="L65" s="109"/>
       <c r="M65" s="154">
         <f>SUM(M4:M62)</f>
-        <v>4604356</v>
+        <v>6604633</v>
       </c>
       <c r="N65" s="235"/>
     </row>
@@ -26103,20 +26464,20 @@
         <v>0.2384333333333333</v>
       </c>
       <c r="K69" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-816703</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-820665</v>
       </c>
       <c r="L69" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
-        <v>-2.7223433333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
+        <v>-2.7355499999999999</v>
       </c>
       <c r="M69" s="153">
         <f t="shared" ref="M69:N69" si="29">G69+I69+K69</f>
-        <v>-130193</v>
+        <v>-134155</v>
       </c>
       <c r="N69" s="167">
         <f t="shared" si="29"/>
-        <v>-0.43397666666666623</v>
+        <v>-0.44718333333333282</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -26153,11 +26514,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="153">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>87266</v>
       </c>
       <c r="L70" s="155">
-        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADW$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$ADY$124,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$DZ$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="153">
@@ -26182,508 +26543,508 @@
       <c r="J71" s="104"/>
       <c r="K71" s="93">
         <f>SUM(K69:K70)</f>
-        <v>-729437</v>
+        <v>-733399</v>
       </c>
       <c r="L71" s="113"/>
       <c r="M71" s="93">
         <f>SUM(M69:M70)</f>
-        <v>1125958</v>
+        <v>1121996</v>
       </c>
       <c r="N71" s="236"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
-    <cfRule type="expression" dxfId="391" priority="229">
+    <cfRule type="expression" dxfId="392" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="390" priority="228">
+    <cfRule type="expression" dxfId="391" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="389" priority="227">
+    <cfRule type="expression" dxfId="390" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="388" priority="226">
+    <cfRule type="expression" dxfId="389" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="387" priority="222">
+    <cfRule type="expression" dxfId="388" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="386" priority="220">
+    <cfRule type="expression" dxfId="387" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="385" priority="218">
+    <cfRule type="expression" dxfId="386" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="384" priority="212">
+    <cfRule type="expression" dxfId="385" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="383" priority="202">
+    <cfRule type="expression" dxfId="384" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="382" priority="207">
+    <cfRule type="expression" dxfId="383" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="381" priority="203">
+    <cfRule type="expression" dxfId="382" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="380" priority="188">
+    <cfRule type="expression" dxfId="381" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="379" priority="183">
+    <cfRule type="expression" dxfId="380" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="378" priority="189">
+    <cfRule type="expression" dxfId="379" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="377" priority="174">
+    <cfRule type="expression" dxfId="378" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="376" priority="172">
+    <cfRule type="expression" dxfId="377" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="375" priority="171">
+    <cfRule type="expression" dxfId="376" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="374" priority="166">
+    <cfRule type="expression" dxfId="375" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="373" priority="162">
+    <cfRule type="expression" dxfId="374" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="372" priority="163">
+    <cfRule type="expression" dxfId="373" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="371" priority="157">
+    <cfRule type="expression" dxfId="372" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="370" priority="143">
+    <cfRule type="expression" dxfId="371" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="369" priority="142">
+    <cfRule type="expression" dxfId="370" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="368" priority="132">
+    <cfRule type="expression" dxfId="369" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="367" priority="126">
+    <cfRule type="expression" dxfId="368" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="366" priority="125">
+    <cfRule type="expression" dxfId="367" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="365" priority="124">
+    <cfRule type="expression" dxfId="366" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="364" priority="123">
+    <cfRule type="expression" dxfId="365" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="363" priority="122">
+    <cfRule type="expression" dxfId="364" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="362" priority="121">
+    <cfRule type="expression" dxfId="363" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="361" priority="120">
+    <cfRule type="expression" dxfId="362" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="360" priority="109">
+    <cfRule type="expression" dxfId="361" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="359" priority="105">
+    <cfRule type="expression" dxfId="360" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="358" priority="104">
+    <cfRule type="expression" dxfId="359" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="357" priority="101">
+    <cfRule type="expression" dxfId="358" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="356" priority="97">
+    <cfRule type="expression" dxfId="357" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="355" priority="92">
+    <cfRule type="expression" dxfId="356" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="354" priority="91">
+    <cfRule type="expression" dxfId="355" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="353" priority="88">
+    <cfRule type="expression" dxfId="354" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="352" priority="89">
+    <cfRule type="expression" dxfId="353" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="351" priority="83">
+    <cfRule type="expression" dxfId="352" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="350" priority="82">
+    <cfRule type="expression" dxfId="351" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="349" priority="74">
+    <cfRule type="expression" dxfId="350" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="348" priority="73">
+    <cfRule type="expression" dxfId="349" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="347" priority="70">
+    <cfRule type="expression" dxfId="348" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="346" priority="71">
+    <cfRule type="expression" dxfId="347" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="345" priority="63">
+    <cfRule type="expression" dxfId="346" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="344" priority="62">
+    <cfRule type="expression" dxfId="345" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="343" priority="61">
+    <cfRule type="expression" dxfId="344" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="342" priority="60">
+    <cfRule type="expression" dxfId="343" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="341" priority="59">
+    <cfRule type="expression" dxfId="342" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="340" priority="58">
+    <cfRule type="expression" dxfId="341" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="339" priority="47">
+    <cfRule type="expression" dxfId="340" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="338" priority="57">
+    <cfRule type="expression" dxfId="339" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="337" priority="56">
+    <cfRule type="expression" dxfId="338" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="336" priority="55">
+    <cfRule type="expression" dxfId="337" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="335" priority="54">
+    <cfRule type="expression" dxfId="336" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="334" priority="53">
+    <cfRule type="expression" dxfId="335" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="333" priority="52">
+    <cfRule type="expression" dxfId="334" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="332" priority="51">
+    <cfRule type="expression" dxfId="333" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="331" priority="50">
+    <cfRule type="expression" dxfId="332" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="330" priority="48">
+    <cfRule type="expression" dxfId="331" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="329" priority="46">
+    <cfRule type="expression" dxfId="330" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="328" priority="45">
+    <cfRule type="expression" dxfId="329" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="327" priority="42">
+    <cfRule type="expression" dxfId="328" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="326" priority="41">
+    <cfRule type="expression" dxfId="327" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="325" priority="34">
+    <cfRule type="expression" dxfId="326" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 M64:N64">
-    <cfRule type="expression" dxfId="324" priority="33">
+    <cfRule type="expression" dxfId="325" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="323" priority="32">
+    <cfRule type="expression" dxfId="324" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="322" priority="31">
+    <cfRule type="expression" dxfId="323" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="321" priority="30">
+    <cfRule type="expression" dxfId="322" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="320" priority="29">
+    <cfRule type="expression" dxfId="321" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="319" priority="28">
+    <cfRule type="expression" dxfId="320" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="318" priority="27">
+    <cfRule type="expression" dxfId="319" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="317" priority="26">
+    <cfRule type="expression" dxfId="318" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="316" priority="25">
+    <cfRule type="expression" dxfId="317" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="315" priority="24">
+    <cfRule type="expression" dxfId="316" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="314" priority="20">
+    <cfRule type="expression" dxfId="315" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="313" priority="23">
+    <cfRule type="expression" dxfId="314" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="312" priority="22">
+    <cfRule type="expression" dxfId="313" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="311" priority="21">
+    <cfRule type="expression" dxfId="312" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="310" priority="19">
+    <cfRule type="expression" dxfId="311" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="309" priority="17">
+    <cfRule type="expression" dxfId="310" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="308" priority="16">
+    <cfRule type="expression" dxfId="309" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="307" priority="15">
+    <cfRule type="expression" dxfId="308" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="306" priority="14">
+    <cfRule type="expression" dxfId="307" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="305" priority="13">
+    <cfRule type="expression" dxfId="306" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="304" priority="12">
+    <cfRule type="expression" dxfId="305" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="303" priority="11">
+    <cfRule type="expression" dxfId="304" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="302" priority="10">
+    <cfRule type="expression" dxfId="303" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="301" priority="9">
+    <cfRule type="expression" dxfId="302" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="300" priority="8">
+    <cfRule type="expression" dxfId="301" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="299" priority="7">
+    <cfRule type="expression" dxfId="300" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="298" priority="6">
+    <cfRule type="expression" dxfId="299" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="297" priority="5">
+    <cfRule type="expression" dxfId="298" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="296" priority="4">
+    <cfRule type="expression" dxfId="297" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="295" priority="3">
+    <cfRule type="expression" dxfId="296" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:J57 M57:N57">
-    <cfRule type="expression" dxfId="294" priority="2">
+    <cfRule type="expression" dxfId="295" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:L70">
-    <cfRule type="expression" dxfId="293" priority="1">
+    <cfRule type="expression" dxfId="294" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32374,42 +32735,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="292" priority="13">
+    <cfRule type="expression" dxfId="293" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="291" priority="12">
+    <cfRule type="expression" dxfId="292" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="290" priority="11">
+    <cfRule type="expression" dxfId="291" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="289" priority="5">
+    <cfRule type="expression" dxfId="290" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="288" priority="4">
+    <cfRule type="expression" dxfId="289" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="287" priority="3">
+    <cfRule type="expression" dxfId="288" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="286" priority="2">
+    <cfRule type="expression" dxfId="287" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="285" priority="1">
+    <cfRule type="expression" dxfId="286" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38447,112 +38808,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="284" priority="28">
+    <cfRule type="expression" dxfId="285" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="283" priority="27">
+    <cfRule type="expression" dxfId="284" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="282" priority="26">
+    <cfRule type="expression" dxfId="283" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="281" priority="25">
+    <cfRule type="expression" dxfId="282" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="280" priority="23">
+    <cfRule type="expression" dxfId="281" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="279" priority="22">
+    <cfRule type="expression" dxfId="280" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="278" priority="20">
+    <cfRule type="expression" dxfId="279" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="277" priority="19">
+    <cfRule type="expression" dxfId="278" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="276" priority="15">
+    <cfRule type="expression" dxfId="277" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="275" priority="14">
+    <cfRule type="expression" dxfId="276" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="274" priority="13">
+    <cfRule type="expression" dxfId="275" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="273" priority="12">
+    <cfRule type="expression" dxfId="274" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="272" priority="11">
+    <cfRule type="expression" dxfId="273" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="271" priority="10">
+    <cfRule type="expression" dxfId="272" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="270" priority="9">
+    <cfRule type="expression" dxfId="271" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="269" priority="8">
+    <cfRule type="expression" dxfId="270" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="268" priority="7">
+    <cfRule type="expression" dxfId="269" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="267" priority="6">
+    <cfRule type="expression" dxfId="268" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="266" priority="1">
+    <cfRule type="expression" dxfId="267" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="265" priority="5">
+    <cfRule type="expression" dxfId="266" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="264" priority="4">
+    <cfRule type="expression" dxfId="265" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="263" priority="2">
+    <cfRule type="expression" dxfId="264" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44467,107 +44828,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="262" priority="24">
+    <cfRule type="expression" dxfId="263" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="261" priority="23">
+    <cfRule type="expression" dxfId="262" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="260" priority="22">
+    <cfRule type="expression" dxfId="261" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="259" priority="21">
+    <cfRule type="expression" dxfId="260" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="258" priority="20">
+    <cfRule type="expression" dxfId="259" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="257" priority="19">
+    <cfRule type="expression" dxfId="258" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="256" priority="18">
+    <cfRule type="expression" dxfId="257" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="255" priority="15">
+    <cfRule type="expression" dxfId="256" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="254" priority="14">
+    <cfRule type="expression" dxfId="255" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="253" priority="13">
+    <cfRule type="expression" dxfId="254" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="252" priority="12">
+    <cfRule type="expression" dxfId="253" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="251" priority="1">
+    <cfRule type="expression" dxfId="252" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="250" priority="10">
+    <cfRule type="expression" dxfId="251" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="249" priority="9">
+    <cfRule type="expression" dxfId="250" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="248" priority="8">
+    <cfRule type="expression" dxfId="249" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="247" priority="7">
+    <cfRule type="expression" dxfId="248" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="246" priority="6">
+    <cfRule type="expression" dxfId="247" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="245" priority="5">
+    <cfRule type="expression" dxfId="246" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="244" priority="4">
+    <cfRule type="expression" dxfId="245" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="243" priority="3">
+    <cfRule type="expression" dxfId="244" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="242" priority="2">
+    <cfRule type="expression" dxfId="243" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44919,11 +45280,11 @@
       <c r="O6" s="215"/>
       <c r="P6" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-89692</v>
+        <v>-476456</v>
       </c>
       <c r="Q6" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.7938400000000001</v>
+        <v>-9.5291199999999989</v>
       </c>
       <c r="R6" s="159"/>
       <c r="S6" s="153">
@@ -44940,11 +45301,11 @@
       <c r="X6" s="132"/>
       <c r="Y6" s="154">
         <f t="shared" si="0"/>
-        <v>-138028</v>
+        <v>-524792</v>
       </c>
       <c r="Z6" s="168">
         <f t="shared" si="1"/>
-        <v>-2.7605599999999999</v>
+        <v>-10.495839999999999</v>
       </c>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45001,11 +45362,11 @@
       <c r="O7" s="215"/>
       <c r="P7" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-175187</v>
+        <v>1808</v>
       </c>
       <c r="Q7" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.58395666666666668</v>
+        <v>6.0266666666667357E-3</v>
       </c>
       <c r="R7" s="159"/>
       <c r="S7" s="88">
@@ -45022,11 +45383,11 @@
       <c r="X7"/>
       <c r="Y7" s="154">
         <f t="shared" si="0"/>
-        <v>1159087</v>
+        <v>1336082</v>
       </c>
       <c r="Z7" s="168">
         <f t="shared" si="1"/>
-        <v>3.8636233333333339</v>
+        <v>4.4536066666666674</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45198,11 +45559,11 @@
       <c r="O10" s="215"/>
       <c r="P10" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-499493</v>
+        <v>-414643</v>
       </c>
       <c r="Q10" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.6649766666666668</v>
+        <v>-1.3821433333333335</v>
       </c>
       <c r="R10" s="159"/>
       <c r="S10" s="88">
@@ -45218,11 +45579,11 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="154">
         <f t="shared" si="0"/>
-        <v>-858402</v>
+        <v>-773552</v>
       </c>
       <c r="Z10" s="168">
         <f t="shared" si="1"/>
-        <v>-4.3056566666666667</v>
+        <v>-4.0228233333333332</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45279,11 +45640,11 @@
       <c r="O11" s="215"/>
       <c r="P11" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-275433</v>
+        <v>-263938</v>
       </c>
       <c r="Q11" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.8362200000000004</v>
+        <v>-1.7595866666666671</v>
       </c>
       <c r="R11" s="159"/>
       <c r="S11" s="153">
@@ -45299,11 +45660,11 @@
       <c r="W11" s="150"/>
       <c r="Y11" s="154">
         <f t="shared" si="0"/>
-        <v>-450395</v>
+        <v>-438900</v>
       </c>
       <c r="Z11" s="168">
         <f t="shared" si="1"/>
-        <v>-3.0026333333333337</v>
+        <v>-2.9260000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45360,11 +45721,11 @@
       <c r="O12" s="215"/>
       <c r="P12" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-183812</v>
+        <v>-159067</v>
       </c>
       <c r="Q12" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.0635333333333334</v>
+        <v>-2.6511166666666668</v>
       </c>
       <c r="R12" s="159"/>
       <c r="S12" s="153">
@@ -45380,11 +45741,11 @@
       <c r="W12" s="150"/>
       <c r="Y12" s="154">
         <f t="shared" ref="Y12" si="10">M12+P12+S12+V12</f>
-        <v>-183812</v>
+        <v>-159067</v>
       </c>
       <c r="Z12" s="168">
         <f t="shared" ref="Z12" si="11">(N12+Q12+T12+W12)</f>
-        <v>-3.0635333333333334</v>
+        <v>-2.6511166666666668</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45441,11 +45802,11 @@
       <c r="O13" s="215"/>
       <c r="P13" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>207343</v>
+        <v>248043</v>
       </c>
       <c r="Q13" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.13822866666666678</v>
+        <v>0.16536200000000012</v>
       </c>
       <c r="R13" s="159"/>
       <c r="S13" s="88">
@@ -45462,11 +45823,11 @@
       <c r="X13"/>
       <c r="Y13" s="154">
         <f t="shared" si="0"/>
-        <v>-1160856</v>
+        <v>-1120156</v>
       </c>
       <c r="Z13" s="168">
         <f t="shared" si="1"/>
-        <v>-0.77390399999999993</v>
+        <v>-0.74677066666666658</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45850,11 +46211,11 @@
       <c r="O18" s="215"/>
       <c r="P18" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>397851</v>
+        <v>417173</v>
       </c>
       <c r="Q18" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.66308500000000015</v>
+        <v>0.6952883333333334</v>
       </c>
       <c r="R18" s="159"/>
       <c r="S18" s="88">
@@ -45870,11 +46231,11 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="154">
         <f t="shared" si="0"/>
-        <v>202517</v>
+        <v>221839</v>
       </c>
       <c r="Z18" s="168">
         <f t="shared" si="1"/>
-        <v>-2.7545349999999997</v>
+        <v>-2.7223316666666664</v>
       </c>
     </row>
     <row r="19" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45931,11 +46292,11 @@
       <c r="O19" s="215"/>
       <c r="P19" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5619</v>
+        <v>8379</v>
       </c>
       <c r="Q19" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>5.6190000000000004E-2</v>
+        <v>8.3790000000000003E-2</v>
       </c>
       <c r="R19" s="159"/>
       <c r="S19" s="153">
@@ -45951,11 +46312,11 @@
       <c r="W19" s="150"/>
       <c r="Y19" s="154">
         <f t="shared" si="0"/>
-        <v>9298</v>
+        <v>12058</v>
       </c>
       <c r="Z19" s="168">
         <f t="shared" si="1"/>
-        <v>9.2980000000000007E-2</v>
+        <v>0.12058000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46102,11 +46463,11 @@
       <c r="O21" s="215"/>
       <c r="P21" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>32628</v>
+        <v>36772</v>
       </c>
       <c r="Q21" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.13051199999999996</v>
+        <v>0.14708799999999994</v>
       </c>
       <c r="R21" s="159"/>
       <c r="S21" s="88">
@@ -46122,11 +46483,11 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="154">
         <f t="shared" si="0"/>
-        <v>-234788</v>
+        <v>-230644</v>
       </c>
       <c r="Z21" s="168">
         <f t="shared" si="1"/>
-        <v>-2.5436480000000001</v>
+        <v>-2.527072</v>
       </c>
     </row>
     <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46183,11 +46544,11 @@
       <c r="O22" s="215"/>
       <c r="P22" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-98544</v>
+        <v>-92142</v>
       </c>
       <c r="Q22" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.44792727272727267</v>
+        <v>-0.41882727272727271</v>
       </c>
       <c r="R22" s="159"/>
       <c r="S22" s="88">
@@ -46203,11 +46564,11 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="154">
         <f t="shared" si="0"/>
-        <v>-187444</v>
+        <v>-181042</v>
       </c>
       <c r="Z22" s="168">
         <f t="shared" si="1"/>
-        <v>-1.3369272727272727</v>
+        <v>-1.3078272727272728</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46345,11 +46706,11 @@
       <c r="O24" s="215"/>
       <c r="P24" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>55069</v>
+        <v>76772</v>
       </c>
       <c r="Q24" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.55069000000000001</v>
+        <v>0.76771999999999996</v>
       </c>
       <c r="R24" s="159"/>
       <c r="S24" s="88">
@@ -46365,11 +46726,11 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="154">
         <f t="shared" si="0"/>
-        <v>1770414</v>
+        <v>1792117</v>
       </c>
       <c r="Z24" s="168">
         <f t="shared" si="1"/>
-        <v>17.704139999999999</v>
+        <v>17.92117</v>
       </c>
     </row>
     <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46830,11 +47191,11 @@
       <c r="O30" s="215"/>
       <c r="P30" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>13363</v>
+        <v>54624</v>
       </c>
       <c r="Q30" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.12148181818181814</v>
+        <v>0.49658181818181807</v>
       </c>
       <c r="R30" s="159"/>
       <c r="S30" s="88">
@@ -46851,11 +47212,11 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="154">
         <f t="shared" si="0"/>
-        <v>13081</v>
+        <v>54342</v>
       </c>
       <c r="Z30" s="168">
         <f t="shared" si="1"/>
-        <v>0.11891818181818181</v>
+        <v>0.49401818181818175</v>
       </c>
     </row>
     <row r="31" spans="1:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47001,11 +47362,11 @@
       <c r="O32" s="215"/>
       <c r="P32" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-166530</v>
+        <v>-133184</v>
       </c>
       <c r="Q32" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.1102000000000001</v>
+        <v>-0.8878933333333332</v>
       </c>
       <c r="R32" s="159"/>
       <c r="S32" s="88">
@@ -47022,11 +47383,11 @@
       <c r="X32"/>
       <c r="Y32" s="154">
         <f t="shared" si="0"/>
-        <v>-671599</v>
+        <v>-638253</v>
       </c>
       <c r="Z32" s="168">
         <f t="shared" si="1"/>
-        <v>-4.4773266666666673</v>
+        <v>-4.2550200000000009</v>
       </c>
     </row>
     <row r="33" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47164,11 +47525,11 @@
       <c r="O34" s="215"/>
       <c r="P34" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>202910</v>
+        <v>216872</v>
       </c>
       <c r="Q34" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.8446363636363632</v>
+        <v>1.9715636363636357</v>
       </c>
       <c r="R34" s="159"/>
       <c r="S34" s="88">
@@ -47184,11 +47545,11 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="154">
         <f t="shared" si="0"/>
-        <v>-116030</v>
+        <v>-102068</v>
       </c>
       <c r="Z34" s="168">
         <f t="shared" si="1"/>
-        <v>-1.0548181818181819</v>
+        <v>-0.92789090909090932</v>
       </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -47333,11 +47694,11 @@
       <c r="O36" s="215"/>
       <c r="P36" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-913262</v>
+        <v>-701385</v>
       </c>
       <c r="Q36" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.9707043478260879</v>
+        <v>-3.0495000000000005</v>
       </c>
       <c r="R36" s="159"/>
       <c r="S36" s="88">
@@ -47353,11 +47714,11 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="154">
         <f t="shared" si="0"/>
-        <v>3247841</v>
+        <v>3459718</v>
       </c>
       <c r="Z36" s="168">
         <f t="shared" si="1"/>
-        <v>14.121047826086956</v>
+        <v>15.042252173913043</v>
       </c>
     </row>
     <row r="37" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47412,11 +47773,11 @@
       <c r="O37" s="215"/>
       <c r="P37" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-12717</v>
+        <v>-14294</v>
       </c>
       <c r="Q37" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.63584999999999992</v>
+        <v>-0.71469999999999989</v>
       </c>
       <c r="R37" s="159"/>
       <c r="S37" s="153">
@@ -47432,11 +47793,11 @@
       <c r="W37" s="150"/>
       <c r="Y37" s="154">
         <f t="shared" ref="Y37" si="20">M37+P37+S37+V37</f>
-        <v>-12717</v>
+        <v>-14294</v>
       </c>
       <c r="Z37" s="168">
         <f t="shared" ref="Z37" si="21">(N37+Q37+T37+W37)</f>
-        <v>-0.63584999999999992</v>
+        <v>-0.71469999999999989</v>
       </c>
     </row>
     <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48171,11 +48532,11 @@
       <c r="O46" s="215"/>
       <c r="P46" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>907647</v>
+        <v>1132596</v>
       </c>
       <c r="Q46" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.815294</v>
+        <v>2.2651919999999999</v>
       </c>
       <c r="R46" s="159"/>
       <c r="S46" s="88">
@@ -48192,11 +48553,11 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="154">
         <f t="shared" si="22"/>
-        <v>859909</v>
+        <v>1084858</v>
       </c>
       <c r="Z46" s="168">
         <f t="shared" si="23"/>
-        <v>1.7198179999999998</v>
+        <v>2.1697159999999998</v>
       </c>
       <c r="AA46" s="1"/>
     </row>
@@ -48254,11 +48615,11 @@
       <c r="O47" s="215"/>
       <c r="P47" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-276885</v>
+        <v>-217539</v>
       </c>
       <c r="Q47" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-5.5377000000000001</v>
+        <v>-4.3507800000000003</v>
       </c>
       <c r="R47" s="159"/>
       <c r="S47" s="88">
@@ -48274,11 +48635,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="154">
         <f t="shared" si="22"/>
-        <v>-159990</v>
+        <v>-100644</v>
       </c>
       <c r="Z47" s="168">
         <f t="shared" si="23"/>
-        <v>-3.1998000000000002</v>
+        <v>-2.0128800000000004</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -48423,11 +48784,11 @@
       <c r="O49" s="215"/>
       <c r="P49" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>43456</v>
+        <v>53712</v>
       </c>
       <c r="Q49" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.0864</v>
+        <v>1.3428000000000002</v>
       </c>
       <c r="R49" s="159"/>
       <c r="S49" s="88">
@@ -48443,11 +48804,11 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="154">
         <f t="shared" si="22"/>
-        <v>31628</v>
+        <v>41884</v>
       </c>
       <c r="Z49" s="168">
         <f t="shared" si="23"/>
-        <v>0.79069999999999996</v>
+        <v>1.0471000000000001</v>
       </c>
       <c r="AD49"/>
       <c r="AE49"/>
@@ -48678,11 +49039,11 @@
       <c r="O52" s="215"/>
       <c r="P52" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>547783</v>
+        <v>551129</v>
       </c>
       <c r="Q52" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.3694575000000002</v>
+        <v>1.3778225000000002</v>
       </c>
       <c r="R52" s="159"/>
       <c r="S52" s="88">
@@ -48698,11 +49059,11 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="154">
         <f t="shared" si="22"/>
-        <v>147484</v>
+        <v>150830</v>
       </c>
       <c r="Z52" s="168">
         <f t="shared" si="23"/>
-        <v>0.36871000000000009</v>
+        <v>0.37707500000000005</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48759,11 +49120,11 @@
       <c r="O53" s="215"/>
       <c r="P53" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>42553</v>
+        <v>121628</v>
       </c>
       <c r="Q53" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.42552999999999996</v>
+        <v>1.2162799999999998</v>
       </c>
       <c r="R53" s="159"/>
       <c r="S53" s="88">
@@ -48779,11 +49140,11 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="154">
         <f t="shared" si="22"/>
-        <v>788346</v>
+        <v>867421</v>
       </c>
       <c r="Z53" s="168">
         <f t="shared" si="23"/>
-        <v>7.8834600000000012</v>
+        <v>8.6742100000000004</v>
       </c>
     </row>
     <row r="54" spans="1:34" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48921,11 +49282,11 @@
       <c r="O55" s="215"/>
       <c r="P55" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-26966</v>
+        <v>-16082</v>
       </c>
       <c r="Q55" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.5393199999999998</v>
+        <v>-0.32163999999999993</v>
       </c>
       <c r="R55" s="159"/>
       <c r="S55" s="153">
@@ -48942,11 +49303,11 @@
       <c r="X55" s="132"/>
       <c r="Y55" s="154">
         <f t="shared" si="22"/>
-        <v>-272744</v>
+        <v>-261860</v>
       </c>
       <c r="Z55" s="168">
         <f t="shared" si="23"/>
-        <v>-5.4548800000000002</v>
+        <v>-5.2371999999999996</v>
       </c>
       <c r="AA55" s="132"/>
     </row>
@@ -49004,11 +49365,11 @@
       <c r="O56" s="215"/>
       <c r="P56" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-183198</v>
+        <v>-69136</v>
       </c>
       <c r="Q56" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.61065999999999998</v>
+        <v>-0.23045333333333332</v>
       </c>
       <c r="R56" s="159"/>
       <c r="S56" s="88">
@@ -49024,11 +49385,11 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="154">
         <f t="shared" si="22"/>
-        <v>-4882173</v>
+        <v>-4768111</v>
       </c>
       <c r="Z56" s="168">
         <f t="shared" si="23"/>
-        <v>-16.273910000000004</v>
+        <v>-15.893703333333336</v>
       </c>
       <c r="AB56" s="132"/>
       <c r="AC56" s="132"/>
@@ -49258,11 +49619,11 @@
       <c r="O59" s="215"/>
       <c r="P59" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>20595</v>
+        <v>6723</v>
       </c>
       <c r="Q59" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>9.1299999999999992E-2</v>
+        <v>-0.18614000000000003</v>
       </c>
       <c r="R59" s="159"/>
       <c r="S59" s="88">
@@ -49279,11 +49640,11 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="154">
         <f t="shared" si="22"/>
-        <v>57318</v>
+        <v>43446</v>
       </c>
       <c r="Z59" s="168">
         <f t="shared" si="23"/>
-        <v>0.4201333333333333</v>
+        <v>0.14269333333333328</v>
       </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -49347,11 +49708,11 @@
       <c r="O60" s="215"/>
       <c r="P60" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>449421</v>
+        <v>666452</v>
       </c>
       <c r="Q60" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>4.4942099999999998</v>
+        <v>6.6645199999999996</v>
       </c>
       <c r="R60" s="159"/>
       <c r="S60" s="88">
@@ -49367,11 +49728,11 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="154">
         <f t="shared" si="22"/>
-        <v>3999490</v>
+        <v>4216521</v>
       </c>
       <c r="Z60" s="168">
         <f t="shared" si="23"/>
-        <v>39.994900000000001</v>
+        <v>42.165210000000002</v>
       </c>
       <c r="AB60" s="132"/>
       <c r="AC60" s="132"/>
@@ -49433,11 +49794,11 @@
       <c r="O61" s="215"/>
       <c r="P61" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>4235</v>
+        <v>6503</v>
       </c>
       <c r="Q61" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.42349999999999999</v>
+        <v>0.65029999999999988</v>
       </c>
       <c r="R61" s="159"/>
       <c r="S61" s="153">
@@ -49453,11 +49814,11 @@
       <c r="W61" s="150"/>
       <c r="Y61" s="154">
         <f t="shared" ref="Y61" si="37">M61+P61+S61+V61</f>
-        <v>4235</v>
+        <v>6503</v>
       </c>
       <c r="Z61" s="168">
         <f t="shared" ref="Z61" si="38">(N61+Q61+T61+W61)</f>
-        <v>0.42349999999999999</v>
+        <v>0.65029999999999988</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49514,11 +49875,11 @@
       <c r="O62" s="215"/>
       <c r="P62" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>155985</v>
+        <v>253289</v>
       </c>
       <c r="Q62" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>0.51995000000000002</v>
+        <v>0.84429666666666681</v>
       </c>
       <c r="R62" s="159"/>
       <c r="S62" s="88">
@@ -49534,11 +49895,11 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="154">
         <f t="shared" si="22"/>
-        <v>828834</v>
+        <v>926138</v>
       </c>
       <c r="Z62" s="168">
         <f t="shared" si="23"/>
-        <v>2.7627799999999998</v>
+        <v>3.0871266666666664</v>
       </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -49927,11 +50288,11 @@
       <c r="O67" s="215"/>
       <c r="P67" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1469416</v>
+        <v>-629705</v>
       </c>
       <c r="Q67" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1.469516</v>
+        <v>-0.62980499999999995</v>
       </c>
       <c r="R67" s="159"/>
       <c r="S67" s="153">
@@ -49947,11 +50308,11 @@
       <c r="W67" s="150"/>
       <c r="Y67" s="154">
         <f t="shared" ref="Y67" si="43">M67+P67+S67+V67</f>
-        <v>-1469416</v>
+        <v>-629705</v>
       </c>
       <c r="Z67" s="168">
         <f t="shared" ref="Z67" si="44">(N67+Q67+T67+W67)</f>
-        <v>-1.469516</v>
+        <v>-0.62980499999999995</v>
       </c>
     </row>
     <row r="68" spans="1:26" s="132" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50065,11 +50426,11 @@
       <c r="O69" s="215"/>
       <c r="P69" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>373</v>
+        <v>-5723</v>
       </c>
       <c r="Q69" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>7.4600000000000222E-3</v>
+        <v>-0.11446000000000001</v>
       </c>
       <c r="R69" s="159"/>
       <c r="S69" s="153">
@@ -50085,11 +50446,11 @@
       <c r="W69" s="150"/>
       <c r="Y69" s="154">
         <f t="shared" si="22"/>
-        <v>-46281</v>
+        <v>-52377</v>
       </c>
       <c r="Z69" s="168">
         <f t="shared" si="23"/>
-        <v>-0.92562</v>
+        <v>-1.0475400000000001</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
@@ -50628,11 +50989,11 @@
       <c r="O76" s="215"/>
       <c r="P76" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>512183</v>
+        <v>558288</v>
       </c>
       <c r="Q76" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>1.0243659999999999</v>
+        <v>1.116576</v>
       </c>
       <c r="R76" s="159"/>
       <c r="S76" s="153">
@@ -50648,11 +51009,11 @@
       <c r="W76" s="150"/>
       <c r="Y76" s="154">
         <f t="shared" si="53"/>
-        <v>512183</v>
+        <v>558288</v>
       </c>
       <c r="Z76" s="168">
         <f t="shared" si="54"/>
-        <v>1.0243659999999999</v>
+        <v>1.116576</v>
       </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
@@ -50685,7 +51046,7 @@
       <c r="O77" s="122"/>
       <c r="P77" s="109">
         <f>SUM(P4:P74)</f>
-        <v>4751570</v>
+        <v>6695055</v>
       </c>
       <c r="Q77" s="122"/>
       <c r="R77" s="122"/>
@@ -50696,7 +51057,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="154">
         <f>SUM(Y4:Y76)</f>
-        <v>24712853</v>
+        <v>26702443</v>
       </c>
       <c r="Z77" s="161"/>
     </row>
@@ -50992,11 +51353,11 @@
       <c r="O82" s="167"/>
       <c r="P82" s="153">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-130193</v>
+        <v>-134155</v>
       </c>
       <c r="Q82" s="155">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-0.43397666666666623</v>
+        <v>-0.44718333333333282</v>
       </c>
       <c r="R82" s="159"/>
       <c r="S82" s="153">
@@ -51013,11 +51374,11 @@
       <c r="X82" s="132"/>
       <c r="Y82" s="52">
         <f t="shared" si="56"/>
-        <v>81307</v>
+        <v>77345</v>
       </c>
       <c r="Z82" s="53">
         <f t="shared" si="56"/>
-        <v>-0.43397666666666623</v>
+        <v>-0.44718333333333282</v>
       </c>
       <c r="AA82" s="132"/>
     </row>
@@ -51127,7 +51488,7 @@
       <c r="O84" s="123"/>
       <c r="P84" s="112">
         <f>SUM(P80:P83)</f>
-        <v>1125958</v>
+        <v>1121996</v>
       </c>
       <c r="Q84" s="123"/>
       <c r="R84" s="123"/>
@@ -51151,1212 +51512,1212 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 Y4:Z11 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R44:W44 R72:W74 R7:W9 R13:W16 R34:W36 R45:U46 R17:U17 R22:U30 R48:U53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:U43 M38:O53 I38:L43 Y38:Z53 W38:W39 G84:W84 K69:O74 G69:J69 W66:W68 R62:U71 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:U60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 G77:W78">
-    <cfRule type="expression" dxfId="241" priority="448">
+    <cfRule type="expression" dxfId="242" priority="448">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="240" priority="447">
+    <cfRule type="expression" dxfId="241" priority="447">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="239" priority="444">
+    <cfRule type="expression" dxfId="240" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="238" priority="441">
+    <cfRule type="expression" dxfId="239" priority="441">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="237" priority="442">
+    <cfRule type="expression" dxfId="238" priority="442">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="236" priority="432">
+    <cfRule type="expression" dxfId="237" priority="432">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="235" priority="433">
+    <cfRule type="expression" dxfId="236" priority="433">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="234" priority="422">
+    <cfRule type="expression" dxfId="235" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="233" priority="420">
+    <cfRule type="expression" dxfId="234" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="232" priority="418">
+    <cfRule type="expression" dxfId="233" priority="418">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="231" priority="409">
+    <cfRule type="expression" dxfId="232" priority="409">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="230" priority="408">
+    <cfRule type="expression" dxfId="231" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="229" priority="380">
+    <cfRule type="expression" dxfId="230" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="228" priority="406">
+    <cfRule type="expression" dxfId="229" priority="406">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="227" priority="405">
+    <cfRule type="expression" dxfId="228" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="226" priority="403">
+    <cfRule type="expression" dxfId="227" priority="403">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="225" priority="402">
+    <cfRule type="expression" dxfId="226" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="224" priority="400">
+    <cfRule type="expression" dxfId="225" priority="400">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="223" priority="387">
+    <cfRule type="expression" dxfId="224" priority="387">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:U4 T20:U21">
-    <cfRule type="expression" dxfId="222" priority="331">
+    <cfRule type="expression" dxfId="223" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="221" priority="378">
+    <cfRule type="expression" dxfId="222" priority="378">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:U4 S20:U21">
-    <cfRule type="expression" dxfId="220" priority="330">
+    <cfRule type="expression" dxfId="221" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="219" priority="383">
+    <cfRule type="expression" dxfId="220" priority="383">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="218" priority="349">
+    <cfRule type="expression" dxfId="219" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="217" priority="347">
+    <cfRule type="expression" dxfId="218" priority="347">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="216" priority="355">
+    <cfRule type="expression" dxfId="217" priority="355">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="215" priority="354">
+    <cfRule type="expression" dxfId="216" priority="354">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="214" priority="339">
+    <cfRule type="expression" dxfId="215" priority="339">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="213" priority="338">
+    <cfRule type="expression" dxfId="214" priority="338">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="212" priority="369">
+    <cfRule type="expression" dxfId="213" priority="369">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="211" priority="329">
+    <cfRule type="expression" dxfId="212" priority="329">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="210" priority="340">
+    <cfRule type="expression" dxfId="211" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="209" priority="350">
+    <cfRule type="expression" dxfId="210" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="208" priority="348">
+    <cfRule type="expression" dxfId="209" priority="348">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="207" priority="341">
+    <cfRule type="expression" dxfId="208" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="206" priority="328">
+    <cfRule type="expression" dxfId="207" priority="328">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="205" priority="286">
+    <cfRule type="expression" dxfId="206" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="204" priority="285">
+    <cfRule type="expression" dxfId="205" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:U18">
-    <cfRule type="expression" dxfId="203" priority="283">
+    <cfRule type="expression" dxfId="204" priority="283">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="202" priority="275">
+    <cfRule type="expression" dxfId="203" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="201" priority="274">
+    <cfRule type="expression" dxfId="202" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="200" priority="288">
+    <cfRule type="expression" dxfId="201" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="199" priority="287">
+    <cfRule type="expression" dxfId="200" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="198" priority="284">
+    <cfRule type="expression" dxfId="199" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S18:U18">
-    <cfRule type="expression" dxfId="197" priority="282">
+    <cfRule type="expression" dxfId="198" priority="282">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="196" priority="273">
+    <cfRule type="expression" dxfId="197" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S31:U31">
-    <cfRule type="expression" dxfId="195" priority="267">
+    <cfRule type="expression" dxfId="196" priority="267">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="194" priority="272">
+    <cfRule type="expression" dxfId="195" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="193" priority="271">
+    <cfRule type="expression" dxfId="194" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T31:U31">
-    <cfRule type="expression" dxfId="192" priority="268">
+    <cfRule type="expression" dxfId="193" priority="268">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="191" priority="270">
+    <cfRule type="expression" dxfId="192" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="190" priority="269">
+    <cfRule type="expression" dxfId="191" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="189" priority="260">
+    <cfRule type="expression" dxfId="190" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="188" priority="259">
+    <cfRule type="expression" dxfId="189" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="187" priority="256">
+    <cfRule type="expression" dxfId="188" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="186" priority="255">
+    <cfRule type="expression" dxfId="187" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S10:U11">
-    <cfRule type="expression" dxfId="185" priority="253">
+    <cfRule type="expression" dxfId="186" priority="253">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="184" priority="258">
+    <cfRule type="expression" dxfId="185" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="183" priority="257">
+    <cfRule type="expression" dxfId="184" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T10:U11">
-    <cfRule type="expression" dxfId="182" priority="254">
+    <cfRule type="expression" dxfId="183" priority="254">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="181" priority="246">
+    <cfRule type="expression" dxfId="182" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="180" priority="245">
+    <cfRule type="expression" dxfId="181" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="179" priority="244">
+    <cfRule type="expression" dxfId="180" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T47:U47">
-    <cfRule type="expression" dxfId="178" priority="239">
+    <cfRule type="expression" dxfId="179" priority="239">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S47:U47">
-    <cfRule type="expression" dxfId="177" priority="238">
+    <cfRule type="expression" dxfId="178" priority="238">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="176" priority="242">
+    <cfRule type="expression" dxfId="177" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="175" priority="241">
+    <cfRule type="expression" dxfId="176" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="174" priority="240">
+    <cfRule type="expression" dxfId="175" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="173" priority="243">
+    <cfRule type="expression" dxfId="174" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="172" priority="231">
+    <cfRule type="expression" dxfId="173" priority="231">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="171" priority="227">
+    <cfRule type="expression" dxfId="172" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="170" priority="226">
+    <cfRule type="expression" dxfId="171" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T5:U5">
-    <cfRule type="expression" dxfId="169" priority="220">
+    <cfRule type="expression" dxfId="170" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:U5">
-    <cfRule type="expression" dxfId="168" priority="219">
+    <cfRule type="expression" dxfId="169" priority="219">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="167" priority="223">
+    <cfRule type="expression" dxfId="168" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="166" priority="222">
+    <cfRule type="expression" dxfId="167" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="165" priority="221">
+    <cfRule type="expression" dxfId="166" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="164" priority="224">
+    <cfRule type="expression" dxfId="165" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="163" priority="208">
+    <cfRule type="expression" dxfId="164" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="162" priority="207">
+    <cfRule type="expression" dxfId="163" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="161" priority="206">
+    <cfRule type="expression" dxfId="162" priority="206">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="160" priority="200">
+    <cfRule type="expression" dxfId="161" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="159" priority="199">
+    <cfRule type="expression" dxfId="160" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S32:U32">
-    <cfRule type="expression" dxfId="158" priority="193">
+    <cfRule type="expression" dxfId="159" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="157" priority="198">
+    <cfRule type="expression" dxfId="158" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="156" priority="197">
+    <cfRule type="expression" dxfId="157" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:U32">
-    <cfRule type="expression" dxfId="155" priority="194">
+    <cfRule type="expression" dxfId="156" priority="194">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="154" priority="196">
+    <cfRule type="expression" dxfId="155" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="153" priority="195">
+    <cfRule type="expression" dxfId="154" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="152" priority="191">
+    <cfRule type="expression" dxfId="153" priority="191">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="151" priority="190">
+    <cfRule type="expression" dxfId="152" priority="190">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="150" priority="177">
+    <cfRule type="expression" dxfId="151" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="149" priority="186">
+    <cfRule type="expression" dxfId="150" priority="186">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="148" priority="185">
+    <cfRule type="expression" dxfId="149" priority="185">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="147" priority="175">
+    <cfRule type="expression" dxfId="148" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="146" priority="174">
+    <cfRule type="expression" dxfId="147" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="145" priority="173">
+    <cfRule type="expression" dxfId="146" priority="173">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="144" priority="168">
+    <cfRule type="expression" dxfId="145" priority="168">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="143" priority="165">
+    <cfRule type="expression" dxfId="144" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="142" priority="164">
+    <cfRule type="expression" dxfId="143" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="141" priority="163">
+    <cfRule type="expression" dxfId="142" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="140" priority="162">
+    <cfRule type="expression" dxfId="141" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="139" priority="161">
+    <cfRule type="expression" dxfId="140" priority="161">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="138" priority="160">
+    <cfRule type="expression" dxfId="139" priority="160">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="137" priority="147">
+    <cfRule type="expression" dxfId="138" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="136" priority="157">
+    <cfRule type="expression" dxfId="137" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="135" priority="156">
+    <cfRule type="expression" dxfId="136" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="134" priority="155">
+    <cfRule type="expression" dxfId="135" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="133" priority="154">
+    <cfRule type="expression" dxfId="134" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="132" priority="153">
+    <cfRule type="expression" dxfId="133" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="131" priority="152">
+    <cfRule type="expression" dxfId="132" priority="152">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="130" priority="151">
+    <cfRule type="expression" dxfId="131" priority="151">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="129" priority="142">
+    <cfRule type="expression" dxfId="130" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="128" priority="148">
+    <cfRule type="expression" dxfId="129" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="127" priority="146">
+    <cfRule type="expression" dxfId="128" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="126" priority="145">
+    <cfRule type="expression" dxfId="127" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="125" priority="144">
+    <cfRule type="expression" dxfId="126" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="124" priority="143">
+    <cfRule type="expression" dxfId="125" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="123" priority="141">
+    <cfRule type="expression" dxfId="124" priority="141">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="122" priority="138">
+    <cfRule type="expression" dxfId="123" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="121" priority="137">
+    <cfRule type="expression" dxfId="122" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="120" priority="136">
+    <cfRule type="expression" dxfId="121" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="119" priority="135">
+    <cfRule type="expression" dxfId="120" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="118" priority="134">
+    <cfRule type="expression" dxfId="119" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="117" priority="133">
+    <cfRule type="expression" dxfId="118" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="116" priority="130">
+    <cfRule type="expression" dxfId="117" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="115" priority="132">
+    <cfRule type="expression" dxfId="116" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="114" priority="131">
+    <cfRule type="expression" dxfId="115" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="113" priority="129">
+    <cfRule type="expression" dxfId="114" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="112" priority="128">
+    <cfRule type="expression" dxfId="113" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="111" priority="127">
+    <cfRule type="expression" dxfId="112" priority="127">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="110" priority="126">
+    <cfRule type="expression" dxfId="111" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="109" priority="124">
+    <cfRule type="expression" dxfId="110" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="108" priority="123">
+    <cfRule type="expression" dxfId="109" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="107" priority="122">
+    <cfRule type="expression" dxfId="108" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="106" priority="121">
+    <cfRule type="expression" dxfId="107" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="105" priority="120">
+    <cfRule type="expression" dxfId="106" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T6:U6">
-    <cfRule type="expression" dxfId="104" priority="115">
+    <cfRule type="expression" dxfId="105" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S6:U6">
-    <cfRule type="expression" dxfId="103" priority="114">
+    <cfRule type="expression" dxfId="104" priority="114">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="102" priority="118">
+    <cfRule type="expression" dxfId="103" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="101" priority="117">
+    <cfRule type="expression" dxfId="102" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="100" priority="116">
+    <cfRule type="expression" dxfId="101" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="99" priority="119">
+    <cfRule type="expression" dxfId="100" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="98" priority="113">
+    <cfRule type="expression" dxfId="99" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="97" priority="111">
+    <cfRule type="expression" dxfId="98" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="96" priority="109">
+    <cfRule type="expression" dxfId="97" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="95" priority="108">
+    <cfRule type="expression" dxfId="96" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="94" priority="107">
+    <cfRule type="expression" dxfId="95" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="93" priority="106">
+    <cfRule type="expression" dxfId="94" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="92" priority="105">
+    <cfRule type="expression" dxfId="93" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="91" priority="104">
+    <cfRule type="expression" dxfId="92" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="90" priority="102">
+    <cfRule type="expression" dxfId="91" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S19:U19">
-    <cfRule type="expression" dxfId="89" priority="92">
+    <cfRule type="expression" dxfId="90" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="88" priority="100">
+    <cfRule type="expression" dxfId="89" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="87" priority="99">
+    <cfRule type="expression" dxfId="88" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="86" priority="96">
+    <cfRule type="expression" dxfId="87" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="85" priority="95">
+    <cfRule type="expression" dxfId="86" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19:U19">
-    <cfRule type="expression" dxfId="84" priority="93">
+    <cfRule type="expression" dxfId="85" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="83" priority="98">
+    <cfRule type="expression" dxfId="84" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="82" priority="97">
+    <cfRule type="expression" dxfId="83" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="81" priority="94">
+    <cfRule type="expression" dxfId="82" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="80" priority="91">
+    <cfRule type="expression" dxfId="81" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="79" priority="90">
+    <cfRule type="expression" dxfId="80" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="78" priority="89">
+    <cfRule type="expression" dxfId="79" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="77" priority="88">
+    <cfRule type="expression" dxfId="78" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="76" priority="87">
+    <cfRule type="expression" dxfId="77" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="75" priority="86">
+    <cfRule type="expression" dxfId="76" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="74" priority="85">
+    <cfRule type="expression" dxfId="75" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="73" priority="84">
+    <cfRule type="expression" dxfId="74" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="72" priority="72">
+    <cfRule type="expression" dxfId="73" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="71" priority="82">
+    <cfRule type="expression" dxfId="72" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="70" priority="81">
+    <cfRule type="expression" dxfId="71" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="69" priority="80">
+    <cfRule type="expression" dxfId="70" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="68" priority="79">
+    <cfRule type="expression" dxfId="69" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="67" priority="78">
+    <cfRule type="expression" dxfId="68" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="66" priority="77">
+    <cfRule type="expression" dxfId="67" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="65" priority="76">
+    <cfRule type="expression" dxfId="66" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="64" priority="75">
+    <cfRule type="expression" dxfId="65" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="63" priority="74">
+    <cfRule type="expression" dxfId="64" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="62" priority="73">
+    <cfRule type="expression" dxfId="63" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="61" priority="71">
+    <cfRule type="expression" dxfId="62" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="60" priority="70">
+    <cfRule type="expression" dxfId="61" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="59" priority="69">
+    <cfRule type="expression" dxfId="60" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="58" priority="68">
+    <cfRule type="expression" dxfId="59" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:U33">
-    <cfRule type="expression" dxfId="57" priority="62">
+    <cfRule type="expression" dxfId="58" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="56" priority="67">
+    <cfRule type="expression" dxfId="57" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="55" priority="66">
+    <cfRule type="expression" dxfId="56" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T33:U33">
-    <cfRule type="expression" dxfId="54" priority="63">
+    <cfRule type="expression" dxfId="55" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="53" priority="65">
+    <cfRule type="expression" dxfId="54" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="52" priority="64">
+    <cfRule type="expression" dxfId="53" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q11 Q38:Q53 Q55:Q60 Q62:Q76">
-    <cfRule type="expression" dxfId="51" priority="59">
+    <cfRule type="expression" dxfId="52" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q11 P38:Q53 P55:Q60 P62:Q76">
-    <cfRule type="expression" dxfId="50" priority="58">
+    <cfRule type="expression" dxfId="51" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="49" priority="57">
+    <cfRule type="expression" dxfId="50" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="48" priority="56">
+    <cfRule type="expression" dxfId="49" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="47" priority="55">
+    <cfRule type="expression" dxfId="48" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="46" priority="54">
+    <cfRule type="expression" dxfId="47" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="45" priority="53">
+    <cfRule type="expression" dxfId="46" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:W76">
-    <cfRule type="expression" dxfId="44" priority="52">
+    <cfRule type="expression" dxfId="45" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="43" priority="39">
+    <cfRule type="expression" dxfId="44" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="42" priority="48">
+    <cfRule type="expression" dxfId="43" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="41" priority="24">
+    <cfRule type="expression" dxfId="42" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="40" priority="46">
+    <cfRule type="expression" dxfId="41" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61:U61">
-    <cfRule type="expression" dxfId="39" priority="45">
+    <cfRule type="expression" dxfId="40" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="38" priority="44">
+    <cfRule type="expression" dxfId="39" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="37" priority="43">
+    <cfRule type="expression" dxfId="38" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="36" priority="42">
+    <cfRule type="expression" dxfId="37" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37:W37">
-    <cfRule type="expression" dxfId="35" priority="41">
+    <cfRule type="expression" dxfId="36" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="34" priority="40">
+    <cfRule type="expression" dxfId="35" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="33" priority="25">
+    <cfRule type="expression" dxfId="34" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="33" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="31" priority="35">
+    <cfRule type="expression" dxfId="32" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="30" priority="34">
+    <cfRule type="expression" dxfId="31" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="29" priority="33">
+    <cfRule type="expression" dxfId="30" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="28" priority="32">
+    <cfRule type="expression" dxfId="29" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="27" priority="31">
+    <cfRule type="expression" dxfId="28" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="26" priority="30">
+    <cfRule type="expression" dxfId="27" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="25" priority="29">
+    <cfRule type="expression" dxfId="26" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="24" priority="28">
+    <cfRule type="expression" dxfId="25" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="23" priority="27">
+    <cfRule type="expression" dxfId="24" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="22" priority="26">
+    <cfRule type="expression" dxfId="23" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="22" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="18" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S12:U12">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="10" priority="15">
+    <cfRule type="expression" dxfId="11" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T12:U12">
-    <cfRule type="expression" dxfId="8" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54:U54 G54:O54 Y54:Z54">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3236" uniqueCount="331">
   <si>
     <t>Sudeep</t>
   </si>
@@ -2357,7 +2357,21 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="559">
+  <dxfs count="561">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6602,7 +6616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:Z65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="132" customWidth="1" outlineLevel="1"/>
@@ -6612,19 +6626,19 @@
     <col min="5" max="5" width="9.42578125" style="132" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="132" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="132" customWidth="1"/>
-    <col min="8" max="10" width="13.42578125" style="132" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" style="132" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" style="132" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="10.7109375" style="132" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="19" width="9.140625" style="132"/>
-    <col min="20" max="20" width="14.140625" style="132" customWidth="1"/>
-    <col min="21" max="21" width="12" style="132" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="132" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="132"/>
+    <col min="8" max="12" width="13.42578125" style="132" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="132" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" style="132" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="10.7109375" style="132" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="21" width="9.140625" style="132"/>
+    <col min="22" max="22" width="14.140625" style="132" customWidth="1"/>
+    <col min="23" max="23" width="12" style="132" customWidth="1"/>
+    <col min="24" max="24" width="15.85546875" style="132" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="132"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="220"/>
       <c r="H2" s="255">
         <v>46296</v>
@@ -6635,15 +6649,21 @@
       <c r="J2" s="255">
         <v>46301</v>
       </c>
-      <c r="K2" s="182"/>
-      <c r="L2" s="183" t="s">
+      <c r="K2" s="255">
+        <v>46302</v>
+      </c>
+      <c r="L2" s="255">
+        <v>46303</v>
+      </c>
+      <c r="M2" s="182"/>
+      <c r="N2" s="183" t="s">
         <v>325</v>
       </c>
-      <c r="M2" s="184" t="s">
+      <c r="O2" s="184" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="185" t="s">
         <v>54</v>
       </c>
@@ -6672,17 +6692,23 @@
       <c r="J3" s="178" t="s">
         <v>233</v>
       </c>
-      <c r="K3" s="179"/>
-      <c r="L3" s="188"/>
+      <c r="K3" s="178" t="s">
+        <v>237</v>
+      </c>
+      <c r="L3" s="178" t="s">
+        <v>236</v>
+      </c>
       <c r="M3" s="179"/>
-      <c r="T3" s="132" t="s">
+      <c r="N3" s="188"/>
+      <c r="O3" s="179"/>
+      <c r="V3" s="132" t="s">
         <v>198</v>
       </c>
-      <c r="U3" s="132">
+      <c r="W3" s="132">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="141" t="s">
         <v>216</v>
       </c>
@@ -6711,23 +6737,27 @@
       <c r="J4" s="157">
         <v>22112</v>
       </c>
-      <c r="K4" s="210"/>
-      <c r="L4" s="170">
-        <f t="shared" ref="L4:L35" si="0">SUM(H4:K4)</f>
-        <v>15268</v>
-      </c>
-      <c r="M4" s="148">
-        <f t="shared" ref="M4:M35" si="1">IFERROR(L4/F4*100,0)/10000000</f>
-        <v>0.30536000000000002</v>
-      </c>
-      <c r="T4" s="132" t="s">
+      <c r="K4" s="157">
+        <v>29052</v>
+      </c>
+      <c r="L4" s="157"/>
+      <c r="M4" s="210"/>
+      <c r="N4" s="170">
+        <f t="shared" ref="N4:N35" si="0">SUM(H4:M4)</f>
+        <v>44320</v>
+      </c>
+      <c r="O4" s="148">
+        <f t="shared" ref="O4:O35" si="1">IFERROR(N4/F4*100,0)/10000000</f>
+        <v>0.88639999999999997</v>
+      </c>
+      <c r="V4" s="132" t="s">
         <v>170</v>
       </c>
-      <c r="U4" s="132">
+      <c r="W4" s="132">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="141" t="s">
         <v>30</v>
       </c>
@@ -6756,17 +6786,21 @@
       <c r="J5" s="146">
         <v>205000</v>
       </c>
-      <c r="K5" s="173"/>
-      <c r="L5" s="170">
+      <c r="K5" s="146">
+        <v>94938</v>
+      </c>
+      <c r="L5" s="146"/>
+      <c r="M5" s="173"/>
+      <c r="N5" s="170">
         <f t="shared" si="0"/>
-        <v>-798</v>
-      </c>
-      <c r="M5" s="148">
+        <v>94140</v>
+      </c>
+      <c r="O5" s="148">
         <f t="shared" si="1"/>
-        <v>-2.66E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.31380000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="141" t="s">
         <v>323</v>
       </c>
@@ -6795,17 +6829,21 @@
       <c r="J6" s="146">
         <v>-20800</v>
       </c>
-      <c r="K6" s="173"/>
-      <c r="L6" s="170">
+      <c r="K6" s="146">
+        <v>50440</v>
+      </c>
+      <c r="L6" s="146"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="170">
         <f t="shared" si="0"/>
-        <v>-23073</v>
-      </c>
-      <c r="M6" s="148">
+        <v>27367</v>
+      </c>
+      <c r="O6" s="148">
         <f t="shared" si="1"/>
-        <v>-0.23072999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.27367000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="141" t="s">
         <v>134</v>
       </c>
@@ -6834,21 +6872,25 @@
       <c r="J7" s="146">
         <v>-49000</v>
       </c>
-      <c r="K7" s="173"/>
-      <c r="L7" s="170">
+      <c r="K7" s="146">
+        <v>-140210</v>
+      </c>
+      <c r="L7" s="146"/>
+      <c r="M7" s="173"/>
+      <c r="N7" s="170">
         <f t="shared" si="0"/>
-        <v>-67000</v>
-      </c>
-      <c r="M7" s="148">
+        <v>-207210</v>
+      </c>
+      <c r="O7" s="148">
         <f t="shared" si="1"/>
-        <v>-0.2233333333333333</v>
-      </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="133">
-        <v>314093</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.69069999999999998</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="133">
+        <v>-14254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="141" t="s">
         <v>217</v>
       </c>
@@ -6877,21 +6919,25 @@
       <c r="J8" s="146">
         <v>19770</v>
       </c>
-      <c r="K8" s="173"/>
-      <c r="L8" s="170">
+      <c r="K8" s="146">
+        <v>18290</v>
+      </c>
+      <c r="L8" s="146"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="170">
         <f t="shared" si="0"/>
-        <v>90050</v>
-      </c>
-      <c r="M8" s="148">
+        <v>108340</v>
+      </c>
+      <c r="O8" s="148">
         <f t="shared" si="1"/>
-        <v>0.60033333333333339</v>
-      </c>
-      <c r="O8" s="133">
-        <v>1102060</v>
-      </c>
-      <c r="P8" s="133"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.72226666666666672</v>
+      </c>
+      <c r="Q8" s="133">
+        <v>468159</v>
+      </c>
+      <c r="R8" s="133"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="141" t="s">
         <v>313</v>
       </c>
@@ -6918,24 +6964,28 @@
       <c r="J9" s="146">
         <v>-8734</v>
       </c>
-      <c r="K9" s="173"/>
-      <c r="L9" s="170">
+      <c r="K9" s="146">
+        <v>4948</v>
+      </c>
+      <c r="L9" s="146"/>
+      <c r="M9" s="173"/>
+      <c r="N9" s="170">
         <f t="shared" si="0"/>
-        <v>37266</v>
-      </c>
-      <c r="M9" s="148">
+        <v>42214</v>
+      </c>
+      <c r="O9" s="148">
         <f t="shared" si="1"/>
-        <v>0.62109999999999999</v>
-      </c>
-      <c r="O9" s="133">
-        <v>1416153</v>
-      </c>
-      <c r="P9" s="133">
-        <f>(O9+O8)/10000000*13780</f>
-        <v>3470.0975140000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.70356666666666667</v>
+      </c>
+      <c r="Q9" s="133">
+        <v>453904</v>
+      </c>
+      <c r="R9" s="133">
+        <f>(Q9+Q8)/10000000*13780</f>
+        <v>1270.6028140000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>35</v>
       </c>
@@ -6964,19 +7014,23 @@
       <c r="J10" s="146">
         <v>0</v>
       </c>
-      <c r="K10" s="173"/>
-      <c r="L10" s="170">
+      <c r="K10" s="146">
+        <v>13730</v>
+      </c>
+      <c r="L10" s="146"/>
+      <c r="M10" s="173"/>
+      <c r="N10" s="170">
         <f t="shared" si="0"/>
-        <v>-170250</v>
-      </c>
-      <c r="M10" s="148">
+        <v>-156520</v>
+      </c>
+      <c r="O10" s="148">
         <f t="shared" si="1"/>
-        <v>-0.1135</v>
-      </c>
-      <c r="O10" s="133"/>
-      <c r="P10" s="133"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.10434666666666666</v>
+      </c>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="142" t="s">
         <v>137</v>
       </c>
@@ -7005,19 +7059,23 @@
       <c r="J11" s="146">
         <v>170100</v>
       </c>
-      <c r="K11" s="173"/>
-      <c r="L11" s="170">
+      <c r="K11" s="146">
+        <v>0</v>
+      </c>
+      <c r="L11" s="146"/>
+      <c r="M11" s="173"/>
+      <c r="N11" s="170">
         <f t="shared" si="0"/>
         <v>170431</v>
       </c>
-      <c r="M11" s="148">
+      <c r="O11" s="148">
         <f t="shared" si="1"/>
         <v>0.2840516666666667</v>
       </c>
-      <c r="O11" s="133"/>
-      <c r="P11" s="133"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="142" t="s">
         <v>42</v>
       </c>
@@ -7046,19 +7104,23 @@
       <c r="J12" s="146">
         <v>330</v>
       </c>
-      <c r="K12" s="173"/>
-      <c r="L12" s="170">
+      <c r="K12" s="146">
+        <v>-1616</v>
+      </c>
+      <c r="L12" s="146"/>
+      <c r="M12" s="173"/>
+      <c r="N12" s="170">
         <f t="shared" si="0"/>
-        <v>-322</v>
-      </c>
-      <c r="M12" s="148">
+        <v>-1938</v>
+      </c>
+      <c r="O12" s="148">
         <f t="shared" si="1"/>
-        <v>-3.2200000000000002E-3</v>
-      </c>
-      <c r="O12" s="133"/>
-      <c r="P12" s="133"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-1.9380000000000001E-2</v>
+      </c>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="141" t="s">
         <v>212</v>
       </c>
@@ -7087,19 +7149,23 @@
       <c r="J13" s="146">
         <v>41753</v>
       </c>
-      <c r="K13" s="173"/>
-      <c r="L13" s="170">
+      <c r="K13" s="146">
+        <v>0</v>
+      </c>
+      <c r="L13" s="146"/>
+      <c r="M13" s="173"/>
+      <c r="N13" s="170">
         <f t="shared" si="0"/>
         <v>68353</v>
       </c>
-      <c r="M13" s="148">
+      <c r="O13" s="148">
         <f t="shared" si="1"/>
         <v>0.27341199999999999</v>
       </c>
-      <c r="O13" s="133"/>
-      <c r="P13" s="133"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q13" s="133"/>
+      <c r="R13" s="133"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="141" t="s">
         <v>51</v>
       </c>
@@ -7128,29 +7194,33 @@
       <c r="J14" s="146">
         <v>43482</v>
       </c>
-      <c r="K14" s="173"/>
-      <c r="L14" s="170">
+      <c r="K14" s="146">
+        <v>0</v>
+      </c>
+      <c r="L14" s="146"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="170">
         <f t="shared" si="0"/>
         <v>77903</v>
       </c>
-      <c r="M14" s="148">
+      <c r="O14" s="148">
         <f t="shared" si="1"/>
         <v>0.35410454545454545</v>
       </c>
-      <c r="O14" s="133"/>
-      <c r="P14" s="192">
-        <f>P7-P9</f>
-        <v>310622.90248599998</v>
-      </c>
-      <c r="S14" s="132">
+      <c r="Q14" s="133"/>
+      <c r="R14" s="192">
+        <f>R7-R9</f>
+        <v>-15524.602814</v>
+      </c>
+      <c r="U14" s="132">
         <v>116185</v>
       </c>
-      <c r="U14" s="132">
-        <f>S14+P14</f>
-        <v>426807.90248599998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W14" s="132">
+        <f>U14+R14</f>
+        <v>100660.397186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="141" t="s">
         <v>43</v>
       </c>
@@ -7179,17 +7249,21 @@
       <c r="J15" s="146">
         <v>19700</v>
       </c>
-      <c r="K15" s="173"/>
-      <c r="L15" s="170">
+      <c r="K15" s="146">
+        <v>-6218</v>
+      </c>
+      <c r="L15" s="146"/>
+      <c r="M15" s="173"/>
+      <c r="N15" s="170">
         <f t="shared" si="0"/>
-        <v>20500</v>
-      </c>
-      <c r="M15" s="148">
+        <v>14282</v>
+      </c>
+      <c r="O15" s="148">
         <f t="shared" si="1"/>
-        <v>0.20499999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.14282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="141" t="s">
         <v>24</v>
       </c>
@@ -7218,28 +7292,32 @@
       <c r="J16" s="146">
         <v>0</v>
       </c>
-      <c r="K16" s="173"/>
-      <c r="L16" s="170">
+      <c r="K16" s="146">
+        <v>0</v>
+      </c>
+      <c r="L16" s="146"/>
+      <c r="M16" s="173"/>
+      <c r="N16" s="170">
         <f t="shared" si="0"/>
         <v>-38551</v>
       </c>
-      <c r="M16" s="148">
+      <c r="O16" s="148">
         <f t="shared" si="1"/>
         <v>-0.15420400000000001</v>
       </c>
-      <c r="U16" s="132">
+      <c r="W16" s="132">
         <v>4000000</v>
       </c>
-      <c r="V16" s="132">
-        <f>U16*7/100</f>
+      <c r="X16" s="132">
+        <f>W16*7/100</f>
         <v>280000</v>
       </c>
-      <c r="X16" s="132">
+      <c r="Z16" s="132">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="141" t="s">
         <v>23</v>
       </c>
@@ -7268,21 +7346,25 @@
       <c r="J17" s="146">
         <v>0</v>
       </c>
-      <c r="K17" s="173"/>
-      <c r="L17" s="170">
+      <c r="K17" s="146">
+        <v>0</v>
+      </c>
+      <c r="L17" s="146"/>
+      <c r="M17" s="173"/>
+      <c r="N17" s="170">
         <f t="shared" si="0"/>
         <v>-34123</v>
       </c>
-      <c r="M17" s="148">
+      <c r="O17" s="148">
         <f t="shared" si="1"/>
         <v>-8.5307499999999994E-2</v>
       </c>
-      <c r="V17" s="132">
-        <f>V16/12</f>
+      <c r="X17" s="132">
+        <f>X16/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="141" t="s">
         <v>165</v>
       </c>
@@ -7311,17 +7393,21 @@
       <c r="J18" s="146">
         <v>65000</v>
       </c>
-      <c r="K18" s="173"/>
-      <c r="L18" s="170">
+      <c r="K18" s="146">
+        <v>-95099</v>
+      </c>
+      <c r="L18" s="146"/>
+      <c r="M18" s="173"/>
+      <c r="N18" s="170">
         <f t="shared" si="0"/>
-        <v>44814</v>
-      </c>
-      <c r="M18" s="148">
+        <v>-50285</v>
+      </c>
+      <c r="O18" s="148">
         <f t="shared" si="1"/>
-        <v>0.29876000000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.33523333333333333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="141" t="s">
         <v>110</v>
       </c>
@@ -7350,20 +7436,24 @@
       <c r="J19" s="146">
         <v>0</v>
       </c>
-      <c r="K19" s="173"/>
-      <c r="L19" s="170">
+      <c r="K19" s="146">
+        <v>0</v>
+      </c>
+      <c r="L19" s="146"/>
+      <c r="M19" s="173"/>
+      <c r="N19" s="170">
         <f t="shared" si="0"/>
         <v>-150688</v>
       </c>
-      <c r="M19" s="148">
+      <c r="O19" s="148">
         <f t="shared" si="1"/>
         <v>-1.3698909090909093</v>
       </c>
-      <c r="Q19" s="132">
+      <c r="S19" s="132">
         <v>-132700</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="141" t="s">
         <v>319</v>
       </c>
@@ -7392,20 +7482,24 @@
       <c r="J20" s="146">
         <v>-3830</v>
       </c>
-      <c r="K20" s="173"/>
-      <c r="L20" s="170">
+      <c r="K20" s="146">
+        <v>7212</v>
+      </c>
+      <c r="L20" s="146"/>
+      <c r="M20" s="173"/>
+      <c r="N20" s="170">
         <f t="shared" si="0"/>
-        <v>-75454</v>
-      </c>
-      <c r="M20" s="148">
+        <v>-68242</v>
+      </c>
+      <c r="O20" s="148">
         <f t="shared" si="1"/>
-        <v>-3.01816</v>
-      </c>
-      <c r="Q20" s="132">
+        <v>-2.7296800000000001</v>
+      </c>
+      <c r="S20" s="132">
         <v>-52140</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="141" t="s">
         <v>316</v>
       </c>
@@ -7434,20 +7528,24 @@
       <c r="J21" s="146">
         <v>0</v>
       </c>
-      <c r="K21" s="173"/>
-      <c r="L21" s="170">
+      <c r="K21" s="146">
+        <v>0</v>
+      </c>
+      <c r="L21" s="146"/>
+      <c r="M21" s="173"/>
+      <c r="N21" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M21" s="148">
+      <c r="O21" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S21" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="141" t="s">
         <v>317</v>
       </c>
@@ -7476,17 +7574,21 @@
       <c r="J22" s="146">
         <v>0</v>
       </c>
-      <c r="K22" s="173"/>
-      <c r="L22" s="170">
+      <c r="K22" s="146">
+        <v>0</v>
+      </c>
+      <c r="L22" s="146"/>
+      <c r="M22" s="173"/>
+      <c r="N22" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M22" s="148">
+      <c r="O22" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="141" t="s">
         <v>32</v>
       </c>
@@ -7515,17 +7617,21 @@
       <c r="J23" s="146">
         <v>39988</v>
       </c>
-      <c r="K23" s="173"/>
-      <c r="L23" s="170">
+      <c r="K23" s="146">
+        <v>38700</v>
+      </c>
+      <c r="L23" s="146"/>
+      <c r="M23" s="173"/>
+      <c r="N23" s="170">
         <f t="shared" si="0"/>
-        <v>-10377</v>
-      </c>
-      <c r="M23" s="148">
+        <v>28323</v>
+      </c>
+      <c r="O23" s="148">
         <f t="shared" si="1"/>
-        <v>-9.4336363636363621E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.25748181818181815</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="141" t="s">
         <v>97</v>
       </c>
@@ -7554,17 +7660,21 @@
       <c r="J24" s="146">
         <v>145750</v>
       </c>
-      <c r="K24" s="173"/>
-      <c r="L24" s="170">
+      <c r="K24" s="146">
+        <v>-128600</v>
+      </c>
+      <c r="L24" s="146"/>
+      <c r="M24" s="173"/>
+      <c r="N24" s="170">
         <f t="shared" si="0"/>
-        <v>66800</v>
-      </c>
-      <c r="M24" s="148">
+        <v>-61800</v>
+      </c>
+      <c r="O24" s="148">
         <f t="shared" si="1"/>
-        <v>0.29043478260869571</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.26869565217391306</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="141" t="s">
         <v>302</v>
       </c>
@@ -7591,17 +7701,21 @@
       <c r="J25" s="146">
         <v>-13000</v>
       </c>
-      <c r="K25" s="173"/>
-      <c r="L25" s="170">
+      <c r="K25" s="146">
+        <v>-2835</v>
+      </c>
+      <c r="L25" s="146"/>
+      <c r="M25" s="173"/>
+      <c r="N25" s="170">
         <f t="shared" si="0"/>
-        <v>2726</v>
-      </c>
-      <c r="M25" s="148">
+        <v>-109</v>
+      </c>
+      <c r="O25" s="148">
         <f t="shared" si="1"/>
-        <v>0.1363</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-5.45E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="141" t="s">
         <v>29</v>
       </c>
@@ -7630,17 +7744,21 @@
       <c r="J26" s="146">
         <v>1100</v>
       </c>
-      <c r="K26" s="173"/>
-      <c r="L26" s="170">
+      <c r="K26" s="146">
+        <v>0</v>
+      </c>
+      <c r="L26" s="146"/>
+      <c r="M26" s="173"/>
+      <c r="N26" s="170">
         <f t="shared" si="0"/>
         <v>-115600</v>
       </c>
-      <c r="M26" s="148">
+      <c r="O26" s="148">
         <f t="shared" si="1"/>
         <v>-0.23119999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="141" t="s">
         <v>28</v>
       </c>
@@ -7669,17 +7787,21 @@
       <c r="J27" s="146">
         <v>11535</v>
       </c>
-      <c r="K27" s="173"/>
-      <c r="L27" s="170">
+      <c r="K27" s="146">
+        <v>302380</v>
+      </c>
+      <c r="L27" s="146"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="170">
         <f t="shared" si="0"/>
-        <v>110335</v>
-      </c>
-      <c r="M27" s="148">
+        <v>412715</v>
+      </c>
+      <c r="O27" s="148">
         <f t="shared" si="1"/>
-        <v>0.110335</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0.412715</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="141" t="s">
         <v>65</v>
       </c>
@@ -7708,17 +7830,21 @@
       <c r="J28" s="146">
         <v>310622</v>
       </c>
-      <c r="K28" s="173"/>
-      <c r="L28" s="170">
+      <c r="K28" s="146">
+        <v>0</v>
+      </c>
+      <c r="L28" s="146"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="170">
         <f t="shared" si="0"/>
         <v>401130</v>
       </c>
-      <c r="M28" s="148">
+      <c r="O28" s="148">
         <f t="shared" si="1"/>
         <v>0.80225999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="140" t="s">
         <v>34</v>
       </c>
@@ -7747,17 +7873,21 @@
       <c r="J29" s="146">
         <v>0</v>
       </c>
-      <c r="K29" s="173"/>
-      <c r="L29" s="170">
+      <c r="K29" s="146">
+        <v>2600</v>
+      </c>
+      <c r="L29" s="146"/>
+      <c r="M29" s="173"/>
+      <c r="N29" s="170">
         <f t="shared" si="0"/>
-        <v>-110750</v>
-      </c>
-      <c r="M29" s="148">
+        <v>-108150</v>
+      </c>
+      <c r="O29" s="148">
         <f t="shared" si="1"/>
-        <v>-0.2215</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-0.21629999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="140" t="s">
         <v>131</v>
       </c>
@@ -7786,17 +7916,21 @@
       <c r="J30" s="146">
         <v>48621</v>
       </c>
-      <c r="K30" s="173"/>
-      <c r="L30" s="170">
+      <c r="K30" s="146">
+        <v>-7694</v>
+      </c>
+      <c r="L30" s="146"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="170">
         <f t="shared" si="0"/>
-        <v>11493</v>
-      </c>
-      <c r="M30" s="148">
+        <v>3799</v>
+      </c>
+      <c r="O30" s="148">
         <f t="shared" si="1"/>
-        <v>0.22986000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+        <v>7.5980000000000006E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>67</v>
       </c>
@@ -7825,18 +7959,22 @@
       <c r="J31" s="146">
         <v>42650</v>
       </c>
-      <c r="K31" s="173"/>
-      <c r="L31" s="170">
+      <c r="K31" s="146">
+        <v>1293</v>
+      </c>
+      <c r="L31" s="146"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="170">
         <f t="shared" si="0"/>
-        <v>80175</v>
-      </c>
-      <c r="M31" s="148">
+        <v>81468</v>
+      </c>
+      <c r="O31" s="148">
         <f t="shared" si="1"/>
-        <v>2.004375</v>
-      </c>
-      <c r="P31" s="133"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2.0367000000000002</v>
+      </c>
+      <c r="R31" s="133"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="141" t="s">
         <v>31</v>
       </c>
@@ -7865,21 +8003,25 @@
       <c r="J32" s="146">
         <v>81490</v>
       </c>
-      <c r="K32" s="173"/>
-      <c r="L32" s="170">
+      <c r="K32" s="146">
+        <v>-98197</v>
+      </c>
+      <c r="L32" s="146"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="170">
         <f t="shared" si="0"/>
-        <v>-49332</v>
-      </c>
-      <c r="M32" s="148">
+        <v>-147529</v>
+      </c>
+      <c r="O32" s="148">
         <f t="shared" si="1"/>
-        <v>-0.12333</v>
-      </c>
-      <c r="O32" s="5"/>
-      <c r="P32" s="133">
-        <v>106500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-0.3688225</v>
+      </c>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="133">
+        <v>18950</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="141" t="s">
         <v>104</v>
       </c>
@@ -7908,19 +8050,23 @@
       <c r="J33" s="146">
         <v>51300</v>
       </c>
-      <c r="K33" s="173"/>
-      <c r="L33" s="170">
+      <c r="K33" s="146">
+        <v>-13148</v>
+      </c>
+      <c r="L33" s="146"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="170">
         <f t="shared" si="0"/>
-        <v>22822</v>
-      </c>
-      <c r="M33" s="148">
+        <v>9674</v>
+      </c>
+      <c r="O33" s="148">
         <f t="shared" si="1"/>
-        <v>0.22822000000000001</v>
-      </c>
-      <c r="O33" s="5"/>
-      <c r="P33" s="133"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9.6740000000000007E-2</v>
+      </c>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="133"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="141" t="s">
         <v>314</v>
       </c>
@@ -7947,24 +8093,28 @@
       <c r="J34" s="146">
         <v>0</v>
       </c>
-      <c r="K34" s="173"/>
-      <c r="L34" s="170">
+      <c r="K34" s="146">
+        <v>0</v>
+      </c>
+      <c r="L34" s="146"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M34" s="148">
+      <c r="O34" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O34" s="133">
-        <v>592248</v>
-      </c>
-      <c r="P34" s="133">
-        <f>(O35+O34)/10000000*13780</f>
-        <v>1785.1135639999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" s="133">
+        <v>585803</v>
+      </c>
+      <c r="R34" s="133">
+        <f>(Q35+Q34)/10000000*13780</f>
+        <v>1640.587546</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="141" t="s">
         <v>229</v>
       </c>
@@ -7993,21 +8143,25 @@
       <c r="J35" s="146">
         <v>19175</v>
       </c>
-      <c r="K35" s="173"/>
-      <c r="L35" s="170">
+      <c r="K35" s="146">
+        <v>-15524</v>
+      </c>
+      <c r="L35" s="146"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="170">
         <f t="shared" si="0"/>
-        <v>6629</v>
-      </c>
-      <c r="M35" s="148">
+        <v>-8895</v>
+      </c>
+      <c r="O35" s="148">
         <f t="shared" si="1"/>
-        <v>0.13258</v>
-      </c>
-      <c r="O35" s="133">
-        <v>703190</v>
-      </c>
-      <c r="P35" s="133"/>
-    </row>
-    <row r="36" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-0.1779</v>
+      </c>
+      <c r="Q35" s="133">
+        <v>604754</v>
+      </c>
+      <c r="R35" s="133"/>
+    </row>
+    <row r="36" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="141" t="s">
         <v>45</v>
       </c>
@@ -8036,22 +8190,26 @@
       <c r="J36" s="146">
         <v>276700</v>
       </c>
-      <c r="K36" s="173"/>
-      <c r="L36" s="170">
-        <f t="shared" ref="L36:L67" si="2">SUM(H36:K36)</f>
-        <v>104100</v>
-      </c>
-      <c r="M36" s="148">
-        <f t="shared" ref="M36:M67" si="3">IFERROR(L36/F36*100,0)/10000000</f>
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="O36" s="133"/>
-      <c r="P36" s="133">
-        <f>+P32-P34</f>
-        <v>104714.886436</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K36" s="146">
+        <v>79524</v>
+      </c>
+      <c r="L36" s="146"/>
+      <c r="M36" s="173"/>
+      <c r="N36" s="170">
+        <f t="shared" ref="N36:N67" si="2">SUM(H36:M36)</f>
+        <v>183624</v>
+      </c>
+      <c r="O36" s="148">
+        <f t="shared" ref="O36:O67" si="3">IFERROR(N36/F36*100,0)/10000000</f>
+        <v>0.61207999999999996</v>
+      </c>
+      <c r="Q36" s="133"/>
+      <c r="R36" s="133">
+        <f>+R32-R34</f>
+        <v>17309.412454000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="141" t="s">
         <v>292</v>
       </c>
@@ -8078,19 +8236,23 @@
       <c r="J37" s="146">
         <v>-7417</v>
       </c>
-      <c r="K37" s="173"/>
-      <c r="L37" s="170">
+      <c r="K37" s="146">
+        <v>-19285</v>
+      </c>
+      <c r="L37" s="146"/>
+      <c r="M37" s="173"/>
+      <c r="N37" s="170">
         <f t="shared" si="2"/>
-        <v>25653</v>
-      </c>
-      <c r="M37" s="148">
+        <v>6368</v>
+      </c>
+      <c r="O37" s="148">
         <f t="shared" si="3"/>
-        <v>2.5653000000000001</v>
-      </c>
-      <c r="O37" s="133"/>
-      <c r="P37" s="133"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.63680000000000003</v>
+      </c>
+      <c r="Q37" s="133"/>
+      <c r="R37" s="133"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="141" t="s">
         <v>132</v>
       </c>
@@ -8119,19 +8281,23 @@
       <c r="J38" s="146">
         <v>12200</v>
       </c>
-      <c r="K38" s="173"/>
-      <c r="L38" s="170">
+      <c r="K38" s="146">
+        <v>-16500</v>
+      </c>
+      <c r="L38" s="146"/>
+      <c r="M38" s="173"/>
+      <c r="N38" s="170">
         <f t="shared" si="2"/>
-        <v>19800</v>
-      </c>
-      <c r="M38" s="148">
+        <v>3300</v>
+      </c>
+      <c r="O38" s="148">
         <f t="shared" si="3"/>
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="O38" s="133"/>
-      <c r="P38" s="133"/>
-    </row>
-    <row r="39" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="Q38" s="133"/>
+      <c r="R38" s="133"/>
+    </row>
+    <row r="39" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="141" t="s">
         <v>48</v>
       </c>
@@ -8160,19 +8326,23 @@
       <c r="J39" s="146">
         <v>174856</v>
       </c>
-      <c r="K39" s="173"/>
-      <c r="L39" s="170">
+      <c r="K39" s="146">
+        <v>-85245</v>
+      </c>
+      <c r="L39" s="146"/>
+      <c r="M39" s="173"/>
+      <c r="N39" s="170">
         <f t="shared" si="2"/>
-        <v>-85984</v>
-      </c>
-      <c r="M39" s="148">
+        <v>-171229</v>
+      </c>
+      <c r="O39" s="148">
         <f t="shared" si="3"/>
-        <v>-0.85984000000000005</v>
-      </c>
-      <c r="O39" s="133"/>
-      <c r="P39" s="133"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-1.7122900000000001</v>
+      </c>
+      <c r="Q39" s="133"/>
+      <c r="R39" s="133"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="141" t="s">
         <v>301</v>
       </c>
@@ -8199,18 +8369,22 @@
       <c r="J40" s="146">
         <v>-6862</v>
       </c>
-      <c r="K40" s="173"/>
-      <c r="L40" s="170">
+      <c r="K40" s="146">
+        <v>-21500</v>
+      </c>
+      <c r="L40" s="146"/>
+      <c r="M40" s="173"/>
+      <c r="N40" s="170">
         <f t="shared" si="2"/>
-        <v>4265</v>
-      </c>
-      <c r="M40" s="148">
+        <v>-17235</v>
+      </c>
+      <c r="O40" s="148">
         <f t="shared" si="3"/>
-        <v>0.42649999999999999</v>
-      </c>
-      <c r="O40" s="133"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>-1.7235</v>
+      </c>
+      <c r="Q40" s="133"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="142" t="s">
         <v>168</v>
       </c>
@@ -8239,17 +8413,21 @@
       <c r="J41" s="146">
         <v>0</v>
       </c>
-      <c r="K41" s="173"/>
-      <c r="L41" s="170">
+      <c r="K41" s="146">
+        <v>0</v>
+      </c>
+      <c r="L41" s="146"/>
+      <c r="M41" s="173"/>
+      <c r="N41" s="170">
         <f t="shared" si="2"/>
         <v>2920</v>
       </c>
-      <c r="M41" s="148">
+      <c r="O41" s="148">
         <f t="shared" si="3"/>
         <v>7.3000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
         <v>202</v>
       </c>
@@ -8278,17 +8456,21 @@
       <c r="J42" s="146">
         <v>60600</v>
       </c>
-      <c r="K42" s="173"/>
-      <c r="L42" s="170">
+      <c r="K42" s="146">
+        <v>0</v>
+      </c>
+      <c r="L42" s="146"/>
+      <c r="M42" s="173"/>
+      <c r="N42" s="170">
         <f t="shared" si="2"/>
         <v>40600</v>
       </c>
-      <c r="M42" s="148">
+      <c r="O42" s="148">
         <f t="shared" si="3"/>
         <v>0.10150000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="142" t="s">
         <v>33</v>
       </c>
@@ -8317,17 +8499,21 @@
       <c r="J43" s="146">
         <v>307794</v>
       </c>
-      <c r="K43" s="173"/>
-      <c r="L43" s="170">
+      <c r="K43" s="146">
+        <v>-135130</v>
+      </c>
+      <c r="L43" s="146"/>
+      <c r="M43" s="173"/>
+      <c r="N43" s="170">
         <f t="shared" si="2"/>
-        <v>168258</v>
-      </c>
-      <c r="M43" s="148">
+        <v>33128</v>
+      </c>
+      <c r="O43" s="148">
         <f t="shared" si="3"/>
-        <v>0.56086000000000003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.11042666666666665</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="59" t="s">
         <v>306</v>
       </c>
@@ -8354,17 +8540,21 @@
       <c r="J44" s="150">
         <v>338000</v>
       </c>
-      <c r="K44" s="173"/>
-      <c r="L44" s="170">
+      <c r="K44" s="150">
+        <v>63150</v>
+      </c>
+      <c r="L44" s="150"/>
+      <c r="M44" s="173"/>
+      <c r="N44" s="170">
         <f t="shared" si="2"/>
-        <v>143600</v>
-      </c>
-      <c r="M44" s="148">
+        <v>206750</v>
+      </c>
+      <c r="O44" s="148">
         <f t="shared" si="3"/>
-        <v>0.14360000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.20674999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="59" t="s">
         <v>320</v>
       </c>
@@ -8389,17 +8579,21 @@
       <c r="J45" s="150">
         <v>0</v>
       </c>
-      <c r="K45" s="173"/>
-      <c r="L45" s="170">
+      <c r="K45" s="150">
+        <v>0</v>
+      </c>
+      <c r="L45" s="150"/>
+      <c r="M45" s="173"/>
+      <c r="N45" s="170">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M45" s="148">
+      <c r="O45" s="148">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="59" t="s">
         <v>197</v>
       </c>
@@ -8428,17 +8622,21 @@
       <c r="J46" s="150">
         <v>24836</v>
       </c>
-      <c r="K46" s="173"/>
-      <c r="L46" s="170">
+      <c r="K46" s="150">
+        <v>30076</v>
+      </c>
+      <c r="L46" s="150"/>
+      <c r="M46" s="173"/>
+      <c r="N46" s="170">
         <f t="shared" si="2"/>
-        <v>35409</v>
-      </c>
-      <c r="M46" s="148">
+        <v>65485</v>
+      </c>
+      <c r="O46" s="148">
         <f t="shared" si="3"/>
-        <v>0.70818000000000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.3097000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="59" t="s">
         <v>213</v>
       </c>
@@ -8467,17 +8665,21 @@
       <c r="J47" s="150">
         <v>168400</v>
       </c>
-      <c r="K47" s="173"/>
-      <c r="L47" s="170">
+      <c r="K47" s="150">
+        <v>0</v>
+      </c>
+      <c r="L47" s="150"/>
+      <c r="M47" s="173"/>
+      <c r="N47" s="170">
         <f t="shared" si="2"/>
         <v>306496</v>
       </c>
-      <c r="M47" s="148">
+      <c r="O47" s="148">
         <f t="shared" si="3"/>
         <v>0.4715323076923077</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>214</v>
       </c>
@@ -8506,17 +8708,21 @@
       <c r="J48" s="150">
         <v>0</v>
       </c>
-      <c r="K48" s="173"/>
-      <c r="L48" s="170">
+      <c r="K48" s="150">
+        <v>0</v>
+      </c>
+      <c r="L48" s="150"/>
+      <c r="M48" s="173"/>
+      <c r="N48" s="170">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M48" s="148">
+      <c r="O48" s="148">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>49</v>
       </c>
@@ -8545,17 +8751,21 @@
       <c r="J49" s="150">
         <v>43650</v>
       </c>
-      <c r="K49" s="173"/>
-      <c r="L49" s="170">
+      <c r="K49" s="150">
+        <v>0</v>
+      </c>
+      <c r="L49" s="150"/>
+      <c r="M49" s="173"/>
+      <c r="N49" s="170">
         <f t="shared" si="2"/>
         <v>56120</v>
       </c>
-      <c r="M49" s="148">
+      <c r="O49" s="148">
         <f t="shared" si="3"/>
         <v>0.18706666666666669</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="59"/>
       <c r="B50" s="59" t="s">
         <v>286</v>
@@ -8582,17 +8792,21 @@
       <c r="J50" s="150">
         <v>0</v>
       </c>
-      <c r="K50" s="173"/>
-      <c r="L50" s="170">
+      <c r="K50" s="150">
+        <v>520</v>
+      </c>
+      <c r="L50" s="150"/>
+      <c r="M50" s="173"/>
+      <c r="N50" s="170">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="M50" s="148">
+        <v>570</v>
+      </c>
+      <c r="O50" s="148">
         <f t="shared" si="3"/>
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="59" t="s">
         <v>288</v>
       </c>
@@ -8621,17 +8835,21 @@
       <c r="J51" s="150">
         <v>104715</v>
       </c>
-      <c r="K51" s="173"/>
-      <c r="L51" s="170">
+      <c r="K51" s="150">
+        <v>17309</v>
+      </c>
+      <c r="L51" s="150"/>
+      <c r="M51" s="173"/>
+      <c r="N51" s="170">
         <f t="shared" si="2"/>
-        <v>83647</v>
-      </c>
-      <c r="M51" s="148">
+        <v>100956</v>
+      </c>
+      <c r="O51" s="148">
         <f t="shared" si="3"/>
-        <v>0.16729400000000003</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.20191200000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="24"/>
       <c r="B52" s="25"/>
       <c r="C52" s="26"/>
@@ -8653,18 +8871,26 @@
       </c>
       <c r="K52" s="253">
         <f>SUM(K4:K51)</f>
-        <v>0</v>
+        <v>-32639</v>
       </c>
       <c r="L52" s="253">
+        <f>SUM(L4:L51)</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="253">
+        <f>SUM(M4:M51)</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="253">
         <f t="shared" si="2"/>
-        <v>1285311</v>
-      </c>
-      <c r="M52" s="254">
+        <v>1252672</v>
+      </c>
+      <c r="O52" s="254">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="249"/>
       <c r="B53" s="249"/>
       <c r="C53" s="249"/>
@@ -8677,9 +8903,11 @@
       <c r="J53" s="249"/>
       <c r="K53" s="249"/>
       <c r="L53" s="249"/>
-      <c r="M53" s="251"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M53" s="249"/>
+      <c r="N53" s="249"/>
+      <c r="O53" s="251"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="201" t="s">
         <v>241</v>
       </c>
@@ -8708,17 +8936,21 @@
       <c r="J54" s="161">
         <v>160555</v>
       </c>
-      <c r="K54" s="245"/>
-      <c r="L54" s="246">
-        <f>SUM(H54:K54)</f>
-        <v>135526</v>
-      </c>
-      <c r="M54" s="247">
-        <f>IFERROR(L54/F54*100,0)/10000000</f>
-        <v>0.4517533333333334</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K54" s="161">
+        <v>15600</v>
+      </c>
+      <c r="L54" s="161"/>
+      <c r="M54" s="245"/>
+      <c r="N54" s="246">
+        <f>SUM(H54:M54)</f>
+        <v>151126</v>
+      </c>
+      <c r="O54" s="247">
+        <f>IFERROR(N54/F54*100,0)/10000000</f>
+        <v>0.50375333333333339</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="201" t="s">
         <v>273</v>
       </c>
@@ -8745,17 +8977,21 @@
       <c r="J55" s="161">
         <v>149000</v>
       </c>
-      <c r="K55" s="173"/>
-      <c r="L55" s="170">
-        <f>SUM(H55:K55)</f>
+      <c r="K55" s="161">
+        <v>0</v>
+      </c>
+      <c r="L55" s="161"/>
+      <c r="M55" s="173"/>
+      <c r="N55" s="170">
+        <f>SUM(H55:M55)</f>
         <v>98000</v>
       </c>
-      <c r="M55" s="148">
-        <f>IFERROR(L55/F55*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O55" s="148">
+        <f>IFERROR(N55/F55*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="199"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -8764,7 +9000,7 @@
       <c r="F56" s="74"/>
       <c r="G56" s="17"/>
       <c r="H56" s="169">
-        <f t="shared" ref="H56:J56" si="4">SUM(H54:H55)</f>
+        <f t="shared" ref="H56:L56" si="4">SUM(H54:H55)</f>
         <v>5771</v>
       </c>
       <c r="I56" s="169">
@@ -8776,129 +9012,137 @@
         <v>309555</v>
       </c>
       <c r="K56" s="169">
-        <f>SUM(K54:K55)</f>
-        <v>0</v>
-      </c>
-      <c r="L56" s="256">
-        <f>SUM(H56:K56)</f>
-        <v>233526</v>
-      </c>
-      <c r="M56" s="172"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P57" s="133"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O58" s="133"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O59" s="5"/>
-      <c r="P59" s="133"/>
-      <c r="Q59" s="236"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O60" s="133"/>
-      <c r="P60" s="133"/>
-      <c r="Q60" s="236"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O61" s="133"/>
-      <c r="P61" s="133"/>
-      <c r="Q61" s="236"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O62" s="133"/>
-      <c r="P62" s="133"/>
-      <c r="Q62" s="236"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O63" s="133"/>
-      <c r="P63" s="133"/>
-      <c r="Q63" s="236"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="O64" s="133"/>
-      <c r="P64" s="236"/>
-      <c r="Q64" s="236"/>
-    </row>
-    <row r="65" spans="15:17" x14ac:dyDescent="0.25">
-      <c r="O65" s="236"/>
-      <c r="P65" s="236"/>
+        <f t="shared" si="4"/>
+        <v>15600</v>
+      </c>
+      <c r="L56" s="169">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="169">
+        <f>SUM(M54:M55)</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="256">
+        <f>SUM(H56:M56)</f>
+        <v>249126</v>
+      </c>
+      <c r="O56" s="172"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R57" s="133"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q58" s="133"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q59" s="5"/>
+      <c r="R59" s="133"/>
+      <c r="S59" s="236"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q60" s="133"/>
+      <c r="R60" s="133"/>
+      <c r="S60" s="236"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q61" s="133"/>
+      <c r="R61" s="133"/>
+      <c r="S61" s="236"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q62" s="133"/>
+      <c r="R62" s="133"/>
+      <c r="S62" s="236"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q63" s="133"/>
+      <c r="R63" s="133"/>
+      <c r="S63" s="236"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q64" s="133"/>
+      <c r="R64" s="236"/>
+      <c r="S64" s="236"/>
+    </row>
+    <row r="65" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q65" s="236"/>
+      <c r="R65" s="236"/>
+      <c r="S65" s="236"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 M52:M53 M56 L39:M39 L23:M24 M10:M20 L10:L21 H2:M3 A54:M55 A34:L34 A35:K35 G36:K36 L41:M51 L5:M9 L26:L33 M26:M32 A4:K33 L35:L37 M36 A37:K52 A56:K56">
-    <cfRule type="expression" dxfId="558" priority="17">
+  <conditionalFormatting sqref="G2 A3:G3 O52:O53 O56 N39:O39 N23:O24 O10:O20 N10:N21 H2:O3 A54:O55 A34:N34 A35:M35 G36:M36 N41:O51 N5:O9 N26:N33 O26:O32 A4:M33 N35:N37 O36 A37:M52 A56:M56">
+    <cfRule type="expression" dxfId="560" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M33">
-    <cfRule type="expression" dxfId="557" priority="16">
+  <conditionalFormatting sqref="O33">
+    <cfRule type="expression" dxfId="559" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:M4">
-    <cfRule type="expression" dxfId="556" priority="14">
+  <conditionalFormatting sqref="N4:O4">
+    <cfRule type="expression" dxfId="558" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M35">
-    <cfRule type="expression" dxfId="555" priority="13">
+  <conditionalFormatting sqref="O35">
+    <cfRule type="expression" dxfId="557" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M21">
-    <cfRule type="expression" dxfId="554" priority="12">
+  <conditionalFormatting sqref="O21">
+    <cfRule type="expression" dxfId="556" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L52">
-    <cfRule type="expression" dxfId="553" priority="11">
+  <conditionalFormatting sqref="N52">
+    <cfRule type="expression" dxfId="555" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M37">
-    <cfRule type="expression" dxfId="552" priority="10">
+  <conditionalFormatting sqref="O37">
+    <cfRule type="expression" dxfId="554" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L25:M25">
-    <cfRule type="expression" dxfId="551" priority="9">
+  <conditionalFormatting sqref="N25:O25">
+    <cfRule type="expression" dxfId="553" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L40:M40">
-    <cfRule type="expression" dxfId="550" priority="7">
+  <conditionalFormatting sqref="N40:O40">
+    <cfRule type="expression" dxfId="552" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L56">
-    <cfRule type="expression" dxfId="549" priority="6">
+  <conditionalFormatting sqref="N56">
+    <cfRule type="expression" dxfId="551" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38:M38">
-    <cfRule type="expression" dxfId="548" priority="5">
+  <conditionalFormatting sqref="N38:O38">
+    <cfRule type="expression" dxfId="550" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L22">
-    <cfRule type="expression" dxfId="547" priority="4">
+  <conditionalFormatting sqref="N22">
+    <cfRule type="expression" dxfId="549" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M22">
-    <cfRule type="expression" dxfId="546" priority="3">
+  <conditionalFormatting sqref="O22">
+    <cfRule type="expression" dxfId="548" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34">
-    <cfRule type="expression" dxfId="545" priority="2">
+  <conditionalFormatting sqref="O34">
+    <cfRule type="expression" dxfId="547" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:F36">
-    <cfRule type="expression" dxfId="544" priority="1">
+    <cfRule type="expression" dxfId="546" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9258,7 +9502,7 @@
       <c r="R6" s="158"/>
       <c r="S6" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>15268</v>
+        <v>44320</v>
       </c>
       <c r="T6" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9270,7 +9514,7 @@
       <c r="X6" s="131"/>
       <c r="Y6" s="153">
         <f t="shared" si="0"/>
-        <v>-537206</v>
+        <v>-508154</v>
       </c>
       <c r="Z6" s="167">
         <f t="shared" si="1"/>
@@ -9340,7 +9584,7 @@
       <c r="R7" s="158"/>
       <c r="S7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-798</v>
+        <v>94140</v>
       </c>
       <c r="T7" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9352,7 +9596,7 @@
       <c r="X7"/>
       <c r="Y7" s="153">
         <f t="shared" si="0"/>
-        <v>1241416</v>
+        <v>1336354</v>
       </c>
       <c r="Z7" s="167">
         <f t="shared" si="1"/>
@@ -9476,7 +9720,7 @@
       <c r="R9" s="158"/>
       <c r="S9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-23073</v>
+        <v>27367</v>
       </c>
       <c r="T9" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9487,7 +9731,7 @@
       <c r="W9" s="149"/>
       <c r="Y9" s="153">
         <f t="shared" ref="Y9" si="6">M9+P9+S9+V9</f>
-        <v>-159459</v>
+        <v>-109019</v>
       </c>
       <c r="Z9" s="167">
         <f t="shared" ref="Z9" si="7">(N9+Q9+T9+W9)</f>
@@ -9557,7 +9801,7 @@
       <c r="R10" s="158"/>
       <c r="S10" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-67000</v>
+        <v>-207210</v>
       </c>
       <c r="T10" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9568,7 +9812,7 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="153">
         <f t="shared" si="0"/>
-        <v>-1243067</v>
+        <v>-1383277</v>
       </c>
       <c r="Z10" s="167">
         <f t="shared" si="1"/>
@@ -9638,7 +9882,7 @@
       <c r="R11" s="158"/>
       <c r="S11" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>90050</v>
+        <v>108340</v>
       </c>
       <c r="T11" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9649,7 +9893,7 @@
       <c r="W11" s="149"/>
       <c r="Y11" s="153">
         <f t="shared" si="0"/>
-        <v>-311825</v>
+        <v>-293535</v>
       </c>
       <c r="Z11" s="167">
         <f t="shared" si="1"/>
@@ -9719,7 +9963,7 @@
       <c r="R12" s="158"/>
       <c r="S12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>37266</v>
+        <v>42214</v>
       </c>
       <c r="T12" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9730,7 +9974,7 @@
       <c r="W12" s="149"/>
       <c r="Y12" s="153">
         <f t="shared" ref="Y12" si="12">M12+P12+S12+V12</f>
-        <v>-52663</v>
+        <v>-47715</v>
       </c>
       <c r="Z12" s="167">
         <f t="shared" ref="Z12" si="13">(N12+Q12+T12+W12)</f>
@@ -9800,7 +10044,7 @@
       <c r="R13" s="158"/>
       <c r="S13" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-170250</v>
+        <v>-156520</v>
       </c>
       <c r="T13" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9812,7 +10056,7 @@
       <c r="X13"/>
       <c r="Y13" s="153">
         <f t="shared" si="0"/>
-        <v>-1154518</v>
+        <v>-1140788</v>
       </c>
       <c r="Z13" s="167">
         <f t="shared" si="1"/>
@@ -10290,7 +10534,7 @@
       <c r="R19" s="158"/>
       <c r="S19" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-322</v>
+        <v>-1938</v>
       </c>
       <c r="T19" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10301,7 +10545,7 @@
       <c r="W19" s="149"/>
       <c r="Y19" s="153">
         <f t="shared" si="0"/>
-        <v>2253</v>
+        <v>637</v>
       </c>
       <c r="Z19" s="167">
         <f t="shared" si="1"/>
@@ -10704,7 +10948,7 @@
       <c r="R24" s="158"/>
       <c r="S24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>20500</v>
+        <v>14282</v>
       </c>
       <c r="T24" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10715,7 +10959,7 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="153">
         <f t="shared" si="0"/>
-        <v>1766681</v>
+        <v>1760463</v>
       </c>
       <c r="Z24" s="167">
         <f t="shared" si="1"/>
@@ -11360,7 +11604,7 @@
       <c r="R32" s="158"/>
       <c r="S32" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>44814</v>
+        <v>-50285</v>
       </c>
       <c r="T32" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11372,7 +11616,7 @@
       <c r="X32"/>
       <c r="Y32" s="153">
         <f t="shared" si="0"/>
-        <v>-441191</v>
+        <v>-536290</v>
       </c>
       <c r="Z32" s="167">
         <f t="shared" si="1"/>
@@ -11523,7 +11767,7 @@
       <c r="R34" s="158"/>
       <c r="S34" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-10377</v>
+        <v>28323</v>
       </c>
       <c r="T34" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11534,7 +11778,7 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="153">
         <f t="shared" si="0"/>
-        <v>-158004</v>
+        <v>-119304</v>
       </c>
       <c r="Z34" s="167">
         <f t="shared" si="1"/>
@@ -11692,7 +11936,7 @@
       <c r="R36" s="158"/>
       <c r="S36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>66800</v>
+        <v>-61800</v>
       </c>
       <c r="T36" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11703,7 +11947,7 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="153">
         <f t="shared" si="0"/>
-        <v>2969426</v>
+        <v>2840826</v>
       </c>
       <c r="Z36" s="167">
         <f t="shared" si="1"/>
@@ -11771,7 +12015,7 @@
       <c r="R37" s="158"/>
       <c r="S37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>2726</v>
+        <v>-109</v>
       </c>
       <c r="T37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11782,7 +12026,7 @@
       <c r="W37" s="149"/>
       <c r="Y37" s="153">
         <f t="shared" ref="Y37" si="22">M37+P37+S37+V37</f>
-        <v>-40940</v>
+        <v>-43775</v>
       </c>
       <c r="Z37" s="167">
         <f t="shared" ref="Z37" si="23">(N37+Q37+T37+W37)</f>
@@ -11933,7 +12177,7 @@
       <c r="R39" s="158"/>
       <c r="S39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>110335</v>
+        <v>412715</v>
       </c>
       <c r="T39" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11945,7 +12189,7 @@
       <c r="X39" s="131"/>
       <c r="Y39" s="153">
         <f t="shared" ref="Y39:Y74" si="24">M39+P39+S39+V39</f>
-        <v>5391082</v>
+        <v>5693462</v>
       </c>
       <c r="Z39" s="167">
         <f t="shared" ref="Z39:Z74" si="25">(N39+Q39+T39+W39)</f>
@@ -12530,7 +12774,7 @@
       <c r="R46" s="158"/>
       <c r="S46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-110750</v>
+        <v>-108150</v>
       </c>
       <c r="T46" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12542,7 +12786,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="153">
         <f t="shared" si="24"/>
-        <v>662121</v>
+        <v>664721</v>
       </c>
       <c r="Z46" s="167">
         <f t="shared" si="25"/>
@@ -12613,7 +12857,7 @@
       <c r="R47" s="158"/>
       <c r="S47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>11493</v>
+        <v>3799</v>
       </c>
       <c r="T47" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12624,7 +12868,7 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="153">
         <f t="shared" si="24"/>
-        <v>-67557</v>
+        <v>-75251</v>
       </c>
       <c r="Z47" s="167">
         <f t="shared" si="25"/>
@@ -12782,7 +13026,7 @@
       <c r="R49" s="158"/>
       <c r="S49" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>80175</v>
+        <v>81468</v>
       </c>
       <c r="T49" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12793,7 +13037,7 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="153">
         <f t="shared" si="24"/>
-        <v>148440</v>
+        <v>149733</v>
       </c>
       <c r="Z49" s="167">
         <f t="shared" si="25"/>
@@ -13037,7 +13281,7 @@
       <c r="R52" s="158"/>
       <c r="S52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-49332</v>
+        <v>-147529</v>
       </c>
       <c r="T52" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13048,7 +13292,7 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="153">
         <f t="shared" si="24"/>
-        <v>145729</v>
+        <v>47532</v>
       </c>
       <c r="Z52" s="167">
         <f t="shared" si="25"/>
@@ -13118,7 +13362,7 @@
       <c r="R53" s="158"/>
       <c r="S53" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>22822</v>
+        <v>9674</v>
       </c>
       <c r="T53" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13129,7 +13373,7 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="153">
         <f t="shared" si="24"/>
-        <v>683071</v>
+        <v>669923</v>
       </c>
       <c r="Z53" s="167">
         <f t="shared" si="25"/>
@@ -13280,7 +13524,7 @@
       <c r="R55" s="158"/>
       <c r="S55" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>6629</v>
+        <v>-8895</v>
       </c>
       <c r="T55" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13292,7 +13536,7 @@
       <c r="X55" s="131"/>
       <c r="Y55" s="153">
         <f t="shared" si="24"/>
-        <v>-267396</v>
+        <v>-282920</v>
       </c>
       <c r="Z55" s="167">
         <f t="shared" si="25"/>
@@ -13363,7 +13607,7 @@
       <c r="R56" s="158"/>
       <c r="S56" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>104100</v>
+        <v>183624</v>
       </c>
       <c r="T56" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13374,7 +13618,7 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="153">
         <f t="shared" si="24"/>
-        <v>-4550235</v>
+        <v>-4470711</v>
       </c>
       <c r="Z56" s="167">
         <f t="shared" si="25"/>
@@ -13617,7 +13861,7 @@
       <c r="R59" s="158"/>
       <c r="S59" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>19800</v>
+        <v>3300</v>
       </c>
       <c r="T59" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13629,7 +13873,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="153">
         <f t="shared" si="24"/>
-        <v>52491</v>
+        <v>35991</v>
       </c>
       <c r="Z59" s="167">
         <f t="shared" si="25"/>
@@ -13706,7 +13950,7 @@
       <c r="R60" s="158"/>
       <c r="S60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-85984</v>
+        <v>-171229</v>
       </c>
       <c r="T60" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13717,7 +13961,7 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="153">
         <f t="shared" si="24"/>
-        <v>3593631</v>
+        <v>3508386</v>
       </c>
       <c r="Z60" s="167">
         <f t="shared" si="25"/>
@@ -13792,7 +14036,7 @@
       <c r="R61" s="158"/>
       <c r="S61" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>4265</v>
+        <v>-17235</v>
       </c>
       <c r="T61" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13803,7 +14047,7 @@
       <c r="W61" s="149"/>
       <c r="Y61" s="153">
         <f t="shared" ref="Y61" si="39">M61+P61+S61+V61</f>
-        <v>17556</v>
+        <v>-3944</v>
       </c>
       <c r="Z61" s="167">
         <f t="shared" ref="Z61" si="40">(N61+Q61+T61+W61)</f>
@@ -13873,7 +14117,7 @@
       <c r="R62" s="158"/>
       <c r="S62" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>168258</v>
+        <v>33128</v>
       </c>
       <c r="T62" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13884,7 +14128,7 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="153">
         <f t="shared" si="24"/>
-        <v>1011359</v>
+        <v>876229</v>
       </c>
       <c r="Z62" s="167">
         <f t="shared" si="25"/>
@@ -14286,7 +14530,7 @@
       <c r="R67" s="158"/>
       <c r="S67" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>143600</v>
+        <v>206750</v>
       </c>
       <c r="T67" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14297,7 +14541,7 @@
       <c r="W67" s="149"/>
       <c r="Y67" s="153">
         <f t="shared" ref="Y67" si="45">M67+P67+S67+V67</f>
-        <v>-819229</v>
+        <v>-756079</v>
       </c>
       <c r="Z67" s="167">
         <f t="shared" ref="Z67" si="46">(N67+Q67+T67+W67)</f>
@@ -14424,7 +14668,7 @@
       <c r="R69" s="158"/>
       <c r="S69" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>35409</v>
+        <v>65485</v>
       </c>
       <c r="T69" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14435,7 +14679,7 @@
       <c r="W69" s="149"/>
       <c r="Y69" s="153">
         <f t="shared" si="24"/>
-        <v>-34476</v>
+        <v>-4400</v>
       </c>
       <c r="Z69" s="167">
         <f t="shared" si="25"/>
@@ -14987,7 +15231,7 @@
       <c r="R76" s="158"/>
       <c r="S76" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>83647</v>
+        <v>100956</v>
       </c>
       <c r="T76" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14998,7 +15242,7 @@
       <c r="W76" s="149"/>
       <c r="Y76" s="153">
         <f t="shared" si="55"/>
-        <v>574500</v>
+        <v>591809</v>
       </c>
       <c r="Z76" s="167">
         <f t="shared" si="56"/>
@@ -15041,7 +15285,7 @@
       <c r="R77" s="122"/>
       <c r="S77" s="109">
         <f>SUM(S4:S74)</f>
-        <v>1251415</v>
+        <v>1213020</v>
       </c>
       <c r="T77" s="122"/>
       <c r="U77" s="122"/>
@@ -15049,7 +15293,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="153">
         <f>SUM(Y4:Y76)</f>
-        <v>24716278</v>
+        <v>24695192</v>
       </c>
       <c r="Z77" s="160"/>
     </row>
@@ -15507,1222 +15751,1222 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R34:R36 R13:R17 R22:R30 R48:R53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:R46 M38:O53 I38:L43 Y38:Z53 W38:W39 K69:O74 G69:J69 W66:W68 R62:R74 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:R60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 R7:R9 U55:U60 U62:U71 U38:U43 U48:U53 U22:U30 U17 U45:U46 U34:W36 U13:W16 U72:W74 U44:W44 Y4:Z11 U7:W9 G77:W78 G84:W84">
-    <cfRule type="expression" dxfId="243" priority="450">
+    <cfRule type="expression" dxfId="245" priority="450">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="242" priority="449">
+    <cfRule type="expression" dxfId="244" priority="449">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="241" priority="446">
+    <cfRule type="expression" dxfId="243" priority="446">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="240" priority="443">
+    <cfRule type="expression" dxfId="242" priority="443">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="239" priority="444">
+    <cfRule type="expression" dxfId="241" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="238" priority="434">
+    <cfRule type="expression" dxfId="240" priority="434">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="237" priority="435">
+    <cfRule type="expression" dxfId="239" priority="435">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="236" priority="424">
+    <cfRule type="expression" dxfId="238" priority="424">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="235" priority="422">
+    <cfRule type="expression" dxfId="237" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="234" priority="420">
+    <cfRule type="expression" dxfId="236" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="233" priority="411">
+    <cfRule type="expression" dxfId="235" priority="411">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="232" priority="410">
+    <cfRule type="expression" dxfId="234" priority="410">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="231" priority="382">
+    <cfRule type="expression" dxfId="233" priority="382">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="230" priority="408">
+    <cfRule type="expression" dxfId="232" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="229" priority="407">
+    <cfRule type="expression" dxfId="231" priority="407">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="228" priority="405">
+    <cfRule type="expression" dxfId="230" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="227" priority="404">
+    <cfRule type="expression" dxfId="229" priority="404">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="226" priority="402">
+    <cfRule type="expression" dxfId="228" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="225" priority="389">
+    <cfRule type="expression" dxfId="227" priority="389">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4 U20:U21">
-    <cfRule type="expression" dxfId="224" priority="333">
+    <cfRule type="expression" dxfId="226" priority="333">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="223" priority="380">
+    <cfRule type="expression" dxfId="225" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4 U20:U21">
-    <cfRule type="expression" dxfId="222" priority="332">
+    <cfRule type="expression" dxfId="224" priority="332">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="221" priority="385">
+    <cfRule type="expression" dxfId="223" priority="385">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="220" priority="351">
+    <cfRule type="expression" dxfId="222" priority="351">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="219" priority="349">
+    <cfRule type="expression" dxfId="221" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="218" priority="357">
+    <cfRule type="expression" dxfId="220" priority="357">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="217" priority="356">
+    <cfRule type="expression" dxfId="219" priority="356">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="216" priority="341">
+    <cfRule type="expression" dxfId="218" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="215" priority="340">
+    <cfRule type="expression" dxfId="217" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="214" priority="371">
+    <cfRule type="expression" dxfId="216" priority="371">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="213" priority="331">
+    <cfRule type="expression" dxfId="215" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="212" priority="342">
+    <cfRule type="expression" dxfId="214" priority="342">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="211" priority="352">
+    <cfRule type="expression" dxfId="213" priority="352">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="210" priority="350">
+    <cfRule type="expression" dxfId="212" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="209" priority="343">
+    <cfRule type="expression" dxfId="211" priority="343">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="208" priority="330">
+    <cfRule type="expression" dxfId="210" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="207" priority="288">
+    <cfRule type="expression" dxfId="209" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="206" priority="287">
+    <cfRule type="expression" dxfId="208" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U18">
-    <cfRule type="expression" dxfId="205" priority="285">
+    <cfRule type="expression" dxfId="207" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="204" priority="277">
+    <cfRule type="expression" dxfId="206" priority="277">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="203" priority="276">
+    <cfRule type="expression" dxfId="205" priority="276">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="202" priority="290">
+    <cfRule type="expression" dxfId="204" priority="290">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="201" priority="289">
+    <cfRule type="expression" dxfId="203" priority="289">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="200" priority="286">
+    <cfRule type="expression" dxfId="202" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U18">
-    <cfRule type="expression" dxfId="199" priority="284">
+    <cfRule type="expression" dxfId="201" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="198" priority="275">
+    <cfRule type="expression" dxfId="200" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31">
-    <cfRule type="expression" dxfId="197" priority="269">
+    <cfRule type="expression" dxfId="199" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="196" priority="274">
+    <cfRule type="expression" dxfId="198" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="195" priority="273">
+    <cfRule type="expression" dxfId="197" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31">
-    <cfRule type="expression" dxfId="194" priority="270">
+    <cfRule type="expression" dxfId="196" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="193" priority="272">
+    <cfRule type="expression" dxfId="195" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="192" priority="271">
+    <cfRule type="expression" dxfId="194" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="191" priority="262">
+    <cfRule type="expression" dxfId="193" priority="262">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="190" priority="261">
+    <cfRule type="expression" dxfId="192" priority="261">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="189" priority="258">
+    <cfRule type="expression" dxfId="191" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="188" priority="257">
+    <cfRule type="expression" dxfId="190" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:U11">
-    <cfRule type="expression" dxfId="187" priority="255">
+    <cfRule type="expression" dxfId="189" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="186" priority="260">
+    <cfRule type="expression" dxfId="188" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="185" priority="259">
+    <cfRule type="expression" dxfId="187" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:U11">
-    <cfRule type="expression" dxfId="184" priority="256">
+    <cfRule type="expression" dxfId="186" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="183" priority="248">
+    <cfRule type="expression" dxfId="185" priority="248">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="182" priority="247">
+    <cfRule type="expression" dxfId="184" priority="247">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="181" priority="246">
+    <cfRule type="expression" dxfId="183" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U47">
-    <cfRule type="expression" dxfId="180" priority="241">
+    <cfRule type="expression" dxfId="182" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U47">
-    <cfRule type="expression" dxfId="179" priority="240">
+    <cfRule type="expression" dxfId="181" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="178" priority="244">
+    <cfRule type="expression" dxfId="180" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="177" priority="243">
+    <cfRule type="expression" dxfId="179" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="176" priority="242">
+    <cfRule type="expression" dxfId="178" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="175" priority="245">
+    <cfRule type="expression" dxfId="177" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="174" priority="233">
+    <cfRule type="expression" dxfId="176" priority="233">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="173" priority="229">
+    <cfRule type="expression" dxfId="175" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="172" priority="228">
+    <cfRule type="expression" dxfId="174" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5">
-    <cfRule type="expression" dxfId="171" priority="222">
+    <cfRule type="expression" dxfId="173" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5">
-    <cfRule type="expression" dxfId="170" priority="221">
+    <cfRule type="expression" dxfId="172" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="169" priority="225">
+    <cfRule type="expression" dxfId="171" priority="225">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="168" priority="224">
+    <cfRule type="expression" dxfId="170" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="167" priority="223">
+    <cfRule type="expression" dxfId="169" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="166" priority="226">
+    <cfRule type="expression" dxfId="168" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="165" priority="210">
+    <cfRule type="expression" dxfId="167" priority="210">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="164" priority="209">
+    <cfRule type="expression" dxfId="166" priority="209">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="163" priority="208">
+    <cfRule type="expression" dxfId="165" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="162" priority="202">
+    <cfRule type="expression" dxfId="164" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="161" priority="201">
+    <cfRule type="expression" dxfId="163" priority="201">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32">
-    <cfRule type="expression" dxfId="160" priority="195">
+    <cfRule type="expression" dxfId="162" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="159" priority="200">
+    <cfRule type="expression" dxfId="161" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="158" priority="199">
+    <cfRule type="expression" dxfId="160" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32">
-    <cfRule type="expression" dxfId="157" priority="196">
+    <cfRule type="expression" dxfId="159" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="156" priority="198">
+    <cfRule type="expression" dxfId="158" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="155" priority="197">
+    <cfRule type="expression" dxfId="157" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="154" priority="193">
+    <cfRule type="expression" dxfId="156" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="153" priority="192">
+    <cfRule type="expression" dxfId="155" priority="192">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="152" priority="179">
+    <cfRule type="expression" dxfId="154" priority="179">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="151" priority="188">
+    <cfRule type="expression" dxfId="153" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="150" priority="187">
+    <cfRule type="expression" dxfId="152" priority="187">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="149" priority="177">
+    <cfRule type="expression" dxfId="151" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="148" priority="176">
+    <cfRule type="expression" dxfId="150" priority="176">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="147" priority="175">
+    <cfRule type="expression" dxfId="149" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="146" priority="170">
+    <cfRule type="expression" dxfId="148" priority="170">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="145" priority="167">
+    <cfRule type="expression" dxfId="147" priority="167">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="144" priority="166">
+    <cfRule type="expression" dxfId="146" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="143" priority="165">
+    <cfRule type="expression" dxfId="145" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="142" priority="164">
+    <cfRule type="expression" dxfId="144" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="141" priority="163">
+    <cfRule type="expression" dxfId="143" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="140" priority="162">
+    <cfRule type="expression" dxfId="142" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="139" priority="149">
+    <cfRule type="expression" dxfId="141" priority="149">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="138" priority="159">
+    <cfRule type="expression" dxfId="140" priority="159">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="137" priority="158">
+    <cfRule type="expression" dxfId="139" priority="158">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="136" priority="157">
+    <cfRule type="expression" dxfId="138" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="135" priority="156">
+    <cfRule type="expression" dxfId="137" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="134" priority="155">
+    <cfRule type="expression" dxfId="136" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="133" priority="154">
+    <cfRule type="expression" dxfId="135" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="132" priority="153">
+    <cfRule type="expression" dxfId="134" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="131" priority="144">
+    <cfRule type="expression" dxfId="133" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="130" priority="150">
+    <cfRule type="expression" dxfId="132" priority="150">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="129" priority="148">
+    <cfRule type="expression" dxfId="131" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="128" priority="147">
+    <cfRule type="expression" dxfId="130" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="127" priority="146">
+    <cfRule type="expression" dxfId="129" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="126" priority="145">
+    <cfRule type="expression" dxfId="128" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="125" priority="143">
+    <cfRule type="expression" dxfId="127" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="124" priority="140">
+    <cfRule type="expression" dxfId="126" priority="140">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="123" priority="139">
+    <cfRule type="expression" dxfId="125" priority="139">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="122" priority="138">
+    <cfRule type="expression" dxfId="124" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="121" priority="137">
+    <cfRule type="expression" dxfId="123" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="120" priority="136">
+    <cfRule type="expression" dxfId="122" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="119" priority="135">
+    <cfRule type="expression" dxfId="121" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="118" priority="132">
+    <cfRule type="expression" dxfId="120" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="117" priority="134">
+    <cfRule type="expression" dxfId="119" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="116" priority="133">
+    <cfRule type="expression" dxfId="118" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="115" priority="131">
+    <cfRule type="expression" dxfId="117" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="114" priority="130">
+    <cfRule type="expression" dxfId="116" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="113" priority="129">
+    <cfRule type="expression" dxfId="115" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="112" priority="128">
+    <cfRule type="expression" dxfId="114" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="111" priority="126">
+    <cfRule type="expression" dxfId="113" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="110" priority="125">
+    <cfRule type="expression" dxfId="112" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="109" priority="124">
+    <cfRule type="expression" dxfId="111" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="108" priority="123">
+    <cfRule type="expression" dxfId="110" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="107" priority="122">
+    <cfRule type="expression" dxfId="109" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6">
-    <cfRule type="expression" dxfId="106" priority="117">
+    <cfRule type="expression" dxfId="108" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6">
-    <cfRule type="expression" dxfId="105" priority="116">
+    <cfRule type="expression" dxfId="107" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="104" priority="120">
+    <cfRule type="expression" dxfId="106" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="103" priority="119">
+    <cfRule type="expression" dxfId="105" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="102" priority="118">
+    <cfRule type="expression" dxfId="104" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="101" priority="121">
+    <cfRule type="expression" dxfId="103" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="100" priority="115">
+    <cfRule type="expression" dxfId="102" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="99" priority="113">
+    <cfRule type="expression" dxfId="101" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="98" priority="111">
+    <cfRule type="expression" dxfId="100" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="97" priority="110">
+    <cfRule type="expression" dxfId="99" priority="110">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="96" priority="109">
+    <cfRule type="expression" dxfId="98" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="95" priority="108">
+    <cfRule type="expression" dxfId="97" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="94" priority="107">
+    <cfRule type="expression" dxfId="96" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="93" priority="106">
+    <cfRule type="expression" dxfId="95" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="92" priority="104">
+    <cfRule type="expression" dxfId="94" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U19">
-    <cfRule type="expression" dxfId="91" priority="94">
+    <cfRule type="expression" dxfId="93" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="90" priority="102">
+    <cfRule type="expression" dxfId="92" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="89" priority="101">
+    <cfRule type="expression" dxfId="91" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="88" priority="98">
+    <cfRule type="expression" dxfId="90" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="87" priority="97">
+    <cfRule type="expression" dxfId="89" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U19">
-    <cfRule type="expression" dxfId="86" priority="95">
+    <cfRule type="expression" dxfId="88" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="85" priority="100">
+    <cfRule type="expression" dxfId="87" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="84" priority="99">
+    <cfRule type="expression" dxfId="86" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="83" priority="96">
+    <cfRule type="expression" dxfId="85" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="82" priority="93">
+    <cfRule type="expression" dxfId="84" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="81" priority="92">
+    <cfRule type="expression" dxfId="83" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="80" priority="91">
+    <cfRule type="expression" dxfId="82" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="79" priority="90">
+    <cfRule type="expression" dxfId="81" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="78" priority="89">
+    <cfRule type="expression" dxfId="80" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="77" priority="88">
+    <cfRule type="expression" dxfId="79" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="76" priority="87">
+    <cfRule type="expression" dxfId="78" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="75" priority="86">
+    <cfRule type="expression" dxfId="77" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="74" priority="74">
+    <cfRule type="expression" dxfId="76" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="73" priority="84">
+    <cfRule type="expression" dxfId="75" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="72" priority="83">
+    <cfRule type="expression" dxfId="74" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="71" priority="82">
+    <cfRule type="expression" dxfId="73" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="70" priority="81">
+    <cfRule type="expression" dxfId="72" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="69" priority="80">
+    <cfRule type="expression" dxfId="71" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="68" priority="79">
+    <cfRule type="expression" dxfId="70" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="67" priority="78">
+    <cfRule type="expression" dxfId="69" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="66" priority="77">
+    <cfRule type="expression" dxfId="68" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="65" priority="76">
+    <cfRule type="expression" dxfId="67" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="64" priority="75">
+    <cfRule type="expression" dxfId="66" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="63" priority="73">
+    <cfRule type="expression" dxfId="65" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="62" priority="72">
+    <cfRule type="expression" dxfId="64" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="61" priority="71">
+    <cfRule type="expression" dxfId="63" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="60" priority="70">
+    <cfRule type="expression" dxfId="62" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33">
-    <cfRule type="expression" dxfId="59" priority="64">
+    <cfRule type="expression" dxfId="61" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="58" priority="69">
+    <cfRule type="expression" dxfId="60" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="57" priority="68">
+    <cfRule type="expression" dxfId="59" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33">
-    <cfRule type="expression" dxfId="56" priority="65">
+    <cfRule type="expression" dxfId="58" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="55" priority="67">
+    <cfRule type="expression" dxfId="57" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="54" priority="66">
+    <cfRule type="expression" dxfId="56" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q38:Q53 Q55:Q60 Q62:Q76 Q4:Q11">
-    <cfRule type="expression" dxfId="53" priority="61">
+    <cfRule type="expression" dxfId="55" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38:Q53 P55:Q60 P62:Q76 P4:Q11">
-    <cfRule type="expression" dxfId="52" priority="60">
+    <cfRule type="expression" dxfId="54" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="51" priority="59">
+    <cfRule type="expression" dxfId="53" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="50" priority="58">
+    <cfRule type="expression" dxfId="52" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="49" priority="57">
+    <cfRule type="expression" dxfId="51" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="48" priority="56">
+    <cfRule type="expression" dxfId="50" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="47" priority="55">
+    <cfRule type="expression" dxfId="49" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:R76 U75:W76">
-    <cfRule type="expression" dxfId="46" priority="54">
+    <cfRule type="expression" dxfId="48" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="45" priority="41">
+    <cfRule type="expression" dxfId="47" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="44" priority="50">
+    <cfRule type="expression" dxfId="46" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="43" priority="26">
+    <cfRule type="expression" dxfId="45" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="42" priority="48">
+    <cfRule type="expression" dxfId="44" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61 U61">
-    <cfRule type="expression" dxfId="41" priority="47">
+    <cfRule type="expression" dxfId="43" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="40" priority="46">
+    <cfRule type="expression" dxfId="42" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="39" priority="45">
+    <cfRule type="expression" dxfId="41" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="38" priority="44">
+    <cfRule type="expression" dxfId="40" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37 U37:W37">
-    <cfRule type="expression" dxfId="37" priority="43">
+    <cfRule type="expression" dxfId="39" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="36" priority="42">
+    <cfRule type="expression" dxfId="38" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="35" priority="27">
+    <cfRule type="expression" dxfId="37" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="34" priority="38">
+    <cfRule type="expression" dxfId="36" priority="38">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="33" priority="37">
+    <cfRule type="expression" dxfId="35" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="32" priority="36">
+    <cfRule type="expression" dxfId="34" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="31" priority="35">
+    <cfRule type="expression" dxfId="33" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="30" priority="34">
+    <cfRule type="expression" dxfId="32" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="29" priority="33">
+    <cfRule type="expression" dxfId="31" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="28" priority="32">
+    <cfRule type="expression" dxfId="30" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="27" priority="31">
+    <cfRule type="expression" dxfId="29" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="26" priority="30">
+    <cfRule type="expression" dxfId="28" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="25" priority="29">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="24" priority="28">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="23" priority="25">
+    <cfRule type="expression" dxfId="25" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="22" priority="24">
+    <cfRule type="expression" dxfId="24" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="23" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="22" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="15" priority="15">
+    <cfRule type="expression" dxfId="17" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="16" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U12">
-    <cfRule type="expression" dxfId="13" priority="12">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="12" priority="17">
+    <cfRule type="expression" dxfId="14" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="11" priority="16">
+    <cfRule type="expression" dxfId="13" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U12">
-    <cfRule type="expression" dxfId="10" priority="13">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54 G54:O54 Y54:Z54 U54">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T76">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:T76">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16831,12 +17075,12 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>15268</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>44320</v>
       </c>
       <c r="H4" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.30536000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.88639999999999997</v>
       </c>
       <c r="I4" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -16856,11 +17100,11 @@
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N58" si="0">G4+I4+K4</f>
-        <v>15268</v>
+        <v>44320</v>
       </c>
       <c r="N4" s="165">
         <f t="shared" si="0"/>
-        <v>0.30536000000000002</v>
+        <v>0.88639999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -16883,12 +17127,12 @@
         <v>3.5</v>
       </c>
       <c r="G5" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-798</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>94140</v>
       </c>
       <c r="H5" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-2.66E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.31380000000000002</v>
       </c>
       <c r="I5" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -16908,11 +17152,11 @@
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>-798</v>
+        <v>94140</v>
       </c>
       <c r="N5" s="165">
         <f t="shared" si="0"/>
-        <v>-2.66E-3</v>
+        <v>0.31380000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -16935,12 +17179,12 @@
         <v>1</v>
       </c>
       <c r="G6" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-23073</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>27367</v>
       </c>
       <c r="H6" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.23072999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.27367000000000002</v>
       </c>
       <c r="I6" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -16960,11 +17204,11 @@
       </c>
       <c r="M6" s="71">
         <f t="shared" si="0"/>
-        <v>-23073</v>
+        <v>27367</v>
       </c>
       <c r="N6" s="165">
         <f t="shared" si="0"/>
-        <v>-0.23072999999999999</v>
+        <v>0.27367000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -16987,12 +17231,12 @@
         <v>3</v>
       </c>
       <c r="G7" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-67000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-207210</v>
       </c>
       <c r="H7" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.2233333333333333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.69069999999999998</v>
       </c>
       <c r="I7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17012,11 +17256,11 @@
       </c>
       <c r="M7" s="71">
         <f t="shared" si="0"/>
-        <v>-67000</v>
+        <v>-207210</v>
       </c>
       <c r="N7" s="165">
         <f t="shared" si="0"/>
-        <v>-0.2233333333333333</v>
+        <v>-0.69069999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -17039,12 +17283,12 @@
         <v>1.5</v>
       </c>
       <c r="G8" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>90050</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>108340</v>
       </c>
       <c r="H8" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.60033333333333339</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.72226666666666672</v>
       </c>
       <c r="I8" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17064,11 +17308,11 @@
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>90050</v>
+        <v>108340</v>
       </c>
       <c r="N8" s="165">
         <f t="shared" si="0"/>
-        <v>0.60033333333333339</v>
+        <v>0.72226666666666672</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -17091,12 +17335,12 @@
         <v>0.6</v>
       </c>
       <c r="G9" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>37266</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>42214</v>
       </c>
       <c r="H9" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.62109999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.70356666666666667</v>
       </c>
       <c r="I9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17116,11 +17360,11 @@
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>37266</v>
+        <v>42214</v>
       </c>
       <c r="N9" s="165">
         <f t="shared" si="0"/>
-        <v>0.62109999999999999</v>
+        <v>0.70356666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -17143,12 +17387,12 @@
         <v>15</v>
       </c>
       <c r="G10" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-170250</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-156520</v>
       </c>
       <c r="H10" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.1135</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.10434666666666666</v>
       </c>
       <c r="I10" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17168,11 +17412,11 @@
       </c>
       <c r="M10" s="71">
         <f t="shared" si="0"/>
-        <v>-170250</v>
+        <v>-156520</v>
       </c>
       <c r="N10" s="165">
         <f t="shared" si="0"/>
-        <v>-0.1135</v>
+        <v>-0.10434666666666666</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -17195,11 +17439,11 @@
         <v>6</v>
       </c>
       <c r="G11" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>170431</v>
       </c>
       <c r="H11" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.2840516666666667</v>
       </c>
       <c r="I11" s="152">
@@ -17247,12 +17491,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-322</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-1938</v>
       </c>
       <c r="H12" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-3.2200000000000002E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-1.9380000000000001E-2</v>
       </c>
       <c r="I12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17272,11 +17516,11 @@
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>-322</v>
+        <v>-1938</v>
       </c>
       <c r="N12" s="165">
         <f t="shared" si="0"/>
-        <v>-3.2200000000000002E-3</v>
+        <v>-1.9380000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -17299,11 +17543,11 @@
         <v>1</v>
       </c>
       <c r="G13" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>68353</v>
       </c>
       <c r="H13" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.27341199999999999</v>
       </c>
       <c r="I13" s="152">
@@ -17351,11 +17595,11 @@
         <v>1</v>
       </c>
       <c r="G14" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H14" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I14" s="152">
@@ -17403,12 +17647,12 @@
         <v>1</v>
       </c>
       <c r="G15" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>20500</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>14282</v>
       </c>
       <c r="H15" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.20499999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.14282</v>
       </c>
       <c r="I15" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17428,11 +17672,11 @@
       </c>
       <c r="M15" s="71">
         <f t="shared" si="0"/>
-        <v>20500</v>
+        <v>14282</v>
       </c>
       <c r="N15" s="165">
         <f t="shared" si="0"/>
-        <v>0.20499999999999999</v>
+        <v>0.14282</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -17455,11 +17699,11 @@
         <v>0.2</v>
       </c>
       <c r="G16" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>77903</v>
       </c>
       <c r="H16" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.35410454545454545</v>
       </c>
       <c r="I16" s="152">
@@ -17507,11 +17751,11 @@
         <v>2.5</v>
       </c>
       <c r="G17" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-38551</v>
       </c>
       <c r="H17" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-0.15420400000000001</v>
       </c>
       <c r="I17" s="152">
@@ -17559,11 +17803,11 @@
         <v>4</v>
       </c>
       <c r="G18" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-34123</v>
       </c>
       <c r="H18" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-8.5307499999999994E-2</v>
       </c>
       <c r="I18" s="152">
@@ -17611,11 +17855,11 @@
         <v>0.25</v>
       </c>
       <c r="G19" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-150688</v>
       </c>
       <c r="H19" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-1.3698909090909093</v>
       </c>
       <c r="I19" s="152">
@@ -17663,12 +17907,12 @@
         <v>0.25</v>
       </c>
       <c r="G20" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-75454</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-68242</v>
       </c>
       <c r="H20" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-3.01816</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-2.7296800000000001</v>
       </c>
       <c r="I20" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17688,11 +17932,11 @@
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>-75454</v>
+        <v>-68242</v>
       </c>
       <c r="N20" s="165">
         <f t="shared" si="0"/>
-        <v>-3.01816</v>
+        <v>-2.7296800000000001</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -17715,11 +17959,11 @@
         <v>2</v>
       </c>
       <c r="G21" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H21" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I21" s="152">
@@ -17767,12 +18011,12 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>44814</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-50285</v>
       </c>
       <c r="H22" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.29876000000000003</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.33523333333333333</v>
       </c>
       <c r="I22" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17792,11 +18036,11 @@
       </c>
       <c r="M22" s="71">
         <f t="shared" si="0"/>
-        <v>44814</v>
+        <v>-50285</v>
       </c>
       <c r="N22" s="165">
         <f t="shared" si="0"/>
-        <v>0.29876000000000003</v>
+        <v>-0.33523333333333333</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -17819,11 +18063,11 @@
         <v>1</v>
       </c>
       <c r="G23" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H23" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I23" s="152">
@@ -17871,12 +18115,12 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G24" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-10377</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>28323</v>
       </c>
       <c r="H24" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-9.4336363636363621E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.25748181818181815</v>
       </c>
       <c r="I24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17896,11 +18140,11 @@
       </c>
       <c r="M24" s="71">
         <f t="shared" si="0"/>
-        <v>-10377</v>
+        <v>28323</v>
       </c>
       <c r="N24" s="165">
         <f t="shared" si="0"/>
-        <v>-9.4336363636363621E-2</v>
+        <v>0.25748181818181815</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -17923,12 +18167,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G25" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>66800</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-61800</v>
       </c>
       <c r="H25" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.29043478260869571</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.26869565217391306</v>
       </c>
       <c r="I25" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17948,11 +18192,11 @@
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>66800</v>
+        <v>-61800</v>
       </c>
       <c r="N25" s="165">
         <f t="shared" si="0"/>
-        <v>0.29043478260869571</v>
+        <v>-0.26869565217391306</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -17973,12 +18217,12 @@
         <v>0.2</v>
       </c>
       <c r="G26" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>2726</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-109</v>
       </c>
       <c r="H26" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.1363</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-5.45E-3</v>
       </c>
       <c r="I26" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17998,11 +18242,11 @@
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>2726</v>
+        <v>-109</v>
       </c>
       <c r="N26" s="165">
         <f t="shared" si="0"/>
-        <v>0.1363</v>
+        <v>-5.45E-3</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -18025,11 +18269,11 @@
         <v>5</v>
       </c>
       <c r="G27" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-115600</v>
       </c>
       <c r="H27" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>-0.23119999999999999</v>
       </c>
       <c r="I27" s="152">
@@ -18077,12 +18321,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>110335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>412715</v>
       </c>
       <c r="H28" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.110335</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.412715</v>
       </c>
       <c r="I28" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18102,11 +18346,11 @@
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>110335</v>
+        <v>412715</v>
       </c>
       <c r="N28" s="165">
         <f t="shared" si="0"/>
-        <v>0.110335</v>
+        <v>0.412715</v>
       </c>
       <c r="O28" s="130"/>
     </row>
@@ -18130,11 +18374,11 @@
         <v>13</v>
       </c>
       <c r="G29" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H29" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I29" s="152">
@@ -18182,11 +18426,11 @@
         <v>1.5</v>
       </c>
       <c r="G30" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H30" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I30" s="152">
@@ -18234,11 +18478,11 @@
         <v>6</v>
       </c>
       <c r="G31" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H31" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I31" s="152">
@@ -18286,11 +18530,11 @@
         <v>1.3</v>
       </c>
       <c r="G32" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H32" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I32" s="152">
@@ -18338,11 +18582,11 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I33" s="152">
@@ -18390,11 +18634,11 @@
         <v>5</v>
       </c>
       <c r="G34" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>401130</v>
       </c>
       <c r="H34" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.80225999999999997</v>
       </c>
       <c r="I34" s="152">
@@ -18442,12 +18686,12 @@
         <v>5</v>
       </c>
       <c r="G35" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-110750</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-108150</v>
       </c>
       <c r="H35" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.2215</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.21629999999999999</v>
       </c>
       <c r="I35" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18467,11 +18711,11 @@
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>-110750</v>
+        <v>-108150</v>
       </c>
       <c r="N35" s="165">
         <f t="shared" si="0"/>
-        <v>-0.2215</v>
+        <v>-0.21629999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -18494,12 +18738,12 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>11493</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>3799</v>
       </c>
       <c r="H36" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.22986000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>7.5980000000000006E-2</v>
       </c>
       <c r="I36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18519,11 +18763,11 @@
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>11493</v>
+        <v>3799</v>
       </c>
       <c r="N36" s="165">
         <f t="shared" si="0"/>
-        <v>0.22986000000000001</v>
+        <v>7.5980000000000006E-2</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -18546,12 +18790,12 @@
         <v>0.4</v>
       </c>
       <c r="G37" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>80175</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>81468</v>
       </c>
       <c r="H37" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>2.004375</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>2.0367000000000002</v>
       </c>
       <c r="I37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18571,11 +18815,11 @@
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>80175</v>
+        <v>81468</v>
       </c>
       <c r="N37" s="165">
         <f t="shared" si="0"/>
-        <v>2.004375</v>
+        <v>2.0367000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -18598,12 +18842,12 @@
         <v>4</v>
       </c>
       <c r="G38" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-49332</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-147529</v>
       </c>
       <c r="H38" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.12333</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.3688225</v>
       </c>
       <c r="I38" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18623,11 +18867,11 @@
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-49332</v>
+        <v>-147529</v>
       </c>
       <c r="N38" s="165">
         <f t="shared" si="0"/>
-        <v>-0.12333</v>
+        <v>-0.3688225</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -18650,12 +18894,12 @@
         <v>1</v>
       </c>
       <c r="G39" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>22822</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>9674</v>
       </c>
       <c r="H39" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.22822000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>9.6740000000000007E-2</v>
       </c>
       <c r="I39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18675,11 +18919,11 @@
       </c>
       <c r="M39" s="71">
         <f t="shared" si="0"/>
-        <v>22822</v>
+        <v>9674</v>
       </c>
       <c r="N39" s="165">
         <f t="shared" si="0"/>
-        <v>0.22822000000000001</v>
+        <v>9.6740000000000007E-2</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -18700,11 +18944,11 @@
       </c>
       <c r="F40" s="155"/>
       <c r="G40" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H40" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I40" s="152">
@@ -18752,12 +18996,12 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>6629</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-8895</v>
       </c>
       <c r="H41" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.13258</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-0.1779</v>
       </c>
       <c r="I41" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18777,11 +19021,11 @@
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>6629</v>
+        <v>-8895</v>
       </c>
       <c r="N41" s="165">
         <f t="shared" si="0"/>
-        <v>0.13258</v>
+        <v>-0.1779</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -18804,12 +19048,12 @@
         <v>1</v>
       </c>
       <c r="G42" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>104100</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>183624</v>
       </c>
       <c r="H42" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.34699999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.61207999999999996</v>
       </c>
       <c r="I42" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18829,11 +19073,11 @@
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>104100</v>
+        <v>183624</v>
       </c>
       <c r="N42" s="165">
         <f t="shared" si="0"/>
-        <v>0.34699999999999998</v>
+        <v>0.61207999999999996</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -18856,11 +19100,11 @@
         <v>3</v>
       </c>
       <c r="G43" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H43" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I43" s="152">
@@ -18906,12 +19150,12 @@
         <v>0.1</v>
       </c>
       <c r="G44" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>25653</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>6368</v>
       </c>
       <c r="H44" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>2.5653000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.63680000000000003</v>
       </c>
       <c r="I44" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18931,11 +19175,11 @@
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>25653</v>
+        <v>6368</v>
       </c>
       <c r="N44" s="165">
         <f t="shared" si="0"/>
-        <v>2.5653000000000001</v>
+        <v>0.63680000000000003</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -18958,12 +19202,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>19800</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>3300</v>
       </c>
       <c r="H45" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.39600000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="I45" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18983,11 +19227,11 @@
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>19800</v>
+        <v>3300</v>
       </c>
       <c r="N45" s="165">
         <f t="shared" si="0"/>
-        <v>0.39600000000000002</v>
+        <v>6.6000000000000003E-2</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -19010,12 +19254,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-85984</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-171229</v>
       </c>
       <c r="H46" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>-0.85984000000000005</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-1.7122900000000001</v>
       </c>
       <c r="I46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19035,11 +19279,11 @@
       </c>
       <c r="M46" s="71">
         <f t="shared" si="0"/>
-        <v>-85984</v>
+        <v>-171229</v>
       </c>
       <c r="N46" s="165">
         <f t="shared" si="0"/>
-        <v>-0.85984000000000005</v>
+        <v>-1.7122900000000001</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -19060,12 +19304,12 @@
         <v>0.1</v>
       </c>
       <c r="G47" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>4265</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-17235</v>
       </c>
       <c r="H47" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.42649999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>-1.7235</v>
       </c>
       <c r="I47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19085,11 +19329,11 @@
       </c>
       <c r="M47" s="71">
         <f t="shared" si="0"/>
-        <v>4265</v>
+        <v>-17235</v>
       </c>
       <c r="N47" s="165">
         <f t="shared" si="0"/>
-        <v>0.42649999999999999</v>
+        <v>-1.7235</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -19112,12 +19356,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>168258</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>33128</v>
       </c>
       <c r="H48" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.56086000000000003</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.11042666666666665</v>
       </c>
       <c r="I48" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19137,11 +19381,11 @@
       </c>
       <c r="M48" s="71">
         <f t="shared" si="0"/>
-        <v>168258</v>
+        <v>33128</v>
       </c>
       <c r="N48" s="165">
         <f t="shared" si="0"/>
-        <v>0.56086000000000003</v>
+        <v>0.11042666666666665</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -19158,11 +19402,11 @@
         <v>1</v>
       </c>
       <c r="G49" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H49" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I49" s="152">
@@ -19210,11 +19454,11 @@
         <v>4</v>
       </c>
       <c r="G50" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>2920</v>
       </c>
       <c r="H50" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>7.3000000000000001E-3</v>
       </c>
       <c r="I50" s="152">
@@ -19262,11 +19506,11 @@
         <v>4</v>
       </c>
       <c r="G51" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>40600</v>
       </c>
       <c r="H51" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.10150000000000001</v>
       </c>
       <c r="I51" s="152">
@@ -19312,12 +19556,12 @@
         <v>0.1</v>
       </c>
       <c r="G52" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>143600</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>206750</v>
       </c>
       <c r="H52" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.14360000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.20674999999999999</v>
       </c>
       <c r="I52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19337,11 +19581,11 @@
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>143600</v>
+        <v>206750</v>
       </c>
       <c r="N52" s="165">
         <f t="shared" si="0"/>
-        <v>0.14360000000000001</v>
+        <v>0.20674999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -19358,11 +19602,11 @@
       </c>
       <c r="F53" s="114"/>
       <c r="G53" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H53" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I53" s="152">
@@ -19410,12 +19654,12 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>35409</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>65485</v>
       </c>
       <c r="H54" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.70818000000000003</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>1.3097000000000001</v>
       </c>
       <c r="I54" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19435,11 +19679,11 @@
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>35409</v>
+        <v>65485</v>
       </c>
       <c r="N54" s="165">
         <f t="shared" si="0"/>
-        <v>0.70818000000000003</v>
+        <v>1.3097000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -19462,11 +19706,11 @@
         <v>5</v>
       </c>
       <c r="G55" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>306496</v>
       </c>
       <c r="H55" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.4715323076923077</v>
       </c>
       <c r="I55" s="152">
@@ -19514,11 +19758,11 @@
         <v>1</v>
       </c>
       <c r="G56" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H56" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I56" s="152">
@@ -19566,11 +19810,11 @@
         <v>2.5</v>
       </c>
       <c r="G57" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>56120</v>
       </c>
       <c r="H57" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0.18706666666666669</v>
       </c>
       <c r="I57" s="152">
@@ -19618,11 +19862,11 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H58" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I58" s="152">
@@ -19670,11 +19914,11 @@
         <v>0.25</v>
       </c>
       <c r="G59" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H59" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I59" s="152">
@@ -19722,12 +19966,12 @@
         <v>5</v>
       </c>
       <c r="G60" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>83647</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>100956</v>
       </c>
       <c r="H60" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.16729400000000003</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.20191200000000001</v>
       </c>
       <c r="I60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19747,11 +19991,11 @@
       </c>
       <c r="M60" s="71">
         <f t="shared" si="1"/>
-        <v>83647</v>
+        <v>100956</v>
       </c>
       <c r="N60" s="165">
         <f t="shared" si="1"/>
-        <v>0.16729400000000003</v>
+        <v>0.20191200000000001</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -19763,7 +20007,7 @@
       <c r="F61" s="233"/>
       <c r="G61" s="230">
         <f>SUM(G4:G58)</f>
-        <v>1201614</v>
+        <v>1151146</v>
       </c>
       <c r="H61" s="90"/>
       <c r="I61" s="99">
@@ -19778,7 +20022,7 @@
       <c r="L61" s="109"/>
       <c r="M61" s="153">
         <f>SUM(M4:M58)</f>
-        <v>1201614</v>
+        <v>1151146</v>
       </c>
       <c r="N61" s="234"/>
     </row>
@@ -19842,12 +20086,12 @@
       <c r="E65" s="208"/>
       <c r="F65" s="206"/>
       <c r="G65" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>135526</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>151126</v>
       </c>
       <c r="H65" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
-        <v>0.4517533333333334</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <v>0.50375333333333339</v>
       </c>
       <c r="I65" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19867,11 +20111,11 @@
       </c>
       <c r="M65" s="152">
         <f t="shared" ref="M65:N66" si="2">G65+I65+K65</f>
-        <v>135526</v>
+        <v>151126</v>
       </c>
       <c r="N65" s="166">
         <f t="shared" si="2"/>
-        <v>0.4517533333333334</v>
+        <v>0.50375333333333339</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -19892,11 +20136,11 @@
       </c>
       <c r="F66" s="237"/>
       <c r="G66" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>98000</v>
       </c>
       <c r="H66" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACU$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CV$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I66" s="152">
@@ -19927,7 +20171,7 @@
     <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G67" s="93">
         <f>SUM(G65:G66)</f>
-        <v>233526</v>
+        <v>249126</v>
       </c>
       <c r="H67" s="94"/>
       <c r="I67" s="93">
@@ -19942,483 +20186,483 @@
       <c r="L67" s="113"/>
       <c r="M67" s="93">
         <f>SUM(M65:M66)</f>
-        <v>233526</v>
+        <v>249126</v>
       </c>
       <c r="N67" s="235"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A42:C42 A10:C10 A3:F3 L2:L3 A38:C38 A5 A31:F31 F10 F39:F40 F42 A57:C57 A58:E58 A33:F35 E38:F38 A46:F46 A22 A37:F37 A51:F51 F55:F58 E57 G61:N62 A24:F25 M24:N25 A61:E61 C49:F49 M22:N22 A27:F28 A48:F48 F52:F53 A13:F15 M13:N15 M54:N59 M27:N39 M10:N11 C5:F5 M50:N52 A17:F18 M17:N19 M65:N66 G67:N67 M5:N8 A6:F6 M41:N48 G4:L60">
-    <cfRule type="expression" dxfId="543" priority="102">
+    <cfRule type="expression" dxfId="545" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="542" priority="101">
+    <cfRule type="expression" dxfId="544" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="541" priority="100">
+    <cfRule type="expression" dxfId="543" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="540" priority="99">
+    <cfRule type="expression" dxfId="542" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:C39 E39 A40">
-    <cfRule type="expression" dxfId="539" priority="98">
+    <cfRule type="expression" dxfId="541" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="expression" dxfId="538" priority="97">
+    <cfRule type="expression" dxfId="540" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="537" priority="96">
+    <cfRule type="expression" dxfId="539" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="536" priority="92">
+    <cfRule type="expression" dxfId="538" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:C11 E11:F11">
-    <cfRule type="expression" dxfId="535" priority="94">
+    <cfRule type="expression" dxfId="537" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="534" priority="93">
+    <cfRule type="expression" dxfId="536" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:N11">
-    <cfRule type="expression" dxfId="533" priority="90">
+    <cfRule type="expression" dxfId="535" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22 E22:F22">
-    <cfRule type="expression" dxfId="532" priority="89">
+    <cfRule type="expression" dxfId="534" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11">
-    <cfRule type="expression" dxfId="531" priority="91">
+    <cfRule type="expression" dxfId="533" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:C7 E7:F7 A8:F8 A9:B9 D9:F9">
-    <cfRule type="expression" dxfId="530" priority="88">
+    <cfRule type="expression" dxfId="532" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N8">
-    <cfRule type="expression" dxfId="529" priority="87">
+    <cfRule type="expression" dxfId="531" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N8">
-    <cfRule type="expression" dxfId="528" priority="86">
+    <cfRule type="expression" dxfId="530" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:C36 E36:F36">
-    <cfRule type="expression" dxfId="527" priority="85">
+    <cfRule type="expression" dxfId="529" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M36:N36">
-    <cfRule type="expression" dxfId="526" priority="83">
+    <cfRule type="expression" dxfId="528" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N36">
-    <cfRule type="expression" dxfId="525" priority="84">
+    <cfRule type="expression" dxfId="527" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:C45 E45:F45">
-    <cfRule type="expression" dxfId="524" priority="82">
+    <cfRule type="expression" dxfId="526" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="expression" dxfId="523" priority="81">
+    <cfRule type="expression" dxfId="525" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:N22">
-    <cfRule type="expression" dxfId="522" priority="80">
+    <cfRule type="expression" dxfId="524" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="521" priority="79">
+    <cfRule type="expression" dxfId="523" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63:L64">
-    <cfRule type="expression" dxfId="520" priority="78">
+    <cfRule type="expression" dxfId="522" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63:I64">
-    <cfRule type="expression" dxfId="519" priority="77">
+    <cfRule type="expression" dxfId="521" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J63:J64">
-    <cfRule type="expression" dxfId="518" priority="76">
+    <cfRule type="expression" dxfId="520" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K64">
-    <cfRule type="expression" dxfId="517" priority="75">
+    <cfRule type="expression" dxfId="519" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:F29">
-    <cfRule type="expression" dxfId="516" priority="74">
+    <cfRule type="expression" dxfId="518" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="515" priority="73">
+    <cfRule type="expression" dxfId="517" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:F32">
-    <cfRule type="expression" dxfId="514" priority="72">
+    <cfRule type="expression" dxfId="516" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="513" priority="71">
+    <cfRule type="expression" dxfId="515" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C56 E55:E56">
-    <cfRule type="expression" dxfId="512" priority="70">
+    <cfRule type="expression" dxfId="514" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55:N56">
-    <cfRule type="expression" dxfId="511" priority="69">
+    <cfRule type="expression" dxfId="513" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:C43 E43:F43">
-    <cfRule type="expression" dxfId="510" priority="68">
+    <cfRule type="expression" dxfId="512" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:B50">
-    <cfRule type="expression" dxfId="509" priority="67">
+    <cfRule type="expression" dxfId="511" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="508" priority="66">
+    <cfRule type="expression" dxfId="510" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="507" priority="65">
+    <cfRule type="expression" dxfId="509" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="506" priority="63">
+    <cfRule type="expression" dxfId="508" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="505" priority="64">
+    <cfRule type="expression" dxfId="507" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:C41 E41:F41">
-    <cfRule type="expression" dxfId="504" priority="62">
+    <cfRule type="expression" dxfId="506" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65:F65 F66">
-    <cfRule type="expression" dxfId="503" priority="61">
+    <cfRule type="expression" dxfId="505" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:F12">
-    <cfRule type="expression" dxfId="502" priority="60">
+    <cfRule type="expression" dxfId="504" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="501" priority="59">
+    <cfRule type="expression" dxfId="503" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="500" priority="57">
+    <cfRule type="expression" dxfId="502" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="499" priority="58">
+    <cfRule type="expression" dxfId="501" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="expression" dxfId="498" priority="56">
+    <cfRule type="expression" dxfId="500" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:E50">
-    <cfRule type="expression" dxfId="497" priority="55">
+    <cfRule type="expression" dxfId="499" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="496" priority="54">
+    <cfRule type="expression" dxfId="498" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="495" priority="53">
+    <cfRule type="expression" dxfId="497" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11">
-    <cfRule type="expression" dxfId="494" priority="52">
+    <cfRule type="expression" dxfId="496" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22">
-    <cfRule type="expression" dxfId="493" priority="51">
+    <cfRule type="expression" dxfId="495" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D56">
-    <cfRule type="expression" dxfId="492" priority="41">
+    <cfRule type="expression" dxfId="494" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36">
-    <cfRule type="expression" dxfId="491" priority="50">
+    <cfRule type="expression" dxfId="493" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39 D41">
-    <cfRule type="expression" dxfId="490" priority="49">
+    <cfRule type="expression" dxfId="492" priority="49">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D38">
-    <cfRule type="expression" dxfId="489" priority="48">
+    <cfRule type="expression" dxfId="491" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42">
-    <cfRule type="expression" dxfId="488" priority="47">
+    <cfRule type="expression" dxfId="490" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43">
-    <cfRule type="expression" dxfId="487" priority="46">
+    <cfRule type="expression" dxfId="489" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="486" priority="44">
+    <cfRule type="expression" dxfId="488" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="485" priority="43">
+    <cfRule type="expression" dxfId="487" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="484" priority="42">
+    <cfRule type="expression" dxfId="486" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:F23">
-    <cfRule type="expression" dxfId="483" priority="40">
+    <cfRule type="expression" dxfId="485" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="482" priority="39">
+    <cfRule type="expression" dxfId="484" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="481" priority="38">
+    <cfRule type="expression" dxfId="483" priority="38">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="480" priority="37">
+    <cfRule type="expression" dxfId="482" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:C60 E60:F60">
-    <cfRule type="expression" dxfId="479" priority="36">
+    <cfRule type="expression" dxfId="481" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60:N60">
-    <cfRule type="expression" dxfId="478" priority="35">
+    <cfRule type="expression" dxfId="480" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:B49">
-    <cfRule type="expression" dxfId="477" priority="34">
+    <cfRule type="expression" dxfId="479" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49:N49">
-    <cfRule type="expression" dxfId="476" priority="33">
+    <cfRule type="expression" dxfId="478" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:F44">
-    <cfRule type="expression" dxfId="475" priority="30">
+    <cfRule type="expression" dxfId="477" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:F16">
-    <cfRule type="expression" dxfId="474" priority="29">
+    <cfRule type="expression" dxfId="476" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16:N16">
-    <cfRule type="expression" dxfId="473" priority="28">
+    <cfRule type="expression" dxfId="475" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:F21 C20:F20">
-    <cfRule type="expression" dxfId="472" priority="27">
+    <cfRule type="expression" dxfId="474" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:N21">
-    <cfRule type="expression" dxfId="471" priority="26">
+    <cfRule type="expression" dxfId="473" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26:N26">
-    <cfRule type="expression" dxfId="470" priority="22">
+    <cfRule type="expression" dxfId="472" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:F26">
-    <cfRule type="expression" dxfId="469" priority="25">
+    <cfRule type="expression" dxfId="471" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:F47">
-    <cfRule type="expression" dxfId="468" priority="24">
+    <cfRule type="expression" dxfId="470" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="467" priority="23">
+    <cfRule type="expression" dxfId="469" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66:E66">
-    <cfRule type="expression" dxfId="466" priority="21">
+    <cfRule type="expression" dxfId="468" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:E52 A53">
-    <cfRule type="expression" dxfId="465" priority="20">
+    <cfRule type="expression" dxfId="467" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53:E53">
-    <cfRule type="expression" dxfId="464" priority="17">
+    <cfRule type="expression" dxfId="466" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="463" priority="16">
+    <cfRule type="expression" dxfId="465" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="462" priority="15">
+    <cfRule type="expression" dxfId="464" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N9">
-    <cfRule type="expression" dxfId="461" priority="14">
+    <cfRule type="expression" dxfId="463" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9">
-    <cfRule type="expression" dxfId="460" priority="13">
+    <cfRule type="expression" dxfId="462" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N9">
-    <cfRule type="expression" dxfId="459" priority="12">
+    <cfRule type="expression" dxfId="461" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
-    <cfRule type="expression" dxfId="458" priority="11">
+    <cfRule type="expression" dxfId="460" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="expression" dxfId="457" priority="10">
+    <cfRule type="expression" dxfId="459" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E40">
-    <cfRule type="expression" dxfId="456" priority="9">
+    <cfRule type="expression" dxfId="458" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M40:N40">
-    <cfRule type="expression" dxfId="455" priority="8">
+    <cfRule type="expression" dxfId="457" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="expression" dxfId="454" priority="7">
+    <cfRule type="expression" dxfId="456" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A21">
-    <cfRule type="expression" dxfId="453" priority="6">
+    <cfRule type="expression" dxfId="455" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53:N53">
-    <cfRule type="expression" dxfId="452" priority="5">
+    <cfRule type="expression" dxfId="454" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G65:L66">
-    <cfRule type="expression" dxfId="451" priority="3">
+    <cfRule type="expression" dxfId="453" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60">
-    <cfRule type="expression" dxfId="450" priority="2">
+    <cfRule type="expression" dxfId="452" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="449" priority="1">
+    <cfRule type="expression" dxfId="451" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25981,87 +26225,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD57:AD58 AC56:AD56 AD61 AC43:AD43 AC5:AD10 AC24:AD25 H2:AD3 A59:AD60 A37:AC37 AD11:AD21 AC11:AC22 AC45:AD53 AC27:AC36 AD27:AD35 A4:AB36 AC38:AC41 A38:AB39 G40:AB40 A41:AB57 A61:AB61">
-    <cfRule type="expression" dxfId="448" priority="21">
+    <cfRule type="expression" dxfId="450" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD36">
-    <cfRule type="expression" dxfId="447" priority="20">
+    <cfRule type="expression" dxfId="449" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD39:AD40">
-    <cfRule type="expression" dxfId="446" priority="19">
+    <cfRule type="expression" dxfId="448" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="445" priority="18">
+    <cfRule type="expression" dxfId="447" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD38">
-    <cfRule type="expression" dxfId="444" priority="17">
+    <cfRule type="expression" dxfId="446" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD22">
-    <cfRule type="expression" dxfId="443" priority="14">
+    <cfRule type="expression" dxfId="445" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC57">
-    <cfRule type="expression" dxfId="442" priority="13">
+    <cfRule type="expression" dxfId="444" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="441" priority="12">
+    <cfRule type="expression" dxfId="443" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC26:AD26">
-    <cfRule type="expression" dxfId="440" priority="11">
+    <cfRule type="expression" dxfId="442" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AD55">
-    <cfRule type="expression" dxfId="439" priority="10">
+    <cfRule type="expression" dxfId="441" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC44:AD44">
-    <cfRule type="expression" dxfId="438" priority="9">
+    <cfRule type="expression" dxfId="440" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC61">
-    <cfRule type="expression" dxfId="437" priority="8">
+    <cfRule type="expression" dxfId="439" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC42:AD42">
-    <cfRule type="expression" dxfId="436" priority="6">
+    <cfRule type="expression" dxfId="438" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC23">
-    <cfRule type="expression" dxfId="435" priority="5">
+    <cfRule type="expression" dxfId="437" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD23">
-    <cfRule type="expression" dxfId="434" priority="4">
+    <cfRule type="expression" dxfId="436" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD37">
-    <cfRule type="expression" dxfId="433" priority="2">
+    <cfRule type="expression" dxfId="435" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="432" priority="1">
+    <cfRule type="expression" dxfId="434" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32530,112 +32774,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="431" priority="22">
+    <cfRule type="expression" dxfId="433" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="430" priority="21">
+    <cfRule type="expression" dxfId="432" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="429" priority="20">
+    <cfRule type="expression" dxfId="431" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="428" priority="19">
+    <cfRule type="expression" dxfId="430" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="427" priority="18">
+    <cfRule type="expression" dxfId="429" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="426" priority="17">
+    <cfRule type="expression" dxfId="428" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="425" priority="16">
+    <cfRule type="expression" dxfId="427" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="424" priority="15">
+    <cfRule type="expression" dxfId="426" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="423" priority="14">
+    <cfRule type="expression" dxfId="425" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="422" priority="13">
+    <cfRule type="expression" dxfId="424" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="421" priority="12">
+    <cfRule type="expression" dxfId="423" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="420" priority="11">
+    <cfRule type="expression" dxfId="422" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="419" priority="10">
+    <cfRule type="expression" dxfId="421" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="418" priority="9">
+    <cfRule type="expression" dxfId="420" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="417" priority="8">
+    <cfRule type="expression" dxfId="419" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="416" priority="7">
+    <cfRule type="expression" dxfId="418" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="415" priority="6">
+    <cfRule type="expression" dxfId="417" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="414" priority="5">
+    <cfRule type="expression" dxfId="416" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="413" priority="4">
+    <cfRule type="expression" dxfId="415" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="412" priority="3">
+    <cfRule type="expression" dxfId="414" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="411" priority="2">
+    <cfRule type="expression" dxfId="413" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="410" priority="1">
+    <cfRule type="expression" dxfId="412" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38935,82 +39179,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="409" priority="20">
+    <cfRule type="expression" dxfId="411" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="408" priority="19">
+    <cfRule type="expression" dxfId="410" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="407" priority="18">
+    <cfRule type="expression" dxfId="409" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="406" priority="16">
+    <cfRule type="expression" dxfId="408" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="405" priority="14">
+    <cfRule type="expression" dxfId="407" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="404" priority="13">
+    <cfRule type="expression" dxfId="406" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="403" priority="12">
+    <cfRule type="expression" dxfId="405" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="402" priority="11">
+    <cfRule type="expression" dxfId="404" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="401" priority="10">
+    <cfRule type="expression" dxfId="403" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="400" priority="9">
+    <cfRule type="expression" dxfId="402" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="399" priority="6">
+    <cfRule type="expression" dxfId="401" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="398" priority="5">
+    <cfRule type="expression" dxfId="400" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="397" priority="4">
+    <cfRule type="expression" dxfId="399" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="396" priority="3">
+    <cfRule type="expression" dxfId="398" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="395" priority="2">
+    <cfRule type="expression" dxfId="397" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="394" priority="1">
+    <cfRule type="expression" dxfId="396" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42439,497 +42683,497 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
-    <cfRule type="expression" dxfId="393" priority="229">
+    <cfRule type="expression" dxfId="395" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="392" priority="228">
+    <cfRule type="expression" dxfId="394" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="391" priority="227">
+    <cfRule type="expression" dxfId="393" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="390" priority="226">
+    <cfRule type="expression" dxfId="392" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="389" priority="222">
+    <cfRule type="expression" dxfId="391" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="388" priority="220">
+    <cfRule type="expression" dxfId="390" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="387" priority="218">
+    <cfRule type="expression" dxfId="389" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="386" priority="212">
+    <cfRule type="expression" dxfId="388" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="385" priority="202">
+    <cfRule type="expression" dxfId="387" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="384" priority="207">
+    <cfRule type="expression" dxfId="386" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="383" priority="203">
+    <cfRule type="expression" dxfId="385" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="382" priority="188">
+    <cfRule type="expression" dxfId="384" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="381" priority="183">
+    <cfRule type="expression" dxfId="383" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="380" priority="189">
+    <cfRule type="expression" dxfId="382" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="379" priority="174">
+    <cfRule type="expression" dxfId="381" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="378" priority="172">
+    <cfRule type="expression" dxfId="380" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="377" priority="171">
+    <cfRule type="expression" dxfId="379" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="376" priority="166">
+    <cfRule type="expression" dxfId="378" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="375" priority="162">
+    <cfRule type="expression" dxfId="377" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="374" priority="163">
+    <cfRule type="expression" dxfId="376" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="373" priority="157">
+    <cfRule type="expression" dxfId="375" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="372" priority="143">
+    <cfRule type="expression" dxfId="374" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="371" priority="142">
+    <cfRule type="expression" dxfId="373" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="370" priority="132">
+    <cfRule type="expression" dxfId="372" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="369" priority="126">
+    <cfRule type="expression" dxfId="371" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="368" priority="125">
+    <cfRule type="expression" dxfId="370" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="367" priority="124">
+    <cfRule type="expression" dxfId="369" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="366" priority="123">
+    <cfRule type="expression" dxfId="368" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="365" priority="122">
+    <cfRule type="expression" dxfId="367" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="364" priority="121">
+    <cfRule type="expression" dxfId="366" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="363" priority="120">
+    <cfRule type="expression" dxfId="365" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="362" priority="109">
+    <cfRule type="expression" dxfId="364" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="361" priority="105">
+    <cfRule type="expression" dxfId="363" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="360" priority="104">
+    <cfRule type="expression" dxfId="362" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="359" priority="101">
+    <cfRule type="expression" dxfId="361" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="358" priority="97">
+    <cfRule type="expression" dxfId="360" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="357" priority="92">
+    <cfRule type="expression" dxfId="359" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="356" priority="91">
+    <cfRule type="expression" dxfId="358" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="355" priority="88">
+    <cfRule type="expression" dxfId="357" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="354" priority="89">
+    <cfRule type="expression" dxfId="356" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="353" priority="83">
+    <cfRule type="expression" dxfId="355" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="352" priority="82">
+    <cfRule type="expression" dxfId="354" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="351" priority="74">
+    <cfRule type="expression" dxfId="353" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="350" priority="73">
+    <cfRule type="expression" dxfId="352" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="349" priority="70">
+    <cfRule type="expression" dxfId="351" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="348" priority="71">
+    <cfRule type="expression" dxfId="350" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="347" priority="63">
+    <cfRule type="expression" dxfId="349" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="346" priority="62">
+    <cfRule type="expression" dxfId="348" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="345" priority="61">
+    <cfRule type="expression" dxfId="347" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="344" priority="60">
+    <cfRule type="expression" dxfId="346" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="343" priority="59">
+    <cfRule type="expression" dxfId="345" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="342" priority="58">
+    <cfRule type="expression" dxfId="344" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="341" priority="47">
+    <cfRule type="expression" dxfId="343" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="340" priority="57">
+    <cfRule type="expression" dxfId="342" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="339" priority="56">
+    <cfRule type="expression" dxfId="341" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="338" priority="55">
+    <cfRule type="expression" dxfId="340" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="337" priority="54">
+    <cfRule type="expression" dxfId="339" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="336" priority="53">
+    <cfRule type="expression" dxfId="338" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="335" priority="52">
+    <cfRule type="expression" dxfId="337" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="334" priority="51">
+    <cfRule type="expression" dxfId="336" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="333" priority="50">
+    <cfRule type="expression" dxfId="335" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="332" priority="48">
+    <cfRule type="expression" dxfId="334" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="331" priority="46">
+    <cfRule type="expression" dxfId="333" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="330" priority="45">
+    <cfRule type="expression" dxfId="332" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="329" priority="42">
+    <cfRule type="expression" dxfId="331" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="328" priority="41">
+    <cfRule type="expression" dxfId="330" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="327" priority="34">
+    <cfRule type="expression" dxfId="329" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 M64:N64">
-    <cfRule type="expression" dxfId="326" priority="33">
+    <cfRule type="expression" dxfId="328" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="325" priority="32">
+    <cfRule type="expression" dxfId="327" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="324" priority="31">
+    <cfRule type="expression" dxfId="326" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="323" priority="30">
+    <cfRule type="expression" dxfId="325" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="322" priority="29">
+    <cfRule type="expression" dxfId="324" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="321" priority="28">
+    <cfRule type="expression" dxfId="323" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="320" priority="27">
+    <cfRule type="expression" dxfId="322" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="319" priority="26">
+    <cfRule type="expression" dxfId="321" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="318" priority="25">
+    <cfRule type="expression" dxfId="320" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="317" priority="24">
+    <cfRule type="expression" dxfId="319" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="316" priority="20">
+    <cfRule type="expression" dxfId="318" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="315" priority="23">
+    <cfRule type="expression" dxfId="317" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="314" priority="22">
+    <cfRule type="expression" dxfId="316" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="313" priority="21">
+    <cfRule type="expression" dxfId="315" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="312" priority="19">
+    <cfRule type="expression" dxfId="314" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="311" priority="17">
+    <cfRule type="expression" dxfId="313" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="310" priority="16">
+    <cfRule type="expression" dxfId="312" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="309" priority="15">
+    <cfRule type="expression" dxfId="311" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="308" priority="14">
+    <cfRule type="expression" dxfId="310" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="307" priority="13">
+    <cfRule type="expression" dxfId="309" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="306" priority="12">
+    <cfRule type="expression" dxfId="308" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="305" priority="11">
+    <cfRule type="expression" dxfId="307" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="304" priority="10">
+    <cfRule type="expression" dxfId="306" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="303" priority="9">
+    <cfRule type="expression" dxfId="305" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="302" priority="8">
+    <cfRule type="expression" dxfId="304" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="301" priority="7">
+    <cfRule type="expression" dxfId="303" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="300" priority="6">
+    <cfRule type="expression" dxfId="302" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="299" priority="5">
+    <cfRule type="expression" dxfId="301" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="298" priority="4">
+    <cfRule type="expression" dxfId="300" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="297" priority="3">
+    <cfRule type="expression" dxfId="299" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:J57 M57:N57">
-    <cfRule type="expression" dxfId="296" priority="2">
+    <cfRule type="expression" dxfId="298" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:L70">
-    <cfRule type="expression" dxfId="295" priority="1">
+    <cfRule type="expression" dxfId="297" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48620,42 +48864,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="294" priority="13">
+    <cfRule type="expression" dxfId="296" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="293" priority="12">
+    <cfRule type="expression" dxfId="295" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="292" priority="11">
+    <cfRule type="expression" dxfId="294" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="291" priority="5">
+    <cfRule type="expression" dxfId="293" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="290" priority="4">
+    <cfRule type="expression" dxfId="292" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="289" priority="3">
+    <cfRule type="expression" dxfId="291" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="288" priority="2">
+    <cfRule type="expression" dxfId="290" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="287" priority="1">
+    <cfRule type="expression" dxfId="289" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54693,112 +54937,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="286" priority="28">
+    <cfRule type="expression" dxfId="288" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="285" priority="27">
+    <cfRule type="expression" dxfId="287" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="284" priority="26">
+    <cfRule type="expression" dxfId="286" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="283" priority="25">
+    <cfRule type="expression" dxfId="285" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="282" priority="23">
+    <cfRule type="expression" dxfId="284" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="281" priority="22">
+    <cfRule type="expression" dxfId="283" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="280" priority="20">
+    <cfRule type="expression" dxfId="282" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="279" priority="19">
+    <cfRule type="expression" dxfId="281" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="278" priority="15">
+    <cfRule type="expression" dxfId="280" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="277" priority="14">
+    <cfRule type="expression" dxfId="279" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="276" priority="13">
+    <cfRule type="expression" dxfId="278" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="275" priority="12">
+    <cfRule type="expression" dxfId="277" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="274" priority="11">
+    <cfRule type="expression" dxfId="276" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="273" priority="10">
+    <cfRule type="expression" dxfId="275" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="272" priority="9">
+    <cfRule type="expression" dxfId="274" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="271" priority="8">
+    <cfRule type="expression" dxfId="273" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="270" priority="7">
+    <cfRule type="expression" dxfId="272" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="269" priority="6">
+    <cfRule type="expression" dxfId="271" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="268" priority="1">
+    <cfRule type="expression" dxfId="270" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="267" priority="5">
+    <cfRule type="expression" dxfId="269" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="266" priority="4">
+    <cfRule type="expression" dxfId="268" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="265" priority="2">
+    <cfRule type="expression" dxfId="267" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60713,107 +60957,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="264" priority="24">
+    <cfRule type="expression" dxfId="266" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="263" priority="23">
+    <cfRule type="expression" dxfId="265" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="262" priority="22">
+    <cfRule type="expression" dxfId="264" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="261" priority="21">
+    <cfRule type="expression" dxfId="263" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="260" priority="20">
+    <cfRule type="expression" dxfId="262" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="259" priority="19">
+    <cfRule type="expression" dxfId="261" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="258" priority="18">
+    <cfRule type="expression" dxfId="260" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="257" priority="15">
+    <cfRule type="expression" dxfId="259" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="256" priority="14">
+    <cfRule type="expression" dxfId="258" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="255" priority="13">
+    <cfRule type="expression" dxfId="257" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="254" priority="12">
+    <cfRule type="expression" dxfId="256" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="253" priority="1">
+    <cfRule type="expression" dxfId="255" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="252" priority="10">
+    <cfRule type="expression" dxfId="254" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="251" priority="9">
+    <cfRule type="expression" dxfId="253" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="250" priority="8">
+    <cfRule type="expression" dxfId="252" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="249" priority="7">
+    <cfRule type="expression" dxfId="251" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="248" priority="6">
+    <cfRule type="expression" dxfId="250" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="247" priority="5">
+    <cfRule type="expression" dxfId="249" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="246" priority="4">
+    <cfRule type="expression" dxfId="248" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="245" priority="3">
+    <cfRule type="expression" dxfId="247" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="244" priority="2">
+    <cfRule type="expression" dxfId="246" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3236" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="332">
   <si>
     <t>Sudeep</t>
   </si>
@@ -1020,6 +1020,9 @@
   </si>
   <si>
     <t>DEC ROI</t>
+  </si>
+  <si>
+    <t>P3445</t>
   </si>
 </sst>
 </file>
@@ -6740,15 +6743,17 @@
       <c r="K4" s="157">
         <v>29052</v>
       </c>
-      <c r="L4" s="157"/>
+      <c r="L4" s="157">
+        <v>42300</v>
+      </c>
       <c r="M4" s="210"/>
       <c r="N4" s="170">
         <f t="shared" ref="N4:N35" si="0">SUM(H4:M4)</f>
-        <v>44320</v>
+        <v>86620</v>
       </c>
       <c r="O4" s="148">
         <f t="shared" ref="O4:O35" si="1">IFERROR(N4/F4*100,0)/10000000</f>
-        <v>0.88639999999999997</v>
+        <v>1.7323999999999999</v>
       </c>
       <c r="V4" s="132" t="s">
         <v>170</v>
@@ -6789,15 +6794,17 @@
       <c r="K5" s="146">
         <v>94938</v>
       </c>
-      <c r="L5" s="146"/>
+      <c r="L5" s="146">
+        <v>96755</v>
+      </c>
       <c r="M5" s="173"/>
       <c r="N5" s="170">
         <f t="shared" si="0"/>
-        <v>94140</v>
+        <v>190895</v>
       </c>
       <c r="O5" s="148">
         <f t="shared" si="1"/>
-        <v>0.31380000000000002</v>
+        <v>0.63631666666666664</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -6832,15 +6839,17 @@
       <c r="K6" s="146">
         <v>50440</v>
       </c>
-      <c r="L6" s="146"/>
+      <c r="L6" s="146">
+        <v>44170</v>
+      </c>
       <c r="M6" s="173"/>
       <c r="N6" s="170">
         <f t="shared" si="0"/>
-        <v>27367</v>
+        <v>71537</v>
       </c>
       <c r="O6" s="148">
         <f t="shared" si="1"/>
-        <v>0.27367000000000002</v>
+        <v>0.71536999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6875,15 +6884,17 @@
       <c r="K7" s="146">
         <v>-140210</v>
       </c>
-      <c r="L7" s="146"/>
+      <c r="L7" s="146">
+        <v>-117400</v>
+      </c>
       <c r="M7" s="173"/>
       <c r="N7" s="170">
         <f t="shared" si="0"/>
-        <v>-207210</v>
+        <v>-324610</v>
       </c>
       <c r="O7" s="148">
         <f t="shared" si="1"/>
-        <v>-0.69069999999999998</v>
+        <v>-1.0820333333333332</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="133">
@@ -6922,15 +6933,17 @@
       <c r="K8" s="146">
         <v>18290</v>
       </c>
-      <c r="L8" s="146"/>
+      <c r="L8" s="146">
+        <v>11000</v>
+      </c>
       <c r="M8" s="173"/>
       <c r="N8" s="170">
         <f t="shared" si="0"/>
-        <v>108340</v>
+        <v>119340</v>
       </c>
       <c r="O8" s="148">
         <f t="shared" si="1"/>
-        <v>0.72226666666666672</v>
+        <v>0.79559999999999997</v>
       </c>
       <c r="Q8" s="133">
         <v>468159</v>
@@ -6967,15 +6980,17 @@
       <c r="K9" s="146">
         <v>4948</v>
       </c>
-      <c r="L9" s="146"/>
+      <c r="L9" s="146">
+        <v>25000</v>
+      </c>
       <c r="M9" s="173"/>
       <c r="N9" s="170">
         <f t="shared" si="0"/>
-        <v>42214</v>
+        <v>67214</v>
       </c>
       <c r="O9" s="148">
         <f t="shared" si="1"/>
-        <v>0.70356666666666667</v>
+        <v>1.1202333333333334</v>
       </c>
       <c r="Q9" s="133">
         <v>453904</v>
@@ -7017,7 +7032,9 @@
       <c r="K10" s="146">
         <v>13730</v>
       </c>
-      <c r="L10" s="146"/>
+      <c r="L10" s="146">
+        <v>0</v>
+      </c>
       <c r="M10" s="173"/>
       <c r="N10" s="170">
         <f t="shared" si="0"/>
@@ -7062,15 +7079,17 @@
       <c r="K11" s="146">
         <v>0</v>
       </c>
-      <c r="L11" s="146"/>
+      <c r="L11" s="146">
+        <v>55700</v>
+      </c>
       <c r="M11" s="173"/>
       <c r="N11" s="170">
         <f t="shared" si="0"/>
-        <v>170431</v>
+        <v>226131</v>
       </c>
       <c r="O11" s="148">
         <f t="shared" si="1"/>
-        <v>0.2840516666666667</v>
+        <v>0.37688500000000003</v>
       </c>
       <c r="Q11" s="133"/>
       <c r="R11" s="133"/>
@@ -7107,15 +7126,17 @@
       <c r="K12" s="146">
         <v>-1616</v>
       </c>
-      <c r="L12" s="146"/>
+      <c r="L12" s="146">
+        <v>-2953</v>
+      </c>
       <c r="M12" s="173"/>
       <c r="N12" s="170">
         <f t="shared" si="0"/>
-        <v>-1938</v>
+        <v>-4891</v>
       </c>
       <c r="O12" s="148">
         <f t="shared" si="1"/>
-        <v>-1.9380000000000001E-2</v>
+        <v>-4.8910000000000002E-2</v>
       </c>
       <c r="Q12" s="133"/>
       <c r="R12" s="133"/>
@@ -7152,15 +7173,17 @@
       <c r="K13" s="146">
         <v>0</v>
       </c>
-      <c r="L13" s="146"/>
+      <c r="L13" s="146">
+        <v>22700</v>
+      </c>
       <c r="M13" s="173"/>
       <c r="N13" s="170">
         <f t="shared" si="0"/>
-        <v>68353</v>
+        <v>91053</v>
       </c>
       <c r="O13" s="148">
         <f t="shared" si="1"/>
-        <v>0.27341199999999999</v>
+        <v>0.36421199999999998</v>
       </c>
       <c r="Q13" s="133"/>
       <c r="R13" s="133"/>
@@ -7197,15 +7220,17 @@
       <c r="K14" s="146">
         <v>0</v>
       </c>
-      <c r="L14" s="146"/>
+      <c r="L14" s="146">
+        <v>30900</v>
+      </c>
       <c r="M14" s="173"/>
       <c r="N14" s="170">
         <f t="shared" si="0"/>
-        <v>77903</v>
+        <v>108803</v>
       </c>
       <c r="O14" s="148">
         <f t="shared" si="1"/>
-        <v>0.35410454545454545</v>
+        <v>0.49455909090909089</v>
       </c>
       <c r="Q14" s="133"/>
       <c r="R14" s="192">
@@ -7252,15 +7277,17 @@
       <c r="K15" s="146">
         <v>-6218</v>
       </c>
-      <c r="L15" s="146"/>
+      <c r="L15" s="146">
+        <v>-30200</v>
+      </c>
       <c r="M15" s="173"/>
       <c r="N15" s="170">
         <f t="shared" si="0"/>
-        <v>14282</v>
+        <v>-15918</v>
       </c>
       <c r="O15" s="148">
         <f t="shared" si="1"/>
-        <v>0.14282</v>
+        <v>-0.15917999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -7295,7 +7322,9 @@
       <c r="K16" s="146">
         <v>0</v>
       </c>
-      <c r="L16" s="146"/>
+      <c r="L16" s="146">
+        <v>0</v>
+      </c>
       <c r="M16" s="173"/>
       <c r="N16" s="170">
         <f t="shared" si="0"/>
@@ -7349,7 +7378,9 @@
       <c r="K17" s="146">
         <v>0</v>
       </c>
-      <c r="L17" s="146"/>
+      <c r="L17" s="146">
+        <v>0</v>
+      </c>
       <c r="M17" s="173"/>
       <c r="N17" s="170">
         <f t="shared" si="0"/>
@@ -7396,15 +7427,17 @@
       <c r="K18" s="146">
         <v>-95099</v>
       </c>
-      <c r="L18" s="146"/>
+      <c r="L18" s="146">
+        <v>141000</v>
+      </c>
       <c r="M18" s="173"/>
       <c r="N18" s="170">
         <f t="shared" si="0"/>
-        <v>-50285</v>
+        <v>90715</v>
       </c>
       <c r="O18" s="148">
         <f t="shared" si="1"/>
-        <v>-0.33523333333333333</v>
+        <v>0.60476666666666656</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -7439,7 +7472,9 @@
       <c r="K19" s="146">
         <v>0</v>
       </c>
-      <c r="L19" s="146"/>
+      <c r="L19" s="146">
+        <v>0</v>
+      </c>
       <c r="M19" s="173"/>
       <c r="N19" s="170">
         <f t="shared" si="0"/>
@@ -7485,15 +7520,17 @@
       <c r="K20" s="146">
         <v>7212</v>
       </c>
-      <c r="L20" s="146"/>
+      <c r="L20" s="146">
+        <v>-17400</v>
+      </c>
       <c r="M20" s="173"/>
       <c r="N20" s="170">
         <f t="shared" si="0"/>
-        <v>-68242</v>
+        <v>-85642</v>
       </c>
       <c r="O20" s="148">
         <f t="shared" si="1"/>
-        <v>-2.7296800000000001</v>
+        <v>-3.4256799999999998</v>
       </c>
       <c r="S20" s="132">
         <v>-52140</v>
@@ -7531,7 +7568,9 @@
       <c r="K21" s="146">
         <v>0</v>
       </c>
-      <c r="L21" s="146"/>
+      <c r="L21" s="146">
+        <v>0</v>
+      </c>
       <c r="M21" s="173"/>
       <c r="N21" s="170">
         <f t="shared" si="0"/>
@@ -7577,7 +7616,9 @@
       <c r="K22" s="146">
         <v>0</v>
       </c>
-      <c r="L22" s="146"/>
+      <c r="L22" s="146">
+        <v>0</v>
+      </c>
       <c r="M22" s="173"/>
       <c r="N22" s="170">
         <f t="shared" si="0"/>
@@ -7620,15 +7661,17 @@
       <c r="K23" s="146">
         <v>38700</v>
       </c>
-      <c r="L23" s="146"/>
+      <c r="L23" s="146">
+        <v>-1623</v>
+      </c>
       <c r="M23" s="173"/>
       <c r="N23" s="170">
         <f t="shared" si="0"/>
-        <v>28323</v>
+        <v>26700</v>
       </c>
       <c r="O23" s="148">
         <f t="shared" si="1"/>
-        <v>0.25748181818181815</v>
+        <v>0.24272727272727271</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -7663,15 +7706,17 @@
       <c r="K24" s="146">
         <v>-128600</v>
       </c>
-      <c r="L24" s="146"/>
+      <c r="L24" s="146">
+        <v>-381800</v>
+      </c>
       <c r="M24" s="173"/>
       <c r="N24" s="170">
         <f t="shared" si="0"/>
-        <v>-61800</v>
+        <v>-443600</v>
       </c>
       <c r="O24" s="148">
         <f t="shared" si="1"/>
-        <v>-0.26869565217391306</v>
+        <v>-1.9286956521739134</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -7704,15 +7749,17 @@
       <c r="K25" s="146">
         <v>-2835</v>
       </c>
-      <c r="L25" s="146"/>
+      <c r="L25" s="146">
+        <v>10900</v>
+      </c>
       <c r="M25" s="173"/>
       <c r="N25" s="170">
         <f t="shared" si="0"/>
-        <v>-109</v>
+        <v>10791</v>
       </c>
       <c r="O25" s="148">
         <f t="shared" si="1"/>
-        <v>-5.45E-3</v>
+        <v>0.53954999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -7747,7 +7794,9 @@
       <c r="K26" s="146">
         <v>0</v>
       </c>
-      <c r="L26" s="146"/>
+      <c r="L26" s="146">
+        <v>0</v>
+      </c>
       <c r="M26" s="173"/>
       <c r="N26" s="170">
         <f t="shared" si="0"/>
@@ -7790,15 +7839,17 @@
       <c r="K27" s="146">
         <v>302380</v>
       </c>
-      <c r="L27" s="146"/>
+      <c r="L27" s="146">
+        <v>55800</v>
+      </c>
       <c r="M27" s="173"/>
       <c r="N27" s="170">
         <f t="shared" si="0"/>
-        <v>412715</v>
+        <v>468515</v>
       </c>
       <c r="O27" s="148">
         <f t="shared" si="1"/>
-        <v>0.412715</v>
+        <v>0.46851500000000001</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -7833,15 +7884,17 @@
       <c r="K28" s="146">
         <v>0</v>
       </c>
-      <c r="L28" s="146"/>
+      <c r="L28" s="146">
+        <v>155700</v>
+      </c>
       <c r="M28" s="173"/>
       <c r="N28" s="170">
         <f t="shared" si="0"/>
-        <v>401130</v>
+        <v>556830</v>
       </c>
       <c r="O28" s="148">
         <f t="shared" si="1"/>
-        <v>0.80225999999999997</v>
+        <v>1.1136600000000001</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -7876,15 +7929,17 @@
       <c r="K29" s="146">
         <v>2600</v>
       </c>
-      <c r="L29" s="146"/>
+      <c r="L29" s="146">
+        <v>44000</v>
+      </c>
       <c r="M29" s="173"/>
       <c r="N29" s="170">
         <f t="shared" si="0"/>
-        <v>-108150</v>
+        <v>-64150</v>
       </c>
       <c r="O29" s="148">
         <f t="shared" si="1"/>
-        <v>-0.21629999999999999</v>
+        <v>-0.1283</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -7919,15 +7974,17 @@
       <c r="K30" s="146">
         <v>-7694</v>
       </c>
-      <c r="L30" s="146"/>
+      <c r="L30" s="146">
+        <v>34100</v>
+      </c>
       <c r="M30" s="173"/>
       <c r="N30" s="170">
         <f t="shared" si="0"/>
-        <v>3799</v>
+        <v>37899</v>
       </c>
       <c r="O30" s="148">
         <f t="shared" si="1"/>
-        <v>7.5980000000000006E-2</v>
+        <v>0.75797999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -7962,15 +8019,17 @@
       <c r="K31" s="146">
         <v>1293</v>
       </c>
-      <c r="L31" s="146"/>
+      <c r="L31" s="146">
+        <v>33700</v>
+      </c>
       <c r="M31" s="173"/>
       <c r="N31" s="170">
         <f t="shared" si="0"/>
-        <v>81468</v>
+        <v>115168</v>
       </c>
       <c r="O31" s="148">
         <f t="shared" si="1"/>
-        <v>2.0367000000000002</v>
+        <v>2.8792</v>
       </c>
       <c r="R31" s="133"/>
     </row>
@@ -8006,15 +8065,17 @@
       <c r="K32" s="146">
         <v>-98197</v>
       </c>
-      <c r="L32" s="146"/>
+      <c r="L32" s="146">
+        <v>149600</v>
+      </c>
       <c r="M32" s="173"/>
       <c r="N32" s="170">
         <f t="shared" si="0"/>
-        <v>-147529</v>
+        <v>2071</v>
       </c>
       <c r="O32" s="148">
         <f t="shared" si="1"/>
-        <v>-0.3688225</v>
+        <v>5.1774999999999998E-3</v>
       </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="133">
@@ -8053,15 +8114,17 @@
       <c r="K33" s="146">
         <v>-13148</v>
       </c>
-      <c r="L33" s="146"/>
+      <c r="L33" s="146">
+        <v>-107400</v>
+      </c>
       <c r="M33" s="173"/>
       <c r="N33" s="170">
         <f t="shared" si="0"/>
-        <v>9674</v>
+        <v>-97726</v>
       </c>
       <c r="O33" s="148">
         <f t="shared" si="1"/>
-        <v>9.6740000000000007E-2</v>
+        <v>-0.97726000000000002</v>
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="133"/>
@@ -8096,7 +8159,9 @@
       <c r="K34" s="146">
         <v>0</v>
       </c>
-      <c r="L34" s="146"/>
+      <c r="L34" s="146">
+        <v>0</v>
+      </c>
       <c r="M34" s="173"/>
       <c r="N34" s="170">
         <f t="shared" si="0"/>
@@ -8146,15 +8211,17 @@
       <c r="K35" s="146">
         <v>-15524</v>
       </c>
-      <c r="L35" s="146"/>
+      <c r="L35" s="146">
+        <v>23400</v>
+      </c>
       <c r="M35" s="173"/>
       <c r="N35" s="170">
         <f t="shared" si="0"/>
-        <v>-8895</v>
+        <v>14505</v>
       </c>
       <c r="O35" s="148">
         <f t="shared" si="1"/>
-        <v>-0.1779</v>
+        <v>0.29010000000000002</v>
       </c>
       <c r="Q35" s="133">
         <v>604754</v>
@@ -8193,15 +8260,17 @@
       <c r="K36" s="146">
         <v>79524</v>
       </c>
-      <c r="L36" s="146"/>
+      <c r="L36" s="146">
+        <v>-8546</v>
+      </c>
       <c r="M36" s="173"/>
       <c r="N36" s="170">
         <f t="shared" ref="N36:N67" si="2">SUM(H36:M36)</f>
-        <v>183624</v>
+        <v>175078</v>
       </c>
       <c r="O36" s="148">
         <f t="shared" ref="O36:O67" si="3">IFERROR(N36/F36*100,0)/10000000</f>
-        <v>0.61207999999999996</v>
+        <v>0.58359333333333341</v>
       </c>
       <c r="Q36" s="133"/>
       <c r="R36" s="133">
@@ -8239,15 +8308,17 @@
       <c r="K37" s="146">
         <v>-19285</v>
       </c>
-      <c r="L37" s="146"/>
+      <c r="L37" s="146">
+        <v>59000</v>
+      </c>
       <c r="M37" s="173"/>
       <c r="N37" s="170">
         <f t="shared" si="2"/>
-        <v>6368</v>
+        <v>65368</v>
       </c>
       <c r="O37" s="148">
         <f t="shared" si="3"/>
-        <v>0.63680000000000003</v>
+        <v>6.5368000000000004</v>
       </c>
       <c r="Q37" s="133"/>
       <c r="R37" s="133"/>
@@ -8284,15 +8355,17 @@
       <c r="K38" s="146">
         <v>-16500</v>
       </c>
-      <c r="L38" s="146"/>
+      <c r="L38" s="146">
+        <v>26900</v>
+      </c>
       <c r="M38" s="173"/>
       <c r="N38" s="170">
         <f t="shared" si="2"/>
-        <v>3300</v>
+        <v>30200</v>
       </c>
       <c r="O38" s="148">
         <f t="shared" si="3"/>
-        <v>6.6000000000000003E-2</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="Q38" s="133"/>
       <c r="R38" s="133"/>
@@ -8329,15 +8402,17 @@
       <c r="K39" s="146">
         <v>-85245</v>
       </c>
-      <c r="L39" s="146"/>
+      <c r="L39" s="146">
+        <v>-484000</v>
+      </c>
       <c r="M39" s="173"/>
       <c r="N39" s="170">
         <f t="shared" si="2"/>
-        <v>-171229</v>
+        <v>-655229</v>
       </c>
       <c r="O39" s="148">
         <f t="shared" si="3"/>
-        <v>-1.7122900000000001</v>
+        <v>-6.5522900000000002</v>
       </c>
       <c r="Q39" s="133"/>
       <c r="R39" s="133"/>
@@ -8372,15 +8447,17 @@
       <c r="K40" s="146">
         <v>-21500</v>
       </c>
-      <c r="L40" s="146"/>
+      <c r="L40" s="146">
+        <v>18000</v>
+      </c>
       <c r="M40" s="173"/>
       <c r="N40" s="170">
         <f t="shared" si="2"/>
-        <v>-17235</v>
+        <v>765</v>
       </c>
       <c r="O40" s="148">
         <f t="shared" si="3"/>
-        <v>-1.7235</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="Q40" s="133"/>
     </row>
@@ -8416,15 +8493,17 @@
       <c r="K41" s="146">
         <v>0</v>
       </c>
-      <c r="L41" s="146"/>
+      <c r="L41" s="146">
+        <v>52100</v>
+      </c>
       <c r="M41" s="173"/>
       <c r="N41" s="170">
         <f t="shared" si="2"/>
-        <v>2920</v>
+        <v>55020</v>
       </c>
       <c r="O41" s="148">
         <f t="shared" si="3"/>
-        <v>7.3000000000000001E-3</v>
+        <v>0.13755000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -8459,7 +8538,9 @@
       <c r="K42" s="146">
         <v>0</v>
       </c>
-      <c r="L42" s="146"/>
+      <c r="L42" s="146">
+        <v>0</v>
+      </c>
       <c r="M42" s="173"/>
       <c r="N42" s="170">
         <f t="shared" si="2"/>
@@ -8502,15 +8583,17 @@
       <c r="K43" s="146">
         <v>-135130</v>
       </c>
-      <c r="L43" s="146"/>
+      <c r="L43" s="146">
+        <v>290000</v>
+      </c>
       <c r="M43" s="173"/>
       <c r="N43" s="170">
         <f t="shared" si="2"/>
-        <v>33128</v>
+        <v>323128</v>
       </c>
       <c r="O43" s="148">
         <f t="shared" si="3"/>
-        <v>0.11042666666666665</v>
+        <v>1.0770933333333332</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -8543,15 +8626,17 @@
       <c r="K44" s="150">
         <v>63150</v>
       </c>
-      <c r="L44" s="150"/>
+      <c r="L44" s="150">
+        <v>-461500</v>
+      </c>
       <c r="M44" s="173"/>
       <c r="N44" s="170">
         <f t="shared" si="2"/>
-        <v>206750</v>
+        <v>-254750</v>
       </c>
       <c r="O44" s="148">
         <f t="shared" si="3"/>
-        <v>0.20674999999999999</v>
+        <v>-0.25474999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -8582,7 +8667,9 @@
       <c r="K45" s="150">
         <v>0</v>
       </c>
-      <c r="L45" s="150"/>
+      <c r="L45" s="150">
+        <v>0</v>
+      </c>
       <c r="M45" s="173"/>
       <c r="N45" s="170">
         <f t="shared" si="2"/>
@@ -8625,15 +8712,17 @@
       <c r="K46" s="150">
         <v>30076</v>
       </c>
-      <c r="L46" s="150"/>
+      <c r="L46" s="150">
+        <v>-25200</v>
+      </c>
       <c r="M46" s="173"/>
       <c r="N46" s="170">
         <f t="shared" si="2"/>
-        <v>65485</v>
+        <v>40285</v>
       </c>
       <c r="O46" s="148">
         <f t="shared" si="3"/>
-        <v>1.3097000000000001</v>
+        <v>0.80569999999999997</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -8668,15 +8757,17 @@
       <c r="K47" s="150">
         <v>0</v>
       </c>
-      <c r="L47" s="150"/>
+      <c r="L47" s="150">
+        <v>53400</v>
+      </c>
       <c r="M47" s="173"/>
       <c r="N47" s="170">
         <f t="shared" si="2"/>
-        <v>306496</v>
+        <v>359896</v>
       </c>
       <c r="O47" s="148">
         <f t="shared" si="3"/>
-        <v>0.4715323076923077</v>
+        <v>0.55368615384615383</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -8711,7 +8802,9 @@
       <c r="K48" s="150">
         <v>0</v>
       </c>
-      <c r="L48" s="150"/>
+      <c r="L48" s="150">
+        <v>0</v>
+      </c>
       <c r="M48" s="173"/>
       <c r="N48" s="170">
         <f t="shared" si="2"/>
@@ -8754,19 +8847,23 @@
       <c r="K49" s="150">
         <v>0</v>
       </c>
-      <c r="L49" s="150"/>
+      <c r="L49" s="150">
+        <v>96100</v>
+      </c>
       <c r="M49" s="173"/>
       <c r="N49" s="170">
         <f t="shared" si="2"/>
-        <v>56120</v>
+        <v>152220</v>
       </c>
       <c r="O49" s="148">
         <f t="shared" si="3"/>
-        <v>0.18706666666666669</v>
+        <v>0.50739999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="59"/>
+      <c r="A50" s="59" t="s">
+        <v>331</v>
+      </c>
       <c r="B50" s="59" t="s">
         <v>286</v>
       </c>
@@ -8795,15 +8892,17 @@
       <c r="K50" s="150">
         <v>520</v>
       </c>
-      <c r="L50" s="150"/>
+      <c r="L50" s="150">
+        <v>-800</v>
+      </c>
       <c r="M50" s="173"/>
       <c r="N50" s="170">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>-230</v>
       </c>
       <c r="O50" s="148">
         <f t="shared" si="3"/>
-        <v>5.7000000000000002E-3</v>
+        <v>-2.3E-3</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8838,15 +8937,17 @@
       <c r="K51" s="150">
         <v>17309</v>
       </c>
-      <c r="L51" s="150"/>
+      <c r="L51" s="150">
+        <v>26900</v>
+      </c>
       <c r="M51" s="173"/>
       <c r="N51" s="170">
         <f t="shared" si="2"/>
-        <v>100956</v>
+        <v>127856</v>
       </c>
       <c r="O51" s="148">
         <f t="shared" si="3"/>
-        <v>0.20191200000000001</v>
+        <v>0.25571199999999999</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8875,7 +8976,7 @@
       </c>
       <c r="L52" s="253">
         <f>SUM(L4:L51)</f>
-        <v>0</v>
+        <v>-39697</v>
       </c>
       <c r="M52" s="253">
         <f>SUM(M4:M51)</f>
@@ -8883,7 +8984,7 @@
       </c>
       <c r="N52" s="253">
         <f t="shared" si="2"/>
-        <v>1252672</v>
+        <v>1212975</v>
       </c>
       <c r="O52" s="254">
         <f t="shared" si="3"/>
@@ -8939,15 +9040,17 @@
       <c r="K54" s="161">
         <v>15600</v>
       </c>
-      <c r="L54" s="161"/>
+      <c r="L54" s="161">
+        <v>149000</v>
+      </c>
       <c r="M54" s="245"/>
       <c r="N54" s="246">
         <f>SUM(H54:M54)</f>
-        <v>151126</v>
+        <v>300126</v>
       </c>
       <c r="O54" s="247">
         <f>IFERROR(N54/F54*100,0)/10000000</f>
-        <v>0.50375333333333339</v>
+        <v>1.0004200000000001</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8980,7 +9083,9 @@
       <c r="K55" s="161">
         <v>0</v>
       </c>
-      <c r="L55" s="161"/>
+      <c r="L55" s="161">
+        <v>0</v>
+      </c>
       <c r="M55" s="173"/>
       <c r="N55" s="170">
         <f>SUM(H55:M55)</f>
@@ -9017,7 +9122,7 @@
       </c>
       <c r="L56" s="169">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="M56" s="169">
         <f>SUM(M54:M55)</f>
@@ -9025,7 +9130,7 @@
       </c>
       <c r="N56" s="256">
         <f>SUM(H56:M56)</f>
-        <v>249126</v>
+        <v>398126</v>
       </c>
       <c r="O56" s="172"/>
     </row>
@@ -9502,7 +9607,7 @@
       <c r="R6" s="158"/>
       <c r="S6" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>44320</v>
+        <v>86620</v>
       </c>
       <c r="T6" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9514,7 +9619,7 @@
       <c r="X6" s="131"/>
       <c r="Y6" s="153">
         <f t="shared" si="0"/>
-        <v>-508154</v>
+        <v>-465854</v>
       </c>
       <c r="Z6" s="167">
         <f t="shared" si="1"/>
@@ -9584,7 +9689,7 @@
       <c r="R7" s="158"/>
       <c r="S7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>94140</v>
+        <v>190895</v>
       </c>
       <c r="T7" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9596,7 +9701,7 @@
       <c r="X7"/>
       <c r="Y7" s="153">
         <f t="shared" si="0"/>
-        <v>1336354</v>
+        <v>1433109</v>
       </c>
       <c r="Z7" s="167">
         <f t="shared" si="1"/>
@@ -9720,7 +9825,7 @@
       <c r="R9" s="158"/>
       <c r="S9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>27367</v>
+        <v>71537</v>
       </c>
       <c r="T9" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9731,7 +9836,7 @@
       <c r="W9" s="149"/>
       <c r="Y9" s="153">
         <f t="shared" ref="Y9" si="6">M9+P9+S9+V9</f>
-        <v>-109019</v>
+        <v>-64849</v>
       </c>
       <c r="Z9" s="167">
         <f t="shared" ref="Z9" si="7">(N9+Q9+T9+W9)</f>
@@ -9801,7 +9906,7 @@
       <c r="R10" s="158"/>
       <c r="S10" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-207210</v>
+        <v>-324610</v>
       </c>
       <c r="T10" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9812,7 +9917,7 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="153">
         <f t="shared" si="0"/>
-        <v>-1383277</v>
+        <v>-1500677</v>
       </c>
       <c r="Z10" s="167">
         <f t="shared" si="1"/>
@@ -9882,7 +9987,7 @@
       <c r="R11" s="158"/>
       <c r="S11" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>108340</v>
+        <v>119340</v>
       </c>
       <c r="T11" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9893,7 +9998,7 @@
       <c r="W11" s="149"/>
       <c r="Y11" s="153">
         <f t="shared" si="0"/>
-        <v>-293535</v>
+        <v>-282535</v>
       </c>
       <c r="Z11" s="167">
         <f t="shared" si="1"/>
@@ -9963,7 +10068,7 @@
       <c r="R12" s="158"/>
       <c r="S12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>42214</v>
+        <v>67214</v>
       </c>
       <c r="T12" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9974,7 +10079,7 @@
       <c r="W12" s="149"/>
       <c r="Y12" s="153">
         <f t="shared" ref="Y12" si="12">M12+P12+S12+V12</f>
-        <v>-47715</v>
+        <v>-22715</v>
       </c>
       <c r="Z12" s="167">
         <f t="shared" ref="Z12" si="13">(N12+Q12+T12+W12)</f>
@@ -10453,7 +10558,7 @@
       <c r="R18" s="158"/>
       <c r="S18" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>170431</v>
+        <v>226131</v>
       </c>
       <c r="T18" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10464,7 +10569,7 @@
       <c r="W18" s="72"/>
       <c r="Y18" s="153">
         <f t="shared" si="0"/>
-        <v>370483</v>
+        <v>426183</v>
       </c>
       <c r="Z18" s="167">
         <f t="shared" si="1"/>
@@ -10534,7 +10639,7 @@
       <c r="R19" s="158"/>
       <c r="S19" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-1938</v>
+        <v>-4891</v>
       </c>
       <c r="T19" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10545,7 +10650,7 @@
       <c r="W19" s="149"/>
       <c r="Y19" s="153">
         <f t="shared" si="0"/>
-        <v>637</v>
+        <v>-2316</v>
       </c>
       <c r="Z19" s="167">
         <f t="shared" si="1"/>
@@ -10705,7 +10810,7 @@
       <c r="R21" s="158"/>
       <c r="S21" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>68353</v>
+        <v>91053</v>
       </c>
       <c r="T21" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10716,7 +10821,7 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="153">
         <f t="shared" si="0"/>
-        <v>-182829</v>
+        <v>-160129</v>
       </c>
       <c r="Z21" s="167">
         <f t="shared" si="1"/>
@@ -10786,7 +10891,7 @@
       <c r="R22" s="158"/>
       <c r="S22" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>77903</v>
+        <v>108803</v>
       </c>
       <c r="T22" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10797,7 +10902,7 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="153">
         <f t="shared" si="0"/>
-        <v>-125720</v>
+        <v>-94820</v>
       </c>
       <c r="Z22" s="167">
         <f t="shared" si="1"/>
@@ -10948,7 +11053,7 @@
       <c r="R24" s="158"/>
       <c r="S24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>14282</v>
+        <v>-15918</v>
       </c>
       <c r="T24" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10959,7 +11064,7 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="153">
         <f t="shared" si="0"/>
-        <v>1760463</v>
+        <v>1730263</v>
       </c>
       <c r="Z24" s="167">
         <f t="shared" si="1"/>
@@ -11604,7 +11709,7 @@
       <c r="R32" s="158"/>
       <c r="S32" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-50285</v>
+        <v>90715</v>
       </c>
       <c r="T32" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11616,7 +11721,7 @@
       <c r="X32"/>
       <c r="Y32" s="153">
         <f t="shared" si="0"/>
-        <v>-536290</v>
+        <v>-395290</v>
       </c>
       <c r="Z32" s="167">
         <f t="shared" si="1"/>
@@ -11767,7 +11872,7 @@
       <c r="R34" s="158"/>
       <c r="S34" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>28323</v>
+        <v>26700</v>
       </c>
       <c r="T34" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11778,7 +11883,7 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="153">
         <f t="shared" si="0"/>
-        <v>-119304</v>
+        <v>-120927</v>
       </c>
       <c r="Z34" s="167">
         <f t="shared" si="1"/>
@@ -11936,7 +12041,7 @@
       <c r="R36" s="158"/>
       <c r="S36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-61800</v>
+        <v>-443600</v>
       </c>
       <c r="T36" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11947,7 +12052,7 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="153">
         <f t="shared" si="0"/>
-        <v>2840826</v>
+        <v>2459026</v>
       </c>
       <c r="Z36" s="167">
         <f t="shared" si="1"/>
@@ -12015,7 +12120,7 @@
       <c r="R37" s="158"/>
       <c r="S37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-109</v>
+        <v>10791</v>
       </c>
       <c r="T37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12026,7 +12131,7 @@
       <c r="W37" s="149"/>
       <c r="Y37" s="153">
         <f t="shared" ref="Y37" si="22">M37+P37+S37+V37</f>
-        <v>-43775</v>
+        <v>-32875</v>
       </c>
       <c r="Z37" s="167">
         <f t="shared" ref="Z37" si="23">(N37+Q37+T37+W37)</f>
@@ -12177,7 +12282,7 @@
       <c r="R39" s="158"/>
       <c r="S39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>412715</v>
+        <v>468515</v>
       </c>
       <c r="T39" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12189,7 +12294,7 @@
       <c r="X39" s="131"/>
       <c r="Y39" s="153">
         <f t="shared" ref="Y39:Y74" si="24">M39+P39+S39+V39</f>
-        <v>5693462</v>
+        <v>5749262</v>
       </c>
       <c r="Z39" s="167">
         <f t="shared" ref="Z39:Z74" si="25">(N39+Q39+T39+W39)</f>
@@ -12693,7 +12798,7 @@
       <c r="R45" s="158"/>
       <c r="S45" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>401130</v>
+        <v>556830</v>
       </c>
       <c r="T45" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12704,7 +12809,7 @@
       <c r="W45" s="72"/>
       <c r="Y45" s="153">
         <f t="shared" si="24"/>
-        <v>1502008</v>
+        <v>1657708</v>
       </c>
       <c r="Z45" s="167">
         <f t="shared" si="25"/>
@@ -12774,7 +12879,7 @@
       <c r="R46" s="158"/>
       <c r="S46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-108150</v>
+        <v>-64150</v>
       </c>
       <c r="T46" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12786,7 +12891,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="153">
         <f t="shared" si="24"/>
-        <v>664721</v>
+        <v>708721</v>
       </c>
       <c r="Z46" s="167">
         <f t="shared" si="25"/>
@@ -12852,12 +12957,12 @@
       </c>
       <c r="Q47" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q2'!$A$4:$ABW$124,MATCH('FY-(26-27)Q1'!$P$2:$Q$2,'FY-(26-27)Q2'!$A$2:$BX$2,0),0),0)</f>
-        <v>-3.9188999999999998</v>
+        <v>-1.9594499999999999</v>
       </c>
       <c r="R47" s="158"/>
       <c r="S47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>3799</v>
+        <v>37899</v>
       </c>
       <c r="T47" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12868,11 +12973,11 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="153">
         <f t="shared" si="24"/>
-        <v>-75251</v>
+        <v>-41151</v>
       </c>
       <c r="Z47" s="167">
         <f t="shared" si="25"/>
-        <v>-1.581</v>
+        <v>0.37844999999999995</v>
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
@@ -13026,7 +13131,7 @@
       <c r="R49" s="158"/>
       <c r="S49" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>81468</v>
+        <v>115168</v>
       </c>
       <c r="T49" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13037,7 +13142,7 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="153">
         <f t="shared" si="24"/>
-        <v>149733</v>
+        <v>183433</v>
       </c>
       <c r="Z49" s="167">
         <f t="shared" si="25"/>
@@ -13281,7 +13386,7 @@
       <c r="R52" s="158"/>
       <c r="S52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-147529</v>
+        <v>2071</v>
       </c>
       <c r="T52" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13292,7 +13397,7 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="153">
         <f t="shared" si="24"/>
-        <v>47532</v>
+        <v>197132</v>
       </c>
       <c r="Z52" s="167">
         <f t="shared" si="25"/>
@@ -13362,7 +13467,7 @@
       <c r="R53" s="158"/>
       <c r="S53" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>9674</v>
+        <v>-97726</v>
       </c>
       <c r="T53" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13373,7 +13478,7 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="153">
         <f t="shared" si="24"/>
-        <v>669923</v>
+        <v>562523</v>
       </c>
       <c r="Z53" s="167">
         <f t="shared" si="25"/>
@@ -13524,7 +13629,7 @@
       <c r="R55" s="158"/>
       <c r="S55" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-8895</v>
+        <v>14505</v>
       </c>
       <c r="T55" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13536,7 +13641,7 @@
       <c r="X55" s="131"/>
       <c r="Y55" s="153">
         <f t="shared" si="24"/>
-        <v>-282920</v>
+        <v>-259520</v>
       </c>
       <c r="Z55" s="167">
         <f t="shared" si="25"/>
@@ -13607,7 +13712,7 @@
       <c r="R56" s="158"/>
       <c r="S56" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>183624</v>
+        <v>175078</v>
       </c>
       <c r="T56" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13618,7 +13723,7 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="153">
         <f t="shared" si="24"/>
-        <v>-4470711</v>
+        <v>-4479257</v>
       </c>
       <c r="Z56" s="167">
         <f t="shared" si="25"/>
@@ -13861,7 +13966,7 @@
       <c r="R59" s="158"/>
       <c r="S59" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>3300</v>
+        <v>30200</v>
       </c>
       <c r="T59" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13873,7 +13978,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="153">
         <f t="shared" si="24"/>
-        <v>35991</v>
+        <v>62891</v>
       </c>
       <c r="Z59" s="167">
         <f t="shared" si="25"/>
@@ -13950,7 +14055,7 @@
       <c r="R60" s="158"/>
       <c r="S60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-171229</v>
+        <v>-655229</v>
       </c>
       <c r="T60" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13961,7 +14066,7 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="153">
         <f t="shared" si="24"/>
-        <v>3508386</v>
+        <v>3024386</v>
       </c>
       <c r="Z60" s="167">
         <f t="shared" si="25"/>
@@ -14036,7 +14141,7 @@
       <c r="R61" s="158"/>
       <c r="S61" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-17235</v>
+        <v>765</v>
       </c>
       <c r="T61" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14047,7 +14152,7 @@
       <c r="W61" s="149"/>
       <c r="Y61" s="153">
         <f t="shared" ref="Y61" si="39">M61+P61+S61+V61</f>
-        <v>-3944</v>
+        <v>14056</v>
       </c>
       <c r="Z61" s="167">
         <f t="shared" ref="Z61" si="40">(N61+Q61+T61+W61)</f>
@@ -14117,7 +14222,7 @@
       <c r="R62" s="158"/>
       <c r="S62" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>33128</v>
+        <v>323128</v>
       </c>
       <c r="T62" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14128,7 +14233,7 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="153">
         <f t="shared" si="24"/>
-        <v>876229</v>
+        <v>1166229</v>
       </c>
       <c r="Z62" s="167">
         <f t="shared" si="25"/>
@@ -14205,7 +14310,7 @@
       <c r="R63" s="158"/>
       <c r="S63" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>2920</v>
+        <v>55020</v>
       </c>
       <c r="T63" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14216,7 +14321,7 @@
       <c r="W63" s="72"/>
       <c r="Y63" s="153">
         <f t="shared" si="24"/>
-        <v>967793</v>
+        <v>1019893</v>
       </c>
       <c r="Z63" s="167">
         <f t="shared" si="25"/>
@@ -14530,7 +14635,7 @@
       <c r="R67" s="158"/>
       <c r="S67" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>206750</v>
+        <v>-254750</v>
       </c>
       <c r="T67" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14541,7 +14646,7 @@
       <c r="W67" s="149"/>
       <c r="Y67" s="153">
         <f t="shared" ref="Y67" si="45">M67+P67+S67+V67</f>
-        <v>-756079</v>
+        <v>-1217579</v>
       </c>
       <c r="Z67" s="167">
         <f t="shared" ref="Z67" si="46">(N67+Q67+T67+W67)</f>
@@ -14668,7 +14773,7 @@
       <c r="R69" s="158"/>
       <c r="S69" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>65485</v>
+        <v>40285</v>
       </c>
       <c r="T69" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14679,7 +14784,7 @@
       <c r="W69" s="149"/>
       <c r="Y69" s="153">
         <f t="shared" si="24"/>
-        <v>-4400</v>
+        <v>-29600</v>
       </c>
       <c r="Z69" s="167">
         <f t="shared" si="25"/>
@@ -14749,7 +14854,7 @@
       <c r="R70" s="158"/>
       <c r="S70" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>306496</v>
+        <v>359896</v>
       </c>
       <c r="T70" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14760,7 +14865,7 @@
       <c r="W70" s="149"/>
       <c r="Y70" s="153">
         <f t="shared" si="24"/>
-        <v>-54335</v>
+        <v>-935</v>
       </c>
       <c r="Z70" s="167">
         <f t="shared" si="25"/>
@@ -14992,7 +15097,7 @@
       <c r="R73" s="158"/>
       <c r="S73" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>56120</v>
+        <v>152220</v>
       </c>
       <c r="T73" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -15003,7 +15108,7 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="153">
         <f t="shared" si="24"/>
-        <v>428424</v>
+        <v>524524</v>
       </c>
       <c r="Z73" s="167">
         <f t="shared" si="25"/>
@@ -15231,7 +15336,7 @@
       <c r="R76" s="158"/>
       <c r="S76" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>100956</v>
+        <v>127856</v>
       </c>
       <c r="T76" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -15242,7 +15347,7 @@
       <c r="W76" s="149"/>
       <c r="Y76" s="153">
         <f t="shared" si="55"/>
-        <v>591809</v>
+        <v>618709</v>
       </c>
       <c r="Z76" s="167">
         <f t="shared" si="56"/>
@@ -15285,7 +15390,7 @@
       <c r="R77" s="122"/>
       <c r="S77" s="109">
         <f>SUM(S4:S74)</f>
-        <v>1213020</v>
+        <v>1105623</v>
       </c>
       <c r="T77" s="122"/>
       <c r="U77" s="122"/>
@@ -15293,7 +15398,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="153">
         <f>SUM(Y4:Y76)</f>
-        <v>24695192</v>
+        <v>24614695</v>
       </c>
       <c r="Z77" s="160"/>
     </row>
@@ -17076,11 +17181,11 @@
       </c>
       <c r="G4" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>44320</v>
+        <v>86620</v>
       </c>
       <c r="H4" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.88639999999999997</v>
+        <v>1.7323999999999999</v>
       </c>
       <c r="I4" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17100,11 +17205,11 @@
       </c>
       <c r="M4" s="71">
         <f t="shared" ref="M4:N58" si="0">G4+I4+K4</f>
-        <v>44320</v>
+        <v>86620</v>
       </c>
       <c r="N4" s="165">
         <f t="shared" si="0"/>
-        <v>0.88639999999999997</v>
+        <v>1.7323999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -17128,11 +17233,11 @@
       </c>
       <c r="G5" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>94140</v>
+        <v>190895</v>
       </c>
       <c r="H5" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.31380000000000002</v>
+        <v>0.63631666666666664</v>
       </c>
       <c r="I5" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17152,11 +17257,11 @@
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>94140</v>
+        <v>190895</v>
       </c>
       <c r="N5" s="165">
         <f t="shared" si="0"/>
-        <v>0.31380000000000002</v>
+        <v>0.63631666666666664</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -17180,11 +17285,11 @@
       </c>
       <c r="G6" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>27367</v>
+        <v>71537</v>
       </c>
       <c r="H6" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.27367000000000002</v>
+        <v>0.71536999999999995</v>
       </c>
       <c r="I6" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17204,11 +17309,11 @@
       </c>
       <c r="M6" s="71">
         <f t="shared" si="0"/>
-        <v>27367</v>
+        <v>71537</v>
       </c>
       <c r="N6" s="165">
         <f t="shared" si="0"/>
-        <v>0.27367000000000002</v>
+        <v>0.71536999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -17232,11 +17337,11 @@
       </c>
       <c r="G7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-207210</v>
+        <v>-324610</v>
       </c>
       <c r="H7" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.69069999999999998</v>
+        <v>-1.0820333333333332</v>
       </c>
       <c r="I7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17256,11 +17361,11 @@
       </c>
       <c r="M7" s="71">
         <f t="shared" si="0"/>
-        <v>-207210</v>
+        <v>-324610</v>
       </c>
       <c r="N7" s="165">
         <f t="shared" si="0"/>
-        <v>-0.69069999999999998</v>
+        <v>-1.0820333333333332</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -17284,11 +17389,11 @@
       </c>
       <c r="G8" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>108340</v>
+        <v>119340</v>
       </c>
       <c r="H8" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.72226666666666672</v>
+        <v>0.79559999999999997</v>
       </c>
       <c r="I8" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17308,11 +17413,11 @@
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>108340</v>
+        <v>119340</v>
       </c>
       <c r="N8" s="165">
         <f t="shared" si="0"/>
-        <v>0.72226666666666672</v>
+        <v>0.79559999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -17336,11 +17441,11 @@
       </c>
       <c r="G9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>42214</v>
+        <v>67214</v>
       </c>
       <c r="H9" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.70356666666666667</v>
+        <v>1.1202333333333334</v>
       </c>
       <c r="I9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17360,11 +17465,11 @@
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>42214</v>
+        <v>67214</v>
       </c>
       <c r="N9" s="165">
         <f t="shared" si="0"/>
-        <v>0.70356666666666667</v>
+        <v>1.1202333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -17440,11 +17545,11 @@
       </c>
       <c r="G11" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>170431</v>
+        <v>226131</v>
       </c>
       <c r="H11" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.2840516666666667</v>
+        <v>0.37688500000000003</v>
       </c>
       <c r="I11" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17464,11 +17569,11 @@
       </c>
       <c r="M11" s="71">
         <f t="shared" si="0"/>
-        <v>170431</v>
+        <v>226131</v>
       </c>
       <c r="N11" s="165">
         <f t="shared" si="0"/>
-        <v>0.2840516666666667</v>
+        <v>0.37688500000000003</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -17492,11 +17597,11 @@
       </c>
       <c r="G12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-1938</v>
+        <v>-4891</v>
       </c>
       <c r="H12" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-1.9380000000000001E-2</v>
+        <v>-4.8910000000000002E-2</v>
       </c>
       <c r="I12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17516,11 +17621,11 @@
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>-1938</v>
+        <v>-4891</v>
       </c>
       <c r="N12" s="165">
         <f t="shared" si="0"/>
-        <v>-1.9380000000000001E-2</v>
+        <v>-4.8910000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -17544,11 +17649,11 @@
       </c>
       <c r="G13" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>68353</v>
+        <v>91053</v>
       </c>
       <c r="H13" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.27341199999999999</v>
+        <v>0.36421199999999998</v>
       </c>
       <c r="I13" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17568,11 +17673,11 @@
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>68353</v>
+        <v>91053</v>
       </c>
       <c r="N13" s="165">
         <f t="shared" si="0"/>
-        <v>0.27341199999999999</v>
+        <v>0.36421199999999998</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -17648,11 +17753,11 @@
       </c>
       <c r="G15" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>14282</v>
+        <v>-15918</v>
       </c>
       <c r="H15" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.14282</v>
+        <v>-0.15917999999999999</v>
       </c>
       <c r="I15" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17672,11 +17777,11 @@
       </c>
       <c r="M15" s="71">
         <f t="shared" si="0"/>
-        <v>14282</v>
+        <v>-15918</v>
       </c>
       <c r="N15" s="165">
         <f t="shared" si="0"/>
-        <v>0.14282</v>
+        <v>-0.15917999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -17700,11 +17805,11 @@
       </c>
       <c r="G16" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>77903</v>
+        <v>108803</v>
       </c>
       <c r="H16" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.35410454545454545</v>
+        <v>0.49455909090909089</v>
       </c>
       <c r="I16" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17724,11 +17829,11 @@
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>77903</v>
+        <v>108803</v>
       </c>
       <c r="N16" s="165">
         <f t="shared" si="0"/>
-        <v>0.35410454545454545</v>
+        <v>0.49455909090909089</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -17908,11 +18013,11 @@
       </c>
       <c r="G20" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-68242</v>
+        <v>-85642</v>
       </c>
       <c r="H20" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-2.7296800000000001</v>
+        <v>-3.4256799999999998</v>
       </c>
       <c r="I20" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17932,11 +18037,11 @@
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>-68242</v>
+        <v>-85642</v>
       </c>
       <c r="N20" s="165">
         <f t="shared" si="0"/>
-        <v>-2.7296800000000001</v>
+        <v>-3.4256799999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -18012,11 +18117,11 @@
       </c>
       <c r="G22" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-50285</v>
+        <v>90715</v>
       </c>
       <c r="H22" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.33523333333333333</v>
+        <v>0.60476666666666656</v>
       </c>
       <c r="I22" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18036,11 +18141,11 @@
       </c>
       <c r="M22" s="71">
         <f t="shared" si="0"/>
-        <v>-50285</v>
+        <v>90715</v>
       </c>
       <c r="N22" s="165">
         <f t="shared" si="0"/>
-        <v>-0.33523333333333333</v>
+        <v>0.60476666666666656</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -18116,11 +18221,11 @@
       </c>
       <c r="G24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>28323</v>
+        <v>26700</v>
       </c>
       <c r="H24" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.25748181818181815</v>
+        <v>0.24272727272727271</v>
       </c>
       <c r="I24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18140,11 +18245,11 @@
       </c>
       <c r="M24" s="71">
         <f t="shared" si="0"/>
-        <v>28323</v>
+        <v>26700</v>
       </c>
       <c r="N24" s="165">
         <f t="shared" si="0"/>
-        <v>0.25748181818181815</v>
+        <v>0.24272727272727271</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -18168,11 +18273,11 @@
       </c>
       <c r="G25" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-61800</v>
+        <v>-443600</v>
       </c>
       <c r="H25" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.26869565217391306</v>
+        <v>-1.9286956521739134</v>
       </c>
       <c r="I25" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18192,11 +18297,11 @@
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>-61800</v>
+        <v>-443600</v>
       </c>
       <c r="N25" s="165">
         <f t="shared" si="0"/>
-        <v>-0.26869565217391306</v>
+        <v>-1.9286956521739134</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -18218,11 +18323,11 @@
       </c>
       <c r="G26" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-109</v>
+        <v>10791</v>
       </c>
       <c r="H26" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-5.45E-3</v>
+        <v>0.53954999999999997</v>
       </c>
       <c r="I26" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18242,11 +18347,11 @@
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>-109</v>
+        <v>10791</v>
       </c>
       <c r="N26" s="165">
         <f t="shared" si="0"/>
-        <v>-5.45E-3</v>
+        <v>0.53954999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -18322,11 +18427,11 @@
       </c>
       <c r="G28" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>412715</v>
+        <v>468515</v>
       </c>
       <c r="H28" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.412715</v>
+        <v>0.46851500000000001</v>
       </c>
       <c r="I28" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18346,11 +18451,11 @@
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>412715</v>
+        <v>468515</v>
       </c>
       <c r="N28" s="165">
         <f t="shared" si="0"/>
-        <v>0.412715</v>
+        <v>0.46851500000000001</v>
       </c>
       <c r="O28" s="130"/>
     </row>
@@ -18635,11 +18740,11 @@
       </c>
       <c r="G34" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>401130</v>
+        <v>556830</v>
       </c>
       <c r="H34" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.80225999999999997</v>
+        <v>1.1136600000000001</v>
       </c>
       <c r="I34" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18659,11 +18764,11 @@
       </c>
       <c r="M34" s="71">
         <f t="shared" si="0"/>
-        <v>401130</v>
+        <v>556830</v>
       </c>
       <c r="N34" s="165">
         <f t="shared" si="0"/>
-        <v>0.80225999999999997</v>
+        <v>1.1136600000000001</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -18687,11 +18792,11 @@
       </c>
       <c r="G35" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-108150</v>
+        <v>-64150</v>
       </c>
       <c r="H35" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.21629999999999999</v>
+        <v>-0.1283</v>
       </c>
       <c r="I35" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18711,11 +18816,11 @@
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>-108150</v>
+        <v>-64150</v>
       </c>
       <c r="N35" s="165">
         <f t="shared" si="0"/>
-        <v>-0.21629999999999999</v>
+        <v>-0.1283</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -18739,11 +18844,11 @@
       </c>
       <c r="G36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>3799</v>
+        <v>37899</v>
       </c>
       <c r="H36" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>7.5980000000000006E-2</v>
+        <v>0.75797999999999999</v>
       </c>
       <c r="I36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18763,11 +18868,11 @@
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>3799</v>
+        <v>37899</v>
       </c>
       <c r="N36" s="165">
         <f t="shared" si="0"/>
-        <v>7.5980000000000006E-2</v>
+        <v>0.75797999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -18791,11 +18896,11 @@
       </c>
       <c r="G37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>81468</v>
+        <v>115168</v>
       </c>
       <c r="H37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>2.0367000000000002</v>
+        <v>2.8792</v>
       </c>
       <c r="I37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18815,11 +18920,11 @@
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>81468</v>
+        <v>115168</v>
       </c>
       <c r="N37" s="165">
         <f t="shared" si="0"/>
-        <v>2.0367000000000002</v>
+        <v>2.8792</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -18843,11 +18948,11 @@
       </c>
       <c r="G38" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-147529</v>
+        <v>2071</v>
       </c>
       <c r="H38" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.3688225</v>
+        <v>5.1774999999999998E-3</v>
       </c>
       <c r="I38" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18867,11 +18972,11 @@
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>-147529</v>
+        <v>2071</v>
       </c>
       <c r="N38" s="165">
         <f t="shared" si="0"/>
-        <v>-0.3688225</v>
+        <v>5.1774999999999998E-3</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -18895,11 +19000,11 @@
       </c>
       <c r="G39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>9674</v>
+        <v>-97726</v>
       </c>
       <c r="H39" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>9.6740000000000007E-2</v>
+        <v>-0.97726000000000002</v>
       </c>
       <c r="I39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18919,11 +19024,11 @@
       </c>
       <c r="M39" s="71">
         <f t="shared" si="0"/>
-        <v>9674</v>
+        <v>-97726</v>
       </c>
       <c r="N39" s="165">
         <f t="shared" si="0"/>
-        <v>9.6740000000000007E-2</v>
+        <v>-0.97726000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -18997,11 +19102,11 @@
       </c>
       <c r="G41" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-8895</v>
+        <v>14505</v>
       </c>
       <c r="H41" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.1779</v>
+        <v>0.29010000000000002</v>
       </c>
       <c r="I41" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19021,11 +19126,11 @@
       </c>
       <c r="M41" s="71">
         <f t="shared" si="0"/>
-        <v>-8895</v>
+        <v>14505</v>
       </c>
       <c r="N41" s="165">
         <f t="shared" si="0"/>
-        <v>-0.1779</v>
+        <v>0.29010000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -19049,11 +19154,11 @@
       </c>
       <c r="G42" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>183624</v>
+        <v>175078</v>
       </c>
       <c r="H42" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.61207999999999996</v>
+        <v>0.58359333333333341</v>
       </c>
       <c r="I42" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19073,11 +19178,11 @@
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>183624</v>
+        <v>175078</v>
       </c>
       <c r="N42" s="165">
         <f t="shared" si="0"/>
-        <v>0.61207999999999996</v>
+        <v>0.58359333333333341</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -19151,11 +19256,11 @@
       </c>
       <c r="G44" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>6368</v>
+        <v>65368</v>
       </c>
       <c r="H44" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.63680000000000003</v>
+        <v>6.5368000000000004</v>
       </c>
       <c r="I44" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19175,11 +19280,11 @@
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>6368</v>
+        <v>65368</v>
       </c>
       <c r="N44" s="165">
         <f t="shared" si="0"/>
-        <v>0.63680000000000003</v>
+        <v>6.5368000000000004</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -19203,11 +19308,11 @@
       </c>
       <c r="G45" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>3300</v>
+        <v>30200</v>
       </c>
       <c r="H45" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>6.6000000000000003E-2</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="I45" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19227,11 +19332,11 @@
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>3300</v>
+        <v>30200</v>
       </c>
       <c r="N45" s="165">
         <f t="shared" si="0"/>
-        <v>6.6000000000000003E-2</v>
+        <v>0.60399999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -19255,11 +19360,11 @@
       </c>
       <c r="G46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-171229</v>
+        <v>-655229</v>
       </c>
       <c r="H46" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-1.7122900000000001</v>
+        <v>-6.5522900000000002</v>
       </c>
       <c r="I46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19279,11 +19384,11 @@
       </c>
       <c r="M46" s="71">
         <f t="shared" si="0"/>
-        <v>-171229</v>
+        <v>-655229</v>
       </c>
       <c r="N46" s="165">
         <f t="shared" si="0"/>
-        <v>-1.7122900000000001</v>
+        <v>-6.5522900000000002</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -19305,11 +19410,11 @@
       </c>
       <c r="G47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-17235</v>
+        <v>765</v>
       </c>
       <c r="H47" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-1.7235</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="I47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19329,11 +19434,11 @@
       </c>
       <c r="M47" s="71">
         <f t="shared" si="0"/>
-        <v>-17235</v>
+        <v>765</v>
       </c>
       <c r="N47" s="165">
         <f t="shared" si="0"/>
-        <v>-1.7235</v>
+        <v>7.6499999999999999E-2</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -19357,11 +19462,11 @@
       </c>
       <c r="G48" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>33128</v>
+        <v>323128</v>
       </c>
       <c r="H48" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.11042666666666665</v>
+        <v>1.0770933333333332</v>
       </c>
       <c r="I48" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19381,11 +19486,11 @@
       </c>
       <c r="M48" s="71">
         <f t="shared" si="0"/>
-        <v>33128</v>
+        <v>323128</v>
       </c>
       <c r="N48" s="165">
         <f t="shared" si="0"/>
-        <v>0.11042666666666665</v>
+        <v>1.0770933333333332</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -19455,11 +19560,11 @@
       </c>
       <c r="G50" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>2920</v>
+        <v>55020</v>
       </c>
       <c r="H50" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>7.3000000000000001E-3</v>
+        <v>0.13755000000000001</v>
       </c>
       <c r="I50" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19479,11 +19584,11 @@
       </c>
       <c r="M50" s="71">
         <f t="shared" si="0"/>
-        <v>2920</v>
+        <v>55020</v>
       </c>
       <c r="N50" s="165">
         <f t="shared" si="0"/>
-        <v>7.3000000000000001E-3</v>
+        <v>0.13755000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -19557,11 +19662,11 @@
       </c>
       <c r="G52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>206750</v>
+        <v>-254750</v>
       </c>
       <c r="H52" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.20674999999999999</v>
+        <v>-0.25474999999999998</v>
       </c>
       <c r="I52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19581,11 +19686,11 @@
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>206750</v>
+        <v>-254750</v>
       </c>
       <c r="N52" s="165">
         <f t="shared" si="0"/>
-        <v>0.20674999999999999</v>
+        <v>-0.25474999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -19655,11 +19760,11 @@
       </c>
       <c r="G54" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>65485</v>
+        <v>40285</v>
       </c>
       <c r="H54" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>1.3097000000000001</v>
+        <v>0.80569999999999997</v>
       </c>
       <c r="I54" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19679,11 +19784,11 @@
       </c>
       <c r="M54" s="71">
         <f t="shared" si="0"/>
-        <v>65485</v>
+        <v>40285</v>
       </c>
       <c r="N54" s="165">
         <f t="shared" si="0"/>
-        <v>1.3097000000000001</v>
+        <v>0.80569999999999997</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -19707,11 +19812,11 @@
       </c>
       <c r="G55" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>306496</v>
+        <v>359896</v>
       </c>
       <c r="H55" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.4715323076923077</v>
+        <v>0.55368615384615383</v>
       </c>
       <c r="I55" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19731,11 +19836,11 @@
       </c>
       <c r="M55" s="71">
         <f t="shared" si="0"/>
-        <v>306496</v>
+        <v>359896</v>
       </c>
       <c r="N55" s="165">
         <f t="shared" si="0"/>
-        <v>0.4715323076923077</v>
+        <v>0.55368615384615383</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -19811,11 +19916,11 @@
       </c>
       <c r="G57" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>56120</v>
+        <v>152220</v>
       </c>
       <c r="H57" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.18706666666666669</v>
+        <v>0.50739999999999996</v>
       </c>
       <c r="I57" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19835,11 +19940,11 @@
       </c>
       <c r="M57" s="71">
         <f t="shared" si="0"/>
-        <v>56120</v>
+        <v>152220</v>
       </c>
       <c r="N57" s="165">
         <f t="shared" si="0"/>
-        <v>0.18706666666666669</v>
+        <v>0.50739999999999996</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -19967,11 +20072,11 @@
       </c>
       <c r="G60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>100956</v>
+        <v>127856</v>
       </c>
       <c r="H60" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.20191200000000001</v>
+        <v>0.25571199999999999</v>
       </c>
       <c r="I60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19991,11 +20096,11 @@
       </c>
       <c r="M60" s="71">
         <f t="shared" si="1"/>
-        <v>100956</v>
+        <v>127856</v>
       </c>
       <c r="N60" s="165">
         <f t="shared" si="1"/>
-        <v>0.20191200000000001</v>
+        <v>0.25571199999999999</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -20007,7 +20112,7 @@
       <c r="F61" s="233"/>
       <c r="G61" s="230">
         <f>SUM(G4:G58)</f>
-        <v>1151146</v>
+        <v>1085349</v>
       </c>
       <c r="H61" s="90"/>
       <c r="I61" s="99">
@@ -20022,7 +20127,7 @@
       <c r="L61" s="109"/>
       <c r="M61" s="153">
         <f>SUM(M4:M58)</f>
-        <v>1151146</v>
+        <v>1085349</v>
       </c>
       <c r="N61" s="234"/>
     </row>
@@ -20087,11 +20192,11 @@
       <c r="F65" s="206"/>
       <c r="G65" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>151126</v>
+        <v>300126</v>
       </c>
       <c r="H65" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.50375333333333339</v>
+        <v>1.0004200000000001</v>
       </c>
       <c r="I65" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -20111,11 +20216,11 @@
       </c>
       <c r="M65" s="152">
         <f t="shared" ref="M65:N66" si="2">G65+I65+K65</f>
-        <v>151126</v>
+        <v>300126</v>
       </c>
       <c r="N65" s="166">
         <f t="shared" si="2"/>
-        <v>0.50375333333333339</v>
+        <v>1.0004200000000001</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -20171,7 +20276,7 @@
     <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G67" s="93">
         <f>SUM(G65:G66)</f>
-        <v>249126</v>
+        <v>398126</v>
       </c>
       <c r="H67" s="94"/>
       <c r="I67" s="93">
@@ -20186,7 +20291,7 @@
       <c r="L67" s="113"/>
       <c r="M67" s="93">
         <f>SUM(M65:M66)</f>
-        <v>249126</v>
+        <v>398126</v>
       </c>
       <c r="N67" s="235"/>
     </row>
@@ -23422,7 +23527,7 @@
         <v>256</v>
       </c>
       <c r="F31" s="118">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G31" s="196"/>
       <c r="H31" s="146">
@@ -23494,7 +23599,7 @@
       </c>
       <c r="AD31" s="148">
         <f t="shared" ref="AD31:AD57" si="3">IFERROR(AC31/F31*100,0)/10000000</f>
-        <v>-2.33162</v>
+        <v>-1.16581</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
@@ -29650,7 +29755,7 @@
         <v>256</v>
       </c>
       <c r="F38" s="118">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G38" s="196"/>
       <c r="H38" s="146">
@@ -29722,7 +29827,7 @@
       </c>
       <c r="AD38" s="148">
         <f t="shared" si="1"/>
-        <v>-1.28678</v>
+        <v>-0.64339000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.25">
@@ -36163,7 +36268,7 @@
         <v>256</v>
       </c>
       <c r="F35" s="118">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G35" s="196"/>
       <c r="H35" s="146">
@@ -36241,7 +36346,7 @@
       </c>
       <c r="AF35" s="148">
         <f t="shared" si="1"/>
-        <v>-0.30049999999999999</v>
+        <v>-0.15024999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.25">
@@ -41082,7 +41187,7 @@
       </c>
       <c r="H37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'JULY-2026'!$A$4:$ACS$118,MATCH('FY-(26-27)Q2'!$G$2:$H$2,'JULY-2026'!$A$2:$CT$2,0),0),0)</f>
-        <v>-0.30049999999999999</v>
+        <v>-0.15024999999999999</v>
       </c>
       <c r="I37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -41090,7 +41195,7 @@
       </c>
       <c r="J37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'AUG-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q2'!$I$2:$J$2,'AUG-2026'!$A$2:$DM$2,0),0),0)</f>
-        <v>-1.28678</v>
+        <v>-0.64339000000000002</v>
       </c>
       <c r="K37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$AEE$125,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$EF$2,0),0),0)</f>
@@ -41098,7 +41203,7 @@
       </c>
       <c r="L37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$126,'SEP-2026'!$A$4:$AEE$125,MATCH('FY-(26-27)Q2'!$K$2:$L$2,'SEP-2026'!$A$2:$EF$2,0),0),0)</f>
-        <v>-2.33162</v>
+        <v>-1.16581</v>
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
@@ -41106,7 +41211,7 @@
       </c>
       <c r="N37" s="165">
         <f t="shared" si="0"/>
-        <v>-3.9188999999999998</v>
+        <v>-1.9594499999999999</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3242" uniqueCount="334">
   <si>
     <t>Sudeep</t>
   </si>
@@ -1023,6 +1023,12 @@
   </si>
   <si>
     <t>P3445</t>
+  </si>
+  <si>
+    <t>P3446</t>
+  </si>
+  <si>
+    <t>Gargi Bharti</t>
   </si>
 </sst>
 </file>
@@ -2360,7 +2366,35 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="561">
+  <dxfs count="565">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6619,7 +6653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z65"/>
+  <dimension ref="A1:AA66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="132" customWidth="1" outlineLevel="1"/>
@@ -6629,19 +6663,20 @@
     <col min="5" max="5" width="9.42578125" style="132" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="132" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="132" customWidth="1"/>
-    <col min="8" max="12" width="13.42578125" style="132" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="132" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" style="132" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="10.7109375" style="132" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="21" width="9.140625" style="132"/>
-    <col min="22" max="22" width="14.140625" style="132" customWidth="1"/>
-    <col min="23" max="23" width="12" style="132" customWidth="1"/>
-    <col min="24" max="24" width="15.85546875" style="132" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="132"/>
+    <col min="8" max="13" width="13.42578125" style="132" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" style="132" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="10.7109375" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="9.140625" style="132" collapsed="1"/>
+    <col min="18" max="22" width="9.140625" style="132"/>
+    <col min="23" max="23" width="14.140625" style="132" customWidth="1"/>
+    <col min="24" max="24" width="12" style="132" customWidth="1"/>
+    <col min="25" max="25" width="15.85546875" style="132" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="132"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="220"/>
       <c r="H2" s="255">
         <v>46296</v>
@@ -6658,15 +6693,18 @@
       <c r="L2" s="255">
         <v>46303</v>
       </c>
-      <c r="M2" s="182"/>
-      <c r="N2" s="183" t="s">
+      <c r="M2" s="255">
+        <v>46304</v>
+      </c>
+      <c r="N2" s="182"/>
+      <c r="O2" s="183" t="s">
         <v>325</v>
       </c>
-      <c r="O2" s="184" t="s">
+      <c r="P2" s="184" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="185" t="s">
         <v>54</v>
       </c>
@@ -6701,17 +6739,20 @@
       <c r="L3" s="178" t="s">
         <v>236</v>
       </c>
-      <c r="M3" s="179"/>
-      <c r="N3" s="188"/>
-      <c r="O3" s="179"/>
-      <c r="V3" s="132" t="s">
+      <c r="M3" s="178" t="s">
+        <v>235</v>
+      </c>
+      <c r="N3" s="179"/>
+      <c r="O3" s="188"/>
+      <c r="P3" s="179"/>
+      <c r="W3" s="132" t="s">
         <v>198</v>
       </c>
-      <c r="W3" s="132">
+      <c r="X3" s="132">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="141" t="s">
         <v>216</v>
       </c>
@@ -6746,23 +6787,26 @@
       <c r="L4" s="157">
         <v>42300</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="170">
-        <f t="shared" ref="N4:N35" si="0">SUM(H4:M4)</f>
+      <c r="M4" s="157">
+        <v>0</v>
+      </c>
+      <c r="N4" s="210"/>
+      <c r="O4" s="170">
+        <f t="shared" ref="O4:O36" si="0">SUM(H4:N4)</f>
         <v>86620</v>
       </c>
-      <c r="O4" s="148">
-        <f t="shared" ref="O4:O35" si="1">IFERROR(N4/F4*100,0)/10000000</f>
+      <c r="P4" s="148">
+        <f t="shared" ref="P4:P36" si="1">IFERROR(O4/F4*100,0)/10000000</f>
         <v>1.7323999999999999</v>
       </c>
-      <c r="V4" s="132" t="s">
+      <c r="W4" s="132" t="s">
         <v>170</v>
       </c>
-      <c r="W4" s="132">
+      <c r="X4" s="132">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="141" t="s">
         <v>30</v>
       </c>
@@ -6797,17 +6841,20 @@
       <c r="L5" s="146">
         <v>96755</v>
       </c>
-      <c r="M5" s="173"/>
-      <c r="N5" s="170">
+      <c r="M5" s="146">
+        <v>117145</v>
+      </c>
+      <c r="N5" s="173"/>
+      <c r="O5" s="170">
         <f t="shared" si="0"/>
-        <v>190895</v>
-      </c>
-      <c r="O5" s="148">
+        <v>308040</v>
+      </c>
+      <c r="P5" s="148">
         <f t="shared" si="1"/>
-        <v>0.63631666666666664</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.0267999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="141" t="s">
         <v>323</v>
       </c>
@@ -6842,17 +6889,20 @@
       <c r="L6" s="146">
         <v>44170</v>
       </c>
-      <c r="M6" s="173"/>
-      <c r="N6" s="170">
+      <c r="M6" s="146">
+        <v>56800</v>
+      </c>
+      <c r="N6" s="173"/>
+      <c r="O6" s="170">
         <f t="shared" si="0"/>
-        <v>71537</v>
-      </c>
-      <c r="O6" s="148">
+        <v>128337</v>
+      </c>
+      <c r="P6" s="148">
         <f t="shared" si="1"/>
-        <v>0.71536999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1.2833699999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="141" t="s">
         <v>134</v>
       </c>
@@ -6887,21 +6937,24 @@
       <c r="L7" s="146">
         <v>-117400</v>
       </c>
-      <c r="M7" s="173"/>
-      <c r="N7" s="170">
+      <c r="M7" s="146">
+        <v>124400</v>
+      </c>
+      <c r="N7" s="173"/>
+      <c r="O7" s="170">
         <f t="shared" si="0"/>
-        <v>-324610</v>
-      </c>
-      <c r="O7" s="148">
+        <v>-200210</v>
+      </c>
+      <c r="P7" s="148">
         <f t="shared" si="1"/>
-        <v>-1.0820333333333332</v>
-      </c>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="133">
-        <v>-14254</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+        <v>-0.66736666666666666</v>
+      </c>
+      <c r="R7" s="5"/>
+      <c r="S7" s="133">
+        <v>20436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="141" t="s">
         <v>217</v>
       </c>
@@ -6936,21 +6989,24 @@
       <c r="L8" s="146">
         <v>11000</v>
       </c>
-      <c r="M8" s="173"/>
-      <c r="N8" s="170">
+      <c r="M8" s="146">
+        <v>31390</v>
+      </c>
+      <c r="N8" s="173"/>
+      <c r="O8" s="170">
         <f t="shared" si="0"/>
-        <v>119340</v>
-      </c>
-      <c r="O8" s="148">
+        <v>150730</v>
+      </c>
+      <c r="P8" s="148">
         <f t="shared" si="1"/>
-        <v>0.79559999999999997</v>
-      </c>
-      <c r="Q8" s="133">
-        <v>468159</v>
-      </c>
-      <c r="R8" s="133"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.0048666666666668</v>
+      </c>
+      <c r="R8" s="133">
+        <v>487305</v>
+      </c>
+      <c r="S8" s="133"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="141" t="s">
         <v>313</v>
       </c>
@@ -6983,24 +7039,27 @@
       <c r="L9" s="146">
         <v>25000</v>
       </c>
-      <c r="M9" s="173"/>
-      <c r="N9" s="170">
+      <c r="M9" s="146">
+        <v>11000</v>
+      </c>
+      <c r="N9" s="173"/>
+      <c r="O9" s="170">
         <f t="shared" si="0"/>
-        <v>67214</v>
-      </c>
-      <c r="O9" s="148">
+        <v>78214</v>
+      </c>
+      <c r="P9" s="148">
         <f t="shared" si="1"/>
-        <v>1.1202333333333334</v>
-      </c>
-      <c r="Q9" s="133">
-        <v>453904</v>
+        <v>1.3035666666666668</v>
       </c>
       <c r="R9" s="133">
-        <f>(Q9+Q8)/10000000*13780</f>
-        <v>1270.6028140000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+        <v>507741</v>
+      </c>
+      <c r="S9" s="133">
+        <f>(R9+R8)/10000000*13780</f>
+        <v>1371.1733879999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>35</v>
       </c>
@@ -7035,19 +7094,22 @@
       <c r="L10" s="146">
         <v>0</v>
       </c>
-      <c r="M10" s="173"/>
-      <c r="N10" s="170">
+      <c r="M10" s="146">
+        <v>4400</v>
+      </c>
+      <c r="N10" s="173"/>
+      <c r="O10" s="170">
         <f t="shared" si="0"/>
-        <v>-156520</v>
-      </c>
-      <c r="O10" s="148">
+        <v>-152120</v>
+      </c>
+      <c r="P10" s="148">
         <f t="shared" si="1"/>
-        <v>-0.10434666666666666</v>
-      </c>
-      <c r="Q10" s="133"/>
+        <v>-0.10141333333333334</v>
+      </c>
       <c r="R10" s="133"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S10" s="133"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="142" t="s">
         <v>137</v>
       </c>
@@ -7082,19 +7144,22 @@
       <c r="L11" s="146">
         <v>55700</v>
       </c>
-      <c r="M11" s="173"/>
-      <c r="N11" s="170">
+      <c r="M11" s="146">
+        <v>0</v>
+      </c>
+      <c r="N11" s="173"/>
+      <c r="O11" s="170">
         <f t="shared" si="0"/>
         <v>226131</v>
       </c>
-      <c r="O11" s="148">
+      <c r="P11" s="148">
         <f t="shared" si="1"/>
         <v>0.37688500000000003</v>
       </c>
-      <c r="Q11" s="133"/>
       <c r="R11" s="133"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S11" s="133"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="142" t="s">
         <v>42</v>
       </c>
@@ -7129,19 +7194,22 @@
       <c r="L12" s="146">
         <v>-2953</v>
       </c>
-      <c r="M12" s="173"/>
-      <c r="N12" s="170">
+      <c r="M12" s="146">
+        <v>3600</v>
+      </c>
+      <c r="N12" s="173"/>
+      <c r="O12" s="170">
         <f t="shared" si="0"/>
-        <v>-4891</v>
-      </c>
-      <c r="O12" s="148">
+        <v>-1291</v>
+      </c>
+      <c r="P12" s="148">
         <f t="shared" si="1"/>
-        <v>-4.8910000000000002E-2</v>
-      </c>
-      <c r="Q12" s="133"/>
+        <v>-1.291E-2</v>
+      </c>
       <c r="R12" s="133"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S12" s="133"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="141" t="s">
         <v>212</v>
       </c>
@@ -7176,19 +7244,22 @@
       <c r="L13" s="146">
         <v>22700</v>
       </c>
-      <c r="M13" s="173"/>
-      <c r="N13" s="170">
+      <c r="M13" s="146">
+        <v>25100</v>
+      </c>
+      <c r="N13" s="173"/>
+      <c r="O13" s="170">
         <f t="shared" si="0"/>
-        <v>91053</v>
-      </c>
-      <c r="O13" s="148">
+        <v>116153</v>
+      </c>
+      <c r="P13" s="148">
         <f t="shared" si="1"/>
-        <v>0.36421199999999998</v>
-      </c>
-      <c r="Q13" s="133"/>
+        <v>0.46461200000000002</v>
+      </c>
       <c r="R13" s="133"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S13" s="133"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="141" t="s">
         <v>51</v>
       </c>
@@ -7223,29 +7294,32 @@
       <c r="L14" s="146">
         <v>30900</v>
       </c>
-      <c r="M14" s="173"/>
-      <c r="N14" s="170">
+      <c r="M14" s="146">
+        <v>22730</v>
+      </c>
+      <c r="N14" s="173"/>
+      <c r="O14" s="170">
         <f t="shared" si="0"/>
-        <v>108803</v>
-      </c>
-      <c r="O14" s="148">
+        <v>131533</v>
+      </c>
+      <c r="P14" s="148">
         <f t="shared" si="1"/>
-        <v>0.49455909090909089</v>
-      </c>
-      <c r="Q14" s="133"/>
-      <c r="R14" s="192">
-        <f>R7-R9</f>
-        <v>-15524.602814</v>
-      </c>
-      <c r="U14" s="132">
+        <v>0.59787727272727265</v>
+      </c>
+      <c r="R14" s="133"/>
+      <c r="S14" s="192">
+        <f>S7-S9</f>
+        <v>19064.826612000001</v>
+      </c>
+      <c r="V14" s="132">
         <v>116185</v>
       </c>
-      <c r="W14" s="132">
-        <f>U14+R14</f>
-        <v>100660.397186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X14" s="132">
+        <f>V14+S14</f>
+        <v>135249.826612</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="141" t="s">
         <v>43</v>
       </c>
@@ -7280,17 +7354,20 @@
       <c r="L15" s="146">
         <v>-30200</v>
       </c>
-      <c r="M15" s="173"/>
-      <c r="N15" s="170">
+      <c r="M15" s="146">
+        <v>20000</v>
+      </c>
+      <c r="N15" s="173"/>
+      <c r="O15" s="170">
         <f t="shared" si="0"/>
-        <v>-15918</v>
-      </c>
-      <c r="O15" s="148">
+        <v>4082</v>
+      </c>
+      <c r="P15" s="148">
         <f t="shared" si="1"/>
-        <v>-0.15917999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+        <v>4.0820000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="141" t="s">
         <v>24</v>
       </c>
@@ -7325,28 +7402,31 @@
       <c r="L16" s="146">
         <v>0</v>
       </c>
-      <c r="M16" s="173"/>
-      <c r="N16" s="170">
+      <c r="M16" s="146">
+        <v>-43080</v>
+      </c>
+      <c r="N16" s="173"/>
+      <c r="O16" s="170">
         <f t="shared" si="0"/>
-        <v>-38551</v>
-      </c>
-      <c r="O16" s="148">
+        <v>-81631</v>
+      </c>
+      <c r="P16" s="148">
         <f t="shared" si="1"/>
-        <v>-0.15420400000000001</v>
-      </c>
-      <c r="W16" s="132">
+        <v>-0.32652399999999998</v>
+      </c>
+      <c r="X16" s="132">
         <v>4000000</v>
       </c>
-      <c r="X16" s="132">
-        <f>W16*7/100</f>
+      <c r="Y16" s="132">
+        <f>X16*7/100</f>
         <v>280000</v>
       </c>
-      <c r="Z16" s="132">
+      <c r="AA16" s="132">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="141" t="s">
         <v>23</v>
       </c>
@@ -7381,21 +7461,24 @@
       <c r="L17" s="146">
         <v>0</v>
       </c>
-      <c r="M17" s="173"/>
-      <c r="N17" s="170">
+      <c r="M17" s="146">
+        <v>34600</v>
+      </c>
+      <c r="N17" s="173"/>
+      <c r="O17" s="170">
         <f t="shared" si="0"/>
-        <v>-34123</v>
-      </c>
-      <c r="O17" s="148">
+        <v>477</v>
+      </c>
+      <c r="P17" s="148">
         <f t="shared" si="1"/>
-        <v>-8.5307499999999994E-2</v>
-      </c>
-      <c r="X17" s="132">
-        <f>X16/12</f>
+        <v>1.1925E-3</v>
+      </c>
+      <c r="Y17" s="132">
+        <f>Y16/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="141" t="s">
         <v>165</v>
       </c>
@@ -7430,17 +7513,20 @@
       <c r="L18" s="146">
         <v>141000</v>
       </c>
-      <c r="M18" s="173"/>
-      <c r="N18" s="170">
+      <c r="M18" s="146">
+        <v>136800</v>
+      </c>
+      <c r="N18" s="173"/>
+      <c r="O18" s="170">
         <f t="shared" si="0"/>
-        <v>90715</v>
-      </c>
-      <c r="O18" s="148">
+        <v>227515</v>
+      </c>
+      <c r="P18" s="148">
         <f t="shared" si="1"/>
-        <v>0.60476666666666656</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+        <v>1.5167666666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="141" t="s">
         <v>110</v>
       </c>
@@ -7475,20 +7561,23 @@
       <c r="L19" s="146">
         <v>0</v>
       </c>
-      <c r="M19" s="173"/>
-      <c r="N19" s="170">
+      <c r="M19" s="146">
+        <v>0</v>
+      </c>
+      <c r="N19" s="173"/>
+      <c r="O19" s="170">
         <f t="shared" si="0"/>
         <v>-150688</v>
       </c>
-      <c r="O19" s="148">
+      <c r="P19" s="148">
         <f t="shared" si="1"/>
         <v>-1.3698909090909093</v>
       </c>
-      <c r="S19" s="132">
+      <c r="T19" s="132">
         <v>-132700</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="141" t="s">
         <v>319</v>
       </c>
@@ -7523,20 +7612,23 @@
       <c r="L20" s="146">
         <v>-17400</v>
       </c>
-      <c r="M20" s="173"/>
-      <c r="N20" s="170">
+      <c r="M20" s="146">
+        <v>-10893</v>
+      </c>
+      <c r="N20" s="173"/>
+      <c r="O20" s="170">
         <f t="shared" si="0"/>
-        <v>-85642</v>
-      </c>
-      <c r="O20" s="148">
+        <v>-96535</v>
+      </c>
+      <c r="P20" s="148">
         <f t="shared" si="1"/>
-        <v>-3.4256799999999998</v>
-      </c>
-      <c r="S20" s="132">
+        <v>-3.8614000000000002</v>
+      </c>
+      <c r="T20" s="132">
         <v>-52140</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="141" t="s">
         <v>316</v>
       </c>
@@ -7571,20 +7663,23 @@
       <c r="L21" s="146">
         <v>0</v>
       </c>
-      <c r="M21" s="173"/>
-      <c r="N21" s="170">
+      <c r="M21" s="146">
+        <v>0</v>
+      </c>
+      <c r="N21" s="173"/>
+      <c r="O21" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O21" s="148">
+      <c r="P21" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S21" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="T21" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="141" t="s">
         <v>317</v>
       </c>
@@ -7619,17 +7714,20 @@
       <c r="L22" s="146">
         <v>0</v>
       </c>
-      <c r="M22" s="173"/>
-      <c r="N22" s="170">
+      <c r="M22" s="146">
+        <v>0</v>
+      </c>
+      <c r="N22" s="173"/>
+      <c r="O22" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O22" s="148">
+      <c r="P22" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="141" t="s">
         <v>32</v>
       </c>
@@ -7664,17 +7762,20 @@
       <c r="L23" s="146">
         <v>-1623</v>
       </c>
-      <c r="M23" s="173"/>
-      <c r="N23" s="170">
+      <c r="M23" s="146">
+        <v>561</v>
+      </c>
+      <c r="N23" s="173"/>
+      <c r="O23" s="170">
         <f t="shared" si="0"/>
-        <v>26700</v>
-      </c>
-      <c r="O23" s="148">
+        <v>27261</v>
+      </c>
+      <c r="P23" s="148">
         <f t="shared" si="1"/>
-        <v>0.24272727272727271</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.2478272727272727</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="141" t="s">
         <v>97</v>
       </c>
@@ -7709,17 +7810,20 @@
       <c r="L24" s="146">
         <v>-381800</v>
       </c>
-      <c r="M24" s="173"/>
-      <c r="N24" s="170">
+      <c r="M24" s="146">
+        <v>239700</v>
+      </c>
+      <c r="N24" s="173"/>
+      <c r="O24" s="170">
         <f t="shared" si="0"/>
-        <v>-443600</v>
-      </c>
-      <c r="O24" s="148">
+        <v>-203900</v>
+      </c>
+      <c r="P24" s="148">
         <f t="shared" si="1"/>
-        <v>-1.9286956521739134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.88652173913043497</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="141" t="s">
         <v>302</v>
       </c>
@@ -7752,17 +7856,20 @@
       <c r="L25" s="146">
         <v>10900</v>
       </c>
-      <c r="M25" s="173"/>
-      <c r="N25" s="170">
+      <c r="M25" s="146">
+        <v>-200</v>
+      </c>
+      <c r="N25" s="173"/>
+      <c r="O25" s="170">
         <f t="shared" si="0"/>
-        <v>10791</v>
-      </c>
-      <c r="O25" s="148">
+        <v>10591</v>
+      </c>
+      <c r="P25" s="148">
         <f t="shared" si="1"/>
-        <v>0.53954999999999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.52954999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="141" t="s">
         <v>29</v>
       </c>
@@ -7797,17 +7904,20 @@
       <c r="L26" s="146">
         <v>0</v>
       </c>
-      <c r="M26" s="173"/>
-      <c r="N26" s="170">
+      <c r="M26" s="146">
+        <v>-25000</v>
+      </c>
+      <c r="N26" s="173"/>
+      <c r="O26" s="170">
         <f t="shared" si="0"/>
-        <v>-115600</v>
-      </c>
-      <c r="O26" s="148">
+        <v>-140600</v>
+      </c>
+      <c r="P26" s="148">
         <f t="shared" si="1"/>
-        <v>-0.23119999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+        <v>-0.28120000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="141" t="s">
         <v>28</v>
       </c>
@@ -7842,673 +7952,714 @@
       <c r="L27" s="146">
         <v>55800</v>
       </c>
-      <c r="M27" s="173"/>
-      <c r="N27" s="170">
+      <c r="M27" s="146">
+        <v>16200</v>
+      </c>
+      <c r="N27" s="173"/>
+      <c r="O27" s="170">
         <f t="shared" si="0"/>
-        <v>468515</v>
-      </c>
-      <c r="O27" s="148">
+        <v>484715</v>
+      </c>
+      <c r="P27" s="148">
         <f t="shared" si="1"/>
-        <v>0.46851500000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+        <v>0.48471500000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="141" t="s">
-        <v>65</v>
+        <v>332</v>
       </c>
       <c r="B28" s="140" t="s">
-        <v>64</v>
+        <v>333</v>
       </c>
       <c r="C28" s="140" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="141" t="s">
-        <v>152</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="D28" s="141"/>
       <c r="E28" s="141" t="s">
         <v>256</v>
       </c>
       <c r="F28" s="155">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="190"/>
+      <c r="H28" s="146"/>
+      <c r="I28" s="146">
+        <v>3624</v>
+      </c>
+      <c r="J28" s="146">
+        <v>14752</v>
+      </c>
+      <c r="K28" s="146">
+        <v>-6445</v>
+      </c>
+      <c r="L28" s="146">
+        <v>7920</v>
+      </c>
+      <c r="M28" s="146">
+        <v>6919</v>
+      </c>
+      <c r="N28" s="173"/>
+      <c r="O28" s="170">
+        <f t="shared" ref="O28" si="2">SUM(H28:N28)</f>
+        <v>26770</v>
+      </c>
+      <c r="P28" s="148">
+        <f t="shared" ref="P28" si="3">IFERROR(O28/F28*100,0)/10000000</f>
+        <v>0.53539999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" s="141" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="140" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="141" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="141" t="s">
+        <v>256</v>
+      </c>
+      <c r="F29" s="155">
         <v>5</v>
       </c>
-      <c r="G28" s="189"/>
-      <c r="H28" s="146">
+      <c r="G29" s="189"/>
+      <c r="H29" s="146">
         <v>90508</v>
       </c>
-      <c r="I28" s="146">
-        <v>0</v>
-      </c>
-      <c r="J28" s="146">
+      <c r="I29" s="146">
+        <v>0</v>
+      </c>
+      <c r="J29" s="146">
         <v>310622</v>
       </c>
-      <c r="K28" s="146">
-        <v>0</v>
-      </c>
-      <c r="L28" s="146">
+      <c r="K29" s="146">
+        <v>0</v>
+      </c>
+      <c r="L29" s="146">
         <v>155700</v>
       </c>
-      <c r="M28" s="173"/>
-      <c r="N28" s="170">
+      <c r="M29" s="146">
+        <v>0</v>
+      </c>
+      <c r="N29" s="173"/>
+      <c r="O29" s="170">
         <f t="shared" si="0"/>
         <v>556830</v>
       </c>
-      <c r="O28" s="148">
+      <c r="P29" s="148">
         <f t="shared" si="1"/>
         <v>1.1136600000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="140" t="s">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="142" t="s">
+      <c r="B30" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="140" t="s">
+      <c r="C30" s="140" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="141" t="s">
+      <c r="D30" s="141" t="s">
         <v>152</v>
-      </c>
-      <c r="E29" s="141" t="s">
-        <v>256</v>
-      </c>
-      <c r="F29" s="118">
-        <v>5</v>
-      </c>
-      <c r="G29" s="196"/>
-      <c r="H29" s="146">
-        <v>115180</v>
-      </c>
-      <c r="I29" s="146">
-        <v>-225930</v>
-      </c>
-      <c r="J29" s="146">
-        <v>0</v>
-      </c>
-      <c r="K29" s="146">
-        <v>2600</v>
-      </c>
-      <c r="L29" s="146">
-        <v>44000</v>
-      </c>
-      <c r="M29" s="173"/>
-      <c r="N29" s="170">
-        <f t="shared" si="0"/>
-        <v>-64150</v>
-      </c>
-      <c r="O29" s="148">
-        <f t="shared" si="1"/>
-        <v>-0.1283</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="140" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="142" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="140" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="141" t="s">
-        <v>262</v>
       </c>
       <c r="E30" s="141" t="s">
         <v>256</v>
       </c>
       <c r="F30" s="118">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="G30" s="196"/>
       <c r="H30" s="146">
-        <v>-51008</v>
+        <v>115180</v>
       </c>
       <c r="I30" s="146">
-        <v>13880</v>
+        <v>-225930</v>
       </c>
       <c r="J30" s="146">
-        <v>48621</v>
+        <v>0</v>
       </c>
       <c r="K30" s="146">
-        <v>-7694</v>
+        <v>2600</v>
       </c>
       <c r="L30" s="146">
-        <v>34100</v>
-      </c>
-      <c r="M30" s="173"/>
-      <c r="N30" s="170">
+        <v>44000</v>
+      </c>
+      <c r="M30" s="146">
+        <v>39485</v>
+      </c>
+      <c r="N30" s="173"/>
+      <c r="O30" s="170">
         <f t="shared" si="0"/>
-        <v>37899</v>
-      </c>
-      <c r="O30" s="148">
+        <v>-24665</v>
+      </c>
+      <c r="P30" s="148">
         <f t="shared" si="1"/>
-        <v>0.75797999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="140" t="s">
-        <v>154</v>
+        <v>-4.9329999999999999E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="140" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="142" t="s">
+        <v>130</v>
       </c>
       <c r="C31" s="140" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D31" s="141" t="s">
-        <v>4</v>
+        <v>262</v>
       </c>
       <c r="E31" s="141" t="s">
         <v>256</v>
       </c>
-      <c r="F31" s="155">
-        <v>0.4</v>
-      </c>
-      <c r="G31" s="190"/>
+      <c r="F31" s="118">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="196"/>
       <c r="H31" s="146">
-        <v>9270</v>
+        <v>-51008</v>
       </c>
       <c r="I31" s="146">
-        <v>28255</v>
+        <v>13880</v>
       </c>
       <c r="J31" s="146">
-        <v>42650</v>
+        <v>48621</v>
       </c>
       <c r="K31" s="146">
-        <v>1293</v>
+        <v>-7694</v>
       </c>
       <c r="L31" s="146">
-        <v>33700</v>
-      </c>
-      <c r="M31" s="173"/>
-      <c r="N31" s="170">
+        <v>34100</v>
+      </c>
+      <c r="M31" s="146">
+        <v>19000</v>
+      </c>
+      <c r="N31" s="173"/>
+      <c r="O31" s="170">
         <f t="shared" si="0"/>
-        <v>115168</v>
-      </c>
-      <c r="O31" s="148">
+        <v>56899</v>
+      </c>
+      <c r="P31" s="148">
         <f t="shared" si="1"/>
-        <v>2.8792</v>
-      </c>
-      <c r="R31" s="133"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="141" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="142" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="141" t="s">
-        <v>222</v>
+        <v>1.13798</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A32" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="140" t="s">
+        <v>154</v>
+      </c>
+      <c r="C32" s="140" t="s">
+        <v>60</v>
       </c>
       <c r="D32" s="141" t="s">
-        <v>263</v>
+        <v>4</v>
       </c>
       <c r="E32" s="141" t="s">
         <v>256</v>
       </c>
       <c r="F32" s="155">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="190"/>
       <c r="H32" s="146">
-        <v>-91628</v>
+        <v>9270</v>
       </c>
       <c r="I32" s="146">
-        <v>-39194</v>
+        <v>28255</v>
       </c>
       <c r="J32" s="146">
-        <v>81490</v>
+        <v>42650</v>
       </c>
       <c r="K32" s="146">
-        <v>-98197</v>
+        <v>1293</v>
       </c>
       <c r="L32" s="146">
-        <v>149600</v>
-      </c>
-      <c r="M32" s="173"/>
-      <c r="N32" s="170">
+        <v>33700</v>
+      </c>
+      <c r="M32" s="146">
+        <v>17495</v>
+      </c>
+      <c r="N32" s="173"/>
+      <c r="O32" s="170">
         <f t="shared" si="0"/>
-        <v>2071</v>
-      </c>
-      <c r="O32" s="148">
+        <v>132663</v>
+      </c>
+      <c r="P32" s="148">
         <f t="shared" si="1"/>
-        <v>5.1774999999999998E-3</v>
-      </c>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="133">
-        <v>18950</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+        <v>3.3165749999999998</v>
+      </c>
+      <c r="S32" s="133"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="141" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="B33" s="142" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="C33" s="141" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>106</v>
+        <v>263</v>
       </c>
       <c r="E33" s="141" t="s">
-        <v>106</v>
+        <v>256</v>
       </c>
       <c r="F33" s="155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G33" s="190"/>
       <c r="H33" s="146">
-        <v>-49178</v>
+        <v>-91628</v>
       </c>
       <c r="I33" s="146">
-        <v>20700</v>
+        <v>-39194</v>
       </c>
       <c r="J33" s="146">
-        <v>51300</v>
+        <v>81490</v>
       </c>
       <c r="K33" s="146">
-        <v>-13148</v>
+        <v>-98197</v>
       </c>
       <c r="L33" s="146">
-        <v>-107400</v>
-      </c>
-      <c r="M33" s="173"/>
-      <c r="N33" s="170">
+        <v>149600</v>
+      </c>
+      <c r="M33" s="146">
+        <v>77460</v>
+      </c>
+      <c r="N33" s="173"/>
+      <c r="O33" s="170">
         <f t="shared" si="0"/>
-        <v>-97726</v>
-      </c>
-      <c r="O33" s="148">
+        <v>79531</v>
+      </c>
+      <c r="P33" s="148">
         <f t="shared" si="1"/>
-        <v>-0.97726000000000002</v>
-      </c>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="133"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0.19882749999999999</v>
+      </c>
+      <c r="R33" s="5"/>
+      <c r="S33" s="133">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="141" t="s">
-        <v>314</v>
+        <v>104</v>
       </c>
       <c r="B34" s="142" t="s">
         <v>105</v>
       </c>
       <c r="C34" s="141" t="s">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="D34" s="141" t="s">
-        <v>256</v>
+        <v>106</v>
       </c>
       <c r="E34" s="141" t="s">
-        <v>256</v>
-      </c>
-      <c r="F34" s="155"/>
+        <v>106</v>
+      </c>
+      <c r="F34" s="155">
+        <v>1</v>
+      </c>
       <c r="G34" s="190"/>
       <c r="H34" s="146">
-        <v>0</v>
+        <v>-49178</v>
       </c>
       <c r="I34" s="146">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="J34" s="146">
-        <v>0</v>
+        <v>51300</v>
       </c>
       <c r="K34" s="146">
-        <v>0</v>
+        <v>-13148</v>
       </c>
       <c r="L34" s="146">
-        <v>0</v>
-      </c>
-      <c r="M34" s="173"/>
-      <c r="N34" s="170">
+        <v>-107400</v>
+      </c>
+      <c r="M34" s="146">
+        <v>56914</v>
+      </c>
+      <c r="N34" s="173"/>
+      <c r="O34" s="170">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="148">
+        <v>-40812</v>
+      </c>
+      <c r="P34" s="148">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="133">
-        <v>585803</v>
-      </c>
-      <c r="R34" s="133">
-        <f>(Q35+Q34)/10000000*13780</f>
-        <v>1640.587546</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.40811999999999998</v>
+      </c>
+      <c r="R34" s="5"/>
+      <c r="S34" s="133"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="141" t="s">
-        <v>229</v>
+        <v>314</v>
       </c>
       <c r="B35" s="142" t="s">
         <v>105</v>
       </c>
       <c r="C35" s="141" t="s">
-        <v>218</v>
+        <v>15</v>
       </c>
       <c r="D35" s="141" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E35" s="141" t="s">
         <v>256</v>
       </c>
-      <c r="F35" s="155">
-        <v>0.5</v>
-      </c>
+      <c r="F35" s="155"/>
       <c r="G35" s="190"/>
       <c r="H35" s="146">
+        <v>0</v>
+      </c>
+      <c r="I35" s="146">
+        <v>0</v>
+      </c>
+      <c r="J35" s="146">
+        <v>0</v>
+      </c>
+      <c r="K35" s="146">
+        <v>0</v>
+      </c>
+      <c r="L35" s="146">
+        <v>0</v>
+      </c>
+      <c r="M35" s="146">
+        <v>0</v>
+      </c>
+      <c r="N35" s="173"/>
+      <c r="O35" s="170">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="148">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="133">
+        <v>380481</v>
+      </c>
+      <c r="S35" s="133">
+        <f>(R36+R35)/10000000*13780</f>
+        <v>1046.388434</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="141" t="s">
+        <v>229</v>
+      </c>
+      <c r="B36" s="142" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="141" t="s">
+        <v>218</v>
+      </c>
+      <c r="D36" s="141" t="s">
+        <v>264</v>
+      </c>
+      <c r="E36" s="141" t="s">
+        <v>256</v>
+      </c>
+      <c r="F36" s="155">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="190"/>
+      <c r="H36" s="146">
         <v>3712</v>
       </c>
-      <c r="I35" s="146">
+      <c r="I36" s="146">
         <v>-16258</v>
       </c>
-      <c r="J35" s="146">
+      <c r="J36" s="146">
         <v>19175</v>
       </c>
-      <c r="K35" s="146">
+      <c r="K36" s="146">
         <v>-15524</v>
       </c>
-      <c r="L35" s="146">
+      <c r="L36" s="146">
         <v>23400</v>
       </c>
-      <c r="M35" s="173"/>
-      <c r="N35" s="170">
+      <c r="M36" s="146">
+        <v>0</v>
+      </c>
+      <c r="N36" s="173"/>
+      <c r="O36" s="170">
         <f t="shared" si="0"/>
         <v>14505</v>
       </c>
-      <c r="O35" s="148">
+      <c r="P36" s="148">
         <f t="shared" si="1"/>
         <v>0.29010000000000002</v>
       </c>
-      <c r="Q35" s="133">
-        <v>604754</v>
-      </c>
-      <c r="R35" s="133"/>
-    </row>
-    <row r="36" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="141" t="s">
+      <c r="R36" s="133">
+        <v>378872</v>
+      </c>
+      <c r="S36" s="133"/>
+    </row>
+    <row r="37" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="142" t="s">
+      <c r="B37" s="142" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="141" t="s">
+      <c r="C37" s="141" t="s">
         <v>220</v>
       </c>
-      <c r="D36" s="141" t="s">
+      <c r="D37" s="141" t="s">
         <v>266</v>
       </c>
-      <c r="E36" s="141" t="s">
-        <v>256</v>
-      </c>
-      <c r="F36" s="155">
-        <v>3</v>
-      </c>
-      <c r="G36" s="190"/>
-      <c r="H36" s="146">
-        <v>158900</v>
-      </c>
-      <c r="I36" s="146">
-        <v>-331500</v>
-      </c>
-      <c r="J36" s="146">
-        <v>276700</v>
-      </c>
-      <c r="K36" s="146">
-        <v>79524</v>
-      </c>
-      <c r="L36" s="146">
-        <v>-8546</v>
-      </c>
-      <c r="M36" s="173"/>
-      <c r="N36" s="170">
-        <f t="shared" ref="N36:N67" si="2">SUM(H36:M36)</f>
-        <v>175078</v>
-      </c>
-      <c r="O36" s="148">
-        <f t="shared" ref="O36:O67" si="3">IFERROR(N36/F36*100,0)/10000000</f>
-        <v>0.58359333333333341</v>
-      </c>
-      <c r="Q36" s="133"/>
-      <c r="R36" s="133">
-        <f>+R32-R34</f>
-        <v>17309.412454000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="141" t="s">
-        <v>292</v>
-      </c>
-      <c r="B37" s="142" t="s">
-        <v>291</v>
-      </c>
-      <c r="C37" s="141" t="s">
-        <v>293</v>
-      </c>
-      <c r="D37" s="141"/>
       <c r="E37" s="141" t="s">
         <v>256</v>
       </c>
       <c r="F37" s="155">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="G37" s="190"/>
       <c r="H37" s="146">
-        <v>18070</v>
+        <v>158900</v>
       </c>
       <c r="I37" s="146">
-        <v>15000</v>
+        <v>-331500</v>
       </c>
       <c r="J37" s="146">
-        <v>-7417</v>
+        <v>276700</v>
       </c>
       <c r="K37" s="146">
-        <v>-19285</v>
+        <v>79524</v>
       </c>
       <c r="L37" s="146">
-        <v>59000</v>
-      </c>
-      <c r="M37" s="173"/>
-      <c r="N37" s="170">
-        <f t="shared" si="2"/>
-        <v>65368</v>
-      </c>
-      <c r="O37" s="148">
-        <f t="shared" si="3"/>
-        <v>6.5368000000000004</v>
-      </c>
-      <c r="Q37" s="133"/>
+        <v>-8546</v>
+      </c>
+      <c r="M37" s="146">
+        <v>-110144</v>
+      </c>
+      <c r="N37" s="173"/>
+      <c r="O37" s="170">
+        <f t="shared" ref="O37:O68" si="4">SUM(H37:N37)</f>
+        <v>64934</v>
+      </c>
+      <c r="P37" s="148">
+        <f t="shared" ref="P37:P68" si="5">IFERROR(O37/F37*100,0)/10000000</f>
+        <v>0.2164466666666667</v>
+      </c>
       <c r="R37" s="133"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S37" s="133">
+        <f>+S33-S35</f>
+        <v>561.61156600000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="141" t="s">
-        <v>132</v>
+        <v>292</v>
       </c>
       <c r="B38" s="142" t="s">
-        <v>129</v>
+        <v>291</v>
       </c>
       <c r="C38" s="141" t="s">
-        <v>307</v>
-      </c>
-      <c r="D38" s="141" t="s">
-        <v>267</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="D38" s="141"/>
       <c r="E38" s="141" t="s">
         <v>256</v>
       </c>
       <c r="F38" s="155">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G38" s="190"/>
       <c r="H38" s="146">
-        <v>0</v>
+        <v>18070</v>
       </c>
       <c r="I38" s="146">
-        <v>7600</v>
+        <v>15000</v>
       </c>
       <c r="J38" s="146">
-        <v>12200</v>
+        <v>-7417</v>
       </c>
       <c r="K38" s="146">
-        <v>-16500</v>
+        <v>-19285</v>
       </c>
       <c r="L38" s="146">
-        <v>26900</v>
-      </c>
-      <c r="M38" s="173"/>
-      <c r="N38" s="170">
-        <f t="shared" si="2"/>
-        <v>30200</v>
-      </c>
-      <c r="O38" s="148">
-        <f t="shared" si="3"/>
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="Q38" s="133"/>
+        <v>59000</v>
+      </c>
+      <c r="M38" s="146">
+        <v>19459</v>
+      </c>
+      <c r="N38" s="173"/>
+      <c r="O38" s="170">
+        <f t="shared" si="4"/>
+        <v>84827</v>
+      </c>
+      <c r="P38" s="148">
+        <f t="shared" si="5"/>
+        <v>8.4826999999999995</v>
+      </c>
       <c r="R38" s="133"/>
-    </row>
-    <row r="39" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S38" s="133"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="141" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" s="140" t="s">
-        <v>95</v>
+        <v>132</v>
+      </c>
+      <c r="B39" s="142" t="s">
+        <v>129</v>
       </c>
       <c r="C39" s="141" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D39" s="141" t="s">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="E39" s="141" t="s">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="F39" s="155">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G39" s="190"/>
       <c r="H39" s="146">
-        <v>-219160</v>
+        <v>0</v>
       </c>
       <c r="I39" s="146">
-        <v>-41680</v>
+        <v>7600</v>
       </c>
       <c r="J39" s="146">
-        <v>174856</v>
+        <v>12200</v>
       </c>
       <c r="K39" s="146">
-        <v>-85245</v>
+        <v>-16500</v>
       </c>
       <c r="L39" s="146">
-        <v>-484000</v>
-      </c>
-      <c r="M39" s="173"/>
-      <c r="N39" s="170">
-        <f t="shared" si="2"/>
-        <v>-655229</v>
-      </c>
-      <c r="O39" s="148">
-        <f t="shared" si="3"/>
-        <v>-6.5522900000000002</v>
-      </c>
-      <c r="Q39" s="133"/>
+        <v>26900</v>
+      </c>
+      <c r="M39" s="146">
+        <v>12000</v>
+      </c>
+      <c r="N39" s="173"/>
+      <c r="O39" s="170">
+        <f t="shared" si="4"/>
+        <v>42200</v>
+      </c>
+      <c r="P39" s="148">
+        <f t="shared" si="5"/>
+        <v>0.84399999999999997</v>
+      </c>
       <c r="R39" s="133"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S39" s="133"/>
+    </row>
+    <row r="40" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="141" t="s">
-        <v>301</v>
+        <v>48</v>
       </c>
       <c r="B40" s="140" t="s">
-        <v>295</v>
-      </c>
-      <c r="C40" s="162" t="s">
-        <v>296</v>
-      </c>
-      <c r="D40" s="162"/>
-      <c r="E40" s="162" t="s">
-        <v>256</v>
-      </c>
-      <c r="F40" s="163">
-        <v>0.1</v>
+        <v>95</v>
+      </c>
+      <c r="C40" s="141" t="s">
+        <v>228</v>
+      </c>
+      <c r="D40" s="141" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="141" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="155">
+        <v>1</v>
       </c>
       <c r="G40" s="190"/>
       <c r="H40" s="146">
-        <v>34200</v>
+        <v>-219160</v>
       </c>
       <c r="I40" s="146">
-        <v>-23073</v>
+        <v>-41680</v>
       </c>
       <c r="J40" s="146">
-        <v>-6862</v>
+        <v>174856</v>
       </c>
       <c r="K40" s="146">
-        <v>-21500</v>
+        <v>-85245</v>
       </c>
       <c r="L40" s="146">
-        <v>18000</v>
-      </c>
-      <c r="M40" s="173"/>
-      <c r="N40" s="170">
-        <f t="shared" si="2"/>
-        <v>765</v>
-      </c>
-      <c r="O40" s="148">
-        <f t="shared" si="3"/>
-        <v>7.6499999999999999E-2</v>
-      </c>
-      <c r="Q40" s="133"/>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="142" t="s">
-        <v>168</v>
+        <v>-484000</v>
+      </c>
+      <c r="M40" s="146">
+        <v>-52500</v>
+      </c>
+      <c r="N40" s="173"/>
+      <c r="O40" s="170">
+        <f t="shared" si="4"/>
+        <v>-707729</v>
+      </c>
+      <c r="P40" s="148">
+        <f t="shared" si="5"/>
+        <v>-7.0772899999999996</v>
+      </c>
+      <c r="R40" s="133"/>
+      <c r="S40" s="133"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="141" t="s">
+        <v>301</v>
       </c>
       <c r="B41" s="140" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="D41" s="162" t="s">
-        <v>253</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="C41" s="162" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41" s="162"/>
       <c r="E41" s="162" t="s">
-        <v>253</v>
-      </c>
-      <c r="F41" s="114">
-        <v>4</v>
+        <v>256</v>
+      </c>
+      <c r="F41" s="163">
+        <v>0.1</v>
       </c>
       <c r="G41" s="190"/>
       <c r="H41" s="146">
-        <v>2920</v>
+        <v>34200</v>
       </c>
       <c r="I41" s="146">
-        <v>0</v>
+        <v>-23073</v>
       </c>
       <c r="J41" s="146">
-        <v>0</v>
+        <v>-6862</v>
       </c>
       <c r="K41" s="146">
-        <v>0</v>
+        <v>-21500</v>
       </c>
       <c r="L41" s="146">
-        <v>52100</v>
-      </c>
-      <c r="M41" s="173"/>
-      <c r="N41" s="170">
-        <f t="shared" si="2"/>
-        <v>55020</v>
-      </c>
-      <c r="O41" s="148">
-        <f t="shared" si="3"/>
-        <v>0.13755000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+        <v>18000</v>
+      </c>
+      <c r="M41" s="146">
+        <v>3517</v>
+      </c>
+      <c r="N41" s="173"/>
+      <c r="O41" s="170">
+        <f t="shared" si="4"/>
+        <v>4282</v>
+      </c>
+      <c r="P41" s="148">
+        <f t="shared" si="5"/>
+        <v>0.42820000000000003</v>
+      </c>
+      <c r="R41" s="133"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="142" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B42" s="140" t="s">
         <v>169</v>
@@ -8517,268 +8668,286 @@
         <v>252</v>
       </c>
       <c r="D42" s="162" t="s">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="E42" s="162" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F42" s="114">
         <v>4</v>
       </c>
       <c r="G42" s="190"/>
       <c r="H42" s="146">
-        <v>0</v>
+        <v>2920</v>
       </c>
       <c r="I42" s="146">
+        <v>0</v>
+      </c>
+      <c r="J42" s="146">
+        <v>0</v>
+      </c>
+      <c r="K42" s="146">
+        <v>0</v>
+      </c>
+      <c r="L42" s="146">
+        <v>52100</v>
+      </c>
+      <c r="M42" s="146">
+        <v>0</v>
+      </c>
+      <c r="N42" s="173"/>
+      <c r="O42" s="170">
+        <f t="shared" si="4"/>
+        <v>55020</v>
+      </c>
+      <c r="P42" s="148">
+        <f t="shared" si="5"/>
+        <v>0.13755000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="142" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" s="140" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="162" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" s="162" t="s">
+        <v>256</v>
+      </c>
+      <c r="F43" s="114">
+        <v>4</v>
+      </c>
+      <c r="G43" s="190"/>
+      <c r="H43" s="146">
+        <v>0</v>
+      </c>
+      <c r="I43" s="146">
         <v>-20000</v>
       </c>
-      <c r="J42" s="146">
+      <c r="J43" s="146">
         <v>60600</v>
       </c>
-      <c r="K42" s="146">
-        <v>0</v>
-      </c>
-      <c r="L42" s="146">
-        <v>0</v>
-      </c>
-      <c r="M42" s="173"/>
-      <c r="N42" s="170">
-        <f t="shared" si="2"/>
-        <v>40600</v>
-      </c>
-      <c r="O42" s="148">
-        <f t="shared" si="3"/>
-        <v>0.10150000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="142" t="s">
+      <c r="K43" s="146">
+        <v>0</v>
+      </c>
+      <c r="L43" s="146">
+        <v>0</v>
+      </c>
+      <c r="M43" s="146">
+        <v>-1200</v>
+      </c>
+      <c r="N43" s="173"/>
+      <c r="O43" s="170">
+        <f t="shared" si="4"/>
+        <v>39400</v>
+      </c>
+      <c r="P43" s="148">
+        <f t="shared" si="5"/>
+        <v>9.8500000000000004E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="140" t="s">
+      <c r="B44" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="142" t="s">
+      <c r="C44" s="142" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="140" t="s">
+      <c r="D44" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="140" t="s">
-        <v>256</v>
-      </c>
-      <c r="F43" s="118">
-        <v>3</v>
-      </c>
-      <c r="G43" s="196"/>
-      <c r="H43" s="146">
-        <v>174105</v>
-      </c>
-      <c r="I43" s="146">
-        <v>-313641</v>
-      </c>
-      <c r="J43" s="146">
-        <v>307794</v>
-      </c>
-      <c r="K43" s="146">
-        <v>-135130</v>
-      </c>
-      <c r="L43" s="146">
-        <v>290000</v>
-      </c>
-      <c r="M43" s="173"/>
-      <c r="N43" s="170">
-        <f t="shared" si="2"/>
-        <v>323128</v>
-      </c>
-      <c r="O43" s="148">
-        <f t="shared" si="3"/>
-        <v>1.0770933333333332</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="59" t="s">
-        <v>306</v>
-      </c>
-      <c r="B44" s="62" t="s">
-        <v>304</v>
-      </c>
-      <c r="C44" s="59" t="s">
-        <v>308</v>
-      </c>
-      <c r="D44" s="140"/>
       <c r="E44" s="140" t="s">
         <v>256</v>
       </c>
-      <c r="F44" s="114">
-        <v>10</v>
-      </c>
-      <c r="G44" s="23"/>
-      <c r="H44" s="150">
-        <v>-214000</v>
-      </c>
-      <c r="I44" s="150">
-        <v>19600</v>
-      </c>
-      <c r="J44" s="150">
-        <v>338000</v>
-      </c>
-      <c r="K44" s="150">
-        <v>63150</v>
-      </c>
-      <c r="L44" s="150">
-        <v>-461500</v>
-      </c>
-      <c r="M44" s="173"/>
-      <c r="N44" s="170">
-        <f t="shared" si="2"/>
-        <v>-254750</v>
-      </c>
-      <c r="O44" s="148">
-        <f t="shared" si="3"/>
-        <v>-0.25474999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="F44" s="118">
+        <v>3</v>
+      </c>
+      <c r="G44" s="196"/>
+      <c r="H44" s="146">
+        <v>174105</v>
+      </c>
+      <c r="I44" s="146">
+        <v>-313641</v>
+      </c>
+      <c r="J44" s="146">
+        <v>307794</v>
+      </c>
+      <c r="K44" s="146">
+        <v>-135130</v>
+      </c>
+      <c r="L44" s="146">
+        <v>290000</v>
+      </c>
+      <c r="M44" s="146">
+        <v>102008</v>
+      </c>
+      <c r="N44" s="173"/>
+      <c r="O44" s="170">
+        <f t="shared" si="4"/>
+        <v>425136</v>
+      </c>
+      <c r="P44" s="148">
+        <f t="shared" si="5"/>
+        <v>1.4171199999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="59" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B45" s="62" t="s">
         <v>304</v>
       </c>
       <c r="C45" s="59" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D45" s="140"/>
       <c r="E45" s="140" t="s">
         <v>256</v>
       </c>
-      <c r="F45" s="114"/>
+      <c r="F45" s="114">
+        <v>10</v>
+      </c>
       <c r="G45" s="23"/>
       <c r="H45" s="150">
-        <v>0</v>
+        <v>-214000</v>
       </c>
       <c r="I45" s="150">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="J45" s="150">
-        <v>0</v>
+        <v>338000</v>
       </c>
       <c r="K45" s="150">
-        <v>0</v>
+        <v>63150</v>
       </c>
       <c r="L45" s="150">
-        <v>0</v>
-      </c>
-      <c r="M45" s="173"/>
-      <c r="N45" s="170">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O45" s="148">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-461500</v>
+      </c>
+      <c r="M45" s="150">
+        <v>-70400</v>
+      </c>
+      <c r="N45" s="173"/>
+      <c r="O45" s="170">
+        <f t="shared" si="4"/>
+        <v>-325150</v>
+      </c>
+      <c r="P45" s="148">
+        <f t="shared" si="5"/>
+        <v>-0.32514999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="59" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>195</v>
+        <v>304</v>
       </c>
       <c r="C46" s="59" t="s">
-        <v>196</v>
-      </c>
-      <c r="D46" s="141" t="s">
-        <v>268</v>
-      </c>
-      <c r="E46" s="162" t="s">
+        <v>274</v>
+      </c>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140" t="s">
         <v>256</v>
       </c>
-      <c r="F46" s="114">
-        <v>0.5</v>
-      </c>
+      <c r="F46" s="114"/>
       <c r="G46" s="23"/>
       <c r="H46" s="150">
-        <v>21524</v>
+        <v>0</v>
       </c>
       <c r="I46" s="150">
-        <v>-10951</v>
+        <v>0</v>
       </c>
       <c r="J46" s="150">
-        <v>24836</v>
+        <v>0</v>
       </c>
       <c r="K46" s="150">
-        <v>30076</v>
+        <v>0</v>
       </c>
       <c r="L46" s="150">
-        <v>-25200</v>
-      </c>
-      <c r="M46" s="173"/>
-      <c r="N46" s="170">
-        <f t="shared" si="2"/>
-        <v>40285</v>
-      </c>
-      <c r="O46" s="148">
-        <f t="shared" si="3"/>
-        <v>0.80569999999999997</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="M46" s="150">
+        <v>0</v>
+      </c>
+      <c r="N46" s="173"/>
+      <c r="O46" s="170">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="148">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="59" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B47" s="62" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C47" s="59" t="s">
-        <v>210</v>
-      </c>
-      <c r="D47" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="E47" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" s="141" t="s">
+        <v>268</v>
+      </c>
+      <c r="E47" s="162" t="s">
         <v>256</v>
       </c>
       <c r="F47" s="114">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="G47" s="23"/>
       <c r="H47" s="150">
-        <v>138096</v>
+        <v>21524</v>
       </c>
       <c r="I47" s="150">
-        <v>0</v>
+        <v>-10951</v>
       </c>
       <c r="J47" s="150">
-        <v>168400</v>
+        <v>24836</v>
       </c>
       <c r="K47" s="150">
-        <v>0</v>
+        <v>30076</v>
       </c>
       <c r="L47" s="150">
-        <v>53400</v>
-      </c>
-      <c r="M47" s="173"/>
-      <c r="N47" s="170">
-        <f t="shared" si="2"/>
-        <v>359896</v>
-      </c>
-      <c r="O47" s="148">
-        <f t="shared" si="3"/>
-        <v>0.55368615384615383</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-25200</v>
+      </c>
+      <c r="M47" s="150">
+        <v>0</v>
+      </c>
+      <c r="N47" s="173"/>
+      <c r="O47" s="170">
+        <f t="shared" si="4"/>
+        <v>40285</v>
+      </c>
+      <c r="P47" s="148">
+        <f t="shared" si="5"/>
+        <v>0.80569999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" s="62" t="s">
         <v>209</v>
       </c>
       <c r="C48" s="59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="62" t="s">
         <v>209</v>
@@ -8787,133 +8956,142 @@
         <v>256</v>
       </c>
       <c r="F48" s="114">
-        <v>1.25</v>
+        <v>6.5</v>
       </c>
       <c r="G48" s="23"/>
       <c r="H48" s="150">
-        <v>0</v>
+        <v>138096</v>
       </c>
       <c r="I48" s="150">
         <v>0</v>
       </c>
       <c r="J48" s="150">
-        <v>0</v>
+        <v>168400</v>
       </c>
       <c r="K48" s="150">
         <v>0</v>
       </c>
       <c r="L48" s="150">
-        <v>0</v>
-      </c>
-      <c r="M48" s="173"/>
-      <c r="N48" s="170">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O48" s="148">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+        <v>53400</v>
+      </c>
+      <c r="M48" s="150">
+        <v>0</v>
+      </c>
+      <c r="N48" s="173"/>
+      <c r="O48" s="170">
+        <f t="shared" si="4"/>
+        <v>359896</v>
+      </c>
+      <c r="P48" s="148">
+        <f t="shared" si="5"/>
+        <v>0.55368615384615383</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="59" t="s">
-        <v>99</v>
+        <v>214</v>
+      </c>
+      <c r="B49" s="62" t="s">
+        <v>209</v>
       </c>
       <c r="C49" s="59" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="E49" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="D49" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" s="62" t="s">
         <v>256</v>
       </c>
       <c r="F49" s="114">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="G49" s="23"/>
       <c r="H49" s="150">
-        <v>12470</v>
+        <v>0</v>
       </c>
       <c r="I49" s="150">
         <v>0</v>
       </c>
       <c r="J49" s="150">
-        <v>43650</v>
+        <v>0</v>
       </c>
       <c r="K49" s="150">
         <v>0</v>
       </c>
       <c r="L49" s="150">
-        <v>96100</v>
-      </c>
-      <c r="M49" s="173"/>
-      <c r="N49" s="170">
-        <f t="shared" si="2"/>
-        <v>152220</v>
-      </c>
-      <c r="O49" s="148">
-        <f t="shared" si="3"/>
-        <v>0.50739999999999996</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="M49" s="150">
+        <v>0</v>
+      </c>
+      <c r="N49" s="173"/>
+      <c r="O49" s="170">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="148">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
-        <v>331</v>
+        <v>49</v>
       </c>
       <c r="B50" s="59" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
       <c r="C50" s="59" t="s">
-        <v>324</v>
+        <v>100</v>
       </c>
       <c r="D50" s="59" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
       <c r="E50" s="59" t="s">
         <v>256</v>
       </c>
       <c r="F50" s="114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="23"/>
       <c r="H50" s="150">
-        <v>0</v>
+        <v>12470</v>
       </c>
       <c r="I50" s="150">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J50" s="150">
-        <v>0</v>
+        <v>43650</v>
       </c>
       <c r="K50" s="150">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="L50" s="150">
-        <v>-800</v>
-      </c>
-      <c r="M50" s="173"/>
-      <c r="N50" s="170">
-        <f t="shared" si="2"/>
-        <v>-230</v>
-      </c>
-      <c r="O50" s="148">
-        <f t="shared" si="3"/>
-        <v>-2.3E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>96100</v>
+      </c>
+      <c r="M50" s="150">
+        <v>5967</v>
+      </c>
+      <c r="N50" s="173"/>
+      <c r="O50" s="170">
+        <f t="shared" si="4"/>
+        <v>158187</v>
+      </c>
+      <c r="P50" s="148">
+        <f t="shared" si="5"/>
+        <v>0.52729000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="B51" s="59" t="s">
         <v>286</v>
       </c>
       <c r="C51" s="59" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="D51" s="59" t="s">
         <v>286</v>
@@ -8922,143 +9100,154 @@
         <v>256</v>
       </c>
       <c r="F51" s="114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G51" s="23"/>
       <c r="H51" s="150">
+        <v>0</v>
+      </c>
+      <c r="I51" s="150">
+        <v>50</v>
+      </c>
+      <c r="J51" s="150">
+        <v>0</v>
+      </c>
+      <c r="K51" s="150">
+        <v>520</v>
+      </c>
+      <c r="L51" s="150">
+        <v>-800</v>
+      </c>
+      <c r="M51" s="150">
+        <v>280</v>
+      </c>
+      <c r="N51" s="173"/>
+      <c r="O51" s="170">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="P51" s="148">
+        <f t="shared" si="5"/>
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="B52" s="59" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="59" t="s">
+        <v>285</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>286</v>
+      </c>
+      <c r="E52" s="59" t="s">
+        <v>256</v>
+      </c>
+      <c r="F52" s="114">
+        <v>5</v>
+      </c>
+      <c r="G52" s="23"/>
+      <c r="H52" s="150">
         <v>-28000</v>
       </c>
-      <c r="I51" s="150">
+      <c r="I52" s="150">
         <v>6932</v>
       </c>
-      <c r="J51" s="150">
+      <c r="J52" s="150">
         <v>104715</v>
       </c>
-      <c r="K51" s="150">
+      <c r="K52" s="150">
         <v>17309</v>
       </c>
-      <c r="L51" s="150">
+      <c r="L52" s="150">
         <v>26900</v>
       </c>
-      <c r="M51" s="173"/>
-      <c r="N51" s="170">
-        <f t="shared" si="2"/>
-        <v>127856</v>
-      </c>
-      <c r="O51" s="148">
-        <f t="shared" si="3"/>
-        <v>0.25571199999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="253">
-        <f>SUM(H4:H51)</f>
+      <c r="M52" s="150">
+        <v>-5815</v>
+      </c>
+      <c r="N52" s="173"/>
+      <c r="O52" s="170">
+        <f t="shared" si="4"/>
+        <v>122041</v>
+      </c>
+      <c r="P52" s="148">
+        <f t="shared" si="5"/>
+        <v>0.24408199999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="24"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="115"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="253">
+        <f>SUM(H4:H52)</f>
         <v>38252</v>
       </c>
-      <c r="I52" s="253">
-        <f>SUM(I4:I51)</f>
-        <v>-1494527</v>
-      </c>
-      <c r="J52" s="253">
-        <f>SUM(J4:J51)</f>
-        <v>2741586</v>
-      </c>
-      <c r="K52" s="253">
-        <f>SUM(K4:K51)</f>
-        <v>-32639</v>
-      </c>
-      <c r="L52" s="253">
-        <f>SUM(L4:L51)</f>
-        <v>-39697</v>
-      </c>
-      <c r="M52" s="253">
-        <f>SUM(M4:M51)</f>
-        <v>0</v>
-      </c>
-      <c r="N52" s="253">
-        <f t="shared" si="2"/>
-        <v>1212975</v>
-      </c>
-      <c r="O52" s="254">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="249"/>
-      <c r="B53" s="249"/>
-      <c r="C53" s="249"/>
-      <c r="D53" s="249"/>
-      <c r="E53" s="249"/>
-      <c r="F53" s="250"/>
-      <c r="G53" s="249"/>
-      <c r="H53" s="249"/>
-      <c r="I53" s="249"/>
-      <c r="J53" s="249"/>
-      <c r="K53" s="249"/>
-      <c r="L53" s="249"/>
-      <c r="M53" s="249"/>
-      <c r="N53" s="249"/>
-      <c r="O53" s="251"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="201" t="s">
+      <c r="I53" s="253">
+        <f>SUM(I4:I52)</f>
+        <v>-1490903</v>
+      </c>
+      <c r="J53" s="253">
+        <f>SUM(J4:J52)</f>
+        <v>2756338</v>
+      </c>
+      <c r="K53" s="253">
+        <f>SUM(K4:K52)</f>
+        <v>-39084</v>
+      </c>
+      <c r="L53" s="253">
+        <f>SUM(L4:L52)</f>
+        <v>-31777</v>
+      </c>
+      <c r="M53" s="253">
+        <f>SUM(M4:M52)</f>
+        <v>885698</v>
+      </c>
+      <c r="N53" s="253">
+        <f>SUM(N4:N52)</f>
+        <v>0</v>
+      </c>
+      <c r="O53" s="253">
+        <f t="shared" si="4"/>
+        <v>2118524</v>
+      </c>
+      <c r="P53" s="254">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="249"/>
+      <c r="B54" s="249"/>
+      <c r="C54" s="249"/>
+      <c r="D54" s="249"/>
+      <c r="E54" s="249"/>
+      <c r="F54" s="250"/>
+      <c r="G54" s="249"/>
+      <c r="H54" s="249"/>
+      <c r="I54" s="249"/>
+      <c r="J54" s="249"/>
+      <c r="K54" s="249"/>
+      <c r="L54" s="249"/>
+      <c r="M54" s="249"/>
+      <c r="N54" s="249"/>
+      <c r="O54" s="249"/>
+      <c r="P54" s="251"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="201" t="s">
         <v>241</v>
       </c>
-      <c r="B54" s="202" t="s">
+      <c r="B55" s="202" t="s">
         <v>240</v>
-      </c>
-      <c r="C54" s="202" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="202" t="s">
-        <v>87</v>
-      </c>
-      <c r="E54" s="202" t="s">
-        <v>256</v>
-      </c>
-      <c r="F54" s="203">
-        <v>3</v>
-      </c>
-      <c r="G54" s="204"/>
-      <c r="H54" s="161">
-        <v>5771</v>
-      </c>
-      <c r="I54" s="161">
-        <v>-30800</v>
-      </c>
-      <c r="J54" s="161">
-        <v>160555</v>
-      </c>
-      <c r="K54" s="161">
-        <v>15600</v>
-      </c>
-      <c r="L54" s="161">
-        <v>149000</v>
-      </c>
-      <c r="M54" s="245"/>
-      <c r="N54" s="246">
-        <f>SUM(H54:M54)</f>
-        <v>300126</v>
-      </c>
-      <c r="O54" s="247">
-        <f>IFERROR(N54/F54*100,0)/10000000</f>
-        <v>1.0004200000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="201" t="s">
-        <v>273</v>
-      </c>
-      <c r="B55" s="202" t="s">
-        <v>272</v>
       </c>
       <c r="C55" s="202" t="s">
         <v>57</v>
@@ -9069,185 +9258,245 @@
       <c r="E55" s="202" t="s">
         <v>256</v>
       </c>
-      <c r="F55" s="203"/>
+      <c r="F55" s="203">
+        <v>3</v>
+      </c>
       <c r="G55" s="204"/>
       <c r="H55" s="161">
-        <v>0</v>
+        <v>5771</v>
       </c>
       <c r="I55" s="161">
+        <v>-30800</v>
+      </c>
+      <c r="J55" s="161">
+        <v>160555</v>
+      </c>
+      <c r="K55" s="161">
+        <v>15600</v>
+      </c>
+      <c r="L55" s="161">
+        <v>149000</v>
+      </c>
+      <c r="M55" s="161">
+        <v>2277</v>
+      </c>
+      <c r="N55" s="245"/>
+      <c r="O55" s="246">
+        <f>SUM(H55:N55)</f>
+        <v>302403</v>
+      </c>
+      <c r="P55" s="247">
+        <f>IFERROR(O55/F55*100,0)/10000000</f>
+        <v>1.0080100000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="201" t="s">
+        <v>273</v>
+      </c>
+      <c r="B56" s="202" t="s">
+        <v>272</v>
+      </c>
+      <c r="C56" s="202" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="202" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" s="202" t="s">
+        <v>256</v>
+      </c>
+      <c r="F56" s="203"/>
+      <c r="G56" s="204"/>
+      <c r="H56" s="161">
+        <v>0</v>
+      </c>
+      <c r="I56" s="161">
         <v>-51000</v>
       </c>
-      <c r="J55" s="161">
+      <c r="J56" s="161">
         <v>149000</v>
       </c>
-      <c r="K55" s="161">
-        <v>0</v>
-      </c>
-      <c r="L55" s="161">
-        <v>0</v>
-      </c>
-      <c r="M55" s="173"/>
-      <c r="N55" s="170">
-        <f>SUM(H55:M55)</f>
-        <v>98000</v>
-      </c>
-      <c r="O55" s="148">
-        <f>IFERROR(N55/F55*100,0)/10000000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="199"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="169">
-        <f t="shared" ref="H56:L56" si="4">SUM(H54:H55)</f>
+      <c r="K56" s="161">
+        <v>0</v>
+      </c>
+      <c r="L56" s="161">
+        <v>0</v>
+      </c>
+      <c r="M56" s="161">
+        <v>-11300</v>
+      </c>
+      <c r="N56" s="173"/>
+      <c r="O56" s="170">
+        <f>SUM(H56:N56)</f>
+        <v>86700</v>
+      </c>
+      <c r="P56" s="148">
+        <f>IFERROR(O56/F56*100,0)/10000000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" s="248" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="199"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="74"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="169">
+        <f t="shared" ref="H57:M57" si="6">SUM(H55:H56)</f>
         <v>5771</v>
       </c>
-      <c r="I56" s="169">
-        <f t="shared" si="4"/>
+      <c r="I57" s="169">
+        <f t="shared" si="6"/>
         <v>-81800</v>
       </c>
-      <c r="J56" s="169">
-        <f t="shared" si="4"/>
+      <c r="J57" s="169">
+        <f t="shared" si="6"/>
         <v>309555</v>
       </c>
-      <c r="K56" s="169">
-        <f t="shared" si="4"/>
+      <c r="K57" s="169">
+        <f t="shared" si="6"/>
         <v>15600</v>
       </c>
-      <c r="L56" s="169">
-        <f t="shared" si="4"/>
+      <c r="L57" s="169">
+        <f t="shared" si="6"/>
         <v>149000</v>
       </c>
-      <c r="M56" s="169">
-        <f>SUM(M54:M55)</f>
-        <v>0</v>
-      </c>
-      <c r="N56" s="256">
-        <f>SUM(H56:M56)</f>
-        <v>398126</v>
-      </c>
-      <c r="O56" s="172"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="R57" s="133"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q58" s="133"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q59" s="5"/>
+      <c r="M57" s="169">
+        <f t="shared" si="6"/>
+        <v>-9023</v>
+      </c>
+      <c r="N57" s="169">
+        <f>SUM(N55:N56)</f>
+        <v>0</v>
+      </c>
+      <c r="O57" s="256">
+        <f>SUM(H57:N57)</f>
+        <v>389103</v>
+      </c>
+      <c r="P57" s="172"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S58" s="133"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R59" s="133"/>
-      <c r="S59" s="236"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q60" s="133"/>
-      <c r="R60" s="133"/>
-      <c r="S60" s="236"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q61" s="133"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R60" s="5"/>
+      <c r="S60" s="133"/>
+      <c r="T60" s="236"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R61" s="133"/>
-      <c r="S61" s="236"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q62" s="133"/>
+      <c r="S61" s="133"/>
+      <c r="T61" s="236"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R62" s="133"/>
-      <c r="S62" s="236"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q63" s="133"/>
+      <c r="S62" s="133"/>
+      <c r="T62" s="236"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R63" s="133"/>
-      <c r="S63" s="236"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q64" s="133"/>
-      <c r="R64" s="236"/>
-      <c r="S64" s="236"/>
-    </row>
-    <row r="65" spans="17:19" x14ac:dyDescent="0.25">
-      <c r="Q65" s="236"/>
-      <c r="R65" s="236"/>
+      <c r="S63" s="133"/>
+      <c r="T63" s="236"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R64" s="133"/>
+      <c r="S64" s="133"/>
+      <c r="T64" s="236"/>
+    </row>
+    <row r="65" spans="18:20" x14ac:dyDescent="0.25">
+      <c r="R65" s="133"/>
       <c r="S65" s="236"/>
+      <c r="T65" s="236"/>
+    </row>
+    <row r="66" spans="18:20" x14ac:dyDescent="0.25">
+      <c r="R66" s="236"/>
+      <c r="S66" s="236"/>
+      <c r="T66" s="236"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2 A3:G3 O52:O53 O56 N39:O39 N23:O24 O10:O20 N10:N21 H2:O3 A54:O55 A34:N34 A35:M35 G36:M36 N41:O51 N5:O9 N26:N33 O26:O32 A4:M33 N35:N37 O36 A37:M52 A56:M56">
-    <cfRule type="expression" dxfId="560" priority="17">
+  <conditionalFormatting sqref="G2 A3:G3 P53:P54 P57 O40:P40 O23:P24 P10:P20 O10:O21 H2:P3 A55:P56 A35:O35 A36:N36 G37:N37 O42:P52 O5:P9 O26:P27 O36:O38 P37 A38:N53 A57:N57 A4:N34 P29:P33 O29:O34">
+    <cfRule type="expression" dxfId="562" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O33">
-    <cfRule type="expression" dxfId="559" priority="16">
+  <conditionalFormatting sqref="P34">
+    <cfRule type="expression" dxfId="561" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O4">
-    <cfRule type="expression" dxfId="558" priority="14">
+  <conditionalFormatting sqref="O4:P4">
+    <cfRule type="expression" dxfId="560" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O35">
-    <cfRule type="expression" dxfId="557" priority="13">
+  <conditionalFormatting sqref="P36">
+    <cfRule type="expression" dxfId="559" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O21">
-    <cfRule type="expression" dxfId="556" priority="12">
+  <conditionalFormatting sqref="P21">
+    <cfRule type="expression" dxfId="558" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N52">
-    <cfRule type="expression" dxfId="555" priority="11">
+  <conditionalFormatting sqref="O53">
+    <cfRule type="expression" dxfId="557" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O37">
-    <cfRule type="expression" dxfId="554" priority="10">
+  <conditionalFormatting sqref="P38">
+    <cfRule type="expression" dxfId="556" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N25:O25">
-    <cfRule type="expression" dxfId="553" priority="9">
+  <conditionalFormatting sqref="O25:P25">
+    <cfRule type="expression" dxfId="555" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N40:O40">
-    <cfRule type="expression" dxfId="552" priority="7">
+  <conditionalFormatting sqref="O41:P41">
+    <cfRule type="expression" dxfId="554" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N56">
-    <cfRule type="expression" dxfId="551" priority="6">
+  <conditionalFormatting sqref="O57">
+    <cfRule type="expression" dxfId="553" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N38:O38">
-    <cfRule type="expression" dxfId="550" priority="5">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22">
-    <cfRule type="expression" dxfId="549" priority="4">
+  <conditionalFormatting sqref="O39:P39">
+    <cfRule type="expression" dxfId="552" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22">
-    <cfRule type="expression" dxfId="548" priority="3">
+    <cfRule type="expression" dxfId="551" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O34">
-    <cfRule type="expression" dxfId="547" priority="2">
+  <conditionalFormatting sqref="P22">
+    <cfRule type="expression" dxfId="550" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A36:F36">
-    <cfRule type="expression" dxfId="546" priority="1">
+  <conditionalFormatting sqref="P35">
+    <cfRule type="expression" dxfId="549" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37:F37">
+    <cfRule type="expression" dxfId="548" priority="2">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O28:P28">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9689,7 +9938,7 @@
       <c r="R7" s="158"/>
       <c r="S7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>190895</v>
+        <v>308040</v>
       </c>
       <c r="T7" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9701,7 +9950,7 @@
       <c r="X7"/>
       <c r="Y7" s="153">
         <f t="shared" si="0"/>
-        <v>1433109</v>
+        <v>1550254</v>
       </c>
       <c r="Z7" s="167">
         <f t="shared" si="1"/>
@@ -9825,7 +10074,7 @@
       <c r="R9" s="158"/>
       <c r="S9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>71537</v>
+        <v>128337</v>
       </c>
       <c r="T9" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9836,7 +10085,7 @@
       <c r="W9" s="149"/>
       <c r="Y9" s="153">
         <f t="shared" ref="Y9" si="6">M9+P9+S9+V9</f>
-        <v>-64849</v>
+        <v>-8049</v>
       </c>
       <c r="Z9" s="167">
         <f t="shared" ref="Z9" si="7">(N9+Q9+T9+W9)</f>
@@ -9906,7 +10155,7 @@
       <c r="R10" s="158"/>
       <c r="S10" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-324610</v>
+        <v>-200210</v>
       </c>
       <c r="T10" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9917,7 +10166,7 @@
       <c r="W10" s="72"/>
       <c r="Y10" s="153">
         <f t="shared" si="0"/>
-        <v>-1500677</v>
+        <v>-1376277</v>
       </c>
       <c r="Z10" s="167">
         <f t="shared" si="1"/>
@@ -9987,7 +10236,7 @@
       <c r="R11" s="158"/>
       <c r="S11" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>119340</v>
+        <v>150730</v>
       </c>
       <c r="T11" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -9998,7 +10247,7 @@
       <c r="W11" s="149"/>
       <c r="Y11" s="153">
         <f t="shared" si="0"/>
-        <v>-282535</v>
+        <v>-251145</v>
       </c>
       <c r="Z11" s="167">
         <f t="shared" si="1"/>
@@ -10068,7 +10317,7 @@
       <c r="R12" s="158"/>
       <c r="S12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>67214</v>
+        <v>78214</v>
       </c>
       <c r="T12" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10079,7 +10328,7 @@
       <c r="W12" s="149"/>
       <c r="Y12" s="153">
         <f t="shared" ref="Y12" si="12">M12+P12+S12+V12</f>
-        <v>-22715</v>
+        <v>-11715</v>
       </c>
       <c r="Z12" s="167">
         <f t="shared" ref="Z12" si="13">(N12+Q12+T12+W12)</f>
@@ -10149,7 +10398,7 @@
       <c r="R13" s="158"/>
       <c r="S13" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-156520</v>
+        <v>-152120</v>
       </c>
       <c r="T13" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10161,7 +10410,7 @@
       <c r="X13"/>
       <c r="Y13" s="153">
         <f t="shared" si="0"/>
-        <v>-1140788</v>
+        <v>-1136388</v>
       </c>
       <c r="Z13" s="167">
         <f t="shared" si="1"/>
@@ -10639,7 +10888,7 @@
       <c r="R19" s="158"/>
       <c r="S19" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-4891</v>
+        <v>-1291</v>
       </c>
       <c r="T19" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10650,7 +10899,7 @@
       <c r="W19" s="149"/>
       <c r="Y19" s="153">
         <f t="shared" si="0"/>
-        <v>-2316</v>
+        <v>1284</v>
       </c>
       <c r="Z19" s="167">
         <f t="shared" si="1"/>
@@ -10810,7 +11059,7 @@
       <c r="R21" s="158"/>
       <c r="S21" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>91053</v>
+        <v>116153</v>
       </c>
       <c r="T21" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10821,7 +11070,7 @@
       <c r="W21" s="72"/>
       <c r="Y21" s="153">
         <f t="shared" si="0"/>
-        <v>-160129</v>
+        <v>-135029</v>
       </c>
       <c r="Z21" s="167">
         <f t="shared" si="1"/>
@@ -10891,7 +11140,7 @@
       <c r="R22" s="158"/>
       <c r="S22" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>108803</v>
+        <v>131533</v>
       </c>
       <c r="T22" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -10902,7 +11151,7 @@
       <c r="W22" s="72"/>
       <c r="Y22" s="153">
         <f t="shared" si="0"/>
-        <v>-94820</v>
+        <v>-72090</v>
       </c>
       <c r="Z22" s="167">
         <f t="shared" si="1"/>
@@ -11053,7 +11302,7 @@
       <c r="R24" s="158"/>
       <c r="S24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-15918</v>
+        <v>4082</v>
       </c>
       <c r="T24" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11064,7 +11313,7 @@
       <c r="W24" s="72"/>
       <c r="Y24" s="153">
         <f t="shared" si="0"/>
-        <v>1730263</v>
+        <v>1750263</v>
       </c>
       <c r="Z24" s="167">
         <f t="shared" si="1"/>
@@ -11375,7 +11624,7 @@
       <c r="R28" s="158"/>
       <c r="S28" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-38551</v>
+        <v>-81631</v>
       </c>
       <c r="T28" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11386,7 +11635,7 @@
       <c r="W28" s="72"/>
       <c r="Y28" s="153">
         <f t="shared" si="0"/>
-        <v>339717</v>
+        <v>296637</v>
       </c>
       <c r="Z28" s="167">
         <f t="shared" si="1"/>
@@ -11456,7 +11705,7 @@
       <c r="R29" s="158"/>
       <c r="S29" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-34123</v>
+        <v>477</v>
       </c>
       <c r="T29" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11468,7 +11717,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="153">
         <f t="shared" si="0"/>
-        <v>845330</v>
+        <v>879930</v>
       </c>
       <c r="Z29" s="167">
         <f t="shared" si="1"/>
@@ -11709,7 +11958,7 @@
       <c r="R32" s="158"/>
       <c r="S32" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>90715</v>
+        <v>227515</v>
       </c>
       <c r="T32" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11721,7 +11970,7 @@
       <c r="X32"/>
       <c r="Y32" s="153">
         <f t="shared" si="0"/>
-        <v>-395290</v>
+        <v>-258490</v>
       </c>
       <c r="Z32" s="167">
         <f t="shared" si="1"/>
@@ -11872,7 +12121,7 @@
       <c r="R34" s="158"/>
       <c r="S34" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>26700</v>
+        <v>27261</v>
       </c>
       <c r="T34" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -11883,7 +12132,7 @@
       <c r="W34" s="72"/>
       <c r="Y34" s="153">
         <f t="shared" si="0"/>
-        <v>-120927</v>
+        <v>-120366</v>
       </c>
       <c r="Z34" s="167">
         <f t="shared" si="1"/>
@@ -12041,7 +12290,7 @@
       <c r="R36" s="158"/>
       <c r="S36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-443600</v>
+        <v>-203900</v>
       </c>
       <c r="T36" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12052,7 +12301,7 @@
       <c r="W36" s="72"/>
       <c r="Y36" s="153">
         <f t="shared" si="0"/>
-        <v>2459026</v>
+        <v>2698726</v>
       </c>
       <c r="Z36" s="167">
         <f t="shared" si="1"/>
@@ -12120,7 +12369,7 @@
       <c r="R37" s="158"/>
       <c r="S37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>10791</v>
+        <v>10591</v>
       </c>
       <c r="T37" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12131,7 +12380,7 @@
       <c r="W37" s="149"/>
       <c r="Y37" s="153">
         <f t="shared" ref="Y37" si="22">M37+P37+S37+V37</f>
-        <v>-32875</v>
+        <v>-33075</v>
       </c>
       <c r="Z37" s="167">
         <f t="shared" ref="Z37" si="23">(N37+Q37+T37+W37)</f>
@@ -12201,7 +12450,7 @@
       <c r="R38" s="158"/>
       <c r="S38" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-115600</v>
+        <v>-140600</v>
       </c>
       <c r="T38" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12212,7 +12461,7 @@
       <c r="W38" s="72"/>
       <c r="Y38" s="153">
         <f t="shared" si="0"/>
-        <v>2425454</v>
+        <v>2400454</v>
       </c>
       <c r="Z38" s="167">
         <f t="shared" si="1"/>
@@ -12282,7 +12531,7 @@
       <c r="R39" s="158"/>
       <c r="S39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>468515</v>
+        <v>484715</v>
       </c>
       <c r="T39" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12294,7 +12543,7 @@
       <c r="X39" s="131"/>
       <c r="Y39" s="153">
         <f t="shared" ref="Y39:Y74" si="24">M39+P39+S39+V39</f>
-        <v>5749262</v>
+        <v>5765462</v>
       </c>
       <c r="Z39" s="167">
         <f t="shared" ref="Z39:Z74" si="25">(N39+Q39+T39+W39)</f>
@@ -12879,7 +13128,7 @@
       <c r="R46" s="158"/>
       <c r="S46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-64150</v>
+        <v>-24665</v>
       </c>
       <c r="T46" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12891,7 +13140,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="153">
         <f t="shared" si="24"/>
-        <v>708721</v>
+        <v>748206</v>
       </c>
       <c r="Z46" s="167">
         <f t="shared" si="25"/>
@@ -12962,7 +13211,7 @@
       <c r="R47" s="158"/>
       <c r="S47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>37899</v>
+        <v>56899</v>
       </c>
       <c r="T47" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -12973,7 +13222,7 @@
       <c r="W47" s="72"/>
       <c r="Y47" s="153">
         <f t="shared" si="24"/>
-        <v>-41151</v>
+        <v>-22151</v>
       </c>
       <c r="Z47" s="167">
         <f t="shared" si="25"/>
@@ -13131,7 +13380,7 @@
       <c r="R49" s="158"/>
       <c r="S49" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>115168</v>
+        <v>132663</v>
       </c>
       <c r="T49" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13142,7 +13391,7 @@
       <c r="W49" s="72"/>
       <c r="Y49" s="153">
         <f t="shared" si="24"/>
-        <v>183433</v>
+        <v>200928</v>
       </c>
       <c r="Z49" s="167">
         <f t="shared" si="25"/>
@@ -13386,7 +13635,7 @@
       <c r="R52" s="158"/>
       <c r="S52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>2071</v>
+        <v>79531</v>
       </c>
       <c r="T52" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13397,7 +13646,7 @@
       <c r="W52" s="72"/>
       <c r="Y52" s="153">
         <f t="shared" si="24"/>
-        <v>197132</v>
+        <v>274592</v>
       </c>
       <c r="Z52" s="167">
         <f t="shared" si="25"/>
@@ -13467,7 +13716,7 @@
       <c r="R53" s="158"/>
       <c r="S53" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-97726</v>
+        <v>-40812</v>
       </c>
       <c r="T53" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13478,7 +13727,7 @@
       <c r="W53" s="72"/>
       <c r="Y53" s="153">
         <f t="shared" si="24"/>
-        <v>562523</v>
+        <v>619437</v>
       </c>
       <c r="Z53" s="167">
         <f t="shared" si="25"/>
@@ -13712,7 +13961,7 @@
       <c r="R56" s="158"/>
       <c r="S56" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>175078</v>
+        <v>64934</v>
       </c>
       <c r="T56" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13723,7 +13972,7 @@
       <c r="W56" s="72"/>
       <c r="Y56" s="153">
         <f t="shared" si="24"/>
-        <v>-4479257</v>
+        <v>-4589401</v>
       </c>
       <c r="Z56" s="167">
         <f t="shared" si="25"/>
@@ -13966,7 +14215,7 @@
       <c r="R59" s="158"/>
       <c r="S59" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>30200</v>
+        <v>42200</v>
       </c>
       <c r="T59" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -13978,7 +14227,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="153">
         <f t="shared" si="24"/>
-        <v>62891</v>
+        <v>74891</v>
       </c>
       <c r="Z59" s="167">
         <f t="shared" si="25"/>
@@ -14055,7 +14304,7 @@
       <c r="R60" s="158"/>
       <c r="S60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-655229</v>
+        <v>-707729</v>
       </c>
       <c r="T60" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14066,7 +14315,7 @@
       <c r="W60" s="72"/>
       <c r="Y60" s="153">
         <f t="shared" si="24"/>
-        <v>3024386</v>
+        <v>2971886</v>
       </c>
       <c r="Z60" s="167">
         <f t="shared" si="25"/>
@@ -14141,7 +14390,7 @@
       <c r="R61" s="158"/>
       <c r="S61" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>765</v>
+        <v>4282</v>
       </c>
       <c r="T61" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14152,7 +14401,7 @@
       <c r="W61" s="149"/>
       <c r="Y61" s="153">
         <f t="shared" ref="Y61" si="39">M61+P61+S61+V61</f>
-        <v>14056</v>
+        <v>17573</v>
       </c>
       <c r="Z61" s="167">
         <f t="shared" ref="Z61" si="40">(N61+Q61+T61+W61)</f>
@@ -14222,7 +14471,7 @@
       <c r="R62" s="158"/>
       <c r="S62" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>323128</v>
+        <v>425136</v>
       </c>
       <c r="T62" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14233,7 +14482,7 @@
       <c r="W62" s="72"/>
       <c r="Y62" s="153">
         <f t="shared" si="24"/>
-        <v>1166229</v>
+        <v>1268237</v>
       </c>
       <c r="Z62" s="167">
         <f t="shared" si="25"/>
@@ -14473,7 +14722,7 @@
       <c r="R65" s="158"/>
       <c r="S65" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>40600</v>
+        <v>39400</v>
       </c>
       <c r="T65" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14485,7 +14734,7 @@
       <c r="X65" s="131"/>
       <c r="Y65" s="153">
         <f t="shared" si="24"/>
-        <v>823381</v>
+        <v>822181</v>
       </c>
       <c r="Z65" s="167">
         <f t="shared" si="25"/>
@@ -14635,7 +14884,7 @@
       <c r="R67" s="158"/>
       <c r="S67" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>-254750</v>
+        <v>-325150</v>
       </c>
       <c r="T67" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -14646,7 +14895,7 @@
       <c r="W67" s="149"/>
       <c r="Y67" s="153">
         <f t="shared" ref="Y67" si="45">M67+P67+S67+V67</f>
-        <v>-1217579</v>
+        <v>-1287979</v>
       </c>
       <c r="Z67" s="167">
         <f t="shared" ref="Z67" si="46">(N67+Q67+T67+W67)</f>
@@ -15097,7 +15346,7 @@
       <c r="R73" s="158"/>
       <c r="S73" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>152220</v>
+        <v>158187</v>
       </c>
       <c r="T73" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -15108,7 +15357,7 @@
       <c r="W73" s="72"/>
       <c r="Y73" s="153">
         <f t="shared" si="24"/>
-        <v>524524</v>
+        <v>530491</v>
       </c>
       <c r="Z73" s="167">
         <f t="shared" si="25"/>
@@ -15336,7 +15585,7 @@
       <c r="R76" s="158"/>
       <c r="S76" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$2,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
-        <v>127856</v>
+        <v>122041</v>
       </c>
       <c r="T76" s="154">
         <f>IFERROR(VLOOKUP($A$3:$A$139,'FY-(26-27)Q3'!$A$4:$ABW$123,MATCH('FY-(26-27)Q1'!$S$2:$T$3,'FY-(26-27)Q3'!$A$2:$BX$2,0),0),0)</f>
@@ -15347,7 +15596,7 @@
       <c r="W76" s="149"/>
       <c r="Y76" s="153">
         <f t="shared" si="55"/>
-        <v>618709</v>
+        <v>612894</v>
       </c>
       <c r="Z76" s="167">
         <f t="shared" si="56"/>
@@ -15390,7 +15639,7 @@
       <c r="R77" s="122"/>
       <c r="S77" s="109">
         <f>SUM(S4:S74)</f>
-        <v>1105623</v>
+        <v>1981371</v>
       </c>
       <c r="T77" s="122"/>
       <c r="U77" s="122"/>
@@ -15398,7 +15647,7 @@
       <c r="W77" s="50"/>
       <c r="Y77" s="153">
         <f>SUM(Y4:Y76)</f>
-        <v>24614695</v>
+        <v>25484628</v>
       </c>
       <c r="Z77" s="160"/>
     </row>
@@ -15856,1222 +16105,1222 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56:C56 V4:W4 A27:F29 V20:W21 A13:C13 W48:W49 A3:F4 L2:L3 A48:F49 A52:C52 W22:W30 A80:F81 C16 W45:W46 W42 A42:H42 G41:H41 F16 F13 F70:F71 W58:W60 G58:J60 A66:J66 Y58:Y60 Y77:Z77 G13:H14 G7:J11 F53 F56:J56 Y56 W52:W53 H4:O4 M5:O5 G16:H18 K5:L11 A20:F24 D5:J5 F72:J74 A44:J44 Y66 Z56:Z60 G45:J53 K44:L53 A73:C73 A74:E74 A45:F46 E52:F52 A60:F60 Y34:Z36 M80:O82 M7:O11 A34:O36 R34:R36 R13:R17 R22:R30 R48:R53 U80:U82 A77:E77 A38:H39 A62:F62 K62:O66 Z62:Z66 Y62:Y63 G62:J63 R38:R46 M38:O53 I38:L43 Y38:Z53 W38:W39 K69:O74 G69:J69 W66:W68 R62:R74 G67:O68 Y67:Z74 A9 F9 I13:O18 Y13:Z18 Y55:Z55 R55:R60 K55:O60 G55:J55 W55:W56 Y20:Z32 G20:O32 A31:A32 P13:Q36 A7:F8 R7:R9 U55:U60 U62:U71 U38:U43 U48:U53 U22:U30 U17 U45:U46 U34:W36 U13:W16 U72:W74 U44:W44 Y4:Z11 U7:W9 G77:W78 G84:W84">
-    <cfRule type="expression" dxfId="245" priority="450">
+    <cfRule type="expression" dxfId="247" priority="450">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V38:V39 V23:V24 V59 V48:V49 V56 V45:V46 V27:V29 G2:I3 V52 G4:H4">
-    <cfRule type="expression" dxfId="244" priority="449">
+    <cfRule type="expression" dxfId="246" priority="449">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="243" priority="446">
+    <cfRule type="expression" dxfId="245" priority="446">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V80:W81">
-    <cfRule type="expression" dxfId="242" priority="443">
+    <cfRule type="expression" dxfId="244" priority="443">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="241" priority="444">
+    <cfRule type="expression" dxfId="243" priority="444">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V60">
-    <cfRule type="expression" dxfId="240" priority="434">
+    <cfRule type="expression" dxfId="242" priority="434">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V22">
-    <cfRule type="expression" dxfId="239" priority="435">
+    <cfRule type="expression" dxfId="241" priority="435">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:C53 E53">
-    <cfRule type="expression" dxfId="238" priority="424">
+    <cfRule type="expression" dxfId="240" priority="424">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V53 V55">
-    <cfRule type="expression" dxfId="237" priority="422">
+    <cfRule type="expression" dxfId="239" priority="422">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="expression" dxfId="236" priority="420">
+    <cfRule type="expression" dxfId="238" priority="420">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V42">
-    <cfRule type="expression" dxfId="235" priority="411">
+    <cfRule type="expression" dxfId="237" priority="411">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="234" priority="410">
+    <cfRule type="expression" dxfId="236" priority="410">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72:C72">
-    <cfRule type="expression" dxfId="233" priority="382">
+    <cfRule type="expression" dxfId="235" priority="382">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V30">
-    <cfRule type="expression" dxfId="232" priority="408">
+    <cfRule type="expression" dxfId="234" priority="408">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:E26">
-    <cfRule type="expression" dxfId="231" priority="407">
+    <cfRule type="expression" dxfId="233" priority="407">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V26">
-    <cfRule type="expression" dxfId="230" priority="405">
+    <cfRule type="expression" dxfId="232" priority="405">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:E25">
-    <cfRule type="expression" dxfId="229" priority="404">
+    <cfRule type="expression" dxfId="231" priority="404">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V25">
-    <cfRule type="expression" dxfId="228" priority="402">
+    <cfRule type="expression" dxfId="230" priority="402">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="227" priority="389">
+    <cfRule type="expression" dxfId="229" priority="389">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4 U20:U21">
-    <cfRule type="expression" dxfId="226" priority="333">
+    <cfRule type="expression" dxfId="228" priority="333">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72">
-    <cfRule type="expression" dxfId="225" priority="380">
+    <cfRule type="expression" dxfId="227" priority="380">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4 U20:U21">
-    <cfRule type="expression" dxfId="224" priority="332">
+    <cfRule type="expression" dxfId="226" priority="332">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V58">
-    <cfRule type="expression" dxfId="223" priority="385">
+    <cfRule type="expression" dxfId="225" priority="385">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="expression" dxfId="222" priority="351">
+    <cfRule type="expression" dxfId="224" priority="351">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:O21 M34:O34">
-    <cfRule type="expression" dxfId="221" priority="349">
+    <cfRule type="expression" dxfId="223" priority="349">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17 A18:C18 E18:F18">
-    <cfRule type="expression" dxfId="220" priority="357">
+    <cfRule type="expression" dxfId="222" priority="357">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V17:W17">
-    <cfRule type="expression" dxfId="219" priority="356">
+    <cfRule type="expression" dxfId="221" priority="356">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="218" priority="341">
+    <cfRule type="expression" dxfId="220" priority="341">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4 R20:R21">
-    <cfRule type="expression" dxfId="217" priority="340">
+    <cfRule type="expression" dxfId="219" priority="340">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V66:V68">
-    <cfRule type="expression" dxfId="216" priority="371">
+    <cfRule type="expression" dxfId="218" priority="371">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W62">
-    <cfRule type="expression" dxfId="215" priority="331">
+    <cfRule type="expression" dxfId="217" priority="331">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M35:O35">
-    <cfRule type="expression" dxfId="214" priority="342">
+    <cfRule type="expression" dxfId="216" priority="342">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="expression" dxfId="213" priority="352">
+    <cfRule type="expression" dxfId="215" priority="352">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:O21 N34:O34">
-    <cfRule type="expression" dxfId="212" priority="350">
+    <cfRule type="expression" dxfId="214" priority="350">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35:O35">
-    <cfRule type="expression" dxfId="211" priority="343">
+    <cfRule type="expression" dxfId="213" priority="343">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V62">
-    <cfRule type="expression" dxfId="210" priority="330">
+    <cfRule type="expression" dxfId="212" priority="330">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:O18">
-    <cfRule type="expression" dxfId="209" priority="288">
+    <cfRule type="expression" dxfId="211" priority="288">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="208" priority="287">
+    <cfRule type="expression" dxfId="210" priority="287">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U18">
-    <cfRule type="expression" dxfId="207" priority="285">
+    <cfRule type="expression" dxfId="209" priority="285">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:F31 B32:C32 E32:F32">
-    <cfRule type="expression" dxfId="206" priority="277">
+    <cfRule type="expression" dxfId="208" priority="277">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W31">
-    <cfRule type="expression" dxfId="205" priority="276">
+    <cfRule type="expression" dxfId="207" priority="276">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V18:W18">
-    <cfRule type="expression" dxfId="204" priority="290">
+    <cfRule type="expression" dxfId="206" priority="290">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N18:O18">
-    <cfRule type="expression" dxfId="203" priority="289">
+    <cfRule type="expression" dxfId="205" priority="289">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R18">
-    <cfRule type="expression" dxfId="202" priority="286">
+    <cfRule type="expression" dxfId="204" priority="286">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U18">
-    <cfRule type="expression" dxfId="201" priority="284">
+    <cfRule type="expression" dxfId="203" priority="284">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V31">
-    <cfRule type="expression" dxfId="200" priority="275">
+    <cfRule type="expression" dxfId="202" priority="275">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31">
-    <cfRule type="expression" dxfId="199" priority="269">
+    <cfRule type="expression" dxfId="201" priority="269">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31:O31">
-    <cfRule type="expression" dxfId="198" priority="274">
+    <cfRule type="expression" dxfId="200" priority="274">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31:O31">
-    <cfRule type="expression" dxfId="197" priority="273">
+    <cfRule type="expression" dxfId="199" priority="273">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31">
-    <cfRule type="expression" dxfId="196" priority="270">
+    <cfRule type="expression" dxfId="198" priority="270">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="195" priority="272">
+    <cfRule type="expression" dxfId="197" priority="272">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="194" priority="271">
+    <cfRule type="expression" dxfId="196" priority="271">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:F11 A10:C10 E10:F10 F12">
-    <cfRule type="expression" dxfId="193" priority="262">
+    <cfRule type="expression" dxfId="195" priority="262">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:W11">
-    <cfRule type="expression" dxfId="192" priority="261">
+    <cfRule type="expression" dxfId="194" priority="261">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="191" priority="258">
+    <cfRule type="expression" dxfId="193" priority="258">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:R11">
-    <cfRule type="expression" dxfId="190" priority="257">
+    <cfRule type="expression" dxfId="192" priority="257">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:U11">
-    <cfRule type="expression" dxfId="189" priority="255">
+    <cfRule type="expression" dxfId="191" priority="255">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10:O11">
-    <cfRule type="expression" dxfId="188" priority="260">
+    <cfRule type="expression" dxfId="190" priority="260">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:O11">
-    <cfRule type="expression" dxfId="187" priority="259">
+    <cfRule type="expression" dxfId="189" priority="259">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:U11">
-    <cfRule type="expression" dxfId="186" priority="256">
+    <cfRule type="expression" dxfId="188" priority="256">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="185" priority="248">
+    <cfRule type="expression" dxfId="187" priority="248">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W47">
-    <cfRule type="expression" dxfId="184" priority="247">
+    <cfRule type="expression" dxfId="186" priority="247">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V47">
-    <cfRule type="expression" dxfId="183" priority="246">
+    <cfRule type="expression" dxfId="185" priority="246">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U47">
-    <cfRule type="expression" dxfId="182" priority="241">
+    <cfRule type="expression" dxfId="184" priority="241">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U47">
-    <cfRule type="expression" dxfId="181" priority="240">
+    <cfRule type="expression" dxfId="183" priority="240">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M47:O47">
-    <cfRule type="expression" dxfId="180" priority="244">
+    <cfRule type="expression" dxfId="182" priority="244">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="179" priority="243">
+    <cfRule type="expression" dxfId="181" priority="243">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="expression" dxfId="178" priority="242">
+    <cfRule type="expression" dxfId="180" priority="242">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N47:O47">
-    <cfRule type="expression" dxfId="177" priority="245">
+    <cfRule type="expression" dxfId="179" priority="245">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="176" priority="233">
+    <cfRule type="expression" dxfId="178" priority="233">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:C5">
-    <cfRule type="expression" dxfId="175" priority="229">
+    <cfRule type="expression" dxfId="177" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W5">
-    <cfRule type="expression" dxfId="174" priority="228">
+    <cfRule type="expression" dxfId="176" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5">
-    <cfRule type="expression" dxfId="173" priority="222">
+    <cfRule type="expression" dxfId="175" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5">
-    <cfRule type="expression" dxfId="172" priority="221">
+    <cfRule type="expression" dxfId="174" priority="221">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:O5">
-    <cfRule type="expression" dxfId="171" priority="225">
+    <cfRule type="expression" dxfId="173" priority="225">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="170" priority="224">
+    <cfRule type="expression" dxfId="172" priority="224">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="expression" dxfId="169" priority="223">
+    <cfRule type="expression" dxfId="171" priority="223">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O5">
-    <cfRule type="expression" dxfId="168" priority="226">
+    <cfRule type="expression" dxfId="170" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:F51">
-    <cfRule type="expression" dxfId="167" priority="210">
+    <cfRule type="expression" dxfId="169" priority="210">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W50:W51">
-    <cfRule type="expression" dxfId="166" priority="209">
+    <cfRule type="expression" dxfId="168" priority="209">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V50:V51">
-    <cfRule type="expression" dxfId="165" priority="208">
+    <cfRule type="expression" dxfId="167" priority="208">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W32">
-    <cfRule type="expression" dxfId="164" priority="202">
+    <cfRule type="expression" dxfId="166" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V32">
-    <cfRule type="expression" dxfId="163" priority="201">
+    <cfRule type="expression" dxfId="165" priority="201">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32">
-    <cfRule type="expression" dxfId="162" priority="195">
+    <cfRule type="expression" dxfId="164" priority="195">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32:O32">
-    <cfRule type="expression" dxfId="161" priority="200">
+    <cfRule type="expression" dxfId="163" priority="200">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M32:O32">
-    <cfRule type="expression" dxfId="160" priority="199">
+    <cfRule type="expression" dxfId="162" priority="199">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U32">
-    <cfRule type="expression" dxfId="159" priority="196">
+    <cfRule type="expression" dxfId="161" priority="196">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="158" priority="198">
+    <cfRule type="expression" dxfId="160" priority="198">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R32">
-    <cfRule type="expression" dxfId="157" priority="197">
+    <cfRule type="expression" dxfId="159" priority="197">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W63">
-    <cfRule type="expression" dxfId="156" priority="193">
+    <cfRule type="expression" dxfId="158" priority="193">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V63">
-    <cfRule type="expression" dxfId="155" priority="192">
+    <cfRule type="expression" dxfId="157" priority="192">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14">
-    <cfRule type="expression" dxfId="154" priority="179">
+    <cfRule type="expression" dxfId="156" priority="179">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W41">
-    <cfRule type="expression" dxfId="153" priority="188">
+    <cfRule type="expression" dxfId="155" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V41">
-    <cfRule type="expression" dxfId="152" priority="187">
+    <cfRule type="expression" dxfId="154" priority="187">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:C69 E69:F69">
-    <cfRule type="expression" dxfId="151" priority="177">
+    <cfRule type="expression" dxfId="153" priority="177">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W69">
-    <cfRule type="expression" dxfId="150" priority="176">
+    <cfRule type="expression" dxfId="152" priority="176">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V69">
-    <cfRule type="expression" dxfId="149" priority="175">
+    <cfRule type="expression" dxfId="151" priority="175">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G80:G81">
-    <cfRule type="expression" dxfId="148" priority="170">
+    <cfRule type="expression" dxfId="150" priority="170">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H80">
-    <cfRule type="expression" dxfId="147" priority="167">
+    <cfRule type="expression" dxfId="149" priority="167">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H81">
-    <cfRule type="expression" dxfId="146" priority="166">
+    <cfRule type="expression" dxfId="148" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L79">
-    <cfRule type="expression" dxfId="145" priority="165">
+    <cfRule type="expression" dxfId="147" priority="165">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G79:I79">
-    <cfRule type="expression" dxfId="144" priority="164">
+    <cfRule type="expression" dxfId="146" priority="164">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J79">
-    <cfRule type="expression" dxfId="143" priority="163">
+    <cfRule type="expression" dxfId="145" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K79">
-    <cfRule type="expression" dxfId="142" priority="162">
+    <cfRule type="expression" dxfId="144" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y80:Z81">
-    <cfRule type="expression" dxfId="141" priority="149">
+    <cfRule type="expression" dxfId="143" priority="149">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="140" priority="159">
+    <cfRule type="expression" dxfId="142" priority="159">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:F41">
-    <cfRule type="expression" dxfId="139" priority="158">
+    <cfRule type="expression" dxfId="141" priority="158">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:F43">
-    <cfRule type="expression" dxfId="138" priority="157">
+    <cfRule type="expression" dxfId="140" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W43 G43:H43">
-    <cfRule type="expression" dxfId="137" priority="156">
+    <cfRule type="expression" dxfId="139" priority="156">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V43">
-    <cfRule type="expression" dxfId="136" priority="155">
+    <cfRule type="expression" dxfId="138" priority="155">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W40 G40:H40">
-    <cfRule type="expression" dxfId="135" priority="154">
+    <cfRule type="expression" dxfId="137" priority="154">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V40">
-    <cfRule type="expression" dxfId="134" priority="153">
+    <cfRule type="expression" dxfId="136" priority="153">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="133" priority="144">
+    <cfRule type="expression" dxfId="135" priority="144">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y84:Z84">
-    <cfRule type="expression" dxfId="132" priority="150">
+    <cfRule type="expression" dxfId="134" priority="150">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:B16">
-    <cfRule type="expression" dxfId="131" priority="148">
+    <cfRule type="expression" dxfId="133" priority="148">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="130" priority="147">
+    <cfRule type="expression" dxfId="132" priority="147">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="expression" dxfId="129" priority="146">
+    <cfRule type="expression" dxfId="131" priority="146">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:E16">
-    <cfRule type="expression" dxfId="128" priority="145">
+    <cfRule type="expression" dxfId="130" priority="145">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="expression" dxfId="127" priority="143">
+    <cfRule type="expression" dxfId="129" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J81">
-    <cfRule type="expression" dxfId="126" priority="140">
+    <cfRule type="expression" dxfId="128" priority="140">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80:J81">
-    <cfRule type="expression" dxfId="125" priority="139">
+    <cfRule type="expression" dxfId="127" priority="139">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:C71 E70:E71">
-    <cfRule type="expression" dxfId="124" priority="138">
+    <cfRule type="expression" dxfId="126" priority="138">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:J71 M70:O71">
-    <cfRule type="expression" dxfId="123" priority="137">
+    <cfRule type="expression" dxfId="125" priority="137">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70:W71">
-    <cfRule type="expression" dxfId="122" priority="136">
+    <cfRule type="expression" dxfId="124" priority="136">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V70:V71">
-    <cfRule type="expression" dxfId="121" priority="135">
+    <cfRule type="expression" dxfId="123" priority="135">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V57">
-    <cfRule type="expression" dxfId="120" priority="132">
+    <cfRule type="expression" dxfId="122" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:C57 E57:F57">
-    <cfRule type="expression" dxfId="119" priority="134">
+    <cfRule type="expression" dxfId="121" priority="134">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57 Y57 G57:J57">
-    <cfRule type="expression" dxfId="118" priority="133">
+    <cfRule type="expression" dxfId="120" priority="133">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:A65">
-    <cfRule type="expression" dxfId="117" priority="131">
+    <cfRule type="expression" dxfId="119" priority="131">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:B63">
-    <cfRule type="expression" dxfId="116" priority="130">
+    <cfRule type="expression" dxfId="118" priority="130">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64:B65">
-    <cfRule type="expression" dxfId="115" priority="129">
+    <cfRule type="expression" dxfId="117" priority="129">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:O65 G64:J65 Y64:Y65">
-    <cfRule type="expression" dxfId="114" priority="128">
+    <cfRule type="expression" dxfId="116" priority="128">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W64:W65">
-    <cfRule type="expression" dxfId="113" priority="126">
+    <cfRule type="expression" dxfId="115" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V64:V65">
-    <cfRule type="expression" dxfId="112" priority="125">
+    <cfRule type="expression" dxfId="114" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:C6 E6:F6">
-    <cfRule type="expression" dxfId="111" priority="124">
+    <cfRule type="expression" dxfId="113" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J6 M6:O6">
-    <cfRule type="expression" dxfId="110" priority="123">
+    <cfRule type="expression" dxfId="112" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:W6">
-    <cfRule type="expression" dxfId="109" priority="122">
+    <cfRule type="expression" dxfId="111" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6">
-    <cfRule type="expression" dxfId="108" priority="117">
+    <cfRule type="expression" dxfId="110" priority="117">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6">
-    <cfRule type="expression" dxfId="107" priority="116">
+    <cfRule type="expression" dxfId="109" priority="116">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:O6">
-    <cfRule type="expression" dxfId="106" priority="120">
+    <cfRule type="expression" dxfId="108" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="105" priority="119">
+    <cfRule type="expression" dxfId="107" priority="119">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R6">
-    <cfRule type="expression" dxfId="104" priority="118">
+    <cfRule type="expression" dxfId="106" priority="118">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6:O6">
-    <cfRule type="expression" dxfId="103" priority="121">
+    <cfRule type="expression" dxfId="105" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C55 E55:F55">
-    <cfRule type="expression" dxfId="102" priority="115">
+    <cfRule type="expression" dxfId="104" priority="115">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:F82">
-    <cfRule type="expression" dxfId="101" priority="113">
+    <cfRule type="expression" dxfId="103" priority="113">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V82:W82">
-    <cfRule type="expression" dxfId="100" priority="111">
+    <cfRule type="expression" dxfId="102" priority="111">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="expression" dxfId="99" priority="110">
+    <cfRule type="expression" dxfId="101" priority="110">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H82">
-    <cfRule type="expression" dxfId="98" priority="109">
+    <cfRule type="expression" dxfId="100" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y82:Z82">
-    <cfRule type="expression" dxfId="97" priority="108">
+    <cfRule type="expression" dxfId="99" priority="108">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J82">
-    <cfRule type="expression" dxfId="96" priority="107">
+    <cfRule type="expression" dxfId="98" priority="107">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I82:J82">
-    <cfRule type="expression" dxfId="95" priority="106">
+    <cfRule type="expression" dxfId="97" priority="106">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K80:L82">
-    <cfRule type="expression" dxfId="94" priority="104">
+    <cfRule type="expression" dxfId="96" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U19">
-    <cfRule type="expression" dxfId="93" priority="94">
+    <cfRule type="expression" dxfId="95" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="92" priority="102">
+    <cfRule type="expression" dxfId="94" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y19:Z19 G19:O19">
-    <cfRule type="expression" dxfId="91" priority="101">
+    <cfRule type="expression" dxfId="93" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19:O19">
-    <cfRule type="expression" dxfId="90" priority="98">
+    <cfRule type="expression" dxfId="92" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="89" priority="97">
+    <cfRule type="expression" dxfId="91" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U19">
-    <cfRule type="expression" dxfId="88" priority="95">
+    <cfRule type="expression" dxfId="90" priority="95">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V19:W19">
-    <cfRule type="expression" dxfId="87" priority="100">
+    <cfRule type="expression" dxfId="89" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N19:O19">
-    <cfRule type="expression" dxfId="86" priority="99">
+    <cfRule type="expression" dxfId="88" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="expression" dxfId="85" priority="96">
+    <cfRule type="expression" dxfId="87" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:E73">
-    <cfRule type="expression" dxfId="84" priority="93">
+    <cfRule type="expression" dxfId="86" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="expression" dxfId="83" priority="92">
+    <cfRule type="expression" dxfId="85" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="expression" dxfId="82" priority="91">
+    <cfRule type="expression" dxfId="84" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:E63 C64:E65">
-    <cfRule type="expression" dxfId="81" priority="90">
+    <cfRule type="expression" dxfId="83" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="80" priority="89">
+    <cfRule type="expression" dxfId="82" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="79" priority="88">
+    <cfRule type="expression" dxfId="81" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18">
-    <cfRule type="expression" dxfId="78" priority="87">
+    <cfRule type="expression" dxfId="80" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32">
-    <cfRule type="expression" dxfId="77" priority="86">
+    <cfRule type="expression" dxfId="79" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D70:D71">
-    <cfRule type="expression" dxfId="76" priority="74">
+    <cfRule type="expression" dxfId="78" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="75" priority="84">
+    <cfRule type="expression" dxfId="77" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53 D55">
-    <cfRule type="expression" dxfId="74" priority="83">
+    <cfRule type="expression" dxfId="76" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="73" priority="82">
+    <cfRule type="expression" dxfId="75" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="72" priority="81">
+    <cfRule type="expression" dxfId="74" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="71" priority="80">
+    <cfRule type="expression" dxfId="73" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="70" priority="79">
+    <cfRule type="expression" dxfId="72" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="69" priority="78">
+    <cfRule type="expression" dxfId="71" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73">
-    <cfRule type="expression" dxfId="68" priority="77">
+    <cfRule type="expression" dxfId="70" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D72">
-    <cfRule type="expression" dxfId="67" priority="76">
+    <cfRule type="expression" dxfId="69" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D69">
-    <cfRule type="expression" dxfId="66" priority="75">
+    <cfRule type="expression" dxfId="68" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="65" priority="73">
+    <cfRule type="expression" dxfId="67" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:O33 Y33:Z33">
-    <cfRule type="expression" dxfId="64" priority="72">
+    <cfRule type="expression" dxfId="66" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W33">
-    <cfRule type="expression" dxfId="63" priority="71">
+    <cfRule type="expression" dxfId="65" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V33">
-    <cfRule type="expression" dxfId="62" priority="70">
+    <cfRule type="expression" dxfId="64" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33">
-    <cfRule type="expression" dxfId="61" priority="64">
+    <cfRule type="expression" dxfId="63" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:O33">
-    <cfRule type="expression" dxfId="60" priority="69">
+    <cfRule type="expression" dxfId="62" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:O33">
-    <cfRule type="expression" dxfId="59" priority="68">
+    <cfRule type="expression" dxfId="61" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33">
-    <cfRule type="expression" dxfId="58" priority="65">
+    <cfRule type="expression" dxfId="60" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="57" priority="67">
+    <cfRule type="expression" dxfId="59" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="56" priority="66">
+    <cfRule type="expression" dxfId="58" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q38:Q53 Q55:Q60 Q62:Q76 Q4:Q11">
-    <cfRule type="expression" dxfId="55" priority="61">
+    <cfRule type="expression" dxfId="57" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P38:Q53 P55:Q60 P62:Q76 P4:Q11">
-    <cfRule type="expression" dxfId="54" priority="60">
+    <cfRule type="expression" dxfId="56" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:T82">
-    <cfRule type="expression" dxfId="53" priority="59">
+    <cfRule type="expression" dxfId="55" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q80:Q82">
-    <cfRule type="expression" dxfId="52" priority="58">
+    <cfRule type="expression" dxfId="54" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:Q82">
-    <cfRule type="expression" dxfId="51" priority="57">
+    <cfRule type="expression" dxfId="53" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
-    <cfRule type="expression" dxfId="50" priority="56">
+    <cfRule type="expression" dxfId="52" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:F75">
-    <cfRule type="expression" dxfId="49" priority="55">
+    <cfRule type="expression" dxfId="51" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75:O76 Y75:Z76 R75:R76 U75:W76">
-    <cfRule type="expression" dxfId="48" priority="54">
+    <cfRule type="expression" dxfId="50" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:Q37">
-    <cfRule type="expression" dxfId="47" priority="41">
+    <cfRule type="expression" dxfId="49" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:F37">
-    <cfRule type="expression" dxfId="46" priority="50">
+    <cfRule type="expression" dxfId="48" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:Q83">
-    <cfRule type="expression" dxfId="45" priority="26">
+    <cfRule type="expression" dxfId="47" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:F61">
-    <cfRule type="expression" dxfId="44" priority="48">
+    <cfRule type="expression" dxfId="46" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W61 Y61:Z61 G61:O61 R61 U61">
-    <cfRule type="expression" dxfId="43" priority="47">
+    <cfRule type="expression" dxfId="45" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V61">
-    <cfRule type="expression" dxfId="42" priority="46">
+    <cfRule type="expression" dxfId="44" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q61">
-    <cfRule type="expression" dxfId="41" priority="45">
+    <cfRule type="expression" dxfId="43" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P61:Q61">
-    <cfRule type="expression" dxfId="40" priority="44">
+    <cfRule type="expression" dxfId="42" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y37:Z37 G37:O37 R37 U37:W37">
-    <cfRule type="expression" dxfId="39" priority="43">
+    <cfRule type="expression" dxfId="41" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q37">
-    <cfRule type="expression" dxfId="38" priority="42">
+    <cfRule type="expression" dxfId="40" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q83">
-    <cfRule type="expression" dxfId="37" priority="27">
+    <cfRule type="expression" dxfId="39" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F83">
-    <cfRule type="expression" dxfId="36" priority="38">
+    <cfRule type="expression" dxfId="38" priority="38">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:E83">
-    <cfRule type="expression" dxfId="35" priority="37">
+    <cfRule type="expression" dxfId="37" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:O83 U83">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="36" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83:W83">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="35" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G83">
-    <cfRule type="expression" dxfId="32" priority="34">
+    <cfRule type="expression" dxfId="34" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H83">
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="33" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y83:Z83">
-    <cfRule type="expression" dxfId="30" priority="32">
+    <cfRule type="expression" dxfId="32" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J83">
-    <cfRule type="expression" dxfId="29" priority="31">
+    <cfRule type="expression" dxfId="31" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I83:J83">
-    <cfRule type="expression" dxfId="28" priority="30">
+    <cfRule type="expression" dxfId="30" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K83:L83">
-    <cfRule type="expression" dxfId="27" priority="29">
+    <cfRule type="expression" dxfId="29" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R83:T83">
-    <cfRule type="expression" dxfId="26" priority="28">
+    <cfRule type="expression" dxfId="28" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F67:F68">
-    <cfRule type="expression" dxfId="25" priority="25">
+    <cfRule type="expression" dxfId="27" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A67:E67 A68">
-    <cfRule type="expression" dxfId="24" priority="24">
+    <cfRule type="expression" dxfId="26" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:E68">
-    <cfRule type="expression" dxfId="23" priority="23">
+    <cfRule type="expression" dxfId="25" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:E9">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="24" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12 D12:E12">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="22" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y12:Z12 G12:O12">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V12:W12">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="20" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="19" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R12">
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="18" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U12">
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="17" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
-    <cfRule type="expression" dxfId="14" priority="17">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:O12">
-    <cfRule type="expression" dxfId="13" priority="16">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U12">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q12">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12:Q12">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P54:Q54">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W54 R54 G54:O54 Y54:Z54 U54">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V54">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q54">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T4:T76">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:T76">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17180,11 +17429,11 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>86620</v>
       </c>
       <c r="H4" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>1.7323999999999999</v>
       </c>
       <c r="I4" s="152">
@@ -17232,12 +17481,12 @@
         <v>3.5</v>
       </c>
       <c r="G5" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>190895</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>308040</v>
       </c>
       <c r="H5" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.63631666666666664</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.0267999999999999</v>
       </c>
       <c r="I5" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17257,11 +17506,11 @@
       </c>
       <c r="M5" s="71">
         <f t="shared" si="0"/>
-        <v>190895</v>
+        <v>308040</v>
       </c>
       <c r="N5" s="165">
         <f t="shared" si="0"/>
-        <v>0.63631666666666664</v>
+        <v>1.0267999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -17284,12 +17533,12 @@
         <v>1</v>
       </c>
       <c r="G6" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>71537</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>128337</v>
       </c>
       <c r="H6" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.71536999999999995</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.2833699999999999</v>
       </c>
       <c r="I6" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17309,11 +17558,11 @@
       </c>
       <c r="M6" s="71">
         <f t="shared" si="0"/>
-        <v>71537</v>
+        <v>128337</v>
       </c>
       <c r="N6" s="165">
         <f t="shared" si="0"/>
-        <v>0.71536999999999995</v>
+        <v>1.2833699999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -17336,12 +17585,12 @@
         <v>3</v>
       </c>
       <c r="G7" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-324610</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-200210</v>
       </c>
       <c r="H7" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-1.0820333333333332</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.66736666666666666</v>
       </c>
       <c r="I7" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17361,11 +17610,11 @@
       </c>
       <c r="M7" s="71">
         <f t="shared" si="0"/>
-        <v>-324610</v>
+        <v>-200210</v>
       </c>
       <c r="N7" s="165">
         <f t="shared" si="0"/>
-        <v>-1.0820333333333332</v>
+        <v>-0.66736666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -17388,12 +17637,12 @@
         <v>1.5</v>
       </c>
       <c r="G8" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>119340</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>150730</v>
       </c>
       <c r="H8" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.79559999999999997</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.0048666666666668</v>
       </c>
       <c r="I8" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17413,11 +17662,11 @@
       </c>
       <c r="M8" s="71">
         <f t="shared" si="0"/>
-        <v>119340</v>
+        <v>150730</v>
       </c>
       <c r="N8" s="165">
         <f t="shared" si="0"/>
-        <v>0.79559999999999997</v>
+        <v>1.0048666666666668</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -17440,12 +17689,12 @@
         <v>0.6</v>
       </c>
       <c r="G9" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>67214</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>78214</v>
       </c>
       <c r="H9" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>1.1202333333333334</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.3035666666666668</v>
       </c>
       <c r="I9" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17465,11 +17714,11 @@
       </c>
       <c r="M9" s="71">
         <f t="shared" si="0"/>
-        <v>67214</v>
+        <v>78214</v>
       </c>
       <c r="N9" s="165">
         <f t="shared" si="0"/>
-        <v>1.1202333333333334</v>
+        <v>1.3035666666666668</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -17492,12 +17741,12 @@
         <v>15</v>
       </c>
       <c r="G10" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-156520</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-152120</v>
       </c>
       <c r="H10" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.10434666666666666</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.10141333333333334</v>
       </c>
       <c r="I10" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17517,11 +17766,11 @@
       </c>
       <c r="M10" s="71">
         <f t="shared" si="0"/>
-        <v>-156520</v>
+        <v>-152120</v>
       </c>
       <c r="N10" s="165">
         <f t="shared" si="0"/>
-        <v>-0.10434666666666666</v>
+        <v>-0.10141333333333334</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -17544,11 +17793,11 @@
         <v>6</v>
       </c>
       <c r="G11" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>226131</v>
       </c>
       <c r="H11" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0.37688500000000003</v>
       </c>
       <c r="I11" s="152">
@@ -17596,12 +17845,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-4891</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-1291</v>
       </c>
       <c r="H12" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-4.8910000000000002E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-1.291E-2</v>
       </c>
       <c r="I12" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17621,11 +17870,11 @@
       </c>
       <c r="M12" s="71">
         <f t="shared" si="0"/>
-        <v>-4891</v>
+        <v>-1291</v>
       </c>
       <c r="N12" s="165">
         <f t="shared" si="0"/>
-        <v>-4.8910000000000002E-2</v>
+        <v>-1.291E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -17648,12 +17897,12 @@
         <v>1</v>
       </c>
       <c r="G13" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>91053</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>116153</v>
       </c>
       <c r="H13" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.36421199999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.46461200000000002</v>
       </c>
       <c r="I13" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17673,11 +17922,11 @@
       </c>
       <c r="M13" s="71">
         <f t="shared" si="0"/>
-        <v>91053</v>
+        <v>116153</v>
       </c>
       <c r="N13" s="165">
         <f t="shared" si="0"/>
-        <v>0.36421199999999998</v>
+        <v>0.46461200000000002</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -17700,11 +17949,11 @@
         <v>1</v>
       </c>
       <c r="G14" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H14" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I14" s="152">
@@ -17752,12 +18001,12 @@
         <v>1</v>
       </c>
       <c r="G15" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-15918</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>4082</v>
       </c>
       <c r="H15" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.15917999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>4.0820000000000002E-2</v>
       </c>
       <c r="I15" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17777,11 +18026,11 @@
       </c>
       <c r="M15" s="71">
         <f t="shared" si="0"/>
-        <v>-15918</v>
+        <v>4082</v>
       </c>
       <c r="N15" s="165">
         <f t="shared" si="0"/>
-        <v>-0.15917999999999999</v>
+        <v>4.0820000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -17804,12 +18053,12 @@
         <v>0.2</v>
       </c>
       <c r="G16" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>108803</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>131533</v>
       </c>
       <c r="H16" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.49455909090909089</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.59787727272727265</v>
       </c>
       <c r="I16" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17829,11 +18078,11 @@
       </c>
       <c r="M16" s="71">
         <f t="shared" si="0"/>
-        <v>108803</v>
+        <v>131533</v>
       </c>
       <c r="N16" s="165">
         <f t="shared" si="0"/>
-        <v>0.49455909090909089</v>
+        <v>0.59787727272727265</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -17856,12 +18105,12 @@
         <v>2.5</v>
       </c>
       <c r="G17" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-38551</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-81631</v>
       </c>
       <c r="H17" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.15420400000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.32652399999999998</v>
       </c>
       <c r="I17" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17881,11 +18130,11 @@
       </c>
       <c r="M17" s="71">
         <f t="shared" si="0"/>
-        <v>-38551</v>
+        <v>-81631</v>
       </c>
       <c r="N17" s="165">
         <f t="shared" si="0"/>
-        <v>-0.15420400000000001</v>
+        <v>-0.32652399999999998</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -17908,12 +18157,12 @@
         <v>4</v>
       </c>
       <c r="G18" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-34123</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>477</v>
       </c>
       <c r="H18" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-8.5307499999999994E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.1925E-3</v>
       </c>
       <c r="I18" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -17933,11 +18182,11 @@
       </c>
       <c r="M18" s="71">
         <f t="shared" si="0"/>
-        <v>-34123</v>
+        <v>477</v>
       </c>
       <c r="N18" s="165">
         <f t="shared" si="0"/>
-        <v>-8.5307499999999994E-2</v>
+        <v>1.1925E-3</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -17960,11 +18209,11 @@
         <v>0.25</v>
       </c>
       <c r="G19" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>-150688</v>
       </c>
       <c r="H19" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>-1.3698909090909093</v>
       </c>
       <c r="I19" s="152">
@@ -18012,12 +18261,12 @@
         <v>0.25</v>
       </c>
       <c r="G20" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-85642</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-96535</v>
       </c>
       <c r="H20" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-3.4256799999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-3.8614000000000002</v>
       </c>
       <c r="I20" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18037,11 +18286,11 @@
       </c>
       <c r="M20" s="71">
         <f t="shared" si="0"/>
-        <v>-85642</v>
+        <v>-96535</v>
       </c>
       <c r="N20" s="165">
         <f t="shared" si="0"/>
-        <v>-3.4256799999999998</v>
+        <v>-3.8614000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -18064,11 +18313,11 @@
         <v>2</v>
       </c>
       <c r="G21" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H21" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I21" s="152">
@@ -18116,12 +18365,12 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>90715</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>227515</v>
       </c>
       <c r="H22" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.60476666666666656</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.5167666666666666</v>
       </c>
       <c r="I22" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18141,11 +18390,11 @@
       </c>
       <c r="M22" s="71">
         <f t="shared" si="0"/>
-        <v>90715</v>
+        <v>227515</v>
       </c>
       <c r="N22" s="165">
         <f t="shared" si="0"/>
-        <v>0.60476666666666656</v>
+        <v>1.5167666666666666</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -18168,11 +18417,11 @@
         <v>1</v>
       </c>
       <c r="G23" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H23" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I23" s="152">
@@ -18220,12 +18469,12 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G24" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>26700</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>27261</v>
       </c>
       <c r="H24" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.24272727272727271</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.2478272727272727</v>
       </c>
       <c r="I24" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18245,11 +18494,11 @@
       </c>
       <c r="M24" s="71">
         <f t="shared" si="0"/>
-        <v>26700</v>
+        <v>27261</v>
       </c>
       <c r="N24" s="165">
         <f t="shared" si="0"/>
-        <v>0.24272727272727271</v>
+        <v>0.2478272727272727</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -18272,12 +18521,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G25" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-443600</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-203900</v>
       </c>
       <c r="H25" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-1.9286956521739134</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.88652173913043497</v>
       </c>
       <c r="I25" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18297,11 +18546,11 @@
       </c>
       <c r="M25" s="71">
         <f t="shared" si="0"/>
-        <v>-443600</v>
+        <v>-203900</v>
       </c>
       <c r="N25" s="165">
         <f t="shared" si="0"/>
-        <v>-1.9286956521739134</v>
+        <v>-0.88652173913043497</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -18322,12 +18571,12 @@
         <v>0.2</v>
       </c>
       <c r="G26" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>10791</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>10591</v>
       </c>
       <c r="H26" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.53954999999999997</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.52954999999999997</v>
       </c>
       <c r="I26" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18347,11 +18596,11 @@
       </c>
       <c r="M26" s="71">
         <f t="shared" si="0"/>
-        <v>10791</v>
+        <v>10591</v>
       </c>
       <c r="N26" s="165">
         <f t="shared" si="0"/>
-        <v>0.53954999999999997</v>
+        <v>0.52954999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -18374,12 +18623,12 @@
         <v>5</v>
       </c>
       <c r="G27" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-115600</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-140600</v>
       </c>
       <c r="H27" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.23119999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.28120000000000001</v>
       </c>
       <c r="I27" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18399,11 +18648,11 @@
       </c>
       <c r="M27" s="71">
         <f t="shared" si="0"/>
-        <v>-115600</v>
+        <v>-140600</v>
       </c>
       <c r="N27" s="165">
         <f t="shared" si="0"/>
-        <v>-0.23119999999999999</v>
+        <v>-0.28120000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -18426,12 +18675,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>468515</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>484715</v>
       </c>
       <c r="H28" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.46851500000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.48471500000000001</v>
       </c>
       <c r="I28" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18451,11 +18700,11 @@
       </c>
       <c r="M28" s="71">
         <f t="shared" si="0"/>
-        <v>468515</v>
+        <v>484715</v>
       </c>
       <c r="N28" s="165">
         <f t="shared" si="0"/>
-        <v>0.46851500000000001</v>
+        <v>0.48471500000000001</v>
       </c>
       <c r="O28" s="130"/>
     </row>
@@ -18479,11 +18728,11 @@
         <v>13</v>
       </c>
       <c r="G29" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H29" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I29" s="152">
@@ -18531,11 +18780,11 @@
         <v>1.5</v>
       </c>
       <c r="G30" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H30" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I30" s="152">
@@ -18583,11 +18832,11 @@
         <v>6</v>
       </c>
       <c r="G31" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H31" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I31" s="152">
@@ -18635,11 +18884,11 @@
         <v>1.3</v>
       </c>
       <c r="G32" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H32" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I32" s="152">
@@ -18687,11 +18936,11 @@
         <v>1.5</v>
       </c>
       <c r="G33" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H33" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I33" s="152">
@@ -18739,11 +18988,11 @@
         <v>5</v>
       </c>
       <c r="G34" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>556830</v>
       </c>
       <c r="H34" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>1.1136600000000001</v>
       </c>
       <c r="I34" s="152">
@@ -18791,12 +19040,12 @@
         <v>5</v>
       </c>
       <c r="G35" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-64150</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-24665</v>
       </c>
       <c r="H35" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.1283</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-4.9329999999999999E-2</v>
       </c>
       <c r="I35" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18816,11 +19065,11 @@
       </c>
       <c r="M35" s="71">
         <f t="shared" si="0"/>
-        <v>-64150</v>
+        <v>-24665</v>
       </c>
       <c r="N35" s="165">
         <f t="shared" si="0"/>
-        <v>-0.1283</v>
+        <v>-4.9329999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -18843,12 +19092,12 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>37899</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>56899</v>
       </c>
       <c r="H36" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.75797999999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.13798</v>
       </c>
       <c r="I36" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18868,11 +19117,11 @@
       </c>
       <c r="M36" s="71">
         <f t="shared" si="0"/>
-        <v>37899</v>
+        <v>56899</v>
       </c>
       <c r="N36" s="165">
         <f t="shared" si="0"/>
-        <v>0.75797999999999999</v>
+        <v>1.13798</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -18895,12 +19144,12 @@
         <v>0.4</v>
       </c>
       <c r="G37" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>115168</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>132663</v>
       </c>
       <c r="H37" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>2.8792</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>3.3165749999999998</v>
       </c>
       <c r="I37" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18920,11 +19169,11 @@
       </c>
       <c r="M37" s="71">
         <f t="shared" si="0"/>
-        <v>115168</v>
+        <v>132663</v>
       </c>
       <c r="N37" s="165">
         <f t="shared" si="0"/>
-        <v>2.8792</v>
+        <v>3.3165749999999998</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -18947,12 +19196,12 @@
         <v>4</v>
       </c>
       <c r="G38" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>2071</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>79531</v>
       </c>
       <c r="H38" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>5.1774999999999998E-3</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.19882749999999999</v>
       </c>
       <c r="I38" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -18972,11 +19221,11 @@
       </c>
       <c r="M38" s="71">
         <f t="shared" si="0"/>
-        <v>2071</v>
+        <v>79531</v>
       </c>
       <c r="N38" s="165">
         <f t="shared" si="0"/>
-        <v>5.1774999999999998E-3</v>
+        <v>0.19882749999999999</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -18999,12 +19248,12 @@
         <v>1</v>
       </c>
       <c r="G39" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-97726</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-40812</v>
       </c>
       <c r="H39" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.97726000000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.40811999999999998</v>
       </c>
       <c r="I39" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19024,11 +19273,11 @@
       </c>
       <c r="M39" s="71">
         <f t="shared" si="0"/>
-        <v>-97726</v>
+        <v>-40812</v>
       </c>
       <c r="N39" s="165">
         <f t="shared" si="0"/>
-        <v>-0.97726000000000002</v>
+        <v>-0.40811999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -19049,11 +19298,11 @@
       </c>
       <c r="F40" s="155"/>
       <c r="G40" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H40" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I40" s="152">
@@ -19101,11 +19350,11 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>14505</v>
       </c>
       <c r="H41" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0.29010000000000002</v>
       </c>
       <c r="I41" s="152">
@@ -19153,12 +19402,12 @@
         <v>1</v>
       </c>
       <c r="G42" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>175078</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>64934</v>
       </c>
       <c r="H42" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.58359333333333341</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.2164466666666667</v>
       </c>
       <c r="I42" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19178,11 +19427,11 @@
       </c>
       <c r="M42" s="71">
         <f t="shared" si="0"/>
-        <v>175078</v>
+        <v>64934</v>
       </c>
       <c r="N42" s="165">
         <f t="shared" si="0"/>
-        <v>0.58359333333333341</v>
+        <v>0.2164466666666667</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -19205,11 +19454,11 @@
         <v>3</v>
       </c>
       <c r="G43" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H43" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I43" s="152">
@@ -19255,12 +19504,12 @@
         <v>0.1</v>
       </c>
       <c r="G44" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>65368</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>84827</v>
       </c>
       <c r="H44" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>6.5368000000000004</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>8.4826999999999995</v>
       </c>
       <c r="I44" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19280,11 +19529,11 @@
       </c>
       <c r="M44" s="71">
         <f t="shared" si="0"/>
-        <v>65368</v>
+        <v>84827</v>
       </c>
       <c r="N44" s="165">
         <f t="shared" si="0"/>
-        <v>6.5368000000000004</v>
+        <v>8.4826999999999995</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -19307,12 +19556,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>30200</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>42200</v>
       </c>
       <c r="H45" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.60399999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.84399999999999997</v>
       </c>
       <c r="I45" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19332,11 +19581,11 @@
       </c>
       <c r="M45" s="71">
         <f t="shared" si="0"/>
-        <v>30200</v>
+        <v>42200</v>
       </c>
       <c r="N45" s="165">
         <f t="shared" si="0"/>
-        <v>0.60399999999999998</v>
+        <v>0.84399999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -19359,12 +19608,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-655229</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-707729</v>
       </c>
       <c r="H46" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-6.5522900000000002</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-7.0772899999999996</v>
       </c>
       <c r="I46" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19384,11 +19633,11 @@
       </c>
       <c r="M46" s="71">
         <f t="shared" si="0"/>
-        <v>-655229</v>
+        <v>-707729</v>
       </c>
       <c r="N46" s="165">
         <f t="shared" si="0"/>
-        <v>-6.5522900000000002</v>
+        <v>-7.0772899999999996</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -19409,12 +19658,12 @@
         <v>0.1</v>
       </c>
       <c r="G47" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>765</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>4282</v>
       </c>
       <c r="H47" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>7.6499999999999999E-2</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.42820000000000003</v>
       </c>
       <c r="I47" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19434,11 +19683,11 @@
       </c>
       <c r="M47" s="71">
         <f t="shared" si="0"/>
-        <v>765</v>
+        <v>4282</v>
       </c>
       <c r="N47" s="165">
         <f t="shared" si="0"/>
-        <v>7.6499999999999999E-2</v>
+        <v>0.42820000000000003</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -19461,12 +19710,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>323128</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>425136</v>
       </c>
       <c r="H48" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>1.0770933333333332</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.4171199999999999</v>
       </c>
       <c r="I48" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19486,11 +19735,11 @@
       </c>
       <c r="M48" s="71">
         <f t="shared" si="0"/>
-        <v>323128</v>
+        <v>425136</v>
       </c>
       <c r="N48" s="165">
         <f t="shared" si="0"/>
-        <v>1.0770933333333332</v>
+        <v>1.4171199999999999</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -19507,11 +19756,11 @@
         <v>1</v>
       </c>
       <c r="G49" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H49" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I49" s="152">
@@ -19559,11 +19808,11 @@
         <v>4</v>
       </c>
       <c r="G50" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>55020</v>
       </c>
       <c r="H50" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0.13755000000000001</v>
       </c>
       <c r="I50" s="152">
@@ -19611,12 +19860,12 @@
         <v>4</v>
       </c>
       <c r="G51" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>40600</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>39400</v>
       </c>
       <c r="H51" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.10150000000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>9.8500000000000004E-2</v>
       </c>
       <c r="I51" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19636,11 +19885,11 @@
       </c>
       <c r="M51" s="71">
         <f t="shared" si="0"/>
-        <v>40600</v>
+        <v>39400</v>
       </c>
       <c r="N51" s="165">
         <f t="shared" si="0"/>
-        <v>0.10150000000000001</v>
+        <v>9.8500000000000004E-2</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -19661,12 +19910,12 @@
         <v>0.1</v>
       </c>
       <c r="G52" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-254750</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-325150</v>
       </c>
       <c r="H52" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>-0.25474999999999998</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>-0.32514999999999999</v>
       </c>
       <c r="I52" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19686,11 +19935,11 @@
       </c>
       <c r="M52" s="71">
         <f t="shared" si="0"/>
-        <v>-254750</v>
+        <v>-325150</v>
       </c>
       <c r="N52" s="165">
         <f t="shared" si="0"/>
-        <v>-0.25474999999999998</v>
+        <v>-0.32514999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -19707,11 +19956,11 @@
       </c>
       <c r="F53" s="114"/>
       <c r="G53" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H53" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I53" s="152">
@@ -19759,11 +20008,11 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>40285</v>
       </c>
       <c r="H54" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0.80569999999999997</v>
       </c>
       <c r="I54" s="152">
@@ -19811,11 +20060,11 @@
         <v>5</v>
       </c>
       <c r="G55" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>359896</v>
       </c>
       <c r="H55" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0.55368615384615383</v>
       </c>
       <c r="I55" s="152">
@@ -19863,11 +20112,11 @@
         <v>1</v>
       </c>
       <c r="G56" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H56" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I56" s="152">
@@ -19915,12 +20164,12 @@
         <v>2.5</v>
       </c>
       <c r="G57" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>152220</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>158187</v>
       </c>
       <c r="H57" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.50739999999999996</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.52729000000000004</v>
       </c>
       <c r="I57" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -19940,11 +20189,11 @@
       </c>
       <c r="M57" s="71">
         <f t="shared" si="0"/>
-        <v>152220</v>
+        <v>158187</v>
       </c>
       <c r="N57" s="165">
         <f t="shared" si="0"/>
-        <v>0.50739999999999996</v>
+        <v>0.52729000000000004</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -19967,11 +20216,11 @@
         <v>1.5</v>
       </c>
       <c r="G58" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H58" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I58" s="152">
@@ -20019,11 +20268,11 @@
         <v>0.25</v>
       </c>
       <c r="G59" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="H59" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I59" s="152">
@@ -20071,12 +20320,12 @@
         <v>5</v>
       </c>
       <c r="G60" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>127856</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>122041</v>
       </c>
       <c r="H60" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>0.25571199999999999</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>0.24408199999999999</v>
       </c>
       <c r="I60" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -20096,11 +20345,11 @@
       </c>
       <c r="M60" s="71">
         <f t="shared" si="1"/>
-        <v>127856</v>
+        <v>122041</v>
       </c>
       <c r="N60" s="165">
         <f t="shared" si="1"/>
-        <v>0.25571199999999999</v>
+        <v>0.24408199999999999</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -20112,7 +20361,7 @@
       <c r="F61" s="233"/>
       <c r="G61" s="230">
         <f>SUM(G4:G58)</f>
-        <v>1085349</v>
+        <v>1969663</v>
       </c>
       <c r="H61" s="90"/>
       <c r="I61" s="99">
@@ -20127,7 +20376,7 @@
       <c r="L61" s="109"/>
       <c r="M61" s="153">
         <f>SUM(M4:M58)</f>
-        <v>1085349</v>
+        <v>1969663</v>
       </c>
       <c r="N61" s="234"/>
     </row>
@@ -20191,12 +20440,12 @@
       <c r="E65" s="208"/>
       <c r="F65" s="206"/>
       <c r="G65" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>300126</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>302403</v>
       </c>
       <c r="H65" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>1.0004200000000001</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>1.0080100000000001</v>
       </c>
       <c r="I65" s="152">
         <f>IFERROR(VLOOKUP($A$3:$A$122,'[1]NOV-2026'!$A$4:$ADL$124,MATCH('FY-(26-27)Q3'!$I$2:$J$2,'[1]NOV-2026'!$A$2:$DM$2,0),0),0)</f>
@@ -20216,11 +20465,11 @@
       </c>
       <c r="M65" s="152">
         <f t="shared" ref="M65:N66" si="2">G65+I65+K65</f>
-        <v>300126</v>
+        <v>302403</v>
       </c>
       <c r="N65" s="166">
         <f t="shared" si="2"/>
-        <v>1.0004200000000001</v>
+        <v>1.0080100000000001</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -20241,11 +20490,11 @@
       </c>
       <c r="F66" s="237"/>
       <c r="G66" s="152">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
-        <v>98000</v>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
+        <v>86700</v>
       </c>
       <c r="H66" s="154">
-        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACW$116,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CX$2,0),0),0)</f>
+        <f>IFERROR(VLOOKUP($A$3:$A$122,'OCT-2026'!$A$4:$ACX$117,MATCH('FY-(26-27)Q3'!$G$2:$H$2,'OCT-2026'!$A$2:$CY$2,0),0),0)</f>
         <v>0</v>
       </c>
       <c r="I66" s="152">
@@ -20266,7 +20515,7 @@
       </c>
       <c r="M66" s="152">
         <f t="shared" si="2"/>
-        <v>98000</v>
+        <v>86700</v>
       </c>
       <c r="N66" s="166">
         <f t="shared" si="2"/>
@@ -20276,7 +20525,7 @@
     <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G67" s="93">
         <f>SUM(G65:G66)</f>
-        <v>398126</v>
+        <v>389103</v>
       </c>
       <c r="H67" s="94"/>
       <c r="I67" s="93">
@@ -20291,483 +20540,483 @@
       <c r="L67" s="113"/>
       <c r="M67" s="93">
         <f>SUM(M65:M66)</f>
-        <v>398126</v>
+        <v>389103</v>
       </c>
       <c r="N67" s="235"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A42:C42 A10:C10 A3:F3 L2:L3 A38:C38 A5 A31:F31 F10 F39:F40 F42 A57:C57 A58:E58 A33:F35 E38:F38 A46:F46 A22 A37:F37 A51:F51 F55:F58 E57 G61:N62 A24:F25 M24:N25 A61:E61 C49:F49 M22:N22 A27:F28 A48:F48 F52:F53 A13:F15 M13:N15 M54:N59 M27:N39 M10:N11 C5:F5 M50:N52 A17:F18 M17:N19 M65:N66 G67:N67 M5:N8 A6:F6 M41:N48 G4:L60">
-    <cfRule type="expression" dxfId="545" priority="102">
+    <cfRule type="expression" dxfId="547" priority="102">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="544" priority="101">
+    <cfRule type="expression" dxfId="546" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="543" priority="100">
+    <cfRule type="expression" dxfId="545" priority="100">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="542" priority="99">
+    <cfRule type="expression" dxfId="544" priority="99">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:C39 E39 A40">
-    <cfRule type="expression" dxfId="541" priority="98">
+    <cfRule type="expression" dxfId="543" priority="98">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="expression" dxfId="540" priority="97">
+    <cfRule type="expression" dxfId="542" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:F19">
-    <cfRule type="expression" dxfId="539" priority="96">
+    <cfRule type="expression" dxfId="541" priority="96">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="538" priority="92">
+    <cfRule type="expression" dxfId="540" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:C11 E11:F11">
-    <cfRule type="expression" dxfId="537" priority="94">
+    <cfRule type="expression" dxfId="539" priority="94">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="536" priority="93">
+    <cfRule type="expression" dxfId="538" priority="93">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:N11">
-    <cfRule type="expression" dxfId="535" priority="90">
+    <cfRule type="expression" dxfId="537" priority="90">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:C22 E22:F22">
-    <cfRule type="expression" dxfId="534" priority="89">
+    <cfRule type="expression" dxfId="536" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11">
-    <cfRule type="expression" dxfId="533" priority="91">
+    <cfRule type="expression" dxfId="535" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:C7 E7:F7 A8:F8 A9:B9 D9:F9">
-    <cfRule type="expression" dxfId="532" priority="88">
+    <cfRule type="expression" dxfId="534" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7:N8">
-    <cfRule type="expression" dxfId="531" priority="87">
+    <cfRule type="expression" dxfId="533" priority="87">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:N8">
-    <cfRule type="expression" dxfId="530" priority="86">
+    <cfRule type="expression" dxfId="532" priority="86">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:C36 E36:F36">
-    <cfRule type="expression" dxfId="529" priority="85">
+    <cfRule type="expression" dxfId="531" priority="85">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M36:N36">
-    <cfRule type="expression" dxfId="528" priority="83">
+    <cfRule type="expression" dxfId="530" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N36">
-    <cfRule type="expression" dxfId="527" priority="84">
+    <cfRule type="expression" dxfId="529" priority="84">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45:C45 E45:F45">
-    <cfRule type="expression" dxfId="526" priority="82">
+    <cfRule type="expression" dxfId="528" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="expression" dxfId="525" priority="81">
+    <cfRule type="expression" dxfId="527" priority="81">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M22:N22">
-    <cfRule type="expression" dxfId="524" priority="80">
+    <cfRule type="expression" dxfId="526" priority="80">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:C54 E54:F54">
-    <cfRule type="expression" dxfId="523" priority="79">
+    <cfRule type="expression" dxfId="525" priority="79">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63:L64">
-    <cfRule type="expression" dxfId="522" priority="78">
+    <cfRule type="expression" dxfId="524" priority="78">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63:I64">
-    <cfRule type="expression" dxfId="521" priority="77">
+    <cfRule type="expression" dxfId="523" priority="77">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J63:J64">
-    <cfRule type="expression" dxfId="520" priority="76">
+    <cfRule type="expression" dxfId="522" priority="76">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:K64">
-    <cfRule type="expression" dxfId="519" priority="75">
+    <cfRule type="expression" dxfId="521" priority="75">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:F29">
-    <cfRule type="expression" dxfId="518" priority="74">
+    <cfRule type="expression" dxfId="520" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="517" priority="73">
+    <cfRule type="expression" dxfId="519" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:F32">
-    <cfRule type="expression" dxfId="516" priority="72">
+    <cfRule type="expression" dxfId="518" priority="72">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="515" priority="71">
+    <cfRule type="expression" dxfId="517" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:C56 E55:E56">
-    <cfRule type="expression" dxfId="514" priority="70">
+    <cfRule type="expression" dxfId="516" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55:N56">
-    <cfRule type="expression" dxfId="513" priority="69">
+    <cfRule type="expression" dxfId="515" priority="69">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:C43 E43:F43">
-    <cfRule type="expression" dxfId="512" priority="68">
+    <cfRule type="expression" dxfId="514" priority="68">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:B50">
-    <cfRule type="expression" dxfId="511" priority="67">
+    <cfRule type="expression" dxfId="513" priority="67">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="510" priority="66">
+    <cfRule type="expression" dxfId="512" priority="66">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="509" priority="65">
+    <cfRule type="expression" dxfId="511" priority="65">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="508" priority="63">
+    <cfRule type="expression" dxfId="510" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="507" priority="64">
+    <cfRule type="expression" dxfId="509" priority="64">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41:C41 E41:F41">
-    <cfRule type="expression" dxfId="506" priority="62">
+    <cfRule type="expression" dxfId="508" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65:F65 F66">
-    <cfRule type="expression" dxfId="505" priority="61">
+    <cfRule type="expression" dxfId="507" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:F12">
-    <cfRule type="expression" dxfId="504" priority="60">
+    <cfRule type="expression" dxfId="506" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="503" priority="59">
+    <cfRule type="expression" dxfId="505" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="502" priority="57">
+    <cfRule type="expression" dxfId="504" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="501" priority="58">
+    <cfRule type="expression" dxfId="503" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="expression" dxfId="500" priority="56">
+    <cfRule type="expression" dxfId="502" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:E50">
-    <cfRule type="expression" dxfId="499" priority="55">
+    <cfRule type="expression" dxfId="501" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="498" priority="54">
+    <cfRule type="expression" dxfId="500" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="497" priority="53">
+    <cfRule type="expression" dxfId="499" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11">
-    <cfRule type="expression" dxfId="496" priority="52">
+    <cfRule type="expression" dxfId="498" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D22">
-    <cfRule type="expression" dxfId="495" priority="51">
+    <cfRule type="expression" dxfId="497" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D56">
-    <cfRule type="expression" dxfId="494" priority="41">
+    <cfRule type="expression" dxfId="496" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36">
-    <cfRule type="expression" dxfId="493" priority="50">
+    <cfRule type="expression" dxfId="495" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39 D41">
-    <cfRule type="expression" dxfId="492" priority="49">
+    <cfRule type="expression" dxfId="494" priority="49">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D38">
-    <cfRule type="expression" dxfId="491" priority="48">
+    <cfRule type="expression" dxfId="493" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42">
-    <cfRule type="expression" dxfId="490" priority="47">
+    <cfRule type="expression" dxfId="492" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43">
-    <cfRule type="expression" dxfId="489" priority="46">
+    <cfRule type="expression" dxfId="491" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="488" priority="44">
+    <cfRule type="expression" dxfId="490" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D57">
-    <cfRule type="expression" dxfId="487" priority="43">
+    <cfRule type="expression" dxfId="489" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54">
-    <cfRule type="expression" dxfId="486" priority="42">
+    <cfRule type="expression" dxfId="488" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:F23">
-    <cfRule type="expression" dxfId="485" priority="40">
+    <cfRule type="expression" dxfId="487" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="484" priority="39">
+    <cfRule type="expression" dxfId="486" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="483" priority="38">
+    <cfRule type="expression" dxfId="485" priority="38">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="482" priority="37">
+    <cfRule type="expression" dxfId="484" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:C60 E60:F60">
-    <cfRule type="expression" dxfId="481" priority="36">
+    <cfRule type="expression" dxfId="483" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60:N60">
-    <cfRule type="expression" dxfId="480" priority="35">
+    <cfRule type="expression" dxfId="482" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:B49">
-    <cfRule type="expression" dxfId="479" priority="34">
+    <cfRule type="expression" dxfId="481" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49:N49">
-    <cfRule type="expression" dxfId="478" priority="33">
+    <cfRule type="expression" dxfId="480" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:F44">
-    <cfRule type="expression" dxfId="477" priority="30">
+    <cfRule type="expression" dxfId="479" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:F16">
-    <cfRule type="expression" dxfId="476" priority="29">
+    <cfRule type="expression" dxfId="478" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16:N16">
-    <cfRule type="expression" dxfId="475" priority="28">
+    <cfRule type="expression" dxfId="477" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:F21 C20:F20">
-    <cfRule type="expression" dxfId="474" priority="27">
+    <cfRule type="expression" dxfId="476" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:N21">
-    <cfRule type="expression" dxfId="473" priority="26">
+    <cfRule type="expression" dxfId="475" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M26:N26">
-    <cfRule type="expression" dxfId="472" priority="22">
+    <cfRule type="expression" dxfId="474" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:F26">
-    <cfRule type="expression" dxfId="471" priority="25">
+    <cfRule type="expression" dxfId="473" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:F47">
-    <cfRule type="expression" dxfId="470" priority="24">
+    <cfRule type="expression" dxfId="472" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C59 E59:F59">
-    <cfRule type="expression" dxfId="469" priority="23">
+    <cfRule type="expression" dxfId="471" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66:E66">
-    <cfRule type="expression" dxfId="468" priority="21">
+    <cfRule type="expression" dxfId="470" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:E52 A53">
-    <cfRule type="expression" dxfId="467" priority="20">
+    <cfRule type="expression" dxfId="469" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53:E53">
-    <cfRule type="expression" dxfId="466" priority="17">
+    <cfRule type="expression" dxfId="468" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="465" priority="16">
+    <cfRule type="expression" dxfId="467" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="464" priority="15">
+    <cfRule type="expression" dxfId="466" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N9">
-    <cfRule type="expression" dxfId="463" priority="14">
+    <cfRule type="expression" dxfId="465" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9">
-    <cfRule type="expression" dxfId="462" priority="13">
+    <cfRule type="expression" dxfId="464" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N9">
-    <cfRule type="expression" dxfId="461" priority="12">
+    <cfRule type="expression" dxfId="463" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
-    <cfRule type="expression" dxfId="460" priority="11">
+    <cfRule type="expression" dxfId="462" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="expression" dxfId="459" priority="10">
+    <cfRule type="expression" dxfId="461" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E40">
-    <cfRule type="expression" dxfId="458" priority="9">
+    <cfRule type="expression" dxfId="460" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M40:N40">
-    <cfRule type="expression" dxfId="457" priority="8">
+    <cfRule type="expression" dxfId="459" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="expression" dxfId="456" priority="7">
+    <cfRule type="expression" dxfId="458" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A21">
-    <cfRule type="expression" dxfId="455" priority="6">
+    <cfRule type="expression" dxfId="457" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M53:N53">
-    <cfRule type="expression" dxfId="454" priority="5">
+    <cfRule type="expression" dxfId="456" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G65:L66">
-    <cfRule type="expression" dxfId="453" priority="3">
+    <cfRule type="expression" dxfId="455" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60">
-    <cfRule type="expression" dxfId="452" priority="2">
+    <cfRule type="expression" dxfId="454" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="451" priority="1">
+    <cfRule type="expression" dxfId="453" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26330,87 +26579,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD57:AD58 AC56:AD56 AD61 AC43:AD43 AC5:AD10 AC24:AD25 H2:AD3 A59:AD60 A37:AC37 AD11:AD21 AC11:AC22 AC45:AD53 AC27:AC36 AD27:AD35 A4:AB36 AC38:AC41 A38:AB39 G40:AB40 A41:AB57 A61:AB61">
-    <cfRule type="expression" dxfId="450" priority="21">
+    <cfRule type="expression" dxfId="452" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD36">
-    <cfRule type="expression" dxfId="449" priority="20">
+    <cfRule type="expression" dxfId="451" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD39:AD40">
-    <cfRule type="expression" dxfId="448" priority="19">
+    <cfRule type="expression" dxfId="450" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="447" priority="18">
+    <cfRule type="expression" dxfId="449" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD38">
-    <cfRule type="expression" dxfId="446" priority="17">
+    <cfRule type="expression" dxfId="448" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD22">
-    <cfRule type="expression" dxfId="445" priority="14">
+    <cfRule type="expression" dxfId="447" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC57">
-    <cfRule type="expression" dxfId="444" priority="13">
+    <cfRule type="expression" dxfId="446" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="443" priority="12">
+    <cfRule type="expression" dxfId="445" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC26:AD26">
-    <cfRule type="expression" dxfId="442" priority="11">
+    <cfRule type="expression" dxfId="444" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC54:AD55">
-    <cfRule type="expression" dxfId="441" priority="10">
+    <cfRule type="expression" dxfId="443" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC44:AD44">
-    <cfRule type="expression" dxfId="440" priority="9">
+    <cfRule type="expression" dxfId="442" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC61">
-    <cfRule type="expression" dxfId="439" priority="8">
+    <cfRule type="expression" dxfId="441" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC42:AD42">
-    <cfRule type="expression" dxfId="438" priority="6">
+    <cfRule type="expression" dxfId="440" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC23">
-    <cfRule type="expression" dxfId="437" priority="5">
+    <cfRule type="expression" dxfId="439" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD23">
-    <cfRule type="expression" dxfId="436" priority="4">
+    <cfRule type="expression" dxfId="438" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD37">
-    <cfRule type="expression" dxfId="435" priority="2">
+    <cfRule type="expression" dxfId="437" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="434" priority="1">
+    <cfRule type="expression" dxfId="436" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32879,112 +33128,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AD47:AD48 AD55:AD57 AD68:AD69 AD50 AD11:AD19 AD21:AD23 AC11:AC24 AC29:AC43 AD29:AD42 AC66:AD67 AC54:AC57 AD73 H2:AD3 A68:G68 AC52:AD52 AC5:AD10 AC58:AD64 AC26:AD27 A70:AD72 A4:AB22 A44:S44 A45:AC50 A73:AB73 A26:AB43 B23:AB25 A52:AB67 B51:AB51">
-    <cfRule type="expression" dxfId="433" priority="22">
+    <cfRule type="expression" dxfId="435" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD43">
-    <cfRule type="expression" dxfId="432" priority="21">
+    <cfRule type="expression" dxfId="434" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD46">
-    <cfRule type="expression" dxfId="431" priority="20">
+    <cfRule type="expression" dxfId="433" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AD4">
-    <cfRule type="expression" dxfId="430" priority="19">
+    <cfRule type="expression" dxfId="432" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD45">
-    <cfRule type="expression" dxfId="429" priority="18">
+    <cfRule type="expression" dxfId="431" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20">
-    <cfRule type="expression" dxfId="428" priority="17">
+    <cfRule type="expression" dxfId="430" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD54">
-    <cfRule type="expression" dxfId="427" priority="16">
+    <cfRule type="expression" dxfId="429" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD24">
-    <cfRule type="expression" dxfId="426" priority="15">
+    <cfRule type="expression" dxfId="428" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC68">
-    <cfRule type="expression" dxfId="425" priority="14">
+    <cfRule type="expression" dxfId="427" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD49">
-    <cfRule type="expression" dxfId="424" priority="13">
+    <cfRule type="expression" dxfId="426" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC28:AD28">
-    <cfRule type="expression" dxfId="423" priority="12">
+    <cfRule type="expression" dxfId="425" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC65:AD65">
-    <cfRule type="expression" dxfId="422" priority="11">
+    <cfRule type="expression" dxfId="424" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC53:AD53">
-    <cfRule type="expression" dxfId="421" priority="10">
+    <cfRule type="expression" dxfId="423" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC73">
-    <cfRule type="expression" dxfId="420" priority="9">
+    <cfRule type="expression" dxfId="422" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H68:AB68">
-    <cfRule type="expression" dxfId="419" priority="8">
+    <cfRule type="expression" dxfId="421" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC51:AD51">
-    <cfRule type="expression" dxfId="418" priority="7">
+    <cfRule type="expression" dxfId="420" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC25">
-    <cfRule type="expression" dxfId="417" priority="6">
+    <cfRule type="expression" dxfId="419" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD25">
-    <cfRule type="expression" dxfId="416" priority="5">
+    <cfRule type="expression" dxfId="418" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T44:AC44">
-    <cfRule type="expression" dxfId="415" priority="4">
+    <cfRule type="expression" dxfId="417" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD44">
-    <cfRule type="expression" dxfId="414" priority="3">
+    <cfRule type="expression" dxfId="416" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23:A25">
-    <cfRule type="expression" dxfId="413" priority="2">
+    <cfRule type="expression" dxfId="415" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="expression" dxfId="412" priority="1">
+    <cfRule type="expression" dxfId="414" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39284,82 +39533,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A3:G3 AF43:AF44 AF50:AF52 AF62:AF63 H2:AF3 AF46:AF47 AF9:AF17 AF23:AF24 AF19:AF21 AE9:AE24 AE5:AF8 AE26:AE47 AF26:AF39 AE60:AF61 AE49:AE52 A64:AF66 AF67 A67:AD67 AE53:AF58 A4:AD20 A23:AD62 C21:AD21 B22:AD22">
-    <cfRule type="expression" dxfId="411" priority="20">
+    <cfRule type="expression" dxfId="413" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF40">
-    <cfRule type="expression" dxfId="410" priority="19">
+    <cfRule type="expression" dxfId="412" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="409" priority="18">
+    <cfRule type="expression" dxfId="411" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE4:AF4">
-    <cfRule type="expression" dxfId="408" priority="16">
+    <cfRule type="expression" dxfId="410" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="expression" dxfId="407" priority="14">
+    <cfRule type="expression" dxfId="409" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF18">
-    <cfRule type="expression" dxfId="406" priority="13">
+    <cfRule type="expression" dxfId="408" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF49">
-    <cfRule type="expression" dxfId="405" priority="12">
+    <cfRule type="expression" dxfId="407" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF22">
-    <cfRule type="expression" dxfId="404" priority="11">
+    <cfRule type="expression" dxfId="406" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE62">
-    <cfRule type="expression" dxfId="403" priority="10">
+    <cfRule type="expression" dxfId="405" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF45">
-    <cfRule type="expression" dxfId="402" priority="9">
+    <cfRule type="expression" dxfId="404" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE25:AF25">
-    <cfRule type="expression" dxfId="401" priority="6">
+    <cfRule type="expression" dxfId="403" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE59:AF59">
-    <cfRule type="expression" dxfId="400" priority="5">
+    <cfRule type="expression" dxfId="402" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE48:AF48">
-    <cfRule type="expression" dxfId="399" priority="4">
+    <cfRule type="expression" dxfId="401" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE67">
-    <cfRule type="expression" dxfId="398" priority="3">
+    <cfRule type="expression" dxfId="400" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="397" priority="2">
+    <cfRule type="expression" dxfId="399" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="396" priority="1">
+    <cfRule type="expression" dxfId="398" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42788,497 +43037,497 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A45:C45 A11:C11 A3:F3 L2:L3 A41:C41 A5 A32:F32 F11 F42:F43 F45 A61:C61 A62:E62 A34:F36 E41:F41 A50:F50 A23 A38:F39 A55:F55 F59:F62 E61 G65:N66 A25:F26 M25:N26 A65:E65 C53:F53 M23:N23 G23:H26 A28:F29 A52:F52 G41:H42 G28:H39 F56:F57 G54:H56 A14:H16 M14:N16 M58:N63 M28:N39 M41:N42 M5:N9 G8:J9 G11:I13 M11:N12 I44:J56 M44:N52 G44:H52 G4:L4 C5:J5 M54:N56 A18:F19 G18:H20 M18:N20 I14:I42 J11:J42 I58:J64 G58:H63 K5:L64 G69:H70 M69:N70 G71:N71">
-    <cfRule type="expression" dxfId="395" priority="229">
+    <cfRule type="expression" dxfId="397" priority="229">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:I3">
-    <cfRule type="expression" dxfId="394" priority="228">
+    <cfRule type="expression" dxfId="396" priority="228">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J3">
-    <cfRule type="expression" dxfId="393" priority="227">
+    <cfRule type="expression" dxfId="395" priority="227">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="392" priority="226">
+    <cfRule type="expression" dxfId="394" priority="226">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:C42 E42 A43">
-    <cfRule type="expression" dxfId="391" priority="222">
+    <cfRule type="expression" dxfId="393" priority="222">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45">
-    <cfRule type="expression" dxfId="390" priority="220">
+    <cfRule type="expression" dxfId="392" priority="220">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:F20">
-    <cfRule type="expression" dxfId="389" priority="218">
+    <cfRule type="expression" dxfId="391" priority="218">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:C47 E47:F47">
-    <cfRule type="expression" dxfId="388" priority="212">
+    <cfRule type="expression" dxfId="390" priority="212">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M25:N25">
-    <cfRule type="expression" dxfId="387" priority="202">
+    <cfRule type="expression" dxfId="389" priority="202">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:C12 E12:F12">
-    <cfRule type="expression" dxfId="386" priority="207">
+    <cfRule type="expression" dxfId="388" priority="207">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="expression" dxfId="385" priority="203">
+    <cfRule type="expression" dxfId="387" priority="203">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M12:N12">
-    <cfRule type="expression" dxfId="384" priority="188">
+    <cfRule type="expression" dxfId="386" priority="188">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:C23 E23:F23">
-    <cfRule type="expression" dxfId="383" priority="183">
+    <cfRule type="expression" dxfId="385" priority="183">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="382" priority="189">
+    <cfRule type="expression" dxfId="384" priority="189">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8:C8 E8:F8 A9:F9 A10:B10 D10:F10">
-    <cfRule type="expression" dxfId="381" priority="174">
+    <cfRule type="expression" dxfId="383" priority="174">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="expression" dxfId="380" priority="172">
+    <cfRule type="expression" dxfId="382" priority="172">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:N9">
-    <cfRule type="expression" dxfId="379" priority="171">
+    <cfRule type="expression" dxfId="381" priority="171">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:C37 E37:F37">
-    <cfRule type="expression" dxfId="378" priority="166">
+    <cfRule type="expression" dxfId="380" priority="166">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M37:N37">
-    <cfRule type="expression" dxfId="377" priority="162">
+    <cfRule type="expression" dxfId="379" priority="162">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N37">
-    <cfRule type="expression" dxfId="376" priority="163">
+    <cfRule type="expression" dxfId="378" priority="163">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A49:C49 E49:F49">
-    <cfRule type="expression" dxfId="375" priority="157">
+    <cfRule type="expression" dxfId="377" priority="157">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="expression" dxfId="374" priority="143">
+    <cfRule type="expression" dxfId="376" priority="143">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:N23">
-    <cfRule type="expression" dxfId="373" priority="142">
+    <cfRule type="expression" dxfId="375" priority="142">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:C58 E58:F58">
-    <cfRule type="expression" dxfId="372" priority="132">
+    <cfRule type="expression" dxfId="374" priority="132">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:L68">
-    <cfRule type="expression" dxfId="371" priority="126">
+    <cfRule type="expression" dxfId="373" priority="126">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:I68">
-    <cfRule type="expression" dxfId="370" priority="125">
+    <cfRule type="expression" dxfId="372" priority="125">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67:J68">
-    <cfRule type="expression" dxfId="369" priority="124">
+    <cfRule type="expression" dxfId="371" priority="124">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K67:K68">
-    <cfRule type="expression" dxfId="368" priority="123">
+    <cfRule type="expression" dxfId="370" priority="123">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:F30">
-    <cfRule type="expression" dxfId="367" priority="122">
+    <cfRule type="expression" dxfId="369" priority="122">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31:F31">
-    <cfRule type="expression" dxfId="366" priority="121">
+    <cfRule type="expression" dxfId="368" priority="121">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33:F33">
-    <cfRule type="expression" dxfId="365" priority="120">
+    <cfRule type="expression" dxfId="367" priority="120">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="364" priority="109">
+    <cfRule type="expression" dxfId="366" priority="109">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:C60 E59:E60">
-    <cfRule type="expression" dxfId="363" priority="105">
+    <cfRule type="expression" dxfId="365" priority="105">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M59:N60">
-    <cfRule type="expression" dxfId="362" priority="104">
+    <cfRule type="expression" dxfId="364" priority="104">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:C46 E46:F46">
-    <cfRule type="expression" dxfId="361" priority="101">
+    <cfRule type="expression" dxfId="363" priority="101">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:B54">
-    <cfRule type="expression" dxfId="360" priority="97">
+    <cfRule type="expression" dxfId="362" priority="97">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:C4 E4:F4">
-    <cfRule type="expression" dxfId="359" priority="92">
+    <cfRule type="expression" dxfId="361" priority="92">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="358" priority="91">
+    <cfRule type="expression" dxfId="360" priority="91">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N4">
-    <cfRule type="expression" dxfId="357" priority="88">
+    <cfRule type="expression" dxfId="359" priority="88">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="expression" dxfId="356" priority="89">
+    <cfRule type="expression" dxfId="358" priority="89">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:C44 E44:F44">
-    <cfRule type="expression" dxfId="355" priority="83">
+    <cfRule type="expression" dxfId="357" priority="83">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A69:F69 F70">
-    <cfRule type="expression" dxfId="354" priority="82">
+    <cfRule type="expression" dxfId="356" priority="82">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13">
-    <cfRule type="expression" dxfId="353" priority="74">
+    <cfRule type="expression" dxfId="355" priority="74">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="352" priority="73">
+    <cfRule type="expression" dxfId="354" priority="73">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13:N13">
-    <cfRule type="expression" dxfId="351" priority="70">
+    <cfRule type="expression" dxfId="353" priority="70">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13">
-    <cfRule type="expression" dxfId="350" priority="71">
+    <cfRule type="expression" dxfId="352" priority="71">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="expression" dxfId="349" priority="63">
+    <cfRule type="expression" dxfId="351" priority="63">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D54:E54">
-    <cfRule type="expression" dxfId="348" priority="62">
+    <cfRule type="expression" dxfId="350" priority="62">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="347" priority="61">
+    <cfRule type="expression" dxfId="349" priority="61">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="346" priority="60">
+    <cfRule type="expression" dxfId="348" priority="60">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="345" priority="59">
+    <cfRule type="expression" dxfId="347" priority="59">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23">
-    <cfRule type="expression" dxfId="344" priority="58">
+    <cfRule type="expression" dxfId="346" priority="58">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D60">
-    <cfRule type="expression" dxfId="343" priority="47">
+    <cfRule type="expression" dxfId="345" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37">
-    <cfRule type="expression" dxfId="342" priority="57">
+    <cfRule type="expression" dxfId="344" priority="57">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42 D44">
-    <cfRule type="expression" dxfId="341" priority="56">
+    <cfRule type="expression" dxfId="343" priority="56">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="340" priority="55">
+    <cfRule type="expression" dxfId="342" priority="55">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D45">
-    <cfRule type="expression" dxfId="339" priority="54">
+    <cfRule type="expression" dxfId="341" priority="54">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="338" priority="53">
+    <cfRule type="expression" dxfId="340" priority="53">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47">
-    <cfRule type="expression" dxfId="337" priority="52">
+    <cfRule type="expression" dxfId="339" priority="52">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="336" priority="51">
+    <cfRule type="expression" dxfId="338" priority="51">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="expression" dxfId="335" priority="50">
+    <cfRule type="expression" dxfId="337" priority="50">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58">
-    <cfRule type="expression" dxfId="334" priority="48">
+    <cfRule type="expression" dxfId="336" priority="48">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:F24">
-    <cfRule type="expression" dxfId="333" priority="46">
+    <cfRule type="expression" dxfId="335" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="332" priority="45">
+    <cfRule type="expression" dxfId="334" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="expression" dxfId="331" priority="42">
+    <cfRule type="expression" dxfId="333" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:N24">
-    <cfRule type="expression" dxfId="330" priority="41">
+    <cfRule type="expression" dxfId="332" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:F64">
-    <cfRule type="expression" dxfId="329" priority="34">
+    <cfRule type="expression" dxfId="331" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64 M64:N64">
-    <cfRule type="expression" dxfId="328" priority="33">
+    <cfRule type="expression" dxfId="330" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53">
-    <cfRule type="expression" dxfId="327" priority="32">
+    <cfRule type="expression" dxfId="329" priority="32">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53:H53 M53:N53">
-    <cfRule type="expression" dxfId="326" priority="31">
+    <cfRule type="expression" dxfId="328" priority="31">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:F40">
-    <cfRule type="expression" dxfId="325" priority="30">
+    <cfRule type="expression" dxfId="327" priority="30">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 M40:N40">
-    <cfRule type="expression" dxfId="324" priority="29">
+    <cfRule type="expression" dxfId="326" priority="29">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A48:F48">
-    <cfRule type="expression" dxfId="323" priority="28">
+    <cfRule type="expression" dxfId="325" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:F17">
-    <cfRule type="expression" dxfId="322" priority="27">
+    <cfRule type="expression" dxfId="324" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:H17 M17:N17">
-    <cfRule type="expression" dxfId="321" priority="26">
+    <cfRule type="expression" dxfId="323" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:F22 C21:F21">
-    <cfRule type="expression" dxfId="320" priority="25">
+    <cfRule type="expression" dxfId="322" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:H22 M21:N22">
-    <cfRule type="expression" dxfId="319" priority="24">
+    <cfRule type="expression" dxfId="321" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H27 M27:N27">
-    <cfRule type="expression" dxfId="318" priority="20">
+    <cfRule type="expression" dxfId="320" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F27">
-    <cfRule type="expression" dxfId="317" priority="23">
+    <cfRule type="expression" dxfId="319" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
-    <cfRule type="expression" dxfId="316" priority="22">
+    <cfRule type="expression" dxfId="318" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:F63">
-    <cfRule type="expression" dxfId="315" priority="21">
+    <cfRule type="expression" dxfId="317" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:E70">
-    <cfRule type="expression" dxfId="314" priority="19">
+    <cfRule type="expression" dxfId="316" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56:E56 A57">
-    <cfRule type="expression" dxfId="313" priority="17">
+    <cfRule type="expression" dxfId="315" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:F7">
-    <cfRule type="expression" dxfId="312" priority="16">
+    <cfRule type="expression" dxfId="314" priority="16">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:J7">
-    <cfRule type="expression" dxfId="311" priority="15">
+    <cfRule type="expression" dxfId="313" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B57:E57">
-    <cfRule type="expression" dxfId="310" priority="14">
+    <cfRule type="expression" dxfId="312" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="309" priority="13">
+    <cfRule type="expression" dxfId="311" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="308" priority="12">
+    <cfRule type="expression" dxfId="310" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:J10 M10:N10">
-    <cfRule type="expression" dxfId="307" priority="11">
+    <cfRule type="expression" dxfId="309" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="expression" dxfId="306" priority="10">
+    <cfRule type="expression" dxfId="308" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10:N10">
-    <cfRule type="expression" dxfId="305" priority="9">
+    <cfRule type="expression" dxfId="307" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="304" priority="8">
+    <cfRule type="expression" dxfId="306" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="expression" dxfId="303" priority="7">
+    <cfRule type="expression" dxfId="305" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:E43">
-    <cfRule type="expression" dxfId="302" priority="6">
+    <cfRule type="expression" dxfId="304" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:J43 M43:N43">
-    <cfRule type="expression" dxfId="301" priority="5">
+    <cfRule type="expression" dxfId="303" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="300" priority="4">
+    <cfRule type="expression" dxfId="302" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A22">
-    <cfRule type="expression" dxfId="299" priority="3">
+    <cfRule type="expression" dxfId="301" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57:J57 M57:N57">
-    <cfRule type="expression" dxfId="298" priority="2">
+    <cfRule type="expression" dxfId="300" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69:L70">
-    <cfRule type="expression" dxfId="297" priority="1">
+    <cfRule type="expression" dxfId="299" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48969,42 +49218,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2 A48:A49 AE58 AD56:AE57 AE43:AE55 AD42:AD55 A3:G4 AD6:AE9 AD12:AE19 AD21:AD40 AE21:AE39 H2:AE4 A10:AE11 C48:AC49 A5:AC9 A50:AC57 A12:AC47 A59:AE63">
-    <cfRule type="expression" dxfId="296" priority="13">
+    <cfRule type="expression" dxfId="298" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE40">
-    <cfRule type="expression" dxfId="295" priority="12">
+    <cfRule type="expression" dxfId="297" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42">
-    <cfRule type="expression" dxfId="294" priority="11">
+    <cfRule type="expression" dxfId="296" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="293" priority="5">
+    <cfRule type="expression" dxfId="295" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD5:AE5">
-    <cfRule type="expression" dxfId="292" priority="4">
+    <cfRule type="expression" dxfId="294" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="expression" dxfId="291" priority="3">
+    <cfRule type="expression" dxfId="293" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="expression" dxfId="290" priority="2">
+    <cfRule type="expression" dxfId="292" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD20:AE20">
-    <cfRule type="expression" dxfId="289" priority="1">
+    <cfRule type="expression" dxfId="291" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55042,112 +55291,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G30 G14:G15 G2 A57:G57 G58 A55:A56 H2:AC4 A17:G27 H57:AA62 AC67 AC50:AC64 AB5:AC5 A53:G53 H49:AA54 AB49:AB64 A37:AA40 H5:AA15 AB7:AC15 A16:AC16 A31:G36 H17:AA36 AB65:AC66 AC17:AC46 AB17:AB47 A68:AC71 A54:B54 D54:G54 C55:AA56 A3:G5 A7:G8 A6:C6 E6:G6 A10:G13 A9:C9 E9:G9 A29:G29 A28:C28 E28:G28 A42:AA45 A41:C41 E41:AA41 A47:AA48 A46:C46 E46:AA46 A49:C52 E49:G52 A64:AA66 A59:C63 E63:AA63 E59:G62">
-    <cfRule type="expression" dxfId="288" priority="28">
+    <cfRule type="expression" dxfId="290" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="287" priority="27">
+    <cfRule type="expression" dxfId="289" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC49">
-    <cfRule type="expression" dxfId="286" priority="26">
+    <cfRule type="expression" dxfId="288" priority="26">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:C30 F30">
-    <cfRule type="expression" dxfId="285" priority="25">
+    <cfRule type="expression" dxfId="287" priority="25">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:F14 A15:C15 E15:F15">
-    <cfRule type="expression" dxfId="284" priority="23">
+    <cfRule type="expression" dxfId="286" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="283" priority="22">
+    <cfRule type="expression" dxfId="285" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:F58">
-    <cfRule type="expression" dxfId="282" priority="20">
+    <cfRule type="expression" dxfId="284" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:B56">
-    <cfRule type="expression" dxfId="281" priority="19">
+    <cfRule type="expression" dxfId="283" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AC6">
-    <cfRule type="expression" dxfId="280" priority="15">
+    <cfRule type="expression" dxfId="282" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB48">
-    <cfRule type="expression" dxfId="279" priority="14">
+    <cfRule type="expression" dxfId="281" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="278" priority="13">
+    <cfRule type="expression" dxfId="280" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="277" priority="12">
+    <cfRule type="expression" dxfId="279" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="276" priority="11">
+    <cfRule type="expression" dxfId="278" priority="11">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="275" priority="10">
+    <cfRule type="expression" dxfId="277" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
-    <cfRule type="expression" dxfId="274" priority="9">
+    <cfRule type="expression" dxfId="276" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="273" priority="8">
+    <cfRule type="expression" dxfId="275" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="272" priority="7">
+    <cfRule type="expression" dxfId="274" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="271" priority="6">
+    <cfRule type="expression" dxfId="273" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D63">
-    <cfRule type="expression" dxfId="270" priority="1">
+    <cfRule type="expression" dxfId="272" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50:D51">
-    <cfRule type="expression" dxfId="269" priority="5">
+    <cfRule type="expression" dxfId="271" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="expression" dxfId="268" priority="4">
+    <cfRule type="expression" dxfId="270" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59">
-    <cfRule type="expression" dxfId="267" priority="2">
+    <cfRule type="expression" dxfId="269" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61062,107 +61311,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29 G13:G14 G2 A30:G36 A39:G40 G53 A58:C61 G57 H39:AA53 H56:AA59 A54:A55 F54:AA55 A37:AA38 H2:AC4 A15:G26 H5:AA36 AC49:AC58 AC60:AC64 AC5:AC46 AB5:AB61 A62:AB63 A65:AC68 A3:G7 A9:G12 A8:C8 E8:G8 A28:G28 A27:C27 E27:G27 A42:G45 A41:C41 E41:G41 A52:G52 A46:C51 E46:G51 A56:G56 E58:G59 E60:AA61">
-    <cfRule type="expression" dxfId="266" priority="24">
+    <cfRule type="expression" dxfId="268" priority="24">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC47">
-    <cfRule type="expression" dxfId="265" priority="23">
+    <cfRule type="expression" dxfId="267" priority="23">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC48">
-    <cfRule type="expression" dxfId="264" priority="22">
+    <cfRule type="expression" dxfId="266" priority="22">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:C29 F29">
-    <cfRule type="expression" dxfId="263" priority="21">
+    <cfRule type="expression" dxfId="265" priority="21">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC59">
-    <cfRule type="expression" dxfId="262" priority="20">
+    <cfRule type="expression" dxfId="264" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:F13 A14:C14 E14:F14">
-    <cfRule type="expression" dxfId="261" priority="19">
+    <cfRule type="expression" dxfId="263" priority="19">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:E29">
-    <cfRule type="expression" dxfId="260" priority="18">
+    <cfRule type="expression" dxfId="262" priority="18">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:B53 F53">
-    <cfRule type="expression" dxfId="259" priority="15">
+    <cfRule type="expression" dxfId="261" priority="15">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57:F57">
-    <cfRule type="expression" dxfId="258" priority="14">
+    <cfRule type="expression" dxfId="260" priority="14">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54:B55">
-    <cfRule type="expression" dxfId="257" priority="13">
+    <cfRule type="expression" dxfId="259" priority="13">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:E53 C54:E55">
-    <cfRule type="expression" dxfId="256" priority="12">
+    <cfRule type="expression" dxfId="258" priority="12">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D58:D61">
-    <cfRule type="expression" dxfId="255" priority="1">
+    <cfRule type="expression" dxfId="257" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="254" priority="10">
+    <cfRule type="expression" dxfId="256" priority="10">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="253" priority="9">
+    <cfRule type="expression" dxfId="255" priority="9">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
-    <cfRule type="expression" dxfId="252" priority="8">
+    <cfRule type="expression" dxfId="254" priority="8">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="253" priority="7">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:D48">
-    <cfRule type="expression" dxfId="250" priority="6">
+    <cfRule type="expression" dxfId="252" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46">
-    <cfRule type="expression" dxfId="249" priority="5">
+    <cfRule type="expression" dxfId="251" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D49">
-    <cfRule type="expression" dxfId="248" priority="4">
+    <cfRule type="expression" dxfId="250" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D50">
-    <cfRule type="expression" dxfId="247" priority="3">
+    <cfRule type="expression" dxfId="249" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51">
-    <cfRule type="expression" dxfId="246" priority="2">
+    <cfRule type="expression" dxfId="248" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Quant Strategy(2026-27).xlsx
+++ b/Quant Strategy(2026-27).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3205" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3209" uniqueCount="338">
   <si>
     <t>Sudeep</t>
   </si>
@@ -1035,6 +1035,12 @@
   </si>
   <si>
     <t>P3244</t>
+  </si>
+  <si>
+    <t>P3058</t>
+  </si>
+  <si>
+    <t>ATS_1513</t>
   </si>
 </sst>
 </file>
@@ -2372,28 +2378,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="556">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="553">
     <dxf>
       <fill>
         <patternFill>
@@ -6596,7 +6581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB67"/>
+  <dimension ref="A1:AF67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="132" customWidth="1" outlineLevel="1"/>
@@ -6606,20 +6591,21 @@
     <col min="5" max="5" width="9.42578125" style="132" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" style="132" customWidth="1"/>
     <col min="7" max="7" width="1.7109375" style="132" customWidth="1"/>
-    <col min="8" max="14" width="13.42578125" style="132" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" style="132" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="10.7109375" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="9.140625" style="132" collapsed="1"/>
-    <col min="19" max="23" width="9.140625" style="132"/>
-    <col min="24" max="24" width="14.140625" style="132" customWidth="1"/>
-    <col min="25" max="25" width="12" style="132" customWidth="1"/>
-    <col min="26" max="26" width="15.85546875" style="132" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="132"/>
+    <col min="8" max="17" width="13.42578125" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="13.42578125" style="132" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="11.28515625" style="132" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="10.7109375" style="132" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="9.140625" style="132" collapsed="1"/>
+    <col min="23" max="27" width="9.140625" style="132"/>
+    <col min="28" max="28" width="14.140625" style="132" customWidth="1"/>
+    <col min="29" max="29" width="12" style="132" customWidth="1"/>
+    <col min="30" max="30" width="15.85546875" style="132" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="132"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="220"/>
       <c r="H2" s="255">
         <v>46296</v>
@@ -6642,15 +6628,25 @@
       <c r="N2" s="255">
         <v>46307</v>
       </c>
-      <c r="O2" s="182"/>
-      <c r="P2" s="183" t="s">
+      <c r="O2" s="255">
+        <v>46308</v>
+      </c>
+      <c r="P2" s="255">
+        <v>46309</v>
+      </c>
+      <c r="Q2" s="255">
+        <v>46310</v>
+      </c>
+      <c r="R2" s="255"/>
+      <c r="S2" s="182"/>
+      <c r="T2" s="183" t="s">
         <v>325</v>
       </c>
-      <c r="Q2" s="184" t="s">
+      <c r="U2" s="184" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="185" t="s">
         <v>54</v>
       </c>
@@ -6691,17 +6687,27 @@
       <c r="N3" s="178" t="s">
         <v>234</v>
       </c>
-      <c r="O3" s="179"/>
-      <c r="P3" s="188"/>
-      <c r="Q3" s="179"/>
-      <c r="X3" s="132" t="s">
+      <c r="O3" s="178" t="s">
+        <v>233</v>
+      </c>
+      <c r="P3" s="178" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q3" s="178" t="s">
+        <v>236</v>
+      </c>
+      <c r="R3" s="178"/>
+      <c r="S3" s="179"/>
+      <c r="T3" s="188"/>
+      <c r="U3" s="179"/>
+      <c r="AB3" s="132" t="s">
         <v>198</v>
       </c>
-      <c r="Y3" s="132">
+      <c r="AC3" s="132">
         <v>13780</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="141" t="s">
         <v>216</v>
       </c>
@@ -6742,23 +6748,33 @@
       <c r="N4" s="157">
         <v>20138</v>
       </c>
-      <c r="O4" s="210"/>
-      <c r="P4" s="170">
-        <f t="shared" ref="P4:P37" si="0">SUM(H4:O4)</f>
-        <v>106758</v>
-      </c>
-      <c r="Q4" s="148">
-        <f t="shared" ref="Q4:Q37" si="1">IFERROR(P4/F4*100,0)/10000000</f>
-        <v>2.1351599999999999</v>
-      </c>
-      <c r="X4" s="132" t="s">
+      <c r="O4" s="157">
+        <v>2032</v>
+      </c>
+      <c r="P4" s="157">
+        <v>-4915</v>
+      </c>
+      <c r="Q4" s="157">
+        <v>20376</v>
+      </c>
+      <c r="R4" s="157"/>
+      <c r="S4" s="210"/>
+      <c r="T4" s="170">
+        <f t="shared" ref="T4:T37" si="0">SUM(H4:S4)</f>
+        <v>124251</v>
+      </c>
+      <c r="U4" s="148">
+        <f t="shared" ref="U4:U37" si="1">IFERROR(T4/F4*100,0)/10000000</f>
+        <v>2.48502</v>
+      </c>
+      <c r="AB4" s="132" t="s">
         <v>170</v>
       </c>
-      <c r="Y4" s="132">
+      <c r="AC4" s="132">
         <v>2865</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="141" t="s">
         <v>30</v>
       </c>
@@ -6799,17 +6815,27 @@
       <c r="N5" s="146">
         <v>267650</v>
       </c>
-      <c r="O5" s="173"/>
-      <c r="P5" s="170">
+      <c r="O5" s="146">
+        <v>-166064</v>
+      </c>
+      <c r="P5" s="146">
+        <v>20733</v>
+      </c>
+      <c r="Q5" s="146">
+        <v>-56438</v>
+      </c>
+      <c r="R5" s="146"/>
+      <c r="S5" s="173"/>
+      <c r="T5" s="170">
         <f t="shared" si="0"/>
-        <v>575690</v>
-      </c>
-      <c r="Q5" s="148">
+        <v>373921</v>
+      </c>
+      <c r="U5" s="148">
         <f t="shared" si="1"/>
-        <v>1.9189666666666665</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.2464033333333333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="141" t="s">
         <v>323</v>
       </c>
@@ -6850,17 +6876,27 @@
       <c r="N6" s="146">
         <v>-10500</v>
       </c>
-      <c r="O6" s="173"/>
-      <c r="P6" s="170">
+      <c r="O6" s="146">
+        <v>68700</v>
+      </c>
+      <c r="P6" s="146">
+        <v>47900</v>
+      </c>
+      <c r="Q6" s="146">
+        <v>13400</v>
+      </c>
+      <c r="R6" s="146"/>
+      <c r="S6" s="173"/>
+      <c r="T6" s="170">
         <f t="shared" si="0"/>
-        <v>117837</v>
-      </c>
-      <c r="Q6" s="148">
+        <v>247837</v>
+      </c>
+      <c r="U6" s="148">
         <f t="shared" si="1"/>
-        <v>1.1783699999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2.47837</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="141" t="s">
         <v>134</v>
       </c>
@@ -6901,21 +6937,31 @@
       <c r="N7" s="146">
         <v>-116400</v>
       </c>
-      <c r="O7" s="173"/>
-      <c r="P7" s="170">
+      <c r="O7" s="146">
+        <v>190500</v>
+      </c>
+      <c r="P7" s="146">
+        <v>114600</v>
+      </c>
+      <c r="Q7" s="146">
+        <v>6628</v>
+      </c>
+      <c r="R7" s="146"/>
+      <c r="S7" s="173"/>
+      <c r="T7" s="170">
         <f t="shared" si="0"/>
-        <v>-316610</v>
-      </c>
-      <c r="Q7" s="148">
+        <v>-4882</v>
+      </c>
+      <c r="U7" s="148">
         <f t="shared" si="1"/>
-        <v>-1.0553666666666668</v>
-      </c>
-      <c r="S7" s="5"/>
-      <c r="T7" s="133">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+        <v>-1.6273333333333331E-2</v>
+      </c>
+      <c r="W7" s="5"/>
+      <c r="X7" s="133">
+        <v>-12197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="141" t="s">
         <v>217</v>
       </c>
@@ -6956,21 +7002,31 @@
       <c r="N8" s="146">
         <v>27600</v>
       </c>
-      <c r="O8" s="173"/>
-      <c r="P8" s="170">
+      <c r="O8" s="146">
+        <v>18375</v>
+      </c>
+      <c r="P8" s="146">
+        <v>-2657</v>
+      </c>
+      <c r="Q8" s="146">
+        <v>70564</v>
+      </c>
+      <c r="R8" s="146"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="170">
         <f t="shared" si="0"/>
-        <v>178330</v>
-      </c>
-      <c r="Q8" s="148">
+        <v>264612</v>
+      </c>
+      <c r="U8" s="148">
         <f t="shared" si="1"/>
-        <v>1.1888666666666667</v>
-      </c>
-      <c r="S8" s="133">
-        <v>2143112</v>
-      </c>
-      <c r="T8" s="133"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.7640800000000001</v>
+      </c>
+      <c r="W8" s="133">
+        <v>292763</v>
+      </c>
+      <c r="X8" s="133"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="141" t="s">
         <v>313</v>
       </c>
@@ -7009,24 +7065,34 @@
       <c r="N9" s="146">
         <v>-22490</v>
       </c>
-      <c r="O9" s="173"/>
-      <c r="P9" s="170">
+      <c r="O9" s="146">
+        <v>34300</v>
+      </c>
+      <c r="P9" s="146">
+        <v>-22700</v>
+      </c>
+      <c r="Q9" s="146">
+        <v>29000</v>
+      </c>
+      <c r="R9" s="146"/>
+      <c r="S9" s="173"/>
+      <c r="T9" s="170">
         <f t="shared" si="0"/>
-        <v>55724</v>
-      </c>
-      <c r="Q9" s="148">
+        <v>96324</v>
+      </c>
+      <c r="U9" s="148">
         <f t="shared" si="1"/>
-        <v>0.92873333333333341</v>
-      </c>
-      <c r="S9" s="133">
-        <v>2143122</v>
-      </c>
-      <c r="T9" s="133">
-        <f>(S9+S8)/10000000*13780</f>
-        <v>5906.4304519999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.6053999999999999</v>
+      </c>
+      <c r="W9" s="133">
+        <v>280566</v>
+      </c>
+      <c r="X9" s="133">
+        <f>(W9+W8)/10000000*13780</f>
+        <v>790.04736200000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="142" t="s">
         <v>35</v>
       </c>
@@ -7067,19 +7133,29 @@
       <c r="N10" s="146">
         <v>-66300</v>
       </c>
-      <c r="O10" s="173"/>
-      <c r="P10" s="170">
+      <c r="O10" s="146">
+        <v>316800</v>
+      </c>
+      <c r="P10" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="146">
+        <v>-235700</v>
+      </c>
+      <c r="R10" s="146"/>
+      <c r="S10" s="173"/>
+      <c r="T10" s="170">
         <f t="shared" si="0"/>
-        <v>-218420</v>
-      </c>
-      <c r="Q10" s="148">
+        <v>-137320</v>
+      </c>
+      <c r="U10" s="148">
         <f t="shared" si="1"/>
-        <v>-0.14561333333333334</v>
-      </c>
-      <c r="S10" s="133"/>
-      <c r="T10" s="133"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+        <v>-9.1546666666666665E-2</v>
+      </c>
+      <c r="W10" s="133"/>
+      <c r="X10" s="133"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="142" t="s">
         <v>137</v>
       </c>
@@ -7120,19 +7196,29 @@
       <c r="N11" s="146">
         <v>16000</v>
       </c>
-      <c r="O11" s="173"/>
-      <c r="P11" s="170">
+      <c r="O11" s="146">
+        <v>266734</v>
+      </c>
+      <c r="P11" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="146">
+        <v>102848</v>
+      </c>
+      <c r="R11" s="146"/>
+      <c r="S11" s="173"/>
+      <c r="T11" s="170">
         <f t="shared" si="0"/>
-        <v>242131</v>
-      </c>
-      <c r="Q11" s="148">
+        <v>611713</v>
+      </c>
+      <c r="U11" s="148">
         <f t="shared" si="1"/>
-        <v>0.40355166666666664</v>
-      </c>
-      <c r="S11" s="133"/>
-      <c r="T11" s="133"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+        <v>1.0195216666666669</v>
+      </c>
+      <c r="W11" s="133"/>
+      <c r="X11" s="133"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="142" t="s">
         <v>42</v>
       </c>
@@ -7173,19 +7259,29 @@
       <c r="N12" s="146">
         <v>-1450</v>
       </c>
-      <c r="O12" s="173"/>
-      <c r="P12" s="170">
+      <c r="O12" s="146">
+        <v>1122</v>
+      </c>
+      <c r="P12" s="146">
+        <v>-2961</v>
+      </c>
+      <c r="Q12" s="146">
+        <v>-100</v>
+      </c>
+      <c r="R12" s="146"/>
+      <c r="S12" s="173"/>
+      <c r="T12" s="170">
         <f t="shared" si="0"/>
-        <v>-2741</v>
-      </c>
-      <c r="Q12" s="148">
+        <v>-4680</v>
+      </c>
+      <c r="U12" s="148">
         <f t="shared" si="1"/>
-        <v>-2.741E-2</v>
-      </c>
-      <c r="S12" s="133"/>
-      <c r="T12" s="133"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+        <v>-4.6800000000000001E-2</v>
+      </c>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="141" t="s">
         <v>212</v>
       </c>
@@ -7226,19 +7322,29 @@
       <c r="N13" s="146">
         <v>19400</v>
       </c>
-      <c r="O13" s="173"/>
-      <c r="P13" s="170">
+      <c r="O13" s="146">
+        <v>33540</v>
+      </c>
+      <c r="P13" s="146">
+        <v>-4729</v>
+      </c>
+      <c r="Q13" s="146">
+        <v>-9088</v>
+      </c>
+      <c r="R13" s="146"/>
+      <c r="S13" s="173"/>
+      <c r="T13" s="170">
         <f t="shared" si="0"/>
-        <v>135553</v>
-      </c>
-      <c r="Q13" s="148">
+        <v>155276</v>
+      </c>
+      <c r="U13" s="148">
         <f t="shared" si="1"/>
-        <v>0.54221200000000003</v>
-      </c>
-      <c r="S13" s="133"/>
-      <c r="T13" s="133"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+        <v>0.62110399999999999</v>
+      </c>
+      <c r="W13" s="133"/>
+      <c r="X13" s="133"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="141" t="s">
         <v>51</v>
       </c>
@@ -7279,29 +7385,39 @@
       <c r="N14" s="146">
         <v>14168</v>
       </c>
-      <c r="O14" s="173"/>
-      <c r="P14" s="170">
+      <c r="O14" s="146">
+        <v>37416</v>
+      </c>
+      <c r="P14" s="146">
+        <v>2460</v>
+      </c>
+      <c r="Q14" s="146">
+        <v>-9798</v>
+      </c>
+      <c r="R14" s="146"/>
+      <c r="S14" s="173"/>
+      <c r="T14" s="170">
         <f t="shared" si="0"/>
-        <v>145701</v>
-      </c>
-      <c r="Q14" s="148">
+        <v>175779</v>
+      </c>
+      <c r="U14" s="148">
         <f t="shared" si="1"/>
-        <v>0.66227727272727266</v>
-      </c>
-      <c r="S14" s="133"/>
-      <c r="T14" s="192">
-        <f>T7-T9</f>
-        <v>-5896.4304519999996</v>
-      </c>
-      <c r="W14" s="132">
+        <v>0.7989954545454544</v>
+      </c>
+      <c r="W14" s="133"/>
+      <c r="X14" s="192">
+        <f>X7-X9</f>
+        <v>-12987.047361999999</v>
+      </c>
+      <c r="AA14" s="132">
         <v>116185</v>
       </c>
-      <c r="Y14" s="132">
-        <f>W14+T14</f>
-        <v>110288.569548</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC14" s="132">
+        <f>AA14+X14</f>
+        <v>103197.952638</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="141" t="s">
         <v>43</v>
       </c>
@@ -7342,17 +7458,27 @@
       <c r="N15" s="146">
         <v>-2965</v>
       </c>
-      <c r="O15" s="173"/>
-      <c r="P15" s="170">
+      <c r="O15" s="146">
+        <v>17000</v>
+      </c>
+      <c r="P15" s="146">
+        <v>-1624</v>
+      </c>
+      <c r="Q15" s="146">
+        <v>-6519</v>
+      </c>
+      <c r="R15" s="146"/>
+      <c r="S15" s="173"/>
+      <c r="T15" s="170">
         <f t="shared" si="0"/>
-        <v>1117</v>
-      </c>
-      <c r="Q15" s="148">
+        <v>9974</v>
+      </c>
+      <c r="U15" s="148">
         <f t="shared" si="1"/>
-        <v>1.1169999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+        <v>9.9739999999999995E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="141" t="s">
         <v>24</v>
       </c>
@@ -7393,28 +7519,38 @@
       <c r="N16" s="146">
         <v>49165</v>
       </c>
-      <c r="O16" s="173"/>
-      <c r="P16" s="170">
+      <c r="O16" s="146">
+        <v>42400</v>
+      </c>
+      <c r="P16" s="146">
+        <v>-41370</v>
+      </c>
+      <c r="Q16" s="146">
+        <v>45200</v>
+      </c>
+      <c r="R16" s="146"/>
+      <c r="S16" s="173"/>
+      <c r="T16" s="170">
         <f t="shared" si="0"/>
-        <v>-32466</v>
-      </c>
-      <c r="Q16" s="148">
+        <v>13764</v>
+      </c>
+      <c r="U16" s="148">
         <f t="shared" si="1"/>
-        <v>-0.12986400000000001</v>
-      </c>
-      <c r="Y16" s="132">
+        <v>5.5056000000000001E-2</v>
+      </c>
+      <c r="AC16" s="132">
         <v>4000000</v>
       </c>
-      <c r="Z16" s="132">
-        <f>Y16*7/100</f>
+      <c r="AD16" s="132">
+        <f>AC16*7/100</f>
         <v>280000</v>
       </c>
-      <c r="AB16" s="132">
+      <c r="AF16" s="132">
         <f>15*12</f>
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="141" t="s">
         <v>23</v>
       </c>
@@ -7455,21 +7591,31 @@
       <c r="N17" s="146">
         <v>25724</v>
       </c>
-      <c r="O17" s="173"/>
-      <c r="P17" s="170">
+      <c r="O17" s="146">
+        <v>70400</v>
+      </c>
+      <c r="P17" s="146">
+        <v>-85300</v>
+      </c>
+      <c r="Q17" s="146">
+        <v>38300</v>
+      </c>
+      <c r="R17" s="146"/>
+      <c r="S17" s="173"/>
+      <c r="T17" s="170">
         <f t="shared" si="0"/>
-        <v>26201</v>
-      </c>
-      <c r="Q17" s="148">
+        <v>49601</v>
+      </c>
+      <c r="U17" s="148">
         <f t="shared" si="1"/>
-        <v>6.5502500000000005E-2</v>
-      </c>
-      <c r="Z17" s="132">
-        <f>Z16/12</f>
+        <v>0.1240025</v>
+      </c>
+      <c r="AD17" s="132">
+        <f>AD16/12</f>
         <v>23333.333333333332</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="141" t="s">
         <v>165</v>
       </c>
@@ -7510,17 +7656,27 @@
       <c r="N18" s="146">
         <v>86900</v>
       </c>
-      <c r="O18" s="173"/>
-      <c r="P18" s="170">
+      <c r="O18" s="146">
+        <v>29900</v>
+      </c>
+      <c r="P18" s="146">
+        <v>-50000</v>
+      </c>
+      <c r="Q18" s="146">
+        <v>156158</v>
+      </c>
+      <c r="R18" s="146"/>
+      <c r="S18" s="173"/>
+      <c r="T18" s="170">
         <f t="shared" si="0"/>
-        <v>314415</v>
-      </c>
-      <c r="Q18" s="148">
+        <v>450473</v>
+      </c>
+      <c r="U18" s="148">
         <f t="shared" si="1"/>
-        <v>2.0960999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+        <v>3.0031533333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="141" t="s">
         <v>110</v>
       </c>
@@ -7561,20 +7717,30 @@
       <c r="N19" s="146">
         <v>0</v>
       </c>
-      <c r="O19" s="173"/>
-      <c r="P19" s="170">
+      <c r="O19" s="146">
+        <v>0</v>
+      </c>
+      <c r="P19" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="146">
+        <v>0</v>
+      </c>
+      <c r="R19" s="146"/>
+      <c r="S19" s="173"/>
+      <c r="T19" s="170">
         <f t="shared" si="0"/>
         <v>-150688</v>
       </c>
-      <c r="Q19" s="148">
+      <c r="U19" s="148">
         <f t="shared" si="1"/>
         <v>-1.3698909090909093</v>
       </c>
-      <c r="U19" s="132">
+      <c r="Y19" s="132">
         <v>54000</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="141" t="s">
         <v>319</v>
       </c>
@@ -7615,20 +7781,30 @@
       <c r="N20" s="146">
         <v>-5900</v>
       </c>
-      <c r="O20" s="173"/>
-      <c r="P20" s="170">
+      <c r="O20" s="146">
+        <v>-5537</v>
+      </c>
+      <c r="P20" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="146">
+        <v>0</v>
+      </c>
+      <c r="R20" s="146"/>
+      <c r="S20" s="173"/>
+      <c r="T20" s="170">
         <f t="shared" si="0"/>
-        <v>-102435</v>
-      </c>
-      <c r="Q20" s="148">
+        <v>-107972</v>
+      </c>
+      <c r="U20" s="148">
         <f t="shared" si="1"/>
-        <v>-4.0974000000000004</v>
-      </c>
-      <c r="U20" s="132">
+        <v>-4.3188800000000001</v>
+      </c>
+      <c r="Y20" s="132">
         <v>11100</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="141" t="s">
         <v>316</v>
       </c>
@@ -7669,20 +7845,30 @@
       <c r="N21" s="146">
         <v>0</v>
       </c>
-      <c r="O21" s="173"/>
-      <c r="P21" s="170">
+      <c r="O21" s="146">
+        <v>0</v>
+      </c>
+      <c r="P21" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="146">
+        <v>0</v>
+      </c>
+      <c r="R21" s="146"/>
+      <c r="S21" s="173"/>
+      <c r="T21" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="148">
+      <c r="U21" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U21" s="132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Y21" s="132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="141" t="s">
         <v>317</v>
       </c>
@@ -7723,21 +7909,31 @@
       <c r="N22" s="146">
         <v>0</v>
       </c>
-      <c r="O22" s="173"/>
-      <c r="P22" s="170">
+      <c r="O22" s="146">
+        <v>0</v>
+      </c>
+      <c r="P22" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="146">
+        <v>0</v>
+      </c>
+      <c r="R22" s="146"/>
+      <c r="S22" s="173"/>
+      <c r="T22" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="148">
+      <c r="U22" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U22" s="132">
-        <f>SUM(U19:U21)</f>
+      <c r="Y22" s="132">
+        <f>SUM(Y19:Y21)</f>
         <v>65100</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="141" t="s">
         <v>32</v>
       </c>
@@ -7778,17 +7974,27 @@
       <c r="N23" s="146">
         <v>-32723</v>
       </c>
-      <c r="O23" s="173"/>
-      <c r="P23" s="170">
+      <c r="O23" s="146">
+        <v>-7059</v>
+      </c>
+      <c r="P23" s="146">
+        <v>28800</v>
+      </c>
+      <c r="Q23" s="146">
+        <v>-13000</v>
+      </c>
+      <c r="R23" s="146"/>
+      <c r="S23" s="173"/>
+      <c r="T23" s="170">
         <f t="shared" si="0"/>
-        <v>-5462</v>
-      </c>
-      <c r="Q23" s="148">
+        <v>3279</v>
+      </c>
+      <c r="U23" s="148">
         <f t="shared" si="1"/>
-        <v>-4.9654545454545451E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+        <v>2.9809090909090907E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="141" t="s">
         <v>97</v>
       </c>
@@ -7829,17 +8035,27 @@
       <c r="N24" s="146">
         <v>-28900</v>
       </c>
-      <c r="O24" s="173"/>
-      <c r="P24" s="170">
+      <c r="O24" s="146">
+        <v>226700</v>
+      </c>
+      <c r="P24" s="146">
+        <v>14473</v>
+      </c>
+      <c r="Q24" s="146">
+        <v>-30980</v>
+      </c>
+      <c r="R24" s="146"/>
+      <c r="S24" s="173"/>
+      <c r="T24" s="170">
         <f t="shared" si="0"/>
-        <v>-232800</v>
-      </c>
-      <c r="Q24" s="148">
+        <v>-22607</v>
+      </c>
+      <c r="U24" s="148">
         <f t="shared" si="1"/>
-        <v>-1.0121739130434784</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+        <v>-9.8291304347826097E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="141" t="s">
         <v>335</v>
       </c>
@@ -7864,11 +8080,27 @@
       <c r="N25" s="146">
         <v>-300</v>
       </c>
-      <c r="O25" s="173"/>
-      <c r="P25" s="170"/>
-      <c r="Q25" s="148"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O25" s="146">
+        <v>58100</v>
+      </c>
+      <c r="P25" s="146">
+        <v>10600</v>
+      </c>
+      <c r="Q25" s="146">
+        <v>-13826</v>
+      </c>
+      <c r="R25" s="146"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="170">
+        <f t="shared" ref="T25" si="2">SUM(H25:S25)</f>
+        <v>54574</v>
+      </c>
+      <c r="U25" s="148">
+        <f t="shared" ref="U25" si="3">IFERROR(T25/F25*100,0)/10000000</f>
+        <v>2.7286999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="141" t="s">
         <v>302</v>
       </c>
@@ -7907,17 +8139,27 @@
       <c r="N26" s="146">
         <v>6366</v>
       </c>
-      <c r="O26" s="173"/>
-      <c r="P26" s="170">
+      <c r="O26" s="146">
+        <v>4942</v>
+      </c>
+      <c r="P26" s="146">
+        <v>-7150</v>
+      </c>
+      <c r="Q26" s="146">
+        <v>1600</v>
+      </c>
+      <c r="R26" s="146"/>
+      <c r="S26" s="173"/>
+      <c r="T26" s="170">
         <f t="shared" si="0"/>
-        <v>16957</v>
-      </c>
-      <c r="Q26" s="148">
+        <v>16349</v>
+      </c>
+      <c r="U26" s="148">
         <f t="shared" si="1"/>
-        <v>0.84784999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.81745000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="141" t="s">
         <v>29</v>
       </c>
@@ -7958,17 +8200,27 @@
       <c r="N27" s="146">
         <v>65100</v>
       </c>
-      <c r="O27" s="173"/>
-      <c r="P27" s="170">
+      <c r="O27" s="146">
+        <v>45700</v>
+      </c>
+      <c r="P27" s="146">
+        <v>-133000</v>
+      </c>
+      <c r="Q27" s="146">
+        <v>130000</v>
+      </c>
+      <c r="R27" s="146"/>
+      <c r="S27" s="173"/>
+      <c r="T27" s="170">
         <f t="shared" si="0"/>
-        <v>-75500</v>
-      </c>
-      <c r="Q27" s="148">
+        <v>-32800</v>
+      </c>
+      <c r="U27" s="148">
         <f t="shared" si="1"/>
-        <v>-0.151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+        <v>-6.5600000000000006E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="141" t="s">
         <v>28</v>
       </c>
@@ -8009,17 +8261,27 @@
       <c r="N28" s="146">
         <v>-40416</v>
       </c>
-      <c r="O28" s="173"/>
-      <c r="P28" s="170">
+      <c r="O28" s="146">
+        <v>137300</v>
+      </c>
+      <c r="P28" s="146">
+        <v>583300</v>
+      </c>
+      <c r="Q28" s="146">
+        <v>11260</v>
+      </c>
+      <c r="R28" s="146"/>
+      <c r="S28" s="173"/>
+      <c r="T28" s="170">
         <f t="shared" si="0"/>
-        <v>444299</v>
-      </c>
-      <c r="Q28" s="148">
+        <v>1176159</v>
+      </c>
+      <c r="U28" s="148">
         <f t="shared" si="1"/>
-        <v>0.444299</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.176159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="141" t="s">
         <v>332</v>
       </c>
@@ -8056,17 +8318,27 @@
       <c r="N29" s="146">
         <v>20700</v>
       </c>
-      <c r="O29" s="173"/>
-      <c r="P29" s="170">
-        <f t="shared" ref="P29" si="2">SUM(H29:O29)</f>
-        <v>47470</v>
-      </c>
-      <c r="Q29" s="148">
-        <f t="shared" ref="Q29" si="3">IFERROR(P29/F29*100,0)/10000000</f>
-        <v>0.94940000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="O29" s="146">
+        <v>-10961</v>
+      </c>
+      <c r="P29" s="146">
+        <v>-11200</v>
+      </c>
+      <c r="Q29" s="146">
+        <v>18300</v>
+      </c>
+      <c r="R29" s="146"/>
+      <c r="S29" s="173"/>
+      <c r="T29" s="170">
+        <f t="shared" ref="T29" si="4">SUM(H29:S29)</f>
+        <v>43609</v>
+      </c>
+      <c r="U29" s="148">
+        <f t="shared" ref="U29" si="5">IFERROR(T29/F29*100,0)/10000000</f>
+        <v>0.87217999999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="141" t="s">
         <v>65</v>
       </c>
@@ -8107,17 +8379,27 @@
       <c r="N30" s="146">
         <v>0</v>
       </c>
-      <c r="O30" s="173"/>
-      <c r="P30" s="170">
+      <c r="O30" s="146">
+        <v>226901</v>
+      </c>
+      <c r="P30" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="146">
+        <v>-161746</v>
+      </c>
+      <c r="R30" s="146"/>
+      <c r="S30" s="173"/>
+      <c r="T30" s="170">
         <f t="shared" si="0"/>
-        <v>556830</v>
-      </c>
-      <c r="Q30" s="148">
+        <v>621985</v>
+      </c>
+      <c r="U30" s="148">
         <f t="shared" si="1"/>
-        <v>1.1136600000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+        <v>1.24397</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="140" t="s">
         <v>34</v>
       </c>
@@ -8158,17 +8440,27 @@
       <c r="N31" s="146">
         <v>19560</v>
       </c>
-      <c r="O31" s="173"/>
-      <c r="P31" s="170">
+      <c r="O31" s="146">
+        <v>38370</v>
+      </c>
+      <c r="P31" s="146">
+        <v>10450</v>
+      </c>
+      <c r="Q31" s="146">
+        <v>59316</v>
+      </c>
+      <c r="R31" s="146"/>
+      <c r="S31" s="173"/>
+      <c r="T31" s="170">
         <f t="shared" si="0"/>
-        <v>-5105</v>
-      </c>
-      <c r="Q31" s="148">
+        <v>103031</v>
+      </c>
+      <c r="U31" s="148">
         <f t="shared" si="1"/>
-        <v>-1.021E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0.206062</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="140" t="s">
         <v>131</v>
       </c>
@@ -8209,17 +8501,27 @@
       <c r="N32" s="146">
         <v>20700</v>
       </c>
-      <c r="O32" s="173"/>
-      <c r="P32" s="170">
+      <c r="O32" s="146">
+        <v>12614</v>
+      </c>
+      <c r="P32" s="146">
+        <v>7400</v>
+      </c>
+      <c r="Q32" s="146">
+        <v>19095</v>
+      </c>
+      <c r="R32" s="146"/>
+      <c r="S32" s="173"/>
+      <c r="T32" s="170">
         <f t="shared" si="0"/>
-        <v>77599</v>
-      </c>
-      <c r="Q32" s="148">
+        <v>116708</v>
+      </c>
+      <c r="U32" s="148">
         <f t="shared" si="1"/>
-        <v>1.5519799999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2.3341599999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
         <v>67</v>
       </c>
@@ -8260,18 +8562,28 @@
       <c r="N33" s="146">
         <v>35813</v>
       </c>
-      <c r="O33" s="173"/>
-      <c r="P33" s="170">
+      <c r="O33" s="146">
+        <v>26000</v>
+      </c>
+      <c r="P33" s="146">
+        <v>-45331</v>
+      </c>
+      <c r="Q33" s="146">
+        <v>21700</v>
+      </c>
+      <c r="R33" s="146"/>
+      <c r="S33" s="173"/>
+      <c r="T33" s="170">
         <f t="shared" si="0"/>
-        <v>168476</v>
-      </c>
-      <c r="Q33" s="148">
+        <v>170845</v>
+      </c>
+      <c r="U33" s="148">
         <f t="shared" si="1"/>
-        <v>4.2119</v>
-      </c>
-      <c r="T33" s="133"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4.2711249999999996</v>
+      </c>
+      <c r="X33" s="133"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="141" t="s">
         <v>31</v>
       </c>
@@ -8312,21 +8624,31 @@
       <c r="N34" s="146">
         <v>85200</v>
       </c>
-      <c r="O34" s="173"/>
-      <c r="P34" s="170">
+      <c r="O34" s="146">
+        <v>-20461</v>
+      </c>
+      <c r="P34" s="146">
+        <v>-170280</v>
+      </c>
+      <c r="Q34" s="146">
+        <v>243315</v>
+      </c>
+      <c r="R34" s="146"/>
+      <c r="S34" s="173"/>
+      <c r="T34" s="170">
         <f t="shared" si="0"/>
-        <v>164731</v>
-      </c>
-      <c r="Q34" s="148">
+        <v>217305</v>
+      </c>
+      <c r="U34" s="148">
         <f t="shared" si="1"/>
-        <v>0.41182750000000001</v>
-      </c>
-      <c r="S34" s="5"/>
-      <c r="T34" s="133">
-        <v>-16300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+        <v>0.54326249999999998</v>
+      </c>
+      <c r="W34" s="5"/>
+      <c r="X34" s="133">
+        <v>61235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="141" t="s">
         <v>104</v>
       </c>
@@ -8367,19 +8689,29 @@
       <c r="N35" s="146">
         <v>10400</v>
       </c>
-      <c r="O35" s="173"/>
-      <c r="P35" s="170">
+      <c r="O35" s="146">
+        <v>51221</v>
+      </c>
+      <c r="P35" s="146">
+        <v>-5394</v>
+      </c>
+      <c r="Q35" s="146">
+        <v>-35576</v>
+      </c>
+      <c r="R35" s="146"/>
+      <c r="S35" s="173"/>
+      <c r="T35" s="170">
         <f t="shared" si="0"/>
-        <v>-30412</v>
-      </c>
-      <c r="Q35" s="148">
+        <v>-20161</v>
+      </c>
+      <c r="U35" s="148">
         <f t="shared" si="1"/>
-        <v>-0.30412</v>
-      </c>
-      <c r="S35" s="5"/>
-      <c r="T35" s="133"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+        <v>-0.20161000000000001</v>
+      </c>
+      <c r="W35" s="5"/>
+      <c r="X35" s="133"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="141" t="s">
         <v>314</v>
       </c>
@@ -8418,24 +8750,34 @@
       <c r="N36" s="146">
         <v>0</v>
       </c>
-      <c r="O36" s="173"/>
-      <c r="P36" s="170">
+      <c r="O36" s="146">
+        <v>0</v>
+      </c>
+      <c r="P36" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="146">
+        <v>0</v>
+      </c>
+      <c r="R36" s="146"/>
+      <c r="S36" s="173"/>
+      <c r="T36" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="148">
+      <c r="U36" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S36" s="133">
-        <v>380097</v>
-      </c>
-      <c r="T36" s="133">
-        <f>(S37+S36)/10000000*13780</f>
-        <v>1025.0693960000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="W36" s="133">
+        <v>1404396</v>
+      </c>
+      <c r="X36" s="133">
+        <f>(W37+W36)/10000000*13780</f>
+        <v>3954.8972060000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="141" t="s">
         <v>229</v>
       </c>
@@ -8476,21 +8818,31 @@
       <c r="N37" s="146">
         <v>15668</v>
       </c>
-      <c r="O37" s="173"/>
-      <c r="P37" s="170">
+      <c r="O37" s="146">
+        <v>5849</v>
+      </c>
+      <c r="P37" s="146">
+        <v>-37180</v>
+      </c>
+      <c r="Q37" s="146">
+        <v>-26608</v>
+      </c>
+      <c r="R37" s="146"/>
+      <c r="S37" s="173"/>
+      <c r="T37" s="170">
         <f t="shared" si="0"/>
-        <v>30173</v>
-      </c>
-      <c r="Q37" s="148">
+        <v>-27766</v>
+      </c>
+      <c r="U37" s="148">
         <f t="shared" si="1"/>
-        <v>0.60346</v>
-      </c>
-      <c r="S37" s="133">
-        <v>363785</v>
-      </c>
-      <c r="T37" s="133"/>
-    </row>
-    <row r="38" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>-0.55532000000000004</v>
+      </c>
+      <c r="W37" s="133">
+        <v>1465631</v>
+      </c>
+      <c r="X37" s="133"/>
+    </row>
+    <row r="38" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="141" t="s">
         <v>45</v>
       </c>
@@ -8531,22 +8883,32 @@
       <c r="N38" s="146">
         <v>341200</v>
       </c>
-      <c r="O38" s="173"/>
-      <c r="P38" s="170">
-        <f t="shared" ref="P38:P69" si="4">SUM(H38:O38)</f>
-        <v>406134</v>
-      </c>
-      <c r="Q38" s="148">
-        <f t="shared" ref="Q38:Q69" si="5">IFERROR(P38/F38*100,0)/10000000</f>
-        <v>1.35378</v>
-      </c>
-      <c r="S38" s="133"/>
-      <c r="T38" s="133">
-        <f>+T34-T36</f>
-        <v>-17325.069395999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O38" s="146">
+        <v>-109461</v>
+      </c>
+      <c r="P38" s="146">
+        <v>59000</v>
+      </c>
+      <c r="Q38" s="146">
+        <v>303000</v>
+      </c>
+      <c r="R38" s="146"/>
+      <c r="S38" s="173"/>
+      <c r="T38" s="170">
+        <f t="shared" ref="T38:T54" si="6">SUM(H38:S38)</f>
+        <v>658673</v>
+      </c>
+      <c r="U38" s="148">
+        <f t="shared" ref="U38:U54" si="7">IFERROR(T38/F38*100,0)/10000000</f>
+        <v>2.1955766666666663</v>
+      </c>
+      <c r="W38" s="133"/>
+      <c r="X38" s="133">
+        <f>+X34-X36</f>
+        <v>57280.102793999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="141" t="s">
         <v>292</v>
       </c>
@@ -8585,19 +8947,29 @@
       <c r="N39" s="146">
         <v>-17325</v>
       </c>
-      <c r="O39" s="173"/>
-      <c r="P39" s="170">
-        <f t="shared" si="4"/>
-        <v>67502</v>
-      </c>
-      <c r="Q39" s="148">
-        <f t="shared" si="5"/>
-        <v>6.7502000000000004</v>
-      </c>
-      <c r="S39" s="133"/>
-      <c r="T39" s="133"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O39" s="146">
+        <v>62950</v>
+      </c>
+      <c r="P39" s="146">
+        <v>-33154</v>
+      </c>
+      <c r="Q39" s="146">
+        <v>-64866</v>
+      </c>
+      <c r="R39" s="146"/>
+      <c r="S39" s="173"/>
+      <c r="T39" s="170">
+        <f t="shared" si="6"/>
+        <v>32432</v>
+      </c>
+      <c r="U39" s="148">
+        <f t="shared" si="7"/>
+        <v>3.2431999999999999</v>
+      </c>
+      <c r="W39" s="133"/>
+      <c r="X39" s="133"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="141" t="s">
         <v>132</v>
       </c>
@@ -8638,19 +9010,29 @@
       <c r="N40" s="146">
         <v>0</v>
       </c>
-      <c r="O40" s="173"/>
-      <c r="P40" s="170">
-        <f t="shared" si="4"/>
-        <v>42200</v>
-      </c>
-      <c r="Q40" s="148">
-        <f t="shared" si="5"/>
-        <v>0.84399999999999997</v>
-      </c>
-      <c r="S40" s="133"/>
-      <c r="T40" s="133"/>
-    </row>
-    <row r="41" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O40" s="146">
+        <v>-11341</v>
+      </c>
+      <c r="P40" s="146">
+        <v>-18160</v>
+      </c>
+      <c r="Q40" s="146">
+        <v>12680</v>
+      </c>
+      <c r="R40" s="146"/>
+      <c r="S40" s="173"/>
+      <c r="T40" s="170">
+        <f t="shared" si="6"/>
+        <v>25379</v>
+      </c>
+      <c r="U40" s="148">
+        <f t="shared" si="7"/>
+        <v>0.50758000000000003</v>
+      </c>
+      <c r="W40" s="133"/>
+      <c r="X40" s="133"/>
+    </row>
+    <row r="41" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="141" t="s">
         <v>48</v>
       </c>
@@ -8691,122 +9073,140 @@
       <c r="N41" s="146">
         <v>107800</v>
       </c>
-      <c r="O41" s="173"/>
-      <c r="P41" s="170">
-        <f t="shared" si="4"/>
-        <v>-599929</v>
-      </c>
-      <c r="Q41" s="148">
-        <f t="shared" si="5"/>
-        <v>-5.9992900000000002</v>
-      </c>
-      <c r="S41" s="133"/>
-      <c r="T41" s="133"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O41" s="146">
+        <v>-65513</v>
+      </c>
+      <c r="P41" s="146">
+        <v>139726</v>
+      </c>
+      <c r="Q41" s="146">
+        <v>-435700</v>
+      </c>
+      <c r="R41" s="146"/>
+      <c r="S41" s="173"/>
+      <c r="T41" s="170">
+        <f t="shared" si="6"/>
+        <v>-961416</v>
+      </c>
+      <c r="U41" s="148">
+        <f t="shared" si="7"/>
+        <v>-9.61416</v>
+      </c>
+      <c r="W41" s="133"/>
+      <c r="X41" s="133"/>
+    </row>
+    <row r="42" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="141" t="s">
+        <v>336</v>
+      </c>
+      <c r="B42" s="140" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="141" t="s">
+        <v>337</v>
+      </c>
+      <c r="D42" s="162" t="s">
+        <v>334</v>
+      </c>
+      <c r="E42" s="141" t="s">
+        <v>256</v>
+      </c>
+      <c r="F42" s="163">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="190"/>
+      <c r="H42" s="146"/>
+      <c r="I42" s="146"/>
+      <c r="J42" s="146"/>
+      <c r="K42" s="146"/>
+      <c r="L42" s="146"/>
+      <c r="M42" s="146"/>
+      <c r="N42" s="146"/>
+      <c r="O42" s="146">
+        <v>195644</v>
+      </c>
+      <c r="P42" s="146">
+        <v>33100</v>
+      </c>
+      <c r="Q42" s="146">
+        <v>46908</v>
+      </c>
+      <c r="R42" s="146"/>
+      <c r="S42" s="173"/>
+      <c r="T42" s="170">
+        <f t="shared" ref="T42" si="8">SUM(H42:S42)</f>
+        <v>275652</v>
+      </c>
+      <c r="U42" s="148">
+        <f t="shared" ref="U42" si="9">IFERROR(T42/F42*100,0)/10000000</f>
+        <v>5.5130400000000002</v>
+      </c>
+      <c r="W42" s="133"/>
+      <c r="X42" s="133"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="141" t="s">
         <v>301</v>
       </c>
-      <c r="B42" s="140" t="s">
+      <c r="B43" s="140" t="s">
         <v>295</v>
       </c>
-      <c r="C42" s="162" t="s">
+      <c r="C43" s="162" t="s">
         <v>296</v>
       </c>
-      <c r="D42" s="162"/>
-      <c r="E42" s="162" t="s">
+      <c r="D43" s="162"/>
+      <c r="E43" s="162" t="s">
         <v>256</v>
       </c>
-      <c r="F42" s="163">
+      <c r="F43" s="163">
         <v>0.1</v>
-      </c>
-      <c r="G42" s="190"/>
-      <c r="H42" s="146">
-        <v>34200</v>
-      </c>
-      <c r="I42" s="146">
-        <v>-23073</v>
-      </c>
-      <c r="J42" s="146">
-        <v>-6862</v>
-      </c>
-      <c r="K42" s="146">
-        <v>-21500</v>
-      </c>
-      <c r="L42" s="146">
-        <v>18000</v>
-      </c>
-      <c r="M42" s="146">
-        <v>3517</v>
-      </c>
-      <c r="N42" s="146">
-        <v>4914</v>
-      </c>
-      <c r="O42" s="173"/>
-      <c r="P42" s="170">
-        <f t="shared" si="4"/>
-        <v>9196</v>
-      </c>
-      <c r="Q42" s="148">
-        <f t="shared" si="5"/>
-        <v>0.91959999999999997</v>
-      </c>
-      <c r="S42" s="133"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="142" t="s">
-        <v>168</v>
-      </c>
-      <c r="B43" s="140" t="s">
-        <v>169</v>
-      </c>
-      <c r="C43" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="D43" s="162" t="s">
-        <v>253</v>
-      </c>
-      <c r="E43" s="162" t="s">
-        <v>253</v>
-      </c>
-      <c r="F43" s="114">
-        <v>4</v>
       </c>
       <c r="G43" s="190"/>
       <c r="H43" s="146">
-        <v>2920</v>
+        <v>34200</v>
       </c>
       <c r="I43" s="146">
-        <v>0</v>
+        <v>-23073</v>
       </c>
       <c r="J43" s="146">
-        <v>0</v>
+        <v>-6862</v>
       </c>
       <c r="K43" s="146">
-        <v>0</v>
+        <v>-21500</v>
       </c>
       <c r="L43" s="146">
-        <v>52100</v>
+        <v>18000</v>
       </c>
       <c r="M43" s="146">
-        <v>0</v>
+        <v>3517</v>
       </c>
       <c r="N43" s="146">
-        <v>0</v>
-      </c>
-      <c r="O43" s="173"/>
-      <c r="P43" s="170">
-        <f t="shared" si="4"/>
-        <v>55020</v>
-      </c>
-      <c r="Q43" s="148">
-        <f t="shared" si="5"/>
-        <v>0.13755000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4914</v>
+      </c>
+      <c r="O43" s="146">
+        <v>-17046</v>
+      </c>
+      <c r="P43" s="146">
+        <v>-24153</v>
+      </c>
+      <c r="Q43" s="146">
+        <v>200</v>
+      </c>
+      <c r="R43" s="146"/>
+      <c r="S43" s="173"/>
+      <c r="T43" s="170">
+        <f t="shared" si="6"/>
+        <v>-31803</v>
+      </c>
+      <c r="U43" s="148">
+        <f t="shared" si="7"/>
+        <v>-3.1802999999999999</v>
+      </c>
+      <c r="W43" s="133"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="142" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B44" s="140" t="s">
         <v>169</v>
@@ -8815,194 +9215,238 @@
         <v>252</v>
       </c>
       <c r="D44" s="162" t="s">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="E44" s="162" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F44" s="114">
         <v>4</v>
       </c>
       <c r="G44" s="190"/>
       <c r="H44" s="146">
-        <v>0</v>
+        <v>2920</v>
       </c>
       <c r="I44" s="146">
+        <v>0</v>
+      </c>
+      <c r="J44" s="146">
+        <v>0</v>
+      </c>
+      <c r="K44" s="146">
+        <v>0</v>
+      </c>
+      <c r="L44" s="146">
+        <v>52100</v>
+      </c>
+      <c r="M44" s="146">
+        <v>0</v>
+      </c>
+      <c r="N44" s="146">
+        <v>0</v>
+      </c>
+      <c r="O44" s="146">
+        <v>0</v>
+      </c>
+      <c r="P44" s="146">
+        <v>-22700</v>
+      </c>
+      <c r="Q44" s="146">
+        <v>80000</v>
+      </c>
+      <c r="R44" s="146"/>
+      <c r="S44" s="173"/>
+      <c r="T44" s="170">
+        <f t="shared" si="6"/>
+        <v>112320</v>
+      </c>
+      <c r="U44" s="148">
+        <f t="shared" si="7"/>
+        <v>0.28079999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="142" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="140" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="D45" s="162" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="162" t="s">
+        <v>256</v>
+      </c>
+      <c r="F45" s="114">
+        <v>4</v>
+      </c>
+      <c r="G45" s="190"/>
+      <c r="H45" s="146">
+        <v>0</v>
+      </c>
+      <c r="I45" s="146">
         <v>-20000</v>
       </c>
-      <c r="J44" s="146">
+      <c r="J45" s="146">
         <v>60600</v>
       </c>
-      <c r="K44" s="146">
-        <v>0</v>
-      </c>
-      <c r="L44" s="146">
-        <v>0</v>
-      </c>
-      <c r="M44" s="146">
+      <c r="K45" s="146">
+        <v>0</v>
+      </c>
+      <c r="L45" s="146">
+        <v>0</v>
+      </c>
+      <c r="M45" s="146">
         <v>-1200</v>
       </c>
-      <c r="N44" s="146">
+      <c r="N45" s="146">
         <v>19500</v>
       </c>
-      <c r="O44" s="173"/>
-      <c r="P44" s="170">
-        <f t="shared" si="4"/>
-        <v>58900</v>
-      </c>
-      <c r="Q44" s="148">
-        <f t="shared" si="5"/>
-        <v>0.14724999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" s="142" t="s">
+      <c r="O45" s="146">
+        <v>105800</v>
+      </c>
+      <c r="P45" s="146">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="146">
+        <v>0</v>
+      </c>
+      <c r="R45" s="146"/>
+      <c r="S45" s="173"/>
+      <c r="T45" s="170">
+        <f t="shared" si="6"/>
+        <v>164700</v>
+      </c>
+      <c r="U45" s="148">
+        <f t="shared" si="7"/>
+        <v>0.41175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="140" t="s">
+      <c r="B46" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="142" t="s">
+      <c r="C46" s="142" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="140" t="s">
+      <c r="D46" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="140" t="s">
-        <v>256</v>
-      </c>
-      <c r="F45" s="118">
-        <v>3</v>
-      </c>
-      <c r="G45" s="196"/>
-      <c r="H45" s="146">
-        <v>174105</v>
-      </c>
-      <c r="I45" s="146">
-        <v>-313641</v>
-      </c>
-      <c r="J45" s="146">
-        <v>307794</v>
-      </c>
-      <c r="K45" s="146">
-        <v>-135130</v>
-      </c>
-      <c r="L45" s="146">
-        <v>290000</v>
-      </c>
-      <c r="M45" s="146">
-        <v>102008</v>
-      </c>
-      <c r="N45" s="146">
-        <v>0</v>
-      </c>
-      <c r="O45" s="173"/>
-      <c r="P45" s="170">
-        <f t="shared" si="4"/>
-        <v>425136</v>
-      </c>
-      <c r="Q45" s="148">
-        <f t="shared" si="5"/>
-        <v>1.4171199999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="59" t="s">
-        <v>306</v>
-      </c>
-      <c r="B46" s="62" t="s">
-        <v>304</v>
-      </c>
-      <c r="C46" s="59" t="s">
-        <v>308</v>
-      </c>
-      <c r="D46" s="140"/>
       <c r="E46" s="140" t="s">
         <v>256</v>
       </c>
-      <c r="F46" s="114">
-        <v>10</v>
-      </c>
-      <c r="G46" s="23"/>
-      <c r="H46" s="150">
-        <v>-214000</v>
-      </c>
-      <c r="I46" s="150">
-        <v>19600</v>
-      </c>
-      <c r="J46" s="150">
-        <v>338000</v>
-      </c>
-      <c r="K46" s="150">
-        <v>63150</v>
-      </c>
-      <c r="L46" s="150">
-        <v>-461500</v>
-      </c>
-      <c r="M46" s="150">
-        <v>-70400</v>
-      </c>
-      <c r="N46" s="150">
-        <v>-233800</v>
-      </c>
-      <c r="O46" s="173"/>
-      <c r="P46" s="170">
-        <f t="shared" si="4"/>
-        <v>-558950</v>
-      </c>
-      <c r="Q46" s="148">
-        <f t="shared" si="5"/>
-        <v>-0.55894999999999995</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F46" s="118">
+        <v>3</v>
+      </c>
+      <c r="G46" s="196"/>
+      <c r="H46" s="146">
+        <v>174105</v>
+      </c>
+      <c r="I46" s="146">
+        <v>-313641</v>
+      </c>
+      <c r="J46" s="146">
+        <v>307794</v>
+      </c>
+      <c r="K46" s="146">
+        <v>-135130</v>
+      </c>
+      <c r="L46" s="146">
+        <v>290000</v>
+      </c>
+      <c r="M46" s="146">
+        <v>102008</v>
+      </c>
+      <c r="N46" s="146">
+        <v>0</v>
+      </c>
+      <c r="O46" s="146">
+        <v>355800</v>
+      </c>
+      <c r="P46" s="146">
+        <v>-214711</v>
+      </c>
+      <c r="Q46" s="146">
+        <v>235920</v>
+      </c>
+      <c r="R46" s="146"/>
+      <c r="S46" s="173"/>
+      <c r="T46" s="170">
+        <f t="shared" si="6"/>
+        <v>802145</v>
+      </c>
+      <c r="U46" s="148">
+        <f t="shared" si="7"/>
+        <v>2.6738166666666667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="59" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B47" s="62" t="s">
         <v>304</v>
       </c>
       <c r="C47" s="59" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D47" s="140"/>
       <c r="E47" s="140" t="s">
         <v>256</v>
       </c>
-      <c r="F47" s="114"/>
+      <c r="F47" s="114">
+        <v>10</v>
+      </c>
       <c r="G47" s="23"/>
       <c r="H47" s="150">
-        <v>0</v>
+        <v>-214000</v>
       </c>
       <c r="I47" s="150">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="J47" s="150">
-        <v>0</v>
+        <v>338000</v>
       </c>
       <c r="K47" s="150">
-        <v>0</v>
+        <v>63150</v>
       </c>
       <c r="L47" s="150">
-        <v>0</v>
+        <v>-461500</v>
       </c>
       <c r="M47" s="150">
-        <v>0</v>
+        <v>-70400</v>
       </c>
       <c r="N47" s="150">
-        <v>0</v>
-      </c>
-      <c r="O47" s="173"/>
-      <c r="P47" s="170">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="148">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+        <v>-233800</v>
+      </c>
+      <c r="O47" s="150">
+        <v>-479300</v>
+      </c>
+      <c r="P47" s="150">
+        <v>-344800</v>
+      </c>
+      <c r="Q47" s="150">
+        <v>-341300</v>
+      </c>
+      <c r="R47" s="150"/>
+      <c r="S47" s="173"/>
+      <c r="T47" s="170">
+        <f t="shared" si="6"/>
+        <v>-1724350</v>
+      </c>
+      <c r="U47" s="148">
+        <f t="shared" si="7"/>
+        <v>-1.72435</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="s">
         <v>197</v>
       </c>
@@ -9043,17 +9487,27 @@
       <c r="N48" s="150">
         <v>8261</v>
       </c>
-      <c r="O48" s="173"/>
-      <c r="P48" s="170">
-        <f t="shared" si="4"/>
-        <v>48546</v>
-      </c>
-      <c r="Q48" s="148">
-        <f t="shared" si="5"/>
-        <v>0.97092000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O48" s="150">
+        <v>0</v>
+      </c>
+      <c r="P48" s="150">
+        <v>22914</v>
+      </c>
+      <c r="Q48" s="150">
+        <v>-7848</v>
+      </c>
+      <c r="R48" s="150"/>
+      <c r="S48" s="173"/>
+      <c r="T48" s="170">
+        <f t="shared" si="6"/>
+        <v>63612</v>
+      </c>
+      <c r="U48" s="148">
+        <f t="shared" si="7"/>
+        <v>1.27224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>213</v>
       </c>
@@ -9094,17 +9548,27 @@
       <c r="N49" s="150">
         <v>0</v>
       </c>
-      <c r="O49" s="173"/>
-      <c r="P49" s="170">
-        <f t="shared" si="4"/>
-        <v>359896</v>
-      </c>
-      <c r="Q49" s="148">
-        <f t="shared" si="5"/>
-        <v>0.55368615384615383</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O49" s="150">
+        <v>1127</v>
+      </c>
+      <c r="P49" s="150">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="150">
+        <v>57280</v>
+      </c>
+      <c r="R49" s="150"/>
+      <c r="S49" s="173"/>
+      <c r="T49" s="170">
+        <f t="shared" si="6"/>
+        <v>418303</v>
+      </c>
+      <c r="U49" s="148">
+        <f t="shared" si="7"/>
+        <v>0.643543076923077</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="s">
         <v>214</v>
       </c>
@@ -9145,17 +9609,27 @@
       <c r="N50" s="150">
         <v>0</v>
       </c>
-      <c r="O50" s="173"/>
-      <c r="P50" s="170">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="148">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O50" s="150">
+        <v>0</v>
+      </c>
+      <c r="P50" s="150">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="150">
+        <v>0</v>
+      </c>
+      <c r="R50" s="150"/>
+      <c r="S50" s="173"/>
+      <c r="T50" s="170">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="148">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="s">
         <v>49</v>
       </c>
@@ -9196,17 +9670,27 @@
       <c r="N51" s="150">
         <v>-43200</v>
       </c>
-      <c r="O51" s="173"/>
-      <c r="P51" s="170">
-        <f t="shared" si="4"/>
-        <v>114987</v>
-      </c>
-      <c r="Q51" s="148">
-        <f t="shared" si="5"/>
-        <v>0.38329000000000002</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O51" s="150">
+        <v>63560</v>
+      </c>
+      <c r="P51" s="150">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="150">
+        <v>106000</v>
+      </c>
+      <c r="R51" s="150"/>
+      <c r="S51" s="173"/>
+      <c r="T51" s="170">
+        <f t="shared" si="6"/>
+        <v>284547</v>
+      </c>
+      <c r="U51" s="148">
+        <f t="shared" si="7"/>
+        <v>0.94849000000000006</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>331</v>
       </c>
@@ -9247,17 +9731,27 @@
       <c r="N52" s="150">
         <v>1150</v>
       </c>
-      <c r="O52" s="173"/>
-      <c r="P52" s="170">
-        <f t="shared" si="4"/>
-        <v>1200</v>
-      </c>
-      <c r="Q52" s="148">
-        <f t="shared" si="5"/>
-        <v>1.2E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="